--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -621,6 +621,7 @@
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -679,6 +680,9 @@
       <c r="Q1" s="1" t="n">
         <v>20251212</v>
       </c>
+      <c r="R1" s="1" t="n">
+        <v>20251215</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -736,6 +740,9 @@
       <c r="Q2" t="n">
         <v>58</v>
       </c>
+      <c r="R2" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -793,6 +800,9 @@
       <c r="Q3" t="n">
         <v>-9</v>
       </c>
+      <c r="R3" t="n">
+        <v>-26</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -850,6 +860,9 @@
       <c r="Q4" t="n">
         <v>59</v>
       </c>
+      <c r="R4" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -907,6 +920,9 @@
       <c r="Q5" t="n">
         <v>-80</v>
       </c>
+      <c r="R5" t="n">
+        <v>-87</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -964,6 +980,9 @@
       <c r="Q6" t="n">
         <v>-73</v>
       </c>
+      <c r="R6" t="n">
+        <v>-71</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1021,6 +1040,9 @@
       <c r="Q7" t="n">
         <v>-72</v>
       </c>
+      <c r="R7" t="n">
+        <v>-63</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1078,6 +1100,9 @@
       <c r="Q8" t="n">
         <v>19</v>
       </c>
+      <c r="R8" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1135,6 +1160,9 @@
       <c r="Q9" t="n">
         <v>29</v>
       </c>
+      <c r="R9" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1191,6 +1219,9 @@
       </c>
       <c r="Q10" t="n">
         <v>66</v>
+      </c>
+      <c r="R10" t="n">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1204,7 +1235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE10"/>
+  <dimension ref="A1:BF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1264,6 +1295,7 @@
     <col width="12" customWidth="1" min="55" max="55"/>
     <col width="12" customWidth="1" min="56" max="56"/>
     <col width="12" customWidth="1" min="57" max="57"/>
+    <col width="12" customWidth="1" min="58" max="58"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1552,6 +1584,11 @@
           <t>20251212</t>
         </is>
       </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>20251215</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1729,6 +1766,9 @@
       <c r="BE2" t="n">
         <v>101</v>
       </c>
+      <c r="BF2" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1906,6 +1946,9 @@
       <c r="BE3" t="n">
         <v>99</v>
       </c>
+      <c r="BF3" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2083,6 +2126,9 @@
       <c r="BE4" t="n">
         <v>100</v>
       </c>
+      <c r="BF4" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2260,6 +2306,9 @@
       <c r="BE5" t="n">
         <v>98</v>
       </c>
+      <c r="BF5" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2437,6 +2486,9 @@
       <c r="BE6" t="n">
         <v>62</v>
       </c>
+      <c r="BF6" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2614,6 +2666,9 @@
       <c r="BE7" t="n">
         <v>96</v>
       </c>
+      <c r="BF7" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2791,6 +2846,9 @@
       <c r="BE8" t="n">
         <v>107</v>
       </c>
+      <c r="BF8" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2968,6 +3026,9 @@
       <c r="BE9" t="n">
         <v>101</v>
       </c>
+      <c r="BF9" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3144,6 +3205,9 @@
       </c>
       <c r="BE10" t="n">
         <v>107</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -3157,7 +3221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL10"/>
+  <dimension ref="A1:AM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3198,6 +3262,7 @@
     <col width="12" customWidth="1" min="36" max="36"/>
     <col width="12" customWidth="1" min="37" max="37"/>
     <col width="12" customWidth="1" min="38" max="38"/>
+    <col width="12" customWidth="1" min="39" max="39"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3391,6 +3456,11 @@
           <t>20251212</t>
         </is>
       </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>20251215</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3511,6 +3581,9 @@
       <c r="AL2" t="n">
         <v>25.58</v>
       </c>
+      <c r="AM2" t="n">
+        <v>23.17</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3631,6 +3704,9 @@
       <c r="AL3" t="n">
         <v>-50.8</v>
       </c>
+      <c r="AM3" t="n">
+        <v>-49.35</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3751,6 +3827,9 @@
       <c r="AL4" t="n">
         <v>4.98</v>
       </c>
+      <c r="AM4" t="n">
+        <v>-9.609999999999999</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3871,6 +3950,9 @@
       <c r="AL5" t="n">
         <v>-28.3</v>
       </c>
+      <c r="AM5" t="n">
+        <v>-38</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3991,6 +4073,9 @@
       <c r="AL6" t="n">
         <v>-44.45</v>
       </c>
+      <c r="AM6" t="n">
+        <v>-98.42</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4111,6 +4196,9 @@
       <c r="AL7" t="n">
         <v>-48.01</v>
       </c>
+      <c r="AM7" t="n">
+        <v>-51.08</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4231,6 +4319,9 @@
       <c r="AL8" t="n">
         <v>-16.59</v>
       </c>
+      <c r="AM8" t="n">
+        <v>-14.25</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4351,6 +4442,9 @@
       <c r="AL9" t="n">
         <v>-25.26</v>
       </c>
+      <c r="AM9" t="n">
+        <v>-23.15</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4470,6 +4564,9 @@
       </c>
       <c r="AL10" t="n">
         <v>1.54</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>7.94</v>
       </c>
     </row>
   </sheetData>
@@ -4483,7 +4580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4503,6 +4600,7 @@
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4591,6 +4689,11 @@
           <t>20251212</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>20251215</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4648,6 +4751,9 @@
       <c r="Q2" t="n">
         <v>40</v>
       </c>
+      <c r="R2" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4705,6 +4811,9 @@
       <c r="Q3" t="n">
         <v>37</v>
       </c>
+      <c r="R3" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4762,6 +4871,9 @@
       <c r="Q4" t="n">
         <v>49</v>
       </c>
+      <c r="R4" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4819,6 +4931,9 @@
       <c r="Q5" t="n">
         <v>47</v>
       </c>
+      <c r="R5" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4876,6 +4991,9 @@
       <c r="Q6" t="n">
         <v>135</v>
       </c>
+      <c r="R6" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4933,6 +5051,9 @@
       <c r="Q7" t="n">
         <v>53</v>
       </c>
+      <c r="R7" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4990,6 +5111,9 @@
       <c r="Q8" t="n">
         <v>41</v>
       </c>
+      <c r="R8" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5047,6 +5171,9 @@
       <c r="Q9" t="n">
         <v>46</v>
       </c>
+      <c r="R9" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5103,6 +5230,9 @@
       </c>
       <c r="Q10" t="n">
         <v>57</v>
+      </c>
+      <c r="R10" t="n">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -5116,7 +5246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX10"/>
+  <dimension ref="A1:BY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5195,6 +5325,7 @@
     <col width="12" customWidth="1" min="74" max="74"/>
     <col width="12" customWidth="1" min="75" max="75"/>
     <col width="12" customWidth="1" min="76" max="76"/>
+    <col width="12" customWidth="1" min="77" max="77"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5430,6 +5561,9 @@
       <c r="BX1" s="1" t="n">
         <v>20251212</v>
       </c>
+      <c r="BY1" s="1" t="n">
+        <v>20251215</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5664,6 +5798,9 @@
       <c r="BX2" t="n">
         <v>277.9</v>
       </c>
+      <c r="BY2" t="n">
+        <v>280.15</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5898,6 +6035,9 @@
       <c r="BX3" t="n">
         <v>229.87</v>
       </c>
+      <c r="BY3" t="n">
+        <v>227.93</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6132,6 +6272,9 @@
       <c r="BX4" t="n">
         <v>313.7</v>
       </c>
+      <c r="BY4" t="n">
+        <v>311.315</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6366,6 +6509,9 @@
       <c r="BX5" t="n">
         <v>479.82</v>
       </c>
+      <c r="BY5" t="n">
+        <v>480.1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6600,6 +6746,9 @@
       <c r="BX6" t="n">
         <v>95.5</v>
       </c>
+      <c r="BY6" t="n">
+        <v>96.015</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6834,6 +6983,9 @@
       <c r="BX7" t="n">
         <v>181.11</v>
       </c>
+      <c r="BY7" t="n">
+        <v>177.936</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7068,6 +7220,9 @@
       <c r="BX8" t="n">
         <v>185.81</v>
       </c>
+      <c r="BY8" t="n">
+        <v>185.08</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7302,6 +7457,9 @@
       <c r="BX9" t="n">
         <v>85.11</v>
       </c>
+      <c r="BY9" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7535,6 +7693,9 @@
       </c>
       <c r="BX10" t="n">
         <v>448.09</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>469.44</v>
       </c>
     </row>
   </sheetData>
@@ -7548,7 +7709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX10"/>
+  <dimension ref="A1:BY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7627,6 +7788,7 @@
     <col width="12" customWidth="1" min="74" max="74"/>
     <col width="12" customWidth="1" min="75" max="75"/>
     <col width="12" customWidth="1" min="76" max="76"/>
+    <col width="12" customWidth="1" min="77" max="77"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7862,6 +8024,9 @@
       <c r="BX1" s="1" t="n">
         <v>20251212</v>
       </c>
+      <c r="BY1" s="1" t="n">
+        <v>20251215</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8096,6 +8261,9 @@
       <c r="BX2" t="n">
         <v>279.22</v>
       </c>
+      <c r="BY2" t="n">
+        <v>280.15</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8330,6 +8498,9 @@
       <c r="BX3" t="n">
         <v>230.08</v>
       </c>
+      <c r="BY3" t="n">
+        <v>227.93</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8564,6 +8735,9 @@
       <c r="BX4" t="n">
         <v>314.87</v>
       </c>
+      <c r="BY4" t="n">
+        <v>311.42</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8798,6 +8972,9 @@
       <c r="BX5" t="n">
         <v>482.45</v>
       </c>
+      <c r="BY5" t="n">
+        <v>480.7205</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9032,6 +9209,9 @@
       <c r="BX6" t="n">
         <v>96.92</v>
       </c>
+      <c r="BY6" t="n">
+        <v>96.37</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9266,6 +9446,9 @@
       <c r="BX7" t="n">
         <v>182.82</v>
       </c>
+      <c r="BY7" t="n">
+        <v>178.415</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9500,6 +9683,9 @@
       <c r="BX8" t="n">
         <v>186.525</v>
       </c>
+      <c r="BY8" t="n">
+        <v>187.78</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9734,6 +9920,9 @@
       <c r="BX9" t="n">
         <v>85.925</v>
       </c>
+      <c r="BY9" t="n">
+        <v>87.56</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9967,6 +10156,9 @@
       </c>
       <c r="BX10" t="n">
         <v>463.01</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>481.7694</v>
       </c>
     </row>
   </sheetData>
@@ -9980,7 +10172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX10"/>
+  <dimension ref="A1:BY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10059,6 +10251,7 @@
     <col width="12" customWidth="1" min="74" max="74"/>
     <col width="12" customWidth="1" min="75" max="75"/>
     <col width="12" customWidth="1" min="76" max="76"/>
+    <col width="12" customWidth="1" min="77" max="77"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10294,6 +10487,9 @@
       <c r="BX1" s="1" t="n">
         <v>20251212</v>
       </c>
+      <c r="BY1" s="1" t="n">
+        <v>20251215</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10528,6 +10724,9 @@
       <c r="BX2" t="n">
         <v>276.82</v>
       </c>
+      <c r="BY2" t="n">
+        <v>272.84</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10762,6 +10961,9 @@
       <c r="BX3" t="n">
         <v>225.12</v>
       </c>
+      <c r="BY3" t="n">
+        <v>221.5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10996,6 +11198,9 @@
       <c r="BX4" t="n">
         <v>305.56</v>
       </c>
+      <c r="BY4" t="n">
+        <v>304.88</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11230,6 +11435,9 @@
       <c r="BX5" t="n">
         <v>476.34</v>
       </c>
+      <c r="BY5" t="n">
+        <v>472.52</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11464,6 +11672,9 @@
       <c r="BX6" t="n">
         <v>94.65000000000001</v>
       </c>
+      <c r="BY6" t="n">
+        <v>93.53</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11698,6 +11909,9 @@
       <c r="BX7" t="n">
         <v>174.62</v>
       </c>
+      <c r="BY7" t="n">
+        <v>175.03</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11932,6 +12146,9 @@
       <c r="BX8" t="n">
         <v>177.6668</v>
       </c>
+      <c r="BY8" t="n">
+        <v>180.03</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12166,6 +12383,9 @@
       <c r="BX9" t="n">
         <v>84.86</v>
       </c>
+      <c r="BY9" t="n">
+        <v>84.66</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12399,6 +12619,9 @@
       </c>
       <c r="BX10" t="n">
         <v>441.67</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>467.66</v>
       </c>
     </row>
   </sheetData>
@@ -12412,7 +12635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX10"/>
+  <dimension ref="A1:BY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12491,6 +12714,7 @@
     <col width="12" customWidth="1" min="74" max="74"/>
     <col width="12" customWidth="1" min="75" max="75"/>
     <col width="12" customWidth="1" min="76" max="76"/>
+    <col width="12" customWidth="1" min="77" max="77"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12726,6 +12950,9 @@
       <c r="BX1" s="1" t="n">
         <v>20251212</v>
       </c>
+      <c r="BY1" s="1" t="n">
+        <v>20251215</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12960,6 +13187,9 @@
       <c r="BX2" t="n">
         <v>278.28</v>
       </c>
+      <c r="BY2" t="n">
+        <v>274.11</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13194,6 +13424,9 @@
       <c r="BX3" t="n">
         <v>226.19</v>
       </c>
+      <c r="BY3" t="n">
+        <v>222.54</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13428,6 +13661,9 @@
       <c r="BX4" t="n">
         <v>309.29</v>
       </c>
+      <c r="BY4" t="n">
+        <v>308.22</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13662,6 +13898,9 @@
       <c r="BX5" t="n">
         <v>478.53</v>
       </c>
+      <c r="BY5" t="n">
+        <v>474.82</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13896,6 +14135,9 @@
       <c r="BX6" t="n">
         <v>95.19</v>
       </c>
+      <c r="BY6" t="n">
+        <v>93.77</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14130,6 +14372,9 @@
       <c r="BX7" t="n">
         <v>175.02</v>
       </c>
+      <c r="BY7" t="n">
+        <v>176.29</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14364,6 +14609,9 @@
       <c r="BX8" t="n">
         <v>183.57</v>
       </c>
+      <c r="BY8" t="n">
+        <v>183.25</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14598,6 +14846,9 @@
       <c r="BX9" t="n">
         <v>85.34999999999999</v>
       </c>
+      <c r="BY9" t="n">
+        <v>85.40000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14831,6 +15082,9 @@
       </c>
       <c r="BX10" t="n">
         <v>458.96</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>475.31</v>
       </c>
     </row>
   </sheetData>
@@ -14844,7 +15098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX10"/>
+  <dimension ref="A1:BY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14923,6 +15177,7 @@
     <col width="12" customWidth="1" min="74" max="74"/>
     <col width="12" customWidth="1" min="75" max="75"/>
     <col width="12" customWidth="1" min="76" max="76"/>
+    <col width="12" customWidth="1" min="77" max="77"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15158,6 +15413,9 @@
       <c r="BX1" s="1" t="n">
         <v>20251212</v>
       </c>
+      <c r="BY1" s="1" t="n">
+        <v>20251215</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15392,6 +15650,9 @@
       <c r="BX2" t="n">
         <v>39532887</v>
       </c>
+      <c r="BY2" t="n">
+        <v>50409078</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15626,6 +15887,9 @@
       <c r="BX3" t="n">
         <v>35639118</v>
       </c>
+      <c r="BY3" t="n">
+        <v>47286085</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15860,6 +16124,9 @@
       <c r="BX4" t="n">
         <v>35940170</v>
       </c>
+      <c r="BY4" t="n">
+        <v>29151889</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16094,6 +16361,9 @@
       <c r="BX5" t="n">
         <v>21248102</v>
       </c>
+      <c r="BY5" t="n">
+        <v>23727694</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16328,6 +16598,9 @@
       <c r="BX6" t="n">
         <v>49323122</v>
       </c>
+      <c r="BY6" t="n">
+        <v>40016455</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16562,6 +16835,9 @@
       <c r="BX7" t="n">
         <v>204274918</v>
       </c>
+      <c r="BY7" t="n">
+        <v>164775636</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16796,6 +17072,9 @@
       <c r="BX8" t="n">
         <v>42427356</v>
       </c>
+      <c r="BY8" t="n">
+        <v>32796052</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17030,6 +17309,9 @@
       <c r="BX9" t="n">
         <v>9071499</v>
       </c>
+      <c r="BY9" t="n">
+        <v>11718593</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17263,6 +17545,9 @@
       </c>
       <c r="BX10" t="n">
         <v>95656749</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>114542204</v>
       </c>
     </row>
   </sheetData>
@@ -17276,7 +17561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE10"/>
+  <dimension ref="A1:BF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17336,6 +17621,7 @@
     <col width="10" customWidth="1" min="55" max="55"/>
     <col width="10" customWidth="1" min="56" max="56"/>
     <col width="10" customWidth="1" min="57" max="57"/>
+    <col width="10" customWidth="1" min="58" max="58"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17514,6 +17800,9 @@
       <c r="BE1" s="1" t="n">
         <v>20251212</v>
       </c>
+      <c r="BF1" s="1" t="n">
+        <v>20251215</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17691,6 +17980,9 @@
       <c r="BE2" t="n">
         <v>60</v>
       </c>
+      <c r="BF2" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17868,6 +18160,9 @@
       <c r="BE3" t="n">
         <v>52</v>
       </c>
+      <c r="BF3" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18045,6 +18340,9 @@
       <c r="BE4" t="n">
         <v>70</v>
       </c>
+      <c r="BF4" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18222,6 +18520,9 @@
       <c r="BE5" t="n">
         <v>17</v>
       </c>
+      <c r="BF5" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18399,6 +18700,9 @@
       <c r="BE6" t="n">
         <v>0</v>
       </c>
+      <c r="BF6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18576,6 +18880,9 @@
       <c r="BE7" t="n">
         <v>0</v>
       </c>
+      <c r="BF7" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18753,6 +19060,9 @@
       <c r="BE8" t="n">
         <v>87</v>
       </c>
+      <c r="BF8" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18930,6 +19240,9 @@
       <c r="BE9" t="n">
         <v>64</v>
       </c>
+      <c r="BF9" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -19105,6 +19418,9 @@
         <v>87</v>
       </c>
       <c r="BE10" t="n">
+        <v>100</v>
+      </c>
+      <c r="BF10" t="n">
         <v>100</v>
       </c>
     </row>
@@ -19119,7 +19435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -19139,6 +19455,7 @@
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19197,6 +19514,9 @@
       <c r="Q1" s="1" t="n">
         <v>20251212</v>
       </c>
+      <c r="R1" s="1" t="n">
+        <v>20251215</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19254,6 +19574,9 @@
       <c r="Q2" t="n">
         <v>81</v>
       </c>
+      <c r="R2" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19311,6 +19634,9 @@
       <c r="Q3" t="n">
         <v>32</v>
       </c>
+      <c r="R3" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19368,6 +19694,9 @@
       <c r="Q4" t="n">
         <v>84</v>
       </c>
+      <c r="R4" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19425,6 +19754,9 @@
       <c r="Q5" t="n">
         <v>9</v>
       </c>
+      <c r="R5" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19482,6 +19814,9 @@
       <c r="Q6" t="n">
         <v>0</v>
       </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19539,6 +19874,9 @@
       <c r="Q7" t="n">
         <v>0</v>
       </c>
+      <c r="R7" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19596,6 +19934,9 @@
       <c r="Q8" t="n">
         <v>55</v>
       </c>
+      <c r="R8" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19653,6 +19994,9 @@
       <c r="Q9" t="n">
         <v>78</v>
       </c>
+      <c r="R9" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -19709,6 +20053,9 @@
       </c>
       <c r="Q10" t="n">
         <v>88</v>
+      </c>
+      <c r="R10" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -19722,7 +20069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE10"/>
+  <dimension ref="A1:BF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -19782,6 +20129,7 @@
     <col width="10" customWidth="1" min="55" max="55"/>
     <col width="10" customWidth="1" min="56" max="56"/>
     <col width="10" customWidth="1" min="57" max="57"/>
+    <col width="10" customWidth="1" min="58" max="58"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19960,6 +20308,9 @@
       <c r="BE1" s="1" t="n">
         <v>20251212</v>
       </c>
+      <c r="BF1" s="1" t="n">
+        <v>20251215</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20137,6 +20488,9 @@
       <c r="BE2" t="n">
         <v>17</v>
       </c>
+      <c r="BF2" t="n">
+        <v>-20</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20314,6 +20668,9 @@
       <c r="BE3" t="n">
         <v>-24</v>
       </c>
+      <c r="BF3" t="n">
+        <v>-56</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20491,6 +20848,9 @@
       <c r="BE4" t="n">
         <v>2</v>
       </c>
+      <c r="BF4" t="n">
+        <v>-8</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20668,6 +21028,9 @@
       <c r="BE5" t="n">
         <v>-37</v>
       </c>
+      <c r="BF5" t="n">
+        <v>-55</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20845,6 +21208,9 @@
       <c r="BE6" t="n">
         <v>-13</v>
       </c>
+      <c r="BF6" t="n">
+        <v>-74</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21022,6 +21388,9 @@
       <c r="BE7" t="n">
         <v>-95</v>
       </c>
+      <c r="BF7" t="n">
+        <v>-75</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21199,6 +21568,9 @@
       <c r="BE8" t="n">
         <v>58</v>
       </c>
+      <c r="BF8" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21376,6 +21748,9 @@
       <c r="BE9" t="n">
         <v>24</v>
       </c>
+      <c r="BF9" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21552,6 +21927,9 @@
       </c>
       <c r="BE10" t="n">
         <v>72</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -622,6 +622,7 @@
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -683,6 +684,9 @@
       <c r="R1" s="1" t="n">
         <v>20251215</v>
       </c>
+      <c r="S1" s="1" t="n">
+        <v>20251216</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -743,6 +747,9 @@
       <c r="R2" t="n">
         <v>38</v>
       </c>
+      <c r="S2" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -803,6 +810,9 @@
       <c r="R3" t="n">
         <v>-26</v>
       </c>
+      <c r="S3" t="n">
+        <v>-26</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -863,6 +873,9 @@
       <c r="R4" t="n">
         <v>55</v>
       </c>
+      <c r="S4" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -923,6 +936,9 @@
       <c r="R5" t="n">
         <v>-87</v>
       </c>
+      <c r="S5" t="n">
+        <v>-79</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -983,6 +999,9 @@
       <c r="R6" t="n">
         <v>-71</v>
       </c>
+      <c r="S6" t="n">
+        <v>-68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1043,6 +1062,9 @@
       <c r="R7" t="n">
         <v>-63</v>
       </c>
+      <c r="S7" t="n">
+        <v>-53</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1103,6 +1125,9 @@
       <c r="R8" t="n">
         <v>17</v>
       </c>
+      <c r="S8" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1163,6 +1188,9 @@
       <c r="R9" t="n">
         <v>30</v>
       </c>
+      <c r="S9" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1222,6 +1250,9 @@
       </c>
       <c r="R10" t="n">
         <v>107</v>
+      </c>
+      <c r="S10" t="n">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -1235,7 +1266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF10"/>
+  <dimension ref="A1:BG10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1296,6 +1327,7 @@
     <col width="12" customWidth="1" min="56" max="56"/>
     <col width="12" customWidth="1" min="57" max="57"/>
     <col width="12" customWidth="1" min="58" max="58"/>
+    <col width="12" customWidth="1" min="59" max="59"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1589,6 +1621,11 @@
           <t>20251215</t>
         </is>
       </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>20251216</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1769,6 +1806,9 @@
       <c r="BF2" t="n">
         <v>99</v>
       </c>
+      <c r="BG2" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1949,6 +1989,9 @@
       <c r="BF3" t="n">
         <v>98</v>
       </c>
+      <c r="BG3" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2129,6 +2172,9 @@
       <c r="BF4" t="n">
         <v>99</v>
       </c>
+      <c r="BG4" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2309,6 +2355,9 @@
       <c r="BF5" t="n">
         <v>98</v>
       </c>
+      <c r="BG5" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2489,6 +2538,9 @@
       <c r="BF6" t="n">
         <v>91</v>
       </c>
+      <c r="BG6" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2669,6 +2721,9 @@
       <c r="BF7" t="n">
         <v>97</v>
       </c>
+      <c r="BG7" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2849,6 +2904,9 @@
       <c r="BF8" t="n">
         <v>106</v>
       </c>
+      <c r="BG8" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3029,6 +3087,9 @@
       <c r="BF9" t="n">
         <v>101</v>
       </c>
+      <c r="BG9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3208,6 +3269,9 @@
       </c>
       <c r="BF10" t="n">
         <v>110</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -3221,7 +3285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM10"/>
+  <dimension ref="A1:AN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3263,6 +3327,7 @@
     <col width="12" customWidth="1" min="37" max="37"/>
     <col width="12" customWidth="1" min="38" max="38"/>
     <col width="12" customWidth="1" min="39" max="39"/>
+    <col width="12" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3461,6 +3526,11 @@
           <t>20251215</t>
         </is>
       </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>20251216</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3584,6 +3654,9 @@
       <c r="AM2" t="n">
         <v>23.17</v>
       </c>
+      <c r="AN2" t="n">
+        <v>13.79</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3707,6 +3780,9 @@
       <c r="AM3" t="n">
         <v>-49.35</v>
       </c>
+      <c r="AN3" t="n">
+        <v>-47.52</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3830,6 +3906,9 @@
       <c r="AM4" t="n">
         <v>-9.609999999999999</v>
       </c>
+      <c r="AN4" t="n">
+        <v>-19.22</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3953,6 +4032,9 @@
       <c r="AM5" t="n">
         <v>-38</v>
       </c>
+      <c r="AN5" t="n">
+        <v>-50.08</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4076,6 +4158,9 @@
       <c r="AM6" t="n">
         <v>-98.42</v>
       </c>
+      <c r="AN6" t="n">
+        <v>-98.36</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4199,6 +4284,9 @@
       <c r="AM7" t="n">
         <v>-51.08</v>
       </c>
+      <c r="AN7" t="n">
+        <v>-51.67</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4322,6 +4410,9 @@
       <c r="AM8" t="n">
         <v>-14.25</v>
       </c>
+      <c r="AN8" t="n">
+        <v>-9.93</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4445,6 +4536,9 @@
       <c r="AM9" t="n">
         <v>-23.15</v>
       </c>
+      <c r="AN9" t="n">
+        <v>-22.47</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4567,6 +4661,9 @@
       </c>
       <c r="AM10" t="n">
         <v>7.94</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>18.65</v>
       </c>
     </row>
   </sheetData>
@@ -4580,7 +4677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4601,6 +4698,7 @@
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4694,6 +4792,11 @@
           <t>20251215</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>20251216</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4754,6 +4857,9 @@
       <c r="R2" t="n">
         <v>54</v>
       </c>
+      <c r="S2" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4814,6 +4920,9 @@
       <c r="R3" t="n">
         <v>49</v>
       </c>
+      <c r="S3" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4874,6 +4983,9 @@
       <c r="R4" t="n">
         <v>40</v>
       </c>
+      <c r="S4" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4934,6 +5046,9 @@
       <c r="R5" t="n">
         <v>53</v>
       </c>
+      <c r="S5" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4994,6 +5109,9 @@
       <c r="R6" t="n">
         <v>106</v>
       </c>
+      <c r="S6" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5054,6 +5172,9 @@
       <c r="R7" t="n">
         <v>43</v>
       </c>
+      <c r="S7" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5114,6 +5235,9 @@
       <c r="R8" t="n">
         <v>33</v>
       </c>
+      <c r="S8" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5174,6 +5298,9 @@
       <c r="R9" t="n">
         <v>59</v>
       </c>
+      <c r="S9" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5233,6 +5360,9 @@
       </c>
       <c r="R10" t="n">
         <v>68</v>
+      </c>
+      <c r="S10" t="n">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -5246,7 +5376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY10"/>
+  <dimension ref="A1:BZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5326,6 +5456,7 @@
     <col width="12" customWidth="1" min="75" max="75"/>
     <col width="12" customWidth="1" min="76" max="76"/>
     <col width="12" customWidth="1" min="77" max="77"/>
+    <col width="12" customWidth="1" min="78" max="78"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5564,6 +5695,9 @@
       <c r="BY1" s="1" t="n">
         <v>20251215</v>
       </c>
+      <c r="BZ1" s="1" t="n">
+        <v>20251216</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5801,6 +5935,9 @@
       <c r="BY2" t="n">
         <v>280.15</v>
       </c>
+      <c r="BZ2" t="n">
+        <v>272.82</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6038,6 +6175,9 @@
       <c r="BY3" t="n">
         <v>227.93</v>
       </c>
+      <c r="BZ3" t="n">
+        <v>223.035</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6275,6 +6415,9 @@
       <c r="BY4" t="n">
         <v>311.315</v>
       </c>
+      <c r="BZ4" t="n">
+        <v>304.945</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6512,6 +6655,9 @@
       <c r="BY5" t="n">
         <v>480.1</v>
       </c>
+      <c r="BZ5" t="n">
+        <v>471.905</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6749,6 +6895,9 @@
       <c r="BY6" t="n">
         <v>96.015</v>
       </c>
+      <c r="BZ6" t="n">
+        <v>93.88</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6986,6 +7135,9 @@
       <c r="BY7" t="n">
         <v>177.936</v>
       </c>
+      <c r="BZ7" t="n">
+        <v>176.26</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7223,6 +7375,9 @@
       <c r="BY8" t="n">
         <v>185.08</v>
       </c>
+      <c r="BZ8" t="n">
+        <v>181.655</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7460,6 +7615,9 @@
       <c r="BY9" t="n">
         <v>86</v>
       </c>
+      <c r="BZ9" t="n">
+        <v>85.64</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7696,6 +7854,9 @@
       </c>
       <c r="BY10" t="n">
         <v>469.44</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>472.21</v>
       </c>
     </row>
   </sheetData>
@@ -7709,7 +7870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY10"/>
+  <dimension ref="A1:BZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7789,6 +7950,7 @@
     <col width="12" customWidth="1" min="75" max="75"/>
     <col width="12" customWidth="1" min="76" max="76"/>
     <col width="12" customWidth="1" min="77" max="77"/>
+    <col width="12" customWidth="1" min="78" max="78"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8027,6 +8189,9 @@
       <c r="BY1" s="1" t="n">
         <v>20251215</v>
       </c>
+      <c r="BZ1" s="1" t="n">
+        <v>20251216</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8264,6 +8429,9 @@
       <c r="BY2" t="n">
         <v>280.15</v>
       </c>
+      <c r="BZ2" t="n">
+        <v>275.5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8501,6 +8669,9 @@
       <c r="BY3" t="n">
         <v>227.93</v>
       </c>
+      <c r="BZ3" t="n">
+        <v>223.66</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8738,6 +8909,9 @@
       <c r="BY4" t="n">
         <v>311.42</v>
       </c>
+      <c r="BZ4" t="n">
+        <v>310.77</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8975,6 +9149,9 @@
       <c r="BY5" t="n">
         <v>480.7205</v>
       </c>
+      <c r="BZ5" t="n">
+        <v>477.89</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9212,6 +9389,9 @@
       <c r="BY6" t="n">
         <v>96.37</v>
       </c>
+      <c r="BZ6" t="n">
+        <v>94.93000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9449,6 +9629,9 @@
       <c r="BY7" t="n">
         <v>178.415</v>
       </c>
+      <c r="BZ7" t="n">
+        <v>178.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9686,6 +9869,9 @@
       <c r="BY8" t="n">
         <v>187.78</v>
       </c>
+      <c r="BZ8" t="n">
+        <v>188.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9923,6 +10109,9 @@
       <c r="BY9" t="n">
         <v>87.56</v>
       </c>
+      <c r="BZ9" t="n">
+        <v>86.54000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10159,6 +10348,9 @@
       </c>
       <c r="BY10" t="n">
         <v>481.7694</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>491.5</v>
       </c>
     </row>
   </sheetData>
@@ -10172,7 +10364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY10"/>
+  <dimension ref="A1:BZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10252,6 +10444,7 @@
     <col width="12" customWidth="1" min="75" max="75"/>
     <col width="12" customWidth="1" min="76" max="76"/>
     <col width="12" customWidth="1" min="77" max="77"/>
+    <col width="12" customWidth="1" min="78" max="78"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10490,6 +10683,9 @@
       <c r="BY1" s="1" t="n">
         <v>20251215</v>
       </c>
+      <c r="BZ1" s="1" t="n">
+        <v>20251216</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10727,6 +10923,9 @@
       <c r="BY2" t="n">
         <v>272.84</v>
       </c>
+      <c r="BZ2" t="n">
+        <v>271.79</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10964,6 +11163,9 @@
       <c r="BY3" t="n">
         <v>221.5</v>
       </c>
+      <c r="BZ3" t="n">
+        <v>221.1304</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11201,6 +11403,9 @@
       <c r="BY4" t="n">
         <v>304.88</v>
       </c>
+      <c r="BZ4" t="n">
+        <v>302.59</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11438,6 +11643,9 @@
       <c r="BY5" t="n">
         <v>472.52</v>
       </c>
+      <c r="BZ5" t="n">
+        <v>470.88</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11675,6 +11883,9 @@
       <c r="BY6" t="n">
         <v>93.53</v>
       </c>
+      <c r="BZ6" t="n">
+        <v>93.31999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11912,6 +12123,9 @@
       <c r="BY7" t="n">
         <v>175.03</v>
       </c>
+      <c r="BZ7" t="n">
+        <v>174.9</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12149,6 +12363,9 @@
       <c r="BY8" t="n">
         <v>180.03</v>
       </c>
+      <c r="BZ8" t="n">
+        <v>181.1424</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12386,6 +12603,9 @@
       <c r="BY9" t="n">
         <v>84.66</v>
       </c>
+      <c r="BZ9" t="n">
+        <v>84.72</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12622,6 +12842,9 @@
       </c>
       <c r="BY10" t="n">
         <v>467.66</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>465.83</v>
       </c>
     </row>
   </sheetData>
@@ -12635,7 +12858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY10"/>
+  <dimension ref="A1:BZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12715,6 +12938,7 @@
     <col width="12" customWidth="1" min="75" max="75"/>
     <col width="12" customWidth="1" min="76" max="76"/>
     <col width="12" customWidth="1" min="77" max="77"/>
+    <col width="12" customWidth="1" min="78" max="78"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12953,6 +13177,9 @@
       <c r="BY1" s="1" t="n">
         <v>20251215</v>
       </c>
+      <c r="BZ1" s="1" t="n">
+        <v>20251216</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13190,6 +13417,9 @@
       <c r="BY2" t="n">
         <v>274.11</v>
       </c>
+      <c r="BZ2" t="n">
+        <v>274.61</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13427,6 +13657,9 @@
       <c r="BY3" t="n">
         <v>222.54</v>
       </c>
+      <c r="BZ3" t="n">
+        <v>222.56</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13664,6 +13897,9 @@
       <c r="BY4" t="n">
         <v>308.22</v>
       </c>
+      <c r="BZ4" t="n">
+        <v>306.57</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13901,6 +14137,9 @@
       <c r="BY5" t="n">
         <v>474.82</v>
       </c>
+      <c r="BZ5" t="n">
+        <v>476.39</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14138,6 +14377,9 @@
       <c r="BY6" t="n">
         <v>93.77</v>
       </c>
+      <c r="BZ6" t="n">
+        <v>94.56999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14375,6 +14617,9 @@
       <c r="BY7" t="n">
         <v>176.29</v>
       </c>
+      <c r="BZ7" t="n">
+        <v>177.72</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14612,6 +14857,9 @@
       <c r="BY8" t="n">
         <v>183.25</v>
       </c>
+      <c r="BZ8" t="n">
+        <v>187.75</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14849,6 +15097,9 @@
       <c r="BY9" t="n">
         <v>85.40000000000001</v>
       </c>
+      <c r="BZ9" t="n">
+        <v>85.08</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15085,6 +15336,9 @@
       </c>
       <c r="BY10" t="n">
         <v>475.31</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>489.88</v>
       </c>
     </row>
   </sheetData>
@@ -15098,7 +15352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY10"/>
+  <dimension ref="A1:BZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15178,6 +15432,7 @@
     <col width="12" customWidth="1" min="75" max="75"/>
     <col width="12" customWidth="1" min="76" max="76"/>
     <col width="12" customWidth="1" min="77" max="77"/>
+    <col width="12" customWidth="1" min="78" max="78"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15416,6 +15671,9 @@
       <c r="BY1" s="1" t="n">
         <v>20251215</v>
       </c>
+      <c r="BZ1" s="1" t="n">
+        <v>20251216</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15653,6 +15911,9 @@
       <c r="BY2" t="n">
         <v>50409078</v>
       </c>
+      <c r="BZ2" t="n">
+        <v>37648628</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15890,6 +16151,9 @@
       <c r="BY3" t="n">
         <v>47286085</v>
       </c>
+      <c r="BZ3" t="n">
+        <v>39298857</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16127,6 +16391,9 @@
       <c r="BY4" t="n">
         <v>29151889</v>
       </c>
+      <c r="BZ4" t="n">
+        <v>30585020</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16364,6 +16631,9 @@
       <c r="BY5" t="n">
         <v>23727694</v>
       </c>
+      <c r="BZ5" t="n">
+        <v>20705560</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16601,6 +16871,9 @@
       <c r="BY6" t="n">
         <v>40016455</v>
       </c>
+      <c r="BZ6" t="n">
+        <v>34264989</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16838,6 +17111,9 @@
       <c r="BY7" t="n">
         <v>164775636</v>
       </c>
+      <c r="BZ7" t="n">
+        <v>148588098</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17075,6 +17351,9 @@
       <c r="BY8" t="n">
         <v>32796052</v>
       </c>
+      <c r="BZ8" t="n">
+        <v>42070267</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17312,6 +17591,9 @@
       <c r="BY9" t="n">
         <v>11718593</v>
       </c>
+      <c r="BZ9" t="n">
+        <v>7481392</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17548,6 +17830,9 @@
       </c>
       <c r="BY10" t="n">
         <v>114542204</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>107608075</v>
       </c>
     </row>
   </sheetData>
@@ -17561,7 +17846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF10"/>
+  <dimension ref="A1:BG10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17622,6 +17907,7 @@
     <col width="10" customWidth="1" min="56" max="56"/>
     <col width="10" customWidth="1" min="57" max="57"/>
     <col width="10" customWidth="1" min="58" max="58"/>
+    <col width="10" customWidth="1" min="59" max="59"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17803,6 +18089,9 @@
       <c r="BF1" s="1" t="n">
         <v>20251215</v>
       </c>
+      <c r="BG1" s="1" t="n">
+        <v>20251216</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17983,6 +18272,9 @@
       <c r="BF2" t="n">
         <v>39</v>
       </c>
+      <c r="BG2" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18163,6 +18455,9 @@
       <c r="BF3" t="n">
         <v>31</v>
       </c>
+      <c r="BG3" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18343,6 +18638,9 @@
       <c r="BF4" t="n">
         <v>61</v>
       </c>
+      <c r="BG4" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18523,6 +18821,9 @@
       <c r="BF5" t="n">
         <v>8</v>
       </c>
+      <c r="BG5" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18703,6 +19004,9 @@
       <c r="BF6" t="n">
         <v>5</v>
       </c>
+      <c r="BG6" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18883,6 +19187,9 @@
       <c r="BF7" t="n">
         <v>11</v>
       </c>
+      <c r="BG7" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19063,6 +19370,9 @@
       <c r="BF8" t="n">
         <v>86</v>
       </c>
+      <c r="BG8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19243,6 +19553,9 @@
       <c r="BF9" t="n">
         <v>65</v>
       </c>
+      <c r="BG9" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -19421,6 +19734,9 @@
         <v>100</v>
       </c>
       <c r="BF10" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG10" t="n">
         <v>100</v>
       </c>
     </row>
@@ -19435,7 +19751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -19456,6 +19772,7 @@
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19517,6 +19834,9 @@
       <c r="R1" s="1" t="n">
         <v>20251215</v>
       </c>
+      <c r="S1" s="1" t="n">
+        <v>20251216</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19577,6 +19897,9 @@
       <c r="R2" t="n">
         <v>70</v>
       </c>
+      <c r="S2" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19637,6 +19960,9 @@
       <c r="R3" t="n">
         <v>23</v>
       </c>
+      <c r="S3" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19697,6 +20023,9 @@
       <c r="R4" t="n">
         <v>82</v>
       </c>
+      <c r="S4" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19757,6 +20086,9 @@
       <c r="R5" t="n">
         <v>4</v>
       </c>
+      <c r="S5" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19817,6 +20149,9 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19877,6 +20212,9 @@
       <c r="R7" t="n">
         <v>4</v>
       </c>
+      <c r="S7" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19937,6 +20275,9 @@
       <c r="R8" t="n">
         <v>54</v>
       </c>
+      <c r="S8" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19997,6 +20338,9 @@
       <c r="R9" t="n">
         <v>79</v>
       </c>
+      <c r="S9" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20055,6 +20399,9 @@
         <v>88</v>
       </c>
       <c r="R10" t="n">
+        <v>100</v>
+      </c>
+      <c r="S10" t="n">
         <v>100</v>
       </c>
     </row>
@@ -20069,7 +20416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF10"/>
+  <dimension ref="A1:BG10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20130,6 +20477,7 @@
     <col width="10" customWidth="1" min="56" max="56"/>
     <col width="10" customWidth="1" min="57" max="57"/>
     <col width="10" customWidth="1" min="58" max="58"/>
+    <col width="10" customWidth="1" min="59" max="59"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20311,6 +20659,9 @@
       <c r="BF1" s="1" t="n">
         <v>20251215</v>
       </c>
+      <c r="BG1" s="1" t="n">
+        <v>20251216</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20491,6 +20842,9 @@
       <c r="BF2" t="n">
         <v>-20</v>
       </c>
+      <c r="BG2" t="n">
+        <v>-20</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20671,6 +21025,9 @@
       <c r="BF3" t="n">
         <v>-56</v>
       </c>
+      <c r="BG3" t="n">
+        <v>-51</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20851,6 +21208,9 @@
       <c r="BF4" t="n">
         <v>-8</v>
       </c>
+      <c r="BG4" t="n">
+        <v>-21</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -21031,6 +21391,9 @@
       <c r="BF5" t="n">
         <v>-55</v>
       </c>
+      <c r="BG5" t="n">
+        <v>-46</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21211,6 +21574,9 @@
       <c r="BF6" t="n">
         <v>-74</v>
       </c>
+      <c r="BG6" t="n">
+        <v>-61</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21391,6 +21757,9 @@
       <c r="BF7" t="n">
         <v>-75</v>
       </c>
+      <c r="BG7" t="n">
+        <v>-49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21571,6 +21940,9 @@
       <c r="BF8" t="n">
         <v>52</v>
       </c>
+      <c r="BG8" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21751,6 +22123,9 @@
       <c r="BF9" t="n">
         <v>25</v>
       </c>
+      <c r="BG9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21930,6 +22305,9 @@
       </c>
       <c r="BF10" t="n">
         <v>94</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -623,6 +623,7 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -687,6 +688,9 @@
       <c r="S1" s="1" t="n">
         <v>20251216</v>
       </c>
+      <c r="T1" s="1" t="n">
+        <v>20251217</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -750,6 +754,9 @@
       <c r="S2" t="n">
         <v>39</v>
       </c>
+      <c r="T2" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -813,6 +820,9 @@
       <c r="S3" t="n">
         <v>-26</v>
       </c>
+      <c r="T3" t="n">
+        <v>-32</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -876,6 +886,9 @@
       <c r="S4" t="n">
         <v>51</v>
       </c>
+      <c r="T4" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -939,6 +952,9 @@
       <c r="S5" t="n">
         <v>-79</v>
       </c>
+      <c r="T5" t="n">
+        <v>-76</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1002,6 +1018,9 @@
       <c r="S6" t="n">
         <v>-68</v>
       </c>
+      <c r="T6" t="n">
+        <v>-66</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1065,6 +1084,9 @@
       <c r="S7" t="n">
         <v>-53</v>
       </c>
+      <c r="T7" t="n">
+        <v>-94</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1128,6 +1150,9 @@
       <c r="S8" t="n">
         <v>39</v>
       </c>
+      <c r="T8" t="n">
+        <v>-13</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1191,6 +1216,9 @@
       <c r="S9" t="n">
         <v>22</v>
       </c>
+      <c r="T9" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1253,6 +1281,9 @@
       </c>
       <c r="S10" t="n">
         <v>135</v>
+      </c>
+      <c r="T10" t="n">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1266,7 +1297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG10"/>
+  <dimension ref="A1:BH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1328,6 +1359,7 @@
     <col width="12" customWidth="1" min="57" max="57"/>
     <col width="12" customWidth="1" min="58" max="58"/>
     <col width="12" customWidth="1" min="59" max="59"/>
+    <col width="12" customWidth="1" min="60" max="60"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1626,6 +1658,11 @@
           <t>20251216</t>
         </is>
       </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>20251217</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1809,6 +1846,9 @@
       <c r="BG2" t="n">
         <v>99</v>
       </c>
+      <c r="BH2" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1992,6 +2032,9 @@
       <c r="BG3" t="n">
         <v>98</v>
       </c>
+      <c r="BH3" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2175,6 +2218,9 @@
       <c r="BG4" t="n">
         <v>98</v>
       </c>
+      <c r="BH4" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2358,6 +2404,9 @@
       <c r="BG5" t="n">
         <v>99</v>
       </c>
+      <c r="BH5" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2541,6 +2590,9 @@
       <c r="BG6" t="n">
         <v>92</v>
       </c>
+      <c r="BH6" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2724,6 +2776,9 @@
       <c r="BG7" t="n">
         <v>98</v>
       </c>
+      <c r="BH7" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2907,6 +2962,9 @@
       <c r="BG8" t="n">
         <v>108</v>
       </c>
+      <c r="BH8" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3090,6 +3148,9 @@
       <c r="BG9" t="n">
         <v>100</v>
       </c>
+      <c r="BH9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3272,6 +3333,9 @@
       </c>
       <c r="BG10" t="n">
         <v>113</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -3285,7 +3349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN10"/>
+  <dimension ref="A1:AO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3328,6 +3392,7 @@
     <col width="12" customWidth="1" min="38" max="38"/>
     <col width="12" customWidth="1" min="39" max="39"/>
     <col width="12" customWidth="1" min="40" max="40"/>
+    <col width="12" customWidth="1" min="41" max="41"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3531,6 +3596,11 @@
           <t>20251216</t>
         </is>
       </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>20251217</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3657,6 +3727,9 @@
       <c r="AN2" t="n">
         <v>13.79</v>
       </c>
+      <c r="AO2" t="n">
+        <v>5.87</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3783,6 +3856,9 @@
       <c r="AN3" t="n">
         <v>-47.52</v>
       </c>
+      <c r="AO3" t="n">
+        <v>-44.7</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3909,6 +3985,9 @@
       <c r="AN4" t="n">
         <v>-19.22</v>
       </c>
+      <c r="AO4" t="n">
+        <v>-28.09</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4035,6 +4114,9 @@
       <c r="AN5" t="n">
         <v>-50.08</v>
       </c>
+      <c r="AO5" t="n">
+        <v>-51.66</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4161,6 +4243,9 @@
       <c r="AN6" t="n">
         <v>-98.36</v>
       </c>
+      <c r="AO6" t="n">
+        <v>-98.40000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4287,6 +4372,9 @@
       <c r="AN7" t="n">
         <v>-51.67</v>
       </c>
+      <c r="AO7" t="n">
+        <v>-38.93</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4413,6 +4501,9 @@
       <c r="AN8" t="n">
         <v>-9.93</v>
       </c>
+      <c r="AO8" t="n">
+        <v>-10.43</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4539,6 +4630,9 @@
       <c r="AN9" t="n">
         <v>-22.47</v>
       </c>
+      <c r="AO9" t="n">
+        <v>-22.92</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4664,6 +4758,9 @@
       </c>
       <c r="AN10" t="n">
         <v>18.65</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>15.62</v>
       </c>
     </row>
   </sheetData>
@@ -4677,7 +4774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4699,6 +4796,7 @@
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4797,6 +4895,11 @@
           <t>20251216</t>
         </is>
       </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>20251217</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4860,6 +4963,9 @@
       <c r="S2" t="n">
         <v>41</v>
       </c>
+      <c r="T2" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4923,6 +5029,9 @@
       <c r="S3" t="n">
         <v>41</v>
       </c>
+      <c r="T3" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4986,6 +5095,9 @@
       <c r="S4" t="n">
         <v>42</v>
       </c>
+      <c r="T4" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5049,6 +5161,9 @@
       <c r="S5" t="n">
         <v>46</v>
       </c>
+      <c r="T5" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5112,6 +5227,9 @@
       <c r="S6" t="n">
         <v>88</v>
       </c>
+      <c r="T6" t="n">
+        <v>125</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5175,6 +5293,9 @@
       <c r="S7" t="n">
         <v>39</v>
       </c>
+      <c r="T7" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5238,6 +5359,9 @@
       <c r="S8" t="n">
         <v>42</v>
       </c>
+      <c r="T8" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5301,6 +5425,9 @@
       <c r="S9" t="n">
         <v>38</v>
       </c>
+      <c r="T9" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5363,6 +5490,9 @@
       </c>
       <c r="S10" t="n">
         <v>63</v>
+      </c>
+      <c r="T10" t="n">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -5376,7 +5506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ10"/>
+  <dimension ref="A1:CA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5457,6 +5587,7 @@
     <col width="12" customWidth="1" min="76" max="76"/>
     <col width="12" customWidth="1" min="77" max="77"/>
     <col width="12" customWidth="1" min="78" max="78"/>
+    <col width="12" customWidth="1" min="79" max="79"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5698,6 +5829,9 @@
       <c r="BZ1" s="1" t="n">
         <v>20251216</v>
       </c>
+      <c r="CA1" s="1" t="n">
+        <v>20251217</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5938,6 +6072,9 @@
       <c r="BZ2" t="n">
         <v>272.82</v>
       </c>
+      <c r="CA2" t="n">
+        <v>275.01</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6178,6 +6315,9 @@
       <c r="BZ3" t="n">
         <v>223.035</v>
       </c>
+      <c r="CA3" t="n">
+        <v>224.655</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6418,6 +6558,9 @@
       <c r="BZ4" t="n">
         <v>304.945</v>
       </c>
+      <c r="CA4" t="n">
+        <v>308.01</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6658,6 +6801,9 @@
       <c r="BZ5" t="n">
         <v>471.905</v>
       </c>
+      <c r="CA5" t="n">
+        <v>476.905</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6898,6 +7044,9 @@
       <c r="BZ6" t="n">
         <v>93.88</v>
       </c>
+      <c r="CA6" t="n">
+        <v>95.98</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7138,6 +7287,9 @@
       <c r="BZ7" t="n">
         <v>176.26</v>
       </c>
+      <c r="CA7" t="n">
+        <v>176.1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7378,6 +7530,9 @@
       <c r="BZ8" t="n">
         <v>181.655</v>
       </c>
+      <c r="CA8" t="n">
+        <v>187.715</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7618,6 +7773,9 @@
       <c r="BZ9" t="n">
         <v>85.64</v>
       </c>
+      <c r="CA9" t="n">
+        <v>84.56999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7857,6 +8015,9 @@
       </c>
       <c r="BZ10" t="n">
         <v>472.21</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>488.22</v>
       </c>
     </row>
   </sheetData>
@@ -7870,7 +8031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ10"/>
+  <dimension ref="A1:CA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7951,6 +8112,7 @@
     <col width="12" customWidth="1" min="76" max="76"/>
     <col width="12" customWidth="1" min="77" max="77"/>
     <col width="12" customWidth="1" min="78" max="78"/>
+    <col width="12" customWidth="1" min="79" max="79"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8192,6 +8354,9 @@
       <c r="BZ1" s="1" t="n">
         <v>20251216</v>
       </c>
+      <c r="CA1" s="1" t="n">
+        <v>20251217</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8432,6 +8597,9 @@
       <c r="BZ2" t="n">
         <v>275.5</v>
       </c>
+      <c r="CA2" t="n">
+        <v>276.16</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8672,6 +8840,9 @@
       <c r="BZ3" t="n">
         <v>223.66</v>
       </c>
+      <c r="CA3" t="n">
+        <v>225.19</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8912,6 +9083,9 @@
       <c r="BZ4" t="n">
         <v>310.77</v>
       </c>
+      <c r="CA4" t="n">
+        <v>308.09</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9152,6 +9326,9 @@
       <c r="BZ5" t="n">
         <v>477.89</v>
       </c>
+      <c r="CA5" t="n">
+        <v>480</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9392,6 +9569,9 @@
       <c r="BZ6" t="n">
         <v>94.93000000000001</v>
       </c>
+      <c r="CA6" t="n">
+        <v>97.33</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9632,6 +9812,9 @@
       <c r="BZ7" t="n">
         <v>178.49</v>
       </c>
+      <c r="CA7" t="n">
+        <v>176.13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9872,6 +10055,9 @@
       <c r="BZ8" t="n">
         <v>188.5</v>
       </c>
+      <c r="CA8" t="n">
+        <v>187.75</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10112,6 +10298,9 @@
       <c r="BZ9" t="n">
         <v>86.54000000000001</v>
       </c>
+      <c r="CA9" t="n">
+        <v>85.82899999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10351,6 +10540,9 @@
       </c>
       <c r="BZ10" t="n">
         <v>491.5</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>495.2799</v>
       </c>
     </row>
   </sheetData>
@@ -10364,7 +10556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ10"/>
+  <dimension ref="A1:CA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10445,6 +10637,7 @@
     <col width="12" customWidth="1" min="76" max="76"/>
     <col width="12" customWidth="1" min="77" max="77"/>
     <col width="12" customWidth="1" min="78" max="78"/>
+    <col width="12" customWidth="1" min="79" max="79"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10686,6 +10879,9 @@
       <c r="BZ1" s="1" t="n">
         <v>20251216</v>
       </c>
+      <c r="CA1" s="1" t="n">
+        <v>20251217</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10926,6 +11122,9 @@
       <c r="BZ2" t="n">
         <v>271.79</v>
       </c>
+      <c r="CA2" t="n">
+        <v>271.64</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11166,6 +11365,9 @@
       <c r="BZ3" t="n">
         <v>221.1304</v>
       </c>
+      <c r="CA3" t="n">
+        <v>220.99</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11406,6 +11608,9 @@
       <c r="BZ4" t="n">
         <v>302.59</v>
       </c>
+      <c r="CA4" t="n">
+        <v>296.12</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11646,6 +11851,9 @@
       <c r="BZ5" t="n">
         <v>470.88</v>
       </c>
+      <c r="CA5" t="n">
+        <v>475</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11886,6 +12094,9 @@
       <c r="BZ6" t="n">
         <v>93.31999999999999</v>
       </c>
+      <c r="CA6" t="n">
+        <v>94.45999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12126,6 +12337,9 @@
       <c r="BZ7" t="n">
         <v>174.9</v>
       </c>
+      <c r="CA7" t="n">
+        <v>170.31</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12366,6 +12580,9 @@
       <c r="BZ8" t="n">
         <v>181.1424</v>
       </c>
+      <c r="CA8" t="n">
+        <v>176.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12606,6 +12823,9 @@
       <c r="BZ9" t="n">
         <v>84.72</v>
       </c>
+      <c r="CA9" t="n">
+        <v>84.5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12845,6 +13065,9 @@
       </c>
       <c r="BZ10" t="n">
         <v>465.83</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>466.2</v>
       </c>
     </row>
   </sheetData>
@@ -12858,7 +13081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ10"/>
+  <dimension ref="A1:CA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12939,6 +13162,7 @@
     <col width="12" customWidth="1" min="76" max="76"/>
     <col width="12" customWidth="1" min="77" max="77"/>
     <col width="12" customWidth="1" min="78" max="78"/>
+    <col width="12" customWidth="1" min="79" max="79"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13180,6 +13404,9 @@
       <c r="BZ1" s="1" t="n">
         <v>20251216</v>
       </c>
+      <c r="CA1" s="1" t="n">
+        <v>20251217</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13420,6 +13647,9 @@
       <c r="BZ2" t="n">
         <v>274.61</v>
       </c>
+      <c r="CA2" t="n">
+        <v>271.84</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13660,6 +13890,9 @@
       <c r="BZ3" t="n">
         <v>222.56</v>
       </c>
+      <c r="CA3" t="n">
+        <v>221.27</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13900,6 +14133,9 @@
       <c r="BZ4" t="n">
         <v>306.57</v>
       </c>
+      <c r="CA4" t="n">
+        <v>296.72</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14140,6 +14376,9 @@
       <c r="BZ5" t="n">
         <v>476.39</v>
       </c>
+      <c r="CA5" t="n">
+        <v>476.12</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14380,6 +14619,9 @@
       <c r="BZ6" t="n">
         <v>94.56999999999999</v>
       </c>
+      <c r="CA6" t="n">
+        <v>94.79000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14620,6 +14862,9 @@
       <c r="BZ7" t="n">
         <v>177.72</v>
       </c>
+      <c r="CA7" t="n">
+        <v>170.94</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14860,6 +15105,9 @@
       <c r="BZ8" t="n">
         <v>187.75</v>
       </c>
+      <c r="CA8" t="n">
+        <v>177.29</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15100,6 +15348,9 @@
       <c r="BZ9" t="n">
         <v>85.08</v>
       </c>
+      <c r="CA9" t="n">
+        <v>85.20999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15339,6 +15590,9 @@
       </c>
       <c r="BZ10" t="n">
         <v>489.88</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>467.26</v>
       </c>
     </row>
   </sheetData>
@@ -15352,7 +15606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ10"/>
+  <dimension ref="A1:CA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15433,6 +15687,7 @@
     <col width="12" customWidth="1" min="76" max="76"/>
     <col width="12" customWidth="1" min="77" max="77"/>
     <col width="12" customWidth="1" min="78" max="78"/>
+    <col width="12" customWidth="1" min="79" max="79"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15674,6 +15929,9 @@
       <c r="BZ1" s="1" t="n">
         <v>20251216</v>
       </c>
+      <c r="CA1" s="1" t="n">
+        <v>20251217</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15914,6 +16172,9 @@
       <c r="BZ2" t="n">
         <v>37648628</v>
       </c>
+      <c r="CA2" t="n">
+        <v>50138743</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16154,6 +16415,9 @@
       <c r="BZ3" t="n">
         <v>39298857</v>
       </c>
+      <c r="CA3" t="n">
+        <v>44034418</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16394,6 +16658,9 @@
       <c r="BZ4" t="n">
         <v>30585020</v>
       </c>
+      <c r="CA4" t="n">
+        <v>43930358</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16634,6 +16901,9 @@
       <c r="BZ5" t="n">
         <v>20705560</v>
       </c>
+      <c r="CA5" t="n">
+        <v>24527176</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16874,6 +17144,9 @@
       <c r="BZ6" t="n">
         <v>34264989</v>
       </c>
+      <c r="CA6" t="n">
+        <v>50472781</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17114,6 +17387,9 @@
       <c r="BZ7" t="n">
         <v>148588098</v>
       </c>
+      <c r="CA7" t="n">
+        <v>222775464</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17354,6 +17630,9 @@
       <c r="BZ8" t="n">
         <v>42070267</v>
       </c>
+      <c r="CA8" t="n">
+        <v>50424653</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17594,6 +17873,9 @@
       <c r="BZ9" t="n">
         <v>7481392</v>
       </c>
+      <c r="CA9" t="n">
+        <v>7947026</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17833,6 +18115,9 @@
       </c>
       <c r="BZ10" t="n">
         <v>107608075</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>106490405</v>
       </c>
     </row>
   </sheetData>
@@ -17846,7 +18131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG10"/>
+  <dimension ref="A1:BH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17908,6 +18193,7 @@
     <col width="10" customWidth="1" min="57" max="57"/>
     <col width="10" customWidth="1" min="58" max="58"/>
     <col width="10" customWidth="1" min="59" max="59"/>
+    <col width="10" customWidth="1" min="60" max="60"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18092,6 +18378,9 @@
       <c r="BG1" s="1" t="n">
         <v>20251216</v>
       </c>
+      <c r="BH1" s="1" t="n">
+        <v>20251217</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18275,6 +18564,9 @@
       <c r="BG2" t="n">
         <v>42</v>
       </c>
+      <c r="BH2" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18458,6 +18750,9 @@
       <c r="BG3" t="n">
         <v>31</v>
       </c>
+      <c r="BH3" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18641,6 +18936,9 @@
       <c r="BG4" t="n">
         <v>57</v>
       </c>
+      <c r="BH4" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18824,6 +19122,9 @@
       <c r="BG5" t="n">
         <v>20</v>
       </c>
+      <c r="BH5" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19007,6 +19308,9 @@
       <c r="BG6" t="n">
         <v>9</v>
       </c>
+      <c r="BH6" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19190,6 +19494,9 @@
       <c r="BG7" t="n">
         <v>23</v>
       </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19373,6 +19680,9 @@
       <c r="BG8" t="n">
         <v>100</v>
       </c>
+      <c r="BH8" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19556,6 +19866,9 @@
       <c r="BG9" t="n">
         <v>58</v>
       </c>
+      <c r="BH9" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -19738,6 +20051,9 @@
       </c>
       <c r="BG10" t="n">
         <v>100</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -19751,7 +20067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -19773,6 +20089,7 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19837,6 +20154,9 @@
       <c r="S1" s="1" t="n">
         <v>20251216</v>
       </c>
+      <c r="T1" s="1" t="n">
+        <v>20251217</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19900,6 +20220,9 @@
       <c r="S2" t="n">
         <v>72</v>
       </c>
+      <c r="T2" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19963,6 +20286,9 @@
       <c r="S3" t="n">
         <v>23</v>
       </c>
+      <c r="T3" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20026,6 +20352,9 @@
       <c r="S4" t="n">
         <v>81</v>
       </c>
+      <c r="T4" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20089,6 +20418,9 @@
       <c r="S5" t="n">
         <v>6</v>
       </c>
+      <c r="T5" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20152,6 +20484,9 @@
       <c r="S6" t="n">
         <v>0</v>
       </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20215,6 +20550,9 @@
       <c r="S7" t="n">
         <v>8</v>
       </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20278,6 +20616,9 @@
       <c r="S8" t="n">
         <v>63</v>
       </c>
+      <c r="T8" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20341,6 +20682,9 @@
       <c r="S9" t="n">
         <v>75</v>
       </c>
+      <c r="T9" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20403,6 +20747,9 @@
       </c>
       <c r="S10" t="n">
         <v>100</v>
+      </c>
+      <c r="T10" t="n">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -20416,7 +20763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG10"/>
+  <dimension ref="A1:BH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20478,6 +20825,7 @@
     <col width="10" customWidth="1" min="57" max="57"/>
     <col width="10" customWidth="1" min="58" max="58"/>
     <col width="10" customWidth="1" min="59" max="59"/>
+    <col width="10" customWidth="1" min="60" max="60"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20662,6 +21010,9 @@
       <c r="BG1" s="1" t="n">
         <v>20251216</v>
       </c>
+      <c r="BH1" s="1" t="n">
+        <v>20251217</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20845,6 +21196,9 @@
       <c r="BG2" t="n">
         <v>-20</v>
       </c>
+      <c r="BH2" t="n">
+        <v>-52</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21028,6 +21382,9 @@
       <c r="BG3" t="n">
         <v>-51</v>
       </c>
+      <c r="BH3" t="n">
+        <v>-63</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -21211,6 +21568,9 @@
       <c r="BG4" t="n">
         <v>-21</v>
       </c>
+      <c r="BH4" t="n">
+        <v>-76</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -21394,6 +21754,9 @@
       <c r="BG5" t="n">
         <v>-46</v>
       </c>
+      <c r="BH5" t="n">
+        <v>-44</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21577,6 +21940,9 @@
       <c r="BG6" t="n">
         <v>-61</v>
       </c>
+      <c r="BH6" t="n">
+        <v>-55</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21760,6 +22126,9 @@
       <c r="BG7" t="n">
         <v>-49</v>
       </c>
+      <c r="BH7" t="n">
+        <v>-122</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21943,6 +22312,9 @@
       <c r="BG8" t="n">
         <v>67</v>
       </c>
+      <c r="BH8" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22126,6 +22498,9 @@
       <c r="BG9" t="n">
         <v>11</v>
       </c>
+      <c r="BH9" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22308,6 +22683,9 @@
       </c>
       <c r="BG10" t="n">
         <v>104</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -624,6 +624,7 @@
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="10" customWidth="1" min="19" max="19"/>
     <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -691,6 +692,9 @@
       <c r="T1" s="1" t="n">
         <v>20251217</v>
       </c>
+      <c r="U1" s="1" t="n">
+        <v>20251218</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -757,6 +761,9 @@
       <c r="T2" t="n">
         <v>25</v>
       </c>
+      <c r="U2" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -823,6 +830,9 @@
       <c r="T3" t="n">
         <v>-32</v>
       </c>
+      <c r="U3" t="n">
+        <v>-6</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -889,6 +899,9 @@
       <c r="T4" t="n">
         <v>32</v>
       </c>
+      <c r="U4" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -955,6 +968,9 @@
       <c r="T5" t="n">
         <v>-76</v>
       </c>
+      <c r="U5" t="n">
+        <v>-53</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1021,6 +1037,9 @@
       <c r="T6" t="n">
         <v>-66</v>
       </c>
+      <c r="U6" t="n">
+        <v>-63</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1087,6 +1106,9 @@
       <c r="T7" t="n">
         <v>-94</v>
       </c>
+      <c r="U7" t="n">
+        <v>-73</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1153,6 +1175,9 @@
       <c r="T8" t="n">
         <v>-13</v>
       </c>
+      <c r="U8" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1219,6 +1244,9 @@
       <c r="T9" t="n">
         <v>25</v>
       </c>
+      <c r="U9" t="n">
+        <v>117</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1284,6 +1312,9 @@
       </c>
       <c r="T10" t="n">
         <v>74</v>
+      </c>
+      <c r="U10" t="n">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1297,7 +1328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH10"/>
+  <dimension ref="A1:BI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1360,6 +1391,7 @@
     <col width="12" customWidth="1" min="58" max="58"/>
     <col width="12" customWidth="1" min="59" max="59"/>
     <col width="12" customWidth="1" min="60" max="60"/>
+    <col width="12" customWidth="1" min="61" max="61"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1663,6 +1695,11 @@
           <t>20251217</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>20251218</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1849,6 +1886,9 @@
       <c r="BH2" t="n">
         <v>98</v>
       </c>
+      <c r="BI2" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2035,6 +2075,9 @@
       <c r="BH3" t="n">
         <v>97</v>
       </c>
+      <c r="BI3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2221,6 +2264,9 @@
       <c r="BH4" t="n">
         <v>95</v>
       </c>
+      <c r="BI4" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2407,6 +2453,9 @@
       <c r="BH5" t="n">
         <v>99</v>
       </c>
+      <c r="BI5" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2593,6 +2642,9 @@
       <c r="BH6" t="n">
         <v>93</v>
       </c>
+      <c r="BI6" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2779,6 +2831,9 @@
       <c r="BH7" t="n">
         <v>95</v>
       </c>
+      <c r="BI7" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2965,6 +3020,9 @@
       <c r="BH8" t="n">
         <v>102</v>
       </c>
+      <c r="BI8" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3151,6 +3209,9 @@
       <c r="BH9" t="n">
         <v>100</v>
       </c>
+      <c r="BI9" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3336,6 +3397,9 @@
       </c>
       <c r="BH10" t="n">
         <v>107</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -3349,7 +3413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3393,6 +3457,7 @@
     <col width="12" customWidth="1" min="39" max="39"/>
     <col width="12" customWidth="1" min="40" max="40"/>
     <col width="12" customWidth="1" min="41" max="41"/>
+    <col width="12" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3601,6 +3666,11 @@
           <t>20251217</t>
         </is>
       </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>20251218</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3730,6 +3800,9 @@
       <c r="AO2" t="n">
         <v>5.87</v>
       </c>
+      <c r="AP2" t="n">
+        <v>-1.14</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3859,6 +3932,9 @@
       <c r="AO3" t="n">
         <v>-44.7</v>
       </c>
+      <c r="AP3" t="n">
+        <v>-44.08</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3988,6 +4064,9 @@
       <c r="AO4" t="n">
         <v>-28.09</v>
       </c>
+      <c r="AP4" t="n">
+        <v>-33.33</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4117,6 +4196,9 @@
       <c r="AO5" t="n">
         <v>-51.66</v>
       </c>
+      <c r="AP5" t="n">
+        <v>-50.83</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4246,6 +4328,9 @@
       <c r="AO6" t="n">
         <v>-98.40000000000001</v>
       </c>
+      <c r="AP6" t="n">
+        <v>-98.36</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4375,6 +4460,9 @@
       <c r="AO7" t="n">
         <v>-38.93</v>
       </c>
+      <c r="AP7" t="n">
+        <v>-37.85</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4504,6 +4592,9 @@
       <c r="AO8" t="n">
         <v>-10.43</v>
       </c>
+      <c r="AP8" t="n">
+        <v>-9.220000000000001</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4633,6 +4724,9 @@
       <c r="AO9" t="n">
         <v>-22.92</v>
       </c>
+      <c r="AP9" t="n">
+        <v>-3.74</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4761,6 +4855,9 @@
       </c>
       <c r="AO10" t="n">
         <v>15.62</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>16.69</v>
       </c>
     </row>
   </sheetData>
@@ -4774,7 +4871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4797,6 +4894,7 @@
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4900,6 +4998,11 @@
           <t>20251217</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>20251218</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4966,6 +5069,9 @@
       <c r="T2" t="n">
         <v>55</v>
       </c>
+      <c r="U2" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5032,6 +5138,9 @@
       <c r="T3" t="n">
         <v>47</v>
       </c>
+      <c r="U3" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5098,6 +5207,9 @@
       <c r="T4" t="n">
         <v>60</v>
       </c>
+      <c r="U4" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5164,6 +5276,9 @@
       <c r="T5" t="n">
         <v>55</v>
       </c>
+      <c r="U5" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5230,6 +5345,9 @@
       <c r="T6" t="n">
         <v>125</v>
       </c>
+      <c r="U6" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5296,6 +5414,9 @@
       <c r="T7" t="n">
         <v>59</v>
       </c>
+      <c r="U7" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5362,6 +5483,9 @@
       <c r="T8" t="n">
         <v>50</v>
       </c>
+      <c r="U8" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5428,6 +5552,9 @@
       <c r="T9" t="n">
         <v>40</v>
       </c>
+      <c r="U9" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5493,6 +5620,9 @@
       </c>
       <c r="T10" t="n">
         <v>62</v>
+      </c>
+      <c r="U10" t="n">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -5506,7 +5636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA10"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5588,6 +5718,7 @@
     <col width="12" customWidth="1" min="77" max="77"/>
     <col width="12" customWidth="1" min="78" max="78"/>
     <col width="12" customWidth="1" min="79" max="79"/>
+    <col width="12" customWidth="1" min="80" max="80"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5832,6 +5963,9 @@
       <c r="CA1" s="1" t="n">
         <v>20251217</v>
       </c>
+      <c r="CB1" s="1" t="n">
+        <v>20251218</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6075,6 +6209,9 @@
       <c r="CA2" t="n">
         <v>275.01</v>
       </c>
+      <c r="CB2" t="n">
+        <v>273.605</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6318,6 +6455,9 @@
       <c r="CA3" t="n">
         <v>224.655</v>
       </c>
+      <c r="CB3" t="n">
+        <v>225.705</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6561,6 +6701,9 @@
       <c r="CA4" t="n">
         <v>308.01</v>
       </c>
+      <c r="CB4" t="n">
+        <v>301.72</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6804,6 +6947,9 @@
       <c r="CA5" t="n">
         <v>476.905</v>
       </c>
+      <c r="CB5" t="n">
+        <v>478.19</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7047,6 +7193,9 @@
       <c r="CA6" t="n">
         <v>95.98</v>
       </c>
+      <c r="CB6" t="n">
+        <v>95.02</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7290,6 +7439,9 @@
       <c r="CA7" t="n">
         <v>176.1</v>
       </c>
+      <c r="CB7" t="n">
+        <v>174.53</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7533,6 +7685,9 @@
       <c r="CA8" t="n">
         <v>187.715</v>
       </c>
+      <c r="CB8" t="n">
+        <v>181.51</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7776,6 +7931,9 @@
       <c r="CA9" t="n">
         <v>84.56999999999999</v>
       </c>
+      <c r="CB9" t="n">
+        <v>87.68899999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8018,6 +8176,9 @@
       </c>
       <c r="CA10" t="n">
         <v>488.22</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>478.16</v>
       </c>
     </row>
   </sheetData>
@@ -8031,7 +8192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA10"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8113,6 +8274,7 @@
     <col width="12" customWidth="1" min="77" max="77"/>
     <col width="12" customWidth="1" min="78" max="78"/>
     <col width="12" customWidth="1" min="79" max="79"/>
+    <col width="12" customWidth="1" min="80" max="80"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8357,6 +8519,9 @@
       <c r="CA1" s="1" t="n">
         <v>20251217</v>
       </c>
+      <c r="CB1" s="1" t="n">
+        <v>20251218</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8600,6 +8765,9 @@
       <c r="CA2" t="n">
         <v>276.16</v>
       </c>
+      <c r="CB2" t="n">
+        <v>273.63</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8843,6 +9011,9 @@
       <c r="CA3" t="n">
         <v>225.19</v>
       </c>
+      <c r="CB3" t="n">
+        <v>229.225</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9086,6 +9257,9 @@
       <c r="CA4" t="n">
         <v>308.09</v>
       </c>
+      <c r="CB4" t="n">
+        <v>303.96</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9329,6 +9503,9 @@
       <c r="CA5" t="n">
         <v>480</v>
       </c>
+      <c r="CB5" t="n">
+        <v>489.6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9572,6 +9749,9 @@
       <c r="CA6" t="n">
         <v>97.33</v>
       </c>
+      <c r="CB6" t="n">
+        <v>95.81</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9815,6 +9995,9 @@
       <c r="CA7" t="n">
         <v>176.13</v>
       </c>
+      <c r="CB7" t="n">
+        <v>176.15</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10058,6 +10241,9 @@
       <c r="CA8" t="n">
         <v>187.75</v>
       </c>
+      <c r="CB8" t="n">
+        <v>187.33</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10301,6 +10487,9 @@
       <c r="CA9" t="n">
         <v>85.82899999999999</v>
       </c>
+      <c r="CB9" t="n">
+        <v>90.575</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10543,6 +10732,9 @@
       </c>
       <c r="CA10" t="n">
         <v>495.2799</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>490.86</v>
       </c>
     </row>
   </sheetData>
@@ -10556,7 +10748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA10"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10638,6 +10830,7 @@
     <col width="12" customWidth="1" min="77" max="77"/>
     <col width="12" customWidth="1" min="78" max="78"/>
     <col width="12" customWidth="1" min="79" max="79"/>
+    <col width="12" customWidth="1" min="80" max="80"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10882,6 +11075,9 @@
       <c r="CA1" s="1" t="n">
         <v>20251217</v>
       </c>
+      <c r="CB1" s="1" t="n">
+        <v>20251218</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11125,6 +11321,9 @@
       <c r="CA2" t="n">
         <v>271.64</v>
       </c>
+      <c r="CB2" t="n">
+        <v>266.95</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11368,6 +11567,9 @@
       <c r="CA3" t="n">
         <v>220.99</v>
       </c>
+      <c r="CB3" t="n">
+        <v>224.41</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11611,6 +11813,9 @@
       <c r="CA4" t="n">
         <v>296.12</v>
       </c>
+      <c r="CB4" t="n">
+        <v>299.2308</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11854,6 +12059,9 @@
       <c r="CA5" t="n">
         <v>475</v>
       </c>
+      <c r="CB5" t="n">
+        <v>477.89</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12097,6 +12305,9 @@
       <c r="CA6" t="n">
         <v>94.45999999999999</v>
       </c>
+      <c r="CB6" t="n">
+        <v>93.59</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12340,6 +12551,9 @@
       <c r="CA7" t="n">
         <v>170.31</v>
       </c>
+      <c r="CB7" t="n">
+        <v>171.82</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12583,6 +12797,9 @@
       <c r="CA8" t="n">
         <v>176.5</v>
       </c>
+      <c r="CB8" t="n">
+        <v>181.51</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12826,6 +13043,9 @@
       <c r="CA9" t="n">
         <v>84.5</v>
       </c>
+      <c r="CB9" t="n">
+        <v>87.3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13068,6 +13288,9 @@
       </c>
       <c r="CA10" t="n">
         <v>466.2</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>473.12</v>
       </c>
     </row>
   </sheetData>
@@ -13081,7 +13304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA10"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13163,6 +13386,7 @@
     <col width="12" customWidth="1" min="77" max="77"/>
     <col width="12" customWidth="1" min="78" max="78"/>
     <col width="12" customWidth="1" min="79" max="79"/>
+    <col width="12" customWidth="1" min="80" max="80"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13407,6 +13631,9 @@
       <c r="CA1" s="1" t="n">
         <v>20251217</v>
       </c>
+      <c r="CB1" s="1" t="n">
+        <v>20251218</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13650,6 +13877,9 @@
       <c r="CA2" t="n">
         <v>271.84</v>
       </c>
+      <c r="CB2" t="n">
+        <v>272.19</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13893,6 +14123,9 @@
       <c r="CA3" t="n">
         <v>221.27</v>
       </c>
+      <c r="CB3" t="n">
+        <v>226.76</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14136,6 +14369,9 @@
       <c r="CA4" t="n">
         <v>296.72</v>
       </c>
+      <c r="CB4" t="n">
+        <v>302.46</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14379,6 +14615,9 @@
       <c r="CA5" t="n">
         <v>476.12</v>
       </c>
+      <c r="CB5" t="n">
+        <v>483.98</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14622,6 +14861,9 @@
       <c r="CA6" t="n">
         <v>94.79000000000001</v>
       </c>
+      <c r="CB6" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14865,6 +15107,9 @@
       <c r="CA7" t="n">
         <v>170.94</v>
       </c>
+      <c r="CB7" t="n">
+        <v>174.14</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15108,6 +15353,9 @@
       <c r="CA8" t="n">
         <v>177.29</v>
       </c>
+      <c r="CB8" t="n">
+        <v>185.69</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15351,6 +15599,9 @@
       <c r="CA9" t="n">
         <v>85.20999999999999</v>
       </c>
+      <c r="CB9" t="n">
+        <v>89.42</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15593,6 +15844,9 @@
       </c>
       <c r="CA10" t="n">
         <v>467.26</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>483.37</v>
       </c>
     </row>
   </sheetData>
@@ -15606,7 +15860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA10"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15688,6 +15942,7 @@
     <col width="12" customWidth="1" min="77" max="77"/>
     <col width="12" customWidth="1" min="78" max="78"/>
     <col width="12" customWidth="1" min="79" max="79"/>
+    <col width="12" customWidth="1" min="80" max="80"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15932,6 +16187,9 @@
       <c r="CA1" s="1" t="n">
         <v>20251217</v>
       </c>
+      <c r="CB1" s="1" t="n">
+        <v>20251218</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16175,6 +16433,9 @@
       <c r="CA2" t="n">
         <v>50138743</v>
       </c>
+      <c r="CB2" t="n">
+        <v>51630721</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16418,6 +16679,9 @@
       <c r="CA3" t="n">
         <v>44034418</v>
       </c>
+      <c r="CB3" t="n">
+        <v>50272419</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16661,6 +16925,9 @@
       <c r="CA4" t="n">
         <v>43930358</v>
       </c>
+      <c r="CB4" t="n">
+        <v>33518048</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16904,6 +17171,9 @@
       <c r="CA5" t="n">
         <v>24527176</v>
       </c>
+      <c r="CB5" t="n">
+        <v>28573545</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17147,6 +17417,9 @@
       <c r="CA6" t="n">
         <v>50472781</v>
       </c>
+      <c r="CB6" t="n">
+        <v>37244734</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17390,6 +17663,9 @@
       <c r="CA7" t="n">
         <v>222775464</v>
       </c>
+      <c r="CB7" t="n">
+        <v>176096001</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17633,6 +17909,9 @@
       <c r="CA8" t="n">
         <v>50424653</v>
       </c>
+      <c r="CB8" t="n">
+        <v>40221476</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17876,6 +18155,9 @@
       <c r="CA9" t="n">
         <v>7947026</v>
       </c>
+      <c r="CB9" t="n">
+        <v>16466099</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18118,6 +18400,9 @@
       </c>
       <c r="CA10" t="n">
         <v>106490405</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>95168446</v>
       </c>
     </row>
   </sheetData>
@@ -18131,7 +18416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH10"/>
+  <dimension ref="A1:BI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18194,6 +18479,7 @@
     <col width="10" customWidth="1" min="58" max="58"/>
     <col width="10" customWidth="1" min="59" max="59"/>
     <col width="10" customWidth="1" min="60" max="60"/>
+    <col width="10" customWidth="1" min="61" max="61"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18381,6 +18667,9 @@
       <c r="BH1" s="1" t="n">
         <v>20251217</v>
       </c>
+      <c r="BI1" s="1" t="n">
+        <v>20251218</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18567,6 +18856,9 @@
       <c r="BH2" t="n">
         <v>28</v>
       </c>
+      <c r="BI2" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18753,6 +19045,9 @@
       <c r="BH3" t="n">
         <v>24</v>
       </c>
+      <c r="BI3" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18939,6 +19234,9 @@
       <c r="BH4" t="n">
         <v>21</v>
       </c>
+      <c r="BI4" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19125,6 +19423,9 @@
       <c r="BH5" t="n">
         <v>20</v>
       </c>
+      <c r="BI5" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19311,6 +19612,9 @@
       <c r="BH6" t="n">
         <v>12</v>
       </c>
+      <c r="BI6" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19497,6 +19801,9 @@
       <c r="BH7" t="n">
         <v>0</v>
       </c>
+      <c r="BI7" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19683,6 +19990,9 @@
       <c r="BH8" t="n">
         <v>68</v>
       </c>
+      <c r="BI8" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19869,6 +20179,9 @@
       <c r="BH9" t="n">
         <v>61</v>
       </c>
+      <c r="BI9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20054,6 +20367,9 @@
       </c>
       <c r="BH10" t="n">
         <v>77</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -20067,7 +20383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20090,6 +20406,7 @@
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="10" customWidth="1" min="19" max="19"/>
     <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20157,6 +20474,9 @@
       <c r="T1" s="1" t="n">
         <v>20251217</v>
       </c>
+      <c r="U1" s="1" t="n">
+        <v>20251218</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20223,6 +20543,9 @@
       <c r="T2" t="n">
         <v>65</v>
       </c>
+      <c r="U2" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20289,6 +20612,9 @@
       <c r="T3" t="n">
         <v>20</v>
       </c>
+      <c r="U3" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20355,6 +20681,9 @@
       <c r="T4" t="n">
         <v>69</v>
       </c>
+      <c r="U4" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20421,6 +20750,9 @@
       <c r="T5" t="n">
         <v>6</v>
       </c>
+      <c r="U5" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20487,6 +20819,9 @@
       <c r="T6" t="n">
         <v>0</v>
       </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20553,6 +20888,9 @@
       <c r="T7" t="n">
         <v>0</v>
       </c>
+      <c r="U7" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20619,6 +20957,9 @@
       <c r="T8" t="n">
         <v>43</v>
       </c>
+      <c r="U8" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20685,6 +21026,9 @@
       <c r="T9" t="n">
         <v>77</v>
       </c>
+      <c r="U9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20750,6 +21094,9 @@
       </c>
       <c r="T10" t="n">
         <v>77</v>
+      </c>
+      <c r="U10" t="n">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -20763,7 +21110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH10"/>
+  <dimension ref="A1:BI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20826,6 +21173,7 @@
     <col width="10" customWidth="1" min="58" max="58"/>
     <col width="10" customWidth="1" min="59" max="59"/>
     <col width="10" customWidth="1" min="60" max="60"/>
+    <col width="10" customWidth="1" min="61" max="61"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21013,6 +21361,9 @@
       <c r="BH1" s="1" t="n">
         <v>20251217</v>
       </c>
+      <c r="BI1" s="1" t="n">
+        <v>20251218</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21199,6 +21550,9 @@
       <c r="BH2" t="n">
         <v>-52</v>
       </c>
+      <c r="BI2" t="n">
+        <v>-53</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21385,6 +21739,9 @@
       <c r="BH3" t="n">
         <v>-63</v>
       </c>
+      <c r="BI3" t="n">
+        <v>-9</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -21571,6 +21928,9 @@
       <c r="BH4" t="n">
         <v>-76</v>
       </c>
+      <c r="BI4" t="n">
+        <v>-53</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -21757,6 +22117,9 @@
       <c r="BH5" t="n">
         <v>-44</v>
       </c>
+      <c r="BI5" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21943,6 +22306,9 @@
       <c r="BH6" t="n">
         <v>-55</v>
       </c>
+      <c r="BI6" t="n">
+        <v>-56</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -22129,6 +22495,9 @@
       <c r="BH7" t="n">
         <v>-122</v>
       </c>
+      <c r="BI7" t="n">
+        <v>-73</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22315,6 +22684,9 @@
       <c r="BH8" t="n">
         <v>15</v>
       </c>
+      <c r="BI8" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22501,6 +22873,9 @@
       <c r="BH9" t="n">
         <v>13</v>
       </c>
+      <c r="BI9" t="n">
+        <v>129</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22686,6 +23061,9 @@
       </c>
       <c r="BH10" t="n">
         <v>55</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U10"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -625,6 +625,7 @@
     <col width="10" customWidth="1" min="19" max="19"/>
     <col width="10" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -695,6 +696,9 @@
       <c r="U1" s="1" t="n">
         <v>20251218</v>
       </c>
+      <c r="V1" s="1" t="n">
+        <v>20251219</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -764,6 +768,9 @@
       <c r="U2" t="n">
         <v>25</v>
       </c>
+      <c r="V2" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -833,6 +840,9 @@
       <c r="U3" t="n">
         <v>-6</v>
       </c>
+      <c r="V3" t="n">
+        <v>-4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -902,6 +912,9 @@
       <c r="U4" t="n">
         <v>41</v>
       </c>
+      <c r="V4" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -971,6 +984,9 @@
       <c r="U5" t="n">
         <v>-53</v>
       </c>
+      <c r="V5" t="n">
+        <v>-47</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1040,6 +1056,9 @@
       <c r="U6" t="n">
         <v>-63</v>
       </c>
+      <c r="V6" t="n">
+        <v>-61</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1109,6 +1128,9 @@
       <c r="U7" t="n">
         <v>-73</v>
       </c>
+      <c r="V7" t="n">
+        <v>-30</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1178,6 +1200,9 @@
       <c r="U8" t="n">
         <v>29</v>
       </c>
+      <c r="V8" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1247,6 +1272,9 @@
       <c r="U9" t="n">
         <v>117</v>
       </c>
+      <c r="V9" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1315,6 +1343,9 @@
       </c>
       <c r="U10" t="n">
         <v>108</v>
+      </c>
+      <c r="V10" t="n">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1328,7 +1359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI10"/>
+  <dimension ref="A1:BJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1392,6 +1423,7 @@
     <col width="12" customWidth="1" min="59" max="59"/>
     <col width="12" customWidth="1" min="60" max="60"/>
     <col width="12" customWidth="1" min="61" max="61"/>
+    <col width="12" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1700,6 +1732,11 @@
           <t>20251218</t>
         </is>
       </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>20251219</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1889,6 +1926,9 @@
       <c r="BI2" t="n">
         <v>98</v>
       </c>
+      <c r="BJ2" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2078,6 +2118,9 @@
       <c r="BI3" t="n">
         <v>100</v>
       </c>
+      <c r="BJ3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2267,6 +2310,9 @@
       <c r="BI4" t="n">
         <v>97</v>
       </c>
+      <c r="BJ4" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2456,6 +2502,9 @@
       <c r="BI5" t="n">
         <v>100</v>
       </c>
+      <c r="BJ5" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2645,6 +2694,9 @@
       <c r="BI6" t="n">
         <v>93</v>
       </c>
+      <c r="BJ6" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2834,6 +2886,9 @@
       <c r="BI7" t="n">
         <v>97</v>
       </c>
+      <c r="BJ7" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3023,6 +3078,9 @@
       <c r="BI8" t="n">
         <v>106</v>
       </c>
+      <c r="BJ8" t="n">
+        <v>109</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3212,6 +3270,9 @@
       <c r="BI9" t="n">
         <v>105</v>
       </c>
+      <c r="BJ9" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3400,6 +3461,9 @@
       </c>
       <c r="BI10" t="n">
         <v>109</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -3413,7 +3477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP10"/>
+  <dimension ref="A1:AQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3458,6 +3522,7 @@
     <col width="12" customWidth="1" min="40" max="40"/>
     <col width="12" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="12" customWidth="1" min="43" max="43"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3671,6 +3736,11 @@
           <t>20251218</t>
         </is>
       </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>20251219</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3803,6 +3873,9 @@
       <c r="AP2" t="n">
         <v>-1.14</v>
       </c>
+      <c r="AQ2" t="n">
+        <v>-16.44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3935,6 +4008,9 @@
       <c r="AP3" t="n">
         <v>-44.08</v>
       </c>
+      <c r="AQ3" t="n">
+        <v>-49.9</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4067,6 +4143,9 @@
       <c r="AP4" t="n">
         <v>-33.33</v>
       </c>
+      <c r="AQ4" t="n">
+        <v>-44.65</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4199,6 +4278,9 @@
       <c r="AP5" t="n">
         <v>-50.83</v>
       </c>
+      <c r="AQ5" t="n">
+        <v>-48.57</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4331,6 +4413,9 @@
       <c r="AP6" t="n">
         <v>-98.36</v>
       </c>
+      <c r="AQ6" t="n">
+        <v>-98.25</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4463,6 +4548,9 @@
       <c r="AP7" t="n">
         <v>-37.85</v>
       </c>
+      <c r="AQ7" t="n">
+        <v>-35.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4595,6 +4683,9 @@
       <c r="AP8" t="n">
         <v>-9.220000000000001</v>
       </c>
+      <c r="AQ8" t="n">
+        <v>-10.41</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4727,6 +4818,9 @@
       <c r="AP9" t="n">
         <v>-3.74</v>
       </c>
+      <c r="AQ9" t="n">
+        <v>-0.51</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4858,6 +4952,9 @@
       </c>
       <c r="AP10" t="n">
         <v>16.69</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>11.18</v>
       </c>
     </row>
   </sheetData>
@@ -4871,7 +4968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U10"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4895,6 +4992,7 @@
     <col width="12" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5003,6 +5101,11 @@
           <t>20251218</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>20251219</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5072,6 +5175,9 @@
       <c r="U2" t="n">
         <v>56</v>
       </c>
+      <c r="V2" t="n">
+        <v>153</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5141,6 +5247,9 @@
       <c r="U3" t="n">
         <v>53</v>
       </c>
+      <c r="V3" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5210,6 +5319,9 @@
       <c r="U4" t="n">
         <v>46</v>
       </c>
+      <c r="V4" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5279,6 +5391,9 @@
       <c r="U5" t="n">
         <v>63</v>
       </c>
+      <c r="V5" t="n">
+        <v>151</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5348,6 +5463,9 @@
       <c r="U6" t="n">
         <v>90</v>
       </c>
+      <c r="V6" t="n">
+        <v>179</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5417,6 +5535,9 @@
       <c r="U7" t="n">
         <v>46</v>
       </c>
+      <c r="V7" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5486,6 +5607,9 @@
       <c r="U8" t="n">
         <v>40</v>
       </c>
+      <c r="V8" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5555,6 +5679,9 @@
       <c r="U9" t="n">
         <v>83</v>
       </c>
+      <c r="V9" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5623,6 +5750,9 @@
       </c>
       <c r="U10" t="n">
         <v>56</v>
+      </c>
+      <c r="V10" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -5636,7 +5766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5719,6 +5849,7 @@
     <col width="12" customWidth="1" min="78" max="78"/>
     <col width="12" customWidth="1" min="79" max="79"/>
     <col width="12" customWidth="1" min="80" max="80"/>
+    <col width="12" customWidth="1" min="81" max="81"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5966,6 +6097,9 @@
       <c r="CB1" s="1" t="n">
         <v>20251218</v>
       </c>
+      <c r="CC1" s="1" t="n">
+        <v>20251219</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6212,6 +6346,9 @@
       <c r="CB2" t="n">
         <v>273.605</v>
       </c>
+      <c r="CC2" t="n">
+        <v>272.145</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6458,6 +6595,9 @@
       <c r="CB3" t="n">
         <v>225.705</v>
       </c>
+      <c r="CC3" t="n">
+        <v>226.76</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6704,6 +6844,9 @@
       <c r="CB4" t="n">
         <v>301.72</v>
       </c>
+      <c r="CC4" t="n">
+        <v>301.73</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6950,6 +7093,9 @@
       <c r="CB5" t="n">
         <v>478.19</v>
       </c>
+      <c r="CC5" t="n">
+        <v>487.36</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7196,6 +7342,9 @@
       <c r="CB6" t="n">
         <v>95.02</v>
       </c>
+      <c r="CC6" t="n">
+        <v>93.56999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7442,6 +7591,9 @@
       <c r="CB7" t="n">
         <v>174.53</v>
       </c>
+      <c r="CC7" t="n">
+        <v>176.665</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7688,6 +7840,9 @@
       <c r="CB8" t="n">
         <v>181.51</v>
       </c>
+      <c r="CC8" t="n">
+        <v>186.74</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7934,6 +8089,9 @@
       <c r="CB9" t="n">
         <v>87.68899999999999</v>
       </c>
+      <c r="CC9" t="n">
+        <v>89.215</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8179,6 +8337,9 @@
       </c>
       <c r="CB10" t="n">
         <v>478.16</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>488.12</v>
       </c>
     </row>
   </sheetData>
@@ -8192,7 +8353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8275,6 +8436,7 @@
     <col width="12" customWidth="1" min="78" max="78"/>
     <col width="12" customWidth="1" min="79" max="79"/>
     <col width="12" customWidth="1" min="80" max="80"/>
+    <col width="12" customWidth="1" min="81" max="81"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8522,6 +8684,9 @@
       <c r="CB1" s="1" t="n">
         <v>20251218</v>
       </c>
+      <c r="CC1" s="1" t="n">
+        <v>20251219</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8768,6 +8933,9 @@
       <c r="CB2" t="n">
         <v>273.63</v>
       </c>
+      <c r="CC2" t="n">
+        <v>274.6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9014,6 +9182,9 @@
       <c r="CB3" t="n">
         <v>229.225</v>
       </c>
+      <c r="CC3" t="n">
+        <v>229.125</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9260,6 +9431,9 @@
       <c r="CB4" t="n">
         <v>303.96</v>
       </c>
+      <c r="CC4" t="n">
+        <v>307.25</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9506,6 +9680,9 @@
       <c r="CB5" t="n">
         <v>489.6</v>
       </c>
+      <c r="CC5" t="n">
+        <v>487.85</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9752,6 +9929,9 @@
       <c r="CB6" t="n">
         <v>95.81</v>
       </c>
+      <c r="CC6" t="n">
+        <v>95.54000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9998,6 +10178,9 @@
       <c r="CB7" t="n">
         <v>176.15</v>
       </c>
+      <c r="CC7" t="n">
+        <v>181.45</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10244,6 +10427,9 @@
       <c r="CB8" t="n">
         <v>187.33</v>
       </c>
+      <c r="CC8" t="n">
+        <v>195</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10490,6 +10676,9 @@
       <c r="CB9" t="n">
         <v>90.575</v>
       </c>
+      <c r="CC9" t="n">
+        <v>89.26000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10735,6 +10924,9 @@
       </c>
       <c r="CB10" t="n">
         <v>490.86</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>490.49</v>
       </c>
     </row>
   </sheetData>
@@ -10748,7 +10940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10831,6 +11023,7 @@
     <col width="12" customWidth="1" min="78" max="78"/>
     <col width="12" customWidth="1" min="79" max="79"/>
     <col width="12" customWidth="1" min="80" max="80"/>
+    <col width="12" customWidth="1" min="81" max="81"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11078,6 +11271,9 @@
       <c r="CB1" s="1" t="n">
         <v>20251218</v>
       </c>
+      <c r="CC1" s="1" t="n">
+        <v>20251219</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11324,6 +11520,9 @@
       <c r="CB2" t="n">
         <v>266.95</v>
       </c>
+      <c r="CC2" t="n">
+        <v>269.9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11570,6 +11769,9 @@
       <c r="CB3" t="n">
         <v>224.41</v>
       </c>
+      <c r="CC3" t="n">
+        <v>225.58</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11816,6 +12018,9 @@
       <c r="CB4" t="n">
         <v>299.2308</v>
       </c>
+      <c r="CC4" t="n">
+        <v>300.97</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12062,6 +12267,9 @@
       <c r="CB5" t="n">
         <v>477.89</v>
       </c>
+      <c r="CC5" t="n">
+        <v>482.49</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12308,6 +12516,9 @@
       <c r="CB6" t="n">
         <v>93.59</v>
       </c>
+      <c r="CC6" t="n">
+        <v>93.45</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12554,6 +12765,9 @@
       <c r="CB7" t="n">
         <v>171.82</v>
       </c>
+      <c r="CC7" t="n">
+        <v>176.34</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12800,6 +13014,9 @@
       <c r="CB8" t="n">
         <v>181.51</v>
       </c>
+      <c r="CC8" t="n">
+        <v>186.73</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13046,6 +13263,9 @@
       <c r="CB9" t="n">
         <v>87.3</v>
       </c>
+      <c r="CC9" t="n">
+        <v>88.25</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13291,6 +13511,9 @@
       </c>
       <c r="CB10" t="n">
         <v>473.12</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>474.72</v>
       </c>
     </row>
   </sheetData>
@@ -13304,7 +13527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13387,6 +13610,7 @@
     <col width="12" customWidth="1" min="78" max="78"/>
     <col width="12" customWidth="1" min="79" max="79"/>
     <col width="12" customWidth="1" min="80" max="80"/>
+    <col width="12" customWidth="1" min="81" max="81"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13634,6 +13858,9 @@
       <c r="CB1" s="1" t="n">
         <v>20251218</v>
       </c>
+      <c r="CC1" s="1" t="n">
+        <v>20251219</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13880,6 +14107,9 @@
       <c r="CB2" t="n">
         <v>272.19</v>
       </c>
+      <c r="CC2" t="n">
+        <v>273.67</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14126,6 +14356,9 @@
       <c r="CB3" t="n">
         <v>226.76</v>
       </c>
+      <c r="CC3" t="n">
+        <v>227.35</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14372,6 +14605,9 @@
       <c r="CB4" t="n">
         <v>302.46</v>
       </c>
+      <c r="CC4" t="n">
+        <v>307.16</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14618,6 +14854,9 @@
       <c r="CB5" t="n">
         <v>483.98</v>
       </c>
+      <c r="CC5" t="n">
+        <v>485.92</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14864,6 +15103,9 @@
       <c r="CB6" t="n">
         <v>94</v>
       </c>
+      <c r="CC6" t="n">
+        <v>94.39</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15110,6 +15352,9 @@
       <c r="CB7" t="n">
         <v>174.14</v>
       </c>
+      <c r="CC7" t="n">
+        <v>180.99</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15356,6 +15601,9 @@
       <c r="CB8" t="n">
         <v>185.69</v>
       </c>
+      <c r="CC8" t="n">
+        <v>193.38</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15602,6 +15850,9 @@
       <c r="CB9" t="n">
         <v>89.42</v>
       </c>
+      <c r="CC9" t="n">
+        <v>88.33</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15847,6 +16098,9 @@
       </c>
       <c r="CB10" t="n">
         <v>483.37</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>481.2</v>
       </c>
     </row>
   </sheetData>
@@ -15860,7 +16114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15943,6 +16197,7 @@
     <col width="12" customWidth="1" min="78" max="78"/>
     <col width="12" customWidth="1" min="79" max="79"/>
     <col width="12" customWidth="1" min="80" max="80"/>
+    <col width="12" customWidth="1" min="81" max="81"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16190,6 +16445,9 @@
       <c r="CB1" s="1" t="n">
         <v>20251218</v>
       </c>
+      <c r="CC1" s="1" t="n">
+        <v>20251219</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16436,6 +16694,9 @@
       <c r="CB2" t="n">
         <v>51630721</v>
       </c>
+      <c r="CC2" t="n">
+        <v>144632048</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16682,6 +16943,9 @@
       <c r="CB3" t="n">
         <v>50272419</v>
       </c>
+      <c r="CC3" t="n">
+        <v>85544374</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16928,6 +17192,9 @@
       <c r="CB4" t="n">
         <v>33518048</v>
       </c>
+      <c r="CC4" t="n">
+        <v>59943239</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -17174,6 +17441,9 @@
       <c r="CB5" t="n">
         <v>28573545</v>
       </c>
+      <c r="CC5" t="n">
+        <v>70836105</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17420,6 +17690,9 @@
       <c r="CB6" t="n">
         <v>37244734</v>
       </c>
+      <c r="CC6" t="n">
+        <v>78990153</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17666,6 +17939,9 @@
       <c r="CB7" t="n">
         <v>176096001</v>
       </c>
+      <c r="CC7" t="n">
+        <v>324925927</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17912,6 +18188,9 @@
       <c r="CB8" t="n">
         <v>40221476</v>
       </c>
+      <c r="CC8" t="n">
+        <v>76929380</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18158,6 +18437,9 @@
       <c r="CB9" t="n">
         <v>16466099</v>
       </c>
+      <c r="CC9" t="n">
+        <v>16986660</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18403,6 +18685,9 @@
       </c>
       <c r="CB10" t="n">
         <v>95168446</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>85313134</v>
       </c>
     </row>
   </sheetData>
@@ -18416,7 +18701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI10"/>
+  <dimension ref="A1:BJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18480,6 +18765,7 @@
     <col width="10" customWidth="1" min="59" max="59"/>
     <col width="10" customWidth="1" min="60" max="60"/>
     <col width="10" customWidth="1" min="61" max="61"/>
+    <col width="10" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18670,6 +18956,9 @@
       <c r="BI1" s="1" t="n">
         <v>20251218</v>
       </c>
+      <c r="BJ1" s="1" t="n">
+        <v>20251219</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18859,6 +19148,9 @@
       <c r="BI2" t="n">
         <v>30</v>
       </c>
+      <c r="BJ2" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19048,6 +19340,9 @@
       <c r="BI3" t="n">
         <v>56</v>
       </c>
+      <c r="BJ3" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19237,6 +19532,9 @@
       <c r="BI4" t="n">
         <v>38</v>
       </c>
+      <c r="BJ4" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19426,6 +19724,9 @@
       <c r="BI5" t="n">
         <v>60</v>
       </c>
+      <c r="BJ5" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19615,6 +19916,9 @@
       <c r="BI6" t="n">
         <v>8</v>
       </c>
+      <c r="BJ6" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19804,6 +20108,9 @@
       <c r="BI7" t="n">
         <v>22</v>
       </c>
+      <c r="BJ7" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19993,6 +20300,9 @@
       <c r="BI8" t="n">
         <v>93</v>
       </c>
+      <c r="BJ8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20182,6 +20492,9 @@
       <c r="BI9" t="n">
         <v>100</v>
       </c>
+      <c r="BJ9" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20370,6 +20683,9 @@
       </c>
       <c r="BI10" t="n">
         <v>93</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -20383,7 +20699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U10"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20407,6 +20723,7 @@
     <col width="10" customWidth="1" min="19" max="19"/>
     <col width="10" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20477,6 +20794,9 @@
       <c r="U1" s="1" t="n">
         <v>20251218</v>
       </c>
+      <c r="V1" s="1" t="n">
+        <v>20251219</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20546,6 +20866,9 @@
       <c r="U2" t="n">
         <v>66</v>
       </c>
+      <c r="V2" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20615,6 +20938,9 @@
       <c r="U3" t="n">
         <v>33</v>
       </c>
+      <c r="V3" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20684,6 +21010,9 @@
       <c r="U4" t="n">
         <v>76</v>
       </c>
+      <c r="V4" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20753,6 +21082,9 @@
       <c r="U5" t="n">
         <v>17</v>
       </c>
+      <c r="V5" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20822,6 +21154,9 @@
       <c r="U6" t="n">
         <v>0</v>
       </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20891,6 +21226,9 @@
       <c r="U7" t="n">
         <v>9</v>
       </c>
+      <c r="V7" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20960,6 +21298,9 @@
       <c r="U8" t="n">
         <v>59</v>
       </c>
+      <c r="V8" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21029,6 +21370,9 @@
       <c r="U9" t="n">
         <v>100</v>
       </c>
+      <c r="V9" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21097,6 +21441,9 @@
       </c>
       <c r="U10" t="n">
         <v>93</v>
+      </c>
+      <c r="V10" t="n">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -21110,7 +21457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI10"/>
+  <dimension ref="A1:BJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21174,6 +21521,7 @@
     <col width="10" customWidth="1" min="59" max="59"/>
     <col width="10" customWidth="1" min="60" max="60"/>
     <col width="10" customWidth="1" min="61" max="61"/>
+    <col width="10" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21364,6 +21712,9 @@
       <c r="BI1" s="1" t="n">
         <v>20251218</v>
       </c>
+      <c r="BJ1" s="1" t="n">
+        <v>20251219</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21553,6 +21904,9 @@
       <c r="BI2" t="n">
         <v>-53</v>
       </c>
+      <c r="BJ2" t="n">
+        <v>-48</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21742,6 +22096,9 @@
       <c r="BI3" t="n">
         <v>-9</v>
       </c>
+      <c r="BJ3" t="n">
+        <v>-9</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -21931,6 +22288,9 @@
       <c r="BI4" t="n">
         <v>-53</v>
       </c>
+      <c r="BJ4" t="n">
+        <v>-40</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -22120,6 +22480,9 @@
       <c r="BI5" t="n">
         <v>19</v>
       </c>
+      <c r="BJ5" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -22309,6 +22672,9 @@
       <c r="BI6" t="n">
         <v>-56</v>
       </c>
+      <c r="BJ6" t="n">
+        <v>-48</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -22498,6 +22864,9 @@
       <c r="BI7" t="n">
         <v>-73</v>
       </c>
+      <c r="BJ7" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22687,6 +23056,9 @@
       <c r="BI8" t="n">
         <v>50</v>
       </c>
+      <c r="BJ8" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22876,6 +23248,9 @@
       <c r="BI9" t="n">
         <v>129</v>
       </c>
+      <c r="BJ9" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23064,6 +23439,9 @@
       </c>
       <c r="BI10" t="n">
         <v>78</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:W10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -626,6 +626,7 @@
     <col width="10" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -699,6 +700,9 @@
       <c r="V1" s="1" t="n">
         <v>20251219</v>
       </c>
+      <c r="W1" s="1" t="n">
+        <v>20251222</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -771,6 +775,9 @@
       <c r="V2" t="n">
         <v>31</v>
       </c>
+      <c r="W2" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -843,6 +850,9 @@
       <c r="V3" t="n">
         <v>-4</v>
       </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -915,6 +925,9 @@
       <c r="V4" t="n">
         <v>48</v>
       </c>
+      <c r="W4" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -987,6 +1000,9 @@
       <c r="V5" t="n">
         <v>-47</v>
       </c>
+      <c r="W5" t="n">
+        <v>-48</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1059,6 +1075,9 @@
       <c r="V6" t="n">
         <v>-61</v>
       </c>
+      <c r="W6" t="n">
+        <v>-59</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1131,6 +1150,9 @@
       <c r="V7" t="n">
         <v>-30</v>
       </c>
+      <c r="W7" t="n">
+        <v>-14</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1203,6 +1225,9 @@
       <c r="V8" t="n">
         <v>65</v>
       </c>
+      <c r="W8" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1275,6 +1300,9 @@
       <c r="V9" t="n">
         <v>89</v>
       </c>
+      <c r="W9" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1346,6 +1374,9 @@
       </c>
       <c r="V10" t="n">
         <v>98</v>
+      </c>
+      <c r="W10" t="n">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -1359,7 +1390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ10"/>
+  <dimension ref="A1:BK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1424,6 +1455,7 @@
     <col width="12" customWidth="1" min="60" max="60"/>
     <col width="12" customWidth="1" min="61" max="61"/>
     <col width="12" customWidth="1" min="62" max="62"/>
+    <col width="12" customWidth="1" min="63" max="63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1737,6 +1769,11 @@
           <t>20251219</t>
         </is>
       </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>20251222</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1929,6 +1966,9 @@
       <c r="BJ2" t="n">
         <v>99</v>
       </c>
+      <c r="BK2" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2121,6 +2161,9 @@
       <c r="BJ3" t="n">
         <v>100</v>
       </c>
+      <c r="BK3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2313,6 +2356,9 @@
       <c r="BJ4" t="n">
         <v>98</v>
       </c>
+      <c r="BK4" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2505,6 +2551,9 @@
       <c r="BJ5" t="n">
         <v>101</v>
       </c>
+      <c r="BK5" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2697,6 +2746,9 @@
       <c r="BJ6" t="n">
         <v>94</v>
       </c>
+      <c r="BK6" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2889,6 +2941,9 @@
       <c r="BJ7" t="n">
         <v>101</v>
       </c>
+      <c r="BK7" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3081,6 +3136,9 @@
       <c r="BJ8" t="n">
         <v>109</v>
       </c>
+      <c r="BK8" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3273,6 +3331,9 @@
       <c r="BJ9" t="n">
         <v>103</v>
       </c>
+      <c r="BK9" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3463,6 +3524,9 @@
         <v>109</v>
       </c>
       <c r="BJ10" t="n">
+        <v>108</v>
+      </c>
+      <c r="BK10" t="n">
         <v>108</v>
       </c>
     </row>
@@ -3477,7 +3541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ10"/>
+  <dimension ref="A1:AR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3523,6 +3587,7 @@
     <col width="12" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="12" customWidth="1" min="43" max="43"/>
+    <col width="12" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3741,6 +3806,11 @@
           <t>20251219</t>
         </is>
       </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>20251222</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3876,6 +3946,9 @@
       <c r="AQ2" t="n">
         <v>-16.44</v>
       </c>
+      <c r="AR2" t="n">
+        <v>-17.11</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4011,6 +4084,9 @@
       <c r="AQ3" t="n">
         <v>-49.9</v>
       </c>
+      <c r="AR3" t="n">
+        <v>-52.36</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4146,6 +4222,9 @@
       <c r="AQ4" t="n">
         <v>-44.65</v>
       </c>
+      <c r="AR4" t="n">
+        <v>-49.08</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4281,6 +4360,9 @@
       <c r="AQ5" t="n">
         <v>-48.57</v>
       </c>
+      <c r="AR5" t="n">
+        <v>-49.41</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4416,6 +4498,9 @@
       <c r="AQ6" t="n">
         <v>-98.25</v>
       </c>
+      <c r="AR6" t="n">
+        <v>-98.09</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4551,6 +4636,9 @@
       <c r="AQ7" t="n">
         <v>-35.49</v>
       </c>
+      <c r="AR7" t="n">
+        <v>-31.07</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4686,6 +4774,9 @@
       <c r="AQ8" t="n">
         <v>-10.41</v>
       </c>
+      <c r="AR8" t="n">
+        <v>-14.73</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4821,6 +4912,9 @@
       <c r="AQ9" t="n">
         <v>-0.51</v>
       </c>
+      <c r="AR9" t="n">
+        <v>1.25</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4955,6 +5049,9 @@
       </c>
       <c r="AQ10" t="n">
         <v>11.18</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.76</v>
       </c>
     </row>
   </sheetData>
@@ -4968,7 +5065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:W10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4993,6 +5090,7 @@
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5106,6 +5204,11 @@
           <t>20251219</t>
         </is>
       </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>20251222</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5178,6 +5281,9 @@
       <c r="V2" t="n">
         <v>153</v>
       </c>
+      <c r="W2" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5250,6 +5356,9 @@
       <c r="V3" t="n">
         <v>90</v>
       </c>
+      <c r="W3" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5322,6 +5431,9 @@
       <c r="V4" t="n">
         <v>81</v>
       </c>
+      <c r="W4" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5394,6 +5506,9 @@
       <c r="V5" t="n">
         <v>151</v>
       </c>
+      <c r="W5" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5466,6 +5581,9 @@
       <c r="V6" t="n">
         <v>179</v>
       </c>
+      <c r="W6" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5538,6 +5656,9 @@
       <c r="V7" t="n">
         <v>84</v>
       </c>
+      <c r="W7" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5610,6 +5731,9 @@
       <c r="V8" t="n">
         <v>77</v>
       </c>
+      <c r="W8" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5682,6 +5806,9 @@
       <c r="V9" t="n">
         <v>84</v>
       </c>
+      <c r="W9" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5753,6 +5880,9 @@
       </c>
       <c r="V10" t="n">
         <v>50</v>
+      </c>
+      <c r="W10" t="n">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -5766,7 +5896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CC10"/>
+  <dimension ref="A1:CD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5850,6 +5980,7 @@
     <col width="12" customWidth="1" min="79" max="79"/>
     <col width="12" customWidth="1" min="80" max="80"/>
     <col width="12" customWidth="1" min="81" max="81"/>
+    <col width="12" customWidth="1" min="82" max="82"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6100,6 +6231,9 @@
       <c r="CC1" s="1" t="n">
         <v>20251219</v>
       </c>
+      <c r="CD1" s="1" t="n">
+        <v>20251222</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6349,6 +6483,9 @@
       <c r="CC2" t="n">
         <v>272.145</v>
       </c>
+      <c r="CD2" t="n">
+        <v>272.86</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6598,6 +6735,9 @@
       <c r="CC3" t="n">
         <v>226.76</v>
       </c>
+      <c r="CD3" t="n">
+        <v>228.61</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6847,6 +6987,9 @@
       <c r="CC4" t="n">
         <v>301.73</v>
       </c>
+      <c r="CD4" t="n">
+        <v>309.875</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7096,6 +7239,9 @@
       <c r="CC5" t="n">
         <v>487.36</v>
       </c>
+      <c r="CD5" t="n">
+        <v>486.12</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7345,6 +7491,9 @@
       <c r="CC6" t="n">
         <v>93.56999999999999</v>
       </c>
+      <c r="CD6" t="n">
+        <v>94.70999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7594,6 +7743,9 @@
       <c r="CC7" t="n">
         <v>176.665</v>
       </c>
+      <c r="CD7" t="n">
+        <v>183.92</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7843,6 +7995,9 @@
       <c r="CC8" t="n">
         <v>186.74</v>
       </c>
+      <c r="CD8" t="n">
+        <v>195.04</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8092,6 +8247,9 @@
       <c r="CC9" t="n">
         <v>89.215</v>
       </c>
+      <c r="CD9" t="n">
+        <v>88.16</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8340,6 +8498,9 @@
       </c>
       <c r="CC10" t="n">
         <v>488.12</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>489.88</v>
       </c>
     </row>
   </sheetData>
@@ -8353,7 +8514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CC10"/>
+  <dimension ref="A1:CD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8437,6 +8598,7 @@
     <col width="12" customWidth="1" min="79" max="79"/>
     <col width="12" customWidth="1" min="80" max="80"/>
     <col width="12" customWidth="1" min="81" max="81"/>
+    <col width="12" customWidth="1" min="82" max="82"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8687,6 +8849,9 @@
       <c r="CC1" s="1" t="n">
         <v>20251219</v>
       </c>
+      <c r="CD1" s="1" t="n">
+        <v>20251222</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8936,6 +9101,9 @@
       <c r="CC2" t="n">
         <v>274.6</v>
       </c>
+      <c r="CD2" t="n">
+        <v>273.88</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9185,6 +9353,9 @@
       <c r="CC3" t="n">
         <v>229.125</v>
       </c>
+      <c r="CD3" t="n">
+        <v>229.48</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9434,6 +9605,9 @@
       <c r="CC4" t="n">
         <v>307.25</v>
       </c>
+      <c r="CD4" t="n">
+        <v>310.13</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9683,6 +9857,9 @@
       <c r="CC5" t="n">
         <v>487.85</v>
       </c>
+      <c r="CD5" t="n">
+        <v>488.73</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9932,6 +10109,9 @@
       <c r="CC6" t="n">
         <v>95.54000000000001</v>
       </c>
+      <c r="CD6" t="n">
+        <v>94.70999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10181,6 +10361,9 @@
       <c r="CC7" t="n">
         <v>181.45</v>
       </c>
+      <c r="CD7" t="n">
+        <v>184.16</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10430,6 +10613,9 @@
       <c r="CC8" t="n">
         <v>195</v>
       </c>
+      <c r="CD8" t="n">
+        <v>198.88</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10679,6 +10865,9 @@
       <c r="CC9" t="n">
         <v>89.26000000000001</v>
       </c>
+      <c r="CD9" t="n">
+        <v>88.62</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10927,6 +11116,9 @@
       </c>
       <c r="CC10" t="n">
         <v>490.49</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>498.83</v>
       </c>
     </row>
   </sheetData>
@@ -10940,7 +11132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CC10"/>
+  <dimension ref="A1:CD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11024,6 +11216,7 @@
     <col width="12" customWidth="1" min="79" max="79"/>
     <col width="12" customWidth="1" min="80" max="80"/>
     <col width="12" customWidth="1" min="81" max="81"/>
+    <col width="12" customWidth="1" min="82" max="82"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11274,6 +11467,9 @@
       <c r="CC1" s="1" t="n">
         <v>20251219</v>
       </c>
+      <c r="CD1" s="1" t="n">
+        <v>20251222</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11523,6 +11719,9 @@
       <c r="CC2" t="n">
         <v>269.9</v>
       </c>
+      <c r="CD2" t="n">
+        <v>270.505</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11772,6 +11971,9 @@
       <c r="CC3" t="n">
         <v>225.58</v>
       </c>
+      <c r="CD3" t="n">
+        <v>226.71</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12021,6 +12223,9 @@
       <c r="CC4" t="n">
         <v>300.97</v>
       </c>
+      <c r="CD4" t="n">
+        <v>305.3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12270,6 +12475,9 @@
       <c r="CC5" t="n">
         <v>482.49</v>
       </c>
+      <c r="CD5" t="n">
+        <v>482.69</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12519,6 +12727,9 @@
       <c r="CC6" t="n">
         <v>93.45</v>
       </c>
+      <c r="CD6" t="n">
+        <v>92.91</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12768,6 +12979,9 @@
       <c r="CC7" t="n">
         <v>176.34</v>
       </c>
+      <c r="CD7" t="n">
+        <v>182.35</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13017,6 +13231,9 @@
       <c r="CC8" t="n">
         <v>186.73</v>
       </c>
+      <c r="CD8" t="n">
+        <v>192.43</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13266,6 +13483,9 @@
       <c r="CC9" t="n">
         <v>88.25</v>
       </c>
+      <c r="CD9" t="n">
+        <v>86.04000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13514,6 +13734,9 @@
       </c>
       <c r="CC10" t="n">
         <v>474.72</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>485.33</v>
       </c>
     </row>
   </sheetData>
@@ -13527,7 +13750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CC10"/>
+  <dimension ref="A1:CD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13611,6 +13834,7 @@
     <col width="12" customWidth="1" min="79" max="79"/>
     <col width="12" customWidth="1" min="80" max="80"/>
     <col width="12" customWidth="1" min="81" max="81"/>
+    <col width="12" customWidth="1" min="82" max="82"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13861,6 +14085,9 @@
       <c r="CC1" s="1" t="n">
         <v>20251219</v>
       </c>
+      <c r="CD1" s="1" t="n">
+        <v>20251222</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14110,6 +14337,9 @@
       <c r="CC2" t="n">
         <v>273.67</v>
       </c>
+      <c r="CD2" t="n">
+        <v>270.97</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14359,6 +14589,9 @@
       <c r="CC3" t="n">
         <v>227.35</v>
       </c>
+      <c r="CD3" t="n">
+        <v>228.43</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14608,6 +14841,9 @@
       <c r="CC4" t="n">
         <v>307.16</v>
       </c>
+      <c r="CD4" t="n">
+        <v>309.78</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14857,6 +15093,9 @@
       <c r="CC5" t="n">
         <v>485.92</v>
       </c>
+      <c r="CD5" t="n">
+        <v>484.92</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15106,6 +15345,9 @@
       <c r="CC6" t="n">
         <v>94.39</v>
       </c>
+      <c r="CD6" t="n">
+        <v>93.23</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15355,6 +15597,9 @@
       <c r="CC7" t="n">
         <v>180.99</v>
       </c>
+      <c r="CD7" t="n">
+        <v>183.69</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15604,6 +15849,9 @@
       <c r="CC8" t="n">
         <v>193.38</v>
       </c>
+      <c r="CD8" t="n">
+        <v>193.98</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15853,6 +16101,9 @@
       <c r="CC9" t="n">
         <v>88.33</v>
       </c>
+      <c r="CD9" t="n">
+        <v>86.17</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16101,6 +16352,9 @@
       </c>
       <c r="CC10" t="n">
         <v>481.2</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>488.73</v>
       </c>
     </row>
   </sheetData>
@@ -16114,7 +16368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CC10"/>
+  <dimension ref="A1:CD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -16198,6 +16452,7 @@
     <col width="12" customWidth="1" min="79" max="79"/>
     <col width="12" customWidth="1" min="80" max="80"/>
     <col width="12" customWidth="1" min="81" max="81"/>
+    <col width="12" customWidth="1" min="82" max="82"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16448,6 +16703,9 @@
       <c r="CC1" s="1" t="n">
         <v>20251219</v>
       </c>
+      <c r="CD1" s="1" t="n">
+        <v>20251222</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16697,6 +16955,9 @@
       <c r="CC2" t="n">
         <v>144632048</v>
       </c>
+      <c r="CD2" t="n">
+        <v>36571827</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16946,6 +17207,9 @@
       <c r="CC3" t="n">
         <v>85544374</v>
       </c>
+      <c r="CD3" t="n">
+        <v>32261329</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17195,6 +17459,9 @@
       <c r="CC4" t="n">
         <v>59943239</v>
       </c>
+      <c r="CD4" t="n">
+        <v>26429937</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -17444,6 +17711,9 @@
       <c r="CC5" t="n">
         <v>70836105</v>
       </c>
+      <c r="CD5" t="n">
+        <v>16963019</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17693,6 +17963,9 @@
       <c r="CC6" t="n">
         <v>78990153</v>
       </c>
+      <c r="CD6" t="n">
+        <v>39484765</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17942,6 +18215,9 @@
       <c r="CC7" t="n">
         <v>324925927</v>
       </c>
+      <c r="CD7" t="n">
+        <v>129064369</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18191,6 +18467,9 @@
       <c r="CC8" t="n">
         <v>76929380</v>
       </c>
+      <c r="CD8" t="n">
+        <v>36686036</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18440,6 +18719,9 @@
       <c r="CC9" t="n">
         <v>16986660</v>
       </c>
+      <c r="CD9" t="n">
+        <v>7161621</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18688,6 +18970,9 @@
       </c>
       <c r="CC10" t="n">
         <v>85313134</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>86916066</v>
       </c>
     </row>
   </sheetData>
@@ -18701,7 +18986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ10"/>
+  <dimension ref="A1:BK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18766,6 +19051,7 @@
     <col width="10" customWidth="1" min="60" max="60"/>
     <col width="10" customWidth="1" min="61" max="61"/>
     <col width="10" customWidth="1" min="62" max="62"/>
+    <col width="10" customWidth="1" min="63" max="63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18959,6 +19245,9 @@
       <c r="BJ1" s="1" t="n">
         <v>20251219</v>
       </c>
+      <c r="BK1" s="1" t="n">
+        <v>20251222</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19151,6 +19440,9 @@
       <c r="BJ2" t="n">
         <v>15</v>
       </c>
+      <c r="BK2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19343,6 +19635,9 @@
       <c r="BJ3" t="n">
         <v>49</v>
       </c>
+      <c r="BK3" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19535,6 +19830,9 @@
       <c r="BJ4" t="n">
         <v>39</v>
       </c>
+      <c r="BK4" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19727,6 +20025,9 @@
       <c r="BJ5" t="n">
         <v>69</v>
       </c>
+      <c r="BK5" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19919,6 +20220,9 @@
       <c r="BJ6" t="n">
         <v>10</v>
       </c>
+      <c r="BK6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20111,6 +20415,9 @@
       <c r="BJ7" t="n">
         <v>69</v>
       </c>
+      <c r="BK7" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20303,6 +20610,9 @@
       <c r="BJ8" t="n">
         <v>100</v>
       </c>
+      <c r="BK8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20495,6 +20805,9 @@
       <c r="BJ9" t="n">
         <v>85</v>
       </c>
+      <c r="BK9" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20686,6 +20999,9 @@
       </c>
       <c r="BJ10" t="n">
         <v>91</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -20699,7 +21015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:W10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20724,6 +21040,7 @@
     <col width="10" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20797,6 +21114,9 @@
       <c r="V1" s="1" t="n">
         <v>20251219</v>
       </c>
+      <c r="W1" s="1" t="n">
+        <v>20251222</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20869,6 +21189,9 @@
       <c r="V2" t="n">
         <v>69</v>
       </c>
+      <c r="W2" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20941,6 +21264,9 @@
       <c r="V3" t="n">
         <v>35</v>
       </c>
+      <c r="W3" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -21013,6 +21339,9 @@
       <c r="V4" t="n">
         <v>81</v>
       </c>
+      <c r="W4" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -21085,6 +21414,9 @@
       <c r="V5" t="n">
         <v>20</v>
       </c>
+      <c r="W5" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21157,6 +21489,9 @@
       <c r="V6" t="n">
         <v>0</v>
       </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21229,6 +21564,9 @@
       <c r="V7" t="n">
         <v>28</v>
       </c>
+      <c r="W7" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21301,6 +21639,9 @@
       <c r="V8" t="n">
         <v>74</v>
       </c>
+      <c r="W8" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21373,6 +21714,9 @@
       <c r="V9" t="n">
         <v>90</v>
       </c>
+      <c r="W9" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21444,6 +21788,9 @@
       </c>
       <c r="V10" t="n">
         <v>91</v>
+      </c>
+      <c r="W10" t="n">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -21457,7 +21804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ10"/>
+  <dimension ref="A1:BK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21522,6 +21869,7 @@
     <col width="10" customWidth="1" min="60" max="60"/>
     <col width="10" customWidth="1" min="61" max="61"/>
     <col width="10" customWidth="1" min="62" max="62"/>
+    <col width="10" customWidth="1" min="63" max="63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21715,6 +22063,9 @@
       <c r="BJ1" s="1" t="n">
         <v>20251219</v>
       </c>
+      <c r="BK1" s="1" t="n">
+        <v>20251222</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21907,6 +22258,9 @@
       <c r="BJ2" t="n">
         <v>-48</v>
       </c>
+      <c r="BK2" t="n">
+        <v>-81</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22099,6 +22453,9 @@
       <c r="BJ3" t="n">
         <v>-9</v>
       </c>
+      <c r="BK3" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22291,6 +22648,9 @@
       <c r="BJ4" t="n">
         <v>-40</v>
       </c>
+      <c r="BK4" t="n">
+        <v>-28</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -22483,6 +22843,9 @@
       <c r="BJ5" t="n">
         <v>31</v>
       </c>
+      <c r="BK5" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -22675,6 +23038,9 @@
       <c r="BJ6" t="n">
         <v>-48</v>
       </c>
+      <c r="BK6" t="n">
+        <v>-52</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -22867,6 +23233,9 @@
       <c r="BJ7" t="n">
         <v>17</v>
       </c>
+      <c r="BK7" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23059,6 +23428,9 @@
       <c r="BJ8" t="n">
         <v>79</v>
       </c>
+      <c r="BK8" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23251,6 +23623,9 @@
       <c r="BJ9" t="n">
         <v>86</v>
       </c>
+      <c r="BK9" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23442,6 +23817,9 @@
       </c>
       <c r="BJ10" t="n">
         <v>68</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W10"/>
+  <dimension ref="A1:X10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -627,6 +627,7 @@
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
     <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -703,6 +704,9 @@
       <c r="W1" s="1" t="n">
         <v>20251222</v>
       </c>
+      <c r="X1" s="1" t="n">
+        <v>20251223</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -778,6 +782,9 @@
       <c r="W2" t="n">
         <v>17</v>
       </c>
+      <c r="X2" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -853,6 +860,9 @@
       <c r="W3" t="n">
         <v>1</v>
       </c>
+      <c r="X3" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -928,6 +938,9 @@
       <c r="W4" t="n">
         <v>51</v>
       </c>
+      <c r="X4" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1003,6 +1016,9 @@
       <c r="W5" t="n">
         <v>-48</v>
       </c>
+      <c r="X5" t="n">
+        <v>-42</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1078,6 +1094,9 @@
       <c r="W6" t="n">
         <v>-59</v>
       </c>
+      <c r="X6" t="n">
+        <v>-57</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1153,6 +1172,9 @@
       <c r="W7" t="n">
         <v>-14</v>
       </c>
+      <c r="X7" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1228,6 +1250,9 @@
       <c r="W8" t="n">
         <v>66</v>
       </c>
+      <c r="X8" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1303,6 +1328,9 @@
       <c r="W9" t="n">
         <v>40</v>
       </c>
+      <c r="X9" t="n">
+        <v>-10</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1377,6 +1405,9 @@
       </c>
       <c r="W10" t="n">
         <v>109</v>
+      </c>
+      <c r="X10" t="n">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1390,7 +1421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK10"/>
+  <dimension ref="A1:BL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1456,6 +1487,7 @@
     <col width="12" customWidth="1" min="61" max="61"/>
     <col width="12" customWidth="1" min="62" max="62"/>
     <col width="12" customWidth="1" min="63" max="63"/>
+    <col width="12" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1774,6 +1806,11 @@
           <t>20251222</t>
         </is>
       </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>20251223</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1969,6 +2006,9 @@
       <c r="BK2" t="n">
         <v>98</v>
       </c>
+      <c r="BL2" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2164,6 +2204,9 @@
       <c r="BK3" t="n">
         <v>100</v>
       </c>
+      <c r="BL3" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2359,6 +2402,9 @@
       <c r="BK4" t="n">
         <v>99</v>
       </c>
+      <c r="BL4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2554,6 +2600,9 @@
       <c r="BK5" t="n">
         <v>100</v>
       </c>
+      <c r="BL5" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2749,6 +2798,9 @@
       <c r="BK6" t="n">
         <v>94</v>
       </c>
+      <c r="BL6" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2944,6 +2996,9 @@
       <c r="BK7" t="n">
         <v>102</v>
       </c>
+      <c r="BL7" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3139,6 +3194,9 @@
       <c r="BK8" t="n">
         <v>108</v>
       </c>
+      <c r="BL8" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3334,6 +3392,9 @@
       <c r="BK9" t="n">
         <v>101</v>
       </c>
+      <c r="BL9" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3528,6 +3589,9 @@
       </c>
       <c r="BK10" t="n">
         <v>108</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -3541,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR10"/>
+  <dimension ref="A1:AS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3588,6 +3652,7 @@
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="12" customWidth="1" min="43" max="43"/>
     <col width="12" customWidth="1" min="44" max="44"/>
+    <col width="12" customWidth="1" min="45" max="45"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3811,6 +3876,11 @@
           <t>20251222</t>
         </is>
       </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>20251223</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3949,6 +4019,9 @@
       <c r="AR2" t="n">
         <v>-17.11</v>
       </c>
+      <c r="AS2" t="n">
+        <v>-15.46</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4087,6 +4160,9 @@
       <c r="AR3" t="n">
         <v>-52.36</v>
       </c>
+      <c r="AS3" t="n">
+        <v>-49.14</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4225,6 +4301,9 @@
       <c r="AR4" t="n">
         <v>-49.08</v>
       </c>
+      <c r="AS4" t="n">
+        <v>-49.06</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4363,6 +4442,9 @@
       <c r="AR5" t="n">
         <v>-49.41</v>
       </c>
+      <c r="AS5" t="n">
+        <v>-49.02</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4501,6 +4583,9 @@
       <c r="AR6" t="n">
         <v>-98.09</v>
       </c>
+      <c r="AS6" t="n">
+        <v>-97.98</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4639,6 +4724,9 @@
       <c r="AR7" t="n">
         <v>-31.07</v>
       </c>
+      <c r="AS7" t="n">
+        <v>-19.09</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4777,6 +4865,9 @@
       <c r="AR8" t="n">
         <v>-14.73</v>
       </c>
+      <c r="AS8" t="n">
+        <v>-14.85</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4915,6 +5006,9 @@
       <c r="AR9" t="n">
         <v>1.25</v>
       </c>
+      <c r="AS9" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5052,6 +5146,9 @@
       </c>
       <c r="AR10" t="n">
         <v>2.76</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2.05</v>
       </c>
     </row>
   </sheetData>
@@ -5065,7 +5162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W10"/>
+  <dimension ref="A1:X10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5091,6 +5188,7 @@
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5209,6 +5307,11 @@
           <t>20251222</t>
         </is>
       </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>20251223</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5284,6 +5387,9 @@
       <c r="W2" t="n">
         <v>39</v>
       </c>
+      <c r="X2" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5359,6 +5465,9 @@
       <c r="W3" t="n">
         <v>34</v>
       </c>
+      <c r="X3" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5434,6 +5543,9 @@
       <c r="W4" t="n">
         <v>36</v>
       </c>
+      <c r="X4" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5509,6 +5621,9 @@
       <c r="W5" t="n">
         <v>36</v>
       </c>
+      <c r="X5" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5584,6 +5699,9 @@
       <c r="W6" t="n">
         <v>87</v>
       </c>
+      <c r="X6" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5659,6 +5777,9 @@
       <c r="W7" t="n">
         <v>34</v>
       </c>
+      <c r="X7" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5734,6 +5855,9 @@
       <c r="W8" t="n">
         <v>37</v>
       </c>
+      <c r="X8" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5809,6 +5933,9 @@
       <c r="W9" t="n">
         <v>35</v>
       </c>
+      <c r="X9" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5883,6 +6010,9 @@
       </c>
       <c r="W10" t="n">
         <v>51</v>
+      </c>
+      <c r="X10" t="n">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -5896,7 +6026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CD10"/>
+  <dimension ref="A1:CE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5981,6 +6111,7 @@
     <col width="12" customWidth="1" min="80" max="80"/>
     <col width="12" customWidth="1" min="81" max="81"/>
     <col width="12" customWidth="1" min="82" max="82"/>
+    <col width="12" customWidth="1" min="83" max="83"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6234,6 +6365,9 @@
       <c r="CD1" s="1" t="n">
         <v>20251222</v>
       </c>
+      <c r="CE1" s="1" t="n">
+        <v>20251223</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6486,6 +6620,9 @@
       <c r="CD2" t="n">
         <v>272.86</v>
       </c>
+      <c r="CE2" t="n">
+        <v>270.84</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6738,6 +6875,9 @@
       <c r="CD3" t="n">
         <v>228.61</v>
       </c>
+      <c r="CE3" t="n">
+        <v>229.055</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6990,6 +7130,9 @@
       <c r="CD4" t="n">
         <v>309.875</v>
       </c>
+      <c r="CE4" t="n">
+        <v>309.625</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7242,6 +7385,9 @@
       <c r="CD5" t="n">
         <v>486.12</v>
       </c>
+      <c r="CE5" t="n">
+        <v>484.98</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7494,6 +7640,9 @@
       <c r="CD6" t="n">
         <v>94.70999999999999</v>
       </c>
+      <c r="CE6" t="n">
+        <v>93.395</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7746,6 +7895,9 @@
       <c r="CD7" t="n">
         <v>183.92</v>
       </c>
+      <c r="CE7" t="n">
+        <v>182.97</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7998,6 +8150,9 @@
       <c r="CD8" t="n">
         <v>195.04</v>
       </c>
+      <c r="CE8" t="n">
+        <v>192.825</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8250,6 +8405,9 @@
       <c r="CD9" t="n">
         <v>88.16</v>
       </c>
+      <c r="CE9" t="n">
+        <v>86.02</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8501,6 +8659,9 @@
       </c>
       <c r="CD10" t="n">
         <v>489.88</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>489.395</v>
       </c>
     </row>
   </sheetData>
@@ -8514,7 +8675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CD10"/>
+  <dimension ref="A1:CE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8599,6 +8760,7 @@
     <col width="12" customWidth="1" min="80" max="80"/>
     <col width="12" customWidth="1" min="81" max="81"/>
     <col width="12" customWidth="1" min="82" max="82"/>
+    <col width="12" customWidth="1" min="83" max="83"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8852,6 +9014,9 @@
       <c r="CD1" s="1" t="n">
         <v>20251222</v>
       </c>
+      <c r="CE1" s="1" t="n">
+        <v>20251223</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9104,6 +9269,9 @@
       <c r="CD2" t="n">
         <v>273.88</v>
       </c>
+      <c r="CE2" t="n">
+        <v>272.5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9356,6 +9524,9 @@
       <c r="CD3" t="n">
         <v>229.48</v>
       </c>
+      <c r="CE3" t="n">
+        <v>232.445</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9608,6 +9779,9 @@
       <c r="CD4" t="n">
         <v>310.13</v>
       </c>
+      <c r="CE4" t="n">
+        <v>314.94</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9860,6 +10034,9 @@
       <c r="CD5" t="n">
         <v>488.73</v>
       </c>
+      <c r="CE5" t="n">
+        <v>487.83</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10112,6 +10289,9 @@
       <c r="CD6" t="n">
         <v>94.70999999999999</v>
       </c>
+      <c r="CE6" t="n">
+        <v>93.81</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10364,6 +10544,9 @@
       <c r="CD7" t="n">
         <v>184.16</v>
       </c>
+      <c r="CE7" t="n">
+        <v>189.33</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10616,6 +10799,9 @@
       <c r="CD8" t="n">
         <v>198.88</v>
       </c>
+      <c r="CE8" t="n">
+        <v>195.37</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10868,6 +11054,9 @@
       <c r="CD9" t="n">
         <v>88.62</v>
       </c>
+      <c r="CE9" t="n">
+        <v>86.14</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11119,6 +11308,9 @@
       </c>
       <c r="CD10" t="n">
         <v>498.83</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>491.97</v>
       </c>
     </row>
   </sheetData>
@@ -11132,7 +11324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CD10"/>
+  <dimension ref="A1:CE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11217,6 +11409,7 @@
     <col width="12" customWidth="1" min="80" max="80"/>
     <col width="12" customWidth="1" min="81" max="81"/>
     <col width="12" customWidth="1" min="82" max="82"/>
+    <col width="12" customWidth="1" min="83" max="83"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11470,6 +11663,9 @@
       <c r="CD1" s="1" t="n">
         <v>20251222</v>
       </c>
+      <c r="CE1" s="1" t="n">
+        <v>20251223</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11722,6 +11918,9 @@
       <c r="CD2" t="n">
         <v>270.505</v>
       </c>
+      <c r="CE2" t="n">
+        <v>269.56</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11974,6 +12173,9 @@
       <c r="CD3" t="n">
         <v>226.71</v>
       </c>
+      <c r="CE3" t="n">
+        <v>228.73</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12226,6 +12428,9 @@
       <c r="CD4" t="n">
         <v>305.3</v>
       </c>
+      <c r="CE4" t="n">
+        <v>309.32</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12478,6 +12683,9 @@
       <c r="CD5" t="n">
         <v>482.69</v>
       </c>
+      <c r="CE5" t="n">
+        <v>484.74</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12730,6 +12938,9 @@
       <c r="CD6" t="n">
         <v>92.91</v>
       </c>
+      <c r="CE6" t="n">
+        <v>91.33</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12982,6 +13193,9 @@
       <c r="CD7" t="n">
         <v>182.35</v>
       </c>
+      <c r="CE7" t="n">
+        <v>182.9</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13234,6 +13448,9 @@
       <c r="CD8" t="n">
         <v>192.43</v>
       </c>
+      <c r="CE8" t="n">
+        <v>191.7351</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13486,6 +13703,9 @@
       <c r="CD9" t="n">
         <v>86.04000000000001</v>
       </c>
+      <c r="CE9" t="n">
+        <v>83.38</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13737,6 +13957,9 @@
       </c>
       <c r="CD10" t="n">
         <v>485.33</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>482.84</v>
       </c>
     </row>
   </sheetData>
@@ -13750,7 +13973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CD10"/>
+  <dimension ref="A1:CE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13835,6 +14058,7 @@
     <col width="12" customWidth="1" min="80" max="80"/>
     <col width="12" customWidth="1" min="81" max="81"/>
     <col width="12" customWidth="1" min="82" max="82"/>
+    <col width="12" customWidth="1" min="83" max="83"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14088,6 +14312,9 @@
       <c r="CD1" s="1" t="n">
         <v>20251222</v>
       </c>
+      <c r="CE1" s="1" t="n">
+        <v>20251223</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14340,6 +14567,9 @@
       <c r="CD2" t="n">
         <v>270.97</v>
       </c>
+      <c r="CE2" t="n">
+        <v>272.36</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14592,6 +14822,9 @@
       <c r="CD3" t="n">
         <v>228.43</v>
       </c>
+      <c r="CE3" t="n">
+        <v>232.14</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14844,6 +15077,9 @@
       <c r="CD4" t="n">
         <v>309.78</v>
       </c>
+      <c r="CE4" t="n">
+        <v>314.35</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15096,6 +15332,9 @@
       <c r="CD5" t="n">
         <v>484.92</v>
       </c>
+      <c r="CE5" t="n">
+        <v>486.85</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15348,6 +15587,9 @@
       <c r="CD6" t="n">
         <v>93.23</v>
       </c>
+      <c r="CE6" t="n">
+        <v>93.5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15600,6 +15842,9 @@
       <c r="CD7" t="n">
         <v>183.69</v>
       </c>
+      <c r="CE7" t="n">
+        <v>189.21</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15852,6 +16097,9 @@
       <c r="CD8" t="n">
         <v>193.98</v>
       </c>
+      <c r="CE8" t="n">
+        <v>194.13</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16104,6 +16352,9 @@
       <c r="CD9" t="n">
         <v>86.17</v>
       </c>
+      <c r="CE9" t="n">
+        <v>83.86</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16355,6 +16606,9 @@
       </c>
       <c r="CD10" t="n">
         <v>488.73</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>485.56</v>
       </c>
     </row>
   </sheetData>
@@ -16368,7 +16622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CD10"/>
+  <dimension ref="A1:CE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -16453,6 +16707,7 @@
     <col width="12" customWidth="1" min="80" max="80"/>
     <col width="12" customWidth="1" min="81" max="81"/>
     <col width="12" customWidth="1" min="82" max="82"/>
+    <col width="12" customWidth="1" min="83" max="83"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16706,6 +16961,9 @@
       <c r="CD1" s="1" t="n">
         <v>20251222</v>
       </c>
+      <c r="CE1" s="1" t="n">
+        <v>20251223</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16958,6 +17216,9 @@
       <c r="CD2" t="n">
         <v>36571827</v>
       </c>
+      <c r="CE2" t="n">
+        <v>29641999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17210,6 +17471,9 @@
       <c r="CD3" t="n">
         <v>32261329</v>
       </c>
+      <c r="CE3" t="n">
+        <v>29230233</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17462,6 +17726,9 @@
       <c r="CD4" t="n">
         <v>26429937</v>
       </c>
+      <c r="CE4" t="n">
+        <v>25478670</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -17714,6 +17981,9 @@
       <c r="CD5" t="n">
         <v>16963019</v>
       </c>
+      <c r="CE5" t="n">
+        <v>14683582</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17966,6 +18236,9 @@
       <c r="CD6" t="n">
         <v>39484765</v>
       </c>
+      <c r="CE6" t="n">
+        <v>25896234</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18218,6 +18491,9 @@
       <c r="CD7" t="n">
         <v>129064369</v>
       </c>
+      <c r="CE7" t="n">
+        <v>174873621</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18470,6 +18746,9 @@
       <c r="CD8" t="n">
         <v>36686036</v>
       </c>
+      <c r="CE8" t="n">
+        <v>24040968</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18722,6 +19001,9 @@
       <c r="CD9" t="n">
         <v>7161621</v>
       </c>
+      <c r="CE9" t="n">
+        <v>9511322</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18973,6 +19255,9 @@
       </c>
       <c r="CD10" t="n">
         <v>86916066</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>58223633</v>
       </c>
     </row>
   </sheetData>
@@ -18986,7 +19271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK10"/>
+  <dimension ref="A1:BL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -19052,6 +19337,7 @@
     <col width="10" customWidth="1" min="61" max="61"/>
     <col width="10" customWidth="1" min="62" max="62"/>
     <col width="10" customWidth="1" min="63" max="63"/>
+    <col width="10" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19248,6 +19534,9 @@
       <c r="BK1" s="1" t="n">
         <v>20251222</v>
       </c>
+      <c r="BL1" s="1" t="n">
+        <v>20251223</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19443,6 +19732,9 @@
       <c r="BK2" t="n">
         <v>0</v>
       </c>
+      <c r="BL2" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19638,6 +19930,9 @@
       <c r="BK3" t="n">
         <v>54</v>
       </c>
+      <c r="BL3" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19833,6 +20128,9 @@
       <c r="BK4" t="n">
         <v>49</v>
       </c>
+      <c r="BL4" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20028,6 +20326,9 @@
       <c r="BK5" t="n">
         <v>61</v>
       </c>
+      <c r="BL5" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20223,6 +20524,9 @@
       <c r="BK6" t="n">
         <v>3</v>
       </c>
+      <c r="BL6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20418,6 +20722,9 @@
       <c r="BK7" t="n">
         <v>87</v>
       </c>
+      <c r="BL7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20613,6 +20920,9 @@
       <c r="BK8" t="n">
         <v>100</v>
       </c>
+      <c r="BL8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20808,6 +21118,9 @@
       <c r="BK9" t="n">
         <v>54</v>
       </c>
+      <c r="BL9" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21002,6 +21315,9 @@
       </c>
       <c r="BK10" t="n">
         <v>98</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -21015,7 +21331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W10"/>
+  <dimension ref="A1:X10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21041,6 +21357,7 @@
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
     <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21117,6 +21434,9 @@
       <c r="W1" s="1" t="n">
         <v>20251222</v>
       </c>
+      <c r="X1" s="1" t="n">
+        <v>20251223</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21192,6 +21512,9 @@
       <c r="W2" t="n">
         <v>63</v>
       </c>
+      <c r="X2" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21267,6 +21590,9 @@
       <c r="W3" t="n">
         <v>38</v>
       </c>
+      <c r="X3" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -21342,6 +21668,9 @@
       <c r="W4" t="n">
         <v>84</v>
       </c>
+      <c r="X4" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -21417,6 +21746,9 @@
       <c r="W5" t="n">
         <v>18</v>
       </c>
+      <c r="X5" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21492,6 +21824,9 @@
       <c r="W6" t="n">
         <v>0</v>
       </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21567,6 +21902,9 @@
       <c r="W7" t="n">
         <v>35</v>
       </c>
+      <c r="X7" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21642,6 +21980,9 @@
       <c r="W8" t="n">
         <v>75</v>
       </c>
+      <c r="X8" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21717,6 +22058,9 @@
       <c r="W9" t="n">
         <v>70</v>
       </c>
+      <c r="X9" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21791,6 +22135,9 @@
       </c>
       <c r="W10" t="n">
         <v>99</v>
+      </c>
+      <c r="X10" t="n">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -21804,7 +22151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK10"/>
+  <dimension ref="A1:BL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21870,6 +22217,7 @@
     <col width="10" customWidth="1" min="61" max="61"/>
     <col width="10" customWidth="1" min="62" max="62"/>
     <col width="10" customWidth="1" min="63" max="63"/>
+    <col width="10" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22066,6 +22414,9 @@
       <c r="BK1" s="1" t="n">
         <v>20251222</v>
       </c>
+      <c r="BL1" s="1" t="n">
+        <v>20251223</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22261,6 +22612,9 @@
       <c r="BK2" t="n">
         <v>-81</v>
       </c>
+      <c r="BL2" t="n">
+        <v>-59</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22456,6 +22810,9 @@
       <c r="BK3" t="n">
         <v>-1</v>
       </c>
+      <c r="BL3" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22651,6 +23008,9 @@
       <c r="BK4" t="n">
         <v>-28</v>
       </c>
+      <c r="BL4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -22846,6 +23206,9 @@
       <c r="BK5" t="n">
         <v>19</v>
       </c>
+      <c r="BL5" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23041,6 +23404,9 @@
       <c r="BK6" t="n">
         <v>-52</v>
       </c>
+      <c r="BL6" t="n">
+        <v>-45</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23236,6 +23602,9 @@
       <c r="BK7" t="n">
         <v>49</v>
       </c>
+      <c r="BL7" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23431,6 +23800,9 @@
       <c r="BK8" t="n">
         <v>78</v>
       </c>
+      <c r="BL8" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23626,6 +23998,9 @@
       <c r="BK9" t="n">
         <v>20</v>
       </c>
+      <c r="BL9" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23820,6 +24195,9 @@
       </c>
       <c r="BK10" t="n">
         <v>80</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X10"/>
+  <dimension ref="A1:Y10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -628,6 +628,7 @@
     <col width="10" customWidth="1" min="22" max="22"/>
     <col width="10" customWidth="1" min="23" max="23"/>
     <col width="10" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -707,6 +708,9 @@
       <c r="X1" s="1" t="n">
         <v>20251223</v>
       </c>
+      <c r="Y1" s="1" t="n">
+        <v>20251224</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -785,6 +789,9 @@
       <c r="X2" t="n">
         <v>22</v>
       </c>
+      <c r="Y2" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -863,6 +870,9 @@
       <c r="X3" t="n">
         <v>19</v>
       </c>
+      <c r="Y3" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -941,6 +951,9 @@
       <c r="X4" t="n">
         <v>57</v>
       </c>
+      <c r="Y4" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1019,6 +1032,9 @@
       <c r="X5" t="n">
         <v>-42</v>
       </c>
+      <c r="Y5" t="n">
+        <v>-37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1097,6 +1113,9 @@
       <c r="X6" t="n">
         <v>-57</v>
       </c>
+      <c r="Y6" t="n">
+        <v>-55</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1175,6 +1194,9 @@
       <c r="X7" t="n">
         <v>21</v>
       </c>
+      <c r="Y7" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1253,6 +1275,9 @@
       <c r="X8" t="n">
         <v>64</v>
       </c>
+      <c r="Y8" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1331,6 +1356,9 @@
       <c r="X9" t="n">
         <v>-10</v>
       </c>
+      <c r="Y9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1408,6 +1436,9 @@
       </c>
       <c r="X10" t="n">
         <v>97</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1421,7 +1452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL10"/>
+  <dimension ref="A1:BM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1488,6 +1519,7 @@
     <col width="12" customWidth="1" min="62" max="62"/>
     <col width="12" customWidth="1" min="63" max="63"/>
     <col width="12" customWidth="1" min="64" max="64"/>
+    <col width="12" customWidth="1" min="65" max="65"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1811,6 +1843,11 @@
           <t>20251223</t>
         </is>
       </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>20251224</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2009,6 +2046,9 @@
       <c r="BL2" t="n">
         <v>98</v>
       </c>
+      <c r="BM2" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2207,6 +2247,9 @@
       <c r="BL3" t="n">
         <v>101</v>
       </c>
+      <c r="BM3" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2405,6 +2448,9 @@
       <c r="BL4" t="n">
         <v>100</v>
       </c>
+      <c r="BM4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2603,6 +2649,9 @@
       <c r="BL5" t="n">
         <v>101</v>
       </c>
+      <c r="BM5" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2801,6 +2850,9 @@
       <c r="BL6" t="n">
         <v>95</v>
       </c>
+      <c r="BM6" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2999,6 +3051,9 @@
       <c r="BL7" t="n">
         <v>105</v>
       </c>
+      <c r="BM7" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3197,6 +3252,9 @@
       <c r="BL8" t="n">
         <v>108</v>
       </c>
+      <c r="BM8" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3395,6 +3453,9 @@
       <c r="BL9" t="n">
         <v>98</v>
       </c>
+      <c r="BM9" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3592,6 +3653,9 @@
       </c>
       <c r="BL10" t="n">
         <v>107</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -3605,7 +3669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS10"/>
+  <dimension ref="A1:AT10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3653,6 +3717,7 @@
     <col width="12" customWidth="1" min="43" max="43"/>
     <col width="12" customWidth="1" min="44" max="44"/>
     <col width="12" customWidth="1" min="45" max="45"/>
+    <col width="12" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3881,6 +3946,11 @@
           <t>20251223</t>
         </is>
       </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>20251224</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4022,6 +4092,9 @@
       <c r="AS2" t="n">
         <v>-15.46</v>
       </c>
+      <c r="AT2" t="n">
+        <v>-15.13</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4163,6 +4236,9 @@
       <c r="AS3" t="n">
         <v>-49.14</v>
       </c>
+      <c r="AT3" t="n">
+        <v>-45.09</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4304,6 +4380,9 @@
       <c r="AS4" t="n">
         <v>-49.06</v>
       </c>
+      <c r="AT4" t="n">
+        <v>-50.84</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4445,6 +4524,9 @@
       <c r="AS5" t="n">
         <v>-49.02</v>
       </c>
+      <c r="AT5" t="n">
+        <v>-46.96</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4586,6 +4668,9 @@
       <c r="AS6" t="n">
         <v>-97.98</v>
       </c>
+      <c r="AT6" t="n">
+        <v>-97.81</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4727,6 +4812,9 @@
       <c r="AS7" t="n">
         <v>-19.09</v>
       </c>
+      <c r="AT7" t="n">
+        <v>-9.07</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4868,6 +4956,9 @@
       <c r="AS8" t="n">
         <v>-14.85</v>
       </c>
+      <c r="AT8" t="n">
+        <v>-16.13</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5009,6 +5100,9 @@
       <c r="AS9" t="n">
         <v>0.4</v>
       </c>
+      <c r="AT9" t="n">
+        <v>2.07</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5149,6 +5243,9 @@
       </c>
       <c r="AS10" t="n">
         <v>2.05</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>-0.54</v>
       </c>
     </row>
   </sheetData>
@@ -5162,7 +5259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X10"/>
+  <dimension ref="A1:Y10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5189,6 +5286,7 @@
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5312,6 +5410,11 @@
           <t>20251223</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>20251224</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5390,6 +5493,9 @@
       <c r="X2" t="n">
         <v>31</v>
       </c>
+      <c r="Y2" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5468,6 +5574,9 @@
       <c r="X3" t="n">
         <v>31</v>
       </c>
+      <c r="Y3" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5546,6 +5655,9 @@
       <c r="X4" t="n">
         <v>34</v>
       </c>
+      <c r="Y4" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5624,6 +5736,9 @@
       <c r="X5" t="n">
         <v>31</v>
       </c>
+      <c r="Y5" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5702,6 +5817,9 @@
       <c r="X6" t="n">
         <v>56</v>
       </c>
+      <c r="Y6" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5780,6 +5898,9 @@
       <c r="X7" t="n">
         <v>46</v>
       </c>
+      <c r="Y7" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5858,6 +5979,9 @@
       <c r="X8" t="n">
         <v>24</v>
       </c>
+      <c r="Y8" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5936,6 +6060,9 @@
       <c r="X9" t="n">
         <v>47</v>
       </c>
+      <c r="Y9" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6013,6 +6140,9 @@
       </c>
       <c r="X10" t="n">
         <v>34</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -6026,7 +6156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE10"/>
+  <dimension ref="A1:CF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6112,6 +6242,7 @@
     <col width="12" customWidth="1" min="81" max="81"/>
     <col width="12" customWidth="1" min="82" max="82"/>
     <col width="12" customWidth="1" min="83" max="83"/>
+    <col width="12" customWidth="1" min="84" max="84"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6368,6 +6499,9 @@
       <c r="CE1" s="1" t="n">
         <v>20251223</v>
       </c>
+      <c r="CF1" s="1" t="n">
+        <v>20251224</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6623,6 +6757,9 @@
       <c r="CE2" t="n">
         <v>270.84</v>
       </c>
+      <c r="CF2" t="n">
+        <v>272.34</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6878,6 +7015,9 @@
       <c r="CE3" t="n">
         <v>229.055</v>
       </c>
+      <c r="CF3" t="n">
+        <v>232.13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7133,6 +7273,9 @@
       <c r="CE4" t="n">
         <v>309.625</v>
       </c>
+      <c r="CF4" t="n">
+        <v>314.77</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7388,6 +7531,9 @@
       <c r="CE5" t="n">
         <v>484.98</v>
       </c>
+      <c r="CF5" t="n">
+        <v>485.68</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7643,6 +7789,9 @@
       <c r="CE6" t="n">
         <v>93.395</v>
       </c>
+      <c r="CF6" t="n">
+        <v>93.11</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7898,6 +8047,9 @@
       <c r="CE7" t="n">
         <v>182.97</v>
       </c>
+      <c r="CF7" t="n">
+        <v>187.94</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8153,6 +8305,9 @@
       <c r="CE8" t="n">
         <v>192.825</v>
       </c>
+      <c r="CF8" t="n">
+        <v>193.16</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8408,6 +8563,9 @@
       <c r="CE9" t="n">
         <v>86.02</v>
       </c>
+      <c r="CF9" t="n">
+        <v>83.84</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8662,6 +8820,9 @@
       </c>
       <c r="CE10" t="n">
         <v>489.395</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>488.48</v>
       </c>
     </row>
   </sheetData>
@@ -8675,7 +8836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE10"/>
+  <dimension ref="A1:CF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8761,6 +8922,7 @@
     <col width="12" customWidth="1" min="81" max="81"/>
     <col width="12" customWidth="1" min="82" max="82"/>
     <col width="12" customWidth="1" min="83" max="83"/>
+    <col width="12" customWidth="1" min="84" max="84"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9017,6 +9179,9 @@
       <c r="CE1" s="1" t="n">
         <v>20251223</v>
       </c>
+      <c r="CF1" s="1" t="n">
+        <v>20251224</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9272,6 +9437,9 @@
       <c r="CE2" t="n">
         <v>272.5</v>
       </c>
+      <c r="CF2" t="n">
+        <v>275.43</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9527,6 +9695,9 @@
       <c r="CE3" t="n">
         <v>232.445</v>
       </c>
+      <c r="CF3" t="n">
+        <v>232.95</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9782,6 +9953,9 @@
       <c r="CE4" t="n">
         <v>314.94</v>
       </c>
+      <c r="CF4" t="n">
+        <v>315.08</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10037,6 +10211,9 @@
       <c r="CE5" t="n">
         <v>487.83</v>
       </c>
+      <c r="CF5" t="n">
+        <v>489.1625</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10292,6 +10469,9 @@
       <c r="CE6" t="n">
         <v>93.81</v>
       </c>
+      <c r="CF6" t="n">
+        <v>93.68000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10547,6 +10727,9 @@
       <c r="CE7" t="n">
         <v>189.33</v>
       </c>
+      <c r="CF7" t="n">
+        <v>188.91</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10802,6 +10985,9 @@
       <c r="CE8" t="n">
         <v>195.37</v>
       </c>
+      <c r="CF8" t="n">
+        <v>195.17</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11057,6 +11243,9 @@
       <c r="CE9" t="n">
         <v>86.14</v>
       </c>
+      <c r="CF9" t="n">
+        <v>84.61499999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11311,6 +11500,9 @@
       </c>
       <c r="CE10" t="n">
         <v>491.97</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>490.9</v>
       </c>
     </row>
   </sheetData>
@@ -11324,7 +11516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE10"/>
+  <dimension ref="A1:CF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11410,6 +11602,7 @@
     <col width="12" customWidth="1" min="81" max="81"/>
     <col width="12" customWidth="1" min="82" max="82"/>
     <col width="12" customWidth="1" min="83" max="83"/>
+    <col width="12" customWidth="1" min="84" max="84"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11666,6 +11859,9 @@
       <c r="CE1" s="1" t="n">
         <v>20251223</v>
       </c>
+      <c r="CF1" s="1" t="n">
+        <v>20251224</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11921,6 +12117,9 @@
       <c r="CE2" t="n">
         <v>269.56</v>
       </c>
+      <c r="CF2" t="n">
+        <v>272.195</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12176,6 +12375,9 @@
       <c r="CE3" t="n">
         <v>228.73</v>
       </c>
+      <c r="CF3" t="n">
+        <v>231.33</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12431,6 +12633,9 @@
       <c r="CE4" t="n">
         <v>309.32</v>
       </c>
+      <c r="CF4" t="n">
+        <v>311.92</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12686,6 +12891,9 @@
       <c r="CE5" t="n">
         <v>484.74</v>
       </c>
+      <c r="CF5" t="n">
+        <v>484.83</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12941,6 +13149,9 @@
       <c r="CE6" t="n">
         <v>91.33</v>
       </c>
+      <c r="CF6" t="n">
+        <v>92.66500000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13196,6 +13407,9 @@
       <c r="CE7" t="n">
         <v>182.9</v>
       </c>
+      <c r="CF7" t="n">
+        <v>186.59</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13451,6 +13665,9 @@
       <c r="CE8" t="n">
         <v>191.7351</v>
       </c>
+      <c r="CF8" t="n">
+        <v>192.83</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13706,6 +13923,9 @@
       <c r="CE9" t="n">
         <v>83.38</v>
       </c>
+      <c r="CF9" t="n">
+        <v>83.47</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13960,6 +14180,9 @@
       </c>
       <c r="CE10" t="n">
         <v>482.84</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>476.8</v>
       </c>
     </row>
   </sheetData>
@@ -13973,7 +14196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE10"/>
+  <dimension ref="A1:CF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14059,6 +14282,7 @@
     <col width="12" customWidth="1" min="81" max="81"/>
     <col width="12" customWidth="1" min="82" max="82"/>
     <col width="12" customWidth="1" min="83" max="83"/>
+    <col width="12" customWidth="1" min="84" max="84"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14315,6 +14539,9 @@
       <c r="CE1" s="1" t="n">
         <v>20251223</v>
       </c>
+      <c r="CF1" s="1" t="n">
+        <v>20251224</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14570,6 +14797,9 @@
       <c r="CE2" t="n">
         <v>272.36</v>
       </c>
+      <c r="CF2" t="n">
+        <v>273.81</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14825,6 +15055,9 @@
       <c r="CE3" t="n">
         <v>232.14</v>
       </c>
+      <c r="CF3" t="n">
+        <v>232.38</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15080,6 +15313,9 @@
       <c r="CE4" t="n">
         <v>314.35</v>
       </c>
+      <c r="CF4" t="n">
+        <v>314.09</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15335,6 +15571,9 @@
       <c r="CE5" t="n">
         <v>486.85</v>
       </c>
+      <c r="CF5" t="n">
+        <v>488.02</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15590,6 +15829,9 @@
       <c r="CE6" t="n">
         <v>93.5</v>
       </c>
+      <c r="CF6" t="n">
+        <v>93.64</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15845,6 +16087,9 @@
       <c r="CE7" t="n">
         <v>189.21</v>
       </c>
+      <c r="CF7" t="n">
+        <v>188.61</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16100,6 +16345,9 @@
       <c r="CE8" t="n">
         <v>194.13</v>
       </c>
+      <c r="CF8" t="n">
+        <v>194.17</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16355,6 +16603,9 @@
       <c r="CE9" t="n">
         <v>83.86</v>
       </c>
+      <c r="CF9" t="n">
+        <v>84.56999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16609,6 +16860,9 @@
       </c>
       <c r="CE10" t="n">
         <v>485.56</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>485.4</v>
       </c>
     </row>
   </sheetData>
@@ -16622,7 +16876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE10"/>
+  <dimension ref="A1:CF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -16708,6 +16962,7 @@
     <col width="12" customWidth="1" min="81" max="81"/>
     <col width="12" customWidth="1" min="82" max="82"/>
     <col width="12" customWidth="1" min="83" max="83"/>
+    <col width="12" customWidth="1" min="84" max="84"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16964,6 +17219,9 @@
       <c r="CE1" s="1" t="n">
         <v>20251223</v>
       </c>
+      <c r="CF1" s="1" t="n">
+        <v>20251224</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17219,6 +17477,9 @@
       <c r="CE2" t="n">
         <v>29641999</v>
       </c>
+      <c r="CF2" t="n">
+        <v>17910574</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17474,6 +17735,9 @@
       <c r="CE3" t="n">
         <v>29230233</v>
       </c>
+      <c r="CF3" t="n">
+        <v>11420543</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17729,6 +17993,9 @@
       <c r="CE4" t="n">
         <v>25478670</v>
       </c>
+      <c r="CF4" t="n">
+        <v>10097361</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -17984,6 +18251,9 @@
       <c r="CE5" t="n">
         <v>14683582</v>
       </c>
+      <c r="CF5" t="n">
+        <v>5855880</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18239,6 +18509,9 @@
       <c r="CE6" t="n">
         <v>25896234</v>
       </c>
+      <c r="CF6" t="n">
+        <v>12427895</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18494,6 +18767,9 @@
       <c r="CE7" t="n">
         <v>174873621</v>
       </c>
+      <c r="CF7" t="n">
+        <v>65528545</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18749,6 +19025,9 @@
       <c r="CE8" t="n">
         <v>24040968</v>
       </c>
+      <c r="CF8" t="n">
+        <v>11710125</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19004,6 +19283,9 @@
       <c r="CE9" t="n">
         <v>9511322</v>
       </c>
+      <c r="CF9" t="n">
+        <v>3462748</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -19258,6 +19540,9 @@
       </c>
       <c r="CE10" t="n">
         <v>58223633</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>41285429</v>
       </c>
     </row>
   </sheetData>
@@ -19271,7 +19556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL10"/>
+  <dimension ref="A1:BM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -19338,6 +19623,7 @@
     <col width="10" customWidth="1" min="62" max="62"/>
     <col width="10" customWidth="1" min="63" max="63"/>
     <col width="10" customWidth="1" min="64" max="64"/>
+    <col width="10" customWidth="1" min="65" max="65"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19537,6 +19823,9 @@
       <c r="BL1" s="1" t="n">
         <v>20251223</v>
       </c>
+      <c r="BM1" s="1" t="n">
+        <v>20251224</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19735,6 +20024,9 @@
       <c r="BL2" t="n">
         <v>9</v>
       </c>
+      <c r="BM2" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19933,6 +20225,9 @@
       <c r="BL3" t="n">
         <v>83</v>
       </c>
+      <c r="BM3" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20131,6 +20426,9 @@
       <c r="BL4" t="n">
         <v>66</v>
       </c>
+      <c r="BM4" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20329,6 +20627,9 @@
       <c r="BL5" t="n">
         <v>70</v>
       </c>
+      <c r="BM5" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20527,6 +20828,9 @@
       <c r="BL6" t="n">
         <v>5</v>
       </c>
+      <c r="BM6" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20725,6 +21029,9 @@
       <c r="BL7" t="n">
         <v>100</v>
       </c>
+      <c r="BM7" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20923,6 +21230,9 @@
       <c r="BL8" t="n">
         <v>100</v>
       </c>
+      <c r="BM8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21121,6 +21431,9 @@
       <c r="BL9" t="n">
         <v>22</v>
       </c>
+      <c r="BM9" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21318,6 +21631,9 @@
       </c>
       <c r="BL10" t="n">
         <v>94</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -21331,7 +21647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X10"/>
+  <dimension ref="A1:Y10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21358,6 +21674,7 @@
     <col width="10" customWidth="1" min="22" max="22"/>
     <col width="10" customWidth="1" min="23" max="23"/>
     <col width="10" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21437,6 +21754,9 @@
       <c r="X1" s="1" t="n">
         <v>20251223</v>
       </c>
+      <c r="Y1" s="1" t="n">
+        <v>20251224</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21515,6 +21835,9 @@
       <c r="X2" t="n">
         <v>66</v>
       </c>
+      <c r="Y2" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21593,6 +21916,9 @@
       <c r="X3" t="n">
         <v>47</v>
       </c>
+      <c r="Y3" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -21671,6 +21997,9 @@
       <c r="X4" t="n">
         <v>90</v>
       </c>
+      <c r="Y4" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -21749,6 +22078,9 @@
       <c r="X5" t="n">
         <v>21</v>
       </c>
+      <c r="Y5" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21827,6 +22159,9 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21905,6 +22240,9 @@
       <c r="X7" t="n">
         <v>51</v>
       </c>
+      <c r="Y7" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21983,6 +22321,9 @@
       <c r="X8" t="n">
         <v>75</v>
       </c>
+      <c r="Y8" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22061,6 +22402,9 @@
       <c r="X9" t="n">
         <v>49</v>
       </c>
+      <c r="Y9" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22138,6 +22482,9 @@
       </c>
       <c r="X10" t="n">
         <v>96</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -22151,7 +22498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL10"/>
+  <dimension ref="A1:BM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22218,6 +22565,7 @@
     <col width="10" customWidth="1" min="62" max="62"/>
     <col width="10" customWidth="1" min="63" max="63"/>
     <col width="10" customWidth="1" min="64" max="64"/>
+    <col width="10" customWidth="1" min="65" max="65"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22417,6 +22765,9 @@
       <c r="BL1" s="1" t="n">
         <v>20251223</v>
       </c>
+      <c r="BM1" s="1" t="n">
+        <v>20251224</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22615,6 +22966,9 @@
       <c r="BL2" t="n">
         <v>-59</v>
       </c>
+      <c r="BM2" t="n">
+        <v>-39</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22813,6 +23167,9 @@
       <c r="BL3" t="n">
         <v>45</v>
       </c>
+      <c r="BM3" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23011,6 +23368,9 @@
       <c r="BL4" t="n">
         <v>6</v>
       </c>
+      <c r="BM4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23209,6 +23569,9 @@
       <c r="BL5" t="n">
         <v>32</v>
       </c>
+      <c r="BM5" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23407,6 +23770,9 @@
       <c r="BL6" t="n">
         <v>-45</v>
       </c>
+      <c r="BM6" t="n">
+        <v>-40</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23605,6 +23971,9 @@
       <c r="BL7" t="n">
         <v>103</v>
       </c>
+      <c r="BM7" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23803,6 +24172,9 @@
       <c r="BL8" t="n">
         <v>72</v>
       </c>
+      <c r="BM8" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24001,6 +24373,9 @@
       <c r="BL9" t="n">
         <v>-50</v>
       </c>
+      <c r="BM9" t="n">
+        <v>-26</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24198,6 +24573,9 @@
       </c>
       <c r="BL10" t="n">
         <v>67</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y10"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -629,6 +629,7 @@
     <col width="10" customWidth="1" min="23" max="23"/>
     <col width="10" customWidth="1" min="24" max="24"/>
     <col width="10" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -711,6 +712,9 @@
       <c r="Y1" s="1" t="n">
         <v>20251224</v>
       </c>
+      <c r="Z1" s="1" t="n">
+        <v>20251226</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -792,6 +796,9 @@
       <c r="Y2" t="n">
         <v>28</v>
       </c>
+      <c r="Z2" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -873,6 +880,9 @@
       <c r="Y3" t="n">
         <v>19</v>
       </c>
+      <c r="Z3" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -954,6 +964,9 @@
       <c r="Y4" t="n">
         <v>55</v>
       </c>
+      <c r="Z4" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1035,6 +1048,9 @@
       <c r="Y5" t="n">
         <v>-37</v>
       </c>
+      <c r="Z5" t="n">
+        <v>-37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1116,6 +1132,9 @@
       <c r="Y6" t="n">
         <v>-55</v>
       </c>
+      <c r="Z6" t="n">
+        <v>-53</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1197,6 +1216,9 @@
       <c r="Y7" t="n">
         <v>17</v>
       </c>
+      <c r="Z7" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1278,6 +1300,9 @@
       <c r="Y8" t="n">
         <v>63</v>
       </c>
+      <c r="Z8" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1359,6 +1384,9 @@
       <c r="Y9" t="n">
         <v>6</v>
       </c>
+      <c r="Z9" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1439,6 +1467,9 @@
       </c>
       <c r="Y10" t="n">
         <v>92</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1452,7 +1483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM10"/>
+  <dimension ref="A1:BN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1520,6 +1551,7 @@
     <col width="12" customWidth="1" min="63" max="63"/>
     <col width="12" customWidth="1" min="64" max="64"/>
     <col width="12" customWidth="1" min="65" max="65"/>
+    <col width="12" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1848,6 +1880,11 @@
           <t>20251224</t>
         </is>
       </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>20251226</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2049,6 +2086,9 @@
       <c r="BM2" t="n">
         <v>99</v>
       </c>
+      <c r="BN2" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2250,6 +2290,9 @@
       <c r="BM3" t="n">
         <v>102</v>
       </c>
+      <c r="BN3" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2451,6 +2494,9 @@
       <c r="BM4" t="n">
         <v>100</v>
       </c>
+      <c r="BN4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2652,6 +2698,9 @@
       <c r="BM5" t="n">
         <v>101</v>
       </c>
+      <c r="BN5" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2853,6 +2902,9 @@
       <c r="BM6" t="n">
         <v>95</v>
       </c>
+      <c r="BN6" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3054,6 +3106,9 @@
       <c r="BM7" t="n">
         <v>104</v>
       </c>
+      <c r="BN7" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3255,6 +3310,9 @@
       <c r="BM8" t="n">
         <v>107</v>
       </c>
+      <c r="BN8" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3456,6 +3514,9 @@
       <c r="BM9" t="n">
         <v>99</v>
       </c>
+      <c r="BN9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3656,6 +3717,9 @@
       </c>
       <c r="BM10" t="n">
         <v>106</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -3669,7 +3733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT10"/>
+  <dimension ref="A1:AU10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3718,6 +3782,7 @@
     <col width="12" customWidth="1" min="44" max="44"/>
     <col width="12" customWidth="1" min="45" max="45"/>
     <col width="12" customWidth="1" min="46" max="46"/>
+    <col width="12" customWidth="1" min="47" max="47"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3951,6 +4016,11 @@
           <t>20251224</t>
         </is>
       </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>20251226</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4095,6 +4165,9 @@
       <c r="AT2" t="n">
         <v>-15.13</v>
       </c>
+      <c r="AU2" t="n">
+        <v>-14.44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4239,6 +4312,9 @@
       <c r="AT3" t="n">
         <v>-45.09</v>
       </c>
+      <c r="AU3" t="n">
+        <v>-40.56</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4383,6 +4459,9 @@
       <c r="AT4" t="n">
         <v>-50.84</v>
       </c>
+      <c r="AU4" t="n">
+        <v>-50.9</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4527,6 +4606,9 @@
       <c r="AT5" t="n">
         <v>-46.96</v>
       </c>
+      <c r="AU5" t="n">
+        <v>-43.55</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4671,6 +4753,9 @@
       <c r="AT6" t="n">
         <v>-97.81</v>
       </c>
+      <c r="AU6" t="n">
+        <v>-97.69</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4815,6 +4900,9 @@
       <c r="AT7" t="n">
         <v>-9.07</v>
       </c>
+      <c r="AU7" t="n">
+        <v>3.65</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4959,6 +5047,9 @@
       <c r="AT8" t="n">
         <v>-16.13</v>
       </c>
+      <c r="AU8" t="n">
+        <v>-20.53</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5103,6 +5194,9 @@
       <c r="AT9" t="n">
         <v>2.07</v>
       </c>
+      <c r="AU9" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5246,6 +5340,9 @@
       </c>
       <c r="AT10" t="n">
         <v>-0.54</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>-4.83</v>
       </c>
     </row>
   </sheetData>
@@ -5259,7 +5356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y10"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5287,6 +5384,7 @@
     <col width="12" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5415,6 +5513,11 @@
           <t>20251224</t>
         </is>
       </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>20251226</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5496,6 +5599,9 @@
       <c r="Y2" t="n">
         <v>19</v>
       </c>
+      <c r="Z2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5577,6 +5683,9 @@
       <c r="Y3" t="n">
         <v>12</v>
       </c>
+      <c r="Z3" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5658,6 +5767,9 @@
       <c r="Y4" t="n">
         <v>14</v>
       </c>
+      <c r="Z4" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5739,6 +5851,9 @@
       <c r="Y5" t="n">
         <v>13</v>
       </c>
+      <c r="Z5" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5820,6 +5935,9 @@
       <c r="Y6" t="n">
         <v>27</v>
       </c>
+      <c r="Z6" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5901,6 +6019,9 @@
       <c r="Y7" t="n">
         <v>17</v>
       </c>
+      <c r="Z7" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5982,6 +6103,9 @@
       <c r="Y8" t="n">
         <v>12</v>
       </c>
+      <c r="Z8" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6063,6 +6187,9 @@
       <c r="Y9" t="n">
         <v>17</v>
       </c>
+      <c r="Z9" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6143,6 +6270,9 @@
       </c>
       <c r="Y10" t="n">
         <v>25</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -6156,7 +6286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CF10"/>
+  <dimension ref="A1:CG10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6243,6 +6373,7 @@
     <col width="12" customWidth="1" min="82" max="82"/>
     <col width="12" customWidth="1" min="83" max="83"/>
     <col width="12" customWidth="1" min="84" max="84"/>
+    <col width="12" customWidth="1" min="85" max="85"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6502,6 +6633,9 @@
       <c r="CF1" s="1" t="n">
         <v>20251224</v>
       </c>
+      <c r="CG1" s="1" t="n">
+        <v>20251226</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6760,6 +6894,9 @@
       <c r="CF2" t="n">
         <v>272.34</v>
       </c>
+      <c r="CG2" t="n">
+        <v>274.16</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7018,6 +7155,9 @@
       <c r="CF3" t="n">
         <v>232.13</v>
       </c>
+      <c r="CG3" t="n">
+        <v>232.035</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7276,6 +7416,9 @@
       <c r="CF4" t="n">
         <v>314.77</v>
       </c>
+      <c r="CG4" t="n">
+        <v>314.48</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7534,6 +7677,9 @@
       <c r="CF5" t="n">
         <v>485.68</v>
       </c>
+      <c r="CG5" t="n">
+        <v>486.705</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7792,6 +7938,9 @@
       <c r="CF6" t="n">
         <v>93.11</v>
       </c>
+      <c r="CG6" t="n">
+        <v>93.48</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8050,6 +8199,9 @@
       <c r="CF7" t="n">
         <v>187.94</v>
       </c>
+      <c r="CG7" t="n">
+        <v>189.92</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8308,6 +8460,9 @@
       <c r="CF8" t="n">
         <v>193.16</v>
       </c>
+      <c r="CG8" t="n">
+        <v>195.015</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8566,6 +8721,9 @@
       <c r="CF9" t="n">
         <v>83.84</v>
       </c>
+      <c r="CG9" t="n">
+        <v>84.58</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8823,6 +8981,9 @@
       </c>
       <c r="CF10" t="n">
         <v>488.48</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>485.23</v>
       </c>
     </row>
   </sheetData>
@@ -8836,7 +8997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CF10"/>
+  <dimension ref="A1:CG10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8923,6 +9084,7 @@
     <col width="12" customWidth="1" min="82" max="82"/>
     <col width="12" customWidth="1" min="83" max="83"/>
     <col width="12" customWidth="1" min="84" max="84"/>
+    <col width="12" customWidth="1" min="85" max="85"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9182,6 +9344,9 @@
       <c r="CF1" s="1" t="n">
         <v>20251224</v>
       </c>
+      <c r="CG1" s="1" t="n">
+        <v>20251226</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9440,6 +9605,9 @@
       <c r="CF2" t="n">
         <v>275.43</v>
       </c>
+      <c r="CG2" t="n">
+        <v>275.37</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9698,6 +9866,9 @@
       <c r="CF3" t="n">
         <v>232.95</v>
       </c>
+      <c r="CG3" t="n">
+        <v>232.99</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9956,6 +10127,9 @@
       <c r="CF4" t="n">
         <v>315.08</v>
       </c>
+      <c r="CG4" t="n">
+        <v>315.085</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10214,6 +10388,9 @@
       <c r="CF5" t="n">
         <v>489.1625</v>
       </c>
+      <c r="CG5" t="n">
+        <v>488.12</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10472,6 +10649,9 @@
       <c r="CF6" t="n">
         <v>93.68000000000001</v>
       </c>
+      <c r="CG6" t="n">
+        <v>94.685</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10730,6 +10910,9 @@
       <c r="CF7" t="n">
         <v>188.91</v>
       </c>
+      <c r="CG7" t="n">
+        <v>192.69</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10988,6 +11171,9 @@
       <c r="CF8" t="n">
         <v>195.17</v>
       </c>
+      <c r="CG8" t="n">
+        <v>196.35</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11246,6 +11432,9 @@
       <c r="CF9" t="n">
         <v>84.61499999999999</v>
       </c>
+      <c r="CG9" t="n">
+        <v>85.155</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11503,6 +11692,9 @@
       </c>
       <c r="CF10" t="n">
         <v>490.9</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>489.09</v>
       </c>
     </row>
   </sheetData>
@@ -11516,7 +11708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CF10"/>
+  <dimension ref="A1:CG10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11603,6 +11795,7 @@
     <col width="12" customWidth="1" min="82" max="82"/>
     <col width="12" customWidth="1" min="83" max="83"/>
     <col width="12" customWidth="1" min="84" max="84"/>
+    <col width="12" customWidth="1" min="85" max="85"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11862,6 +12055,9 @@
       <c r="CF1" s="1" t="n">
         <v>20251224</v>
       </c>
+      <c r="CG1" s="1" t="n">
+        <v>20251226</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12120,6 +12316,9 @@
       <c r="CF2" t="n">
         <v>272.195</v>
       </c>
+      <c r="CG2" t="n">
+        <v>272.86</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12378,6 +12577,9 @@
       <c r="CF3" t="n">
         <v>231.33</v>
       </c>
+      <c r="CG3" t="n">
+        <v>231.18</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12636,6 +12838,9 @@
       <c r="CF4" t="n">
         <v>311.92</v>
       </c>
+      <c r="CG4" t="n">
+        <v>312.275</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12894,6 +13099,9 @@
       <c r="CF5" t="n">
         <v>484.83</v>
       </c>
+      <c r="CG5" t="n">
+        <v>485.96</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13152,6 +13360,9 @@
       <c r="CF6" t="n">
         <v>92.66500000000001</v>
       </c>
+      <c r="CG6" t="n">
+        <v>93.27</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13410,6 +13621,9 @@
       <c r="CF7" t="n">
         <v>186.59</v>
       </c>
+      <c r="CG7" t="n">
+        <v>188</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13668,6 +13882,9 @@
       <c r="CF8" t="n">
         <v>192.83</v>
       </c>
+      <c r="CG8" t="n">
+        <v>188.62</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13926,6 +14143,9 @@
       <c r="CF9" t="n">
         <v>83.47</v>
       </c>
+      <c r="CG9" t="n">
+        <v>84.42</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14183,6 +14403,9 @@
       </c>
       <c r="CF10" t="n">
         <v>476.8</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>473.82</v>
       </c>
     </row>
   </sheetData>
@@ -14196,7 +14419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CF10"/>
+  <dimension ref="A1:CG10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14283,6 +14506,7 @@
     <col width="12" customWidth="1" min="82" max="82"/>
     <col width="12" customWidth="1" min="83" max="83"/>
     <col width="12" customWidth="1" min="84" max="84"/>
+    <col width="12" customWidth="1" min="85" max="85"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14542,6 +14766,9 @@
       <c r="CF1" s="1" t="n">
         <v>20251224</v>
       </c>
+      <c r="CG1" s="1" t="n">
+        <v>20251226</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14800,6 +15027,9 @@
       <c r="CF2" t="n">
         <v>273.81</v>
       </c>
+      <c r="CG2" t="n">
+        <v>273.4</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15058,6 +15288,9 @@
       <c r="CF3" t="n">
         <v>232.38</v>
       </c>
+      <c r="CG3" t="n">
+        <v>232.52</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15316,6 +15549,9 @@
       <c r="CF4" t="n">
         <v>314.09</v>
       </c>
+      <c r="CG4" t="n">
+        <v>313.51</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15574,6 +15810,9 @@
       <c r="CF5" t="n">
         <v>488.02</v>
       </c>
+      <c r="CG5" t="n">
+        <v>487.71</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15832,6 +16071,9 @@
       <c r="CF6" t="n">
         <v>93.64</v>
       </c>
+      <c r="CG6" t="n">
+        <v>94.47</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16090,6 +16332,9 @@
       <c r="CF7" t="n">
         <v>188.61</v>
       </c>
+      <c r="CG7" t="n">
+        <v>190.53</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16348,6 +16593,9 @@
       <c r="CF8" t="n">
         <v>194.17</v>
       </c>
+      <c r="CG8" t="n">
+        <v>188.71</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16606,6 +16854,9 @@
       <c r="CF9" t="n">
         <v>84.56999999999999</v>
       </c>
+      <c r="CG9" t="n">
+        <v>85.08</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16863,6 +17114,9 @@
       </c>
       <c r="CF10" t="n">
         <v>485.4</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>475.19</v>
       </c>
     </row>
   </sheetData>
@@ -16876,7 +17130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CF10"/>
+  <dimension ref="A1:CG10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -16963,6 +17217,7 @@
     <col width="12" customWidth="1" min="82" max="82"/>
     <col width="12" customWidth="1" min="83" max="83"/>
     <col width="12" customWidth="1" min="84" max="84"/>
+    <col width="12" customWidth="1" min="85" max="85"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17222,6 +17477,9 @@
       <c r="CF1" s="1" t="n">
         <v>20251224</v>
       </c>
+      <c r="CG1" s="1" t="n">
+        <v>20251226</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17480,6 +17738,9 @@
       <c r="CF2" t="n">
         <v>17910574</v>
       </c>
+      <c r="CG2" t="n">
+        <v>21521802</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17738,6 +17999,9 @@
       <c r="CF3" t="n">
         <v>11420543</v>
       </c>
+      <c r="CG3" t="n">
+        <v>15994726</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17996,6 +18260,9 @@
       <c r="CF4" t="n">
         <v>10097361</v>
       </c>
+      <c r="CG4" t="n">
+        <v>10899017</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18254,6 +18521,9 @@
       <c r="CF5" t="n">
         <v>5855880</v>
       </c>
+      <c r="CG5" t="n">
+        <v>8842175</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18512,6 +18782,9 @@
       <c r="CF6" t="n">
         <v>12427895</v>
       </c>
+      <c r="CG6" t="n">
+        <v>22068276</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18770,6 +19043,9 @@
       <c r="CF7" t="n">
         <v>65528545</v>
       </c>
+      <c r="CG7" t="n">
+        <v>139740292</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19028,6 +19304,9 @@
       <c r="CF8" t="n">
         <v>11710125</v>
       </c>
+      <c r="CG8" t="n">
+        <v>26261988</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19286,6 +19565,9 @@
       <c r="CF9" t="n">
         <v>3462748</v>
       </c>
+      <c r="CG9" t="n">
+        <v>5046220</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -19543,6 +19825,9 @@
       </c>
       <c r="CF10" t="n">
         <v>41285429</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>58780659</v>
       </c>
     </row>
   </sheetData>
@@ -19556,7 +19841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM10"/>
+  <dimension ref="A1:BN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -19624,6 +19909,7 @@
     <col width="10" customWidth="1" min="63" max="63"/>
     <col width="10" customWidth="1" min="64" max="64"/>
     <col width="10" customWidth="1" min="65" max="65"/>
+    <col width="10" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19826,6 +20112,9 @@
       <c r="BM1" s="1" t="n">
         <v>20251224</v>
       </c>
+      <c r="BN1" s="1" t="n">
+        <v>20251226</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20027,6 +20316,9 @@
       <c r="BM2" t="n">
         <v>19</v>
       </c>
+      <c r="BN2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20228,6 +20520,9 @@
       <c r="BM3" t="n">
         <v>84</v>
       </c>
+      <c r="BN3" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20429,6 +20724,9 @@
       <c r="BM4" t="n">
         <v>71</v>
       </c>
+      <c r="BN4" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20630,6 +20928,9 @@
       <c r="BM5" t="n">
         <v>77</v>
       </c>
+      <c r="BN5" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20831,6 +21132,9 @@
       <c r="BM6" t="n">
         <v>6</v>
       </c>
+      <c r="BN6" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21032,6 +21336,9 @@
       <c r="BM7" t="n">
         <v>97</v>
       </c>
+      <c r="BN7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21233,6 +21540,9 @@
       <c r="BM8" t="n">
         <v>100</v>
       </c>
+      <c r="BN8" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21434,6 +21744,9 @@
       <c r="BM9" t="n">
         <v>32</v>
       </c>
+      <c r="BN9" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21634,6 +21947,9 @@
       </c>
       <c r="BM10" t="n">
         <v>93</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -21647,7 +21963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y10"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21675,6 +21991,7 @@
     <col width="10" customWidth="1" min="23" max="23"/>
     <col width="10" customWidth="1" min="24" max="24"/>
     <col width="10" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21757,6 +22074,9 @@
       <c r="Y1" s="1" t="n">
         <v>20251224</v>
       </c>
+      <c r="Z1" s="1" t="n">
+        <v>20251226</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21838,6 +22158,9 @@
       <c r="Y2" t="n">
         <v>70</v>
       </c>
+      <c r="Z2" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21919,6 +22242,9 @@
       <c r="Y3" t="n">
         <v>47</v>
       </c>
+      <c r="Z3" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22000,6 +22326,9 @@
       <c r="Y4" t="n">
         <v>89</v>
       </c>
+      <c r="Z4" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -22081,6 +22410,9 @@
       <c r="Y5" t="n">
         <v>23</v>
       </c>
+      <c r="Z5" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -22162,6 +22494,9 @@
       <c r="Y6" t="n">
         <v>0</v>
       </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -22243,6 +22578,9 @@
       <c r="Y7" t="n">
         <v>49</v>
       </c>
+      <c r="Z7" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22324,6 +22662,9 @@
       <c r="Y8" t="n">
         <v>75</v>
       </c>
+      <c r="Z8" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22405,6 +22746,9 @@
       <c r="Y9" t="n">
         <v>56</v>
       </c>
+      <c r="Z9" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22485,6 +22829,9 @@
       </c>
       <c r="Y10" t="n">
         <v>95</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -22498,7 +22845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM10"/>
+  <dimension ref="A1:BN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22566,6 +22913,7 @@
     <col width="10" customWidth="1" min="63" max="63"/>
     <col width="10" customWidth="1" min="64" max="64"/>
     <col width="10" customWidth="1" min="65" max="65"/>
+    <col width="10" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22768,6 +23116,9 @@
       <c r="BM1" s="1" t="n">
         <v>20251224</v>
       </c>
+      <c r="BN1" s="1" t="n">
+        <v>20251226</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22969,6 +23320,9 @@
       <c r="BM2" t="n">
         <v>-39</v>
       </c>
+      <c r="BN2" t="n">
+        <v>-41</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23170,6 +23524,9 @@
       <c r="BM3" t="n">
         <v>45</v>
       </c>
+      <c r="BN3" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23371,6 +23728,9 @@
       <c r="BM4" t="n">
         <v>8</v>
       </c>
+      <c r="BN4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23572,6 +23932,9 @@
       <c r="BM5" t="n">
         <v>38</v>
       </c>
+      <c r="BN5" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23773,6 +24136,9 @@
       <c r="BM6" t="n">
         <v>-40</v>
       </c>
+      <c r="BN6" t="n">
+        <v>-29</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23974,6 +24340,9 @@
       <c r="BM7" t="n">
         <v>83</v>
       </c>
+      <c r="BN7" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24175,6 +24544,9 @@
       <c r="BM8" t="n">
         <v>67</v>
       </c>
+      <c r="BN8" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24376,6 +24748,9 @@
       <c r="BM9" t="n">
         <v>-26</v>
       </c>
+      <c r="BN9" t="n">
+        <v>-9</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24576,6 +24951,9 @@
       </c>
       <c r="BM10" t="n">
         <v>61</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -3733,7 +3733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU10"/>
+  <dimension ref="A1:BN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3783,6 +3783,25 @@
     <col width="12" customWidth="1" min="45" max="45"/>
     <col width="12" customWidth="1" min="46" max="46"/>
     <col width="12" customWidth="1" min="47" max="47"/>
+    <col width="12" customWidth="1" min="48" max="48"/>
+    <col width="12" customWidth="1" min="49" max="49"/>
+    <col width="12" customWidth="1" min="50" max="50"/>
+    <col width="12" customWidth="1" min="51" max="51"/>
+    <col width="12" customWidth="1" min="52" max="52"/>
+    <col width="12" customWidth="1" min="53" max="53"/>
+    <col width="12" customWidth="1" min="54" max="54"/>
+    <col width="12" customWidth="1" min="55" max="55"/>
+    <col width="12" customWidth="1" min="56" max="56"/>
+    <col width="12" customWidth="1" min="57" max="57"/>
+    <col width="12" customWidth="1" min="58" max="58"/>
+    <col width="12" customWidth="1" min="59" max="59"/>
+    <col width="12" customWidth="1" min="60" max="60"/>
+    <col width="12" customWidth="1" min="61" max="61"/>
+    <col width="12" customWidth="1" min="62" max="62"/>
+    <col width="12" customWidth="1" min="63" max="63"/>
+    <col width="12" customWidth="1" min="64" max="64"/>
+    <col width="12" customWidth="1" min="65" max="65"/>
+    <col width="12" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4021,6 +4040,101 @@
           <t>20251226</t>
         </is>
       </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>20251201</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>20251202</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>20251203</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>20251204</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>20251205</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>20251208</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>20251209</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>20251210</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>20251211</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>20251212</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>20251215</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>20251216</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>20251217</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>20251218</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>20251219</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>20251222</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>20251223</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>20251224</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>20251226</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4168,6 +4282,63 @@
       <c r="AU2" t="n">
         <v>-14.44</v>
       </c>
+      <c r="AV2" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>4.22</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4315,6 +4486,63 @@
       <c r="AU3" t="n">
         <v>-40.56</v>
       </c>
+      <c r="AV3" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>3.81</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4462,6 +4690,63 @@
       <c r="AU4" t="n">
         <v>-50.9</v>
       </c>
+      <c r="AV4" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>16.16</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>16.33</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>16.39</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>12.41</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>6.19</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4609,6 +4894,63 @@
       <c r="AU5" t="n">
         <v>-43.55</v>
       </c>
+      <c r="AV5" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>5.38</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4756,6 +5098,63 @@
       <c r="AU6" t="n">
         <v>-97.69</v>
       </c>
+      <c r="AV6" t="n">
+        <v>504.96</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>503.3</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>497.35</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>486</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>469.34</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>446.08</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>413.91</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>370.23</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>308.82</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>219.86</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>5.52</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4903,6 +5302,63 @@
       <c r="AU7" t="n">
         <v>3.65</v>
       </c>
+      <c r="AV7" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>5.05</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5050,6 +5506,63 @@
       <c r="AU8" t="n">
         <v>-20.53</v>
       </c>
+      <c r="AV8" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>8.06</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5197,6 +5710,63 @@
       <c r="AU9" t="n">
         <v>2</v>
       </c>
+      <c r="AV9" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1.6</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5343,6 +5913,63 @@
       </c>
       <c r="AU10" t="n">
         <v>-4.83</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>21.37</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>20.56</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>21.12</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>22.77</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>25.46</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>25.09</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>24.42</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>22.44</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>22.15</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>21.47</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>20.44</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:AA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -630,6 +630,7 @@
     <col width="10" customWidth="1" min="24" max="24"/>
     <col width="10" customWidth="1" min="25" max="25"/>
     <col width="10" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -715,6 +716,9 @@
       <c r="Z1" s="1" t="n">
         <v>20251226</v>
       </c>
+      <c r="AA1" s="1" t="n">
+        <v>20251229</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -799,6 +803,9 @@
       <c r="Z2" t="n">
         <v>25</v>
       </c>
+      <c r="AA2" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -883,6 +890,9 @@
       <c r="Z3" t="n">
         <v>19</v>
       </c>
+      <c r="AA3" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,6 +977,9 @@
       <c r="Z4" t="n">
         <v>52</v>
       </c>
+      <c r="AA4" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1051,6 +1064,9 @@
       <c r="Z5" t="n">
         <v>-37</v>
       </c>
+      <c r="AA5" t="n">
+        <v>-37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1135,6 +1151,9 @@
       <c r="Z6" t="n">
         <v>-53</v>
       </c>
+      <c r="AA6" t="n">
+        <v>-52</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1219,6 +1238,9 @@
       <c r="Z7" t="n">
         <v>28</v>
       </c>
+      <c r="AA7" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1303,6 +1325,9 @@
       <c r="Z8" t="n">
         <v>36</v>
       </c>
+      <c r="AA8" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1387,6 +1412,9 @@
       <c r="Z9" t="n">
         <v>17</v>
       </c>
+      <c r="AA9" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1470,6 +1498,9 @@
       </c>
       <c r="Z10" t="n">
         <v>69</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1483,7 +1514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN10"/>
+  <dimension ref="A1:BO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1552,6 +1583,7 @@
     <col width="12" customWidth="1" min="64" max="64"/>
     <col width="12" customWidth="1" min="65" max="65"/>
     <col width="12" customWidth="1" min="66" max="66"/>
+    <col width="12" customWidth="1" min="67" max="67"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1885,6 +1917,11 @@
           <t>20251226</t>
         </is>
       </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>20251229</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2089,6 +2126,9 @@
       <c r="BN2" t="n">
         <v>99</v>
       </c>
+      <c r="BO2" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2293,6 +2333,9 @@
       <c r="BN3" t="n">
         <v>102</v>
       </c>
+      <c r="BO3" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2497,6 +2540,9 @@
       <c r="BN4" t="n">
         <v>100</v>
       </c>
+      <c r="BO4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2701,6 +2747,9 @@
       <c r="BN5" t="n">
         <v>101</v>
       </c>
+      <c r="BO5" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2905,6 +2954,9 @@
       <c r="BN6" t="n">
         <v>97</v>
       </c>
+      <c r="BO6" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3109,6 +3161,9 @@
       <c r="BN7" t="n">
         <v>105</v>
       </c>
+      <c r="BO7" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3313,6 +3368,9 @@
       <c r="BN8" t="n">
         <v>103</v>
       </c>
+      <c r="BO8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3517,6 +3575,9 @@
       <c r="BN9" t="n">
         <v>100</v>
       </c>
+      <c r="BO9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3720,6 +3781,9 @@
       </c>
       <c r="BN10" t="n">
         <v>103</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -3733,7 +3797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN10"/>
+  <dimension ref="A1:BO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3802,6 +3866,7 @@
     <col width="12" customWidth="1" min="64" max="64"/>
     <col width="12" customWidth="1" min="65" max="65"/>
     <col width="12" customWidth="1" min="66" max="66"/>
+    <col width="12" customWidth="1" min="67" max="67"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4135,6 +4200,11 @@
           <t>20251226</t>
         </is>
       </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>20251229</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4339,6 +4409,9 @@
       <c r="BN2" t="n">
         <v>4.22</v>
       </c>
+      <c r="BO2" t="n">
+        <v>4.25</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4543,6 +4616,9 @@
       <c r="BN3" t="n">
         <v>3.81</v>
       </c>
+      <c r="BO3" t="n">
+        <v>3.75</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4747,6 +4823,9 @@
       <c r="BN4" t="n">
         <v>6.19</v>
       </c>
+      <c r="BO4" t="n">
+        <v>5.96</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4951,6 +5030,9 @@
       <c r="BN5" t="n">
         <v>5.38</v>
       </c>
+      <c r="BO5" t="n">
+        <v>5.11</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5155,6 +5237,9 @@
       <c r="BN6" t="n">
         <v>5.52</v>
       </c>
+      <c r="BO6" t="n">
+        <v>5.08</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5359,6 +5444,9 @@
       <c r="BN7" t="n">
         <v>5.05</v>
       </c>
+      <c r="BO7" t="n">
+        <v>5.16</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5563,6 +5651,9 @@
       <c r="BN8" t="n">
         <v>8.06</v>
       </c>
+      <c r="BO8" t="n">
+        <v>7.32</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5767,6 +5858,9 @@
       <c r="BN9" t="n">
         <v>1.6</v>
       </c>
+      <c r="BO9" t="n">
+        <v>1.56</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5970,6 +6064,9 @@
       </c>
       <c r="BN10" t="n">
         <v>20.44</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>19.18</v>
       </c>
     </row>
   </sheetData>
@@ -5983,7 +6080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:AA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6012,6 +6109,7 @@
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6145,6 +6243,11 @@
           <t>20251226</t>
         </is>
       </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>20251229</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6229,6 +6332,9 @@
       <c r="Z2" t="n">
         <v>23</v>
       </c>
+      <c r="AA2" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6313,6 +6419,9 @@
       <c r="Z3" t="n">
         <v>17</v>
       </c>
+      <c r="AA3" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6397,6 +6506,9 @@
       <c r="Z4" t="n">
         <v>15</v>
       </c>
+      <c r="AA4" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6481,6 +6593,9 @@
       <c r="Z5" t="n">
         <v>19</v>
       </c>
+      <c r="AA5" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6565,6 +6680,9 @@
       <c r="Z6" t="n">
         <v>47</v>
       </c>
+      <c r="AA6" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6649,6 +6767,9 @@
       <c r="Z7" t="n">
         <v>37</v>
       </c>
+      <c r="AA7" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6733,6 +6854,9 @@
       <c r="Z8" t="n">
         <v>27</v>
       </c>
+      <c r="AA8" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6817,6 +6941,9 @@
       <c r="Z9" t="n">
         <v>25</v>
       </c>
+      <c r="AA9" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6900,6 +7027,9 @@
       </c>
       <c r="Z10" t="n">
         <v>35</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -6913,7 +7043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG10"/>
+  <dimension ref="A1:CH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7001,6 +7131,7 @@
     <col width="12" customWidth="1" min="83" max="83"/>
     <col width="12" customWidth="1" min="84" max="84"/>
     <col width="12" customWidth="1" min="85" max="85"/>
+    <col width="12" customWidth="1" min="86" max="86"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7263,6 +7394,9 @@
       <c r="CG1" s="1" t="n">
         <v>20251226</v>
       </c>
+      <c r="CH1" s="1" t="n">
+        <v>20251229</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7524,6 +7658,9 @@
       <c r="CG2" t="n">
         <v>274.16</v>
       </c>
+      <c r="CH2" t="n">
+        <v>272.69</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7785,6 +7922,9 @@
       <c r="CG3" t="n">
         <v>232.035</v>
       </c>
+      <c r="CH3" t="n">
+        <v>231.94</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8046,6 +8186,9 @@
       <c r="CG4" t="n">
         <v>314.48</v>
       </c>
+      <c r="CH4" t="n">
+        <v>311.365</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8307,6 +8450,9 @@
       <c r="CG5" t="n">
         <v>486.705</v>
       </c>
+      <c r="CH5" t="n">
+        <v>484.855</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8568,6 +8714,9 @@
       <c r="CG6" t="n">
         <v>93.48</v>
       </c>
+      <c r="CH6" t="n">
+        <v>93.98999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8829,6 +8978,9 @@
       <c r="CG7" t="n">
         <v>189.92</v>
       </c>
+      <c r="CH7" t="n">
+        <v>187.71</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9090,6 +9242,9 @@
       <c r="CG8" t="n">
         <v>195.015</v>
       </c>
+      <c r="CH8" t="n">
+        <v>186.85</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9351,6 +9506,9 @@
       <c r="CG9" t="n">
         <v>84.58</v>
       </c>
+      <c r="CH9" t="n">
+        <v>85.12</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9611,6 +9769,9 @@
       </c>
       <c r="CG10" t="n">
         <v>485.23</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -9624,7 +9785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG10"/>
+  <dimension ref="A1:CH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9712,6 +9873,7 @@
     <col width="12" customWidth="1" min="83" max="83"/>
     <col width="12" customWidth="1" min="84" max="84"/>
     <col width="12" customWidth="1" min="85" max="85"/>
+    <col width="12" customWidth="1" min="86" max="86"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9974,6 +10136,9 @@
       <c r="CG1" s="1" t="n">
         <v>20251226</v>
       </c>
+      <c r="CH1" s="1" t="n">
+        <v>20251229</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10235,6 +10400,9 @@
       <c r="CG2" t="n">
         <v>275.37</v>
       </c>
+      <c r="CH2" t="n">
+        <v>274.36</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10496,6 +10664,9 @@
       <c r="CG3" t="n">
         <v>232.99</v>
       </c>
+      <c r="CH3" t="n">
+        <v>232.6</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10757,6 +10928,9 @@
       <c r="CG4" t="n">
         <v>315.085</v>
       </c>
+      <c r="CH4" t="n">
+        <v>314.02</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11018,6 +11192,9 @@
       <c r="CG5" t="n">
         <v>488.12</v>
       </c>
+      <c r="CH5" t="n">
+        <v>488.35</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11279,6 +11456,9 @@
       <c r="CG6" t="n">
         <v>94.685</v>
       </c>
+      <c r="CH6" t="n">
+        <v>94.97</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11540,6 +11720,9 @@
       <c r="CG7" t="n">
         <v>192.69</v>
       </c>
+      <c r="CH7" t="n">
+        <v>188.755</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11801,6 +11984,9 @@
       <c r="CG8" t="n">
         <v>196.35</v>
       </c>
+      <c r="CH8" t="n">
+        <v>187.2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12062,6 +12248,9 @@
       <c r="CG9" t="n">
         <v>85.155</v>
       </c>
+      <c r="CH9" t="n">
+        <v>86.7895</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12322,6 +12511,9 @@
       </c>
       <c r="CG10" t="n">
         <v>489.09</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>469.4</v>
       </c>
     </row>
   </sheetData>
@@ -12335,7 +12527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG10"/>
+  <dimension ref="A1:CH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12423,6 +12615,7 @@
     <col width="12" customWidth="1" min="83" max="83"/>
     <col width="12" customWidth="1" min="84" max="84"/>
     <col width="12" customWidth="1" min="85" max="85"/>
+    <col width="12" customWidth="1" min="86" max="86"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12685,6 +12878,9 @@
       <c r="CG1" s="1" t="n">
         <v>20251226</v>
       </c>
+      <c r="CH1" s="1" t="n">
+        <v>20251229</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12946,6 +13142,9 @@
       <c r="CG2" t="n">
         <v>272.86</v>
       </c>
+      <c r="CH2" t="n">
+        <v>272.35</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13207,6 +13406,9 @@
       <c r="CG3" t="n">
         <v>231.18</v>
       </c>
+      <c r="CH3" t="n">
+        <v>230.77</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13468,6 +13670,9 @@
       <c r="CG4" t="n">
         <v>312.275</v>
       </c>
+      <c r="CH4" t="n">
+        <v>310.62</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13729,6 +13934,9 @@
       <c r="CG5" t="n">
         <v>485.96</v>
       </c>
+      <c r="CH5" t="n">
+        <v>484.18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13990,6 +14198,9 @@
       <c r="CG6" t="n">
         <v>93.27</v>
       </c>
+      <c r="CH6" t="n">
+        <v>93.625</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14251,6 +14462,9 @@
       <c r="CG7" t="n">
         <v>188</v>
       </c>
+      <c r="CH7" t="n">
+        <v>185.91</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14512,6 +14726,9 @@
       <c r="CG8" t="n">
         <v>188.62</v>
       </c>
+      <c r="CH8" t="n">
+        <v>183.64</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14773,6 +14990,9 @@
       <c r="CG9" t="n">
         <v>84.42</v>
       </c>
+      <c r="CH9" t="n">
+        <v>84.98</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15033,6 +15253,9 @@
       </c>
       <c r="CG10" t="n">
         <v>473.82</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>459</v>
       </c>
     </row>
   </sheetData>
@@ -15046,7 +15269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG10"/>
+  <dimension ref="A1:CH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15134,6 +15357,7 @@
     <col width="12" customWidth="1" min="83" max="83"/>
     <col width="12" customWidth="1" min="84" max="84"/>
     <col width="12" customWidth="1" min="85" max="85"/>
+    <col width="12" customWidth="1" min="86" max="86"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15396,6 +15620,9 @@
       <c r="CG1" s="1" t="n">
         <v>20251226</v>
       </c>
+      <c r="CH1" s="1" t="n">
+        <v>20251229</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15657,6 +15884,9 @@
       <c r="CG2" t="n">
         <v>273.4</v>
       </c>
+      <c r="CH2" t="n">
+        <v>273.76</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15918,6 +16148,9 @@
       <c r="CG3" t="n">
         <v>232.52</v>
       </c>
+      <c r="CH3" t="n">
+        <v>232.07</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16179,6 +16412,9 @@
       <c r="CG4" t="n">
         <v>313.51</v>
       </c>
+      <c r="CH4" t="n">
+        <v>313.56</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16440,6 +16676,9 @@
       <c r="CG5" t="n">
         <v>487.71</v>
       </c>
+      <c r="CH5" t="n">
+        <v>487.1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16701,6 +16940,9 @@
       <c r="CG6" t="n">
         <v>94.47</v>
       </c>
+      <c r="CH6" t="n">
+        <v>94.15000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16962,6 +17204,9 @@
       <c r="CG7" t="n">
         <v>190.53</v>
       </c>
+      <c r="CH7" t="n">
+        <v>188.22</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17223,6 +17468,9 @@
       <c r="CG8" t="n">
         <v>188.71</v>
       </c>
+      <c r="CH8" t="n">
+        <v>184.18</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17484,6 +17732,9 @@
       <c r="CG9" t="n">
         <v>85.08</v>
       </c>
+      <c r="CH9" t="n">
+        <v>85.56999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17744,6 +17995,9 @@
       </c>
       <c r="CG10" t="n">
         <v>475.19</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>459.64</v>
       </c>
     </row>
   </sheetData>
@@ -17757,7 +18011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG10"/>
+  <dimension ref="A1:CH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17845,6 +18099,7 @@
     <col width="12" customWidth="1" min="83" max="83"/>
     <col width="12" customWidth="1" min="84" max="84"/>
     <col width="12" customWidth="1" min="85" max="85"/>
+    <col width="12" customWidth="1" min="86" max="86"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18107,6 +18362,9 @@
       <c r="CG1" s="1" t="n">
         <v>20251226</v>
       </c>
+      <c r="CH1" s="1" t="n">
+        <v>20251229</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18368,6 +18626,9 @@
       <c r="CG2" t="n">
         <v>21521802</v>
       </c>
+      <c r="CH2" t="n">
+        <v>23715213</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18629,6 +18890,9 @@
       <c r="CG3" t="n">
         <v>15994726</v>
       </c>
+      <c r="CH3" t="n">
+        <v>19797909</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18890,6 +19154,9 @@
       <c r="CG4" t="n">
         <v>10899017</v>
       </c>
+      <c r="CH4" t="n">
+        <v>19621777</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19151,6 +19418,9 @@
       <c r="CG5" t="n">
         <v>8842175</v>
       </c>
+      <c r="CH5" t="n">
+        <v>10893408</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19412,6 +19682,9 @@
       <c r="CG6" t="n">
         <v>22068276</v>
       </c>
+      <c r="CH6" t="n">
+        <v>24493738</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19673,6 +19946,9 @@
       <c r="CG7" t="n">
         <v>139740292</v>
       </c>
+      <c r="CH7" t="n">
+        <v>120006103</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19934,6 +20210,9 @@
       <c r="CG8" t="n">
         <v>26261988</v>
       </c>
+      <c r="CH8" t="n">
+        <v>28242003</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20195,6 +20474,9 @@
       <c r="CG9" t="n">
         <v>5046220</v>
       </c>
+      <c r="CH9" t="n">
+        <v>5352446</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20455,6 +20737,9 @@
       </c>
       <c r="CG10" t="n">
         <v>58780659</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>66263033</v>
       </c>
     </row>
   </sheetData>
@@ -20468,7 +20753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN10"/>
+  <dimension ref="A1:BO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20537,6 +20822,7 @@
     <col width="10" customWidth="1" min="64" max="64"/>
     <col width="10" customWidth="1" min="65" max="65"/>
     <col width="10" customWidth="1" min="66" max="66"/>
+    <col width="10" customWidth="1" min="67" max="67"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20742,6 +21028,9 @@
       <c r="BN1" s="1" t="n">
         <v>20251226</v>
       </c>
+      <c r="BO1" s="1" t="n">
+        <v>20251229</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20946,6 +21235,9 @@
       <c r="BN2" t="n">
         <v>16</v>
       </c>
+      <c r="BO2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21150,6 +21442,9 @@
       <c r="BN3" t="n">
         <v>86</v>
       </c>
+      <c r="BO3" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -21354,6 +21649,9 @@
       <c r="BN4" t="n">
         <v>68</v>
       </c>
+      <c r="BO4" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -21558,6 +21856,9 @@
       <c r="BN5" t="n">
         <v>75</v>
       </c>
+      <c r="BO5" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21762,6 +22063,9 @@
       <c r="BN6" t="n">
         <v>11</v>
       </c>
+      <c r="BO6" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21966,6 +22270,9 @@
       <c r="BN7" t="n">
         <v>100</v>
       </c>
+      <c r="BO7" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22170,6 +22477,9 @@
       <c r="BN8" t="n">
         <v>80</v>
       </c>
+      <c r="BO8" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22374,6 +22684,9 @@
       <c r="BN9" t="n">
         <v>39</v>
       </c>
+      <c r="BO9" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22577,6 +22890,9 @@
       </c>
       <c r="BN10" t="n">
         <v>76</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -22590,7 +22906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:AA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22619,6 +22935,7 @@
     <col width="10" customWidth="1" min="24" max="24"/>
     <col width="10" customWidth="1" min="25" max="25"/>
     <col width="10" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22704,6 +23021,9 @@
       <c r="Z1" s="1" t="n">
         <v>20251226</v>
       </c>
+      <c r="AA1" s="1" t="n">
+        <v>20251229</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22788,6 +23108,9 @@
       <c r="Z2" t="n">
         <v>69</v>
       </c>
+      <c r="AA2" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22872,6 +23195,9 @@
       <c r="Z3" t="n">
         <v>48</v>
       </c>
+      <c r="AA3" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22956,6 +23282,9 @@
       <c r="Z4" t="n">
         <v>89</v>
       </c>
+      <c r="AA4" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23040,6 +23369,9 @@
       <c r="Z5" t="n">
         <v>22</v>
       </c>
+      <c r="AA5" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23124,6 +23456,9 @@
       <c r="Z6" t="n">
         <v>0</v>
       </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23208,6 +23543,9 @@
       <c r="Z7" t="n">
         <v>54</v>
       </c>
+      <c r="AA7" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23292,6 +23630,9 @@
       <c r="Z8" t="n">
         <v>65</v>
       </c>
+      <c r="AA8" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23376,6 +23717,9 @@
       <c r="Z9" t="n">
         <v>60</v>
       </c>
+      <c r="AA9" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23459,6 +23803,9 @@
       </c>
       <c r="Z10" t="n">
         <v>85</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -23472,7 +23819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN10"/>
+  <dimension ref="A1:BO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23541,6 +23888,7 @@
     <col width="10" customWidth="1" min="64" max="64"/>
     <col width="10" customWidth="1" min="65" max="65"/>
     <col width="10" customWidth="1" min="66" max="66"/>
+    <col width="10" customWidth="1" min="67" max="67"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23746,6 +24094,9 @@
       <c r="BN1" s="1" t="n">
         <v>20251226</v>
       </c>
+      <c r="BO1" s="1" t="n">
+        <v>20251229</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23950,6 +24301,9 @@
       <c r="BN2" t="n">
         <v>-41</v>
       </c>
+      <c r="BO2" t="n">
+        <v>-34</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -24154,6 +24508,9 @@
       <c r="BN3" t="n">
         <v>44</v>
       </c>
+      <c r="BO3" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -24358,6 +24715,9 @@
       <c r="BN4" t="n">
         <v>6</v>
       </c>
+      <c r="BO4" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24562,6 +24922,9 @@
       <c r="BN5" t="n">
         <v>34</v>
       </c>
+      <c r="BO5" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24766,6 +25129,9 @@
       <c r="BN6" t="n">
         <v>-29</v>
       </c>
+      <c r="BO6" t="n">
+        <v>-28</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24970,6 +25336,9 @@
       <c r="BN7" t="n">
         <v>89</v>
       </c>
+      <c r="BO7" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25174,6 +25543,9 @@
       <c r="BN8" t="n">
         <v>34</v>
       </c>
+      <c r="BO8" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25378,6 +25750,9 @@
       <c r="BN9" t="n">
         <v>-9</v>
       </c>
+      <c r="BO9" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25581,6 +25956,9 @@
       </c>
       <c r="BN10" t="n">
         <v>34</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>-7</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA10"/>
+  <dimension ref="A1:AB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -631,6 +631,7 @@
     <col width="10" customWidth="1" min="25" max="25"/>
     <col width="10" customWidth="1" min="26" max="26"/>
     <col width="10" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -719,6 +720,9 @@
       <c r="AA1" s="1" t="n">
         <v>20251229</v>
       </c>
+      <c r="AB1" s="1" t="n">
+        <v>20251230</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -806,6 +810,9 @@
       <c r="AA2" t="n">
         <v>26</v>
       </c>
+      <c r="AB2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -893,6 +900,9 @@
       <c r="AA3" t="n">
         <v>16</v>
       </c>
+      <c r="AB3" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -980,6 +990,9 @@
       <c r="AA4" t="n">
         <v>50</v>
       </c>
+      <c r="AB4" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1067,6 +1080,9 @@
       <c r="AA5" t="n">
         <v>-37</v>
       </c>
+      <c r="AB5" t="n">
+        <v>-35</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1154,6 +1170,9 @@
       <c r="AA6" t="n">
         <v>-52</v>
       </c>
+      <c r="AB6" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1241,6 +1260,9 @@
       <c r="AA7" t="n">
         <v>14</v>
       </c>
+      <c r="AB7" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1328,6 +1350,9 @@
       <c r="AA8" t="n">
         <v>15</v>
       </c>
+      <c r="AB8" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1415,6 +1440,9 @@
       <c r="AA9" t="n">
         <v>28</v>
       </c>
+      <c r="AB9" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1501,6 +1529,9 @@
       </c>
       <c r="AA10" t="n">
         <v>35</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1514,7 +1545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO10"/>
+  <dimension ref="A1:BP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1584,6 +1615,7 @@
     <col width="12" customWidth="1" min="65" max="65"/>
     <col width="12" customWidth="1" min="66" max="66"/>
     <col width="12" customWidth="1" min="67" max="67"/>
+    <col width="12" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1922,6 +1954,11 @@
           <t>20251229</t>
         </is>
       </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>20251230</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2129,6 +2166,9 @@
       <c r="BO2" t="n">
         <v>99</v>
       </c>
+      <c r="BP2" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2336,6 +2376,9 @@
       <c r="BO3" t="n">
         <v>101</v>
       </c>
+      <c r="BP3" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2543,6 +2586,9 @@
       <c r="BO4" t="n">
         <v>100</v>
       </c>
+      <c r="BP4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2750,6 +2796,9 @@
       <c r="BO5" t="n">
         <v>101</v>
       </c>
+      <c r="BP5" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2957,6 +3006,9 @@
       <c r="BO6" t="n">
         <v>97</v>
       </c>
+      <c r="BP6" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3164,6 +3216,9 @@
       <c r="BO7" t="n">
         <v>103</v>
       </c>
+      <c r="BP7" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3371,6 +3426,9 @@
       <c r="BO8" t="n">
         <v>100</v>
       </c>
+      <c r="BP8" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3578,6 +3636,9 @@
       <c r="BO9" t="n">
         <v>100</v>
       </c>
+      <c r="BP9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3784,6 +3845,9 @@
       </c>
       <c r="BO10" t="n">
         <v>99</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -3797,7 +3861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO10"/>
+  <dimension ref="A1:BP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3867,6 +3931,7 @@
     <col width="12" customWidth="1" min="65" max="65"/>
     <col width="12" customWidth="1" min="66" max="66"/>
     <col width="12" customWidth="1" min="67" max="67"/>
+    <col width="12" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4205,6 +4270,11 @@
           <t>20251229</t>
         </is>
       </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>20251230</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4412,6 +4482,9 @@
       <c r="BO2" t="n">
         <v>4.25</v>
       </c>
+      <c r="BP2" t="n">
+        <v>4.05</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4619,6 +4692,9 @@
       <c r="BO3" t="n">
         <v>3.75</v>
       </c>
+      <c r="BP3" t="n">
+        <v>3.68</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4826,6 +4902,9 @@
       <c r="BO4" t="n">
         <v>5.96</v>
       </c>
+      <c r="BP4" t="n">
+        <v>5.94</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5033,6 +5112,9 @@
       <c r="BO5" t="n">
         <v>5.11</v>
       </c>
+      <c r="BP5" t="n">
+        <v>5.13</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5240,6 +5322,9 @@
       <c r="BO6" t="n">
         <v>5.08</v>
       </c>
+      <c r="BP6" t="n">
+        <v>4.31</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5447,6 +5532,9 @@
       <c r="BO7" t="n">
         <v>5.16</v>
       </c>
+      <c r="BP7" t="n">
+        <v>5.28</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5654,6 +5742,9 @@
       <c r="BO8" t="n">
         <v>7.32</v>
       </c>
+      <c r="BP8" t="n">
+        <v>6.33</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5861,6 +5952,9 @@
       <c r="BO9" t="n">
         <v>1.56</v>
       </c>
+      <c r="BP9" t="n">
+        <v>1.55</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6067,6 +6161,9 @@
       </c>
       <c r="BO10" t="n">
         <v>19.18</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>17.82</v>
       </c>
     </row>
   </sheetData>
@@ -6080,7 +6177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA10"/>
+  <dimension ref="A1:AB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6110,6 +6207,7 @@
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
     <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6248,6 +6346,11 @@
           <t>20251229</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>20251230</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6335,6 +6438,9 @@
       <c r="AA2" t="n">
         <v>26</v>
       </c>
+      <c r="AB2" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6422,6 +6528,9 @@
       <c r="AA3" t="n">
         <v>22</v>
       </c>
+      <c r="AB3" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6509,6 +6618,9 @@
       <c r="AA4" t="n">
         <v>27</v>
       </c>
+      <c r="AB4" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6596,6 +6708,9 @@
       <c r="AA5" t="n">
         <v>24</v>
       </c>
+      <c r="AB5" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6683,6 +6798,9 @@
       <c r="AA6" t="n">
         <v>51</v>
       </c>
+      <c r="AB6" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6770,6 +6888,9 @@
       <c r="AA7" t="n">
         <v>32</v>
       </c>
+      <c r="AB7" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6857,6 +6978,9 @@
       <c r="AA8" t="n">
         <v>29</v>
       </c>
+      <c r="AB8" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6944,6 +7068,9 @@
       <c r="AA9" t="n">
         <v>27</v>
       </c>
+      <c r="AB9" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7030,6 +7157,9 @@
       </c>
       <c r="AA10" t="n">
         <v>40</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -7043,7 +7173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CH10"/>
+  <dimension ref="A1:CI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7132,6 +7262,7 @@
     <col width="12" customWidth="1" min="84" max="84"/>
     <col width="12" customWidth="1" min="85" max="85"/>
     <col width="12" customWidth="1" min="86" max="86"/>
+    <col width="12" customWidth="1" min="87" max="87"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7397,6 +7528,9 @@
       <c r="CH1" s="1" t="n">
         <v>20251229</v>
       </c>
+      <c r="CI1" s="1" t="n">
+        <v>20251230</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7661,6 +7795,9 @@
       <c r="CH2" t="n">
         <v>272.69</v>
       </c>
+      <c r="CI2" t="n">
+        <v>272.81</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7925,6 +8062,9 @@
       <c r="CH3" t="n">
         <v>231.94</v>
       </c>
+      <c r="CI3" t="n">
+        <v>231.205</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8189,6 +8329,9 @@
       <c r="CH4" t="n">
         <v>311.365</v>
       </c>
+      <c r="CI4" t="n">
+        <v>312.5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8453,6 +8596,9 @@
       <c r="CH5" t="n">
         <v>484.855</v>
       </c>
+      <c r="CI5" t="n">
+        <v>485.93</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8717,6 +8863,9 @@
       <c r="CH6" t="n">
         <v>93.98999999999999</v>
       </c>
+      <c r="CI6" t="n">
+        <v>93.52</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8981,6 +9130,9 @@
       <c r="CH7" t="n">
         <v>187.71</v>
       </c>
+      <c r="CI7" t="n">
+        <v>188.24</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9245,6 +9397,9 @@
       <c r="CH8" t="n">
         <v>186.85</v>
       </c>
+      <c r="CI8" t="n">
+        <v>184.35</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9509,6 +9664,9 @@
       <c r="CH9" t="n">
         <v>85.12</v>
       </c>
+      <c r="CI9" t="n">
+        <v>85.23999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9772,6 +9930,9 @@
       </c>
       <c r="CH10" t="n">
         <v>469</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>461.09</v>
       </c>
     </row>
   </sheetData>
@@ -9785,7 +9946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CH10"/>
+  <dimension ref="A1:CI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9874,6 +10035,7 @@
     <col width="12" customWidth="1" min="84" max="84"/>
     <col width="12" customWidth="1" min="85" max="85"/>
     <col width="12" customWidth="1" min="86" max="86"/>
+    <col width="12" customWidth="1" min="87" max="87"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10139,6 +10301,9 @@
       <c r="CH1" s="1" t="n">
         <v>20251229</v>
       </c>
+      <c r="CI1" s="1" t="n">
+        <v>20251230</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10403,6 +10568,9 @@
       <c r="CH2" t="n">
         <v>274.36</v>
       </c>
+      <c r="CI2" t="n">
+        <v>274.08</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10667,6 +10835,9 @@
       <c r="CH3" t="n">
         <v>232.6</v>
       </c>
+      <c r="CI3" t="n">
+        <v>232.77</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10931,6 +11102,9 @@
       <c r="CH4" t="n">
         <v>314.02</v>
       </c>
+      <c r="CI4" t="n">
+        <v>316.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11195,6 +11369,9 @@
       <c r="CH5" t="n">
         <v>488.35</v>
       </c>
+      <c r="CI5" t="n">
+        <v>489.68</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11459,6 +11636,9 @@
       <c r="CH6" t="n">
         <v>94.97</v>
       </c>
+      <c r="CI6" t="n">
+        <v>93.98990000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11723,6 +11903,9 @@
       <c r="CH7" t="n">
         <v>188.755</v>
       </c>
+      <c r="CI7" t="n">
+        <v>188.99</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11987,6 +12170,9 @@
       <c r="CH8" t="n">
         <v>187.2</v>
       </c>
+      <c r="CI8" t="n">
+        <v>184.7289</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12251,6 +12437,9 @@
       <c r="CH9" t="n">
         <v>86.7895</v>
       </c>
+      <c r="CI9" t="n">
+        <v>85.75</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12514,6 +12703,9 @@
       </c>
       <c r="CH10" t="n">
         <v>469.4</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>463.12</v>
       </c>
     </row>
   </sheetData>
@@ -12527,7 +12719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CH10"/>
+  <dimension ref="A1:CI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12616,6 +12808,7 @@
     <col width="12" customWidth="1" min="84" max="84"/>
     <col width="12" customWidth="1" min="85" max="85"/>
     <col width="12" customWidth="1" min="86" max="86"/>
+    <col width="12" customWidth="1" min="87" max="87"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12881,6 +13074,9 @@
       <c r="CH1" s="1" t="n">
         <v>20251229</v>
       </c>
+      <c r="CI1" s="1" t="n">
+        <v>20251230</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13145,6 +13341,9 @@
       <c r="CH2" t="n">
         <v>272.35</v>
       </c>
+      <c r="CI2" t="n">
+        <v>272.28</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13409,6 +13608,9 @@
       <c r="CH3" t="n">
         <v>230.77</v>
       </c>
+      <c r="CI3" t="n">
+        <v>230.2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13673,6 +13875,9 @@
       <c r="CH4" t="n">
         <v>310.62</v>
       </c>
+      <c r="CI4" t="n">
+        <v>312.46</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13937,6 +14142,9 @@
       <c r="CH5" t="n">
         <v>484.18</v>
       </c>
+      <c r="CI5" t="n">
+        <v>485.5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14201,6 +14409,9 @@
       <c r="CH6" t="n">
         <v>93.625</v>
       </c>
+      <c r="CI6" t="n">
+        <v>93.34</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14465,6 +14676,9 @@
       <c r="CH7" t="n">
         <v>185.91</v>
       </c>
+      <c r="CI7" t="n">
+        <v>186.93</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14729,6 +14943,9 @@
       <c r="CH8" t="n">
         <v>183.64</v>
       </c>
+      <c r="CI8" t="n">
+        <v>180.7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14993,6 +15210,9 @@
       <c r="CH9" t="n">
         <v>84.98</v>
       </c>
+      <c r="CI9" t="n">
+        <v>85.05</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15256,6 +15476,9 @@
       </c>
       <c r="CH10" t="n">
         <v>459</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>453.83</v>
       </c>
     </row>
   </sheetData>
@@ -15269,7 +15492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CH10"/>
+  <dimension ref="A1:CI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15358,6 +15581,7 @@
     <col width="12" customWidth="1" min="84" max="84"/>
     <col width="12" customWidth="1" min="85" max="85"/>
     <col width="12" customWidth="1" min="86" max="86"/>
+    <col width="12" customWidth="1" min="87" max="87"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15623,6 +15847,9 @@
       <c r="CH1" s="1" t="n">
         <v>20251229</v>
       </c>
+      <c r="CI1" s="1" t="n">
+        <v>20251230</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15887,6 +16114,9 @@
       <c r="CH2" t="n">
         <v>273.76</v>
       </c>
+      <c r="CI2" t="n">
+        <v>273.08</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16151,6 +16381,9 @@
       <c r="CH3" t="n">
         <v>232.07</v>
       </c>
+      <c r="CI3" t="n">
+        <v>232.53</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16415,6 +16648,9 @@
       <c r="CH4" t="n">
         <v>313.56</v>
       </c>
+      <c r="CI4" t="n">
+        <v>313.85</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16679,6 +16915,9 @@
       <c r="CH5" t="n">
         <v>487.1</v>
       </c>
+      <c r="CI5" t="n">
+        <v>487.48</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16943,6 +17182,9 @@
       <c r="CH6" t="n">
         <v>94.15000000000001</v>
       </c>
+      <c r="CI6" t="n">
+        <v>93.78</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17207,6 +17449,9 @@
       <c r="CH7" t="n">
         <v>188.22</v>
       </c>
+      <c r="CI7" t="n">
+        <v>187.54</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17471,6 +17716,9 @@
       <c r="CH8" t="n">
         <v>184.18</v>
       </c>
+      <c r="CI8" t="n">
+        <v>180.84</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17735,6 +17983,9 @@
       <c r="CH9" t="n">
         <v>85.56999999999999</v>
       </c>
+      <c r="CI9" t="n">
+        <v>85.25</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17998,6 +18249,9 @@
       </c>
       <c r="CH10" t="n">
         <v>459.64</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>454.43</v>
       </c>
     </row>
   </sheetData>
@@ -18011,7 +18265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CH10"/>
+  <dimension ref="A1:CI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18100,6 +18354,7 @@
     <col width="12" customWidth="1" min="84" max="84"/>
     <col width="12" customWidth="1" min="85" max="85"/>
     <col width="12" customWidth="1" min="86" max="86"/>
+    <col width="12" customWidth="1" min="87" max="87"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18365,6 +18620,9 @@
       <c r="CH1" s="1" t="n">
         <v>20251229</v>
       </c>
+      <c r="CI1" s="1" t="n">
+        <v>20251230</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18629,6 +18887,9 @@
       <c r="CH2" t="n">
         <v>23715213</v>
       </c>
+      <c r="CI2" t="n">
+        <v>22139617</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18893,6 +19154,9 @@
       <c r="CH3" t="n">
         <v>19797909</v>
       </c>
+      <c r="CI3" t="n">
+        <v>21910453</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19157,6 +19421,9 @@
       <c r="CH4" t="n">
         <v>19621777</v>
       </c>
+      <c r="CI4" t="n">
+        <v>17380888</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19421,6 +19688,9 @@
       <c r="CH5" t="n">
         <v>10893408</v>
       </c>
+      <c r="CI5" t="n">
+        <v>13944512</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19685,6 +19955,9 @@
       <c r="CH6" t="n">
         <v>24493738</v>
       </c>
+      <c r="CI6" t="n">
+        <v>23422033</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19949,6 +20222,9 @@
       <c r="CH7" t="n">
         <v>120006103</v>
       </c>
+      <c r="CI7" t="n">
+        <v>97687274</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20213,6 +20489,9 @@
       <c r="CH8" t="n">
         <v>28242003</v>
       </c>
+      <c r="CI8" t="n">
+        <v>23336307</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20477,6 +20756,9 @@
       <c r="CH9" t="n">
         <v>5352446</v>
       </c>
+      <c r="CI9" t="n">
+        <v>4540473</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20740,6 +21022,9 @@
       </c>
       <c r="CH10" t="n">
         <v>66263033</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>59238464</v>
       </c>
     </row>
   </sheetData>
@@ -20753,7 +21038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO10"/>
+  <dimension ref="A1:BP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20823,6 +21108,7 @@
     <col width="10" customWidth="1" min="65" max="65"/>
     <col width="10" customWidth="1" min="66" max="66"/>
     <col width="10" customWidth="1" min="67" max="67"/>
+    <col width="10" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21031,6 +21317,9 @@
       <c r="BO1" s="1" t="n">
         <v>20251229</v>
       </c>
+      <c r="BP1" s="1" t="n">
+        <v>20251230</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21238,6 +21527,9 @@
       <c r="BO2" t="n">
         <v>18</v>
       </c>
+      <c r="BP2" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21445,6 +21737,9 @@
       <c r="BO3" t="n">
         <v>82</v>
       </c>
+      <c r="BP3" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -21652,6 +21947,9 @@
       <c r="BO4" t="n">
         <v>69</v>
       </c>
+      <c r="BP4" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -21859,6 +22157,9 @@
       <c r="BO5" t="n">
         <v>71</v>
       </c>
+      <c r="BP5" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -22066,6 +22367,9 @@
       <c r="BO6" t="n">
         <v>9</v>
       </c>
+      <c r="BP6" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -22273,6 +22577,9 @@
       <c r="BO7" t="n">
         <v>88</v>
       </c>
+      <c r="BP7" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22480,6 +22787,9 @@
       <c r="BO8" t="n">
         <v>63</v>
       </c>
+      <c r="BP8" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22687,6 +22997,9 @@
       <c r="BO9" t="n">
         <v>46</v>
       </c>
+      <c r="BP9" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22893,6 +23206,9 @@
       </c>
       <c r="BO10" t="n">
         <v>50</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -22906,7 +23222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA10"/>
+  <dimension ref="A1:AB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22936,6 +23252,7 @@
     <col width="10" customWidth="1" min="25" max="25"/>
     <col width="10" customWidth="1" min="26" max="26"/>
     <col width="10" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23024,6 +23341,9 @@
       <c r="AA1" s="1" t="n">
         <v>20251229</v>
       </c>
+      <c r="AB1" s="1" t="n">
+        <v>20251230</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23111,6 +23431,9 @@
       <c r="AA2" t="n">
         <v>70</v>
       </c>
+      <c r="AB2" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23198,6 +23521,9 @@
       <c r="AA3" t="n">
         <v>46</v>
       </c>
+      <c r="AB3" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23285,6 +23611,9 @@
       <c r="AA4" t="n">
         <v>89</v>
       </c>
+      <c r="AB4" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23372,6 +23701,9 @@
       <c r="AA5" t="n">
         <v>21</v>
       </c>
+      <c r="AB5" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23459,6 +23791,9 @@
       <c r="AA6" t="n">
         <v>0</v>
       </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23546,6 +23881,9 @@
       <c r="AA7" t="n">
         <v>48</v>
       </c>
+      <c r="AB7" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23633,6 +23971,9 @@
       <c r="AA8" t="n">
         <v>56</v>
       </c>
+      <c r="AB8" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23720,6 +24061,9 @@
       <c r="AA9" t="n">
         <v>65</v>
       </c>
+      <c r="AB9" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23806,6 +24150,9 @@
       </c>
       <c r="AA10" t="n">
         <v>69</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -23819,7 +24166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO10"/>
+  <dimension ref="A1:BP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23889,6 +24236,7 @@
     <col width="10" customWidth="1" min="65" max="65"/>
     <col width="10" customWidth="1" min="66" max="66"/>
     <col width="10" customWidth="1" min="67" max="67"/>
+    <col width="10" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24097,6 +24445,9 @@
       <c r="BO1" s="1" t="n">
         <v>20251229</v>
       </c>
+      <c r="BP1" s="1" t="n">
+        <v>20251230</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24304,6 +24655,9 @@
       <c r="BO2" t="n">
         <v>-34</v>
       </c>
+      <c r="BP2" t="n">
+        <v>-37</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -24511,6 +24865,9 @@
       <c r="BO3" t="n">
         <v>40</v>
       </c>
+      <c r="BP3" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -24718,6 +25075,9 @@
       <c r="BO4" t="n">
         <v>9</v>
       </c>
+      <c r="BP4" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24925,6 +25285,9 @@
       <c r="BO5" t="n">
         <v>32</v>
       </c>
+      <c r="BP5" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -25132,6 +25495,9 @@
       <c r="BO6" t="n">
         <v>-28</v>
       </c>
+      <c r="BP6" t="n">
+        <v>-29</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -25339,6 +25705,9 @@
       <c r="BO7" t="n">
         <v>60</v>
       </c>
+      <c r="BP7" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25546,6 +25915,9 @@
       <c r="BO8" t="n">
         <v>2</v>
       </c>
+      <c r="BP8" t="n">
+        <v>-29</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25753,6 +26125,9 @@
       <c r="BO9" t="n">
         <v>9</v>
       </c>
+      <c r="BP9" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25959,6 +26334,9 @@
       </c>
       <c r="BO10" t="n">
         <v>-7</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>-25</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB10"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -632,6 +632,7 @@
     <col width="10" customWidth="1" min="26" max="26"/>
     <col width="10" customWidth="1" min="27" max="27"/>
     <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -723,6 +724,9 @@
       <c r="AB1" s="1" t="n">
         <v>20251230</v>
       </c>
+      <c r="AC1" s="1" t="n">
+        <v>20251231</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -813,6 +817,9 @@
       <c r="AB2" t="n">
         <v>21</v>
       </c>
+      <c r="AC2" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -903,6 +910,9 @@
       <c r="AB3" t="n">
         <v>17</v>
       </c>
+      <c r="AC3" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -993,6 +1003,9 @@
       <c r="AB4" t="n">
         <v>49</v>
       </c>
+      <c r="AC4" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1083,6 +1096,9 @@
       <c r="AB5" t="n">
         <v>-35</v>
       </c>
+      <c r="AC5" t="n">
+        <v>-44</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1173,6 +1189,9 @@
       <c r="AB6" t="n">
         <v>-50</v>
       </c>
+      <c r="AC6" t="n">
+        <v>-48</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1263,6 +1282,9 @@
       <c r="AB7" t="n">
         <v>9</v>
       </c>
+      <c r="AC7" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1353,6 +1375,9 @@
       <c r="AB8" t="n">
         <v>-1</v>
       </c>
+      <c r="AC8" t="n">
+        <v>-16</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1443,6 +1468,9 @@
       <c r="AB9" t="n">
         <v>21</v>
       </c>
+      <c r="AC9" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1532,6 +1560,9 @@
       </c>
       <c r="AB10" t="n">
         <v>23</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1545,7 +1576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP10"/>
+  <dimension ref="A1:BQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1616,6 +1647,7 @@
     <col width="12" customWidth="1" min="66" max="66"/>
     <col width="12" customWidth="1" min="67" max="67"/>
     <col width="12" customWidth="1" min="68" max="68"/>
+    <col width="12" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1959,6 +1991,11 @@
           <t>20251230</t>
         </is>
       </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>20251231</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2169,6 +2206,9 @@
       <c r="BP2" t="n">
         <v>99</v>
       </c>
+      <c r="BQ2" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2379,6 +2419,9 @@
       <c r="BP3" t="n">
         <v>102</v>
       </c>
+      <c r="BQ3" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2589,6 +2632,9 @@
       <c r="BP4" t="n">
         <v>100</v>
       </c>
+      <c r="BQ4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2799,6 +2845,9 @@
       <c r="BP5" t="n">
         <v>101</v>
       </c>
+      <c r="BQ5" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3009,6 +3058,9 @@
       <c r="BP6" t="n">
         <v>97</v>
       </c>
+      <c r="BQ6" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3219,6 +3271,9 @@
       <c r="BP7" t="n">
         <v>103</v>
       </c>
+      <c r="BQ7" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3429,6 +3484,9 @@
       <c r="BP8" t="n">
         <v>98</v>
       </c>
+      <c r="BQ8" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3639,6 +3697,9 @@
       <c r="BP9" t="n">
         <v>100</v>
       </c>
+      <c r="BQ9" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3848,6 +3909,9 @@
       </c>
       <c r="BP10" t="n">
         <v>98</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -3861,7 +3925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP10"/>
+  <dimension ref="A1:BQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3932,6 +3996,7 @@
     <col width="12" customWidth="1" min="66" max="66"/>
     <col width="12" customWidth="1" min="67" max="67"/>
     <col width="12" customWidth="1" min="68" max="68"/>
+    <col width="12" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4275,6 +4340,11 @@
           <t>20251230</t>
         </is>
       </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>20251231</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4485,6 +4555,9 @@
       <c r="BP2" t="n">
         <v>4.05</v>
       </c>
+      <c r="BQ2" t="n">
+        <v>3.44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4695,6 +4768,9 @@
       <c r="BP3" t="n">
         <v>3.68</v>
       </c>
+      <c r="BQ3" t="n">
+        <v>3.49</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4905,6 +4981,9 @@
       <c r="BP4" t="n">
         <v>5.94</v>
       </c>
+      <c r="BQ4" t="n">
+        <v>5.89</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5115,6 +5194,9 @@
       <c r="BP5" t="n">
         <v>5.13</v>
       </c>
+      <c r="BQ5" t="n">
+        <v>4.93</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5325,6 +5407,9 @@
       <c r="BP6" t="n">
         <v>4.31</v>
       </c>
+      <c r="BQ6" t="n">
+        <v>3.13</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5535,6 +5620,9 @@
       <c r="BP7" t="n">
         <v>5.28</v>
       </c>
+      <c r="BQ7" t="n">
+        <v>5.36</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5745,6 +5833,9 @@
       <c r="BP8" t="n">
         <v>6.33</v>
       </c>
+      <c r="BQ8" t="n">
+        <v>5.71</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5955,6 +6046,9 @@
       <c r="BP9" t="n">
         <v>1.55</v>
       </c>
+      <c r="BQ9" t="n">
+        <v>1.57</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6164,6 +6258,9 @@
       </c>
       <c r="BP10" t="n">
         <v>17.82</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>16.34</v>
       </c>
     </row>
   </sheetData>
@@ -6177,7 +6274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB10"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6208,6 +6305,7 @@
     <col width="12" customWidth="1" min="26" max="26"/>
     <col width="12" customWidth="1" min="27" max="27"/>
     <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6351,6 +6449,11 @@
           <t>20251230</t>
         </is>
       </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>20251231</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6441,6 +6544,9 @@
       <c r="AB2" t="n">
         <v>24</v>
       </c>
+      <c r="AC2" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6531,6 +6637,9 @@
       <c r="AB3" t="n">
         <v>24</v>
       </c>
+      <c r="AC3" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6621,6 +6730,9 @@
       <c r="AB4" t="n">
         <v>24</v>
       </c>
+      <c r="AC4" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6711,6 +6823,9 @@
       <c r="AB5" t="n">
         <v>31</v>
       </c>
+      <c r="AC5" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6801,6 +6916,9 @@
       <c r="AB6" t="n">
         <v>48</v>
       </c>
+      <c r="AC6" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6891,6 +7009,9 @@
       <c r="AB7" t="n">
         <v>26</v>
       </c>
+      <c r="AC7" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6981,6 +7102,9 @@
       <c r="AB8" t="n">
         <v>25</v>
       </c>
+      <c r="AC8" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7071,6 +7195,9 @@
       <c r="AB9" t="n">
         <v>23</v>
       </c>
+      <c r="AC9" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7160,6 +7287,9 @@
       </c>
       <c r="AB10" t="n">
         <v>37</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -7173,7 +7303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI10"/>
+  <dimension ref="A1:CJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7263,6 +7393,7 @@
     <col width="12" customWidth="1" min="85" max="85"/>
     <col width="12" customWidth="1" min="86" max="86"/>
     <col width="12" customWidth="1" min="87" max="87"/>
+    <col width="12" customWidth="1" min="88" max="88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7531,6 +7662,9 @@
       <c r="CI1" s="1" t="n">
         <v>20251230</v>
       </c>
+      <c r="CJ1" s="1" t="n">
+        <v>20251231</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7798,6 +7932,9 @@
       <c r="CI2" t="n">
         <v>272.81</v>
       </c>
+      <c r="CJ2" t="n">
+        <v>273.06</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8065,6 +8202,9 @@
       <c r="CI3" t="n">
         <v>231.205</v>
       </c>
+      <c r="CJ3" t="n">
+        <v>232.905</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8332,6 +8472,9 @@
       <c r="CI4" t="n">
         <v>312.5</v>
       </c>
+      <c r="CJ4" t="n">
+        <v>312.845</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8599,6 +8742,9 @@
       <c r="CI5" t="n">
         <v>485.93</v>
       </c>
+      <c r="CJ5" t="n">
+        <v>487.84</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8866,6 +9012,9 @@
       <c r="CI6" t="n">
         <v>93.52</v>
       </c>
+      <c r="CJ6" t="n">
+        <v>93.59999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9133,6 +9282,9 @@
       <c r="CI7" t="n">
         <v>188.24</v>
       </c>
+      <c r="CJ7" t="n">
+        <v>189.57</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9400,6 +9552,9 @@
       <c r="CI8" t="n">
         <v>184.35</v>
       </c>
+      <c r="CJ8" t="n">
+        <v>181.13</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9667,6 +9822,9 @@
       <c r="CI9" t="n">
         <v>85.23999999999999</v>
       </c>
+      <c r="CJ9" t="n">
+        <v>85.11</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9933,6 +10091,9 @@
       </c>
       <c r="CI10" t="n">
         <v>461.09</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>456.1</v>
       </c>
     </row>
   </sheetData>
@@ -9946,7 +10107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI10"/>
+  <dimension ref="A1:CJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10036,6 +10197,7 @@
     <col width="12" customWidth="1" min="85" max="85"/>
     <col width="12" customWidth="1" min="86" max="86"/>
     <col width="12" customWidth="1" min="87" max="87"/>
+    <col width="12" customWidth="1" min="88" max="88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10304,6 +10466,9 @@
       <c r="CI1" s="1" t="n">
         <v>20251230</v>
       </c>
+      <c r="CJ1" s="1" t="n">
+        <v>20251231</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10571,6 +10736,9 @@
       <c r="CI2" t="n">
         <v>274.08</v>
       </c>
+      <c r="CJ2" t="n">
+        <v>273.68</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10838,6 +11006,9 @@
       <c r="CI3" t="n">
         <v>232.77</v>
       </c>
+      <c r="CJ3" t="n">
+        <v>232.99</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11105,6 +11276,9 @@
       <c r="CI4" t="n">
         <v>316.95</v>
       </c>
+      <c r="CJ4" t="n">
+        <v>314.58</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11372,6 +11546,9 @@
       <c r="CI5" t="n">
         <v>489.68</v>
       </c>
+      <c r="CJ5" t="n">
+        <v>488.14</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11639,6 +11816,9 @@
       <c r="CI6" t="n">
         <v>93.98990000000001</v>
       </c>
+      <c r="CJ6" t="n">
+        <v>94.30500000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11906,6 +12086,9 @@
       <c r="CI7" t="n">
         <v>188.99</v>
       </c>
+      <c r="CJ7" t="n">
+        <v>190.56</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12173,6 +12356,9 @@
       <c r="CI8" t="n">
         <v>184.7289</v>
       </c>
+      <c r="CJ8" t="n">
+        <v>181.53</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12440,6 +12626,9 @@
       <c r="CI9" t="n">
         <v>85.75</v>
       </c>
+      <c r="CJ9" t="n">
+        <v>85.18000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12706,6 +12895,9 @@
       </c>
       <c r="CI10" t="n">
         <v>463.12</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>456.55</v>
       </c>
     </row>
   </sheetData>
@@ -12719,7 +12911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI10"/>
+  <dimension ref="A1:CJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12809,6 +13001,7 @@
     <col width="12" customWidth="1" min="85" max="85"/>
     <col width="12" customWidth="1" min="86" max="86"/>
     <col width="12" customWidth="1" min="87" max="87"/>
+    <col width="12" customWidth="1" min="88" max="88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13077,6 +13270,9 @@
       <c r="CI1" s="1" t="n">
         <v>20251230</v>
       </c>
+      <c r="CJ1" s="1" t="n">
+        <v>20251231</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13344,6 +13540,9 @@
       <c r="CI2" t="n">
         <v>272.28</v>
       </c>
+      <c r="CJ2" t="n">
+        <v>271.75</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13611,6 +13810,9 @@
       <c r="CI3" t="n">
         <v>230.2</v>
       </c>
+      <c r="CJ3" t="n">
+        <v>230.12</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13878,6 +14080,9 @@
       <c r="CI4" t="n">
         <v>312.46</v>
       </c>
+      <c r="CJ4" t="n">
+        <v>311.44</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14145,6 +14350,9 @@
       <c r="CI5" t="n">
         <v>485.5</v>
       </c>
+      <c r="CJ5" t="n">
+        <v>483.3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14412,6 +14620,9 @@
       <c r="CI6" t="n">
         <v>93.34</v>
       </c>
+      <c r="CJ6" t="n">
+        <v>93.2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14679,6 +14890,9 @@
       <c r="CI7" t="n">
         <v>186.93</v>
       </c>
+      <c r="CJ7" t="n">
+        <v>186.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14946,6 +15160,9 @@
       <c r="CI8" t="n">
         <v>180.7</v>
       </c>
+      <c r="CJ8" t="n">
+        <v>177.25</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15213,6 +15430,9 @@
       <c r="CI9" t="n">
         <v>85.05</v>
       </c>
+      <c r="CJ9" t="n">
+        <v>84.12</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15479,6 +15699,9 @@
       </c>
       <c r="CI10" t="n">
         <v>453.83</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>449.3</v>
       </c>
     </row>
   </sheetData>
@@ -15492,7 +15715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI10"/>
+  <dimension ref="A1:CJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15582,6 +15805,7 @@
     <col width="12" customWidth="1" min="85" max="85"/>
     <col width="12" customWidth="1" min="86" max="86"/>
     <col width="12" customWidth="1" min="87" max="87"/>
+    <col width="12" customWidth="1" min="88" max="88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15850,6 +16074,9 @@
       <c r="CI1" s="1" t="n">
         <v>20251230</v>
       </c>
+      <c r="CJ1" s="1" t="n">
+        <v>20251231</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16117,6 +16344,9 @@
       <c r="CI2" t="n">
         <v>273.08</v>
       </c>
+      <c r="CJ2" t="n">
+        <v>271.86</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16384,6 +16614,9 @@
       <c r="CI3" t="n">
         <v>232.53</v>
       </c>
+      <c r="CJ3" t="n">
+        <v>230.82</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16651,6 +16884,9 @@
       <c r="CI4" t="n">
         <v>313.85</v>
       </c>
+      <c r="CJ4" t="n">
+        <v>313</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16918,6 +17154,9 @@
       <c r="CI5" t="n">
         <v>487.48</v>
       </c>
+      <c r="CJ5" t="n">
+        <v>483.62</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17185,6 +17424,9 @@
       <c r="CI6" t="n">
         <v>93.78</v>
       </c>
+      <c r="CJ6" t="n">
+        <v>93.76000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17452,6 +17694,9 @@
       <c r="CI7" t="n">
         <v>187.54</v>
       </c>
+      <c r="CJ7" t="n">
+        <v>186.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17719,6 +17964,9 @@
       <c r="CI8" t="n">
         <v>180.84</v>
       </c>
+      <c r="CJ8" t="n">
+        <v>177.75</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17986,6 +18234,9 @@
       <c r="CI9" t="n">
         <v>85.25</v>
       </c>
+      <c r="CJ9" t="n">
+        <v>84.20999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18252,6 +18503,9 @@
       </c>
       <c r="CI10" t="n">
         <v>454.43</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>449.72</v>
       </c>
     </row>
   </sheetData>
@@ -18265,7 +18519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI10"/>
+  <dimension ref="A1:CJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18355,6 +18609,7 @@
     <col width="12" customWidth="1" min="85" max="85"/>
     <col width="12" customWidth="1" min="86" max="86"/>
     <col width="12" customWidth="1" min="87" max="87"/>
+    <col width="12" customWidth="1" min="88" max="88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18623,6 +18878,9 @@
       <c r="CI1" s="1" t="n">
         <v>20251230</v>
       </c>
+      <c r="CJ1" s="1" t="n">
+        <v>20251231</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18890,6 +19148,9 @@
       <c r="CI2" t="n">
         <v>22139617</v>
       </c>
+      <c r="CJ2" t="n">
+        <v>27293639</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19157,6 +19418,9 @@
       <c r="CI3" t="n">
         <v>21910453</v>
       </c>
+      <c r="CJ3" t="n">
+        <v>24383749</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19424,6 +19688,9 @@
       <c r="CI4" t="n">
         <v>17380888</v>
       </c>
+      <c r="CJ4" t="n">
+        <v>16377689</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19691,6 +19958,9 @@
       <c r="CI5" t="n">
         <v>13944512</v>
       </c>
+      <c r="CJ5" t="n">
+        <v>15601554</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19958,6 +20228,9 @@
       <c r="CI6" t="n">
         <v>23422033</v>
       </c>
+      <c r="CJ6" t="n">
+        <v>23495191</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20225,6 +20498,9 @@
       <c r="CI7" t="n">
         <v>97687274</v>
       </c>
+      <c r="CJ7" t="n">
+        <v>120100484</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20492,6 +20768,9 @@
       <c r="CI8" t="n">
         <v>23336307</v>
       </c>
+      <c r="CJ8" t="n">
+        <v>22997438</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20759,6 +21038,9 @@
       <c r="CI9" t="n">
         <v>4540473</v>
       </c>
+      <c r="CJ9" t="n">
+        <v>5293385</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21025,6 +21307,9 @@
       </c>
       <c r="CI10" t="n">
         <v>59238464</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>49077961</v>
       </c>
     </row>
   </sheetData>
@@ -21038,7 +21323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP10"/>
+  <dimension ref="A1:BQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21109,6 +21394,7 @@
     <col width="10" customWidth="1" min="66" max="66"/>
     <col width="10" customWidth="1" min="67" max="67"/>
     <col width="10" customWidth="1" min="68" max="68"/>
+    <col width="10" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21320,6 +21606,9 @@
       <c r="BP1" s="1" t="n">
         <v>20251230</v>
       </c>
+      <c r="BQ1" s="1" t="n">
+        <v>20251231</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21530,6 +21819,9 @@
       <c r="BP2" t="n">
         <v>14</v>
       </c>
+      <c r="BQ2" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21740,6 +22032,9 @@
       <c r="BP3" t="n">
         <v>86</v>
       </c>
+      <c r="BQ3" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -21950,6 +22245,9 @@
       <c r="BP4" t="n">
         <v>70</v>
       </c>
+      <c r="BQ4" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -22160,6 +22458,9 @@
       <c r="BP5" t="n">
         <v>74</v>
       </c>
+      <c r="BQ5" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -22370,6 +22671,9 @@
       <c r="BP6" t="n">
         <v>6</v>
       </c>
+      <c r="BQ6" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -22580,6 +22884,9 @@
       <c r="BP7" t="n">
         <v>85</v>
       </c>
+      <c r="BQ7" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22790,6 +23097,9 @@
       <c r="BP8" t="n">
         <v>43</v>
       </c>
+      <c r="BQ8" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23000,6 +23310,9 @@
       <c r="BP9" t="n">
         <v>42</v>
       </c>
+      <c r="BQ9" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23209,6 +23522,9 @@
       </c>
       <c r="BP10" t="n">
         <v>42</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -23222,7 +23538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB10"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23253,6 +23569,7 @@
     <col width="10" customWidth="1" min="26" max="26"/>
     <col width="10" customWidth="1" min="27" max="27"/>
     <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23344,6 +23661,9 @@
       <c r="AB1" s="1" t="n">
         <v>20251230</v>
       </c>
+      <c r="AC1" s="1" t="n">
+        <v>20251231</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23434,6 +23754,9 @@
       <c r="AB2" t="n">
         <v>68</v>
       </c>
+      <c r="AC2" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23524,6 +23847,9 @@
       <c r="AB3" t="n">
         <v>48</v>
       </c>
+      <c r="AC3" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23614,6 +23940,9 @@
       <c r="AB4" t="n">
         <v>89</v>
       </c>
+      <c r="AC4" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23704,6 +24033,9 @@
       <c r="AB5" t="n">
         <v>22</v>
       </c>
+      <c r="AC5" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23794,6 +24126,9 @@
       <c r="AB6" t="n">
         <v>0</v>
       </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23884,6 +24219,9 @@
       <c r="AB7" t="n">
         <v>46</v>
       </c>
+      <c r="AC7" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23974,6 +24312,9 @@
       <c r="AB8" t="n">
         <v>50</v>
       </c>
+      <c r="AC8" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24064,6 +24405,9 @@
       <c r="AB9" t="n">
         <v>62</v>
       </c>
+      <c r="AC9" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24153,6 +24497,9 @@
       </c>
       <c r="AB10" t="n">
         <v>64</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -24166,7 +24513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP10"/>
+  <dimension ref="A1:BQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24237,6 +24584,7 @@
     <col width="10" customWidth="1" min="66" max="66"/>
     <col width="10" customWidth="1" min="67" max="67"/>
     <col width="10" customWidth="1" min="68" max="68"/>
+    <col width="10" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24448,6 +24796,9 @@
       <c r="BP1" s="1" t="n">
         <v>20251230</v>
       </c>
+      <c r="BQ1" s="1" t="n">
+        <v>20251231</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24658,6 +25009,9 @@
       <c r="BP2" t="n">
         <v>-37</v>
       </c>
+      <c r="BQ2" t="n">
+        <v>-51</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -24868,6 +25222,9 @@
       <c r="BP3" t="n">
         <v>47</v>
       </c>
+      <c r="BQ3" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -25078,6 +25435,9 @@
       <c r="BP4" t="n">
         <v>12</v>
       </c>
+      <c r="BQ4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -25288,6 +25648,9 @@
       <c r="BP5" t="n">
         <v>36</v>
       </c>
+      <c r="BQ5" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -25498,6 +25861,9 @@
       <c r="BP6" t="n">
         <v>-29</v>
       </c>
+      <c r="BQ6" t="n">
+        <v>-28</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -25708,6 +26074,9 @@
       <c r="BP7" t="n">
         <v>49</v>
       </c>
+      <c r="BQ7" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25918,6 +26287,9 @@
       <c r="BP8" t="n">
         <v>-29</v>
       </c>
+      <c r="BQ8" t="n">
+        <v>-62</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -26128,6 +26500,9 @@
       <c r="BP9" t="n">
         <v>-2</v>
       </c>
+      <c r="BQ9" t="n">
+        <v>-32</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26337,6 +26712,9 @@
       </c>
       <c r="BP10" t="n">
         <v>-25</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>-45</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -633,6 +633,7 @@
     <col width="10" customWidth="1" min="27" max="27"/>
     <col width="10" customWidth="1" min="28" max="28"/>
     <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -727,6 +728,9 @@
       <c r="AC1" s="1" t="n">
         <v>20251231</v>
       </c>
+      <c r="AD1" s="1" t="n">
+        <v>20260102</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -820,6 +824,9 @@
       <c r="AC2" t="n">
         <v>14</v>
       </c>
+      <c r="AD2" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -913,6 +920,9 @@
       <c r="AC3" t="n">
         <v>8</v>
       </c>
+      <c r="AD3" t="n">
+        <v>-15</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1006,6 +1016,9 @@
       <c r="AC4" t="n">
         <v>46</v>
       </c>
+      <c r="AD4" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1099,6 +1112,9 @@
       <c r="AC5" t="n">
         <v>-44</v>
       </c>
+      <c r="AD5" t="n">
+        <v>-70</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1192,6 +1208,9 @@
       <c r="AC6" t="n">
         <v>-48</v>
       </c>
+      <c r="AD6" t="n">
+        <v>-47</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1285,6 +1304,9 @@
       <c r="AC7" t="n">
         <v>3</v>
       </c>
+      <c r="AD7" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1378,6 +1400,9 @@
       <c r="AC8" t="n">
         <v>-16</v>
       </c>
+      <c r="AD8" t="n">
+        <v>-60</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1471,6 +1496,9 @@
       <c r="AC9" t="n">
         <v>-2</v>
       </c>
+      <c r="AD9" t="n">
+        <v>-9</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1563,6 +1591,9 @@
       </c>
       <c r="AC10" t="n">
         <v>14</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-11</v>
       </c>
     </row>
   </sheetData>
@@ -1576,7 +1607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ10"/>
+  <dimension ref="A1:BR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1648,6 +1679,7 @@
     <col width="12" customWidth="1" min="67" max="67"/>
     <col width="12" customWidth="1" min="68" max="68"/>
     <col width="12" customWidth="1" min="69" max="69"/>
+    <col width="12" customWidth="1" min="70" max="70"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1996,6 +2028,11 @@
           <t>20251231</t>
         </is>
       </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>20260102</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2209,6 +2246,9 @@
       <c r="BQ2" t="n">
         <v>99</v>
       </c>
+      <c r="BR2" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2422,6 +2462,9 @@
       <c r="BQ3" t="n">
         <v>101</v>
       </c>
+      <c r="BR3" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2635,6 +2678,9 @@
       <c r="BQ4" t="n">
         <v>100</v>
       </c>
+      <c r="BR4" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2848,6 +2894,9 @@
       <c r="BQ5" t="n">
         <v>100</v>
       </c>
+      <c r="BR5" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3061,6 +3110,9 @@
       <c r="BQ6" t="n">
         <v>98</v>
       </c>
+      <c r="BR6" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3274,6 +3326,9 @@
       <c r="BQ7" t="n">
         <v>102</v>
       </c>
+      <c r="BR7" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3487,6 +3542,9 @@
       <c r="BQ8" t="n">
         <v>96</v>
       </c>
+      <c r="BR8" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3700,6 +3758,9 @@
       <c r="BQ9" t="n">
         <v>99</v>
       </c>
+      <c r="BR9" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3912,6 +3973,9 @@
       </c>
       <c r="BQ10" t="n">
         <v>97</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -6274,7 +6338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6306,6 +6370,7 @@
     <col width="12" customWidth="1" min="27" max="27"/>
     <col width="12" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6454,6 +6519,11 @@
           <t>20251231</t>
         </is>
       </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>20260102</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6547,6 +6617,9 @@
       <c r="AC2" t="n">
         <v>30</v>
       </c>
+      <c r="AD2" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6640,6 +6713,9 @@
       <c r="AC3" t="n">
         <v>27</v>
       </c>
+      <c r="AD3" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6733,6 +6809,9 @@
       <c r="AC4" t="n">
         <v>23</v>
       </c>
+      <c r="AD4" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6826,6 +6905,9 @@
       <c r="AC5" t="n">
         <v>34</v>
       </c>
+      <c r="AD5" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6919,6 +7001,9 @@
       <c r="AC6" t="n">
         <v>48</v>
       </c>
+      <c r="AD6" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7012,6 +7097,9 @@
       <c r="AC7" t="n">
         <v>32</v>
       </c>
+      <c r="AD7" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7105,6 +7193,9 @@
       <c r="AC8" t="n">
         <v>25</v>
       </c>
+      <c r="AD8" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7198,6 +7289,9 @@
       <c r="AC9" t="n">
         <v>27</v>
       </c>
+      <c r="AD9" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7290,6 +7384,9 @@
       </c>
       <c r="AC10" t="n">
         <v>31</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -7303,7 +7400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ10"/>
+  <dimension ref="A1:CK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7394,6 +7491,7 @@
     <col width="12" customWidth="1" min="86" max="86"/>
     <col width="12" customWidth="1" min="87" max="87"/>
     <col width="12" customWidth="1" min="88" max="88"/>
+    <col width="12" customWidth="1" min="89" max="89"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7665,6 +7763,9 @@
       <c r="CJ1" s="1" t="n">
         <v>20251231</v>
       </c>
+      <c r="CK1" s="1" t="n">
+        <v>20260102</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7935,6 +8036,9 @@
       <c r="CJ2" t="n">
         <v>273.06</v>
       </c>
+      <c r="CK2" t="n">
+        <v>272.255</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8205,6 +8309,9 @@
       <c r="CJ3" t="n">
         <v>232.905</v>
       </c>
+      <c r="CK3" t="n">
+        <v>231.34</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8475,6 +8582,9 @@
       <c r="CJ4" t="n">
         <v>312.845</v>
       </c>
+      <c r="CK4" t="n">
+        <v>316.9</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8745,6 +8855,9 @@
       <c r="CJ5" t="n">
         <v>487.84</v>
       </c>
+      <c r="CK5" t="n">
+        <v>484.385</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9015,6 +9128,9 @@
       <c r="CJ6" t="n">
         <v>93.59999999999999</v>
       </c>
+      <c r="CK6" t="n">
+        <v>94.13</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9285,6 +9401,9 @@
       <c r="CJ7" t="n">
         <v>189.57</v>
       </c>
+      <c r="CK7" t="n">
+        <v>189.835</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9555,6 +9674,9 @@
       <c r="CJ8" t="n">
         <v>181.13</v>
       </c>
+      <c r="CK8" t="n">
+        <v>181.3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9825,6 +9947,9 @@
       <c r="CJ9" t="n">
         <v>85.11</v>
       </c>
+      <c r="CK9" t="n">
+        <v>84.22</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10094,6 +10219,9 @@
       </c>
       <c r="CJ10" t="n">
         <v>456.1</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>457.8</v>
       </c>
     </row>
   </sheetData>
@@ -10107,7 +10235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ10"/>
+  <dimension ref="A1:CK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10198,6 +10326,7 @@
     <col width="12" customWidth="1" min="86" max="86"/>
     <col width="12" customWidth="1" min="87" max="87"/>
     <col width="12" customWidth="1" min="88" max="88"/>
+    <col width="12" customWidth="1" min="89" max="89"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10469,6 +10598,9 @@
       <c r="CJ1" s="1" t="n">
         <v>20251231</v>
       </c>
+      <c r="CK1" s="1" t="n">
+        <v>20260102</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10739,6 +10871,9 @@
       <c r="CJ2" t="n">
         <v>273.68</v>
       </c>
+      <c r="CK2" t="n">
+        <v>277.84</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11009,6 +11144,9 @@
       <c r="CJ3" t="n">
         <v>232.99</v>
       </c>
+      <c r="CK3" t="n">
+        <v>235.458</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11279,6 +11417,9 @@
       <c r="CJ4" t="n">
         <v>314.58</v>
       </c>
+      <c r="CK4" t="n">
+        <v>322.5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11549,6 +11690,9 @@
       <c r="CJ5" t="n">
         <v>488.14</v>
       </c>
+      <c r="CK5" t="n">
+        <v>484.66</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11819,6 +11963,9 @@
       <c r="CJ6" t="n">
         <v>94.30500000000001</v>
       </c>
+      <c r="CK6" t="n">
+        <v>94.13</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12089,6 +12236,9 @@
       <c r="CJ7" t="n">
         <v>190.56</v>
       </c>
+      <c r="CK7" t="n">
+        <v>192.9299</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12359,6 +12509,9 @@
       <c r="CJ8" t="n">
         <v>181.53</v>
       </c>
+      <c r="CK8" t="n">
+        <v>181.35</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12629,6 +12782,9 @@
       <c r="CJ9" t="n">
         <v>85.18000000000001</v>
       </c>
+      <c r="CK9" t="n">
+        <v>84.95999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12898,6 +13054,9 @@
       </c>
       <c r="CJ10" t="n">
         <v>456.55</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>458.34</v>
       </c>
     </row>
   </sheetData>
@@ -12911,7 +13070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ10"/>
+  <dimension ref="A1:CK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13002,6 +13161,7 @@
     <col width="12" customWidth="1" min="86" max="86"/>
     <col width="12" customWidth="1" min="87" max="87"/>
     <col width="12" customWidth="1" min="88" max="88"/>
+    <col width="12" customWidth="1" min="89" max="89"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13273,6 +13433,9 @@
       <c r="CJ1" s="1" t="n">
         <v>20251231</v>
       </c>
+      <c r="CK1" s="1" t="n">
+        <v>20260102</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13543,6 +13706,9 @@
       <c r="CJ2" t="n">
         <v>271.75</v>
       </c>
+      <c r="CK2" t="n">
+        <v>269</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13813,6 +13979,9 @@
       <c r="CJ3" t="n">
         <v>230.12</v>
       </c>
+      <c r="CK3" t="n">
+        <v>224.7</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14083,6 +14252,9 @@
       <c r="CJ4" t="n">
         <v>311.44</v>
       </c>
+      <c r="CK4" t="n">
+        <v>310.33</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14353,6 +14525,9 @@
       <c r="CJ5" t="n">
         <v>483.3</v>
       </c>
+      <c r="CK5" t="n">
+        <v>470.16</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14623,6 +14798,9 @@
       <c r="CJ6" t="n">
         <v>93.2</v>
       </c>
+      <c r="CK6" t="n">
+        <v>90.8104</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14893,6 +15071,9 @@
       <c r="CJ7" t="n">
         <v>186.49</v>
       </c>
+      <c r="CK7" t="n">
+        <v>188.26</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15163,6 +15344,9 @@
       <c r="CJ8" t="n">
         <v>177.25</v>
       </c>
+      <c r="CK8" t="n">
+        <v>166.35</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15433,6 +15617,9 @@
       <c r="CJ9" t="n">
         <v>84.12</v>
       </c>
+      <c r="CK9" t="n">
+        <v>83.02</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15702,6 +15889,9 @@
       </c>
       <c r="CJ10" t="n">
         <v>449.3</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>435.3</v>
       </c>
     </row>
   </sheetData>
@@ -15715,7 +15905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ10"/>
+  <dimension ref="A1:CK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15806,6 +15996,7 @@
     <col width="12" customWidth="1" min="86" max="86"/>
     <col width="12" customWidth="1" min="87" max="87"/>
     <col width="12" customWidth="1" min="88" max="88"/>
+    <col width="12" customWidth="1" min="89" max="89"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16077,6 +16268,9 @@
       <c r="CJ1" s="1" t="n">
         <v>20251231</v>
       </c>
+      <c r="CK1" s="1" t="n">
+        <v>20260102</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16347,6 +16541,9 @@
       <c r="CJ2" t="n">
         <v>271.86</v>
       </c>
+      <c r="CK2" t="n">
+        <v>271.01</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16617,6 +16814,9 @@
       <c r="CJ3" t="n">
         <v>230.82</v>
       </c>
+      <c r="CK3" t="n">
+        <v>226.5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16887,6 +17087,9 @@
       <c r="CJ4" t="n">
         <v>313</v>
       </c>
+      <c r="CK4" t="n">
+        <v>315.15</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -17157,6 +17360,9 @@
       <c r="CJ5" t="n">
         <v>483.62</v>
       </c>
+      <c r="CK5" t="n">
+        <v>472.94</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17427,6 +17633,9 @@
       <c r="CJ6" t="n">
         <v>93.76000000000001</v>
       </c>
+      <c r="CK6" t="n">
+        <v>90.98999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17697,6 +17906,9 @@
       <c r="CJ7" t="n">
         <v>186.5</v>
       </c>
+      <c r="CK7" t="n">
+        <v>188.85</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17967,6 +18179,9 @@
       <c r="CJ8" t="n">
         <v>177.75</v>
       </c>
+      <c r="CK8" t="n">
+        <v>167.86</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18237,6 +18452,9 @@
       <c r="CJ9" t="n">
         <v>84.20999999999999</v>
       </c>
+      <c r="CK9" t="n">
+        <v>83.97</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18506,6 +18724,9 @@
       </c>
       <c r="CJ10" t="n">
         <v>449.72</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>438.07</v>
       </c>
     </row>
   </sheetData>
@@ -18519,7 +18740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ10"/>
+  <dimension ref="A1:CK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18610,6 +18831,7 @@
     <col width="12" customWidth="1" min="86" max="86"/>
     <col width="12" customWidth="1" min="87" max="87"/>
     <col width="12" customWidth="1" min="88" max="88"/>
+    <col width="12" customWidth="1" min="89" max="89"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18881,6 +19103,9 @@
       <c r="CJ1" s="1" t="n">
         <v>20251231</v>
       </c>
+      <c r="CK1" s="1" t="n">
+        <v>20260102</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19151,6 +19376,9 @@
       <c r="CJ2" t="n">
         <v>27293639</v>
       </c>
+      <c r="CK2" t="n">
+        <v>37838054</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19421,6 +19649,9 @@
       <c r="CJ3" t="n">
         <v>24383749</v>
       </c>
+      <c r="CK3" t="n">
+        <v>51456229</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19691,6 +19922,9 @@
       <c r="CJ4" t="n">
         <v>16377689</v>
       </c>
+      <c r="CK4" t="n">
+        <v>32009385</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19961,6 +20195,9 @@
       <c r="CJ5" t="n">
         <v>15601554</v>
       </c>
+      <c r="CK5" t="n">
+        <v>25571567</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20231,6 +20468,9 @@
       <c r="CJ6" t="n">
         <v>23495191</v>
       </c>
+      <c r="CK6" t="n">
+        <v>41155402</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20501,6 +20741,9 @@
       <c r="CJ7" t="n">
         <v>120100484</v>
       </c>
+      <c r="CK7" t="n">
+        <v>148240462</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20771,6 +21014,9 @@
       <c r="CJ8" t="n">
         <v>22997438</v>
       </c>
+      <c r="CK8" t="n">
+        <v>60634068</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21041,6 +21287,9 @@
       <c r="CJ9" t="n">
         <v>5293385</v>
       </c>
+      <c r="CK9" t="n">
+        <v>11334890</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21310,6 +21559,9 @@
       </c>
       <c r="CJ10" t="n">
         <v>49077961</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>85535406</v>
       </c>
     </row>
   </sheetData>
@@ -21323,7 +21575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ10"/>
+  <dimension ref="A1:BR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21395,6 +21647,7 @@
     <col width="10" customWidth="1" min="67" max="67"/>
     <col width="10" customWidth="1" min="68" max="68"/>
     <col width="10" customWidth="1" min="69" max="69"/>
+    <col width="10" customWidth="1" min="70" max="70"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21609,6 +21862,9 @@
       <c r="BQ1" s="1" t="n">
         <v>20251231</v>
       </c>
+      <c r="BR1" s="1" t="n">
+        <v>20260102</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21822,6 +22078,9 @@
       <c r="BQ2" t="n">
         <v>7</v>
       </c>
+      <c r="BR2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22035,6 +22294,9 @@
       <c r="BQ3" t="n">
         <v>85</v>
       </c>
+      <c r="BR3" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22248,6 +22510,9 @@
       <c r="BQ4" t="n">
         <v>66</v>
       </c>
+      <c r="BR4" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -22461,6 +22726,9 @@
       <c r="BQ5" t="n">
         <v>51</v>
       </c>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -22674,6 +22942,9 @@
       <c r="BQ6" t="n">
         <v>9</v>
       </c>
+      <c r="BR6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -22887,6 +23158,9 @@
       <c r="BQ7" t="n">
         <v>79</v>
       </c>
+      <c r="BR7" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23100,6 +23374,9 @@
       <c r="BQ8" t="n">
         <v>9</v>
       </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23313,6 +23590,9 @@
       <c r="BQ9" t="n">
         <v>27</v>
       </c>
+      <c r="BR9" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23525,6 +23805,9 @@
       </c>
       <c r="BQ10" t="n">
         <v>20</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -23538,7 +23821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23570,6 +23853,7 @@
     <col width="10" customWidth="1" min="27" max="27"/>
     <col width="10" customWidth="1" min="28" max="28"/>
     <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23664,6 +23948,9 @@
       <c r="AC1" s="1" t="n">
         <v>20251231</v>
       </c>
+      <c r="AD1" s="1" t="n">
+        <v>20260102</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23757,6 +24044,9 @@
       <c r="AC2" t="n">
         <v>65</v>
       </c>
+      <c r="AD2" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23850,6 +24140,9 @@
       <c r="AC3" t="n">
         <v>43</v>
       </c>
+      <c r="AD3" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23943,6 +24236,9 @@
       <c r="AC4" t="n">
         <v>88</v>
       </c>
+      <c r="AD4" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24036,6 +24332,9 @@
       <c r="AC5" t="n">
         <v>16</v>
       </c>
+      <c r="AD5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24129,6 +24428,9 @@
       <c r="AC6" t="n">
         <v>0</v>
       </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24222,6 +24524,9 @@
       <c r="AC7" t="n">
         <v>43</v>
       </c>
+      <c r="AD7" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24315,6 +24620,9 @@
       <c r="AC8" t="n">
         <v>44</v>
       </c>
+      <c r="AD8" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24408,6 +24716,9 @@
       <c r="AC9" t="n">
         <v>52</v>
       </c>
+      <c r="AD9" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24500,6 +24811,9 @@
       </c>
       <c r="AC10" t="n">
         <v>59</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -24513,7 +24827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ10"/>
+  <dimension ref="A1:BR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24585,6 +24899,7 @@
     <col width="10" customWidth="1" min="67" max="67"/>
     <col width="10" customWidth="1" min="68" max="68"/>
     <col width="10" customWidth="1" min="69" max="69"/>
+    <col width="10" customWidth="1" min="70" max="70"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24799,6 +25114,9 @@
       <c r="BQ1" s="1" t="n">
         <v>20251231</v>
       </c>
+      <c r="BR1" s="1" t="n">
+        <v>20260102</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25012,6 +25330,9 @@
       <c r="BQ2" t="n">
         <v>-51</v>
       </c>
+      <c r="BR2" t="n">
+        <v>-63</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25225,6 +25546,9 @@
       <c r="BQ3" t="n">
         <v>29</v>
       </c>
+      <c r="BR3" t="n">
+        <v>-28</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -25438,6 +25762,9 @@
       <c r="BQ4" t="n">
         <v>6</v>
       </c>
+      <c r="BR4" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -25651,6 +25978,9 @@
       <c r="BQ5" t="n">
         <v>2</v>
       </c>
+      <c r="BR5" t="n">
+        <v>-94</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -25864,6 +26194,9 @@
       <c r="BQ6" t="n">
         <v>-28</v>
       </c>
+      <c r="BR6" t="n">
+        <v>-73</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -26077,6 +26410,9 @@
       <c r="BQ7" t="n">
         <v>36</v>
       </c>
+      <c r="BR7" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -26290,6 +26626,9 @@
       <c r="BQ8" t="n">
         <v>-62</v>
       </c>
+      <c r="BR8" t="n">
+        <v>-124</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -26503,6 +26842,9 @@
       <c r="BQ9" t="n">
         <v>-32</v>
       </c>
+      <c r="BR9" t="n">
+        <v>-36</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26715,6 +27057,9 @@
       </c>
       <c r="BQ10" t="n">
         <v>-45</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>-75</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD10"/>
+  <dimension ref="A1:AE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -634,6 +634,7 @@
     <col width="10" customWidth="1" min="28" max="28"/>
     <col width="10" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="10" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -731,6 +732,9 @@
       <c r="AD1" s="1" t="n">
         <v>20260102</v>
       </c>
+      <c r="AE1" s="1" t="n">
+        <v>20260105</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -827,6 +831,9 @@
       <c r="AD2" t="n">
         <v>8</v>
       </c>
+      <c r="AE2" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -923,6 +930,9 @@
       <c r="AD3" t="n">
         <v>-15</v>
       </c>
+      <c r="AE3" t="n">
+        <v>-11</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1019,6 +1029,9 @@
       <c r="AD4" t="n">
         <v>49</v>
       </c>
+      <c r="AE4" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1115,6 +1128,9 @@
       <c r="AD5" t="n">
         <v>-70</v>
       </c>
+      <c r="AE5" t="n">
+        <v>-66</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1211,6 +1227,9 @@
       <c r="AD6" t="n">
         <v>-47</v>
       </c>
+      <c r="AE6" t="n">
+        <v>-46</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1307,6 +1326,9 @@
       <c r="AD7" t="n">
         <v>17</v>
       </c>
+      <c r="AE7" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1403,6 +1425,9 @@
       <c r="AD8" t="n">
         <v>-60</v>
       </c>
+      <c r="AE8" t="n">
+        <v>-30</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1499,6 +1524,9 @@
       <c r="AD9" t="n">
         <v>-9</v>
       </c>
+      <c r="AE9" t="n">
+        <v>-9</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1594,6 +1622,9 @@
       </c>
       <c r="AD10" t="n">
         <v>-11</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1607,7 +1638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR10"/>
+  <dimension ref="A1:BS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1680,6 +1711,7 @@
     <col width="12" customWidth="1" min="68" max="68"/>
     <col width="12" customWidth="1" min="69" max="69"/>
     <col width="12" customWidth="1" min="70" max="70"/>
+    <col width="12" customWidth="1" min="71" max="71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2033,6 +2065,11 @@
           <t>20260102</t>
         </is>
       </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>20260105</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2249,6 +2286,9 @@
       <c r="BR2" t="n">
         <v>99</v>
       </c>
+      <c r="BS2" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2465,6 +2505,9 @@
       <c r="BR3" t="n">
         <v>99</v>
       </c>
+      <c r="BS3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2681,6 +2724,9 @@
       <c r="BR4" t="n">
         <v>101</v>
       </c>
+      <c r="BS4" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2897,6 +2943,9 @@
       <c r="BR5" t="n">
         <v>98</v>
       </c>
+      <c r="BS5" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3113,6 +3162,9 @@
       <c r="BR6" t="n">
         <v>96</v>
       </c>
+      <c r="BS6" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3329,6 +3381,9 @@
       <c r="BR7" t="n">
         <v>103</v>
       </c>
+      <c r="BS7" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3545,6 +3600,9 @@
       <c r="BR8" t="n">
         <v>91</v>
       </c>
+      <c r="BS8" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3761,6 +3819,9 @@
       <c r="BR9" t="n">
         <v>99</v>
       </c>
+      <c r="BS9" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3976,6 +4037,9 @@
       </c>
       <c r="BR10" t="n">
         <v>94</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -6338,7 +6402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD10"/>
+  <dimension ref="A1:AE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6371,6 +6435,7 @@
     <col width="12" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6524,6 +6589,11 @@
           <t>20260102</t>
         </is>
       </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>20260105</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6620,6 +6690,9 @@
       <c r="AD2" t="n">
         <v>42</v>
       </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6716,6 +6789,9 @@
       <c r="AD3" t="n">
         <v>56</v>
       </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6812,6 +6888,9 @@
       <c r="AD4" t="n">
         <v>45</v>
       </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6908,6 +6987,9 @@
       <c r="AD5" t="n">
         <v>56</v>
       </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7004,6 +7086,9 @@
       <c r="AD6" t="n">
         <v>82</v>
       </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7100,6 +7185,9 @@
       <c r="AD7" t="n">
         <v>40</v>
       </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7196,6 +7284,9 @@
       <c r="AD8" t="n">
         <v>65</v>
       </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7292,6 +7383,9 @@
       <c r="AD9" t="n">
         <v>59</v>
       </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7387,6 +7481,9 @@
       </c>
       <c r="AD10" t="n">
         <v>53</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7400,7 +7497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CK10"/>
+  <dimension ref="A1:CL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7492,6 +7589,7 @@
     <col width="12" customWidth="1" min="87" max="87"/>
     <col width="12" customWidth="1" min="88" max="88"/>
     <col width="12" customWidth="1" min="89" max="89"/>
+    <col width="12" customWidth="1" min="90" max="90"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7766,6 +7864,9 @@
       <c r="CK1" s="1" t="n">
         <v>20260102</v>
       </c>
+      <c r="CL1" s="1" t="n">
+        <v>20260105</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8039,6 +8140,9 @@
       <c r="CK2" t="n">
         <v>272.255</v>
       </c>
+      <c r="CL2" t="n">
+        <v>270.82</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8312,6 +8416,9 @@
       <c r="CK3" t="n">
         <v>231.34</v>
       </c>
+      <c r="CL3" t="n">
+        <v>227.13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8585,6 +8692,9 @@
       <c r="CK4" t="n">
         <v>316.9</v>
       </c>
+      <c r="CL4" t="n">
+        <v>315.84</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8858,6 +8968,9 @@
       <c r="CK5" t="n">
         <v>484.385</v>
       </c>
+      <c r="CL5" t="n">
+        <v>473.49</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9131,6 +9244,9 @@
       <c r="CK6" t="n">
         <v>94.13</v>
       </c>
+      <c r="CL6" t="n">
+        <v>91.28</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9404,6 +9520,9 @@
       <c r="CK7" t="n">
         <v>189.835</v>
       </c>
+      <c r="CL7" t="n">
+        <v>189.91</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9677,6 +9796,9 @@
       <c r="CK8" t="n">
         <v>181.3</v>
       </c>
+      <c r="CL8" t="n">
+        <v>174.3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9950,6 +10072,9 @@
       <c r="CK9" t="n">
         <v>84.22</v>
       </c>
+      <c r="CL9" t="n">
+        <v>84.09</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10222,6 +10347,9 @@
       </c>
       <c r="CK10" t="n">
         <v>457.8</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>445.05</v>
       </c>
     </row>
   </sheetData>
@@ -10235,7 +10363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CK10"/>
+  <dimension ref="A1:CL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10327,6 +10455,7 @@
     <col width="12" customWidth="1" min="87" max="87"/>
     <col width="12" customWidth="1" min="88" max="88"/>
     <col width="12" customWidth="1" min="89" max="89"/>
+    <col width="12" customWidth="1" min="90" max="90"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10601,6 +10730,9 @@
       <c r="CK1" s="1" t="n">
         <v>20260102</v>
       </c>
+      <c r="CL1" s="1" t="n">
+        <v>20260105</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10874,6 +11006,9 @@
       <c r="CK2" t="n">
         <v>277.84</v>
       </c>
+      <c r="CL2" t="n">
+        <v>271.03</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11147,6 +11282,9 @@
       <c r="CK3" t="n">
         <v>235.458</v>
       </c>
+      <c r="CL3" t="n">
+        <v>227.68</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11420,6 +11558,9 @@
       <c r="CK4" t="n">
         <v>322.5</v>
       </c>
+      <c r="CL4" t="n">
+        <v>316.29</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11693,6 +11834,9 @@
       <c r="CK5" t="n">
         <v>484.66</v>
       </c>
+      <c r="CL5" t="n">
+        <v>473.77</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11966,6 +12110,9 @@
       <c r="CK6" t="n">
         <v>94.13</v>
       </c>
+      <c r="CL6" t="n">
+        <v>91.34999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12239,6 +12386,9 @@
       <c r="CK7" t="n">
         <v>192.9299</v>
       </c>
+      <c r="CL7" t="n">
+        <v>191.599</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12512,6 +12662,9 @@
       <c r="CK8" t="n">
         <v>181.35</v>
       </c>
+      <c r="CL8" t="n">
+        <v>175.08</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12785,6 +12938,9 @@
       <c r="CK9" t="n">
         <v>84.95999999999999</v>
       </c>
+      <c r="CL9" t="n">
+        <v>84.09999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13057,6 +13213,9 @@
       </c>
       <c r="CK10" t="n">
         <v>458.34</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>446</v>
       </c>
     </row>
   </sheetData>
@@ -13070,7 +13229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CK10"/>
+  <dimension ref="A1:CL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13162,6 +13321,7 @@
     <col width="12" customWidth="1" min="87" max="87"/>
     <col width="12" customWidth="1" min="88" max="88"/>
     <col width="12" customWidth="1" min="89" max="89"/>
+    <col width="12" customWidth="1" min="90" max="90"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13436,6 +13596,9 @@
       <c r="CK1" s="1" t="n">
         <v>20260102</v>
       </c>
+      <c r="CL1" s="1" t="n">
+        <v>20260105</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13709,6 +13872,9 @@
       <c r="CK2" t="n">
         <v>269</v>
       </c>
+      <c r="CL2" t="n">
+        <v>270</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13982,6 +14148,9 @@
       <c r="CK3" t="n">
         <v>224.7</v>
       </c>
+      <c r="CL3" t="n">
+        <v>226.9</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14255,6 +14424,9 @@
       <c r="CK4" t="n">
         <v>310.33</v>
       </c>
+      <c r="CL4" t="n">
+        <v>315.34</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14528,6 +14700,9 @@
       <c r="CK5" t="n">
         <v>470.16</v>
       </c>
+      <c r="CL5" t="n">
+        <v>473.03</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14801,6 +14976,9 @@
       <c r="CK6" t="n">
         <v>90.8104</v>
       </c>
+      <c r="CL6" t="n">
+        <v>90.73</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15074,6 +15252,9 @@
       <c r="CK7" t="n">
         <v>188.26</v>
       </c>
+      <c r="CL7" t="n">
+        <v>189.59</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15347,6 +15528,9 @@
       <c r="CK8" t="n">
         <v>166.35</v>
       </c>
+      <c r="CL8" t="n">
+        <v>173.68</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15620,6 +15804,9 @@
       <c r="CK9" t="n">
         <v>83.02</v>
       </c>
+      <c r="CL9" t="n">
+        <v>83.98999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15892,6 +16079,9 @@
       </c>
       <c r="CK10" t="n">
         <v>435.3</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>443.25</v>
       </c>
     </row>
   </sheetData>
@@ -15905,7 +16095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CK10"/>
+  <dimension ref="A1:CL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15997,6 +16187,7 @@
     <col width="12" customWidth="1" min="87" max="87"/>
     <col width="12" customWidth="1" min="88" max="88"/>
     <col width="12" customWidth="1" min="89" max="89"/>
+    <col width="12" customWidth="1" min="90" max="90"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16271,6 +16462,9 @@
       <c r="CK1" s="1" t="n">
         <v>20260102</v>
       </c>
+      <c r="CL1" s="1" t="n">
+        <v>20260105</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16544,6 +16738,9 @@
       <c r="CK2" t="n">
         <v>271.01</v>
       </c>
+      <c r="CL2" t="n">
+        <v>270.64</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16817,6 +17014,9 @@
       <c r="CK3" t="n">
         <v>226.5</v>
       </c>
+      <c r="CL3" t="n">
+        <v>227.37</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17090,6 +17290,9 @@
       <c r="CK4" t="n">
         <v>315.15</v>
       </c>
+      <c r="CL4" t="n">
+        <v>316.11</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -17363,6 +17566,9 @@
       <c r="CK5" t="n">
         <v>472.94</v>
       </c>
+      <c r="CL5" t="n">
+        <v>473.54</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17636,6 +17842,9 @@
       <c r="CK6" t="n">
         <v>90.98999999999999</v>
       </c>
+      <c r="CL6" t="n">
+        <v>91.12</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17909,6 +18118,9 @@
       <c r="CK7" t="n">
         <v>188.85</v>
       </c>
+      <c r="CL7" t="n">
+        <v>191.58</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18182,6 +18394,9 @@
       <c r="CK8" t="n">
         <v>167.86</v>
       </c>
+      <c r="CL8" t="n">
+        <v>174.1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18455,6 +18670,9 @@
       <c r="CK9" t="n">
         <v>83.97</v>
       </c>
+      <c r="CL9" t="n">
+        <v>84.03</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18727,6 +18945,9 @@
       </c>
       <c r="CK10" t="n">
         <v>438.07</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>444.74</v>
       </c>
     </row>
   </sheetData>
@@ -18740,7 +18961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CK10"/>
+  <dimension ref="A1:CL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18832,6 +19053,7 @@
     <col width="12" customWidth="1" min="87" max="87"/>
     <col width="12" customWidth="1" min="88" max="88"/>
     <col width="12" customWidth="1" min="89" max="89"/>
+    <col width="12" customWidth="1" min="90" max="90"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19106,6 +19328,9 @@
       <c r="CK1" s="1" t="n">
         <v>20260102</v>
       </c>
+      <c r="CL1" s="1" t="n">
+        <v>20260105</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19379,6 +19604,9 @@
       <c r="CK2" t="n">
         <v>37838054</v>
       </c>
+      <c r="CL2" t="n">
+        <v>19188</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19652,6 +19880,9 @@
       <c r="CK3" t="n">
         <v>51456229</v>
       </c>
+      <c r="CL3" t="n">
+        <v>55210</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19925,6 +20156,9 @@
       <c r="CK4" t="n">
         <v>32009385</v>
       </c>
+      <c r="CL4" t="n">
+        <v>26347</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20198,6 +20432,9 @@
       <c r="CK5" t="n">
         <v>25571567</v>
       </c>
+      <c r="CL5" t="n">
+        <v>22327</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20471,6 +20708,9 @@
       <c r="CK6" t="n">
         <v>41155402</v>
       </c>
+      <c r="CL6" t="n">
+        <v>21877</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20744,6 +20984,9 @@
       <c r="CK7" t="n">
         <v>148240462</v>
       </c>
+      <c r="CL7" t="n">
+        <v>314604</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21017,6 +21260,9 @@
       <c r="CK8" t="n">
         <v>60634068</v>
       </c>
+      <c r="CL8" t="n">
+        <v>123479</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21290,6 +21536,9 @@
       <c r="CK9" t="n">
         <v>11334890</v>
       </c>
+      <c r="CL9" t="n">
+        <v>586</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21562,6 +21811,9 @@
       </c>
       <c r="CK10" t="n">
         <v>85535406</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>137324</v>
       </c>
     </row>
   </sheetData>
@@ -21575,7 +21827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR10"/>
+  <dimension ref="A1:BS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21648,6 +21900,7 @@
     <col width="10" customWidth="1" min="68" max="68"/>
     <col width="10" customWidth="1" min="69" max="69"/>
     <col width="10" customWidth="1" min="70" max="70"/>
+    <col width="10" customWidth="1" min="71" max="71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21865,6 +22118,9 @@
       <c r="BR1" s="1" t="n">
         <v>20260102</v>
       </c>
+      <c r="BS1" s="1" t="n">
+        <v>20260105</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22081,6 +22337,9 @@
       <c r="BR2" t="n">
         <v>0</v>
       </c>
+      <c r="BS2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22297,6 +22556,9 @@
       <c r="BR3" t="n">
         <v>46</v>
       </c>
+      <c r="BS3" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22513,6 +22775,9 @@
       <c r="BR4" t="n">
         <v>75</v>
       </c>
+      <c r="BS4" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -22729,6 +22994,9 @@
       <c r="BR5" t="n">
         <v>0</v>
       </c>
+      <c r="BS5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -22945,6 +23213,9 @@
       <c r="BR6" t="n">
         <v>0</v>
       </c>
+      <c r="BS6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23161,6 +23432,9 @@
       <c r="BR7" t="n">
         <v>91</v>
       </c>
+      <c r="BS7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23377,6 +23651,9 @@
       <c r="BR8" t="n">
         <v>0</v>
       </c>
+      <c r="BS8" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23593,6 +23870,9 @@
       <c r="BR9" t="n">
         <v>24</v>
       </c>
+      <c r="BS9" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23808,6 +24088,9 @@
       </c>
       <c r="BR10" t="n">
         <v>0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -23821,7 +24104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD10"/>
+  <dimension ref="A1:AE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23854,6 +24137,7 @@
     <col width="10" customWidth="1" min="28" max="28"/>
     <col width="10" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="10" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23951,6 +24235,9 @@
       <c r="AD1" s="1" t="n">
         <v>20260102</v>
       </c>
+      <c r="AE1" s="1" t="n">
+        <v>20260105</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24047,6 +24334,9 @@
       <c r="AD2" t="n">
         <v>63</v>
       </c>
+      <c r="AE2" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -24143,6 +24433,9 @@
       <c r="AD3" t="n">
         <v>33</v>
       </c>
+      <c r="AE3" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -24239,6 +24532,9 @@
       <c r="AD4" t="n">
         <v>90</v>
       </c>
+      <c r="AE4" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24335,6 +24631,9 @@
       <c r="AD5" t="n">
         <v>1</v>
       </c>
+      <c r="AE5" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24431,6 +24730,9 @@
       <c r="AD6" t="n">
         <v>0</v>
       </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24527,6 +24829,9 @@
       <c r="AD7" t="n">
         <v>50</v>
       </c>
+      <c r="AE7" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24623,6 +24928,9 @@
       <c r="AD8" t="n">
         <v>25</v>
       </c>
+      <c r="AE8" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24719,6 +25027,9 @@
       <c r="AD9" t="n">
         <v>50</v>
       </c>
+      <c r="AE9" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24814,6 +25125,9 @@
       </c>
       <c r="AD10" t="n">
         <v>48</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -24827,7 +25141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR10"/>
+  <dimension ref="A1:BS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24900,6 +25214,7 @@
     <col width="10" customWidth="1" min="68" max="68"/>
     <col width="10" customWidth="1" min="69" max="69"/>
     <col width="10" customWidth="1" min="70" max="70"/>
+    <col width="10" customWidth="1" min="71" max="71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25117,6 +25432,9 @@
       <c r="BR1" s="1" t="n">
         <v>20260102</v>
       </c>
+      <c r="BS1" s="1" t="n">
+        <v>20260105</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25333,6 +25651,9 @@
       <c r="BR2" t="n">
         <v>-63</v>
       </c>
+      <c r="BS2" t="n">
+        <v>-65</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25549,6 +25870,9 @@
       <c r="BR3" t="n">
         <v>-28</v>
       </c>
+      <c r="BS3" t="n">
+        <v>-15</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -25765,6 +26089,9 @@
       <c r="BR4" t="n">
         <v>27</v>
       </c>
+      <c r="BS4" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -25981,6 +26308,9 @@
       <c r="BR5" t="n">
         <v>-94</v>
       </c>
+      <c r="BS5" t="n">
+        <v>-79</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -26197,6 +26527,9 @@
       <c r="BR6" t="n">
         <v>-73</v>
       </c>
+      <c r="BS6" t="n">
+        <v>-80</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -26413,6 +26746,9 @@
       <c r="BR7" t="n">
         <v>52</v>
       </c>
+      <c r="BS7" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -26629,6 +26965,9 @@
       <c r="BR8" t="n">
         <v>-124</v>
       </c>
+      <c r="BS8" t="n">
+        <v>-73</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -26845,6 +27184,9 @@
       <c r="BR9" t="n">
         <v>-36</v>
       </c>
+      <c r="BS9" t="n">
+        <v>-32</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27060,6 +27402,9 @@
       </c>
       <c r="BR10" t="n">
         <v>-75</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>-54</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE10"/>
+  <dimension ref="A1:AF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -635,6 +635,7 @@
     <col width="10" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="10" customWidth="1" min="31" max="31"/>
+    <col width="10" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -735,6 +736,9 @@
       <c r="AE1" s="1" t="n">
         <v>20260105</v>
       </c>
+      <c r="AF1" s="1" t="n">
+        <v>20260106</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -834,6 +838,9 @@
       <c r="AE2" t="n">
         <v>5</v>
       </c>
+      <c r="AF2" t="n">
+        <v>-41</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -933,6 +940,9 @@
       <c r="AE3" t="n">
         <v>-11</v>
       </c>
+      <c r="AF3" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1032,6 +1042,9 @@
       <c r="AE4" t="n">
         <v>49</v>
       </c>
+      <c r="AF4" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1131,6 +1144,9 @@
       <c r="AE5" t="n">
         <v>-66</v>
       </c>
+      <c r="AF5" t="n">
+        <v>-51</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1230,6 +1246,9 @@
       <c r="AE6" t="n">
         <v>-46</v>
       </c>
+      <c r="AF6" t="n">
+        <v>-44</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1329,6 +1348,9 @@
       <c r="AE7" t="n">
         <v>34</v>
       </c>
+      <c r="AF7" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1428,6 +1450,9 @@
       <c r="AE8" t="n">
         <v>-30</v>
       </c>
+      <c r="AF8" t="n">
+        <v>-4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1527,6 +1552,9 @@
       <c r="AE9" t="n">
         <v>-9</v>
       </c>
+      <c r="AF9" t="n">
+        <v>114</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1625,6 +1653,9 @@
       </c>
       <c r="AE10" t="n">
         <v>3</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-22</v>
       </c>
     </row>
   </sheetData>
@@ -1638,7 +1669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS10"/>
+  <dimension ref="A1:BT10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1712,6 +1743,7 @@
     <col width="12" customWidth="1" min="69" max="69"/>
     <col width="12" customWidth="1" min="70" max="70"/>
     <col width="12" customWidth="1" min="71" max="71"/>
+    <col width="12" customWidth="1" min="72" max="72"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2070,6 +2102,11 @@
           <t>20260105</t>
         </is>
       </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>20260106</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2289,6 +2326,9 @@
       <c r="BS2" t="n">
         <v>99</v>
       </c>
+      <c r="BT2" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2508,6 +2548,9 @@
       <c r="BS3" t="n">
         <v>100</v>
       </c>
+      <c r="BT3" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2727,6 +2770,9 @@
       <c r="BS4" t="n">
         <v>101</v>
       </c>
+      <c r="BT4" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2946,6 +2992,9 @@
       <c r="BS5" t="n">
         <v>98</v>
       </c>
+      <c r="BT5" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3165,6 +3214,9 @@
       <c r="BS6" t="n">
         <v>97</v>
       </c>
+      <c r="BT6" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3384,6 +3436,9 @@
       <c r="BS7" t="n">
         <v>104</v>
       </c>
+      <c r="BT7" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3603,6 +3658,9 @@
       <c r="BS8" t="n">
         <v>94</v>
       </c>
+      <c r="BT8" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3822,6 +3880,9 @@
       <c r="BS9" t="n">
         <v>99</v>
       </c>
+      <c r="BT9" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4040,6 +4101,9 @@
       </c>
       <c r="BS10" t="n">
         <v>96</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -6402,7 +6466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE10"/>
+  <dimension ref="A1:AF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6436,6 +6500,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6594,6 +6659,11 @@
           <t>20260105</t>
         </is>
       </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>20260106</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6693,6 +6763,9 @@
       <c r="AE2" t="n">
         <v>0</v>
       </c>
+      <c r="AF2" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6792,6 +6865,9 @@
       <c r="AE3" t="n">
         <v>0</v>
       </c>
+      <c r="AF3" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6891,6 +6967,9 @@
       <c r="AE4" t="n">
         <v>0</v>
       </c>
+      <c r="AF4" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6990,6 +7069,9 @@
       <c r="AE5" t="n">
         <v>0</v>
       </c>
+      <c r="AF5" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7089,6 +7171,9 @@
       <c r="AE6" t="n">
         <v>0</v>
       </c>
+      <c r="AF6" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7188,6 +7273,9 @@
       <c r="AE7" t="n">
         <v>0</v>
       </c>
+      <c r="AF7" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7287,6 +7375,9 @@
       <c r="AE8" t="n">
         <v>0</v>
       </c>
+      <c r="AF8" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7386,6 +7477,9 @@
       <c r="AE9" t="n">
         <v>0</v>
       </c>
+      <c r="AF9" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7484,6 +7578,9 @@
       </c>
       <c r="AE10" t="n">
         <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -7497,7 +7594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CL10"/>
+  <dimension ref="A1:CM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7590,6 +7687,7 @@
     <col width="12" customWidth="1" min="88" max="88"/>
     <col width="12" customWidth="1" min="89" max="89"/>
     <col width="12" customWidth="1" min="90" max="90"/>
+    <col width="12" customWidth="1" min="91" max="91"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7867,6 +7965,9 @@
       <c r="CL1" s="1" t="n">
         <v>20260105</v>
       </c>
+      <c r="CM1" s="1" t="n">
+        <v>20260106</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8143,6 +8244,9 @@
       <c r="CL2" t="n">
         <v>270.82</v>
       </c>
+      <c r="CM2" t="n">
+        <v>267</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8419,6 +8523,9 @@
       <c r="CL3" t="n">
         <v>227.13</v>
       </c>
+      <c r="CM3" t="n">
+        <v>232.1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8695,6 +8802,9 @@
       <c r="CL4" t="n">
         <v>315.84</v>
       </c>
+      <c r="CM4" t="n">
+        <v>316.4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8971,6 +9081,9 @@
       <c r="CL5" t="n">
         <v>473.49</v>
       </c>
+      <c r="CM5" t="n">
+        <v>473.8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9247,6 +9360,9 @@
       <c r="CL6" t="n">
         <v>91.28</v>
       </c>
+      <c r="CM6" t="n">
+        <v>91.54000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9523,6 +9639,9 @@
       <c r="CL7" t="n">
         <v>189.91</v>
       </c>
+      <c r="CM7" t="n">
+        <v>190.52</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9799,6 +9918,9 @@
       <c r="CL8" t="n">
         <v>174.3</v>
       </c>
+      <c r="CM8" t="n">
+        <v>175.76</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10075,6 +10197,9 @@
       <c r="CL9" t="n">
         <v>84.09</v>
       </c>
+      <c r="CM9" t="n">
+        <v>86.56</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10350,6 +10475,9 @@
       </c>
       <c r="CL10" t="n">
         <v>445.05</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>446.38</v>
       </c>
     </row>
   </sheetData>
@@ -10363,7 +10491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CL10"/>
+  <dimension ref="A1:CM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10456,6 +10584,7 @@
     <col width="12" customWidth="1" min="88" max="88"/>
     <col width="12" customWidth="1" min="89" max="89"/>
     <col width="12" customWidth="1" min="90" max="90"/>
+    <col width="12" customWidth="1" min="91" max="91"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10733,6 +10862,9 @@
       <c r="CL1" s="1" t="n">
         <v>20260105</v>
       </c>
+      <c r="CM1" s="1" t="n">
+        <v>20260106</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11009,6 +11141,9 @@
       <c r="CL2" t="n">
         <v>271.03</v>
       </c>
+      <c r="CM2" t="n">
+        <v>267.55</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11285,6 +11420,9 @@
       <c r="CL3" t="n">
         <v>227.68</v>
       </c>
+      <c r="CM3" t="n">
+        <v>243.18</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11561,6 +11699,9 @@
       <c r="CL4" t="n">
         <v>316.29</v>
       </c>
+      <c r="CM4" t="n">
+        <v>320.94</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11837,6 +11978,9 @@
       <c r="CL5" t="n">
         <v>473.77</v>
       </c>
+      <c r="CM5" t="n">
+        <v>478.7367</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12113,6 +12257,9 @@
       <c r="CL6" t="n">
         <v>91.34999999999999</v>
       </c>
+      <c r="CM6" t="n">
+        <v>91.64</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12389,6 +12536,9 @@
       <c r="CL7" t="n">
         <v>191.599</v>
       </c>
+      <c r="CM7" t="n">
+        <v>192.174</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12665,6 +12815,9 @@
       <c r="CL8" t="n">
         <v>175.08</v>
       </c>
+      <c r="CM8" t="n">
+        <v>180.19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12941,6 +13094,9 @@
       <c r="CL9" t="n">
         <v>84.09999999999999</v>
       </c>
+      <c r="CM9" t="n">
+        <v>90.64</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13216,6 +13372,9 @@
       </c>
       <c r="CL10" t="n">
         <v>446</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>448.25</v>
       </c>
     </row>
   </sheetData>
@@ -13229,7 +13388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CL10"/>
+  <dimension ref="A1:CM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13322,6 +13481,7 @@
     <col width="12" customWidth="1" min="88" max="88"/>
     <col width="12" customWidth="1" min="89" max="89"/>
     <col width="12" customWidth="1" min="90" max="90"/>
+    <col width="12" customWidth="1" min="91" max="91"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13599,6 +13759,9 @@
       <c r="CL1" s="1" t="n">
         <v>20260105</v>
       </c>
+      <c r="CM1" s="1" t="n">
+        <v>20260106</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13875,6 +14038,9 @@
       <c r="CL2" t="n">
         <v>270</v>
       </c>
+      <c r="CM2" t="n">
+        <v>262.12</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14151,6 +14317,9 @@
       <c r="CL3" t="n">
         <v>226.9</v>
       </c>
+      <c r="CM3" t="n">
+        <v>232.07</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14427,6 +14596,9 @@
       <c r="CL4" t="n">
         <v>315.34</v>
       </c>
+      <c r="CM4" t="n">
+        <v>311.78</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14703,6 +14875,9 @@
       <c r="CL5" t="n">
         <v>473.03</v>
       </c>
+      <c r="CM5" t="n">
+        <v>469.75</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14979,6 +15154,9 @@
       <c r="CL6" t="n">
         <v>90.73</v>
       </c>
+      <c r="CM6" t="n">
+        <v>89.73999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15255,6 +15433,9 @@
       <c r="CL7" t="n">
         <v>189.59</v>
       </c>
+      <c r="CM7" t="n">
+        <v>186.82</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15531,6 +15712,9 @@
       <c r="CL8" t="n">
         <v>173.68</v>
       </c>
+      <c r="CM8" t="n">
+        <v>174.7701</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15807,6 +15991,9 @@
       <c r="CL9" t="n">
         <v>83.98999999999999</v>
       </c>
+      <c r="CM9" t="n">
+        <v>86.36</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16082,6 +16269,9 @@
       </c>
       <c r="CL10" t="n">
         <v>443.25</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>428.78</v>
       </c>
     </row>
   </sheetData>
@@ -16095,7 +16285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CL10"/>
+  <dimension ref="A1:CM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -16188,6 +16378,7 @@
     <col width="12" customWidth="1" min="88" max="88"/>
     <col width="12" customWidth="1" min="89" max="89"/>
     <col width="12" customWidth="1" min="90" max="90"/>
+    <col width="12" customWidth="1" min="91" max="91"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16465,6 +16656,9 @@
       <c r="CL1" s="1" t="n">
         <v>20260105</v>
       </c>
+      <c r="CM1" s="1" t="n">
+        <v>20260106</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16741,6 +16935,9 @@
       <c r="CL2" t="n">
         <v>270.64</v>
       </c>
+      <c r="CM2" t="n">
+        <v>262.36</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17017,6 +17214,9 @@
       <c r="CL3" t="n">
         <v>227.37</v>
       </c>
+      <c r="CM3" t="n">
+        <v>240.93</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17293,6 +17493,9 @@
       <c r="CL4" t="n">
         <v>316.11</v>
       </c>
+      <c r="CM4" t="n">
+        <v>314.34</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -17569,6 +17772,9 @@
       <c r="CL5" t="n">
         <v>473.54</v>
       </c>
+      <c r="CM5" t="n">
+        <v>478.51</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17845,6 +18051,9 @@
       <c r="CL6" t="n">
         <v>91.12</v>
       </c>
+      <c r="CM6" t="n">
+        <v>90.65000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18121,6 +18330,9 @@
       <c r="CL7" t="n">
         <v>191.58</v>
       </c>
+      <c r="CM7" t="n">
+        <v>187.24</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18397,6 +18609,9 @@
       <c r="CL8" t="n">
         <v>174.1</v>
       </c>
+      <c r="CM8" t="n">
+        <v>179.71</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18673,6 +18888,9 @@
       <c r="CL9" t="n">
         <v>84.03</v>
       </c>
+      <c r="CM9" t="n">
+        <v>89.45999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18948,6 +19166,9 @@
       </c>
       <c r="CL10" t="n">
         <v>444.74</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>432.96</v>
       </c>
     </row>
   </sheetData>
@@ -18961,7 +19182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CL10"/>
+  <dimension ref="A1:CM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -19054,6 +19275,7 @@
     <col width="12" customWidth="1" min="88" max="88"/>
     <col width="12" customWidth="1" min="89" max="89"/>
     <col width="12" customWidth="1" min="90" max="90"/>
+    <col width="12" customWidth="1" min="91" max="91"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19331,6 +19553,9 @@
       <c r="CL1" s="1" t="n">
         <v>20260105</v>
       </c>
+      <c r="CM1" s="1" t="n">
+        <v>20260106</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19607,6 +19832,9 @@
       <c r="CL2" t="n">
         <v>19188</v>
       </c>
+      <c r="CM2" t="n">
+        <v>52352090</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19883,6 +20111,9 @@
       <c r="CL3" t="n">
         <v>55210</v>
       </c>
+      <c r="CM3" t="n">
+        <v>53764677</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20159,6 +20390,9 @@
       <c r="CL4" t="n">
         <v>26347</v>
       </c>
+      <c r="CM4" t="n">
+        <v>31212101</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20435,6 +20669,9 @@
       <c r="CL5" t="n">
         <v>22327</v>
       </c>
+      <c r="CM5" t="n">
+        <v>23037665</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20711,6 +20948,9 @@
       <c r="CL6" t="n">
         <v>21877</v>
       </c>
+      <c r="CM6" t="n">
+        <v>43330972</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20987,6 +21227,9 @@
       <c r="CL7" t="n">
         <v>314604</v>
       </c>
+      <c r="CM7" t="n">
+        <v>176862604</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21263,6 +21506,9 @@
       <c r="CL8" t="n">
         <v>123479</v>
       </c>
+      <c r="CM8" t="n">
+        <v>34838611</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21539,6 +21785,9 @@
       <c r="CL9" t="n">
         <v>586</v>
       </c>
+      <c r="CM9" t="n">
+        <v>11351096</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21814,6 +22063,9 @@
       </c>
       <c r="CL10" t="n">
         <v>137324</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>89093758</v>
       </c>
     </row>
   </sheetData>
@@ -21827,7 +22079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS10"/>
+  <dimension ref="A1:BT10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21901,6 +22153,7 @@
     <col width="10" customWidth="1" min="69" max="69"/>
     <col width="10" customWidth="1" min="70" max="70"/>
     <col width="10" customWidth="1" min="71" max="71"/>
+    <col width="10" customWidth="1" min="72" max="72"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22121,6 +22374,9 @@
       <c r="BS1" s="1" t="n">
         <v>20260105</v>
       </c>
+      <c r="BT1" s="1" t="n">
+        <v>20260106</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22340,6 +22596,9 @@
       <c r="BS2" t="n">
         <v>0</v>
       </c>
+      <c r="BT2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22559,6 +22818,9 @@
       <c r="BS3" t="n">
         <v>54</v>
       </c>
+      <c r="BT3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22778,6 +23040,9 @@
       <c r="BS4" t="n">
         <v>79</v>
       </c>
+      <c r="BT4" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -22997,6 +23262,9 @@
       <c r="BS5" t="n">
         <v>3</v>
       </c>
+      <c r="BT5" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23216,6 +23484,9 @@
       <c r="BS6" t="n">
         <v>1</v>
       </c>
+      <c r="BT6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23435,6 +23706,9 @@
       <c r="BS7" t="n">
         <v>100</v>
       </c>
+      <c r="BT7" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23654,6 +23928,9 @@
       <c r="BS8" t="n">
         <v>24</v>
       </c>
+      <c r="BT8" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23873,6 +24150,9 @@
       <c r="BS9" t="n">
         <v>25</v>
       </c>
+      <c r="BT9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24091,6 +24371,9 @@
       </c>
       <c r="BS10" t="n">
         <v>13</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -24104,7 +24387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE10"/>
+  <dimension ref="A1:AF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24138,6 +24421,7 @@
     <col width="10" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="10" customWidth="1" min="31" max="31"/>
+    <col width="10" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24238,6 +24522,9 @@
       <c r="AE1" s="1" t="n">
         <v>20260105</v>
       </c>
+      <c r="AF1" s="1" t="n">
+        <v>20260106</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24337,6 +24624,9 @@
       <c r="AE2" t="n">
         <v>62</v>
       </c>
+      <c r="AF2" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -24436,6 +24726,9 @@
       <c r="AE3" t="n">
         <v>35</v>
       </c>
+      <c r="AF3" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -24535,6 +24828,9 @@
       <c r="AE4" t="n">
         <v>92</v>
       </c>
+      <c r="AF4" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24634,6 +24930,9 @@
       <c r="AE5" t="n">
         <v>2</v>
       </c>
+      <c r="AF5" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24733,6 +25032,9 @@
       <c r="AE6" t="n">
         <v>0</v>
       </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24832,6 +25134,9 @@
       <c r="AE7" t="n">
         <v>57</v>
       </c>
+      <c r="AF7" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24931,6 +25236,9 @@
       <c r="AE8" t="n">
         <v>37</v>
       </c>
+      <c r="AF8" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25030,6 +25338,9 @@
       <c r="AE9" t="n">
         <v>51</v>
       </c>
+      <c r="AF9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25128,6 +25439,9 @@
       </c>
       <c r="AE10" t="n">
         <v>54</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -25141,7 +25455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS10"/>
+  <dimension ref="A1:BT10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25215,6 +25529,7 @@
     <col width="10" customWidth="1" min="69" max="69"/>
     <col width="10" customWidth="1" min="70" max="70"/>
     <col width="10" customWidth="1" min="71" max="71"/>
+    <col width="10" customWidth="1" min="72" max="72"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25435,6 +25750,9 @@
       <c r="BS1" s="1" t="n">
         <v>20260105</v>
       </c>
+      <c r="BT1" s="1" t="n">
+        <v>20260106</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25654,6 +25972,9 @@
       <c r="BS2" t="n">
         <v>-65</v>
       </c>
+      <c r="BT2" t="n">
+        <v>-151</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25873,6 +26194,9 @@
       <c r="BS3" t="n">
         <v>-15</v>
       </c>
+      <c r="BT3" t="n">
+        <v>133</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -26092,6 +26416,9 @@
       <c r="BS4" t="n">
         <v>36</v>
       </c>
+      <c r="BT4" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -26311,6 +26638,9 @@
       <c r="BS5" t="n">
         <v>-79</v>
       </c>
+      <c r="BT5" t="n">
+        <v>-34</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -26530,6 +26860,9 @@
       <c r="BS6" t="n">
         <v>-80</v>
       </c>
+      <c r="BT6" t="n">
+        <v>-99</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -26749,6 +27082,9 @@
       <c r="BS7" t="n">
         <v>69</v>
       </c>
+      <c r="BT7" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -26968,6 +27304,9 @@
       <c r="BS8" t="n">
         <v>-73</v>
       </c>
+      <c r="BT8" t="n">
+        <v>-32</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -27187,6 +27526,9 @@
       <c r="BS9" t="n">
         <v>-32</v>
       </c>
+      <c r="BT9" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27405,6 +27747,9 @@
       </c>
       <c r="BS10" t="n">
         <v>-54</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>-78</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AG10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -636,6 +636,7 @@
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="10" customWidth="1" min="31" max="31"/>
     <col width="10" customWidth="1" min="32" max="32"/>
+    <col width="10" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -739,6 +740,9 @@
       <c r="AF1" s="1" t="n">
         <v>20260106</v>
       </c>
+      <c r="AG1" s="1" t="n">
+        <v>20260107</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -841,6 +845,9 @@
       <c r="AF2" t="n">
         <v>-41</v>
       </c>
+      <c r="AG2" t="n">
+        <v>-57</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -943,6 +950,9 @@
       <c r="AF3" t="n">
         <v>58</v>
       </c>
+      <c r="AG3" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1045,6 +1055,9 @@
       <c r="AF4" t="n">
         <v>45</v>
       </c>
+      <c r="AG4" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1147,6 +1160,9 @@
       <c r="AF5" t="n">
         <v>-51</v>
       </c>
+      <c r="AG5" t="n">
+        <v>-36</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1249,6 +1265,9 @@
       <c r="AF6" t="n">
         <v>-44</v>
       </c>
+      <c r="AG6" t="n">
+        <v>-43</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1351,6 +1370,9 @@
       <c r="AF7" t="n">
         <v>7</v>
       </c>
+      <c r="AG7" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1453,6 +1475,9 @@
       <c r="AF8" t="n">
         <v>-4</v>
       </c>
+      <c r="AG8" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1555,6 +1580,9 @@
       <c r="AF9" t="n">
         <v>114</v>
       </c>
+      <c r="AG9" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1656,6 +1684,9 @@
       </c>
       <c r="AF10" t="n">
         <v>-22</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-26</v>
       </c>
     </row>
   </sheetData>
@@ -1669,7 +1700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BT10"/>
+  <dimension ref="A1:BU10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1744,6 +1775,7 @@
     <col width="12" customWidth="1" min="70" max="70"/>
     <col width="12" customWidth="1" min="71" max="71"/>
     <col width="12" customWidth="1" min="72" max="72"/>
+    <col width="12" customWidth="1" min="73" max="73"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2107,6 +2139,11 @@
           <t>20260106</t>
         </is>
       </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>20260107</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2329,6 +2366,9 @@
       <c r="BT2" t="n">
         <v>96</v>
       </c>
+      <c r="BU2" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2551,6 +2591,9 @@
       <c r="BT3" t="n">
         <v>105</v>
       </c>
+      <c r="BU3" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2773,6 +2816,9 @@
       <c r="BT4" t="n">
         <v>101</v>
       </c>
+      <c r="BU4" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2995,6 +3041,9 @@
       <c r="BT5" t="n">
         <v>99</v>
       </c>
+      <c r="BU5" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3217,6 +3266,9 @@
       <c r="BT6" t="n">
         <v>97</v>
       </c>
+      <c r="BU6" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3439,6 +3491,9 @@
       <c r="BT7" t="n">
         <v>102</v>
       </c>
+      <c r="BU7" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3661,6 +3716,9 @@
       <c r="BT8" t="n">
         <v>98</v>
       </c>
+      <c r="BU8" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3883,6 +3941,9 @@
       <c r="BT9" t="n">
         <v>105</v>
       </c>
+      <c r="BU9" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4104,6 +4165,9 @@
       </c>
       <c r="BT10" t="n">
         <v>94</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -6466,7 +6530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AG10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6501,6 +6565,7 @@
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="12" customWidth="1" min="31" max="31"/>
     <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6664,6 +6729,11 @@
           <t>20260106</t>
         </is>
       </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>20260107</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6766,6 +6836,9 @@
       <c r="AF2" t="n">
         <v>58</v>
       </c>
+      <c r="AG2" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6868,6 +6941,9 @@
       <c r="AF3" t="n">
         <v>60</v>
       </c>
+      <c r="AG3" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6970,6 +7046,9 @@
       <c r="AF4" t="n">
         <v>44</v>
       </c>
+      <c r="AG4" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7072,6 +7151,9 @@
       <c r="AF5" t="n">
         <v>51</v>
       </c>
+      <c r="AG5" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7174,6 +7256,9 @@
       <c r="AF6" t="n">
         <v>84</v>
       </c>
+      <c r="AG6" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7276,6 +7361,9 @@
       <c r="AF7" t="n">
         <v>48</v>
       </c>
+      <c r="AG7" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7378,6 +7466,9 @@
       <c r="AF8" t="n">
         <v>38</v>
       </c>
+      <c r="AG8" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7480,6 +7571,9 @@
       <c r="AF9" t="n">
         <v>60</v>
       </c>
+      <c r="AG9" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7581,6 +7675,9 @@
       </c>
       <c r="AF10" t="n">
         <v>56</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -7594,7 +7691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CM10"/>
+  <dimension ref="A1:CN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7688,6 +7785,7 @@
     <col width="12" customWidth="1" min="89" max="89"/>
     <col width="12" customWidth="1" min="90" max="90"/>
     <col width="12" customWidth="1" min="91" max="91"/>
+    <col width="12" customWidth="1" min="92" max="92"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7968,6 +8066,9 @@
       <c r="CM1" s="1" t="n">
         <v>20260106</v>
       </c>
+      <c r="CN1" s="1" t="n">
+        <v>20260107</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8247,6 +8348,9 @@
       <c r="CM2" t="n">
         <v>267</v>
       </c>
+      <c r="CN2" t="n">
+        <v>263.2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8526,6 +8630,9 @@
       <c r="CM3" t="n">
         <v>232.1</v>
       </c>
+      <c r="CN3" t="n">
+        <v>239.61</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8805,6 +8912,9 @@
       <c r="CM4" t="n">
         <v>316.4</v>
       </c>
+      <c r="CN4" t="n">
+        <v>314.36</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9084,6 +9194,9 @@
       <c r="CM5" t="n">
         <v>473.8</v>
       </c>
+      <c r="CN5" t="n">
+        <v>479.755</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9363,6 +9476,9 @@
       <c r="CM6" t="n">
         <v>91.54000000000001</v>
       </c>
+      <c r="CN6" t="n">
+        <v>91.55500000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9642,6 +9758,9 @@
       <c r="CM7" t="n">
         <v>190.52</v>
       </c>
+      <c r="CN7" t="n">
+        <v>188.57</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9921,6 +10040,9 @@
       <c r="CM8" t="n">
         <v>175.76</v>
       </c>
+      <c r="CN8" t="n">
+        <v>179.8</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10200,6 +10322,9 @@
       <c r="CM9" t="n">
         <v>86.56</v>
       </c>
+      <c r="CN9" t="n">
+        <v>89.02</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10478,6 +10603,9 @@
       </c>
       <c r="CM10" t="n">
         <v>446.38</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>435.9</v>
       </c>
     </row>
   </sheetData>
@@ -10491,7 +10619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CM10"/>
+  <dimension ref="A1:CN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10585,6 +10713,7 @@
     <col width="12" customWidth="1" min="89" max="89"/>
     <col width="12" customWidth="1" min="90" max="90"/>
     <col width="12" customWidth="1" min="91" max="91"/>
+    <col width="12" customWidth="1" min="92" max="92"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10865,6 +10994,9 @@
       <c r="CM1" s="1" t="n">
         <v>20260106</v>
       </c>
+      <c r="CN1" s="1" t="n">
+        <v>20260107</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11144,6 +11276,9 @@
       <c r="CM2" t="n">
         <v>267.55</v>
       </c>
+      <c r="CN2" t="n">
+        <v>263.68</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11423,6 +11558,9 @@
       <c r="CM3" t="n">
         <v>243.18</v>
       </c>
+      <c r="CN3" t="n">
+        <v>245.29</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11702,6 +11840,9 @@
       <c r="CM4" t="n">
         <v>320.94</v>
       </c>
+      <c r="CN4" t="n">
+        <v>326.15</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11981,6 +12122,9 @@
       <c r="CM5" t="n">
         <v>478.7367</v>
       </c>
+      <c r="CN5" t="n">
+        <v>489.7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12260,6 +12404,9 @@
       <c r="CM6" t="n">
         <v>91.64</v>
       </c>
+      <c r="CN6" t="n">
+        <v>92.419</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12539,6 +12686,9 @@
       <c r="CM7" t="n">
         <v>192.174</v>
       </c>
+      <c r="CN7" t="n">
+        <v>191.37</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12818,6 +12968,9 @@
       <c r="CM8" t="n">
         <v>180.19</v>
       </c>
+      <c r="CN8" t="n">
+        <v>187.28</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13097,6 +13250,9 @@
       <c r="CM9" t="n">
         <v>90.64</v>
       </c>
+      <c r="CN9" t="n">
+        <v>89.38</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13375,6 +13531,9 @@
       </c>
       <c r="CM10" t="n">
         <v>448.25</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>438.37</v>
       </c>
     </row>
   </sheetData>
@@ -13388,7 +13547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CM10"/>
+  <dimension ref="A1:CN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13482,6 +13641,7 @@
     <col width="12" customWidth="1" min="89" max="89"/>
     <col width="12" customWidth="1" min="90" max="90"/>
     <col width="12" customWidth="1" min="91" max="91"/>
+    <col width="12" customWidth="1" min="92" max="92"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13762,6 +13922,9 @@
       <c r="CM1" s="1" t="n">
         <v>20260106</v>
       </c>
+      <c r="CN1" s="1" t="n">
+        <v>20260107</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14041,6 +14204,9 @@
       <c r="CM2" t="n">
         <v>262.12</v>
       </c>
+      <c r="CN2" t="n">
+        <v>259.81</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14320,6 +14486,9 @@
       <c r="CM3" t="n">
         <v>232.07</v>
       </c>
+      <c r="CN3" t="n">
+        <v>239.52</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14599,6 +14768,9 @@
       <c r="CM4" t="n">
         <v>311.78</v>
       </c>
+      <c r="CN4" t="n">
+        <v>314.19</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14878,6 +15050,9 @@
       <c r="CM5" t="n">
         <v>469.75</v>
       </c>
+      <c r="CN5" t="n">
+        <v>477.95</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15157,6 +15332,9 @@
       <c r="CM6" t="n">
         <v>89.73999999999999</v>
       </c>
+      <c r="CN6" t="n">
+        <v>90.06</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15436,6 +15614,9 @@
       <c r="CM7" t="n">
         <v>186.82</v>
       </c>
+      <c r="CN7" t="n">
+        <v>186.56</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15715,6 +15896,9 @@
       <c r="CM8" t="n">
         <v>174.7701</v>
       </c>
+      <c r="CN8" t="n">
+        <v>177.66</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15994,6 +16178,9 @@
       <c r="CM9" t="n">
         <v>86.36</v>
       </c>
+      <c r="CN9" t="n">
+        <v>86.47</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16272,6 +16459,9 @@
       </c>
       <c r="CM10" t="n">
         <v>428.78</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>431.29</v>
       </c>
     </row>
   </sheetData>
@@ -16285,7 +16475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CM10"/>
+  <dimension ref="A1:CN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -16379,6 +16569,7 @@
     <col width="12" customWidth="1" min="89" max="89"/>
     <col width="12" customWidth="1" min="90" max="90"/>
     <col width="12" customWidth="1" min="91" max="91"/>
+    <col width="12" customWidth="1" min="92" max="92"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16659,6 +16850,9 @@
       <c r="CM1" s="1" t="n">
         <v>20260106</v>
       </c>
+      <c r="CN1" s="1" t="n">
+        <v>20260107</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16938,6 +17132,9 @@
       <c r="CM2" t="n">
         <v>262.36</v>
       </c>
+      <c r="CN2" t="n">
+        <v>260.33</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17217,6 +17414,9 @@
       <c r="CM3" t="n">
         <v>240.93</v>
       </c>
+      <c r="CN3" t="n">
+        <v>241.56</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17496,6 +17696,9 @@
       <c r="CM4" t="n">
         <v>314.34</v>
       </c>
+      <c r="CN4" t="n">
+        <v>321.98</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -17775,6 +17978,9 @@
       <c r="CM5" t="n">
         <v>478.51</v>
       </c>
+      <c r="CN5" t="n">
+        <v>483.47</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18054,6 +18260,9 @@
       <c r="CM6" t="n">
         <v>90.65000000000001</v>
       </c>
+      <c r="CN6" t="n">
+        <v>90.73</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18333,6 +18542,9 @@
       <c r="CM7" t="n">
         <v>187.24</v>
       </c>
+      <c r="CN7" t="n">
+        <v>189.11</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18612,6 +18824,9 @@
       <c r="CM8" t="n">
         <v>179.71</v>
       </c>
+      <c r="CN8" t="n">
+        <v>181.68</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18891,6 +19106,9 @@
       <c r="CM9" t="n">
         <v>89.45999999999999</v>
       </c>
+      <c r="CN9" t="n">
+        <v>86.69</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -19169,6 +19387,9 @@
       </c>
       <c r="CM10" t="n">
         <v>432.96</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>431.41</v>
       </c>
     </row>
   </sheetData>
@@ -19182,7 +19403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CM10"/>
+  <dimension ref="A1:CN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -19276,6 +19497,7 @@
     <col width="12" customWidth="1" min="89" max="89"/>
     <col width="12" customWidth="1" min="90" max="90"/>
     <col width="12" customWidth="1" min="91" max="91"/>
+    <col width="12" customWidth="1" min="92" max="92"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19556,6 +19778,9 @@
       <c r="CM1" s="1" t="n">
         <v>20260106</v>
       </c>
+      <c r="CN1" s="1" t="n">
+        <v>20260107</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19835,6 +20060,9 @@
       <c r="CM2" t="n">
         <v>52352090</v>
       </c>
+      <c r="CN2" t="n">
+        <v>48309804</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20114,6 +20342,9 @@
       <c r="CM3" t="n">
         <v>53764677</v>
       </c>
+      <c r="CN3" t="n">
+        <v>42236531</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20393,6 +20624,9 @@
       <c r="CM4" t="n">
         <v>31212101</v>
       </c>
+      <c r="CN4" t="n">
+        <v>35104425</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20672,6 +20906,9 @@
       <c r="CM5" t="n">
         <v>23037665</v>
       </c>
+      <c r="CN5" t="n">
+        <v>25564196</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20951,6 +21188,9 @@
       <c r="CM6" t="n">
         <v>43330972</v>
       </c>
+      <c r="CN6" t="n">
+        <v>36525740</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21230,6 +21470,9 @@
       <c r="CM7" t="n">
         <v>176862604</v>
       </c>
+      <c r="CN7" t="n">
+        <v>153543174</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21509,6 +21752,9 @@
       <c r="CM8" t="n">
         <v>34838611</v>
       </c>
+      <c r="CN8" t="n">
+        <v>45349012</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21788,6 +22034,9 @@
       <c r="CM9" t="n">
         <v>11351096</v>
       </c>
+      <c r="CN9" t="n">
+        <v>9546961</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22066,6 +22315,9 @@
       </c>
       <c r="CM10" t="n">
         <v>89093758</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>59828790</v>
       </c>
     </row>
   </sheetData>
@@ -22079,7 +22331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BT10"/>
+  <dimension ref="A1:BU10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22154,6 +22406,7 @@
     <col width="10" customWidth="1" min="70" max="70"/>
     <col width="10" customWidth="1" min="71" max="71"/>
     <col width="10" customWidth="1" min="72" max="72"/>
+    <col width="10" customWidth="1" min="73" max="73"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22377,6 +22630,9 @@
       <c r="BT1" s="1" t="n">
         <v>20260106</v>
       </c>
+      <c r="BU1" s="1" t="n">
+        <v>20260107</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22599,6 +22855,9 @@
       <c r="BT2" t="n">
         <v>0</v>
       </c>
+      <c r="BU2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22821,6 +23080,9 @@
       <c r="BT3" t="n">
         <v>100</v>
       </c>
+      <c r="BU3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23043,6 +23305,9 @@
       <c r="BT4" t="n">
         <v>75</v>
       </c>
+      <c r="BU4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23265,6 +23530,9 @@
       <c r="BT5" t="n">
         <v>29</v>
       </c>
+      <c r="BU5" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23487,6 +23755,9 @@
       <c r="BT6" t="n">
         <v>0</v>
       </c>
+      <c r="BU6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23709,6 +23980,9 @@
       <c r="BT7" t="n">
         <v>79</v>
       </c>
+      <c r="BU7" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23931,6 +24205,9 @@
       <c r="BT8" t="n">
         <v>45</v>
       </c>
+      <c r="BU8" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24153,6 +24430,9 @@
       <c r="BT9" t="n">
         <v>100</v>
       </c>
+      <c r="BU9" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24373,6 +24653,9 @@
         <v>13</v>
       </c>
       <c r="BT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -24387,7 +24670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AG10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24422,6 +24705,7 @@
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="10" customWidth="1" min="31" max="31"/>
     <col width="10" customWidth="1" min="32" max="32"/>
+    <col width="10" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24525,6 +24809,9 @@
       <c r="AF1" s="1" t="n">
         <v>20260106</v>
       </c>
+      <c r="AG1" s="1" t="n">
+        <v>20260107</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24627,6 +24914,9 @@
       <c r="AF2" t="n">
         <v>42</v>
       </c>
+      <c r="AG2" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -24729,6 +25019,9 @@
       <c r="AF3" t="n">
         <v>68</v>
       </c>
+      <c r="AG3" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -24831,6 +25124,9 @@
       <c r="AF4" t="n">
         <v>90</v>
       </c>
+      <c r="AG4" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24933,6 +25229,9 @@
       <c r="AF5" t="n">
         <v>9</v>
       </c>
+      <c r="AG5" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -25035,6 +25334,9 @@
       <c r="AF6" t="n">
         <v>0</v>
       </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -25137,6 +25439,9 @@
       <c r="AF7" t="n">
         <v>45</v>
       </c>
+      <c r="AG7" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25239,6 +25544,9 @@
       <c r="AF8" t="n">
         <v>48</v>
       </c>
+      <c r="AG8" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25341,6 +25649,9 @@
       <c r="AF9" t="n">
         <v>100</v>
       </c>
+      <c r="AG9" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25442,6 +25753,9 @@
       </c>
       <c r="AF10" t="n">
         <v>42</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -25455,7 +25769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BT10"/>
+  <dimension ref="A1:BU10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25530,6 +25844,7 @@
     <col width="10" customWidth="1" min="70" max="70"/>
     <col width="10" customWidth="1" min="71" max="71"/>
     <col width="10" customWidth="1" min="72" max="72"/>
+    <col width="10" customWidth="1" min="73" max="73"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25753,6 +26068,9 @@
       <c r="BT1" s="1" t="n">
         <v>20260106</v>
       </c>
+      <c r="BU1" s="1" t="n">
+        <v>20260107</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25975,6 +26293,9 @@
       <c r="BT2" t="n">
         <v>-151</v>
       </c>
+      <c r="BU2" t="n">
+        <v>-134</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -26197,6 +26518,9 @@
       <c r="BT3" t="n">
         <v>133</v>
       </c>
+      <c r="BU3" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -26419,6 +26743,9 @@
       <c r="BT4" t="n">
         <v>26</v>
       </c>
+      <c r="BU4" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -26641,6 +26968,9 @@
       <c r="BT5" t="n">
         <v>-34</v>
       </c>
+      <c r="BU5" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -26863,6 +27193,9 @@
       <c r="BT6" t="n">
         <v>-99</v>
       </c>
+      <c r="BU6" t="n">
+        <v>-88</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -27085,6 +27418,9 @@
       <c r="BT7" t="n">
         <v>30</v>
       </c>
+      <c r="BU7" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -27307,6 +27643,9 @@
       <c r="BT8" t="n">
         <v>-32</v>
       </c>
+      <c r="BU8" t="n">
+        <v>-18</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -27529,6 +27868,9 @@
       <c r="BT9" t="n">
         <v>112</v>
       </c>
+      <c r="BU9" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27750,6 +28092,9 @@
       </c>
       <c r="BT10" t="n">
         <v>-78</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>-79</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG10"/>
+  <dimension ref="A1:AH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -637,6 +637,7 @@
     <col width="10" customWidth="1" min="31" max="31"/>
     <col width="10" customWidth="1" min="32" max="32"/>
     <col width="10" customWidth="1" min="33" max="33"/>
+    <col width="10" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -743,6 +744,9 @@
       <c r="AG1" s="1" t="n">
         <v>20260107</v>
       </c>
+      <c r="AH1" s="1" t="n">
+        <v>20260108</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -848,6 +852,9 @@
       <c r="AG2" t="n">
         <v>-57</v>
       </c>
+      <c r="AH2" t="n">
+        <v>-68</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -953,6 +960,9 @@
       <c r="AG3" t="n">
         <v>60</v>
       </c>
+      <c r="AH3" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1058,6 +1068,9 @@
       <c r="AG4" t="n">
         <v>59</v>
       </c>
+      <c r="AH4" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1163,6 +1176,9 @@
       <c r="AG5" t="n">
         <v>-36</v>
       </c>
+      <c r="AH5" t="n">
+        <v>-49</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1268,6 +1284,9 @@
       <c r="AG6" t="n">
         <v>-43</v>
       </c>
+      <c r="AH6" t="n">
+        <v>-41</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1373,6 +1392,9 @@
       <c r="AG7" t="n">
         <v>19</v>
       </c>
+      <c r="AH7" t="n">
+        <v>-7</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1478,6 +1500,9 @@
       <c r="AG8" t="n">
         <v>5</v>
       </c>
+      <c r="AH8" t="n">
+        <v>-18</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1583,6 +1608,9 @@
       <c r="AG9" t="n">
         <v>49</v>
       </c>
+      <c r="AH9" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1687,6 +1715,9 @@
       </c>
       <c r="AG10" t="n">
         <v>-26</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-17</v>
       </c>
     </row>
   </sheetData>
@@ -1700,7 +1731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU10"/>
+  <dimension ref="A1:BV10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1776,6 +1807,7 @@
     <col width="12" customWidth="1" min="71" max="71"/>
     <col width="12" customWidth="1" min="72" max="72"/>
     <col width="12" customWidth="1" min="73" max="73"/>
+    <col width="12" customWidth="1" min="74" max="74"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2144,6 +2176,11 @@
           <t>20260107</t>
         </is>
       </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>20260108</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2369,6 +2406,9 @@
       <c r="BU2" t="n">
         <v>95</v>
       </c>
+      <c r="BV2" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2594,6 +2634,9 @@
       <c r="BU3" t="n">
         <v>105</v>
       </c>
+      <c r="BV3" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2819,6 +2862,9 @@
       <c r="BU4" t="n">
         <v>103</v>
       </c>
+      <c r="BV4" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3044,6 +3090,9 @@
       <c r="BU5" t="n">
         <v>100</v>
       </c>
+      <c r="BV5" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3269,6 +3318,9 @@
       <c r="BU6" t="n">
         <v>97</v>
       </c>
+      <c r="BV6" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3494,6 +3546,9 @@
       <c r="BU7" t="n">
         <v>103</v>
       </c>
+      <c r="BV7" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3719,6 +3774,9 @@
       <c r="BU8" t="n">
         <v>99</v>
       </c>
+      <c r="BV8" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3944,6 +4002,9 @@
       <c r="BU9" t="n">
         <v>101</v>
       </c>
+      <c r="BV9" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4168,6 +4229,9 @@
       </c>
       <c r="BU10" t="n">
         <v>93</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -6530,7 +6594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG10"/>
+  <dimension ref="A1:AH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6566,6 +6630,7 @@
     <col width="12" customWidth="1" min="31" max="31"/>
     <col width="12" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6734,6 +6799,11 @@
           <t>20260107</t>
         </is>
       </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>20260108</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6839,6 +6909,9 @@
       <c r="AG2" t="n">
         <v>54</v>
       </c>
+      <c r="AH2" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6944,6 +7017,9 @@
       <c r="AG3" t="n">
         <v>48</v>
       </c>
+      <c r="AH3" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7049,6 +7125,9 @@
       <c r="AG4" t="n">
         <v>49</v>
       </c>
+      <c r="AH4" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7154,6 +7233,9 @@
       <c r="AG5" t="n">
         <v>56</v>
       </c>
+      <c r="AH5" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7259,6 +7341,9 @@
       <c r="AG6" t="n">
         <v>69</v>
       </c>
+      <c r="AH6" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7364,6 +7449,9 @@
       <c r="AG7" t="n">
         <v>42</v>
       </c>
+      <c r="AH7" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7469,6 +7557,9 @@
       <c r="AG8" t="n">
         <v>50</v>
       </c>
+      <c r="AH8" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7574,6 +7665,9 @@
       <c r="AG9" t="n">
         <v>50</v>
       </c>
+      <c r="AH9" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7678,6 +7772,9 @@
       </c>
       <c r="AG10" t="n">
         <v>38</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -7691,7 +7788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CN10"/>
+  <dimension ref="A1:CO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7786,6 +7883,7 @@
     <col width="12" customWidth="1" min="90" max="90"/>
     <col width="12" customWidth="1" min="91" max="91"/>
     <col width="12" customWidth="1" min="92" max="92"/>
+    <col width="12" customWidth="1" min="93" max="93"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8069,6 +8167,9 @@
       <c r="CN1" s="1" t="n">
         <v>20260107</v>
       </c>
+      <c r="CO1" s="1" t="n">
+        <v>20260108</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8351,6 +8452,9 @@
       <c r="CN2" t="n">
         <v>263.2</v>
       </c>
+      <c r="CO2" t="n">
+        <v>257.02</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8633,6 +8737,9 @@
       <c r="CN3" t="n">
         <v>239.61</v>
       </c>
+      <c r="CO3" t="n">
+        <v>243.06</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8915,6 +9022,9 @@
       <c r="CN4" t="n">
         <v>314.36</v>
       </c>
+      <c r="CO4" t="n">
+        <v>328.965</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9197,6 +9307,9 @@
       <c r="CN5" t="n">
         <v>479.755</v>
       </c>
+      <c r="CO5" t="n">
+        <v>481.24</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9479,6 +9592,9 @@
       <c r="CN6" t="n">
         <v>91.55500000000001</v>
       </c>
+      <c r="CO6" t="n">
+        <v>90.45</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9761,6 +9877,9 @@
       <c r="CN7" t="n">
         <v>188.57</v>
       </c>
+      <c r="CO7" t="n">
+        <v>189.11</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10043,6 +10162,9 @@
       <c r="CN8" t="n">
         <v>179.8</v>
       </c>
+      <c r="CO8" t="n">
+        <v>185.615</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10325,6 +10447,9 @@
       <c r="CN9" t="n">
         <v>89.02</v>
       </c>
+      <c r="CO9" t="n">
+        <v>85.86</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10606,6 +10731,9 @@
       </c>
       <c r="CN10" t="n">
         <v>435.9</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>427.89</v>
       </c>
     </row>
   </sheetData>
@@ -10619,7 +10747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CN10"/>
+  <dimension ref="A1:CO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10714,6 +10842,7 @@
     <col width="12" customWidth="1" min="90" max="90"/>
     <col width="12" customWidth="1" min="91" max="91"/>
     <col width="12" customWidth="1" min="92" max="92"/>
+    <col width="12" customWidth="1" min="93" max="93"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10997,6 +11126,9 @@
       <c r="CN1" s="1" t="n">
         <v>20260107</v>
       </c>
+      <c r="CO1" s="1" t="n">
+        <v>20260108</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11279,6 +11411,9 @@
       <c r="CN2" t="n">
         <v>263.68</v>
       </c>
+      <c r="CO2" t="n">
+        <v>259.29</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11561,6 +11696,9 @@
       <c r="CN3" t="n">
         <v>245.29</v>
       </c>
+      <c r="CO3" t="n">
+        <v>246.41</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11843,6 +11981,9 @@
       <c r="CN4" t="n">
         <v>326.15</v>
       </c>
+      <c r="CO4" t="n">
+        <v>330.3196</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12125,6 +12266,9 @@
       <c r="CN5" t="n">
         <v>489.7</v>
       </c>
+      <c r="CO5" t="n">
+        <v>482.66</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12407,6 +12551,9 @@
       <c r="CN6" t="n">
         <v>92.419</v>
       </c>
+      <c r="CO6" t="n">
+        <v>91.25</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12689,6 +12836,9 @@
       <c r="CN7" t="n">
         <v>191.37</v>
       </c>
+      <c r="CO7" t="n">
+        <v>189.55</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12971,6 +13121,9 @@
       <c r="CN8" t="n">
         <v>187.28</v>
       </c>
+      <c r="CO8" t="n">
+        <v>185.66</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13253,6 +13406,9 @@
       <c r="CN9" t="n">
         <v>89.38</v>
       </c>
+      <c r="CO9" t="n">
+        <v>89.29000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13534,6 +13690,9 @@
       </c>
       <c r="CN10" t="n">
         <v>438.37</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>436.89</v>
       </c>
     </row>
   </sheetData>
@@ -13547,7 +13706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CN10"/>
+  <dimension ref="A1:CO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13642,6 +13801,7 @@
     <col width="12" customWidth="1" min="90" max="90"/>
     <col width="12" customWidth="1" min="91" max="91"/>
     <col width="12" customWidth="1" min="92" max="92"/>
+    <col width="12" customWidth="1" min="93" max="93"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13925,6 +14085,9 @@
       <c r="CN1" s="1" t="n">
         <v>20260107</v>
       </c>
+      <c r="CO1" s="1" t="n">
+        <v>20260108</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14207,6 +14370,9 @@
       <c r="CN2" t="n">
         <v>259.81</v>
       </c>
+      <c r="CO2" t="n">
+        <v>255.7</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14489,6 +14655,9 @@
       <c r="CN3" t="n">
         <v>239.52</v>
       </c>
+      <c r="CO3" t="n">
+        <v>241.88</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14771,6 +14940,9 @@
       <c r="CN4" t="n">
         <v>314.19</v>
       </c>
+      <c r="CO4" t="n">
+        <v>321.5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15053,6 +15225,9 @@
       <c r="CN5" t="n">
         <v>477.95</v>
       </c>
+      <c r="CO5" t="n">
+        <v>475.86</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15335,6 +15510,9 @@
       <c r="CN6" t="n">
         <v>90.06</v>
       </c>
+      <c r="CO6" t="n">
+        <v>89.58</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15617,6 +15795,9 @@
       <c r="CN7" t="n">
         <v>186.56</v>
       </c>
+      <c r="CO7" t="n">
+        <v>183.71</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15899,6 +16080,9 @@
       <c r="CN8" t="n">
         <v>177.66</v>
       </c>
+      <c r="CO8" t="n">
+        <v>174.37</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16181,6 +16365,9 @@
       <c r="CN9" t="n">
         <v>86.47</v>
       </c>
+      <c r="CO9" t="n">
+        <v>85.61</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16462,6 +16649,9 @@
       </c>
       <c r="CN10" t="n">
         <v>431.29</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>424.365</v>
       </c>
     </row>
   </sheetData>
@@ -16475,7 +16665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CN10"/>
+  <dimension ref="A1:CO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -16570,6 +16760,7 @@
     <col width="12" customWidth="1" min="90" max="90"/>
     <col width="12" customWidth="1" min="91" max="91"/>
     <col width="12" customWidth="1" min="92" max="92"/>
+    <col width="12" customWidth="1" min="93" max="93"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16853,6 +17044,9 @@
       <c r="CN1" s="1" t="n">
         <v>20260107</v>
       </c>
+      <c r="CO1" s="1" t="n">
+        <v>20260108</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17135,6 +17329,9 @@
       <c r="CN2" t="n">
         <v>260.33</v>
       </c>
+      <c r="CO2" t="n">
+        <v>259.04</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17417,6 +17614,9 @@
       <c r="CN3" t="n">
         <v>241.56</v>
       </c>
+      <c r="CO3" t="n">
+        <v>246.29</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17699,6 +17899,9 @@
       <c r="CN4" t="n">
         <v>321.98</v>
       </c>
+      <c r="CO4" t="n">
+        <v>325.44</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -17981,6 +18184,9 @@
       <c r="CN5" t="n">
         <v>483.47</v>
       </c>
+      <c r="CO5" t="n">
+        <v>478.11</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18263,6 +18469,9 @@
       <c r="CN6" t="n">
         <v>90.73</v>
       </c>
+      <c r="CO6" t="n">
+        <v>90.53</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18545,6 +18754,9 @@
       <c r="CN7" t="n">
         <v>189.11</v>
       </c>
+      <c r="CO7" t="n">
+        <v>185.04</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18827,6 +19039,9 @@
       <c r="CN8" t="n">
         <v>181.68</v>
       </c>
+      <c r="CO8" t="n">
+        <v>176.86</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19109,6 +19324,9 @@
       <c r="CN9" t="n">
         <v>86.69</v>
       </c>
+      <c r="CO9" t="n">
+        <v>88.18000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -19390,6 +19608,9 @@
       </c>
       <c r="CN10" t="n">
         <v>431.41</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>435.8</v>
       </c>
     </row>
   </sheetData>
@@ -19403,7 +19624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CN10"/>
+  <dimension ref="A1:CO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -19498,6 +19719,7 @@
     <col width="12" customWidth="1" min="90" max="90"/>
     <col width="12" customWidth="1" min="91" max="91"/>
     <col width="12" customWidth="1" min="92" max="92"/>
+    <col width="12" customWidth="1" min="93" max="93"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19781,6 +20003,9 @@
       <c r="CN1" s="1" t="n">
         <v>20260107</v>
       </c>
+      <c r="CO1" s="1" t="n">
+        <v>20260108</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20063,6 +20288,9 @@
       <c r="CN2" t="n">
         <v>48309804</v>
       </c>
+      <c r="CO2" t="n">
+        <v>50419337</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20345,6 +20573,9 @@
       <c r="CN3" t="n">
         <v>42236531</v>
       </c>
+      <c r="CO3" t="n">
+        <v>39509844</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20627,6 +20858,9 @@
       <c r="CN4" t="n">
         <v>35104425</v>
       </c>
+      <c r="CO4" t="n">
+        <v>31896101</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20909,6 +21143,9 @@
       <c r="CN5" t="n">
         <v>25564196</v>
       </c>
+      <c r="CO5" t="n">
+        <v>18162616</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21191,6 +21428,9 @@
       <c r="CN6" t="n">
         <v>36525740</v>
       </c>
+      <c r="CO6" t="n">
+        <v>40068670</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21473,6 +21713,9 @@
       <c r="CN7" t="n">
         <v>153543174</v>
       </c>
+      <c r="CO7" t="n">
+        <v>172457048</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21755,6 +21998,9 @@
       <c r="CN8" t="n">
         <v>45349012</v>
       </c>
+      <c r="CO8" t="n">
+        <v>47304286</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22037,6 +22283,9 @@
       <c r="CN9" t="n">
         <v>9546961</v>
       </c>
+      <c r="CO9" t="n">
+        <v>8140135</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22318,6 +22567,9 @@
       </c>
       <c r="CN10" t="n">
         <v>59828790</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>57041094</v>
       </c>
     </row>
   </sheetData>
@@ -22331,7 +22583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU10"/>
+  <dimension ref="A1:BV10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22407,6 +22659,7 @@
     <col width="10" customWidth="1" min="71" max="71"/>
     <col width="10" customWidth="1" min="72" max="72"/>
     <col width="10" customWidth="1" min="73" max="73"/>
+    <col width="10" customWidth="1" min="74" max="74"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22633,6 +22886,9 @@
       <c r="BU1" s="1" t="n">
         <v>20260107</v>
       </c>
+      <c r="BV1" s="1" t="n">
+        <v>20260108</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22858,6 +23114,9 @@
       <c r="BU2" t="n">
         <v>0</v>
       </c>
+      <c r="BV2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23083,6 +23342,9 @@
       <c r="BU3" t="n">
         <v>100</v>
       </c>
+      <c r="BV3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23308,6 +23570,9 @@
       <c r="BU4" t="n">
         <v>100</v>
       </c>
+      <c r="BV4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23533,6 +23798,9 @@
       <c r="BU5" t="n">
         <v>55</v>
       </c>
+      <c r="BV5" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23758,6 +24026,9 @@
       <c r="BU6" t="n">
         <v>1</v>
       </c>
+      <c r="BV6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23983,6 +24254,9 @@
       <c r="BU7" t="n">
         <v>88</v>
       </c>
+      <c r="BV7" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24208,6 +24482,9 @@
       <c r="BU8" t="n">
         <v>53</v>
       </c>
+      <c r="BV8" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24433,6 +24710,9 @@
       <c r="BU9" t="n">
         <v>61</v>
       </c>
+      <c r="BV9" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24657,6 +24937,9 @@
       </c>
       <c r="BU10" t="n">
         <v>0</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -24670,7 +24953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG10"/>
+  <dimension ref="A1:AH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24706,6 +24989,7 @@
     <col width="10" customWidth="1" min="31" max="31"/>
     <col width="10" customWidth="1" min="32" max="32"/>
     <col width="10" customWidth="1" min="33" max="33"/>
+    <col width="10" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24812,6 +25096,9 @@
       <c r="AG1" s="1" t="n">
         <v>20260107</v>
       </c>
+      <c r="AH1" s="1" t="n">
+        <v>20260108</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24917,6 +25204,9 @@
       <c r="AG2" t="n">
         <v>33</v>
       </c>
+      <c r="AH2" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25022,6 +25312,9 @@
       <c r="AG3" t="n">
         <v>70</v>
       </c>
+      <c r="AH3" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -25127,6 +25420,9 @@
       <c r="AG4" t="n">
         <v>98</v>
       </c>
+      <c r="AH4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -25232,6 +25528,9 @@
       <c r="AG5" t="n">
         <v>16</v>
       </c>
+      <c r="AH5" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -25337,6 +25636,9 @@
       <c r="AG6" t="n">
         <v>0</v>
       </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -25442,6 +25744,9 @@
       <c r="AG7" t="n">
         <v>50</v>
       </c>
+      <c r="AH7" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25547,6 +25852,9 @@
       <c r="AG8" t="n">
         <v>51</v>
       </c>
+      <c r="AH8" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25652,6 +25960,9 @@
       <c r="AG9" t="n">
         <v>72</v>
       </c>
+      <c r="AH9" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25756,6 +26067,9 @@
       </c>
       <c r="AG10" t="n">
         <v>41</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -25769,7 +26083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU10"/>
+  <dimension ref="A1:BV10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25845,6 +26159,7 @@
     <col width="10" customWidth="1" min="71" max="71"/>
     <col width="10" customWidth="1" min="72" max="72"/>
     <col width="10" customWidth="1" min="73" max="73"/>
+    <col width="10" customWidth="1" min="74" max="74"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26071,6 +26386,9 @@
       <c r="BU1" s="1" t="n">
         <v>20260107</v>
       </c>
+      <c r="BV1" s="1" t="n">
+        <v>20260108</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -26296,6 +26614,9 @@
       <c r="BU2" t="n">
         <v>-134</v>
       </c>
+      <c r="BV2" t="n">
+        <v>-118</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -26521,6 +26842,9 @@
       <c r="BU3" t="n">
         <v>113</v>
       </c>
+      <c r="BV3" t="n">
+        <v>122</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -26746,6 +27070,9 @@
       <c r="BU4" t="n">
         <v>85</v>
       </c>
+      <c r="BV4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -26971,6 +27298,9 @@
       <c r="BU5" t="n">
         <v>11</v>
       </c>
+      <c r="BV5" t="n">
+        <v>-33</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -27196,6 +27526,9 @@
       <c r="BU6" t="n">
         <v>-88</v>
       </c>
+      <c r="BV6" t="n">
+        <v>-88</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -27421,6 +27754,9 @@
       <c r="BU7" t="n">
         <v>43</v>
       </c>
+      <c r="BV7" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -27646,6 +27982,9 @@
       <c r="BU8" t="n">
         <v>-18</v>
       </c>
+      <c r="BV8" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -27871,6 +28210,9 @@
       <c r="BU9" t="n">
         <v>34</v>
       </c>
+      <c r="BV9" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28095,6 +28437,9 @@
       </c>
       <c r="BU10" t="n">
         <v>-79</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>-65</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH10"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -638,6 +638,7 @@
     <col width="10" customWidth="1" min="32" max="32"/>
     <col width="10" customWidth="1" min="33" max="33"/>
     <col width="10" customWidth="1" min="34" max="34"/>
+    <col width="10" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -747,6 +748,9 @@
       <c r="AH1" s="1" t="n">
         <v>20260108</v>
       </c>
+      <c r="AI1" s="1" t="n">
+        <v>20260109</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -855,6 +859,9 @@
       <c r="AH2" t="n">
         <v>-68</v>
       </c>
+      <c r="AI2" t="n">
+        <v>-71</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -963,6 +970,9 @@
       <c r="AH3" t="n">
         <v>81</v>
       </c>
+      <c r="AI3" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1071,6 +1081,9 @@
       <c r="AH4" t="n">
         <v>65</v>
       </c>
+      <c r="AI4" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1179,6 +1192,9 @@
       <c r="AH5" t="n">
         <v>-49</v>
       </c>
+      <c r="AI5" t="n">
+        <v>-45</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1287,6 +1303,9 @@
       <c r="AH6" t="n">
         <v>-41</v>
       </c>
+      <c r="AI6" t="n">
+        <v>-40</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1395,6 +1414,9 @@
       <c r="AH7" t="n">
         <v>-7</v>
       </c>
+      <c r="AI7" t="n">
+        <v>-9</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1503,6 +1525,9 @@
       <c r="AH8" t="n">
         <v>-18</v>
       </c>
+      <c r="AI8" t="n">
+        <v>-15</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1611,6 +1636,9 @@
       <c r="AH9" t="n">
         <v>85</v>
       </c>
+      <c r="AI9" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1718,6 +1746,9 @@
       </c>
       <c r="AH10" t="n">
         <v>-17</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1731,7 +1762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV10"/>
+  <dimension ref="A1:BW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1808,6 +1839,7 @@
     <col width="12" customWidth="1" min="72" max="72"/>
     <col width="12" customWidth="1" min="73" max="73"/>
     <col width="12" customWidth="1" min="74" max="74"/>
+    <col width="12" customWidth="1" min="75" max="75"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2181,6 +2213,11 @@
           <t>20260108</t>
         </is>
       </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>20260109</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2409,6 +2446,9 @@
       <c r="BV2" t="n">
         <v>95</v>
       </c>
+      <c r="BW2" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2637,6 +2677,9 @@
       <c r="BV3" t="n">
         <v>107</v>
       </c>
+      <c r="BW3" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2865,6 +2908,9 @@
       <c r="BV4" t="n">
         <v>104</v>
       </c>
+      <c r="BW4" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3093,6 +3139,9 @@
       <c r="BV5" t="n">
         <v>99</v>
       </c>
+      <c r="BW5" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3321,6 +3370,9 @@
       <c r="BV6" t="n">
         <v>97</v>
       </c>
+      <c r="BW6" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3549,6 +3601,9 @@
       <c r="BV7" t="n">
         <v>101</v>
       </c>
+      <c r="BW7" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3777,6 +3832,9 @@
       <c r="BV8" t="n">
         <v>96</v>
       </c>
+      <c r="BW8" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4005,6 +4063,9 @@
       <c r="BV9" t="n">
         <v>103</v>
       </c>
+      <c r="BW9" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4232,6 +4293,9 @@
       </c>
       <c r="BV10" t="n">
         <v>94</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -6594,7 +6658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH10"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6631,6 +6695,7 @@
     <col width="12" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
     <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6804,6 +6869,11 @@
           <t>20260108</t>
         </is>
       </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>20260109</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6912,6 +6982,9 @@
       <c r="AH2" t="n">
         <v>56</v>
       </c>
+      <c r="AI2" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7020,6 +7093,9 @@
       <c r="AH3" t="n">
         <v>44</v>
       </c>
+      <c r="AI3" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7128,6 +7204,9 @@
       <c r="AH4" t="n">
         <v>45</v>
       </c>
+      <c r="AI4" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7236,6 +7315,9 @@
       <c r="AH5" t="n">
         <v>40</v>
       </c>
+      <c r="AI5" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7344,6 +7426,9 @@
       <c r="AH6" t="n">
         <v>74</v>
       </c>
+      <c r="AI6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7452,6 +7537,9 @@
       <c r="AH7" t="n">
         <v>47</v>
       </c>
+      <c r="AI7" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7560,6 +7648,9 @@
       <c r="AH8" t="n">
         <v>52</v>
       </c>
+      <c r="AI8" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7668,6 +7759,9 @@
       <c r="AH9" t="n">
         <v>43</v>
       </c>
+      <c r="AI9" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7775,6 +7869,9 @@
       </c>
       <c r="AH10" t="n">
         <v>37</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -7788,7 +7885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CO10"/>
+  <dimension ref="A1:CP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7884,6 +7981,7 @@
     <col width="12" customWidth="1" min="91" max="91"/>
     <col width="12" customWidth="1" min="92" max="92"/>
     <col width="12" customWidth="1" min="93" max="93"/>
+    <col width="12" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8170,6 +8268,9 @@
       <c r="CO1" s="1" t="n">
         <v>20260108</v>
       </c>
+      <c r="CP1" s="1" t="n">
+        <v>20260109</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8455,6 +8556,9 @@
       <c r="CO2" t="n">
         <v>257.02</v>
       </c>
+      <c r="CP2" t="n">
+        <v>259.075</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8740,6 +8844,9 @@
       <c r="CO3" t="n">
         <v>243.06</v>
       </c>
+      <c r="CP3" t="n">
+        <v>244.568</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9025,6 +9132,9 @@
       <c r="CO4" t="n">
         <v>328.965</v>
       </c>
+      <c r="CP4" t="n">
+        <v>327.09</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9310,6 +9420,9 @@
       <c r="CO5" t="n">
         <v>481.24</v>
       </c>
+      <c r="CP5" t="n">
+        <v>474.06</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9595,6 +9708,9 @@
       <c r="CO6" t="n">
         <v>90.45</v>
       </c>
+      <c r="CP6" t="n">
+        <v>90.03</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9880,6 +9996,9 @@
       <c r="CO7" t="n">
         <v>189.11</v>
       </c>
+      <c r="CP7" t="n">
+        <v>185.08</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10165,6 +10284,9 @@
       <c r="CO8" t="n">
         <v>185.615</v>
       </c>
+      <c r="CP8" t="n">
+        <v>177.02</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10450,6 +10572,9 @@
       <c r="CO9" t="n">
         <v>85.86</v>
       </c>
+      <c r="CP9" t="n">
+        <v>88.34999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10734,6 +10859,9 @@
       </c>
       <c r="CO10" t="n">
         <v>427.89</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>435.945</v>
       </c>
     </row>
   </sheetData>
@@ -10747,7 +10875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CO10"/>
+  <dimension ref="A1:CP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10843,6 +10971,7 @@
     <col width="12" customWidth="1" min="91" max="91"/>
     <col width="12" customWidth="1" min="92" max="92"/>
     <col width="12" customWidth="1" min="93" max="93"/>
+    <col width="12" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11129,6 +11258,9 @@
       <c r="CO1" s="1" t="n">
         <v>20260108</v>
       </c>
+      <c r="CP1" s="1" t="n">
+        <v>20260109</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11414,6 +11546,9 @@
       <c r="CO2" t="n">
         <v>259.29</v>
       </c>
+      <c r="CP2" t="n">
+        <v>260.21</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11699,6 +11834,9 @@
       <c r="CO3" t="n">
         <v>246.41</v>
       </c>
+      <c r="CP3" t="n">
+        <v>247.86</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11984,6 +12122,9 @@
       <c r="CO4" t="n">
         <v>330.3196</v>
       </c>
+      <c r="CP4" t="n">
+        <v>330.83</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12269,6 +12410,9 @@
       <c r="CO5" t="n">
         <v>482.66</v>
       </c>
+      <c r="CP5" t="n">
+        <v>479.82</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12554,6 +12698,9 @@
       <c r="CO6" t="n">
         <v>91.25</v>
       </c>
+      <c r="CP6" t="n">
+        <v>90.05</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12839,6 +12986,9 @@
       <c r="CO7" t="n">
         <v>189.55</v>
       </c>
+      <c r="CP7" t="n">
+        <v>186.34</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13124,6 +13274,9 @@
       <c r="CO8" t="n">
         <v>185.66</v>
       </c>
+      <c r="CP8" t="n">
+        <v>178.72</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13409,6 +13562,9 @@
       <c r="CO9" t="n">
         <v>89.29000000000001</v>
       </c>
+      <c r="CP9" t="n">
+        <v>89.09999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13693,6 +13849,9 @@
       </c>
       <c r="CO10" t="n">
         <v>436.89</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>449.05</v>
       </c>
     </row>
   </sheetData>
@@ -13706,7 +13865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CO10"/>
+  <dimension ref="A1:CP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13802,6 +13961,7 @@
     <col width="12" customWidth="1" min="91" max="91"/>
     <col width="12" customWidth="1" min="92" max="92"/>
     <col width="12" customWidth="1" min="93" max="93"/>
+    <col width="12" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14088,6 +14248,9 @@
       <c r="CO1" s="1" t="n">
         <v>20260108</v>
       </c>
+      <c r="CP1" s="1" t="n">
+        <v>20260109</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14373,6 +14536,9 @@
       <c r="CO2" t="n">
         <v>255.7</v>
       </c>
+      <c r="CP2" t="n">
+        <v>256.22</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14658,6 +14824,9 @@
       <c r="CO3" t="n">
         <v>241.88</v>
       </c>
+      <c r="CP3" t="n">
+        <v>242.24</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14943,6 +15112,9 @@
       <c r="CO4" t="n">
         <v>321.5</v>
       </c>
+      <c r="CP4" t="n">
+        <v>325.8</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15228,6 +15400,9 @@
       <c r="CO5" t="n">
         <v>475.86</v>
       </c>
+      <c r="CP5" t="n">
+        <v>472.2001</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15513,6 +15688,9 @@
       <c r="CO6" t="n">
         <v>89.58</v>
       </c>
+      <c r="CP6" t="n">
+        <v>88.31999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15798,6 +15976,9 @@
       <c r="CO7" t="n">
         <v>183.71</v>
       </c>
+      <c r="CP7" t="n">
+        <v>183.6701</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16083,6 +16264,9 @@
       <c r="CO8" t="n">
         <v>174.37</v>
       </c>
+      <c r="CP8" t="n">
+        <v>174.75</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16368,6 +16552,9 @@
       <c r="CO9" t="n">
         <v>85.61</v>
       </c>
+      <c r="CP9" t="n">
+        <v>86.79000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16652,6 +16839,9 @@
       </c>
       <c r="CO10" t="n">
         <v>424.365</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>430.39</v>
       </c>
     </row>
   </sheetData>
@@ -16665,7 +16855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CO10"/>
+  <dimension ref="A1:CP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -16761,6 +16951,7 @@
     <col width="12" customWidth="1" min="91" max="91"/>
     <col width="12" customWidth="1" min="92" max="92"/>
     <col width="12" customWidth="1" min="93" max="93"/>
+    <col width="12" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17047,6 +17238,9 @@
       <c r="CO1" s="1" t="n">
         <v>20260108</v>
       </c>
+      <c r="CP1" s="1" t="n">
+        <v>20260109</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17332,6 +17526,9 @@
       <c r="CO2" t="n">
         <v>259.04</v>
       </c>
+      <c r="CP2" t="n">
+        <v>259.37</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17617,6 +17814,9 @@
       <c r="CO3" t="n">
         <v>246.29</v>
       </c>
+      <c r="CP3" t="n">
+        <v>247.38</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17902,6 +18102,9 @@
       <c r="CO4" t="n">
         <v>325.44</v>
       </c>
+      <c r="CP4" t="n">
+        <v>328.57</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18187,6 +18390,9 @@
       <c r="CO5" t="n">
         <v>478.11</v>
       </c>
+      <c r="CP5" t="n">
+        <v>479.28</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18472,6 +18678,9 @@
       <c r="CO6" t="n">
         <v>90.53</v>
       </c>
+      <c r="CP6" t="n">
+        <v>89.45999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18757,6 +18966,9 @@
       <c r="CO7" t="n">
         <v>185.04</v>
       </c>
+      <c r="CP7" t="n">
+        <v>184.86</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19042,6 +19254,9 @@
       <c r="CO8" t="n">
         <v>176.86</v>
       </c>
+      <c r="CP8" t="n">
+        <v>177.49</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19327,6 +19542,9 @@
       <c r="CO9" t="n">
         <v>88.18000000000001</v>
       </c>
+      <c r="CP9" t="n">
+        <v>88.88</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -19611,6 +19829,9 @@
       </c>
       <c r="CO10" t="n">
         <v>435.8</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>445.01</v>
       </c>
     </row>
   </sheetData>
@@ -19624,7 +19845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CO10"/>
+  <dimension ref="A1:CP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -19720,6 +19941,7 @@
     <col width="12" customWidth="1" min="91" max="91"/>
     <col width="12" customWidth="1" min="92" max="92"/>
     <col width="12" customWidth="1" min="93" max="93"/>
+    <col width="12" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20006,6 +20228,9 @@
       <c r="CO1" s="1" t="n">
         <v>20260108</v>
       </c>
+      <c r="CP1" s="1" t="n">
+        <v>20260109</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20291,6 +20516,9 @@
       <c r="CO2" t="n">
         <v>50419337</v>
       </c>
+      <c r="CP2" t="n">
+        <v>39996967</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20576,6 +20804,9 @@
       <c r="CO3" t="n">
         <v>39509844</v>
       </c>
+      <c r="CP3" t="n">
+        <v>34559961</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20861,6 +21092,9 @@
       <c r="CO4" t="n">
         <v>31896101</v>
       </c>
+      <c r="CP4" t="n">
+        <v>26214166</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -21146,6 +21380,9 @@
       <c r="CO5" t="n">
         <v>18162616</v>
       </c>
+      <c r="CP5" t="n">
+        <v>18491036</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21431,6 +21668,9 @@
       <c r="CO6" t="n">
         <v>40068670</v>
       </c>
+      <c r="CP6" t="n">
+        <v>55579523</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21716,6 +21956,9 @@
       <c r="CO7" t="n">
         <v>172457048</v>
       </c>
+      <c r="CP7" t="n">
+        <v>131327534</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22001,6 +22244,9 @@
       <c r="CO8" t="n">
         <v>47304286</v>
       </c>
+      <c r="CP8" t="n">
+        <v>31362890</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22286,6 +22532,9 @@
       <c r="CO9" t="n">
         <v>8140135</v>
       </c>
+      <c r="CP9" t="n">
+        <v>7593162</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22570,6 +22819,9 @@
       </c>
       <c r="CO10" t="n">
         <v>57041094</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>67331456</v>
       </c>
     </row>
   </sheetData>
@@ -22583,7 +22835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV10"/>
+  <dimension ref="A1:BW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22660,6 +22912,7 @@
     <col width="10" customWidth="1" min="72" max="72"/>
     <col width="10" customWidth="1" min="73" max="73"/>
     <col width="10" customWidth="1" min="74" max="74"/>
+    <col width="10" customWidth="1" min="75" max="75"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22889,6 +23142,9 @@
       <c r="BV1" s="1" t="n">
         <v>20260108</v>
       </c>
+      <c r="BW1" s="1" t="n">
+        <v>20260109</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23117,6 +23373,9 @@
       <c r="BV2" t="n">
         <v>0</v>
       </c>
+      <c r="BW2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23345,6 +23604,9 @@
       <c r="BV3" t="n">
         <v>100</v>
       </c>
+      <c r="BW3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23573,6 +23835,9 @@
       <c r="BV4" t="n">
         <v>100</v>
       </c>
+      <c r="BW4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23801,6 +24066,9 @@
       <c r="BV5" t="n">
         <v>34</v>
       </c>
+      <c r="BW5" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24029,6 +24297,9 @@
       <c r="BV6" t="n">
         <v>0</v>
       </c>
+      <c r="BW6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24257,6 +24528,9 @@
       <c r="BV7" t="n">
         <v>68</v>
       </c>
+      <c r="BW7" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24485,6 +24759,9 @@
       <c r="BV8" t="n">
         <v>34</v>
       </c>
+      <c r="BW8" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24713,6 +24990,9 @@
       <c r="BV9" t="n">
         <v>77</v>
       </c>
+      <c r="BW9" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24940,6 +25220,9 @@
       </c>
       <c r="BV10" t="n">
         <v>8</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -24953,7 +25236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH10"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24990,6 +25273,7 @@
     <col width="10" customWidth="1" min="32" max="32"/>
     <col width="10" customWidth="1" min="33" max="33"/>
     <col width="10" customWidth="1" min="34" max="34"/>
+    <col width="10" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25099,6 +25383,9 @@
       <c r="AH1" s="1" t="n">
         <v>20260108</v>
       </c>
+      <c r="AI1" s="1" t="n">
+        <v>20260109</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25207,6 +25494,9 @@
       <c r="AH2" t="n">
         <v>30</v>
       </c>
+      <c r="AI2" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25315,6 +25605,9 @@
       <c r="AH3" t="n">
         <v>81</v>
       </c>
+      <c r="AI3" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -25423,6 +25716,9 @@
       <c r="AH4" t="n">
         <v>100</v>
       </c>
+      <c r="AI4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -25531,6 +25827,9 @@
       <c r="AH5" t="n">
         <v>9</v>
       </c>
+      <c r="AI5" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -25639,6 +25938,9 @@
       <c r="AH6" t="n">
         <v>0</v>
       </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -25747,6 +26049,9 @@
       <c r="AH7" t="n">
         <v>39</v>
       </c>
+      <c r="AI7" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25855,6 +26160,9 @@
       <c r="AH8" t="n">
         <v>42</v>
       </c>
+      <c r="AI8" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25963,6 +26271,9 @@
       <c r="AH9" t="n">
         <v>87</v>
       </c>
+      <c r="AI9" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26070,6 +26381,9 @@
       </c>
       <c r="AH10" t="n">
         <v>45</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -26083,7 +26397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV10"/>
+  <dimension ref="A1:BW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -26160,6 +26474,7 @@
     <col width="10" customWidth="1" min="72" max="72"/>
     <col width="10" customWidth="1" min="73" max="73"/>
     <col width="10" customWidth="1" min="74" max="74"/>
+    <col width="10" customWidth="1" min="75" max="75"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26389,6 +26704,9 @@
       <c r="BV1" s="1" t="n">
         <v>20260108</v>
       </c>
+      <c r="BW1" s="1" t="n">
+        <v>20260109</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -26617,6 +26935,9 @@
       <c r="BV2" t="n">
         <v>-118</v>
       </c>
+      <c r="BW2" t="n">
+        <v>-99</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -26845,6 +27166,9 @@
       <c r="BV3" t="n">
         <v>122</v>
       </c>
+      <c r="BW3" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -27073,6 +27397,9 @@
       <c r="BV4" t="n">
         <v>100</v>
       </c>
+      <c r="BW4" t="n">
+        <v>109</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -27301,6 +27628,9 @@
       <c r="BV5" t="n">
         <v>-33</v>
       </c>
+      <c r="BW5" t="n">
+        <v>-22</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -27529,6 +27859,9 @@
       <c r="BV6" t="n">
         <v>-88</v>
       </c>
+      <c r="BW6" t="n">
+        <v>-103</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -27757,6 +28090,9 @@
       <c r="BV7" t="n">
         <v>10</v>
       </c>
+      <c r="BW7" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -27985,6 +28321,9 @@
       <c r="BV8" t="n">
         <v>-50</v>
       </c>
+      <c r="BW8" t="n">
+        <v>-41</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -28213,6 +28552,9 @@
       <c r="BV9" t="n">
         <v>69</v>
       </c>
+      <c r="BW9" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28440,6 +28782,9 @@
       </c>
       <c r="BV10" t="n">
         <v>-65</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>-40</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI10"/>
+  <dimension ref="A1:AJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -639,6 +639,7 @@
     <col width="10" customWidth="1" min="33" max="33"/>
     <col width="10" customWidth="1" min="34" max="34"/>
     <col width="10" customWidth="1" min="35" max="35"/>
+    <col width="10" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -751,6 +752,9 @@
       <c r="AI1" s="1" t="n">
         <v>20260109</v>
       </c>
+      <c r="AJ1" s="1" t="n">
+        <v>20260112</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -862,6 +866,9 @@
       <c r="AI2" t="n">
         <v>-71</v>
       </c>
+      <c r="AJ2" t="n">
+        <v>-70</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -973,6 +980,9 @@
       <c r="AI3" t="n">
         <v>83</v>
       </c>
+      <c r="AJ3" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1084,6 +1094,9 @@
       <c r="AI4" t="n">
         <v>70</v>
       </c>
+      <c r="AJ4" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1195,6 +1208,9 @@
       <c r="AI5" t="n">
         <v>-45</v>
       </c>
+      <c r="AJ5" t="n">
+        <v>-49</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1306,6 +1322,9 @@
       <c r="AI6" t="n">
         <v>-40</v>
       </c>
+      <c r="AJ6" t="n">
+        <v>-39</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1417,6 +1436,9 @@
       <c r="AI7" t="n">
         <v>-9</v>
       </c>
+      <c r="AJ7" t="n">
+        <v>-9</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1528,6 +1550,9 @@
       <c r="AI8" t="n">
         <v>-15</v>
       </c>
+      <c r="AJ8" t="n">
+        <v>-6</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1639,6 +1664,9 @@
       <c r="AI9" t="n">
         <v>99</v>
       </c>
+      <c r="AJ9" t="n">
+        <v>119</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1749,6 +1777,9 @@
       </c>
       <c r="AI10" t="n">
         <v>2</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1762,7 +1793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW10"/>
+  <dimension ref="A1:BX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1840,6 +1871,7 @@
     <col width="12" customWidth="1" min="73" max="73"/>
     <col width="12" customWidth="1" min="74" max="74"/>
     <col width="12" customWidth="1" min="75" max="75"/>
+    <col width="12" customWidth="1" min="76" max="76"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2218,6 +2250,11 @@
           <t>20260109</t>
         </is>
       </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>20260112</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2449,6 +2486,9 @@
       <c r="BW2" t="n">
         <v>96</v>
       </c>
+      <c r="BX2" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2680,6 +2720,9 @@
       <c r="BW3" t="n">
         <v>107</v>
       </c>
+      <c r="BX3" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2911,6 +2954,9 @@
       <c r="BW4" t="n">
         <v>105</v>
       </c>
+      <c r="BX4" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3142,6 +3188,9 @@
       <c r="BW5" t="n">
         <v>100</v>
       </c>
+      <c r="BX5" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3373,6 +3422,9 @@
       <c r="BW6" t="n">
         <v>96</v>
       </c>
+      <c r="BX6" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3604,6 +3656,9 @@
       <c r="BW7" t="n">
         <v>101</v>
       </c>
+      <c r="BX7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3835,6 +3890,9 @@
       <c r="BW8" t="n">
         <v>97</v>
       </c>
+      <c r="BX8" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4066,6 +4124,9 @@
       <c r="BW9" t="n">
         <v>103</v>
       </c>
+      <c r="BX9" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4296,6 +4357,9 @@
       </c>
       <c r="BW10" t="n">
         <v>96</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -6658,7 +6722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI10"/>
+  <dimension ref="A1:AJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6696,6 +6760,7 @@
     <col width="12" customWidth="1" min="33" max="33"/>
     <col width="12" customWidth="1" min="34" max="34"/>
     <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="12" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6874,6 +6939,11 @@
           <t>20260109</t>
         </is>
       </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>20260112</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6985,6 +7055,9 @@
       <c r="AI2" t="n">
         <v>44</v>
       </c>
+      <c r="AJ2" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7096,6 +7169,9 @@
       <c r="AI3" t="n">
         <v>39</v>
       </c>
+      <c r="AJ3" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7207,6 +7283,9 @@
       <c r="AI4" t="n">
         <v>37</v>
       </c>
+      <c r="AJ4" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7318,6 +7397,9 @@
       <c r="AI5" t="n">
         <v>40</v>
       </c>
+      <c r="AJ5" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7429,6 +7511,9 @@
       <c r="AI6" t="n">
         <v>100</v>
       </c>
+      <c r="AJ6" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7540,6 +7625,9 @@
       <c r="AI7" t="n">
         <v>36</v>
       </c>
+      <c r="AJ7" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7651,6 +7739,9 @@
       <c r="AI8" t="n">
         <v>34</v>
       </c>
+      <c r="AJ8" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7762,6 +7853,9 @@
       <c r="AI9" t="n">
         <v>40</v>
       </c>
+      <c r="AJ9" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7872,6 +7966,9 @@
       </c>
       <c r="AI10" t="n">
         <v>43</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -7885,7 +7982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CP10"/>
+  <dimension ref="A1:CQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7982,6 +8079,7 @@
     <col width="12" customWidth="1" min="92" max="92"/>
     <col width="12" customWidth="1" min="93" max="93"/>
     <col width="12" customWidth="1" min="94" max="94"/>
+    <col width="12" customWidth="1" min="95" max="95"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8271,6 +8369,9 @@
       <c r="CP1" s="1" t="n">
         <v>20260109</v>
       </c>
+      <c r="CQ1" s="1" t="n">
+        <v>20260112</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8559,6 +8660,9 @@
       <c r="CP2" t="n">
         <v>259.075</v>
       </c>
+      <c r="CQ2" t="n">
+        <v>259.16</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8847,6 +8951,9 @@
       <c r="CP3" t="n">
         <v>244.568</v>
       </c>
+      <c r="CQ3" t="n">
+        <v>246.73</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9135,6 +9242,9 @@
       <c r="CP4" t="n">
         <v>327.09</v>
       </c>
+      <c r="CQ4" t="n">
+        <v>325.8</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9423,6 +9533,9 @@
       <c r="CP5" t="n">
         <v>474.06</v>
       </c>
+      <c r="CQ5" t="n">
+        <v>476.67</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9711,6 +9824,9 @@
       <c r="CP6" t="n">
         <v>90.03</v>
       </c>
+      <c r="CQ6" t="n">
+        <v>89.69</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9999,6 +10115,9 @@
       <c r="CP7" t="n">
         <v>185.08</v>
       </c>
+      <c r="CQ7" t="n">
+        <v>183.22</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10287,6 +10406,9 @@
       <c r="CP8" t="n">
         <v>177.02</v>
       </c>
+      <c r="CQ8" t="n">
+        <v>177.685</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10575,6 +10697,9 @@
       <c r="CP9" t="n">
         <v>88.34999999999999</v>
       </c>
+      <c r="CQ9" t="n">
+        <v>88.40000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10862,6 +10987,9 @@
       </c>
       <c r="CP10" t="n">
         <v>435.945</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>441.225</v>
       </c>
     </row>
   </sheetData>
@@ -10875,7 +11003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CP10"/>
+  <dimension ref="A1:CQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10972,6 +11100,7 @@
     <col width="12" customWidth="1" min="92" max="92"/>
     <col width="12" customWidth="1" min="93" max="93"/>
     <col width="12" customWidth="1" min="94" max="94"/>
+    <col width="12" customWidth="1" min="95" max="95"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11261,6 +11390,9 @@
       <c r="CP1" s="1" t="n">
         <v>20260109</v>
       </c>
+      <c r="CQ1" s="1" t="n">
+        <v>20260112</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11549,6 +11681,9 @@
       <c r="CP2" t="n">
         <v>260.21</v>
       </c>
+      <c r="CQ2" t="n">
+        <v>261.3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11837,6 +11972,9 @@
       <c r="CP3" t="n">
         <v>247.86</v>
       </c>
+      <c r="CQ3" t="n">
+        <v>248.94</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12125,6 +12263,9 @@
       <c r="CP4" t="n">
         <v>330.83</v>
       </c>
+      <c r="CQ4" t="n">
+        <v>334.04</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12413,6 +12554,9 @@
       <c r="CP5" t="n">
         <v>479.82</v>
       </c>
+      <c r="CQ5" t="n">
+        <v>480.99</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12701,6 +12845,9 @@
       <c r="CP6" t="n">
         <v>90.05</v>
       </c>
+      <c r="CQ6" t="n">
+        <v>90.33499999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12989,6 +13136,9 @@
       <c r="CP7" t="n">
         <v>186.34</v>
       </c>
+      <c r="CQ7" t="n">
+        <v>187.12</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13277,6 +13427,9 @@
       <c r="CP8" t="n">
         <v>178.72</v>
       </c>
+      <c r="CQ8" t="n">
+        <v>182.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13565,6 +13718,9 @@
       <c r="CP9" t="n">
         <v>89.09999999999999</v>
       </c>
+      <c r="CQ9" t="n">
+        <v>90.23</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13852,6 +14008,9 @@
       </c>
       <c r="CP10" t="n">
         <v>449.05</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>454.3</v>
       </c>
     </row>
   </sheetData>
@@ -13865,7 +14024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CP10"/>
+  <dimension ref="A1:CQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13962,6 +14121,7 @@
     <col width="12" customWidth="1" min="92" max="92"/>
     <col width="12" customWidth="1" min="93" max="93"/>
     <col width="12" customWidth="1" min="94" max="94"/>
+    <col width="12" customWidth="1" min="95" max="95"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14251,6 +14411,9 @@
       <c r="CP1" s="1" t="n">
         <v>20260109</v>
       </c>
+      <c r="CQ1" s="1" t="n">
+        <v>20260112</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14539,6 +14702,9 @@
       <c r="CP2" t="n">
         <v>256.22</v>
       </c>
+      <c r="CQ2" t="n">
+        <v>256.8</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14827,6 +14993,9 @@
       <c r="CP3" t="n">
         <v>242.24</v>
       </c>
+      <c r="CQ3" t="n">
+        <v>245.96</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15115,6 +15284,9 @@
       <c r="CP4" t="n">
         <v>325.8</v>
       </c>
+      <c r="CQ4" t="n">
+        <v>325</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15403,6 +15575,9 @@
       <c r="CP5" t="n">
         <v>472.2001</v>
       </c>
+      <c r="CQ5" t="n">
+        <v>475.6803</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15691,6 +15866,9 @@
       <c r="CP6" t="n">
         <v>88.31999999999999</v>
       </c>
+      <c r="CQ6" t="n">
+        <v>89.33</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15979,6 +16157,9 @@
       <c r="CP7" t="n">
         <v>183.6701</v>
       </c>
+      <c r="CQ7" t="n">
+        <v>183.02</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16267,6 +16448,9 @@
       <c r="CP8" t="n">
         <v>174.75</v>
       </c>
+      <c r="CQ8" t="n">
+        <v>176.34</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16555,6 +16739,9 @@
       <c r="CP9" t="n">
         <v>86.79000000000001</v>
       </c>
+      <c r="CQ9" t="n">
+        <v>87.59999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16842,6 +17029,9 @@
       </c>
       <c r="CP10" t="n">
         <v>430.39</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>438</v>
       </c>
     </row>
   </sheetData>
@@ -16855,7 +17045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CP10"/>
+  <dimension ref="A1:CQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -16952,6 +17142,7 @@
     <col width="12" customWidth="1" min="92" max="92"/>
     <col width="12" customWidth="1" min="93" max="93"/>
     <col width="12" customWidth="1" min="94" max="94"/>
+    <col width="12" customWidth="1" min="95" max="95"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17241,6 +17432,9 @@
       <c r="CP1" s="1" t="n">
         <v>20260109</v>
       </c>
+      <c r="CQ1" s="1" t="n">
+        <v>20260112</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17529,6 +17723,9 @@
       <c r="CP2" t="n">
         <v>259.37</v>
       </c>
+      <c r="CQ2" t="n">
+        <v>260.25</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17817,6 +18014,9 @@
       <c r="CP3" t="n">
         <v>247.38</v>
       </c>
+      <c r="CQ3" t="n">
+        <v>246.47</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18105,6 +18305,9 @@
       <c r="CP4" t="n">
         <v>328.57</v>
       </c>
+      <c r="CQ4" t="n">
+        <v>331.86</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18393,6 +18596,9 @@
       <c r="CP5" t="n">
         <v>479.28</v>
       </c>
+      <c r="CQ5" t="n">
+        <v>477.18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18681,6 +18887,9 @@
       <c r="CP6" t="n">
         <v>89.45999999999999</v>
       </c>
+      <c r="CQ6" t="n">
+        <v>89.41</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18969,6 +19178,9 @@
       <c r="CP7" t="n">
         <v>184.86</v>
       </c>
+      <c r="CQ7" t="n">
+        <v>184.94</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19257,6 +19469,9 @@
       <c r="CP8" t="n">
         <v>177.49</v>
       </c>
+      <c r="CQ8" t="n">
+        <v>179.41</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19545,6 +19760,9 @@
       <c r="CP9" t="n">
         <v>88.88</v>
       </c>
+      <c r="CQ9" t="n">
+        <v>89.95999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -19832,6 +20050,9 @@
       </c>
       <c r="CP10" t="n">
         <v>445.01</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>448.96</v>
       </c>
     </row>
   </sheetData>
@@ -19845,7 +20066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CP10"/>
+  <dimension ref="A1:CQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -19942,6 +20163,7 @@
     <col width="12" customWidth="1" min="92" max="92"/>
     <col width="12" customWidth="1" min="93" max="93"/>
     <col width="12" customWidth="1" min="94" max="94"/>
+    <col width="12" customWidth="1" min="95" max="95"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20231,6 +20453,9 @@
       <c r="CP1" s="1" t="n">
         <v>20260109</v>
       </c>
+      <c r="CQ1" s="1" t="n">
+        <v>20260112</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20519,6 +20744,9 @@
       <c r="CP2" t="n">
         <v>39996967</v>
       </c>
+      <c r="CQ2" t="n">
+        <v>45263767</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20807,6 +21035,9 @@
       <c r="CP3" t="n">
         <v>34559961</v>
       </c>
+      <c r="CQ3" t="n">
+        <v>35867770</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -21095,6 +21326,9 @@
       <c r="CP4" t="n">
         <v>26214166</v>
       </c>
+      <c r="CQ4" t="n">
+        <v>33923928</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -21383,6 +21617,9 @@
       <c r="CP5" t="n">
         <v>18491036</v>
       </c>
+      <c r="CQ5" t="n">
+        <v>23519895</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21671,6 +21908,9 @@
       <c r="CP6" t="n">
         <v>55579523</v>
       </c>
+      <c r="CQ6" t="n">
+        <v>36290606</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21959,6 +22199,9 @@
       <c r="CP7" t="n">
         <v>131327534</v>
       </c>
+      <c r="CQ7" t="n">
+        <v>137968453</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22247,6 +22490,9 @@
       <c r="CP8" t="n">
         <v>31362890</v>
       </c>
+      <c r="CQ8" t="n">
+        <v>34954543</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22535,6 +22781,9 @@
       <c r="CP9" t="n">
         <v>7593162</v>
       </c>
+      <c r="CQ9" t="n">
+        <v>7289488</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22822,6 +23071,9 @@
       </c>
       <c r="CP10" t="n">
         <v>67331456</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>61649627</v>
       </c>
     </row>
   </sheetData>
@@ -22835,7 +23087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW10"/>
+  <dimension ref="A1:BX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22913,6 +23165,7 @@
     <col width="10" customWidth="1" min="73" max="73"/>
     <col width="10" customWidth="1" min="74" max="74"/>
     <col width="10" customWidth="1" min="75" max="75"/>
+    <col width="10" customWidth="1" min="76" max="76"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23145,6 +23398,9 @@
       <c r="BW1" s="1" t="n">
         <v>20260109</v>
       </c>
+      <c r="BX1" s="1" t="n">
+        <v>20260112</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23376,6 +23632,9 @@
       <c r="BW2" t="n">
         <v>2</v>
       </c>
+      <c r="BX2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23607,6 +23866,9 @@
       <c r="BW3" t="n">
         <v>100</v>
       </c>
+      <c r="BX3" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23838,6 +24100,9 @@
       <c r="BW4" t="n">
         <v>100</v>
       </c>
+      <c r="BX4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24069,6 +24334,9 @@
       <c r="BW5" t="n">
         <v>42</v>
       </c>
+      <c r="BX5" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24300,6 +24568,9 @@
       <c r="BW6" t="n">
         <v>0</v>
       </c>
+      <c r="BX6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24531,6 +24802,9 @@
       <c r="BW7" t="n">
         <v>67</v>
       </c>
+      <c r="BX7" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24762,6 +25036,9 @@
       <c r="BW8" t="n">
         <v>37</v>
       </c>
+      <c r="BX8" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24993,6 +25270,9 @@
       <c r="BW9" t="n">
         <v>90</v>
       </c>
+      <c r="BX9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25223,6 +25503,9 @@
       </c>
       <c r="BW10" t="n">
         <v>23</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -25236,7 +25519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI10"/>
+  <dimension ref="A1:AJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25274,6 +25557,7 @@
     <col width="10" customWidth="1" min="33" max="33"/>
     <col width="10" customWidth="1" min="34" max="34"/>
     <col width="10" customWidth="1" min="35" max="35"/>
+    <col width="10" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25386,6 +25670,9 @@
       <c r="AI1" s="1" t="n">
         <v>20260109</v>
       </c>
+      <c r="AJ1" s="1" t="n">
+        <v>20260112</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25497,6 +25784,9 @@
       <c r="AI2" t="n">
         <v>31</v>
       </c>
+      <c r="AJ2" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25608,6 +25898,9 @@
       <c r="AI3" t="n">
         <v>84</v>
       </c>
+      <c r="AJ3" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -25719,6 +26012,9 @@
       <c r="AI4" t="n">
         <v>100</v>
       </c>
+      <c r="AJ4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -25830,6 +26126,9 @@
       <c r="AI5" t="n">
         <v>10</v>
       </c>
+      <c r="AJ5" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -25941,6 +26240,9 @@
       <c r="AI6" t="n">
         <v>0</v>
       </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -26052,6 +26354,9 @@
       <c r="AI7" t="n">
         <v>39</v>
       </c>
+      <c r="AJ7" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -26163,6 +26468,9 @@
       <c r="AI8" t="n">
         <v>43</v>
       </c>
+      <c r="AJ8" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -26274,6 +26582,9 @@
       <c r="AI9" t="n">
         <v>94</v>
       </c>
+      <c r="AJ9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26384,6 +26695,9 @@
       </c>
       <c r="AI10" t="n">
         <v>55</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -26397,7 +26711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW10"/>
+  <dimension ref="A1:BX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -26475,6 +26789,7 @@
     <col width="10" customWidth="1" min="73" max="73"/>
     <col width="10" customWidth="1" min="74" max="74"/>
     <col width="10" customWidth="1" min="75" max="75"/>
+    <col width="10" customWidth="1" min="76" max="76"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26707,6 +27022,9 @@
       <c r="BW1" s="1" t="n">
         <v>20260109</v>
       </c>
+      <c r="BX1" s="1" t="n">
+        <v>20260112</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -26938,6 +27256,9 @@
       <c r="BW2" t="n">
         <v>-99</v>
       </c>
+      <c r="BX2" t="n">
+        <v>-81</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -27169,6 +27490,9 @@
       <c r="BW3" t="n">
         <v>107</v>
       </c>
+      <c r="BX3" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -27400,6 +27724,9 @@
       <c r="BW4" t="n">
         <v>109</v>
       </c>
+      <c r="BX4" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -27631,6 +27958,9 @@
       <c r="BW5" t="n">
         <v>-22</v>
       </c>
+      <c r="BX5" t="n">
+        <v>-39</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -27862,6 +28192,9 @@
       <c r="BW6" t="n">
         <v>-103</v>
       </c>
+      <c r="BX6" t="n">
+        <v>-90</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -28093,6 +28426,9 @@
       <c r="BW7" t="n">
         <v>8</v>
       </c>
+      <c r="BX7" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -28324,6 +28660,9 @@
       <c r="BW8" t="n">
         <v>-41</v>
       </c>
+      <c r="BX8" t="n">
+        <v>-25</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -28555,6 +28894,9 @@
       <c r="BW9" t="n">
         <v>78</v>
       </c>
+      <c r="BX9" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28785,6 +29127,9 @@
       </c>
       <c r="BW10" t="n">
         <v>-40</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>-31</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ10"/>
+  <dimension ref="A1:AK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -640,6 +640,7 @@
     <col width="10" customWidth="1" min="34" max="34"/>
     <col width="10" customWidth="1" min="35" max="35"/>
     <col width="10" customWidth="1" min="36" max="36"/>
+    <col width="10" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -755,6 +756,9 @@
       <c r="AJ1" s="1" t="n">
         <v>20260112</v>
       </c>
+      <c r="AK1" s="1" t="n">
+        <v>20260113</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -869,6 +873,9 @@
       <c r="AJ2" t="n">
         <v>-70</v>
       </c>
+      <c r="AK2" t="n">
+        <v>-71</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -983,6 +990,9 @@
       <c r="AJ3" t="n">
         <v>76</v>
       </c>
+      <c r="AK3" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1097,6 +1107,9 @@
       <c r="AJ4" t="n">
         <v>75</v>
       </c>
+      <c r="AK4" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1211,6 +1224,9 @@
       <c r="AJ5" t="n">
         <v>-49</v>
       </c>
+      <c r="AK5" t="n">
+        <v>-64</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1325,6 +1341,9 @@
       <c r="AJ6" t="n">
         <v>-39</v>
       </c>
+      <c r="AK6" t="n">
+        <v>-37</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1439,6 +1458,9 @@
       <c r="AJ7" t="n">
         <v>-9</v>
       </c>
+      <c r="AK7" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1553,6 +1575,9 @@
       <c r="AJ8" t="n">
         <v>-6</v>
       </c>
+      <c r="AK8" t="n">
+        <v>-8</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1667,6 +1692,9 @@
       <c r="AJ9" t="n">
         <v>119</v>
       </c>
+      <c r="AK9" t="n">
+        <v>124</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1780,6 +1808,9 @@
       </c>
       <c r="AJ10" t="n">
         <v>10</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1793,7 +1824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX10"/>
+  <dimension ref="A1:BY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1872,6 +1903,7 @@
     <col width="12" customWidth="1" min="74" max="74"/>
     <col width="12" customWidth="1" min="75" max="75"/>
     <col width="12" customWidth="1" min="76" max="76"/>
+    <col width="12" customWidth="1" min="77" max="77"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2255,6 +2287,11 @@
           <t>20260112</t>
         </is>
       </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>20260113</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2489,6 +2526,9 @@
       <c r="BX2" t="n">
         <v>96</v>
       </c>
+      <c r="BY2" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2723,6 +2763,9 @@
       <c r="BX3" t="n">
         <v>106</v>
       </c>
+      <c r="BY3" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2957,6 +3000,9 @@
       <c r="BX4" t="n">
         <v>106</v>
       </c>
+      <c r="BY4" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3191,6 +3237,9 @@
       <c r="BX5" t="n">
         <v>99</v>
       </c>
+      <c r="BY5" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3425,6 +3474,9 @@
       <c r="BX6" t="n">
         <v>96</v>
       </c>
+      <c r="BY6" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3659,6 +3711,9 @@
       <c r="BX7" t="n">
         <v>100</v>
       </c>
+      <c r="BY7" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3893,6 +3948,9 @@
       <c r="BX8" t="n">
         <v>98</v>
       </c>
+      <c r="BY8" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4127,6 +4185,9 @@
       <c r="BX9" t="n">
         <v>104</v>
       </c>
+      <c r="BY9" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4359,6 +4420,9 @@
         <v>96</v>
       </c>
       <c r="BX10" t="n">
+        <v>97</v>
+      </c>
+      <c r="BY10" t="n">
         <v>97</v>
       </c>
     </row>
@@ -6722,7 +6786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ10"/>
+  <dimension ref="A1:AK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6761,6 +6825,7 @@
     <col width="12" customWidth="1" min="34" max="34"/>
     <col width="12" customWidth="1" min="35" max="35"/>
     <col width="12" customWidth="1" min="36" max="36"/>
+    <col width="12" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6944,6 +7009,11 @@
           <t>20260112</t>
         </is>
       </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>20260113</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7058,6 +7128,9 @@
       <c r="AJ2" t="n">
         <v>50</v>
       </c>
+      <c r="AK2" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7172,6 +7245,9 @@
       <c r="AJ3" t="n">
         <v>41</v>
       </c>
+      <c r="AK3" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7286,6 +7362,9 @@
       <c r="AJ4" t="n">
         <v>47</v>
       </c>
+      <c r="AK4" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7400,6 +7479,9 @@
       <c r="AJ5" t="n">
         <v>51</v>
       </c>
+      <c r="AK5" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7514,6 +7596,9 @@
       <c r="AJ6" t="n">
         <v>64</v>
       </c>
+      <c r="AK6" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7628,6 +7713,9 @@
       <c r="AJ7" t="n">
         <v>38</v>
       </c>
+      <c r="AK7" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7742,6 +7830,9 @@
       <c r="AJ8" t="n">
         <v>38</v>
       </c>
+      <c r="AK8" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7856,6 +7947,9 @@
       <c r="AJ9" t="n">
         <v>39</v>
       </c>
+      <c r="AK9" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7969,6 +8063,9 @@
       </c>
       <c r="AJ10" t="n">
         <v>40</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -7982,7 +8079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CQ10"/>
+  <dimension ref="A1:CR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8080,6 +8177,7 @@
     <col width="12" customWidth="1" min="93" max="93"/>
     <col width="12" customWidth="1" min="94" max="94"/>
     <col width="12" customWidth="1" min="95" max="95"/>
+    <col width="12" customWidth="1" min="96" max="96"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8372,6 +8470,9 @@
       <c r="CQ1" s="1" t="n">
         <v>20260112</v>
       </c>
+      <c r="CR1" s="1" t="n">
+        <v>20260113</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8663,6 +8764,9 @@
       <c r="CQ2" t="n">
         <v>259.16</v>
       </c>
+      <c r="CR2" t="n">
+        <v>258.72</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8954,6 +9058,9 @@
       <c r="CQ3" t="n">
         <v>246.73</v>
       </c>
+      <c r="CR3" t="n">
+        <v>246.53</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9245,6 +9352,9 @@
       <c r="CQ4" t="n">
         <v>325.8</v>
       </c>
+      <c r="CR4" t="n">
+        <v>334.95</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9536,6 +9646,9 @@
       <c r="CQ5" t="n">
         <v>476.67</v>
       </c>
+      <c r="CR5" t="n">
+        <v>474.675</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9827,6 +9940,9 @@
       <c r="CQ6" t="n">
         <v>89.69</v>
       </c>
+      <c r="CR6" t="n">
+        <v>89.44</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10118,6 +10234,9 @@
       <c r="CQ7" t="n">
         <v>183.22</v>
       </c>
+      <c r="CR7" t="n">
+        <v>184.995</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10409,6 +10528,9 @@
       <c r="CQ8" t="n">
         <v>177.685</v>
       </c>
+      <c r="CR8" t="n">
+        <v>178.875</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10700,6 +10822,9 @@
       <c r="CQ9" t="n">
         <v>88.40000000000001</v>
       </c>
+      <c r="CR9" t="n">
+        <v>89.69</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10990,6 +11115,9 @@
       </c>
       <c r="CQ10" t="n">
         <v>441.225</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>450.2</v>
       </c>
     </row>
   </sheetData>
@@ -11003,7 +11131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CQ10"/>
+  <dimension ref="A1:CR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11101,6 +11229,7 @@
     <col width="12" customWidth="1" min="93" max="93"/>
     <col width="12" customWidth="1" min="94" max="94"/>
     <col width="12" customWidth="1" min="95" max="95"/>
+    <col width="12" customWidth="1" min="96" max="96"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11393,6 +11522,9 @@
       <c r="CQ1" s="1" t="n">
         <v>20260112</v>
       </c>
+      <c r="CR1" s="1" t="n">
+        <v>20260113</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11684,6 +11816,9 @@
       <c r="CQ2" t="n">
         <v>261.3</v>
       </c>
+      <c r="CR2" t="n">
+        <v>261.81</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11975,6 +12110,9 @@
       <c r="CQ3" t="n">
         <v>248.94</v>
       </c>
+      <c r="CR3" t="n">
+        <v>247.66</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12266,6 +12404,9 @@
       <c r="CQ4" t="n">
         <v>334.04</v>
       </c>
+      <c r="CR4" t="n">
+        <v>340.49</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12557,6 +12698,9 @@
       <c r="CQ5" t="n">
         <v>480.99</v>
       </c>
+      <c r="CR5" t="n">
+        <v>475.7799</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12848,6 +12992,9 @@
       <c r="CQ6" t="n">
         <v>90.33499999999999</v>
       </c>
+      <c r="CR6" t="n">
+        <v>91.15000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13139,6 +13286,9 @@
       <c r="CQ7" t="n">
         <v>187.12</v>
       </c>
+      <c r="CR7" t="n">
+        <v>188.1099</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13430,6 +13580,9 @@
       <c r="CQ8" t="n">
         <v>182.5</v>
       </c>
+      <c r="CR8" t="n">
+        <v>181.1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13721,6 +13874,9 @@
       <c r="CQ9" t="n">
         <v>90.23</v>
       </c>
+      <c r="CR9" t="n">
+        <v>90.59999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14011,6 +14167,9 @@
       </c>
       <c r="CQ10" t="n">
         <v>454.3</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>451.81</v>
       </c>
     </row>
   </sheetData>
@@ -14024,7 +14183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CQ10"/>
+  <dimension ref="A1:CR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14122,6 +14281,7 @@
     <col width="12" customWidth="1" min="93" max="93"/>
     <col width="12" customWidth="1" min="94" max="94"/>
     <col width="12" customWidth="1" min="95" max="95"/>
+    <col width="12" customWidth="1" min="96" max="96"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14414,6 +14574,9 @@
       <c r="CQ1" s="1" t="n">
         <v>20260112</v>
       </c>
+      <c r="CR1" s="1" t="n">
+        <v>20260113</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14705,6 +14868,9 @@
       <c r="CQ2" t="n">
         <v>256.8</v>
       </c>
+      <c r="CR2" t="n">
+        <v>258.39</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14996,6 +15162,9 @@
       <c r="CQ3" t="n">
         <v>245.96</v>
       </c>
+      <c r="CR3" t="n">
+        <v>240.25</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15287,6 +15456,9 @@
       <c r="CQ4" t="n">
         <v>325</v>
       </c>
+      <c r="CR4" t="n">
+        <v>333.62</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15578,6 +15750,9 @@
       <c r="CQ5" t="n">
         <v>475.6803</v>
       </c>
+      <c r="CR5" t="n">
+        <v>465.95</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15869,6 +16044,9 @@
       <c r="CQ6" t="n">
         <v>89.33</v>
       </c>
+      <c r="CR6" t="n">
+        <v>89.06999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16160,6 +16338,9 @@
       <c r="CQ7" t="n">
         <v>183.02</v>
       </c>
+      <c r="CR7" t="n">
+        <v>183.4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16451,6 +16632,9 @@
       <c r="CQ8" t="n">
         <v>176.34</v>
       </c>
+      <c r="CR8" t="n">
+        <v>176.14</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16742,6 +16926,9 @@
       <c r="CQ9" t="n">
         <v>87.59999999999999</v>
       </c>
+      <c r="CR9" t="n">
+        <v>89.4706</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17032,6 +17219,9 @@
       </c>
       <c r="CQ10" t="n">
         <v>438</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>443.95</v>
       </c>
     </row>
   </sheetData>
@@ -17045,7 +17235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CQ10"/>
+  <dimension ref="A1:CR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17143,6 +17333,7 @@
     <col width="12" customWidth="1" min="93" max="93"/>
     <col width="12" customWidth="1" min="94" max="94"/>
     <col width="12" customWidth="1" min="95" max="95"/>
+    <col width="12" customWidth="1" min="96" max="96"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17435,6 +17626,9 @@
       <c r="CQ1" s="1" t="n">
         <v>20260112</v>
       </c>
+      <c r="CR1" s="1" t="n">
+        <v>20260113</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17726,6 +17920,9 @@
       <c r="CQ2" t="n">
         <v>260.25</v>
       </c>
+      <c r="CR2" t="n">
+        <v>261.05</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18017,6 +18214,9 @@
       <c r="CQ3" t="n">
         <v>246.47</v>
       </c>
+      <c r="CR3" t="n">
+        <v>242.6</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18308,6 +18508,9 @@
       <c r="CQ4" t="n">
         <v>331.86</v>
       </c>
+      <c r="CR4" t="n">
+        <v>335.97</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18599,6 +18802,9 @@
       <c r="CQ5" t="n">
         <v>477.18</v>
       </c>
+      <c r="CR5" t="n">
+        <v>470.67</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18890,6 +19096,9 @@
       <c r="CQ6" t="n">
         <v>89.41</v>
       </c>
+      <c r="CR6" t="n">
+        <v>90.31999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19181,6 +19390,9 @@
       <c r="CQ7" t="n">
         <v>184.94</v>
       </c>
+      <c r="CR7" t="n">
+        <v>185.81</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19472,6 +19684,9 @@
       <c r="CQ8" t="n">
         <v>179.41</v>
       </c>
+      <c r="CR8" t="n">
+        <v>178.96</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19763,6 +19978,9 @@
       <c r="CQ9" t="n">
         <v>89.95999999999999</v>
       </c>
+      <c r="CR9" t="n">
+        <v>90.56</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20053,6 +20271,9 @@
       </c>
       <c r="CQ10" t="n">
         <v>448.96</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>447.2</v>
       </c>
     </row>
   </sheetData>
@@ -20066,7 +20287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CQ10"/>
+  <dimension ref="A1:CR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20164,6 +20385,7 @@
     <col width="12" customWidth="1" min="93" max="93"/>
     <col width="12" customWidth="1" min="94" max="94"/>
     <col width="12" customWidth="1" min="95" max="95"/>
+    <col width="12" customWidth="1" min="96" max="96"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20456,6 +20678,9 @@
       <c r="CQ1" s="1" t="n">
         <v>20260112</v>
       </c>
+      <c r="CR1" s="1" t="n">
+        <v>20260113</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20747,6 +20972,9 @@
       <c r="CQ2" t="n">
         <v>45263767</v>
       </c>
+      <c r="CR2" t="n">
+        <v>45730847</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21038,6 +21266,9 @@
       <c r="CQ3" t="n">
         <v>35867770</v>
       </c>
+      <c r="CR3" t="n">
+        <v>38371778</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -21329,6 +21560,9 @@
       <c r="CQ4" t="n">
         <v>33923928</v>
       </c>
+      <c r="CR4" t="n">
+        <v>33517607</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -21620,6 +21854,9 @@
       <c r="CQ5" t="n">
         <v>23519895</v>
       </c>
+      <c r="CR5" t="n">
+        <v>28545800</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21911,6 +22148,9 @@
       <c r="CQ6" t="n">
         <v>36290606</v>
       </c>
+      <c r="CR6" t="n">
+        <v>45221097</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -22202,6 +22442,9 @@
       <c r="CQ7" t="n">
         <v>137968453</v>
       </c>
+      <c r="CR7" t="n">
+        <v>160128939</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22493,6 +22736,9 @@
       <c r="CQ8" t="n">
         <v>34954543</v>
       </c>
+      <c r="CR8" t="n">
+        <v>27769354</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22784,6 +23030,9 @@
       <c r="CQ9" t="n">
         <v>7289488</v>
       </c>
+      <c r="CR9" t="n">
+        <v>5561860</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23074,6 +23323,9 @@
       </c>
       <c r="CQ10" t="n">
         <v>61649627</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>53719214</v>
       </c>
     </row>
   </sheetData>
@@ -23087,7 +23339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX10"/>
+  <dimension ref="A1:BY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23166,6 +23418,7 @@
     <col width="10" customWidth="1" min="74" max="74"/>
     <col width="10" customWidth="1" min="75" max="75"/>
     <col width="10" customWidth="1" min="76" max="76"/>
+    <col width="10" customWidth="1" min="77" max="77"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23401,6 +23654,9 @@
       <c r="BX1" s="1" t="n">
         <v>20260112</v>
       </c>
+      <c r="BY1" s="1" t="n">
+        <v>20260113</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23635,6 +23891,9 @@
       <c r="BX2" t="n">
         <v>6</v>
       </c>
+      <c r="BY2" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23869,6 +24128,9 @@
       <c r="BX3" t="n">
         <v>97</v>
       </c>
+      <c r="BY3" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -24103,6 +24365,9 @@
       <c r="BX4" t="n">
         <v>100</v>
       </c>
+      <c r="BY4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24337,6 +24602,9 @@
       <c r="BX5" t="n">
         <v>28</v>
       </c>
+      <c r="BY5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24571,6 +24839,9 @@
       <c r="BX6" t="n">
         <v>0</v>
       </c>
+      <c r="BY6" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24805,6 +25076,9 @@
       <c r="BX7" t="n">
         <v>68</v>
       </c>
+      <c r="BY7" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25039,6 +25313,9 @@
       <c r="BX8" t="n">
         <v>44</v>
       </c>
+      <c r="BY8" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25273,6 +25550,9 @@
       <c r="BX9" t="n">
         <v>100</v>
       </c>
+      <c r="BY9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25506,6 +25786,9 @@
       </c>
       <c r="BX10" t="n">
         <v>30</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -25519,7 +25802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ10"/>
+  <dimension ref="A1:AK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25558,6 +25841,7 @@
     <col width="10" customWidth="1" min="34" max="34"/>
     <col width="10" customWidth="1" min="35" max="35"/>
     <col width="10" customWidth="1" min="36" max="36"/>
+    <col width="10" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25673,6 +25957,9 @@
       <c r="AJ1" s="1" t="n">
         <v>20260112</v>
       </c>
+      <c r="AK1" s="1" t="n">
+        <v>20260113</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25787,6 +26074,9 @@
       <c r="AJ2" t="n">
         <v>33</v>
       </c>
+      <c r="AK2" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25901,6 +26191,9 @@
       <c r="AJ3" t="n">
         <v>82</v>
       </c>
+      <c r="AK3" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -26015,6 +26308,9 @@
       <c r="AJ4" t="n">
         <v>100</v>
       </c>
+      <c r="AK4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -26129,6 +26425,9 @@
       <c r="AJ5" t="n">
         <v>7</v>
       </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -26243,6 +26542,9 @@
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -26357,6 +26659,9 @@
       <c r="AJ7" t="n">
         <v>39</v>
       </c>
+      <c r="AK7" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -26471,6 +26776,9 @@
       <c r="AJ8" t="n">
         <v>47</v>
       </c>
+      <c r="AK8" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -26585,6 +26893,9 @@
       <c r="AJ9" t="n">
         <v>100</v>
       </c>
+      <c r="AK9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26698,6 +27009,9 @@
       </c>
       <c r="AJ10" t="n">
         <v>59</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -26711,7 +27025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX10"/>
+  <dimension ref="A1:BY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -26790,6 +27104,7 @@
     <col width="10" customWidth="1" min="74" max="74"/>
     <col width="10" customWidth="1" min="75" max="75"/>
     <col width="10" customWidth="1" min="76" max="76"/>
+    <col width="10" customWidth="1" min="77" max="77"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27025,6 +27340,9 @@
       <c r="BX1" s="1" t="n">
         <v>20260112</v>
       </c>
+      <c r="BY1" s="1" t="n">
+        <v>20260113</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -27259,6 +27577,9 @@
       <c r="BX2" t="n">
         <v>-81</v>
       </c>
+      <c r="BY2" t="n">
+        <v>-67</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -27493,6 +27814,9 @@
       <c r="BX3" t="n">
         <v>87</v>
       </c>
+      <c r="BY3" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -27727,6 +28051,9 @@
       <c r="BX4" t="n">
         <v>108</v>
       </c>
+      <c r="BY4" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -27961,6 +28288,9 @@
       <c r="BX5" t="n">
         <v>-39</v>
       </c>
+      <c r="BY5" t="n">
+        <v>-90</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -28195,6 +28525,9 @@
       <c r="BX6" t="n">
         <v>-90</v>
       </c>
+      <c r="BY6" t="n">
+        <v>-59</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -28429,6 +28762,9 @@
       <c r="BX7" t="n">
         <v>7</v>
       </c>
+      <c r="BY7" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -28663,6 +28999,9 @@
       <c r="BX8" t="n">
         <v>-25</v>
       </c>
+      <c r="BY8" t="n">
+        <v>-27</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -28897,6 +29236,9 @@
       <c r="BX9" t="n">
         <v>91</v>
       </c>
+      <c r="BY9" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -29130,6 +29472,9 @@
       </c>
       <c r="BX10" t="n">
         <v>-31</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>-34</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK10"/>
+  <dimension ref="A1:AL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -641,6 +641,7 @@
     <col width="10" customWidth="1" min="35" max="35"/>
     <col width="10" customWidth="1" min="36" max="36"/>
     <col width="10" customWidth="1" min="37" max="37"/>
+    <col width="10" customWidth="1" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -759,6 +760,9 @@
       <c r="AK1" s="1" t="n">
         <v>20260113</v>
       </c>
+      <c r="AL1" s="1" t="n">
+        <v>20260114</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -876,6 +880,9 @@
       <c r="AK2" t="n">
         <v>-71</v>
       </c>
+      <c r="AL2" t="n">
+        <v>-83</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -993,6 +1000,9 @@
       <c r="AK3" t="n">
         <v>55</v>
       </c>
+      <c r="AL3" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1110,6 +1120,9 @@
       <c r="AK4" t="n">
         <v>82</v>
       </c>
+      <c r="AL4" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1227,6 +1240,9 @@
       <c r="AK5" t="n">
         <v>-64</v>
       </c>
+      <c r="AL5" t="n">
+        <v>-90</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1344,6 +1360,9 @@
       <c r="AK6" t="n">
         <v>-37</v>
       </c>
+      <c r="AL6" t="n">
+        <v>-36</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1461,6 +1480,9 @@
       <c r="AK7" t="n">
         <v>-3</v>
       </c>
+      <c r="AL7" t="n">
+        <v>-21</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1578,6 +1600,9 @@
       <c r="AK8" t="n">
         <v>-8</v>
       </c>
+      <c r="AL8" t="n">
+        <v>-10</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1695,6 +1720,9 @@
       <c r="AK9" t="n">
         <v>124</v>
       </c>
+      <c r="AL9" t="n">
+        <v>128</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1811,6 +1839,9 @@
       </c>
       <c r="AK10" t="n">
         <v>6</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-11</v>
       </c>
     </row>
   </sheetData>
@@ -1824,7 +1855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY10"/>
+  <dimension ref="A1:BZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1904,6 +1935,7 @@
     <col width="12" customWidth="1" min="75" max="75"/>
     <col width="12" customWidth="1" min="76" max="76"/>
     <col width="12" customWidth="1" min="77" max="77"/>
+    <col width="12" customWidth="1" min="78" max="78"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2292,6 +2324,11 @@
           <t>20260113</t>
         </is>
       </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>20260114</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2529,6 +2566,9 @@
       <c r="BY2" t="n">
         <v>97</v>
       </c>
+      <c r="BZ2" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2766,6 +2806,9 @@
       <c r="BY3" t="n">
         <v>104</v>
       </c>
+      <c r="BZ3" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3003,6 +3046,9 @@
       <c r="BY4" t="n">
         <v>107</v>
       </c>
+      <c r="BZ4" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3240,6 +3286,9 @@
       <c r="BY5" t="n">
         <v>98</v>
       </c>
+      <c r="BZ5" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3477,6 +3526,9 @@
       <c r="BY6" t="n">
         <v>98</v>
       </c>
+      <c r="BZ6" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3714,6 +3766,9 @@
       <c r="BY7" t="n">
         <v>101</v>
       </c>
+      <c r="BZ7" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3951,6 +4006,9 @@
       <c r="BY8" t="n">
         <v>98</v>
       </c>
+      <c r="BZ8" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4188,6 +4246,9 @@
       <c r="BY9" t="n">
         <v>105</v>
       </c>
+      <c r="BZ9" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4424,6 +4485,9 @@
       </c>
       <c r="BY10" t="n">
         <v>97</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -6786,7 +6850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK10"/>
+  <dimension ref="A1:AL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6826,6 +6890,7 @@
     <col width="12" customWidth="1" min="35" max="35"/>
     <col width="12" customWidth="1" min="36" max="36"/>
     <col width="12" customWidth="1" min="37" max="37"/>
+    <col width="12" customWidth="1" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7014,6 +7079,11 @@
           <t>20260113</t>
         </is>
       </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>20260114</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7131,6 +7201,9 @@
       <c r="AK2" t="n">
         <v>50</v>
       </c>
+      <c r="AL2" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7248,6 +7321,9 @@
       <c r="AK3" t="n">
         <v>44</v>
       </c>
+      <c r="AL3" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7365,6 +7441,9 @@
       <c r="AK4" t="n">
         <v>46</v>
       </c>
+      <c r="AL4" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7482,6 +7561,9 @@
       <c r="AK5" t="n">
         <v>61</v>
       </c>
+      <c r="AL5" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7599,6 +7681,9 @@
       <c r="AK6" t="n">
         <v>78</v>
       </c>
+      <c r="AL6" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7716,6 +7801,9 @@
       <c r="AK7" t="n">
         <v>44</v>
       </c>
+      <c r="AL7" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7833,6 +7921,9 @@
       <c r="AK8" t="n">
         <v>31</v>
       </c>
+      <c r="AL8" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7950,6 +8041,9 @@
       <c r="AK9" t="n">
         <v>30</v>
       </c>
+      <c r="AL9" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8066,6 +8160,9 @@
       </c>
       <c r="AK10" t="n">
         <v>35</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -8079,7 +8176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR10"/>
+  <dimension ref="A1:CS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8178,6 +8275,7 @@
     <col width="12" customWidth="1" min="94" max="94"/>
     <col width="12" customWidth="1" min="95" max="95"/>
     <col width="12" customWidth="1" min="96" max="96"/>
+    <col width="12" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8473,6 +8571,9 @@
       <c r="CR1" s="1" t="n">
         <v>20260113</v>
       </c>
+      <c r="CS1" s="1" t="n">
+        <v>20260114</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8767,6 +8868,9 @@
       <c r="CR2" t="n">
         <v>258.72</v>
       </c>
+      <c r="CS2" t="n">
+        <v>259.49</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9061,6 +9165,9 @@
       <c r="CR3" t="n">
         <v>246.53</v>
       </c>
+      <c r="CS3" t="n">
+        <v>241.15</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9355,6 +9462,9 @@
       <c r="CR4" t="n">
         <v>334.95</v>
       </c>
+      <c r="CS4" t="n">
+        <v>335.06</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9649,6 +9759,9 @@
       <c r="CR5" t="n">
         <v>474.675</v>
       </c>
+      <c r="CS5" t="n">
+        <v>466.46</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9943,6 +10056,9 @@
       <c r="CR6" t="n">
         <v>89.44</v>
       </c>
+      <c r="CS6" t="n">
+        <v>91.23999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10237,6 +10353,9 @@
       <c r="CR7" t="n">
         <v>184.995</v>
       </c>
+      <c r="CS7" t="n">
+        <v>184.32</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10531,6 +10650,9 @@
       <c r="CR8" t="n">
         <v>178.875</v>
       </c>
+      <c r="CS8" t="n">
+        <v>178.125</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10825,6 +10947,9 @@
       <c r="CR9" t="n">
         <v>89.69</v>
       </c>
+      <c r="CS9" t="n">
+        <v>90.26000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11118,6 +11243,9 @@
       </c>
       <c r="CR10" t="n">
         <v>450.2</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>442.81</v>
       </c>
     </row>
   </sheetData>
@@ -11131,7 +11259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR10"/>
+  <dimension ref="A1:CS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11230,6 +11358,7 @@
     <col width="12" customWidth="1" min="94" max="94"/>
     <col width="12" customWidth="1" min="95" max="95"/>
     <col width="12" customWidth="1" min="96" max="96"/>
+    <col width="12" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11525,6 +11654,9 @@
       <c r="CR1" s="1" t="n">
         <v>20260113</v>
       </c>
+      <c r="CS1" s="1" t="n">
+        <v>20260114</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11819,6 +11951,9 @@
       <c r="CR2" t="n">
         <v>261.81</v>
       </c>
+      <c r="CS2" t="n">
+        <v>261.82</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12113,6 +12248,9 @@
       <c r="CR3" t="n">
         <v>247.66</v>
       </c>
+      <c r="CS3" t="n">
+        <v>241.28</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12407,6 +12545,9 @@
       <c r="CR4" t="n">
         <v>340.49</v>
       </c>
+      <c r="CS4" t="n">
+        <v>336.52</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12701,6 +12842,9 @@
       <c r="CR5" t="n">
         <v>475.7799</v>
       </c>
+      <c r="CS5" t="n">
+        <v>468.2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12995,6 +13139,9 @@
       <c r="CR6" t="n">
         <v>91.15000000000001</v>
       </c>
+      <c r="CS6" t="n">
+        <v>91.58</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13289,6 +13436,9 @@
       <c r="CR7" t="n">
         <v>188.1099</v>
       </c>
+      <c r="CS7" t="n">
+        <v>184.46</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13583,6 +13733,9 @@
       <c r="CR8" t="n">
         <v>181.1</v>
       </c>
+      <c r="CS8" t="n">
+        <v>181.5975</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13877,6 +14030,9 @@
       <c r="CR9" t="n">
         <v>90.59999999999999</v>
       </c>
+      <c r="CS9" t="n">
+        <v>91.52</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14170,6 +14326,9 @@
       </c>
       <c r="CR10" t="n">
         <v>451.81</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>443.91</v>
       </c>
     </row>
   </sheetData>
@@ -14183,7 +14342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR10"/>
+  <dimension ref="A1:CS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14282,6 +14441,7 @@
     <col width="12" customWidth="1" min="94" max="94"/>
     <col width="12" customWidth="1" min="95" max="95"/>
     <col width="12" customWidth="1" min="96" max="96"/>
+    <col width="12" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14577,6 +14737,9 @@
       <c r="CR1" s="1" t="n">
         <v>20260113</v>
       </c>
+      <c r="CS1" s="1" t="n">
+        <v>20260114</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14871,6 +15034,9 @@
       <c r="CR2" t="n">
         <v>258.39</v>
       </c>
+      <c r="CS2" t="n">
+        <v>256.71</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15165,6 +15331,9 @@
       <c r="CR3" t="n">
         <v>240.25</v>
       </c>
+      <c r="CS3" t="n">
+        <v>236.22</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15459,6 +15628,9 @@
       <c r="CR4" t="n">
         <v>333.62</v>
       </c>
+      <c r="CS4" t="n">
+        <v>330.48</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15753,6 +15925,9 @@
       <c r="CR5" t="n">
         <v>465.95</v>
       </c>
+      <c r="CS5" t="n">
+        <v>457.1701</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16047,6 +16222,9 @@
       <c r="CR6" t="n">
         <v>89.06999999999999</v>
       </c>
+      <c r="CS6" t="n">
+        <v>87.95</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16341,6 +16519,9 @@
       <c r="CR7" t="n">
         <v>183.4</v>
       </c>
+      <c r="CS7" t="n">
+        <v>180.8</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16635,6 +16816,9 @@
       <c r="CR8" t="n">
         <v>176.14</v>
       </c>
+      <c r="CS8" t="n">
+        <v>173.95</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16929,6 +17113,9 @@
       <c r="CR9" t="n">
         <v>89.4706</v>
       </c>
+      <c r="CS9" t="n">
+        <v>90.15000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17222,6 +17409,9 @@
       </c>
       <c r="CR10" t="n">
         <v>443.95</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>434.22</v>
       </c>
     </row>
   </sheetData>
@@ -17235,7 +17425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR10"/>
+  <dimension ref="A1:CS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17334,6 +17524,7 @@
     <col width="12" customWidth="1" min="94" max="94"/>
     <col width="12" customWidth="1" min="95" max="95"/>
     <col width="12" customWidth="1" min="96" max="96"/>
+    <col width="12" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17629,6 +17820,9 @@
       <c r="CR1" s="1" t="n">
         <v>20260113</v>
       </c>
+      <c r="CS1" s="1" t="n">
+        <v>20260114</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17923,6 +18117,9 @@
       <c r="CR2" t="n">
         <v>261.05</v>
       </c>
+      <c r="CS2" t="n">
+        <v>259.96</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18217,6 +18414,9 @@
       <c r="CR3" t="n">
         <v>242.6</v>
       </c>
+      <c r="CS3" t="n">
+        <v>236.65</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18511,6 +18711,9 @@
       <c r="CR4" t="n">
         <v>335.97</v>
       </c>
+      <c r="CS4" t="n">
+        <v>335.84</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18805,6 +19008,9 @@
       <c r="CR5" t="n">
         <v>470.67</v>
       </c>
+      <c r="CS5" t="n">
+        <v>459.38</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19099,6 +19305,9 @@
       <c r="CR6" t="n">
         <v>90.31999999999999</v>
       </c>
+      <c r="CS6" t="n">
+        <v>88.55</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19393,6 +19602,9 @@
       <c r="CR7" t="n">
         <v>185.81</v>
       </c>
+      <c r="CS7" t="n">
+        <v>183.14</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19687,6 +19899,9 @@
       <c r="CR8" t="n">
         <v>178.96</v>
       </c>
+      <c r="CS8" t="n">
+        <v>178.4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19981,6 +20196,9 @@
       <c r="CR9" t="n">
         <v>90.56</v>
       </c>
+      <c r="CS9" t="n">
+        <v>91.15000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20274,6 +20492,9 @@
       </c>
       <c r="CR10" t="n">
         <v>447.2</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>439.2</v>
       </c>
     </row>
   </sheetData>
@@ -20287,7 +20508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR10"/>
+  <dimension ref="A1:CS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20386,6 +20607,7 @@
     <col width="12" customWidth="1" min="94" max="94"/>
     <col width="12" customWidth="1" min="95" max="95"/>
     <col width="12" customWidth="1" min="96" max="96"/>
+    <col width="12" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20681,6 +20903,9 @@
       <c r="CR1" s="1" t="n">
         <v>20260113</v>
       </c>
+      <c r="CS1" s="1" t="n">
+        <v>20260114</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20975,6 +21200,9 @@
       <c r="CR2" t="n">
         <v>45730847</v>
       </c>
+      <c r="CS2" t="n">
+        <v>40019421</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21269,6 +21497,9 @@
       <c r="CR3" t="n">
         <v>38371778</v>
       </c>
+      <c r="CS3" t="n">
+        <v>41410578</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -21563,6 +21794,9 @@
       <c r="CR4" t="n">
         <v>33517607</v>
       </c>
+      <c r="CS4" t="n">
+        <v>28525571</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -21857,6 +22091,9 @@
       <c r="CR5" t="n">
         <v>28545800</v>
       </c>
+      <c r="CS5" t="n">
+        <v>28184302</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -22151,6 +22388,9 @@
       <c r="CR6" t="n">
         <v>45221097</v>
       </c>
+      <c r="CS6" t="n">
+        <v>49737704</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -22445,6 +22685,9 @@
       <c r="CR7" t="n">
         <v>160128939</v>
       </c>
+      <c r="CS7" t="n">
+        <v>159586135</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22739,6 +22982,9 @@
       <c r="CR8" t="n">
         <v>27769354</v>
       </c>
+      <c r="CS8" t="n">
+        <v>33651401</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23033,6 +23279,9 @@
       <c r="CR9" t="n">
         <v>5561860</v>
       </c>
+      <c r="CS9" t="n">
+        <v>8373230</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23326,6 +23575,9 @@
       </c>
       <c r="CR10" t="n">
         <v>53719214</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>57259500</v>
       </c>
     </row>
   </sheetData>
@@ -23339,7 +23591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY10"/>
+  <dimension ref="A1:BZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23419,6 +23671,7 @@
     <col width="10" customWidth="1" min="75" max="75"/>
     <col width="10" customWidth="1" min="76" max="76"/>
     <col width="10" customWidth="1" min="77" max="77"/>
+    <col width="10" customWidth="1" min="78" max="78"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23657,6 +23910,9 @@
       <c r="BY1" s="1" t="n">
         <v>20260113</v>
       </c>
+      <c r="BZ1" s="1" t="n">
+        <v>20260114</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23894,6 +24150,9 @@
       <c r="BY2" t="n">
         <v>13</v>
       </c>
+      <c r="BZ2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -24131,6 +24390,9 @@
       <c r="BY3" t="n">
         <v>82</v>
       </c>
+      <c r="BZ3" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -24368,6 +24630,9 @@
       <c r="BY4" t="n">
         <v>100</v>
       </c>
+      <c r="BZ4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24605,6 +24870,9 @@
       <c r="BY5" t="n">
         <v>0</v>
       </c>
+      <c r="BZ5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24842,6 +25110,9 @@
       <c r="BY6" t="n">
         <v>17</v>
       </c>
+      <c r="BZ6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -25079,6 +25350,9 @@
       <c r="BY7" t="n">
         <v>72</v>
       </c>
+      <c r="BZ7" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25316,6 +25590,9 @@
       <c r="BY8" t="n">
         <v>42</v>
       </c>
+      <c r="BZ8" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25553,6 +25830,9 @@
       <c r="BY9" t="n">
         <v>100</v>
       </c>
+      <c r="BZ9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25789,6 +26069,9 @@
       </c>
       <c r="BY10" t="n">
         <v>27</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -25802,7 +26085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK10"/>
+  <dimension ref="A1:AL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25842,6 +26125,7 @@
     <col width="10" customWidth="1" min="35" max="35"/>
     <col width="10" customWidth="1" min="36" max="36"/>
     <col width="10" customWidth="1" min="37" max="37"/>
+    <col width="10" customWidth="1" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25960,6 +26244,9 @@
       <c r="AK1" s="1" t="n">
         <v>20260113</v>
       </c>
+      <c r="AL1" s="1" t="n">
+        <v>20260114</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -26077,6 +26364,9 @@
       <c r="AK2" t="n">
         <v>26</v>
       </c>
+      <c r="AL2" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -26194,6 +26484,9 @@
       <c r="AK3" t="n">
         <v>72</v>
       </c>
+      <c r="AL3" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -26311,6 +26604,9 @@
       <c r="AK4" t="n">
         <v>100</v>
       </c>
+      <c r="AL4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -26428,6 +26724,9 @@
       <c r="AK5" t="n">
         <v>0</v>
       </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -26545,6 +26844,9 @@
       <c r="AK6" t="n">
         <v>0</v>
       </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -26662,6 +26964,9 @@
       <c r="AK7" t="n">
         <v>41</v>
       </c>
+      <c r="AL7" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -26779,6 +27084,9 @@
       <c r="AK8" t="n">
         <v>46</v>
       </c>
+      <c r="AL8" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -26896,6 +27204,9 @@
       <c r="AK9" t="n">
         <v>100</v>
       </c>
+      <c r="AL9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27012,6 +27323,9 @@
       </c>
       <c r="AK10" t="n">
         <v>57</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -27025,7 +27339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY10"/>
+  <dimension ref="A1:BZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -27105,6 +27419,7 @@
     <col width="10" customWidth="1" min="75" max="75"/>
     <col width="10" customWidth="1" min="76" max="76"/>
     <col width="10" customWidth="1" min="77" max="77"/>
+    <col width="10" customWidth="1" min="78" max="78"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27343,6 +27658,9 @@
       <c r="BY1" s="1" t="n">
         <v>20260113</v>
       </c>
+      <c r="BZ1" s="1" t="n">
+        <v>20260114</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -27580,6 +27898,9 @@
       <c r="BY2" t="n">
         <v>-67</v>
       </c>
+      <c r="BZ2" t="n">
+        <v>-68</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -27817,6 +28138,9 @@
       <c r="BY3" t="n">
         <v>57</v>
       </c>
+      <c r="BZ3" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -28054,6 +28378,9 @@
       <c r="BY4" t="n">
         <v>108</v>
       </c>
+      <c r="BZ4" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -28291,6 +28618,9 @@
       <c r="BY5" t="n">
         <v>-90</v>
       </c>
+      <c r="BZ5" t="n">
+        <v>-141</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -28528,6 +28858,9 @@
       <c r="BY6" t="n">
         <v>-59</v>
       </c>
+      <c r="BZ6" t="n">
+        <v>-91</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -28765,6 +29098,9 @@
       <c r="BY7" t="n">
         <v>11</v>
       </c>
+      <c r="BZ7" t="n">
+        <v>-17</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -29002,6 +29338,9 @@
       <c r="BY8" t="n">
         <v>-27</v>
       </c>
+      <c r="BZ8" t="n">
+        <v>-28</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -29239,6 +29578,9 @@
       <c r="BY9" t="n">
         <v>91</v>
       </c>
+      <c r="BZ9" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -29475,6 +29817,9 @@
       </c>
       <c r="BY10" t="n">
         <v>-34</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>-48</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL10"/>
+  <dimension ref="A1:AM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -642,6 +642,7 @@
     <col width="10" customWidth="1" min="36" max="36"/>
     <col width="10" customWidth="1" min="37" max="37"/>
     <col width="10" customWidth="1" min="38" max="38"/>
+    <col width="10" customWidth="1" min="39" max="39"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,6 +764,9 @@
       <c r="AL1" s="1" t="n">
         <v>20260114</v>
       </c>
+      <c r="AM1" s="1" t="n">
+        <v>20260115</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -883,6 +887,9 @@
       <c r="AL2" t="n">
         <v>-83</v>
       </c>
+      <c r="AM2" t="n">
+        <v>-94</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1003,6 +1010,9 @@
       <c r="AL3" t="n">
         <v>23</v>
       </c>
+      <c r="AM3" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1123,6 +1133,9 @@
       <c r="AL4" t="n">
         <v>80</v>
       </c>
+      <c r="AM4" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1243,6 +1256,9 @@
       <c r="AL5" t="n">
         <v>-90</v>
       </c>
+      <c r="AM5" t="n">
+        <v>-93</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1363,6 +1379,9 @@
       <c r="AL6" t="n">
         <v>-36</v>
       </c>
+      <c r="AM6" t="n">
+        <v>-35</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1483,6 +1502,9 @@
       <c r="AL7" t="n">
         <v>-21</v>
       </c>
+      <c r="AM7" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1603,6 +1625,9 @@
       <c r="AL8" t="n">
         <v>-10</v>
       </c>
+      <c r="AM8" t="n">
+        <v>-16</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1723,6 +1748,9 @@
       <c r="AL9" t="n">
         <v>128</v>
       </c>
+      <c r="AM9" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1842,6 +1870,9 @@
       </c>
       <c r="AL10" t="n">
         <v>-11</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-12</v>
       </c>
     </row>
   </sheetData>
@@ -1855,7 +1886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ10"/>
+  <dimension ref="A1:CA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1936,6 +1967,7 @@
     <col width="12" customWidth="1" min="76" max="76"/>
     <col width="12" customWidth="1" min="77" max="77"/>
     <col width="12" customWidth="1" min="78" max="78"/>
+    <col width="12" customWidth="1" min="79" max="79"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2329,6 +2361,11 @@
           <t>20260114</t>
         </is>
       </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>20260115</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2569,6 +2606,9 @@
       <c r="BZ2" t="n">
         <v>97</v>
       </c>
+      <c r="CA2" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2809,6 +2849,9 @@
       <c r="BZ3" t="n">
         <v>101</v>
       </c>
+      <c r="CA3" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3049,6 +3092,9 @@
       <c r="BZ4" t="n">
         <v>106</v>
       </c>
+      <c r="CA4" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3289,6 +3335,9 @@
       <c r="BZ5" t="n">
         <v>96</v>
       </c>
+      <c r="CA5" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3529,6 +3578,9 @@
       <c r="BZ6" t="n">
         <v>96</v>
       </c>
+      <c r="CA6" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3769,6 +3821,9 @@
       <c r="BZ7" t="n">
         <v>99</v>
       </c>
+      <c r="CA7" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4009,6 +4064,9 @@
       <c r="BZ8" t="n">
         <v>98</v>
       </c>
+      <c r="CA8" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4249,6 +4307,9 @@
       <c r="BZ9" t="n">
         <v>105</v>
       </c>
+      <c r="CA9" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4487,6 +4548,9 @@
         <v>97</v>
       </c>
       <c r="BZ10" t="n">
+        <v>96</v>
+      </c>
+      <c r="CA10" t="n">
         <v>96</v>
       </c>
     </row>
@@ -6850,7 +6914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL10"/>
+  <dimension ref="A1:AM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6891,6 +6955,7 @@
     <col width="12" customWidth="1" min="36" max="36"/>
     <col width="12" customWidth="1" min="37" max="37"/>
     <col width="12" customWidth="1" min="38" max="38"/>
+    <col width="12" customWidth="1" min="39" max="39"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7084,6 +7149,11 @@
           <t>20260114</t>
         </is>
       </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>20260115</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7204,6 +7274,9 @@
       <c r="AL2" t="n">
         <v>44</v>
       </c>
+      <c r="AM2" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7324,6 +7397,9 @@
       <c r="AL3" t="n">
         <v>47</v>
       </c>
+      <c r="AM3" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7444,6 +7520,9 @@
       <c r="AL4" t="n">
         <v>40</v>
       </c>
+      <c r="AM4" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7564,6 +7643,9 @@
       <c r="AL5" t="n">
         <v>60</v>
       </c>
+      <c r="AM5" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7684,6 +7766,9 @@
       <c r="AL6" t="n">
         <v>83</v>
       </c>
+      <c r="AM6" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7804,6 +7889,9 @@
       <c r="AL7" t="n">
         <v>44</v>
       </c>
+      <c r="AM7" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7924,6 +8012,9 @@
       <c r="AL8" t="n">
         <v>37</v>
       </c>
+      <c r="AM8" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8044,6 +8135,9 @@
       <c r="AL9" t="n">
         <v>45</v>
       </c>
+      <c r="AM9" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8163,6 +8257,9 @@
       </c>
       <c r="AL10" t="n">
         <v>37</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -8176,7 +8273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS10"/>
+  <dimension ref="A1:CT10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8276,6 +8373,7 @@
     <col width="12" customWidth="1" min="95" max="95"/>
     <col width="12" customWidth="1" min="96" max="96"/>
     <col width="12" customWidth="1" min="97" max="97"/>
+    <col width="12" customWidth="1" min="98" max="98"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8574,6 +8672,9 @@
       <c r="CS1" s="1" t="n">
         <v>20260114</v>
       </c>
+      <c r="CT1" s="1" t="n">
+        <v>20260115</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8871,6 +8972,9 @@
       <c r="CS2" t="n">
         <v>259.49</v>
       </c>
+      <c r="CT2" t="n">
+        <v>260.65</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9168,6 +9272,9 @@
       <c r="CS3" t="n">
         <v>241.15</v>
       </c>
+      <c r="CT3" t="n">
+        <v>239.31</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9465,6 +9572,9 @@
       <c r="CS4" t="n">
         <v>335.06</v>
       </c>
+      <c r="CT4" t="n">
+        <v>337.65</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9762,6 +9872,9 @@
       <c r="CS5" t="n">
         <v>466.46</v>
       </c>
+      <c r="CT5" t="n">
+        <v>464.12</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10059,6 +10172,9 @@
       <c r="CS6" t="n">
         <v>91.23999999999999</v>
       </c>
+      <c r="CT6" t="n">
+        <v>89.02</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10356,6 +10472,9 @@
       <c r="CS7" t="n">
         <v>184.32</v>
       </c>
+      <c r="CT7" t="n">
+        <v>186.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10653,6 +10772,9 @@
       <c r="CS8" t="n">
         <v>178.125</v>
       </c>
+      <c r="CT8" t="n">
+        <v>178.71</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10950,6 +11072,9 @@
       <c r="CS9" t="n">
         <v>90.26000000000001</v>
       </c>
+      <c r="CT9" t="n">
+        <v>92.071</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11246,6 +11371,9 @@
       </c>
       <c r="CS10" t="n">
         <v>442.81</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>441.125</v>
       </c>
     </row>
   </sheetData>
@@ -11259,7 +11387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS10"/>
+  <dimension ref="A1:CT10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11359,6 +11487,7 @@
     <col width="12" customWidth="1" min="95" max="95"/>
     <col width="12" customWidth="1" min="96" max="96"/>
     <col width="12" customWidth="1" min="97" max="97"/>
+    <col width="12" customWidth="1" min="98" max="98"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11657,6 +11786,9 @@
       <c r="CS1" s="1" t="n">
         <v>20260114</v>
       </c>
+      <c r="CT1" s="1" t="n">
+        <v>20260115</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11954,6 +12086,9 @@
       <c r="CS2" t="n">
         <v>261.82</v>
       </c>
+      <c r="CT2" t="n">
+        <v>261.04</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12251,6 +12386,9 @@
       <c r="CS3" t="n">
         <v>241.28</v>
       </c>
+      <c r="CT3" t="n">
+        <v>240.65</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12548,6 +12686,9 @@
       <c r="CS4" t="n">
         <v>336.52</v>
       </c>
+      <c r="CT4" t="n">
+        <v>337.69</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12845,6 +12986,9 @@
       <c r="CS5" t="n">
         <v>468.2</v>
       </c>
+      <c r="CT5" t="n">
+        <v>464.25</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13142,6 +13286,9 @@
       <c r="CS6" t="n">
         <v>91.58</v>
       </c>
+      <c r="CT6" t="n">
+        <v>89.89</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13439,6 +13586,9 @@
       <c r="CS7" t="n">
         <v>184.46</v>
       </c>
+      <c r="CT7" t="n">
+        <v>189.7</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13736,6 +13886,9 @@
       <c r="CS8" t="n">
         <v>181.5975</v>
       </c>
+      <c r="CT8" t="n">
+        <v>180.6</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14033,6 +14186,9 @@
       <c r="CS9" t="n">
         <v>91.52</v>
       </c>
+      <c r="CT9" t="n">
+        <v>94.17</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14329,6 +14485,9 @@
       </c>
       <c r="CS10" t="n">
         <v>443.91</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>445.36</v>
       </c>
     </row>
   </sheetData>
@@ -14342,7 +14501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS10"/>
+  <dimension ref="A1:CT10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14442,6 +14601,7 @@
     <col width="12" customWidth="1" min="95" max="95"/>
     <col width="12" customWidth="1" min="96" max="96"/>
     <col width="12" customWidth="1" min="97" max="97"/>
+    <col width="12" customWidth="1" min="98" max="98"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14740,6 +14900,9 @@
       <c r="CS1" s="1" t="n">
         <v>20260114</v>
       </c>
+      <c r="CT1" s="1" t="n">
+        <v>20260115</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15037,6 +15200,9 @@
       <c r="CS2" t="n">
         <v>256.71</v>
       </c>
+      <c r="CT2" t="n">
+        <v>257.05</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15334,6 +15500,9 @@
       <c r="CS3" t="n">
         <v>236.22</v>
       </c>
+      <c r="CT3" t="n">
+        <v>236.63</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15631,6 +15800,9 @@
       <c r="CS4" t="n">
         <v>330.48</v>
       </c>
+      <c r="CT4" t="n">
+        <v>330.74</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15928,6 +16100,9 @@
       <c r="CS5" t="n">
         <v>457.1701</v>
       </c>
+      <c r="CT5" t="n">
+        <v>455.9</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16225,6 +16400,9 @@
       <c r="CS6" t="n">
         <v>87.95</v>
       </c>
+      <c r="CT6" t="n">
+        <v>87.81999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16522,6 +16700,9 @@
       <c r="CS7" t="n">
         <v>180.8</v>
       </c>
+      <c r="CT7" t="n">
+        <v>186.33</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16819,6 +17000,9 @@
       <c r="CS8" t="n">
         <v>173.95</v>
       </c>
+      <c r="CT8" t="n">
+        <v>176.5301</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17116,6 +17300,9 @@
       <c r="CS9" t="n">
         <v>90.15000000000001</v>
       </c>
+      <c r="CT9" t="n">
+        <v>91.64</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17412,6 +17599,9 @@
       </c>
       <c r="CS10" t="n">
         <v>434.22</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>437.65</v>
       </c>
     </row>
   </sheetData>
@@ -17425,7 +17615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS10"/>
+  <dimension ref="A1:CT10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17525,6 +17715,7 @@
     <col width="12" customWidth="1" min="95" max="95"/>
     <col width="12" customWidth="1" min="96" max="96"/>
     <col width="12" customWidth="1" min="97" max="97"/>
+    <col width="12" customWidth="1" min="98" max="98"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17823,6 +18014,9 @@
       <c r="CS1" s="1" t="n">
         <v>20260114</v>
       </c>
+      <c r="CT1" s="1" t="n">
+        <v>20260115</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18120,6 +18314,9 @@
       <c r="CS2" t="n">
         <v>259.96</v>
       </c>
+      <c r="CT2" t="n">
+        <v>258.21</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18417,6 +18614,9 @@
       <c r="CS3" t="n">
         <v>236.65</v>
       </c>
+      <c r="CT3" t="n">
+        <v>238.18</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18714,6 +18914,9 @@
       <c r="CS4" t="n">
         <v>335.84</v>
       </c>
+      <c r="CT4" t="n">
+        <v>332.78</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19011,6 +19214,9 @@
       <c r="CS5" t="n">
         <v>459.38</v>
       </c>
+      <c r="CT5" t="n">
+        <v>456.66</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19308,6 +19514,9 @@
       <c r="CS6" t="n">
         <v>88.55</v>
       </c>
+      <c r="CT6" t="n">
+        <v>88.05</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19605,6 +19814,9 @@
       <c r="CS7" t="n">
         <v>183.14</v>
       </c>
+      <c r="CT7" t="n">
+        <v>187.05</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19902,6 +20114,9 @@
       <c r="CS8" t="n">
         <v>178.4</v>
       </c>
+      <c r="CT8" t="n">
+        <v>177.07</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20199,6 +20414,9 @@
       <c r="CS9" t="n">
         <v>91.15000000000001</v>
       </c>
+      <c r="CT9" t="n">
+        <v>93.28</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20495,6 +20713,9 @@
       </c>
       <c r="CS10" t="n">
         <v>439.2</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>438.57</v>
       </c>
     </row>
   </sheetData>
@@ -20508,7 +20729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS10"/>
+  <dimension ref="A1:CT10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20608,6 +20829,7 @@
     <col width="12" customWidth="1" min="95" max="95"/>
     <col width="12" customWidth="1" min="96" max="96"/>
     <col width="12" customWidth="1" min="97" max="97"/>
+    <col width="12" customWidth="1" min="98" max="98"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20906,6 +21128,9 @@
       <c r="CS1" s="1" t="n">
         <v>20260114</v>
       </c>
+      <c r="CT1" s="1" t="n">
+        <v>20260115</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21203,6 +21428,9 @@
       <c r="CS2" t="n">
         <v>40019421</v>
       </c>
+      <c r="CT2" t="n">
+        <v>39388564</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21500,6 +21728,9 @@
       <c r="CS3" t="n">
         <v>41410578</v>
       </c>
+      <c r="CT3" t="n">
+        <v>43003571</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -21797,6 +22028,9 @@
       <c r="CS4" t="n">
         <v>28525571</v>
       </c>
+      <c r="CT4" t="n">
+        <v>28442406</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -22094,6 +22328,9 @@
       <c r="CS5" t="n">
         <v>28184302</v>
       </c>
+      <c r="CT5" t="n">
+        <v>23225839</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -22391,6 +22628,9 @@
       <c r="CS6" t="n">
         <v>49737704</v>
       </c>
+      <c r="CT6" t="n">
+        <v>36945057</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -22688,6 +22928,9 @@
       <c r="CS7" t="n">
         <v>159586135</v>
       </c>
+      <c r="CT7" t="n">
+        <v>206188642</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22985,6 +23228,9 @@
       <c r="CS8" t="n">
         <v>33651401</v>
       </c>
+      <c r="CT8" t="n">
+        <v>31109181</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23282,6 +23528,9 @@
       <c r="CS9" t="n">
         <v>8373230</v>
       </c>
+      <c r="CT9" t="n">
+        <v>10001665</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23578,6 +23827,9 @@
       </c>
       <c r="CS10" t="n">
         <v>57259500</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>49465813</v>
       </c>
     </row>
   </sheetData>
@@ -23591,7 +23843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ10"/>
+  <dimension ref="A1:CA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23672,6 +23924,7 @@
     <col width="10" customWidth="1" min="76" max="76"/>
     <col width="10" customWidth="1" min="77" max="77"/>
     <col width="10" customWidth="1" min="78" max="78"/>
+    <col width="10" customWidth="1" min="79" max="79"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23913,6 +24166,9 @@
       <c r="BZ1" s="1" t="n">
         <v>20260114</v>
       </c>
+      <c r="CA1" s="1" t="n">
+        <v>20260115</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24153,6 +24409,9 @@
       <c r="BZ2" t="n">
         <v>6</v>
       </c>
+      <c r="CA2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -24393,6 +24652,9 @@
       <c r="BZ3" t="n">
         <v>59</v>
       </c>
+      <c r="CA3" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -24633,6 +24895,9 @@
       <c r="BZ4" t="n">
         <v>100</v>
       </c>
+      <c r="CA4" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24873,6 +25138,9 @@
       <c r="BZ5" t="n">
         <v>0</v>
       </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -25113,6 +25381,9 @@
       <c r="BZ6" t="n">
         <v>0</v>
       </c>
+      <c r="CA6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -25353,6 +25624,9 @@
       <c r="BZ7" t="n">
         <v>59</v>
       </c>
+      <c r="CA7" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25593,6 +25867,9 @@
       <c r="BZ8" t="n">
         <v>40</v>
       </c>
+      <c r="CA8" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25833,6 +26110,9 @@
       <c r="BZ9" t="n">
         <v>100</v>
       </c>
+      <c r="CA9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26072,6 +26352,9 @@
       </c>
       <c r="BZ10" t="n">
         <v>13</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -26085,7 +26368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL10"/>
+  <dimension ref="A1:AM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -26126,6 +26409,7 @@
     <col width="10" customWidth="1" min="36" max="36"/>
     <col width="10" customWidth="1" min="37" max="37"/>
     <col width="10" customWidth="1" min="38" max="38"/>
+    <col width="10" customWidth="1" min="39" max="39"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26247,6 +26531,9 @@
       <c r="AL1" s="1" t="n">
         <v>20260114</v>
       </c>
+      <c r="AM1" s="1" t="n">
+        <v>20260115</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -26367,6 +26654,9 @@
       <c r="AL2" t="n">
         <v>5</v>
       </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -26487,6 +26777,9 @@
       <c r="AL3" t="n">
         <v>54</v>
       </c>
+      <c r="AM3" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -26607,6 +26900,9 @@
       <c r="AL4" t="n">
         <v>100</v>
       </c>
+      <c r="AM4" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -26727,6 +27023,9 @@
       <c r="AL5" t="n">
         <v>0</v>
       </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -26847,6 +27146,9 @@
       <c r="AL6" t="n">
         <v>0</v>
       </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -26967,6 +27269,9 @@
       <c r="AL7" t="n">
         <v>34</v>
       </c>
+      <c r="AM7" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -27087,6 +27392,9 @@
       <c r="AL8" t="n">
         <v>45</v>
       </c>
+      <c r="AM8" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -27207,6 +27515,9 @@
       <c r="AL9" t="n">
         <v>100</v>
       </c>
+      <c r="AM9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27326,6 +27637,9 @@
       </c>
       <c r="AL10" t="n">
         <v>49</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -27339,7 +27653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ10"/>
+  <dimension ref="A1:CA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -27420,6 +27734,7 @@
     <col width="10" customWidth="1" min="76" max="76"/>
     <col width="10" customWidth="1" min="77" max="77"/>
     <col width="10" customWidth="1" min="78" max="78"/>
+    <col width="10" customWidth="1" min="79" max="79"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27661,6 +27976,9 @@
       <c r="BZ1" s="1" t="n">
         <v>20260114</v>
       </c>
+      <c r="CA1" s="1" t="n">
+        <v>20260115</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -27901,6 +28219,9 @@
       <c r="BZ2" t="n">
         <v>-68</v>
       </c>
+      <c r="CA2" t="n">
+        <v>-73</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -28141,6 +28462,9 @@
       <c r="BZ3" t="n">
         <v>18</v>
       </c>
+      <c r="CA3" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -28381,6 +28705,9 @@
       <c r="BZ4" t="n">
         <v>92</v>
       </c>
+      <c r="CA4" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -28621,6 +28948,9 @@
       <c r="BZ5" t="n">
         <v>-141</v>
       </c>
+      <c r="CA5" t="n">
+        <v>-125</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -28861,6 +29191,9 @@
       <c r="BZ6" t="n">
         <v>-91</v>
       </c>
+      <c r="CA6" t="n">
+        <v>-89</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -29101,6 +29434,9 @@
       <c r="BZ7" t="n">
         <v>-17</v>
       </c>
+      <c r="CA7" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -29341,6 +29677,9 @@
       <c r="BZ8" t="n">
         <v>-28</v>
       </c>
+      <c r="CA8" t="n">
+        <v>-34</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -29581,6 +29920,9 @@
       <c r="BZ9" t="n">
         <v>89</v>
       </c>
+      <c r="CA9" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -29820,6 +30162,9 @@
       </c>
       <c r="BZ10" t="n">
         <v>-48</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>-45</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM10"/>
+  <dimension ref="A1:AN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -643,6 +643,7 @@
     <col width="10" customWidth="1" min="37" max="37"/>
     <col width="10" customWidth="1" min="38" max="38"/>
     <col width="10" customWidth="1" min="39" max="39"/>
+    <col width="10" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -767,6 +768,9 @@
       <c r="AM1" s="1" t="n">
         <v>20260115</v>
       </c>
+      <c r="AN1" s="1" t="n">
+        <v>20260116</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -890,6 +894,9 @@
       <c r="AM2" t="n">
         <v>-94</v>
       </c>
+      <c r="AN2" t="n">
+        <v>-110</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1013,6 +1020,9 @@
       <c r="AM3" t="n">
         <v>30</v>
       </c>
+      <c r="AN3" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1136,6 +1146,9 @@
       <c r="AM4" t="n">
         <v>71</v>
       </c>
+      <c r="AN4" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1259,6 +1272,9 @@
       <c r="AM5" t="n">
         <v>-93</v>
       </c>
+      <c r="AN5" t="n">
+        <v>-81</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1382,6 +1398,9 @@
       <c r="AM6" t="n">
         <v>-35</v>
       </c>
+      <c r="AN6" t="n">
+        <v>-33</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1505,6 +1524,9 @@
       <c r="AM7" t="n">
         <v>4</v>
       </c>
+      <c r="AN7" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1628,6 +1650,9 @@
       <c r="AM8" t="n">
         <v>-16</v>
       </c>
+      <c r="AN8" t="n">
+        <v>-44</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1751,6 +1776,9 @@
       <c r="AM9" t="n">
         <v>156</v>
       </c>
+      <c r="AN9" t="n">
+        <v>138</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1873,6 +1901,9 @@
       </c>
       <c r="AM10" t="n">
         <v>-12</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-14</v>
       </c>
     </row>
   </sheetData>
@@ -1886,7 +1917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA10"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1968,6 +1999,7 @@
     <col width="12" customWidth="1" min="77" max="77"/>
     <col width="12" customWidth="1" min="78" max="78"/>
     <col width="12" customWidth="1" min="79" max="79"/>
+    <col width="12" customWidth="1" min="80" max="80"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2366,6 +2398,11 @@
           <t>20260115</t>
         </is>
       </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>20260116</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2609,6 +2646,9 @@
       <c r="CA2" t="n">
         <v>97</v>
       </c>
+      <c r="CB2" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2852,6 +2892,9 @@
       <c r="CA3" t="n">
         <v>102</v>
       </c>
+      <c r="CB3" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3095,6 +3138,9 @@
       <c r="CA4" t="n">
         <v>105</v>
       </c>
+      <c r="CB4" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3338,6 +3384,9 @@
       <c r="CA5" t="n">
         <v>95</v>
       </c>
+      <c r="CB5" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3581,6 +3630,9 @@
       <c r="CA6" t="n">
         <v>96</v>
       </c>
+      <c r="CB6" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3824,6 +3876,9 @@
       <c r="CA7" t="n">
         <v>101</v>
       </c>
+      <c r="CB7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4067,6 +4122,9 @@
       <c r="CA8" t="n">
         <v>97</v>
       </c>
+      <c r="CB8" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4310,6 +4368,9 @@
       <c r="CA9" t="n">
         <v>107</v>
       </c>
+      <c r="CB9" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4551,6 +4612,9 @@
         <v>96</v>
       </c>
       <c r="CA10" t="n">
+        <v>96</v>
+      </c>
+      <c r="CB10" t="n">
         <v>96</v>
       </c>
     </row>
@@ -6914,7 +6978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM10"/>
+  <dimension ref="A1:AN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6956,6 +7020,7 @@
     <col width="12" customWidth="1" min="37" max="37"/>
     <col width="12" customWidth="1" min="38" max="38"/>
     <col width="12" customWidth="1" min="39" max="39"/>
+    <col width="12" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7154,6 +7219,11 @@
           <t>20260115</t>
         </is>
       </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>20260116</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7277,6 +7347,9 @@
       <c r="AM2" t="n">
         <v>44</v>
       </c>
+      <c r="AN2" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7400,6 +7473,9 @@
       <c r="AM3" t="n">
         <v>49</v>
       </c>
+      <c r="AN3" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7523,6 +7599,9 @@
       <c r="AM4" t="n">
         <v>39</v>
       </c>
+      <c r="AN4" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7646,6 +7725,9 @@
       <c r="AM5" t="n">
         <v>49</v>
       </c>
+      <c r="AN5" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7769,6 +7851,9 @@
       <c r="AM6" t="n">
         <v>61</v>
       </c>
+      <c r="AN6" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7892,6 +7977,9 @@
       <c r="AM7" t="n">
         <v>57</v>
       </c>
+      <c r="AN7" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8015,6 +8103,9 @@
       <c r="AM8" t="n">
         <v>34</v>
       </c>
+      <c r="AN8" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8138,6 +8229,9 @@
       <c r="AM9" t="n">
         <v>53</v>
       </c>
+      <c r="AN9" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8260,6 +8354,9 @@
       </c>
       <c r="AM10" t="n">
         <v>32</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -8273,7 +8370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CT10"/>
+  <dimension ref="A1:CU10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8374,6 +8471,7 @@
     <col width="12" customWidth="1" min="96" max="96"/>
     <col width="12" customWidth="1" min="97" max="97"/>
     <col width="12" customWidth="1" min="98" max="98"/>
+    <col width="12" customWidth="1" min="99" max="99"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8675,6 +8773,9 @@
       <c r="CT1" s="1" t="n">
         <v>20260115</v>
       </c>
+      <c r="CU1" s="1" t="n">
+        <v>20260116</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8975,6 +9076,9 @@
       <c r="CT2" t="n">
         <v>260.65</v>
       </c>
+      <c r="CU2" t="n">
+        <v>257.9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9275,6 +9379,9 @@
       <c r="CT3" t="n">
         <v>239.31</v>
       </c>
+      <c r="CU3" t="n">
+        <v>239.085</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9575,6 +9682,9 @@
       <c r="CT4" t="n">
         <v>337.65</v>
       </c>
+      <c r="CU4" t="n">
+        <v>334.41</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9875,6 +9985,9 @@
       <c r="CT5" t="n">
         <v>464.12</v>
       </c>
+      <c r="CU5" t="n">
+        <v>457.83</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10175,6 +10288,9 @@
       <c r="CT6" t="n">
         <v>89.02</v>
       </c>
+      <c r="CU6" t="n">
+        <v>88.33499999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10475,6 +10591,9 @@
       <c r="CT7" t="n">
         <v>186.5</v>
       </c>
+      <c r="CU7" t="n">
+        <v>189.075</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10775,6 +10894,9 @@
       <c r="CT8" t="n">
         <v>178.71</v>
       </c>
+      <c r="CU8" t="n">
+        <v>179.36</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11075,6 +11197,9 @@
       <c r="CT9" t="n">
         <v>92.071</v>
       </c>
+      <c r="CU9" t="n">
+        <v>93.36</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11374,6 +11499,9 @@
       </c>
       <c r="CT10" t="n">
         <v>441.125</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>439.5</v>
       </c>
     </row>
   </sheetData>
@@ -11387,7 +11515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CT10"/>
+  <dimension ref="A1:CU10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11488,6 +11616,7 @@
     <col width="12" customWidth="1" min="96" max="96"/>
     <col width="12" customWidth="1" min="97" max="97"/>
     <col width="12" customWidth="1" min="98" max="98"/>
+    <col width="12" customWidth="1" min="99" max="99"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11789,6 +11918,9 @@
       <c r="CT1" s="1" t="n">
         <v>20260115</v>
       </c>
+      <c r="CU1" s="1" t="n">
+        <v>20260116</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12089,6 +12221,9 @@
       <c r="CT2" t="n">
         <v>261.04</v>
       </c>
+      <c r="CU2" t="n">
+        <v>258.9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12389,6 +12524,9 @@
       <c r="CT3" t="n">
         <v>240.65</v>
       </c>
+      <c r="CU3" t="n">
+        <v>239.57</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12689,6 +12827,9 @@
       <c r="CT4" t="n">
         <v>337.69</v>
       </c>
+      <c r="CU4" t="n">
+        <v>334.65</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12989,6 +13130,9 @@
       <c r="CT5" t="n">
         <v>464.25</v>
       </c>
+      <c r="CU5" t="n">
+        <v>463.19</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13289,6 +13433,9 @@
       <c r="CT6" t="n">
         <v>89.89</v>
       </c>
+      <c r="CU6" t="n">
+        <v>88.51000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13589,6 +13736,9 @@
       <c r="CT7" t="n">
         <v>189.7</v>
       </c>
+      <c r="CU7" t="n">
+        <v>190.44</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13889,6 +14039,9 @@
       <c r="CT8" t="n">
         <v>180.6</v>
       </c>
+      <c r="CU8" t="n">
+        <v>182.43</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14189,6 +14342,9 @@
       <c r="CT9" t="n">
         <v>94.17</v>
       </c>
+      <c r="CU9" t="n">
+        <v>93.67</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14488,6 +14644,9 @@
       </c>
       <c r="CT10" t="n">
         <v>445.36</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>447.25</v>
       </c>
     </row>
   </sheetData>
@@ -14501,7 +14660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CT10"/>
+  <dimension ref="A1:CU10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14602,6 +14761,7 @@
     <col width="12" customWidth="1" min="96" max="96"/>
     <col width="12" customWidth="1" min="97" max="97"/>
     <col width="12" customWidth="1" min="98" max="98"/>
+    <col width="12" customWidth="1" min="99" max="99"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14903,6 +15063,9 @@
       <c r="CT1" s="1" t="n">
         <v>20260115</v>
       </c>
+      <c r="CU1" s="1" t="n">
+        <v>20260116</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15203,6 +15366,9 @@
       <c r="CT2" t="n">
         <v>257.05</v>
       </c>
+      <c r="CU2" t="n">
+        <v>254.93</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15503,6 +15669,9 @@
       <c r="CT3" t="n">
         <v>236.63</v>
       </c>
+      <c r="CU3" t="n">
+        <v>236.41</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15803,6 +15972,9 @@
       <c r="CT4" t="n">
         <v>330.74</v>
       </c>
+      <c r="CU4" t="n">
+        <v>327.7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16103,6 +16275,9 @@
       <c r="CT5" t="n">
         <v>455.9</v>
       </c>
+      <c r="CU5" t="n">
+        <v>456.48</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16403,6 +16578,9 @@
       <c r="CT6" t="n">
         <v>87.81999999999999</v>
       </c>
+      <c r="CU6" t="n">
+        <v>87.78</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16703,6 +16881,9 @@
       <c r="CT7" t="n">
         <v>186.33</v>
       </c>
+      <c r="CU7" t="n">
+        <v>186.08</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17003,6 +17184,9 @@
       <c r="CT8" t="n">
         <v>176.5301</v>
       </c>
+      <c r="CU8" t="n">
+        <v>170.01</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17303,6 +17487,9 @@
       <c r="CT9" t="n">
         <v>91.64</v>
       </c>
+      <c r="CU9" t="n">
+        <v>92.22</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17602,6 +17789,9 @@
       </c>
       <c r="CT10" t="n">
         <v>437.65</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>435.2601</v>
       </c>
     </row>
   </sheetData>
@@ -17615,7 +17805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CT10"/>
+  <dimension ref="A1:CU10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17716,6 +17906,7 @@
     <col width="12" customWidth="1" min="96" max="96"/>
     <col width="12" customWidth="1" min="97" max="97"/>
     <col width="12" customWidth="1" min="98" max="98"/>
+    <col width="12" customWidth="1" min="99" max="99"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18017,6 +18208,9 @@
       <c r="CT1" s="1" t="n">
         <v>20260115</v>
       </c>
+      <c r="CU1" s="1" t="n">
+        <v>20260116</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18317,6 +18511,9 @@
       <c r="CT2" t="n">
         <v>258.21</v>
       </c>
+      <c r="CU2" t="n">
+        <v>255.53</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18617,6 +18814,9 @@
       <c r="CT3" t="n">
         <v>238.18</v>
       </c>
+      <c r="CU3" t="n">
+        <v>239.12</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18917,6 +19117,9 @@
       <c r="CT4" t="n">
         <v>332.78</v>
       </c>
+      <c r="CU4" t="n">
+        <v>330</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19217,6 +19420,9 @@
       <c r="CT5" t="n">
         <v>456.66</v>
       </c>
+      <c r="CU5" t="n">
+        <v>459.86</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19517,6 +19723,9 @@
       <c r="CT6" t="n">
         <v>88.05</v>
       </c>
+      <c r="CU6" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19817,6 +20026,9 @@
       <c r="CT7" t="n">
         <v>187.05</v>
       </c>
+      <c r="CU7" t="n">
+        <v>186.23</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20117,6 +20329,9 @@
       <c r="CT8" t="n">
         <v>177.07</v>
       </c>
+      <c r="CU8" t="n">
+        <v>170.96</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20417,6 +20632,9 @@
       <c r="CT9" t="n">
         <v>93.28</v>
       </c>
+      <c r="CU9" t="n">
+        <v>92.98999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20716,6 +20934,9 @@
       </c>
       <c r="CT10" t="n">
         <v>438.57</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>437.5</v>
       </c>
     </row>
   </sheetData>
@@ -20729,7 +20950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CT10"/>
+  <dimension ref="A1:CU10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20830,6 +21051,7 @@
     <col width="12" customWidth="1" min="96" max="96"/>
     <col width="12" customWidth="1" min="97" max="97"/>
     <col width="12" customWidth="1" min="98" max="98"/>
+    <col width="12" customWidth="1" min="99" max="99"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21131,6 +21353,9 @@
       <c r="CT1" s="1" t="n">
         <v>20260115</v>
       </c>
+      <c r="CU1" s="1" t="n">
+        <v>20260116</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21431,6 +21656,9 @@
       <c r="CT2" t="n">
         <v>39388564</v>
       </c>
+      <c r="CU2" t="n">
+        <v>72142773</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21731,6 +21959,9 @@
       <c r="CT3" t="n">
         <v>43003571</v>
       </c>
+      <c r="CU3" t="n">
+        <v>45888283</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22031,6 +22262,9 @@
       <c r="CT4" t="n">
         <v>28442406</v>
       </c>
+      <c r="CU4" t="n">
+        <v>40341637</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -22331,6 +22565,9 @@
       <c r="CT5" t="n">
         <v>23225839</v>
       </c>
+      <c r="CU5" t="n">
+        <v>34246650</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -22631,6 +22868,9 @@
       <c r="CT6" t="n">
         <v>36945057</v>
       </c>
+      <c r="CU6" t="n">
+        <v>48130497</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -22931,6 +23171,9 @@
       <c r="CT7" t="n">
         <v>206188642</v>
       </c>
+      <c r="CU7" t="n">
+        <v>187967169</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23231,6 +23474,9 @@
       <c r="CT8" t="n">
         <v>31109181</v>
       </c>
+      <c r="CU8" t="n">
+        <v>59483601</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23531,6 +23777,9 @@
       <c r="CT9" t="n">
         <v>10001665</v>
       </c>
+      <c r="CU9" t="n">
+        <v>8958234</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23830,6 +24079,9 @@
       </c>
       <c r="CT10" t="n">
         <v>49465813</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>60220551</v>
       </c>
     </row>
   </sheetData>
@@ -23843,7 +24095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA10"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23925,6 +24177,7 @@
     <col width="10" customWidth="1" min="77" max="77"/>
     <col width="10" customWidth="1" min="78" max="78"/>
     <col width="10" customWidth="1" min="79" max="79"/>
+    <col width="10" customWidth="1" min="80" max="80"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24169,6 +24422,9 @@
       <c r="CA1" s="1" t="n">
         <v>20260115</v>
       </c>
+      <c r="CB1" s="1" t="n">
+        <v>20260116</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24412,6 +24668,9 @@
       <c r="CA2" t="n">
         <v>0</v>
       </c>
+      <c r="CB2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -24655,6 +24914,9 @@
       <c r="CA3" t="n">
         <v>65</v>
       </c>
+      <c r="CB3" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -24898,6 +25160,9 @@
       <c r="CA4" t="n">
         <v>92</v>
       </c>
+      <c r="CB4" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -25141,6 +25406,9 @@
       <c r="CA5" t="n">
         <v>0</v>
       </c>
+      <c r="CB5" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -25384,6 +25652,9 @@
       <c r="CA6" t="n">
         <v>0</v>
       </c>
+      <c r="CB6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -25627,6 +25898,9 @@
       <c r="CA7" t="n">
         <v>78</v>
       </c>
+      <c r="CB7" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25870,6 +26144,9 @@
       <c r="CA8" t="n">
         <v>35</v>
       </c>
+      <c r="CB8" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -26113,6 +26390,9 @@
       <c r="CA9" t="n">
         <v>100</v>
       </c>
+      <c r="CB9" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26355,6 +26635,9 @@
       </c>
       <c r="CA10" t="n">
         <v>12</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -26368,7 +26651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM10"/>
+  <dimension ref="A1:AN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -26410,6 +26693,7 @@
     <col width="10" customWidth="1" min="37" max="37"/>
     <col width="10" customWidth="1" min="38" max="38"/>
     <col width="10" customWidth="1" min="39" max="39"/>
+    <col width="10" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26534,6 +26818,9 @@
       <c r="AM1" s="1" t="n">
         <v>20260115</v>
       </c>
+      <c r="AN1" s="1" t="n">
+        <v>20260116</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -26657,6 +26944,9 @@
       <c r="AM2" t="n">
         <v>0</v>
       </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -26780,6 +27070,9 @@
       <c r="AM3" t="n">
         <v>57</v>
       </c>
+      <c r="AN3" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -26903,6 +27196,9 @@
       <c r="AM4" t="n">
         <v>96</v>
       </c>
+      <c r="AN4" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -27026,6 +27322,9 @@
       <c r="AM5" t="n">
         <v>0</v>
       </c>
+      <c r="AN5" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -27149,6 +27448,9 @@
       <c r="AM6" t="n">
         <v>0</v>
       </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -27272,6 +27574,9 @@
       <c r="AM7" t="n">
         <v>45</v>
       </c>
+      <c r="AN7" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -27395,6 +27700,9 @@
       <c r="AM8" t="n">
         <v>42</v>
       </c>
+      <c r="AN8" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -27518,6 +27826,9 @@
       <c r="AM9" t="n">
         <v>100</v>
       </c>
+      <c r="AN9" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27640,6 +27951,9 @@
       </c>
       <c r="AM10" t="n">
         <v>48</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -27653,7 +27967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA10"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -27735,6 +28049,7 @@
     <col width="10" customWidth="1" min="77" max="77"/>
     <col width="10" customWidth="1" min="78" max="78"/>
     <col width="10" customWidth="1" min="79" max="79"/>
+    <col width="10" customWidth="1" min="80" max="80"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27979,6 +28294,9 @@
       <c r="CA1" s="1" t="n">
         <v>20260115</v>
       </c>
+      <c r="CB1" s="1" t="n">
+        <v>20260116</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -28222,6 +28540,9 @@
       <c r="CA2" t="n">
         <v>-73</v>
       </c>
+      <c r="CB2" t="n">
+        <v>-82</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -28465,6 +28786,9 @@
       <c r="CA3" t="n">
         <v>24</v>
       </c>
+      <c r="CB3" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -28708,6 +29032,9 @@
       <c r="CA4" t="n">
         <v>69</v>
       </c>
+      <c r="CB4" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -28951,6 +29278,9 @@
       <c r="CA5" t="n">
         <v>-125</v>
       </c>
+      <c r="CB5" t="n">
+        <v>-92</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -29194,6 +29524,9 @@
       <c r="CA6" t="n">
         <v>-89</v>
       </c>
+      <c r="CB6" t="n">
+        <v>-80</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -29437,6 +29770,9 @@
       <c r="CA7" t="n">
         <v>16</v>
       </c>
+      <c r="CB7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -29680,6 +30016,9 @@
       <c r="CA8" t="n">
         <v>-34</v>
       </c>
+      <c r="CB8" t="n">
+        <v>-70</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -29923,6 +30262,9 @@
       <c r="CA9" t="n">
         <v>108</v>
       </c>
+      <c r="CB9" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -30165,6 +30507,9 @@
       </c>
       <c r="CA10" t="n">
         <v>-45</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>-44</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN10"/>
+  <dimension ref="A1:AO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -644,6 +644,7 @@
     <col width="10" customWidth="1" min="38" max="38"/>
     <col width="10" customWidth="1" min="39" max="39"/>
     <col width="10" customWidth="1" min="40" max="40"/>
+    <col width="10" customWidth="1" min="41" max="41"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -771,6 +772,9 @@
       <c r="AN1" s="1" t="n">
         <v>20260116</v>
       </c>
+      <c r="AO1" s="1" t="n">
+        <v>20260120</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -897,6 +901,9 @@
       <c r="AN2" t="n">
         <v>-110</v>
       </c>
+      <c r="AO2" t="n">
+        <v>-160</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1023,6 +1030,9 @@
       <c r="AN3" t="n">
         <v>33</v>
       </c>
+      <c r="AO3" t="n">
+        <v>-13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1149,6 +1159,9 @@
       <c r="AN4" t="n">
         <v>64</v>
       </c>
+      <c r="AO4" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1275,6 +1288,9 @@
       <c r="AN5" t="n">
         <v>-81</v>
       </c>
+      <c r="AO5" t="n">
+        <v>-91</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1401,6 +1417,9 @@
       <c r="AN6" t="n">
         <v>-33</v>
       </c>
+      <c r="AO6" t="n">
+        <v>-32</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1527,6 +1546,9 @@
       <c r="AN7" t="n">
         <v>-2</v>
       </c>
+      <c r="AO7" t="n">
+        <v>-54</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1653,6 +1675,9 @@
       <c r="AN8" t="n">
         <v>-44</v>
       </c>
+      <c r="AO8" t="n">
+        <v>-54</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1779,6 +1804,9 @@
       <c r="AN9" t="n">
         <v>138</v>
       </c>
+      <c r="AO9" t="n">
+        <v>138</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1904,6 +1932,9 @@
       </c>
       <c r="AN10" t="n">
         <v>-14</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-52</v>
       </c>
     </row>
   </sheetData>
@@ -1917,7 +1948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2000,6 +2031,7 @@
     <col width="12" customWidth="1" min="78" max="78"/>
     <col width="12" customWidth="1" min="79" max="79"/>
     <col width="12" customWidth="1" min="80" max="80"/>
+    <col width="12" customWidth="1" min="81" max="81"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2403,6 +2435,11 @@
           <t>20260116</t>
         </is>
       </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>20260120</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2649,6 +2686,9 @@
       <c r="CB2" t="n">
         <v>96</v>
       </c>
+      <c r="CC2" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2895,6 +2935,9 @@
       <c r="CB3" t="n">
         <v>102</v>
       </c>
+      <c r="CC3" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3141,6 +3184,9 @@
       <c r="CB4" t="n">
         <v>103</v>
       </c>
+      <c r="CC4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3387,6 +3433,9 @@
       <c r="CB5" t="n">
         <v>96</v>
       </c>
+      <c r="CC5" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3633,6 +3682,9 @@
       <c r="CB6" t="n">
         <v>96</v>
       </c>
+      <c r="CC6" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3879,6 +3931,9 @@
       <c r="CB7" t="n">
         <v>100</v>
       </c>
+      <c r="CC7" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4125,6 +4180,9 @@
       <c r="CB8" t="n">
         <v>94</v>
       </c>
+      <c r="CC8" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4371,6 +4429,9 @@
       <c r="CB9" t="n">
         <v>106</v>
       </c>
+      <c r="CC9" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4616,6 +4677,9 @@
       </c>
       <c r="CB10" t="n">
         <v>96</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -6978,7 +7042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN10"/>
+  <dimension ref="A1:AO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7021,6 +7085,7 @@
     <col width="12" customWidth="1" min="38" max="38"/>
     <col width="12" customWidth="1" min="39" max="39"/>
     <col width="12" customWidth="1" min="40" max="40"/>
+    <col width="12" customWidth="1" min="41" max="41"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7224,6 +7289,11 @@
           <t>20260116</t>
         </is>
       </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>20260120</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7350,6 +7420,9 @@
       <c r="AN2" t="n">
         <v>81</v>
       </c>
+      <c r="AO2" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7476,6 +7549,9 @@
       <c r="AN3" t="n">
         <v>52</v>
       </c>
+      <c r="AO3" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7602,6 +7678,9 @@
       <c r="AN4" t="n">
         <v>56</v>
       </c>
+      <c r="AO4" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7728,6 +7807,9 @@
       <c r="AN5" t="n">
         <v>72</v>
       </c>
+      <c r="AO5" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7854,6 +7936,9 @@
       <c r="AN6" t="n">
         <v>77</v>
       </c>
+      <c r="AO6" t="n">
+        <v>168</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7980,6 +8065,9 @@
       <c r="AN7" t="n">
         <v>52</v>
       </c>
+      <c r="AO7" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8106,6 +8194,9 @@
       <c r="AN8" t="n">
         <v>65</v>
       </c>
+      <c r="AO8" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8232,6 +8323,9 @@
       <c r="AN9" t="n">
         <v>48</v>
       </c>
+      <c r="AO9" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8357,6 +8451,9 @@
       </c>
       <c r="AN10" t="n">
         <v>39</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -8370,7 +8467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU10"/>
+  <dimension ref="A1:CV10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8472,6 +8569,7 @@
     <col width="12" customWidth="1" min="97" max="97"/>
     <col width="12" customWidth="1" min="98" max="98"/>
     <col width="12" customWidth="1" min="99" max="99"/>
+    <col width="12" customWidth="1" min="100" max="100"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8776,6 +8874,9 @@
       <c r="CU1" s="1" t="n">
         <v>20260116</v>
       </c>
+      <c r="CV1" s="1" t="n">
+        <v>20260120</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9079,6 +9180,9 @@
       <c r="CU2" t="n">
         <v>257.9</v>
       </c>
+      <c r="CV2" t="n">
+        <v>252.73</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9382,6 +9486,9 @@
       <c r="CU3" t="n">
         <v>239.085</v>
       </c>
+      <c r="CV3" t="n">
+        <v>233.76</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9685,6 +9792,9 @@
       <c r="CU4" t="n">
         <v>334.41</v>
       </c>
+      <c r="CV4" t="n">
+        <v>320.87</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9988,6 +10098,9 @@
       <c r="CU5" t="n">
         <v>457.83</v>
       </c>
+      <c r="CV5" t="n">
+        <v>451.215</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10291,6 +10404,9 @@
       <c r="CU6" t="n">
         <v>88.33499999999999</v>
       </c>
+      <c r="CV6" t="n">
+        <v>88.97</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10594,6 +10710,9 @@
       <c r="CU7" t="n">
         <v>189.075</v>
       </c>
+      <c r="CV7" t="n">
+        <v>181.9</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10897,6 +11016,9 @@
       <c r="CU8" t="n">
         <v>179.36</v>
       </c>
+      <c r="CV8" t="n">
+        <v>167.625</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11200,6 +11322,9 @@
       <c r="CU9" t="n">
         <v>93.36</v>
       </c>
+      <c r="CV9" t="n">
+        <v>91.76000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11502,6 +11627,9 @@
       </c>
       <c r="CU10" t="n">
         <v>439.5</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>429.36</v>
       </c>
     </row>
   </sheetData>
@@ -11515,7 +11643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU10"/>
+  <dimension ref="A1:CV10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11617,6 +11745,7 @@
     <col width="12" customWidth="1" min="97" max="97"/>
     <col width="12" customWidth="1" min="98" max="98"/>
     <col width="12" customWidth="1" min="99" max="99"/>
+    <col width="12" customWidth="1" min="100" max="100"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11921,6 +12050,9 @@
       <c r="CU1" s="1" t="n">
         <v>20260116</v>
       </c>
+      <c r="CV1" s="1" t="n">
+        <v>20260120</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12224,6 +12356,9 @@
       <c r="CU2" t="n">
         <v>258.9</v>
       </c>
+      <c r="CV2" t="n">
+        <v>254.79</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12527,6 +12662,9 @@
       <c r="CU3" t="n">
         <v>239.57</v>
       </c>
+      <c r="CV3" t="n">
+        <v>235.09</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12830,6 +12968,9 @@
       <c r="CU4" t="n">
         <v>334.65</v>
       </c>
+      <c r="CV4" t="n">
+        <v>327.73</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13133,6 +13274,9 @@
       <c r="CU5" t="n">
         <v>463.19</v>
       </c>
+      <c r="CV5" t="n">
+        <v>456.8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13436,6 +13580,9 @@
       <c r="CU6" t="n">
         <v>88.51000000000001</v>
       </c>
+      <c r="CV6" t="n">
+        <v>89.90000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13739,6 +13886,9 @@
       <c r="CU7" t="n">
         <v>190.44</v>
       </c>
+      <c r="CV7" t="n">
+        <v>182.3786</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14042,6 +14192,9 @@
       <c r="CU8" t="n">
         <v>182.43</v>
       </c>
+      <c r="CV8" t="n">
+        <v>171.97</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14345,6 +14498,9 @@
       <c r="CU9" t="n">
         <v>93.67</v>
       </c>
+      <c r="CV9" t="n">
+        <v>93.81</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14647,6 +14803,9 @@
       </c>
       <c r="CU10" t="n">
         <v>447.25</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>430.725</v>
       </c>
     </row>
   </sheetData>
@@ -14660,7 +14819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU10"/>
+  <dimension ref="A1:CV10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14762,6 +14921,7 @@
     <col width="12" customWidth="1" min="97" max="97"/>
     <col width="12" customWidth="1" min="98" max="98"/>
     <col width="12" customWidth="1" min="99" max="99"/>
+    <col width="12" customWidth="1" min="100" max="100"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15066,6 +15226,9 @@
       <c r="CU1" s="1" t="n">
         <v>20260116</v>
       </c>
+      <c r="CV1" s="1" t="n">
+        <v>20260120</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15369,6 +15532,9 @@
       <c r="CU2" t="n">
         <v>254.93</v>
       </c>
+      <c r="CV2" t="n">
+        <v>243.42</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15672,6 +15838,9 @@
       <c r="CU3" t="n">
         <v>236.41</v>
       </c>
+      <c r="CV3" t="n">
+        <v>229.34</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15975,6 +16144,9 @@
       <c r="CU4" t="n">
         <v>327.7</v>
       </c>
+      <c r="CV4" t="n">
+        <v>320.43</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16278,6 +16450,9 @@
       <c r="CU5" t="n">
         <v>456.48</v>
       </c>
+      <c r="CV5" t="n">
+        <v>449.28</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16581,6 +16756,9 @@
       <c r="CU6" t="n">
         <v>87.78</v>
       </c>
+      <c r="CV6" t="n">
+        <v>87.02</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16884,6 +17062,9 @@
       <c r="CU7" t="n">
         <v>186.08</v>
       </c>
+      <c r="CV7" t="n">
+        <v>177.61</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17187,6 +17368,9 @@
       <c r="CU8" t="n">
         <v>170.01</v>
       </c>
+      <c r="CV8" t="n">
+        <v>166.24</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17490,6 +17674,9 @@
       <c r="CU9" t="n">
         <v>92.22</v>
       </c>
+      <c r="CV9" t="n">
+        <v>90.78</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17792,6 +17979,9 @@
       </c>
       <c r="CU10" t="n">
         <v>435.2601</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>417.44</v>
       </c>
     </row>
   </sheetData>
@@ -17805,7 +17995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU10"/>
+  <dimension ref="A1:CV10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17907,6 +18097,7 @@
     <col width="12" customWidth="1" min="97" max="97"/>
     <col width="12" customWidth="1" min="98" max="98"/>
     <col width="12" customWidth="1" min="99" max="99"/>
+    <col width="12" customWidth="1" min="100" max="100"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18211,6 +18402,9 @@
       <c r="CU1" s="1" t="n">
         <v>20260116</v>
       </c>
+      <c r="CV1" s="1" t="n">
+        <v>20260120</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18514,6 +18708,9 @@
       <c r="CU2" t="n">
         <v>255.53</v>
       </c>
+      <c r="CV2" t="n">
+        <v>246.7</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18817,6 +19014,9 @@
       <c r="CU3" t="n">
         <v>239.12</v>
       </c>
+      <c r="CV3" t="n">
+        <v>231</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19120,6 +19320,9 @@
       <c r="CU4" t="n">
         <v>330</v>
       </c>
+      <c r="CV4" t="n">
+        <v>322</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19423,6 +19626,9 @@
       <c r="CU5" t="n">
         <v>459.86</v>
       </c>
+      <c r="CV5" t="n">
+        <v>454.52</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19726,6 +19932,9 @@
       <c r="CU6" t="n">
         <v>88</v>
       </c>
+      <c r="CV6" t="n">
+        <v>87.26000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20029,6 +20238,9 @@
       <c r="CU7" t="n">
         <v>186.23</v>
       </c>
+      <c r="CV7" t="n">
+        <v>178.07</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20332,6 +20544,9 @@
       <c r="CU8" t="n">
         <v>170.96</v>
       </c>
+      <c r="CV8" t="n">
+        <v>168.53</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20635,6 +20850,9 @@
       <c r="CU9" t="n">
         <v>92.98999999999999</v>
       </c>
+      <c r="CV9" t="n">
+        <v>93.66</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20937,6 +21155,9 @@
       </c>
       <c r="CU10" t="n">
         <v>437.5</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>419.25</v>
       </c>
     </row>
   </sheetData>
@@ -20950,7 +21171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU10"/>
+  <dimension ref="A1:CV10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21052,6 +21273,7 @@
     <col width="12" customWidth="1" min="97" max="97"/>
     <col width="12" customWidth="1" min="98" max="98"/>
     <col width="12" customWidth="1" min="99" max="99"/>
+    <col width="12" customWidth="1" min="100" max="100"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21356,6 +21578,9 @@
       <c r="CU1" s="1" t="n">
         <v>20260116</v>
       </c>
+      <c r="CV1" s="1" t="n">
+        <v>20260120</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21659,6 +21884,9 @@
       <c r="CU2" t="n">
         <v>72142773</v>
       </c>
+      <c r="CV2" t="n">
+        <v>80267517</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21962,6 +22190,9 @@
       <c r="CU3" t="n">
         <v>45888283</v>
       </c>
+      <c r="CV3" t="n">
+        <v>47737854</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22265,6 +22496,9 @@
       <c r="CU4" t="n">
         <v>40341637</v>
       </c>
+      <c r="CV4" t="n">
+        <v>35361045</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -22568,6 +22802,9 @@
       <c r="CU5" t="n">
         <v>34246650</v>
       </c>
+      <c r="CV5" t="n">
+        <v>26129992</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -22871,6 +23108,9 @@
       <c r="CU6" t="n">
         <v>48130497</v>
       </c>
+      <c r="CV6" t="n">
+        <v>109729663</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23174,6 +23414,9 @@
       <c r="CU7" t="n">
         <v>187967169</v>
       </c>
+      <c r="CV7" t="n">
+        <v>223345257</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23477,6 +23720,9 @@
       <c r="CU8" t="n">
         <v>59483601</v>
       </c>
+      <c r="CV8" t="n">
+        <v>36708497</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23780,6 +24026,9 @@
       <c r="CU9" t="n">
         <v>8958234</v>
       </c>
+      <c r="CV9" t="n">
+        <v>13555205</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24082,6 +24331,9 @@
       </c>
       <c r="CU10" t="n">
         <v>60220551</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>63187336</v>
       </c>
     </row>
   </sheetData>
@@ -24095,7 +24347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24178,6 +24430,7 @@
     <col width="10" customWidth="1" min="78" max="78"/>
     <col width="10" customWidth="1" min="79" max="79"/>
     <col width="10" customWidth="1" min="80" max="80"/>
+    <col width="10" customWidth="1" min="81" max="81"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24425,6 +24678,9 @@
       <c r="CB1" s="1" t="n">
         <v>20260116</v>
       </c>
+      <c r="CC1" s="1" t="n">
+        <v>20260120</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24671,6 +24927,9 @@
       <c r="CB2" t="n">
         <v>0</v>
       </c>
+      <c r="CC2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -24917,6 +25176,9 @@
       <c r="CB3" t="n">
         <v>60</v>
       </c>
+      <c r="CC3" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -25163,6 +25425,9 @@
       <c r="CB4" t="n">
         <v>82</v>
       </c>
+      <c r="CC4" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -25409,6 +25674,9 @@
       <c r="CB5" t="n">
         <v>10</v>
       </c>
+      <c r="CC5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -25655,6 +25923,9 @@
       <c r="CB6" t="n">
         <v>0</v>
       </c>
+      <c r="CC6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -25901,6 +26172,9 @@
       <c r="CB7" t="n">
         <v>69</v>
       </c>
+      <c r="CC7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -26147,6 +26421,9 @@
       <c r="CB8" t="n">
         <v>12</v>
       </c>
+      <c r="CC8" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -26393,6 +26670,9 @@
       <c r="CB9" t="n">
         <v>97</v>
       </c>
+      <c r="CC9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26638,6 +26918,9 @@
       </c>
       <c r="CB10" t="n">
         <v>11</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -26651,7 +26934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN10"/>
+  <dimension ref="A1:AO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -26694,6 +26977,7 @@
     <col width="10" customWidth="1" min="38" max="38"/>
     <col width="10" customWidth="1" min="39" max="39"/>
     <col width="10" customWidth="1" min="40" max="40"/>
+    <col width="10" customWidth="1" min="41" max="41"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26821,6 +27105,9 @@
       <c r="AN1" s="1" t="n">
         <v>20260116</v>
       </c>
+      <c r="AO1" s="1" t="n">
+        <v>20260120</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -26947,6 +27234,9 @@
       <c r="AN2" t="n">
         <v>0</v>
       </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -27073,6 +27363,9 @@
       <c r="AN3" t="n">
         <v>60</v>
       </c>
+      <c r="AO3" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -27199,6 +27492,9 @@
       <c r="AN4" t="n">
         <v>93</v>
       </c>
+      <c r="AO4" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -27325,6 +27621,9 @@
       <c r="AN5" t="n">
         <v>4</v>
       </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -27451,6 +27750,9 @@
       <c r="AN6" t="n">
         <v>0</v>
       </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -27577,6 +27879,9 @@
       <c r="AN7" t="n">
         <v>42</v>
       </c>
+      <c r="AO7" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -27703,6 +28008,9 @@
       <c r="AN8" t="n">
         <v>31</v>
       </c>
+      <c r="AO8" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -27829,6 +28137,9 @@
       <c r="AN9" t="n">
         <v>98</v>
       </c>
+      <c r="AO9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27954,6 +28265,9 @@
       </c>
       <c r="AN10" t="n">
         <v>47</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -27967,7 +28281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -28050,6 +28364,7 @@
     <col width="10" customWidth="1" min="78" max="78"/>
     <col width="10" customWidth="1" min="79" max="79"/>
     <col width="10" customWidth="1" min="80" max="80"/>
+    <col width="10" customWidth="1" min="81" max="81"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28297,6 +28612,9 @@
       <c r="CB1" s="1" t="n">
         <v>20260116</v>
       </c>
+      <c r="CC1" s="1" t="n">
+        <v>20260120</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -28543,6 +28861,9 @@
       <c r="CB2" t="n">
         <v>-82</v>
       </c>
+      <c r="CC2" t="n">
+        <v>-118</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -28789,6 +29110,9 @@
       <c r="CB3" t="n">
         <v>27</v>
       </c>
+      <c r="CC3" t="n">
+        <v>-34</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -29035,6 +29359,9 @@
       <c r="CB4" t="n">
         <v>53</v>
       </c>
+      <c r="CC4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -29281,6 +29608,9 @@
       <c r="CB5" t="n">
         <v>-92</v>
       </c>
+      <c r="CC5" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -29527,6 +29857,9 @@
       <c r="CB6" t="n">
         <v>-80</v>
       </c>
+      <c r="CC6" t="n">
+        <v>-84</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -29773,6 +30106,9 @@
       <c r="CB7" t="n">
         <v>1</v>
       </c>
+      <c r="CC7" t="n">
+        <v>-128</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -30019,6 +30355,9 @@
       <c r="CB8" t="n">
         <v>-70</v>
       </c>
+      <c r="CC8" t="n">
+        <v>-75</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -30265,6 +30604,9 @@
       <c r="CB9" t="n">
         <v>89</v>
       </c>
+      <c r="CC9" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -30510,6 +30852,9 @@
       </c>
       <c r="CB10" t="n">
         <v>-44</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>-79</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -645,6 +645,7 @@
     <col width="10" customWidth="1" min="39" max="39"/>
     <col width="10" customWidth="1" min="40" max="40"/>
     <col width="10" customWidth="1" min="41" max="41"/>
+    <col width="10" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -775,6 +776,9 @@
       <c r="AO1" s="1" t="n">
         <v>20260120</v>
       </c>
+      <c r="AP1" s="1" t="n">
+        <v>20260121</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -904,6 +908,9 @@
       <c r="AO2" t="n">
         <v>-160</v>
       </c>
+      <c r="AP2" t="n">
+        <v>-144</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1033,6 +1040,9 @@
       <c r="AO3" t="n">
         <v>-13</v>
       </c>
+      <c r="AP3" t="n">
+        <v>-12</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1162,6 +1172,9 @@
       <c r="AO4" t="n">
         <v>44</v>
       </c>
+      <c r="AP4" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1291,6 +1304,9 @@
       <c r="AO5" t="n">
         <v>-91</v>
       </c>
+      <c r="AP5" t="n">
+        <v>-112</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1420,6 +1436,9 @@
       <c r="AO6" t="n">
         <v>-32</v>
       </c>
+      <c r="AP6" t="n">
+        <v>-31</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1549,6 +1568,9 @@
       <c r="AO7" t="n">
         <v>-54</v>
       </c>
+      <c r="AP7" t="n">
+        <v>-20</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1678,6 +1700,9 @@
       <c r="AO8" t="n">
         <v>-54</v>
       </c>
+      <c r="AP8" t="n">
+        <v>-66</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1807,6 +1832,9 @@
       <c r="AO9" t="n">
         <v>138</v>
       </c>
+      <c r="AP9" t="n">
+        <v>165</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1935,6 +1963,9 @@
       </c>
       <c r="AO10" t="n">
         <v>-52</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-26</v>
       </c>
     </row>
   </sheetData>
@@ -1948,7 +1979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CC10"/>
+  <dimension ref="A1:CD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2032,6 +2063,7 @@
     <col width="12" customWidth="1" min="79" max="79"/>
     <col width="12" customWidth="1" min="80" max="80"/>
     <col width="12" customWidth="1" min="81" max="81"/>
+    <col width="12" customWidth="1" min="82" max="82"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2440,6 +2472,11 @@
           <t>20260120</t>
         </is>
       </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>20260121</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2689,6 +2726,9 @@
       <c r="CC2" t="n">
         <v>93</v>
       </c>
+      <c r="CD2" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2938,6 +2978,9 @@
       <c r="CC3" t="n">
         <v>98</v>
       </c>
+      <c r="CD3" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3187,6 +3230,9 @@
       <c r="CC4" t="n">
         <v>100</v>
       </c>
+      <c r="CD4" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3436,6 +3482,9 @@
       <c r="CC5" t="n">
         <v>95</v>
       </c>
+      <c r="CD5" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3685,6 +3734,9 @@
       <c r="CC6" t="n">
         <v>96</v>
       </c>
+      <c r="CD6" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3934,6 +3986,9 @@
       <c r="CC7" t="n">
         <v>96</v>
       </c>
+      <c r="CD7" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4183,6 +4238,9 @@
       <c r="CC8" t="n">
         <v>93</v>
       </c>
+      <c r="CD8" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4432,6 +4490,9 @@
       <c r="CC9" t="n">
         <v>107</v>
       </c>
+      <c r="CD9" t="n">
+        <v>109</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4680,6 +4741,9 @@
       </c>
       <c r="CC10" t="n">
         <v>93</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -7042,7 +7106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7086,6 +7150,7 @@
     <col width="12" customWidth="1" min="39" max="39"/>
     <col width="12" customWidth="1" min="40" max="40"/>
     <col width="12" customWidth="1" min="41" max="41"/>
+    <col width="12" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7294,6 +7359,11 @@
           <t>20260120</t>
         </is>
       </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>20260121</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7423,6 +7493,9 @@
       <c r="AO2" t="n">
         <v>89</v>
       </c>
+      <c r="AP2" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7552,6 +7625,9 @@
       <c r="AO3" t="n">
         <v>54</v>
       </c>
+      <c r="AP3" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7681,6 +7757,9 @@
       <c r="AO4" t="n">
         <v>49</v>
       </c>
+      <c r="AP4" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7810,6 +7889,9 @@
       <c r="AO5" t="n">
         <v>54</v>
       </c>
+      <c r="AP5" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7939,6 +8021,9 @@
       <c r="AO6" t="n">
         <v>168</v>
       </c>
+      <c r="AP6" t="n">
+        <v>184</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8068,6 +8153,9 @@
       <c r="AO7" t="n">
         <v>61</v>
       </c>
+      <c r="AP7" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8197,6 +8285,9 @@
       <c r="AO8" t="n">
         <v>41</v>
       </c>
+      <c r="AP8" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8326,6 +8417,9 @@
       <c r="AO9" t="n">
         <v>71</v>
       </c>
+      <c r="AP9" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8454,6 +8548,9 @@
       </c>
       <c r="AO10" t="n">
         <v>41</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -8467,7 +8564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CV10"/>
+  <dimension ref="A1:CW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8570,6 +8667,7 @@
     <col width="12" customWidth="1" min="98" max="98"/>
     <col width="12" customWidth="1" min="99" max="99"/>
     <col width="12" customWidth="1" min="100" max="100"/>
+    <col width="12" customWidth="1" min="101" max="101"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8877,6 +8975,9 @@
       <c r="CV1" s="1" t="n">
         <v>20260120</v>
       </c>
+      <c r="CW1" s="1" t="n">
+        <v>20260121</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9183,6 +9284,9 @@
       <c r="CV2" t="n">
         <v>252.73</v>
       </c>
+      <c r="CW2" t="n">
+        <v>248.7</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9489,6 +9593,9 @@
       <c r="CV3" t="n">
         <v>233.76</v>
       </c>
+      <c r="CW3" t="n">
+        <v>231.085</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9795,6 +9902,9 @@
       <c r="CV4" t="n">
         <v>320.87</v>
       </c>
+      <c r="CW4" t="n">
+        <v>320.92</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10101,6 +10211,9 @@
       <c r="CV5" t="n">
         <v>451.215</v>
       </c>
+      <c r="CW5" t="n">
+        <v>452.595</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10407,6 +10520,9 @@
       <c r="CV6" t="n">
         <v>88.97</v>
       </c>
+      <c r="CW6" t="n">
+        <v>82.515</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10713,6 +10829,9 @@
       <c r="CV7" t="n">
         <v>181.9</v>
       </c>
+      <c r="CW7" t="n">
+        <v>179.05</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11019,6 +11138,9 @@
       <c r="CV8" t="n">
         <v>167.625</v>
       </c>
+      <c r="CW8" t="n">
+        <v>168.402</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11325,6 +11447,9 @@
       <c r="CV9" t="n">
         <v>91.76000000000001</v>
       </c>
+      <c r="CW9" t="n">
+        <v>93.815</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11630,6 +11755,9 @@
       </c>
       <c r="CV10" t="n">
         <v>429.36</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>421.66</v>
       </c>
     </row>
   </sheetData>
@@ -11643,7 +11771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CV10"/>
+  <dimension ref="A1:CW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11746,6 +11874,7 @@
     <col width="12" customWidth="1" min="98" max="98"/>
     <col width="12" customWidth="1" min="99" max="99"/>
     <col width="12" customWidth="1" min="100" max="100"/>
+    <col width="12" customWidth="1" min="101" max="101"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12053,6 +12182,9 @@
       <c r="CV1" s="1" t="n">
         <v>20260120</v>
       </c>
+      <c r="CW1" s="1" t="n">
+        <v>20260121</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12359,6 +12491,9 @@
       <c r="CV2" t="n">
         <v>254.79</v>
       </c>
+      <c r="CW2" t="n">
+        <v>251.56</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12665,6 +12800,9 @@
       <c r="CV3" t="n">
         <v>235.09</v>
       </c>
+      <c r="CW3" t="n">
+        <v>232.3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12971,6 +13109,9 @@
       <c r="CV4" t="n">
         <v>327.73</v>
       </c>
+      <c r="CW4" t="n">
+        <v>332.4799</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13277,6 +13418,9 @@
       <c r="CV5" t="n">
         <v>456.8</v>
       </c>
+      <c r="CW5" t="n">
+        <v>452.69</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13583,6 +13727,9 @@
       <c r="CV6" t="n">
         <v>89.90000000000001</v>
       </c>
+      <c r="CW6" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13889,6 +14036,9 @@
       <c r="CV7" t="n">
         <v>182.3786</v>
       </c>
+      <c r="CW7" t="n">
+        <v>185.379</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14195,6 +14345,9 @@
       <c r="CV8" t="n">
         <v>171.97</v>
       </c>
+      <c r="CW8" t="n">
+        <v>169.49</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14501,6 +14654,9 @@
       <c r="CV9" t="n">
         <v>93.81</v>
       </c>
+      <c r="CW9" t="n">
+        <v>96.52</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14806,6 +14962,9 @@
       </c>
       <c r="CV10" t="n">
         <v>430.725</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>438.2</v>
       </c>
     </row>
   </sheetData>
@@ -14819,7 +14978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CV10"/>
+  <dimension ref="A1:CW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14922,6 +15081,7 @@
     <col width="12" customWidth="1" min="98" max="98"/>
     <col width="12" customWidth="1" min="99" max="99"/>
     <col width="12" customWidth="1" min="100" max="100"/>
+    <col width="12" customWidth="1" min="101" max="101"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15229,6 +15389,9 @@
       <c r="CV1" s="1" t="n">
         <v>20260120</v>
       </c>
+      <c r="CW1" s="1" t="n">
+        <v>20260121</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15535,6 +15698,9 @@
       <c r="CV2" t="n">
         <v>243.42</v>
       </c>
+      <c r="CW2" t="n">
+        <v>245.18</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15841,6 +16007,9 @@
       <c r="CV3" t="n">
         <v>229.34</v>
       </c>
+      <c r="CW3" t="n">
+        <v>226.88</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16147,6 +16316,9 @@
       <c r="CV4" t="n">
         <v>320.43</v>
       </c>
+      <c r="CW4" t="n">
+        <v>319.3518</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16453,6 +16625,9 @@
       <c r="CV5" t="n">
         <v>449.28</v>
       </c>
+      <c r="CW5" t="n">
+        <v>438.68</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16759,6 +16934,9 @@
       <c r="CV6" t="n">
         <v>87.02</v>
       </c>
+      <c r="CW6" t="n">
+        <v>81.93000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17065,6 +17243,9 @@
       <c r="CV7" t="n">
         <v>177.61</v>
       </c>
+      <c r="CW7" t="n">
+        <v>178.4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17371,6 +17552,9 @@
       <c r="CV8" t="n">
         <v>166.24</v>
       </c>
+      <c r="CW8" t="n">
+        <v>161.11</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17677,6 +17861,9 @@
       <c r="CV9" t="n">
         <v>90.78</v>
       </c>
+      <c r="CW9" t="n">
+        <v>93.7308</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17982,6 +18169,9 @@
       </c>
       <c r="CV10" t="n">
         <v>417.44</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>419.6201</v>
       </c>
     </row>
   </sheetData>
@@ -17995,7 +18185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CV10"/>
+  <dimension ref="A1:CW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18098,6 +18288,7 @@
     <col width="12" customWidth="1" min="98" max="98"/>
     <col width="12" customWidth="1" min="99" max="99"/>
     <col width="12" customWidth="1" min="100" max="100"/>
+    <col width="12" customWidth="1" min="101" max="101"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18405,6 +18596,9 @@
       <c r="CV1" s="1" t="n">
         <v>20260120</v>
       </c>
+      <c r="CW1" s="1" t="n">
+        <v>20260121</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18711,6 +18905,9 @@
       <c r="CV2" t="n">
         <v>246.7</v>
       </c>
+      <c r="CW2" t="n">
+        <v>247.65</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19017,6 +19214,9 @@
       <c r="CV3" t="n">
         <v>231</v>
       </c>
+      <c r="CW3" t="n">
+        <v>231.31</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19323,6 +19523,9 @@
       <c r="CV4" t="n">
         <v>322</v>
       </c>
+      <c r="CW4" t="n">
+        <v>328.38</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19629,6 +19832,9 @@
       <c r="CV5" t="n">
         <v>454.52</v>
       </c>
+      <c r="CW5" t="n">
+        <v>444.11</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19935,6 +20141,9 @@
       <c r="CV6" t="n">
         <v>87.26000000000001</v>
       </c>
+      <c r="CW6" t="n">
+        <v>85.36</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20241,6 +20450,9 @@
       <c r="CV7" t="n">
         <v>178.07</v>
       </c>
+      <c r="CW7" t="n">
+        <v>183.32</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20547,6 +20759,9 @@
       <c r="CV8" t="n">
         <v>168.53</v>
       </c>
+      <c r="CW8" t="n">
+        <v>165.33</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20853,6 +21068,9 @@
       <c r="CV9" t="n">
         <v>93.66</v>
       </c>
+      <c r="CW9" t="n">
+        <v>96.43000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21158,6 +21376,9 @@
       </c>
       <c r="CV10" t="n">
         <v>419.25</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>431.44</v>
       </c>
     </row>
   </sheetData>
@@ -21171,7 +21392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CV10"/>
+  <dimension ref="A1:CW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21274,6 +21495,7 @@
     <col width="12" customWidth="1" min="98" max="98"/>
     <col width="12" customWidth="1" min="99" max="99"/>
     <col width="12" customWidth="1" min="100" max="100"/>
+    <col width="12" customWidth="1" min="101" max="101"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21581,6 +21803,9 @@
       <c r="CV1" s="1" t="n">
         <v>20260120</v>
       </c>
+      <c r="CW1" s="1" t="n">
+        <v>20260121</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21887,6 +22112,9 @@
       <c r="CV2" t="n">
         <v>80267517</v>
       </c>
+      <c r="CW2" t="n">
+        <v>54641725</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22193,6 +22421,9 @@
       <c r="CV3" t="n">
         <v>47737854</v>
       </c>
+      <c r="CW3" t="n">
+        <v>47276090</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22499,6 +22730,9 @@
       <c r="CV4" t="n">
         <v>35361045</v>
       </c>
+      <c r="CW4" t="n">
+        <v>35386603</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -22805,6 +23039,9 @@
       <c r="CV5" t="n">
         <v>26129992</v>
       </c>
+      <c r="CW5" t="n">
+        <v>37980510</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23111,6 +23348,9 @@
       <c r="CV6" t="n">
         <v>109729663</v>
       </c>
+      <c r="CW6" t="n">
+        <v>127940744</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23417,6 +23657,9 @@
       <c r="CV7" t="n">
         <v>223345257</v>
       </c>
+      <c r="CW7" t="n">
+        <v>200380959</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23723,6 +23966,9 @@
       <c r="CV8" t="n">
         <v>36708497</v>
       </c>
+      <c r="CW8" t="n">
+        <v>47851224</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24029,6 +24275,9 @@
       <c r="CV9" t="n">
         <v>13555205</v>
       </c>
+      <c r="CW9" t="n">
+        <v>17118139</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24334,6 +24583,9 @@
       </c>
       <c r="CV10" t="n">
         <v>63187336</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>68123987</v>
       </c>
     </row>
   </sheetData>
@@ -24347,7 +24599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CC10"/>
+  <dimension ref="A1:CD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24431,6 +24683,7 @@
     <col width="10" customWidth="1" min="79" max="79"/>
     <col width="10" customWidth="1" min="80" max="80"/>
     <col width="10" customWidth="1" min="81" max="81"/>
+    <col width="10" customWidth="1" min="82" max="82"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24681,6 +24934,9 @@
       <c r="CC1" s="1" t="n">
         <v>20260120</v>
       </c>
+      <c r="CD1" s="1" t="n">
+        <v>20260121</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24930,6 +25186,9 @@
       <c r="CC2" t="n">
         <v>0</v>
       </c>
+      <c r="CD2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25179,6 +25438,9 @@
       <c r="CC3" t="n">
         <v>22</v>
       </c>
+      <c r="CD3" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -25428,6 +25690,9 @@
       <c r="CC4" t="n">
         <v>52</v>
       </c>
+      <c r="CD4" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -25677,6 +25942,9 @@
       <c r="CC5" t="n">
         <v>0</v>
       </c>
+      <c r="CD5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -25926,6 +26194,9 @@
       <c r="CC6" t="n">
         <v>0</v>
       </c>
+      <c r="CD6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -26175,6 +26446,9 @@
       <c r="CC7" t="n">
         <v>0</v>
       </c>
+      <c r="CD7" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -26424,6 +26698,9 @@
       <c r="CC8" t="n">
         <v>3</v>
       </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -26673,6 +26950,9 @@
       <c r="CC9" t="n">
         <v>100</v>
       </c>
+      <c r="CD9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26921,6 +27201,9 @@
       </c>
       <c r="CC10" t="n">
         <v>0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -26934,7 +27217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -26978,6 +27261,7 @@
     <col width="10" customWidth="1" min="39" max="39"/>
     <col width="10" customWidth="1" min="40" max="40"/>
     <col width="10" customWidth="1" min="41" max="41"/>
+    <col width="10" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27108,6 +27392,9 @@
       <c r="AO1" s="1" t="n">
         <v>20260120</v>
       </c>
+      <c r="AP1" s="1" t="n">
+        <v>20260121</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -27237,6 +27524,9 @@
       <c r="AO2" t="n">
         <v>0</v>
       </c>
+      <c r="AP2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -27366,6 +27656,9 @@
       <c r="AO3" t="n">
         <v>38</v>
       </c>
+      <c r="AP3" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -27495,6 +27788,9 @@
       <c r="AO4" t="n">
         <v>83</v>
       </c>
+      <c r="AP4" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -27624,6 +27920,9 @@
       <c r="AO5" t="n">
         <v>0</v>
       </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -27753,6 +28052,9 @@
       <c r="AO6" t="n">
         <v>0</v>
       </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -27882,6 +28184,9 @@
       <c r="AO7" t="n">
         <v>20</v>
       </c>
+      <c r="AP7" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -28011,6 +28316,9 @@
       <c r="AO8" t="n">
         <v>26</v>
       </c>
+      <c r="AP8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -28140,6 +28448,9 @@
       <c r="AO9" t="n">
         <v>100</v>
       </c>
+      <c r="AP9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28268,6 +28579,9 @@
       </c>
       <c r="AO10" t="n">
         <v>29</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -28281,7 +28595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CC10"/>
+  <dimension ref="A1:CD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -28365,6 +28679,7 @@
     <col width="10" customWidth="1" min="79" max="79"/>
     <col width="10" customWidth="1" min="80" max="80"/>
     <col width="10" customWidth="1" min="81" max="81"/>
+    <col width="10" customWidth="1" min="82" max="82"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28615,6 +28930,9 @@
       <c r="CC1" s="1" t="n">
         <v>20260120</v>
       </c>
+      <c r="CD1" s="1" t="n">
+        <v>20260121</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -28864,6 +29182,9 @@
       <c r="CC2" t="n">
         <v>-118</v>
       </c>
+      <c r="CD2" t="n">
+        <v>-95</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -29113,6 +29434,9 @@
       <c r="CC3" t="n">
         <v>-34</v>
       </c>
+      <c r="CD3" t="n">
+        <v>-34</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -29362,6 +29686,9 @@
       <c r="CC4" t="n">
         <v>8</v>
       </c>
+      <c r="CD4" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -29611,6 +29938,9 @@
       <c r="CC5" t="n">
         <v>-100</v>
       </c>
+      <c r="CD5" t="n">
+        <v>-117</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -29860,6 +30190,9 @@
       <c r="CC6" t="n">
         <v>-84</v>
       </c>
+      <c r="CD6" t="n">
+        <v>-105</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -30109,6 +30442,9 @@
       <c r="CC7" t="n">
         <v>-128</v>
       </c>
+      <c r="CD7" t="n">
+        <v>-51</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -30358,6 +30694,9 @@
       <c r="CC8" t="n">
         <v>-75</v>
       </c>
+      <c r="CD8" t="n">
+        <v>-85</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -30607,6 +30946,9 @@
       <c r="CC9" t="n">
         <v>88</v>
       </c>
+      <c r="CD9" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -30855,6 +31197,9 @@
       </c>
       <c r="CC10" t="n">
         <v>-79</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>-45</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP10"/>
+  <dimension ref="A1:AQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -646,6 +646,7 @@
     <col width="10" customWidth="1" min="40" max="40"/>
     <col width="10" customWidth="1" min="41" max="41"/>
     <col width="10" customWidth="1" min="42" max="42"/>
+    <col width="10" customWidth="1" min="43" max="43"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -779,6 +780,9 @@
       <c r="AP1" s="1" t="n">
         <v>20260121</v>
       </c>
+      <c r="AQ1" s="1" t="n">
+        <v>20260122</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -911,6 +915,9 @@
       <c r="AP2" t="n">
         <v>-144</v>
       </c>
+      <c r="AQ2" t="n">
+        <v>-131</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1043,6 +1050,9 @@
       <c r="AP3" t="n">
         <v>-12</v>
       </c>
+      <c r="AQ3" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1175,6 +1185,9 @@
       <c r="AP4" t="n">
         <v>59</v>
       </c>
+      <c r="AQ4" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1307,6 +1320,9 @@
       <c r="AP5" t="n">
         <v>-112</v>
       </c>
+      <c r="AQ5" t="n">
+        <v>-91</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1439,6 +1455,9 @@
       <c r="AP6" t="n">
         <v>-31</v>
       </c>
+      <c r="AQ6" t="n">
+        <v>-30</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1571,6 +1590,9 @@
       <c r="AP7" t="n">
         <v>-20</v>
       </c>
+      <c r="AQ7" t="n">
+        <v>-11</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1703,6 +1725,9 @@
       <c r="AP8" t="n">
         <v>-66</v>
       </c>
+      <c r="AQ8" t="n">
+        <v>-62</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1835,6 +1860,9 @@
       <c r="AP9" t="n">
         <v>165</v>
       </c>
+      <c r="AQ9" t="n">
+        <v>142</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1966,6 +1994,9 @@
       </c>
       <c r="AP10" t="n">
         <v>-26</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1979,7 +2010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CD10"/>
+  <dimension ref="A1:CE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2064,6 +2095,7 @@
     <col width="12" customWidth="1" min="80" max="80"/>
     <col width="12" customWidth="1" min="81" max="81"/>
     <col width="12" customWidth="1" min="82" max="82"/>
+    <col width="12" customWidth="1" min="83" max="83"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2477,6 +2509,11 @@
           <t>20260121</t>
         </is>
       </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>20260122</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2729,6 +2766,9 @@
       <c r="CD2" t="n">
         <v>94</v>
       </c>
+      <c r="CE2" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2981,6 +3021,9 @@
       <c r="CD3" t="n">
         <v>98</v>
       </c>
+      <c r="CE3" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3233,6 +3276,9 @@
       <c r="CD4" t="n">
         <v>102</v>
       </c>
+      <c r="CE4" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3485,6 +3531,9 @@
       <c r="CD5" t="n">
         <v>94</v>
       </c>
+      <c r="CE5" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3737,6 +3786,9 @@
       <c r="CD6" t="n">
         <v>94</v>
       </c>
+      <c r="CE6" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3989,6 +4041,9 @@
       <c r="CD7" t="n">
         <v>98</v>
       </c>
+      <c r="CE7" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4241,6 +4296,9 @@
       <c r="CD8" t="n">
         <v>92</v>
       </c>
+      <c r="CE8" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4493,6 +4551,9 @@
       <c r="CD9" t="n">
         <v>109</v>
       </c>
+      <c r="CE9" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4744,6 +4805,9 @@
       </c>
       <c r="CD10" t="n">
         <v>96</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -7106,7 +7170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP10"/>
+  <dimension ref="A1:AQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7151,6 +7215,7 @@
     <col width="12" customWidth="1" min="40" max="40"/>
     <col width="12" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="12" customWidth="1" min="43" max="43"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7364,6 +7429,11 @@
           <t>20260121</t>
         </is>
       </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>20260122</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7496,6 +7566,9 @@
       <c r="AP2" t="n">
         <v>60</v>
       </c>
+      <c r="AQ2" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7628,6 +7701,9 @@
       <c r="AP3" t="n">
         <v>53</v>
       </c>
+      <c r="AQ3" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7760,6 +7836,9 @@
       <c r="AP4" t="n">
         <v>49</v>
       </c>
+      <c r="AQ4" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7892,6 +7971,9 @@
       <c r="AP5" t="n">
         <v>78</v>
       </c>
+      <c r="AQ5" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8024,6 +8106,9 @@
       <c r="AP6" t="n">
         <v>184</v>
       </c>
+      <c r="AQ6" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8156,6 +8241,9 @@
       <c r="AP7" t="n">
         <v>54</v>
       </c>
+      <c r="AQ7" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8288,6 +8376,9 @@
       <c r="AP8" t="n">
         <v>53</v>
       </c>
+      <c r="AQ8" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8420,6 +8511,9 @@
       <c r="AP9" t="n">
         <v>88</v>
       </c>
+      <c r="AQ9" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8551,6 +8645,9 @@
       </c>
       <c r="AP10" t="n">
         <v>45</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -8564,7 +8661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW10"/>
+  <dimension ref="A1:CX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8668,6 +8765,7 @@
     <col width="12" customWidth="1" min="99" max="99"/>
     <col width="12" customWidth="1" min="100" max="100"/>
     <col width="12" customWidth="1" min="101" max="101"/>
+    <col width="12" customWidth="1" min="102" max="102"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8978,6 +9076,9 @@
       <c r="CW1" s="1" t="n">
         <v>20260121</v>
       </c>
+      <c r="CX1" s="1" t="n">
+        <v>20260122</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9287,6 +9388,9 @@
       <c r="CW2" t="n">
         <v>248.7</v>
       </c>
+      <c r="CX2" t="n">
+        <v>249.2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9596,6 +9700,9 @@
       <c r="CW3" t="n">
         <v>231.085</v>
       </c>
+      <c r="CX3" t="n">
+        <v>234.045</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9905,6 +10012,9 @@
       <c r="CW4" t="n">
         <v>320.92</v>
       </c>
+      <c r="CX4" t="n">
+        <v>334.45</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10214,6 +10324,9 @@
       <c r="CW5" t="n">
         <v>452.595</v>
       </c>
+      <c r="CX5" t="n">
+        <v>447.62</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10523,6 +10636,9 @@
       <c r="CW6" t="n">
         <v>82.515</v>
       </c>
+      <c r="CX6" t="n">
+        <v>85.02</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10832,6 +10948,9 @@
       <c r="CW7" t="n">
         <v>179.05</v>
       </c>
+      <c r="CX7" t="n">
+        <v>184.75</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11141,6 +11260,9 @@
       <c r="CW8" t="n">
         <v>168.402</v>
       </c>
+      <c r="CX8" t="n">
+        <v>168.925</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11450,6 +11572,9 @@
       <c r="CW9" t="n">
         <v>93.815</v>
       </c>
+      <c r="CX9" t="n">
+        <v>96.47</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11758,6 +11883,9 @@
       </c>
       <c r="CW10" t="n">
         <v>421.66</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>435.16</v>
       </c>
     </row>
   </sheetData>
@@ -11771,7 +11899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW10"/>
+  <dimension ref="A1:CX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11875,6 +12003,7 @@
     <col width="12" customWidth="1" min="99" max="99"/>
     <col width="12" customWidth="1" min="100" max="100"/>
     <col width="12" customWidth="1" min="101" max="101"/>
+    <col width="12" customWidth="1" min="102" max="102"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12185,6 +12314,9 @@
       <c r="CW1" s="1" t="n">
         <v>20260121</v>
       </c>
+      <c r="CX1" s="1" t="n">
+        <v>20260122</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12494,6 +12626,9 @@
       <c r="CW2" t="n">
         <v>251.56</v>
       </c>
+      <c r="CX2" t="n">
+        <v>251</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12803,6 +12938,9 @@
       <c r="CW3" t="n">
         <v>232.3</v>
       </c>
+      <c r="CX3" t="n">
+        <v>235.72</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13112,6 +13250,9 @@
       <c r="CW4" t="n">
         <v>332.4799</v>
       </c>
+      <c r="CX4" t="n">
+        <v>335.15</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13421,6 +13562,9 @@
       <c r="CW5" t="n">
         <v>452.69</v>
       </c>
+      <c r="CX5" t="n">
+        <v>452.84</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13730,6 +13874,9 @@
       <c r="CW6" t="n">
         <v>86</v>
       </c>
+      <c r="CX6" t="n">
+        <v>85.09999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14039,6 +14186,9 @@
       <c r="CW7" t="n">
         <v>185.379</v>
       </c>
+      <c r="CX7" t="n">
+        <v>186.17</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14348,6 +14498,9 @@
       <c r="CW8" t="n">
         <v>169.49</v>
       </c>
+      <c r="CX8" t="n">
+        <v>169</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14657,6 +14810,9 @@
       <c r="CW9" t="n">
         <v>96.52</v>
       </c>
+      <c r="CX9" t="n">
+        <v>97.8</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14965,6 +15121,9 @@
       </c>
       <c r="CW10" t="n">
         <v>438.2</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>449.5</v>
       </c>
     </row>
   </sheetData>
@@ -14978,7 +15137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW10"/>
+  <dimension ref="A1:CX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15082,6 +15241,7 @@
     <col width="12" customWidth="1" min="99" max="99"/>
     <col width="12" customWidth="1" min="100" max="100"/>
     <col width="12" customWidth="1" min="101" max="101"/>
+    <col width="12" customWidth="1" min="102" max="102"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15392,6 +15552,9 @@
       <c r="CW1" s="1" t="n">
         <v>20260121</v>
       </c>
+      <c r="CX1" s="1" t="n">
+        <v>20260122</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15701,6 +15864,9 @@
       <c r="CW2" t="n">
         <v>245.18</v>
       </c>
+      <c r="CX2" t="n">
+        <v>248.15</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16010,6 +16176,9 @@
       <c r="CW3" t="n">
         <v>226.88</v>
       </c>
+      <c r="CX3" t="n">
+        <v>230.9</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16319,6 +16488,9 @@
       <c r="CW4" t="n">
         <v>319.3518</v>
       </c>
+      <c r="CX4" t="n">
+        <v>328.75</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16628,6 +16800,9 @@
       <c r="CW5" t="n">
         <v>438.68</v>
       </c>
+      <c r="CX5" t="n">
+        <v>444.7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16937,6 +17112,9 @@
       <c r="CW6" t="n">
         <v>81.93000000000001</v>
       </c>
+      <c r="CX6" t="n">
+        <v>82.98</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17246,6 +17424,9 @@
       <c r="CW7" t="n">
         <v>178.4</v>
       </c>
+      <c r="CX7" t="n">
+        <v>183.93</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17555,6 +17736,9 @@
       <c r="CW8" t="n">
         <v>161.11</v>
       </c>
+      <c r="CX8" t="n">
+        <v>164.95</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17864,6 +18048,9 @@
       <c r="CW9" t="n">
         <v>93.7308</v>
       </c>
+      <c r="CX9" t="n">
+        <v>94.86</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18172,6 +18359,9 @@
       </c>
       <c r="CW10" t="n">
         <v>419.6201</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>432.6293</v>
       </c>
     </row>
   </sheetData>
@@ -18185,7 +18375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW10"/>
+  <dimension ref="A1:CX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18289,6 +18479,7 @@
     <col width="12" customWidth="1" min="99" max="99"/>
     <col width="12" customWidth="1" min="100" max="100"/>
     <col width="12" customWidth="1" min="101" max="101"/>
+    <col width="12" customWidth="1" min="102" max="102"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18599,6 +18790,9 @@
       <c r="CW1" s="1" t="n">
         <v>20260121</v>
       </c>
+      <c r="CX1" s="1" t="n">
+        <v>20260122</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18908,6 +19102,9 @@
       <c r="CW2" t="n">
         <v>247.65</v>
       </c>
+      <c r="CX2" t="n">
+        <v>248.35</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19217,6 +19414,9 @@
       <c r="CW3" t="n">
         <v>231.31</v>
       </c>
+      <c r="CX3" t="n">
+        <v>234.34</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19526,6 +19726,9 @@
       <c r="CW4" t="n">
         <v>328.38</v>
       </c>
+      <c r="CX4" t="n">
+        <v>330.54</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19835,6 +20038,9 @@
       <c r="CW5" t="n">
         <v>444.11</v>
       </c>
+      <c r="CX5" t="n">
+        <v>451.14</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20144,6 +20350,9 @@
       <c r="CW6" t="n">
         <v>85.36</v>
       </c>
+      <c r="CX6" t="n">
+        <v>83.54000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20453,6 +20662,9 @@
       <c r="CW7" t="n">
         <v>183.32</v>
       </c>
+      <c r="CX7" t="n">
+        <v>184.84</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20762,6 +20974,9 @@
       <c r="CW8" t="n">
         <v>165.33</v>
       </c>
+      <c r="CX8" t="n">
+        <v>165.9</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21071,6 +21286,9 @@
       <c r="CW9" t="n">
         <v>96.43000000000001</v>
       </c>
+      <c r="CX9" t="n">
+        <v>95.83</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21379,6 +21597,9 @@
       </c>
       <c r="CW10" t="n">
         <v>431.44</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>449.36</v>
       </c>
     </row>
   </sheetData>
@@ -21392,7 +21613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW10"/>
+  <dimension ref="A1:CX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21496,6 +21717,7 @@
     <col width="12" customWidth="1" min="99" max="99"/>
     <col width="12" customWidth="1" min="100" max="100"/>
     <col width="12" customWidth="1" min="101" max="101"/>
+    <col width="12" customWidth="1" min="102" max="102"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21806,6 +22028,9 @@
       <c r="CW1" s="1" t="n">
         <v>20260121</v>
       </c>
+      <c r="CX1" s="1" t="n">
+        <v>20260122</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22115,6 +22340,9 @@
       <c r="CW2" t="n">
         <v>54641725</v>
       </c>
+      <c r="CX2" t="n">
+        <v>39708340</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22424,6 +22652,9 @@
       <c r="CW3" t="n">
         <v>47276090</v>
       </c>
+      <c r="CX3" t="n">
+        <v>31913325</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22733,6 +22964,9 @@
       <c r="CW4" t="n">
         <v>35386603</v>
       </c>
+      <c r="CX4" t="n">
+        <v>26253640</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23042,6 +23276,9 @@
       <c r="CW5" t="n">
         <v>37980510</v>
       </c>
+      <c r="CX5" t="n">
+        <v>25349378</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23351,6 +23588,9 @@
       <c r="CW6" t="n">
         <v>127940744</v>
       </c>
+      <c r="CX6" t="n">
+        <v>69113304</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23660,6 +23900,9 @@
       <c r="CW7" t="n">
         <v>200380959</v>
       </c>
+      <c r="CX7" t="n">
+        <v>139636626</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23969,6 +24212,9 @@
       <c r="CW8" t="n">
         <v>47851224</v>
       </c>
+      <c r="CX8" t="n">
+        <v>28499472</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24278,6 +24524,9 @@
       <c r="CW9" t="n">
         <v>17118139</v>
       </c>
+      <c r="CX9" t="n">
+        <v>14150762</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24586,6 +24835,9 @@
       </c>
       <c r="CW10" t="n">
         <v>68123987</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>71546729</v>
       </c>
     </row>
   </sheetData>
@@ -24599,7 +24851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CD10"/>
+  <dimension ref="A1:CE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24684,6 +24936,7 @@
     <col width="10" customWidth="1" min="80" max="80"/>
     <col width="10" customWidth="1" min="81" max="81"/>
     <col width="10" customWidth="1" min="82" max="82"/>
+    <col width="10" customWidth="1" min="83" max="83"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24937,6 +25190,9 @@
       <c r="CD1" s="1" t="n">
         <v>20260121</v>
       </c>
+      <c r="CE1" s="1" t="n">
+        <v>20260122</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25189,6 +25445,9 @@
       <c r="CD2" t="n">
         <v>4</v>
       </c>
+      <c r="CE2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25441,6 +25700,9 @@
       <c r="CD3" t="n">
         <v>23</v>
       </c>
+      <c r="CE3" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -25693,6 +25955,9 @@
       <c r="CD4" t="n">
         <v>71</v>
       </c>
+      <c r="CE4" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -25945,6 +26210,9 @@
       <c r="CD5" t="n">
         <v>0</v>
       </c>
+      <c r="CE5" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -26197,6 +26465,9 @@
       <c r="CD6" t="n">
         <v>0</v>
       </c>
+      <c r="CE6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -26449,6 +26720,9 @@
       <c r="CD7" t="n">
         <v>39</v>
       </c>
+      <c r="CE7" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -26701,6 +26975,9 @@
       <c r="CD8" t="n">
         <v>0</v>
       </c>
+      <c r="CE8" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -26953,6 +27230,9 @@
       <c r="CD9" t="n">
         <v>100</v>
       </c>
+      <c r="CE9" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27204,6 +27484,9 @@
       </c>
       <c r="CD10" t="n">
         <v>18</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -27217,7 +27500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP10"/>
+  <dimension ref="A1:AQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -27262,6 +27545,7 @@
     <col width="10" customWidth="1" min="40" max="40"/>
     <col width="10" customWidth="1" min="41" max="41"/>
     <col width="10" customWidth="1" min="42" max="42"/>
+    <col width="10" customWidth="1" min="43" max="43"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27395,6 +27679,9 @@
       <c r="AP1" s="1" t="n">
         <v>20260121</v>
       </c>
+      <c r="AQ1" s="1" t="n">
+        <v>20260122</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -27527,6 +27814,9 @@
       <c r="AP2" t="n">
         <v>2</v>
       </c>
+      <c r="AQ2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -27659,6 +27949,9 @@
       <c r="AP3" t="n">
         <v>38</v>
       </c>
+      <c r="AQ3" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -27791,6 +28084,9 @@
       <c r="AP4" t="n">
         <v>90</v>
       </c>
+      <c r="AQ4" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -27923,6 +28219,9 @@
       <c r="AP5" t="n">
         <v>0</v>
       </c>
+      <c r="AQ5" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -28055,6 +28354,9 @@
       <c r="AP6" t="n">
         <v>0</v>
       </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -28187,6 +28489,9 @@
       <c r="AP7" t="n">
         <v>34</v>
       </c>
+      <c r="AQ7" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -28319,6 +28624,9 @@
       <c r="AP8" t="n">
         <v>20</v>
       </c>
+      <c r="AQ8" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -28451,6 +28759,9 @@
       <c r="AP9" t="n">
         <v>100</v>
       </c>
+      <c r="AQ9" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28582,6 +28893,9 @@
       </c>
       <c r="AP10" t="n">
         <v>41</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -28595,7 +28909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CD10"/>
+  <dimension ref="A1:CE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -28680,6 +28994,7 @@
     <col width="10" customWidth="1" min="80" max="80"/>
     <col width="10" customWidth="1" min="81" max="81"/>
     <col width="10" customWidth="1" min="82" max="82"/>
+    <col width="10" customWidth="1" min="83" max="83"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28933,6 +29248,9 @@
       <c r="CD1" s="1" t="n">
         <v>20260121</v>
       </c>
+      <c r="CE1" s="1" t="n">
+        <v>20260122</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -29185,6 +29503,9 @@
       <c r="CD2" t="n">
         <v>-95</v>
       </c>
+      <c r="CE2" t="n">
+        <v>-80</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -29437,6 +29758,9 @@
       <c r="CD3" t="n">
         <v>-34</v>
       </c>
+      <c r="CE3" t="n">
+        <v>-14</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -29689,6 +30013,9 @@
       <c r="CD4" t="n">
         <v>39</v>
       </c>
+      <c r="CE4" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -29941,6 +30268,9 @@
       <c r="CD5" t="n">
         <v>-117</v>
       </c>
+      <c r="CE5" t="n">
+        <v>-79</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -30193,6 +30523,9 @@
       <c r="CD6" t="n">
         <v>-105</v>
       </c>
+      <c r="CE6" t="n">
+        <v>-113</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -30445,6 +30778,9 @@
       <c r="CD7" t="n">
         <v>-51</v>
       </c>
+      <c r="CE7" t="n">
+        <v>-28</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -30697,6 +31033,9 @@
       <c r="CD8" t="n">
         <v>-85</v>
       </c>
+      <c r="CE8" t="n">
+        <v>-75</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -30949,6 +31288,9 @@
       <c r="CD9" t="n">
         <v>107</v>
       </c>
+      <c r="CE9" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -31200,6 +31542,9 @@
       </c>
       <c r="CD10" t="n">
         <v>-45</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ10"/>
+  <dimension ref="A1:AR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -647,6 +647,7 @@
     <col width="10" customWidth="1" min="41" max="41"/>
     <col width="10" customWidth="1" min="42" max="42"/>
     <col width="10" customWidth="1" min="43" max="43"/>
+    <col width="10" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -783,6 +784,9 @@
       <c r="AQ1" s="1" t="n">
         <v>20260122</v>
       </c>
+      <c r="AR1" s="1" t="n">
+        <v>20260123</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -918,6 +922,9 @@
       <c r="AQ2" t="n">
         <v>-131</v>
       </c>
+      <c r="AR2" t="n">
+        <v>-124</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1053,6 +1060,9 @@
       <c r="AQ3" t="n">
         <v>4</v>
       </c>
+      <c r="AR3" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1188,6 +1198,9 @@
       <c r="AQ4" t="n">
         <v>64</v>
       </c>
+      <c r="AR4" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1323,6 +1336,9 @@
       <c r="AQ5" t="n">
         <v>-91</v>
       </c>
+      <c r="AR5" t="n">
+        <v>-53</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1458,6 +1474,9 @@
       <c r="AQ6" t="n">
         <v>-30</v>
       </c>
+      <c r="AR6" t="n">
+        <v>-29</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1593,6 +1612,9 @@
       <c r="AQ7" t="n">
         <v>-11</v>
       </c>
+      <c r="AR7" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1728,6 +1750,9 @@
       <c r="AQ8" t="n">
         <v>-62</v>
       </c>
+      <c r="AR8" t="n">
+        <v>-44</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1863,6 +1888,9 @@
       <c r="AQ9" t="n">
         <v>142</v>
       </c>
+      <c r="AR9" t="n">
+        <v>152</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1997,6 +2025,9 @@
       </c>
       <c r="AQ10" t="n">
         <v>12</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -2010,7 +2041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE10"/>
+  <dimension ref="A1:CF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2096,6 +2127,7 @@
     <col width="12" customWidth="1" min="81" max="81"/>
     <col width="12" customWidth="1" min="82" max="82"/>
     <col width="12" customWidth="1" min="83" max="83"/>
+    <col width="12" customWidth="1" min="84" max="84"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2514,6 +2546,11 @@
           <t>20260122</t>
         </is>
       </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>20260123</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2769,6 +2806,9 @@
       <c r="CE2" t="n">
         <v>94</v>
       </c>
+      <c r="CF2" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3024,6 +3064,9 @@
       <c r="CE3" t="n">
         <v>99</v>
       </c>
+      <c r="CF3" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3279,6 +3322,9 @@
       <c r="CE4" t="n">
         <v>102</v>
       </c>
+      <c r="CF4" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3534,6 +3580,9 @@
       <c r="CE5" t="n">
         <v>95</v>
       </c>
+      <c r="CF5" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3789,6 +3838,9 @@
       <c r="CE6" t="n">
         <v>92</v>
       </c>
+      <c r="CF6" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4044,6 +4096,9 @@
       <c r="CE7" t="n">
         <v>99</v>
       </c>
+      <c r="CF7" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4299,6 +4354,9 @@
       <c r="CE8" t="n">
         <v>93</v>
       </c>
+      <c r="CF8" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4554,6 +4612,9 @@
       <c r="CE9" t="n">
         <v>108</v>
       </c>
+      <c r="CF9" t="n">
+        <v>109</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4808,6 +4869,9 @@
       </c>
       <c r="CE10" t="n">
         <v>100</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -7170,7 +7234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ10"/>
+  <dimension ref="A1:AR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7216,6 +7280,7 @@
     <col width="12" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="12" customWidth="1" min="43" max="43"/>
+    <col width="12" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7434,6 +7499,11 @@
           <t>20260122</t>
         </is>
       </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>20260123</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7569,6 +7639,9 @@
       <c r="AQ2" t="n">
         <v>43</v>
       </c>
+      <c r="AR2" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7704,6 +7777,9 @@
       <c r="AQ3" t="n">
         <v>36</v>
       </c>
+      <c r="AR3" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7839,6 +7915,9 @@
       <c r="AQ4" t="n">
         <v>36</v>
       </c>
+      <c r="AR4" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7974,6 +8053,9 @@
       <c r="AQ5" t="n">
         <v>52</v>
       </c>
+      <c r="AR5" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8109,6 +8191,9 @@
       <c r="AQ6" t="n">
         <v>97</v>
       </c>
+      <c r="AR6" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8244,6 +8329,9 @@
       <c r="AQ7" t="n">
         <v>38</v>
       </c>
+      <c r="AR7" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8379,6 +8467,9 @@
       <c r="AQ8" t="n">
         <v>31</v>
       </c>
+      <c r="AR8" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8514,6 +8605,9 @@
       <c r="AQ9" t="n">
         <v>72</v>
       </c>
+      <c r="AR9" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8648,6 +8742,9 @@
       </c>
       <c r="AQ10" t="n">
         <v>48</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -8661,7 +8758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CX10"/>
+  <dimension ref="A1:CY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8766,6 +8863,7 @@
     <col width="12" customWidth="1" min="100" max="100"/>
     <col width="12" customWidth="1" min="101" max="101"/>
     <col width="12" customWidth="1" min="102" max="102"/>
+    <col width="12" customWidth="1" min="103" max="103"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9079,6 +9177,9 @@
       <c r="CX1" s="1" t="n">
         <v>20260122</v>
       </c>
+      <c r="CY1" s="1" t="n">
+        <v>20260123</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9391,6 +9492,9 @@
       <c r="CX2" t="n">
         <v>249.2</v>
       </c>
+      <c r="CY2" t="n">
+        <v>247.32</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9703,6 +9807,9 @@
       <c r="CX3" t="n">
         <v>234.045</v>
       </c>
+      <c r="CY3" t="n">
+        <v>234.955</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10015,6 +10122,9 @@
       <c r="CX4" t="n">
         <v>334.45</v>
       </c>
+      <c r="CY4" t="n">
+        <v>332.485</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10327,6 +10437,9 @@
       <c r="CX5" t="n">
         <v>447.62</v>
       </c>
+      <c r="CY5" t="n">
+        <v>451.87</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10639,6 +10752,9 @@
       <c r="CX6" t="n">
         <v>85.02</v>
       </c>
+      <c r="CY6" t="n">
+        <v>83.43000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10951,6 +11067,9 @@
       <c r="CX7" t="n">
         <v>184.75</v>
       </c>
+      <c r="CY7" t="n">
+        <v>187.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11263,6 +11382,9 @@
       <c r="CX8" t="n">
         <v>168.925</v>
       </c>
+      <c r="CY8" t="n">
+        <v>167.27</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11575,6 +11697,9 @@
       <c r="CX9" t="n">
         <v>96.47</v>
       </c>
+      <c r="CY9" t="n">
+        <v>97.095</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11886,6 +12011,9 @@
       </c>
       <c r="CX10" t="n">
         <v>435.16</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>447.425</v>
       </c>
     </row>
   </sheetData>
@@ -11899,7 +12027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CX10"/>
+  <dimension ref="A1:CY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12004,6 +12132,7 @@
     <col width="12" customWidth="1" min="100" max="100"/>
     <col width="12" customWidth="1" min="101" max="101"/>
     <col width="12" customWidth="1" min="102" max="102"/>
+    <col width="12" customWidth="1" min="103" max="103"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12317,6 +12446,9 @@
       <c r="CX1" s="1" t="n">
         <v>20260122</v>
       </c>
+      <c r="CY1" s="1" t="n">
+        <v>20260123</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12629,6 +12761,9 @@
       <c r="CX2" t="n">
         <v>251</v>
       </c>
+      <c r="CY2" t="n">
+        <v>249.41</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12941,6 +13076,9 @@
       <c r="CX3" t="n">
         <v>235.72</v>
       </c>
+      <c r="CY3" t="n">
+        <v>240.45</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13253,6 +13391,9 @@
       <c r="CX4" t="n">
         <v>335.15</v>
       </c>
+      <c r="CY4" t="n">
+        <v>333.6889</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13565,6 +13706,9 @@
       <c r="CX5" t="n">
         <v>452.84</v>
       </c>
+      <c r="CY5" t="n">
+        <v>471.1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13877,6 +14021,9 @@
       <c r="CX6" t="n">
         <v>85.09999999999999</v>
       </c>
+      <c r="CY6" t="n">
+        <v>86.3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14189,6 +14336,9 @@
       <c r="CX7" t="n">
         <v>186.17</v>
       </c>
+      <c r="CY7" t="n">
+        <v>189.6</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14501,6 +14651,9 @@
       <c r="CX8" t="n">
         <v>169</v>
       </c>
+      <c r="CY8" t="n">
+        <v>172</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14813,6 +14966,9 @@
       <c r="CX9" t="n">
         <v>97.8</v>
       </c>
+      <c r="CY9" t="n">
+        <v>97.89</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15124,6 +15280,9 @@
       </c>
       <c r="CX10" t="n">
         <v>449.5</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>452.43</v>
       </c>
     </row>
   </sheetData>
@@ -15137,7 +15296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CX10"/>
+  <dimension ref="A1:CY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15242,6 +15401,7 @@
     <col width="12" customWidth="1" min="100" max="100"/>
     <col width="12" customWidth="1" min="101" max="101"/>
     <col width="12" customWidth="1" min="102" max="102"/>
+    <col width="12" customWidth="1" min="103" max="103"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15555,6 +15715,9 @@
       <c r="CX1" s="1" t="n">
         <v>20260122</v>
       </c>
+      <c r="CY1" s="1" t="n">
+        <v>20260123</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15867,6 +16030,9 @@
       <c r="CX2" t="n">
         <v>248.15</v>
       </c>
+      <c r="CY2" t="n">
+        <v>244.68</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16179,6 +16345,9 @@
       <c r="CX3" t="n">
         <v>230.9</v>
       </c>
+      <c r="CY3" t="n">
+        <v>234.57</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16491,6 +16660,9 @@
       <c r="CX4" t="n">
         <v>328.75</v>
       </c>
+      <c r="CY4" t="n">
+        <v>327.45</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16803,6 +16975,9 @@
       <c r="CX5" t="n">
         <v>444.7</v>
       </c>
+      <c r="CY5" t="n">
+        <v>450.53</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17115,6 +17290,9 @@
       <c r="CX6" t="n">
         <v>82.98</v>
       </c>
+      <c r="CY6" t="n">
+        <v>83.28</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17427,6 +17605,9 @@
       <c r="CX7" t="n">
         <v>183.93</v>
       </c>
+      <c r="CY7" t="n">
+        <v>186.8233</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17739,6 +17920,9 @@
       <c r="CX8" t="n">
         <v>164.95</v>
       </c>
+      <c r="CY8" t="n">
+        <v>166.3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18051,6 +18235,9 @@
       <c r="CX9" t="n">
         <v>94.86</v>
       </c>
+      <c r="CY9" t="n">
+        <v>95.76000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18362,6 +18549,9 @@
       </c>
       <c r="CX10" t="n">
         <v>432.6293</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>444.04</v>
       </c>
     </row>
   </sheetData>
@@ -18375,7 +18565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CX10"/>
+  <dimension ref="A1:CY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18480,6 +18670,7 @@
     <col width="12" customWidth="1" min="100" max="100"/>
     <col width="12" customWidth="1" min="101" max="101"/>
     <col width="12" customWidth="1" min="102" max="102"/>
+    <col width="12" customWidth="1" min="103" max="103"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18793,6 +18984,9 @@
       <c r="CX1" s="1" t="n">
         <v>20260122</v>
       </c>
+      <c r="CY1" s="1" t="n">
+        <v>20260123</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19105,6 +19299,9 @@
       <c r="CX2" t="n">
         <v>248.35</v>
       </c>
+      <c r="CY2" t="n">
+        <v>248.04</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19417,6 +19614,9 @@
       <c r="CX3" t="n">
         <v>234.34</v>
       </c>
+      <c r="CY3" t="n">
+        <v>239.16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19729,6 +19929,9 @@
       <c r="CX4" t="n">
         <v>330.54</v>
       </c>
+      <c r="CY4" t="n">
+        <v>327.93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20041,6 +20244,9 @@
       <c r="CX5" t="n">
         <v>451.14</v>
       </c>
+      <c r="CY5" t="n">
+        <v>465.95</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20353,6 +20559,9 @@
       <c r="CX6" t="n">
         <v>83.54000000000001</v>
       </c>
+      <c r="CY6" t="n">
+        <v>86.12</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20665,6 +20874,9 @@
       <c r="CX7" t="n">
         <v>184.84</v>
       </c>
+      <c r="CY7" t="n">
+        <v>187.67</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20977,6 +21189,9 @@
       <c r="CX8" t="n">
         <v>165.9</v>
       </c>
+      <c r="CY8" t="n">
+        <v>169.6</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21289,6 +21504,9 @@
       <c r="CX9" t="n">
         <v>95.83</v>
       </c>
+      <c r="CY9" t="n">
+        <v>97.62</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21600,6 +21818,9 @@
       </c>
       <c r="CX10" t="n">
         <v>449.36</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>449.06</v>
       </c>
     </row>
   </sheetData>
@@ -21613,7 +21834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CX10"/>
+  <dimension ref="A1:CY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21718,6 +21939,7 @@
     <col width="12" customWidth="1" min="100" max="100"/>
     <col width="12" customWidth="1" min="101" max="101"/>
     <col width="12" customWidth="1" min="102" max="102"/>
+    <col width="12" customWidth="1" min="103" max="103"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22031,6 +22253,9 @@
       <c r="CX1" s="1" t="n">
         <v>20260122</v>
       </c>
+      <c r="CY1" s="1" t="n">
+        <v>20260123</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22343,6 +22568,9 @@
       <c r="CX2" t="n">
         <v>39708340</v>
       </c>
+      <c r="CY2" t="n">
+        <v>41688982</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22655,6 +22883,9 @@
       <c r="CX3" t="n">
         <v>31913325</v>
       </c>
+      <c r="CY3" t="n">
+        <v>33778478</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22967,6 +23198,9 @@
       <c r="CX4" t="n">
         <v>26253640</v>
       </c>
+      <c r="CY4" t="n">
+        <v>27279974</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23279,6 +23513,9 @@
       <c r="CX5" t="n">
         <v>25349378</v>
       </c>
+      <c r="CY5" t="n">
+        <v>38000159</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23591,6 +23828,9 @@
       <c r="CX6" t="n">
         <v>69113304</v>
       </c>
+      <c r="CY6" t="n">
+        <v>64520383</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23903,6 +24143,9 @@
       <c r="CX7" t="n">
         <v>139636626</v>
       </c>
+      <c r="CY7" t="n">
+        <v>142748076</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24215,6 +24458,9 @@
       <c r="CX8" t="n">
         <v>28499472</v>
       </c>
+      <c r="CY8" t="n">
+        <v>30285671</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24527,6 +24773,9 @@
       <c r="CX9" t="n">
         <v>14150762</v>
       </c>
+      <c r="CY9" t="n">
+        <v>11759837</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24838,6 +25087,9 @@
       </c>
       <c r="CX10" t="n">
         <v>71546729</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>56771364</v>
       </c>
     </row>
   </sheetData>
@@ -24851,7 +25103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE10"/>
+  <dimension ref="A1:CF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24937,6 +25189,7 @@
     <col width="10" customWidth="1" min="81" max="81"/>
     <col width="10" customWidth="1" min="82" max="82"/>
     <col width="10" customWidth="1" min="83" max="83"/>
+    <col width="10" customWidth="1" min="84" max="84"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25193,6 +25446,9 @@
       <c r="CE1" s="1" t="n">
         <v>20260122</v>
       </c>
+      <c r="CF1" s="1" t="n">
+        <v>20260123</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25448,6 +25704,9 @@
       <c r="CE2" t="n">
         <v>6</v>
       </c>
+      <c r="CF2" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25703,6 +25962,9 @@
       <c r="CE3" t="n">
         <v>38</v>
       </c>
+      <c r="CF3" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -25958,6 +26220,9 @@
       <c r="CE4" t="n">
         <v>76</v>
       </c>
+      <c r="CF4" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -26213,6 +26478,9 @@
       <c r="CE5" t="n">
         <v>16</v>
       </c>
+      <c r="CF5" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -26468,6 +26736,9 @@
       <c r="CE6" t="n">
         <v>0</v>
       </c>
+      <c r="CF6" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -26723,6 +26994,9 @@
       <c r="CE7" t="n">
         <v>50</v>
       </c>
+      <c r="CF7" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -26978,6 +27252,9 @@
       <c r="CE8" t="n">
         <v>2</v>
       </c>
+      <c r="CF8" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -27233,6 +27510,9 @@
       <c r="CE9" t="n">
         <v>95</v>
       </c>
+      <c r="CF9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27486,6 +27766,9 @@
         <v>18</v>
       </c>
       <c r="CE10" t="n">
+        <v>45</v>
+      </c>
+      <c r="CF10" t="n">
         <v>45</v>
       </c>
     </row>
@@ -27500,7 +27783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ10"/>
+  <dimension ref="A1:AR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -27546,6 +27829,7 @@
     <col width="10" customWidth="1" min="41" max="41"/>
     <col width="10" customWidth="1" min="42" max="42"/>
     <col width="10" customWidth="1" min="43" max="43"/>
+    <col width="10" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27682,6 +27966,9 @@
       <c r="AQ1" s="1" t="n">
         <v>20260122</v>
       </c>
+      <c r="AR1" s="1" t="n">
+        <v>20260123</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -27817,6 +28104,9 @@
       <c r="AQ2" t="n">
         <v>4</v>
       </c>
+      <c r="AR2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -27952,6 +28242,9 @@
       <c r="AQ3" t="n">
         <v>47</v>
       </c>
+      <c r="AR3" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -28087,6 +28380,9 @@
       <c r="AQ4" t="n">
         <v>92</v>
       </c>
+      <c r="AR4" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -28222,6 +28518,9 @@
       <c r="AQ5" t="n">
         <v>7</v>
       </c>
+      <c r="AR5" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -28357,6 +28656,9 @@
       <c r="AQ6" t="n">
         <v>0</v>
       </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -28492,6 +28794,9 @@
       <c r="AQ7" t="n">
         <v>39</v>
       </c>
+      <c r="AR7" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -28627,6 +28932,9 @@
       <c r="AQ8" t="n">
         <v>21</v>
       </c>
+      <c r="AR8" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -28762,6 +29070,9 @@
       <c r="AQ9" t="n">
         <v>96</v>
       </c>
+      <c r="AR9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28895,6 +29206,9 @@
         <v>41</v>
       </c>
       <c r="AQ10" t="n">
+        <v>59</v>
+      </c>
+      <c r="AR10" t="n">
         <v>59</v>
       </c>
     </row>
@@ -28909,7 +29223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE10"/>
+  <dimension ref="A1:CF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -28995,6 +29309,7 @@
     <col width="10" customWidth="1" min="81" max="81"/>
     <col width="10" customWidth="1" min="82" max="82"/>
     <col width="10" customWidth="1" min="83" max="83"/>
+    <col width="10" customWidth="1" min="84" max="84"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29251,6 +29566,9 @@
       <c r="CE1" s="1" t="n">
         <v>20260122</v>
       </c>
+      <c r="CF1" s="1" t="n">
+        <v>20260123</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -29506,6 +29824,9 @@
       <c r="CE2" t="n">
         <v>-80</v>
       </c>
+      <c r="CF2" t="n">
+        <v>-73</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -29761,6 +30082,9 @@
       <c r="CE3" t="n">
         <v>-14</v>
       </c>
+      <c r="CF3" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -30016,6 +30340,9 @@
       <c r="CE4" t="n">
         <v>47</v>
       </c>
+      <c r="CF4" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -30271,6 +30598,9 @@
       <c r="CE5" t="n">
         <v>-79</v>
       </c>
+      <c r="CF5" t="n">
+        <v>-22</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -30526,6 +30856,9 @@
       <c r="CE6" t="n">
         <v>-113</v>
       </c>
+      <c r="CF6" t="n">
+        <v>-63</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -30781,6 +31114,9 @@
       <c r="CE7" t="n">
         <v>-28</v>
       </c>
+      <c r="CF7" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -31036,6 +31372,9 @@
       <c r="CE8" t="n">
         <v>-75</v>
       </c>
+      <c r="CF8" t="n">
+        <v>-49</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -31291,6 +31630,9 @@
       <c r="CE9" t="n">
         <v>86</v>
       </c>
+      <c r="CF9" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -31545,6 +31887,9 @@
       </c>
       <c r="CE10" t="n">
         <v>5</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -16,6 +16,7 @@
     <sheet name="gap" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="std" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="quant" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="z30" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -8752,6 +8753,2376 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BV10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="10" customWidth="1" min="31" max="31"/>
+    <col width="10" customWidth="1" min="32" max="32"/>
+    <col width="10" customWidth="1" min="33" max="33"/>
+    <col width="10" customWidth="1" min="34" max="34"/>
+    <col width="10" customWidth="1" min="35" max="35"/>
+    <col width="10" customWidth="1" min="36" max="36"/>
+    <col width="10" customWidth="1" min="37" max="37"/>
+    <col width="10" customWidth="1" min="38" max="38"/>
+    <col width="10" customWidth="1" min="39" max="39"/>
+    <col width="10" customWidth="1" min="40" max="40"/>
+    <col width="10" customWidth="1" min="41" max="41"/>
+    <col width="10" customWidth="1" min="42" max="42"/>
+    <col width="10" customWidth="1" min="43" max="43"/>
+    <col width="10" customWidth="1" min="44" max="44"/>
+    <col width="10" customWidth="1" min="45" max="45"/>
+    <col width="10" customWidth="1" min="46" max="46"/>
+    <col width="10" customWidth="1" min="47" max="47"/>
+    <col width="10" customWidth="1" min="48" max="48"/>
+    <col width="10" customWidth="1" min="49" max="49"/>
+    <col width="10" customWidth="1" min="50" max="50"/>
+    <col width="10" customWidth="1" min="51" max="51"/>
+    <col width="10" customWidth="1" min="52" max="52"/>
+    <col width="10" customWidth="1" min="53" max="53"/>
+    <col width="10" customWidth="1" min="54" max="54"/>
+    <col width="10" customWidth="1" min="55" max="55"/>
+    <col width="10" customWidth="1" min="56" max="56"/>
+    <col width="10" customWidth="1" min="57" max="57"/>
+    <col width="10" customWidth="1" min="58" max="58"/>
+    <col width="10" customWidth="1" min="59" max="59"/>
+    <col width="10" customWidth="1" min="60" max="60"/>
+    <col width="10" customWidth="1" min="61" max="61"/>
+    <col width="10" customWidth="1" min="62" max="62"/>
+    <col width="10" customWidth="1" min="63" max="63"/>
+    <col width="10" customWidth="1" min="64" max="64"/>
+    <col width="10" customWidth="1" min="65" max="65"/>
+    <col width="10" customWidth="1" min="66" max="66"/>
+    <col width="10" customWidth="1" min="67" max="67"/>
+    <col width="10" customWidth="1" min="68" max="68"/>
+    <col width="10" customWidth="1" min="69" max="69"/>
+    <col width="10" customWidth="1" min="70" max="70"/>
+    <col width="10" customWidth="1" min="71" max="71"/>
+    <col width="10" customWidth="1" min="72" max="72"/>
+    <col width="10" customWidth="1" min="73" max="73"/>
+    <col width="10" customWidth="1" min="74" max="74"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>종목코드</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="n">
+        <v>20251010</v>
+      </c>
+      <c r="D1" s="1" t="n">
+        <v>20251013</v>
+      </c>
+      <c r="E1" s="1" t="n">
+        <v>20251014</v>
+      </c>
+      <c r="F1" s="1" t="n">
+        <v>20251015</v>
+      </c>
+      <c r="G1" s="1" t="n">
+        <v>20251016</v>
+      </c>
+      <c r="H1" s="1" t="n">
+        <v>20251017</v>
+      </c>
+      <c r="I1" s="1" t="n">
+        <v>20251020</v>
+      </c>
+      <c r="J1" s="1" t="n">
+        <v>20251021</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>20251022</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>20251023</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>20251024</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>20251027</v>
+      </c>
+      <c r="O1" s="1" t="n">
+        <v>20251028</v>
+      </c>
+      <c r="P1" s="1" t="n">
+        <v>20251029</v>
+      </c>
+      <c r="Q1" s="1" t="n">
+        <v>20251030</v>
+      </c>
+      <c r="R1" s="1" t="n">
+        <v>20251031</v>
+      </c>
+      <c r="S1" s="1" t="n">
+        <v>20251103</v>
+      </c>
+      <c r="T1" s="1" t="n">
+        <v>20251104</v>
+      </c>
+      <c r="U1" s="1" t="n">
+        <v>20251105</v>
+      </c>
+      <c r="V1" s="1" t="n">
+        <v>20251106</v>
+      </c>
+      <c r="W1" s="1" t="n">
+        <v>20251107</v>
+      </c>
+      <c r="X1" s="1" t="n">
+        <v>20251110</v>
+      </c>
+      <c r="Y1" s="1" t="n">
+        <v>20251111</v>
+      </c>
+      <c r="Z1" s="1" t="n">
+        <v>20251112</v>
+      </c>
+      <c r="AA1" s="1" t="n">
+        <v>20251113</v>
+      </c>
+      <c r="AB1" s="1" t="n">
+        <v>20251114</v>
+      </c>
+      <c r="AC1" s="1" t="n">
+        <v>20251117</v>
+      </c>
+      <c r="AD1" s="1" t="n">
+        <v>20251118</v>
+      </c>
+      <c r="AE1" s="1" t="n">
+        <v>20251119</v>
+      </c>
+      <c r="AF1" s="1" t="n">
+        <v>20251120</v>
+      </c>
+      <c r="AG1" s="1" t="n">
+        <v>20251121</v>
+      </c>
+      <c r="AH1" s="1" t="n">
+        <v>20251124</v>
+      </c>
+      <c r="AI1" s="1" t="n">
+        <v>20251125</v>
+      </c>
+      <c r="AJ1" s="1" t="n">
+        <v>20251126</v>
+      </c>
+      <c r="AK1" s="1" t="n">
+        <v>20251128</v>
+      </c>
+      <c r="AL1" s="1" t="n">
+        <v>20251201</v>
+      </c>
+      <c r="AM1" s="1" t="n">
+        <v>20251202</v>
+      </c>
+      <c r="AN1" s="1" t="n">
+        <v>20251203</v>
+      </c>
+      <c r="AO1" s="1" t="n">
+        <v>20251204</v>
+      </c>
+      <c r="AP1" s="1" t="n">
+        <v>20251205</v>
+      </c>
+      <c r="AQ1" s="1" t="n">
+        <v>20251208</v>
+      </c>
+      <c r="AR1" s="1" t="n">
+        <v>20251209</v>
+      </c>
+      <c r="AS1" s="1" t="n">
+        <v>20251210</v>
+      </c>
+      <c r="AT1" s="1" t="n">
+        <v>20251211</v>
+      </c>
+      <c r="AU1" s="1" t="n">
+        <v>20251212</v>
+      </c>
+      <c r="AV1" s="1" t="n">
+        <v>20251215</v>
+      </c>
+      <c r="AW1" s="1" t="n">
+        <v>20251216</v>
+      </c>
+      <c r="AX1" s="1" t="n">
+        <v>20251217</v>
+      </c>
+      <c r="AY1" s="1" t="n">
+        <v>20251218</v>
+      </c>
+      <c r="AZ1" s="1" t="n">
+        <v>20251219</v>
+      </c>
+      <c r="BA1" s="1" t="n">
+        <v>20251222</v>
+      </c>
+      <c r="BB1" s="1" t="n">
+        <v>20251223</v>
+      </c>
+      <c r="BC1" s="1" t="n">
+        <v>20251224</v>
+      </c>
+      <c r="BD1" s="1" t="n">
+        <v>20251226</v>
+      </c>
+      <c r="BE1" s="1" t="n">
+        <v>20251229</v>
+      </c>
+      <c r="BF1" s="1" t="n">
+        <v>20251230</v>
+      </c>
+      <c r="BG1" s="1" t="n">
+        <v>20251231</v>
+      </c>
+      <c r="BH1" s="1" t="n">
+        <v>20260102</v>
+      </c>
+      <c r="BI1" s="1" t="n">
+        <v>20260105</v>
+      </c>
+      <c r="BJ1" s="1" t="n">
+        <v>20260106</v>
+      </c>
+      <c r="BK1" s="1" t="n">
+        <v>20260107</v>
+      </c>
+      <c r="BL1" s="1" t="n">
+        <v>20260108</v>
+      </c>
+      <c r="BM1" s="1" t="n">
+        <v>20260109</v>
+      </c>
+      <c r="BN1" s="1" t="n">
+        <v>20260112</v>
+      </c>
+      <c r="BO1" s="1" t="n">
+        <v>20260113</v>
+      </c>
+      <c r="BP1" s="1" t="n">
+        <v>20260114</v>
+      </c>
+      <c r="BQ1" s="1" t="n">
+        <v>20260115</v>
+      </c>
+      <c r="BR1" s="1" t="n">
+        <v>20260116</v>
+      </c>
+      <c r="BS1" s="1" t="n">
+        <v>20260120</v>
+      </c>
+      <c r="BT1" s="1" t="n">
+        <v>20260121</v>
+      </c>
+      <c r="BU1" s="1" t="n">
+        <v>20260122</v>
+      </c>
+      <c r="BV1" s="1" t="n">
+        <v>20260123</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>애플</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>25</v>
+      </c>
+      <c r="I2" t="n">
+        <v>72</v>
+      </c>
+      <c r="J2" t="n">
+        <v>70</v>
+      </c>
+      <c r="K2" t="n">
+        <v>46</v>
+      </c>
+      <c r="L2" t="n">
+        <v>51</v>
+      </c>
+      <c r="M2" t="n">
+        <v>70</v>
+      </c>
+      <c r="N2" t="n">
+        <v>103</v>
+      </c>
+      <c r="O2" t="n">
+        <v>98</v>
+      </c>
+      <c r="P2" t="n">
+        <v>98</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>105</v>
+      </c>
+      <c r="R2" t="n">
+        <v>90</v>
+      </c>
+      <c r="S2" t="n">
+        <v>75</v>
+      </c>
+      <c r="T2" t="n">
+        <v>75</v>
+      </c>
+      <c r="U2" t="n">
+        <v>70</v>
+      </c>
+      <c r="V2" t="n">
+        <v>63</v>
+      </c>
+      <c r="W2" t="n">
+        <v>52</v>
+      </c>
+      <c r="X2" t="n">
+        <v>54</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>81</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>66</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>59</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>52</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>39</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>63</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>68</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>71</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>84</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>118</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>127</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>99</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>52</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>41</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>33</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>35</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>35</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>-29</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>-27</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>-14</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>-42</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>-29</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>-14</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>-18</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>-15</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>-22</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>-38</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>-50</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>-56</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>-137</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>-135</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>-125</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>-91</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>-79</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>-80</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>-86</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>-97</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>-112</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>-98</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>아마존닷컴</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>-84</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-50</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-74</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-75</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-78</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-81</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-53</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-8</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-39</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="M3" t="n">
+        <v>19</v>
+      </c>
+      <c r="N3" t="n">
+        <v>46</v>
+      </c>
+      <c r="O3" t="n">
+        <v>73</v>
+      </c>
+      <c r="P3" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>14</v>
+      </c>
+      <c r="R3" t="n">
+        <v>185</v>
+      </c>
+      <c r="S3" t="n">
+        <v>187</v>
+      </c>
+      <c r="T3" t="n">
+        <v>133</v>
+      </c>
+      <c r="U3" t="n">
+        <v>118</v>
+      </c>
+      <c r="V3" t="n">
+        <v>78</v>
+      </c>
+      <c r="W3" t="n">
+        <v>77</v>
+      </c>
+      <c r="X3" t="n">
+        <v>86</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>81</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>31</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-31</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-49</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-37</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-16</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>-23</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>-23</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-37</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-32</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-13</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>-21</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>-43</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>-57</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>-59</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>-26</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>-20</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>31</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>41</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>47</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>29</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>-20</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>-13</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>135</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>127</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>145</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>130</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>108</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>74</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>31</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>41</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>45</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>-11</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>-9</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>알파벳 A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>-27</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>52</v>
+      </c>
+      <c r="G4" t="n">
+        <v>54</v>
+      </c>
+      <c r="H4" t="n">
+        <v>68</v>
+      </c>
+      <c r="I4" t="n">
+        <v>95</v>
+      </c>
+      <c r="J4" t="n">
+        <v>33</v>
+      </c>
+      <c r="K4" t="n">
+        <v>42</v>
+      </c>
+      <c r="L4" t="n">
+        <v>54</v>
+      </c>
+      <c r="M4" t="n">
+        <v>114</v>
+      </c>
+      <c r="N4" t="n">
+        <v>162</v>
+      </c>
+      <c r="O4" t="n">
+        <v>126</v>
+      </c>
+      <c r="P4" t="n">
+        <v>143</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>148</v>
+      </c>
+      <c r="R4" t="n">
+        <v>126</v>
+      </c>
+      <c r="S4" t="n">
+        <v>118</v>
+      </c>
+      <c r="T4" t="n">
+        <v>86</v>
+      </c>
+      <c r="U4" t="n">
+        <v>99</v>
+      </c>
+      <c r="V4" t="n">
+        <v>91</v>
+      </c>
+      <c r="W4" t="n">
+        <v>66</v>
+      </c>
+      <c r="X4" t="n">
+        <v>93</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>88</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>69</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>43</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>56</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>83</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>124</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>122</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>102</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>94</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>76</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>73</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>77</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>69</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>74</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>52</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>57</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>62</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>-19</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>17</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>27</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>23</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>66</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>89</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>107</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>117</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>126</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>110</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>85</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>66</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>24</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>55</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>61</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>마이크로소프트</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>25</v>
+      </c>
+      <c r="J5" t="n">
+        <v>29</v>
+      </c>
+      <c r="K5" t="n">
+        <v>50</v>
+      </c>
+      <c r="L5" t="n">
+        <v>49</v>
+      </c>
+      <c r="M5" t="n">
+        <v>72</v>
+      </c>
+      <c r="N5" t="n">
+        <v>123</v>
+      </c>
+      <c r="O5" t="n">
+        <v>162</v>
+      </c>
+      <c r="P5" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>39</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-7</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-13</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-30</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-71</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-120</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-109</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-60</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-45</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-31</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-65</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-31</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-41</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-95</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-110</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-124</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-125</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-106</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-88</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-60</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-40</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-51</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-40</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-67</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-46</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-24</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-19</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-54</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-38</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-53</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-63</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-53</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>-19</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-9</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-12</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>22</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>-83</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>-72</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>-32</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>-42</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>-33</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>-49</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>-98</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>-155</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>-110</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>-120</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>-141</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>-100</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>-37</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>넷플릭스</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D6" t="n">
+        <v>13</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-48</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-16</v>
+      </c>
+      <c r="I6" t="n">
+        <v>64</v>
+      </c>
+      <c r="J6" t="n">
+        <v>75</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-157</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-135</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-137</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-118</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-98</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-91</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-93</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-58</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-72</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-73</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-63</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-60</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-50</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-32</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-15</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-36</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-255</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-180</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-146</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-125</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-110</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-98</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-89</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-81</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-75</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-69</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-64</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-61</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-57</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-53</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-50</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-47</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-44</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-41</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-38</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-36</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-33</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-28</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-25</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-23</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>-20</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>-18</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-14</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-47</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-44</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-63</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>-59</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-59</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>-55</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>-53</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>-59</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>-56</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>-46</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>-64</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>-75</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>-76</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>-90</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>-117</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>-129</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>-82</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>엔비디아</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>32</v>
+      </c>
+      <c r="D7" t="n">
+        <v>64</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="n">
+        <v>21</v>
+      </c>
+      <c r="I7" t="n">
+        <v>13</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-14</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>41</v>
+      </c>
+      <c r="N7" t="n">
+        <v>85</v>
+      </c>
+      <c r="O7" t="n">
+        <v>146</v>
+      </c>
+      <c r="P7" t="n">
+        <v>162</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>116</v>
+      </c>
+      <c r="R7" t="n">
+        <v>102</v>
+      </c>
+      <c r="S7" t="n">
+        <v>113</v>
+      </c>
+      <c r="T7" t="n">
+        <v>62</v>
+      </c>
+      <c r="U7" t="n">
+        <v>39</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="X7" t="n">
+        <v>57</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-22</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-53</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-21</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-53</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-61</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-39</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-65</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>-51</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>-67</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>-50</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>-41</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-51</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-31</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-36</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-19</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-21</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>-39</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-72</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>-61</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>-53</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-99</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>-71</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>-14</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>66</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>65</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>89</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>64</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>59</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>48</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>68</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>90</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>45</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>59</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>20</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>16</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>15</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>21</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>31</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>21</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>-57</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>-7</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>팔란티어 테크</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>13</v>
+      </c>
+      <c r="D8" t="n">
+        <v>19</v>
+      </c>
+      <c r="E8" t="n">
+        <v>29</v>
+      </c>
+      <c r="F8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G8" t="n">
+        <v>15</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="n">
+        <v>34</v>
+      </c>
+      <c r="J8" t="n">
+        <v>32</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-26</v>
+      </c>
+      <c r="L8" t="n">
+        <v>19</v>
+      </c>
+      <c r="M8" t="n">
+        <v>61</v>
+      </c>
+      <c r="N8" t="n">
+        <v>103</v>
+      </c>
+      <c r="O8" t="n">
+        <v>101</v>
+      </c>
+      <c r="P8" t="n">
+        <v>170</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>113</v>
+      </c>
+      <c r="R8" t="n">
+        <v>137</v>
+      </c>
+      <c r="S8" t="n">
+        <v>150</v>
+      </c>
+      <c r="T8" t="n">
+        <v>43</v>
+      </c>
+      <c r="U8" t="n">
+        <v>24</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-56</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-38</v>
+      </c>
+      <c r="X8" t="n">
+        <v>56</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>37</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-71</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-60</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-73</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-87</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-89</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-119</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-110</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-74</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-65</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>-53</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-41</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-43</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-29</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>37</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>54</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>49</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>80</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>76</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>77</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>76</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>29</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>-45</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>-19</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>-21</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>-22</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>-13</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>-20</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>-28</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>-41</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>-84</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>-94</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>-104</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>-91</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>-64</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>스타벅스</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SBUX</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>-113</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-77</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-53</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-12</v>
+      </c>
+      <c r="G9" t="n">
+        <v>25</v>
+      </c>
+      <c r="H9" t="n">
+        <v>50</v>
+      </c>
+      <c r="I9" t="n">
+        <v>30</v>
+      </c>
+      <c r="J9" t="n">
+        <v>60</v>
+      </c>
+      <c r="K9" t="n">
+        <v>48</v>
+      </c>
+      <c r="L9" t="n">
+        <v>43</v>
+      </c>
+      <c r="M9" t="n">
+        <v>55</v>
+      </c>
+      <c r="N9" t="n">
+        <v>74</v>
+      </c>
+      <c r="O9" t="n">
+        <v>34</v>
+      </c>
+      <c r="P9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-17</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-63</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-57</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-79</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-11</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-23</v>
+      </c>
+      <c r="W9" t="n">
+        <v>43</v>
+      </c>
+      <c r="X9" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>71</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>56</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-26</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>31</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-21</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>59</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>63</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-27</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-52</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>135</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>94</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>-41</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>-18</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>16</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-28</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>-37</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>-36</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>124</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>38</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>77</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>89</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>107</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>109</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>108</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>130</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>110</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>107</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>127</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>106</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>테슬라</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" t="n">
+        <v>34</v>
+      </c>
+      <c r="E10" t="n">
+        <v>23</v>
+      </c>
+      <c r="F10" t="n">
+        <v>28</v>
+      </c>
+      <c r="G10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H10" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" t="n">
+        <v>43</v>
+      </c>
+      <c r="J10" t="n">
+        <v>33</v>
+      </c>
+      <c r="K10" t="n">
+        <v>24</v>
+      </c>
+      <c r="L10" t="n">
+        <v>59</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>77</v>
+      </c>
+      <c r="O10" t="n">
+        <v>103</v>
+      </c>
+      <c r="P10" t="n">
+        <v>97</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>72</v>
+      </c>
+      <c r="S10" t="n">
+        <v>109</v>
+      </c>
+      <c r="T10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U10" t="n">
+        <v>77</v>
+      </c>
+      <c r="V10" t="n">
+        <v>11</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-54</v>
+      </c>
+      <c r="X10" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-13</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-46</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-137</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-114</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-90</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-102</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-86</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-98</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-101</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-37</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-32</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>-15</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>35</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>61</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>93</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>116</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>66</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>93</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>82</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>87</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>76</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>71</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>51</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>24</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>-20</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>-11</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>-39</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>-50</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>-42</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>-24</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>-16</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>-23</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>-46</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>-49</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>-51</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>-91</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>-57</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>-13</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>-14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -602,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR10"/>
+  <dimension ref="A1:AS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -649,6 +649,7 @@
     <col width="10" customWidth="1" min="42" max="42"/>
     <col width="10" customWidth="1" min="43" max="43"/>
     <col width="10" customWidth="1" min="44" max="44"/>
+    <col width="10" customWidth="1" min="45" max="45"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -788,6 +789,9 @@
       <c r="AR1" s="1" t="n">
         <v>20260123</v>
       </c>
+      <c r="AS1" s="1" t="n">
+        <v>20260126</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -926,6 +930,9 @@
       <c r="AR2" t="n">
         <v>-124</v>
       </c>
+      <c r="AS2" t="n">
+        <v>-79</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1064,6 +1071,9 @@
       <c r="AR3" t="n">
         <v>31</v>
       </c>
+      <c r="AS3" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1202,6 +1212,9 @@
       <c r="AR4" t="n">
         <v>56</v>
       </c>
+      <c r="AS4" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1340,6 +1353,9 @@
       <c r="AR5" t="n">
         <v>-53</v>
       </c>
+      <c r="AS5" t="n">
+        <v>-42</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1478,6 +1494,9 @@
       <c r="AR6" t="n">
         <v>-29</v>
       </c>
+      <c r="AS6" t="n">
+        <v>-27</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1616,6 +1635,9 @@
       <c r="AR7" t="n">
         <v>8</v>
       </c>
+      <c r="AS7" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1754,6 +1776,9 @@
       <c r="AR8" t="n">
         <v>-44</v>
       </c>
+      <c r="AS8" t="n">
+        <v>-51</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1892,6 +1917,9 @@
       <c r="AR9" t="n">
         <v>152</v>
       </c>
+      <c r="AS9" t="n">
+        <v>125</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2029,6 +2057,9 @@
       </c>
       <c r="AR10" t="n">
         <v>11</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-17</v>
       </c>
     </row>
   </sheetData>
@@ -2042,7 +2073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CF10"/>
+  <dimension ref="A1:CG10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2129,6 +2160,7 @@
     <col width="12" customWidth="1" min="82" max="82"/>
     <col width="12" customWidth="1" min="83" max="83"/>
     <col width="12" customWidth="1" min="84" max="84"/>
+    <col width="12" customWidth="1" min="85" max="85"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2552,6 +2584,11 @@
           <t>20260123</t>
         </is>
       </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>20260126</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2810,6 +2847,9 @@
       <c r="CF2" t="n">
         <v>95</v>
       </c>
+      <c r="CG2" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3068,6 +3108,9 @@
       <c r="CF3" t="n">
         <v>101</v>
       </c>
+      <c r="CG3" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3326,6 +3369,9 @@
       <c r="CF4" t="n">
         <v>101</v>
       </c>
+      <c r="CG4" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3584,6 +3630,9 @@
       <c r="CF5" t="n">
         <v>99</v>
       </c>
+      <c r="CG5" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3842,6 +3891,9 @@
       <c r="CF6" t="n">
         <v>96</v>
       </c>
+      <c r="CG6" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4100,6 +4152,9 @@
       <c r="CF7" t="n">
         <v>101</v>
       </c>
+      <c r="CG7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4358,6 +4413,9 @@
       <c r="CF8" t="n">
         <v>96</v>
       </c>
+      <c r="CG8" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4616,6 +4674,9 @@
       <c r="CF9" t="n">
         <v>109</v>
       </c>
+      <c r="CG9" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4873,6 +4934,9 @@
       </c>
       <c r="CF10" t="n">
         <v>101</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -7235,7 +7299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR10"/>
+  <dimension ref="A1:AS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7282,6 +7346,7 @@
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="12" customWidth="1" min="43" max="43"/>
     <col width="12" customWidth="1" min="44" max="44"/>
+    <col width="12" customWidth="1" min="45" max="45"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7505,6 +7570,11 @@
           <t>20260123</t>
         </is>
       </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>20260126</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7643,6 +7713,9 @@
       <c r="AR2" t="n">
         <v>46</v>
       </c>
+      <c r="AS2" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7781,6 +7854,9 @@
       <c r="AR3" t="n">
         <v>38</v>
       </c>
+      <c r="AS3" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7919,6 +7995,9 @@
       <c r="AR4" t="n">
         <v>38</v>
       </c>
+      <c r="AS4" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8057,6 +8136,9 @@
       <c r="AR5" t="n">
         <v>76</v>
       </c>
+      <c r="AS5" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8195,6 +8277,9 @@
       <c r="AR6" t="n">
         <v>88</v>
       </c>
+      <c r="AS6" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8333,6 +8418,9 @@
       <c r="AR7" t="n">
         <v>39</v>
       </c>
+      <c r="AS7" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8471,6 +8559,9 @@
       <c r="AR8" t="n">
         <v>34</v>
       </c>
+      <c r="AS8" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8609,6 +8700,9 @@
       <c r="AR9" t="n">
         <v>59</v>
       </c>
+      <c r="AS9" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8746,6 +8840,9 @@
       </c>
       <c r="AR10" t="n">
         <v>38</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -8759,7 +8856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV10"/>
+  <dimension ref="A1:BW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8836,6 +8933,7 @@
     <col width="10" customWidth="1" min="72" max="72"/>
     <col width="10" customWidth="1" min="73" max="73"/>
     <col width="10" customWidth="1" min="74" max="74"/>
+    <col width="10" customWidth="1" min="75" max="75"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9065,6 +9163,9 @@
       <c r="BV1" s="1" t="n">
         <v>20260123</v>
       </c>
+      <c r="BW1" s="1" t="n">
+        <v>20260126</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9293,6 +9394,9 @@
       <c r="BV2" t="n">
         <v>-90</v>
       </c>
+      <c r="BW2" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9521,6 +9625,9 @@
       <c r="BV3" t="n">
         <v>41</v>
       </c>
+      <c r="BW3" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9749,6 +9856,9 @@
       <c r="BV4" t="n">
         <v>46</v>
       </c>
+      <c r="BW4" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9977,6 +10087,9 @@
       <c r="BV5" t="n">
         <v>-37</v>
       </c>
+      <c r="BW5" t="n">
+        <v>-18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10205,6 +10318,9 @@
       <c r="BV6" t="n">
         <v>-82</v>
       </c>
+      <c r="BW6" t="n">
+        <v>-81</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10433,6 +10549,9 @@
       <c r="BV7" t="n">
         <v>35</v>
       </c>
+      <c r="BW7" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10661,6 +10780,9 @@
       <c r="BV8" t="n">
         <v>-64</v>
       </c>
+      <c r="BW8" t="n">
+        <v>-71</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10889,6 +11011,9 @@
       <c r="BV9" t="n">
         <v>115</v>
       </c>
+      <c r="BW9" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11116,6 +11241,9 @@
       </c>
       <c r="BV10" t="n">
         <v>-14</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>-47</v>
       </c>
     </row>
   </sheetData>
@@ -11129,7 +11257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CY10"/>
+  <dimension ref="A1:CZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11235,6 +11363,7 @@
     <col width="12" customWidth="1" min="101" max="101"/>
     <col width="12" customWidth="1" min="102" max="102"/>
     <col width="12" customWidth="1" min="103" max="103"/>
+    <col width="12" customWidth="1" min="104" max="104"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11551,6 +11680,9 @@
       <c r="CY1" s="1" t="n">
         <v>20260123</v>
       </c>
+      <c r="CZ1" s="1" t="n">
+        <v>20260126</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11866,6 +11998,9 @@
       <c r="CY2" t="n">
         <v>247.32</v>
       </c>
+      <c r="CZ2" t="n">
+        <v>251.48</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12181,6 +12316,9 @@
       <c r="CY3" t="n">
         <v>234.955</v>
       </c>
+      <c r="CZ3" t="n">
+        <v>239.98</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12496,6 +12634,9 @@
       <c r="CY4" t="n">
         <v>332.485</v>
       </c>
+      <c r="CZ4" t="n">
+        <v>327.805</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12811,6 +12952,9 @@
       <c r="CY5" t="n">
         <v>451.87</v>
       </c>
+      <c r="CZ5" t="n">
+        <v>465.305</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13126,6 +13270,9 @@
       <c r="CY6" t="n">
         <v>83.43000000000001</v>
       </c>
+      <c r="CZ6" t="n">
+        <v>86.92</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13441,6 +13588,9 @@
       <c r="CY7" t="n">
         <v>187.5</v>
       </c>
+      <c r="CZ7" t="n">
+        <v>187.16</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13756,6 +13906,9 @@
       <c r="CY8" t="n">
         <v>167.27</v>
       </c>
+      <c r="CZ8" t="n">
+        <v>168.21</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14071,6 +14224,9 @@
       <c r="CY9" t="n">
         <v>97.095</v>
       </c>
+      <c r="CZ9" t="n">
+        <v>97.20999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14385,6 +14541,9 @@
       </c>
       <c r="CY10" t="n">
         <v>447.425</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>445</v>
       </c>
     </row>
   </sheetData>
@@ -14398,7 +14557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CY10"/>
+  <dimension ref="A1:CZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14504,6 +14663,7 @@
     <col width="12" customWidth="1" min="101" max="101"/>
     <col width="12" customWidth="1" min="102" max="102"/>
     <col width="12" customWidth="1" min="103" max="103"/>
+    <col width="12" customWidth="1" min="104" max="104"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14820,6 +14980,9 @@
       <c r="CY1" s="1" t="n">
         <v>20260123</v>
       </c>
+      <c r="CZ1" s="1" t="n">
+        <v>20260126</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15135,6 +15298,9 @@
       <c r="CY2" t="n">
         <v>249.41</v>
       </c>
+      <c r="CZ2" t="n">
+        <v>256.56</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15450,6 +15616,9 @@
       <c r="CY3" t="n">
         <v>240.45</v>
       </c>
+      <c r="CZ3" t="n">
+        <v>240.95</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15765,6 +15934,9 @@
       <c r="CY4" t="n">
         <v>333.6889</v>
       </c>
+      <c r="CZ4" t="n">
+        <v>335.84</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16080,6 +16252,9 @@
       <c r="CY5" t="n">
         <v>471.1</v>
       </c>
+      <c r="CZ5" t="n">
+        <v>474.25</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16395,6 +16570,9 @@
       <c r="CY6" t="n">
         <v>86.3</v>
       </c>
+      <c r="CZ6" t="n">
+        <v>86.94</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16710,6 +16888,9 @@
       <c r="CY7" t="n">
         <v>189.6</v>
       </c>
+      <c r="CZ7" t="n">
+        <v>189.12</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17025,6 +17206,9 @@
       <c r="CY8" t="n">
         <v>172</v>
       </c>
+      <c r="CZ8" t="n">
+        <v>170.5897</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17340,6 +17524,9 @@
       <c r="CY9" t="n">
         <v>97.89</v>
       </c>
+      <c r="CZ9" t="n">
+        <v>97.97</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17654,6 +17841,9 @@
       </c>
       <c r="CY10" t="n">
         <v>452.43</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>445.04</v>
       </c>
     </row>
   </sheetData>
@@ -17667,7 +17857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CY10"/>
+  <dimension ref="A1:CZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17773,6 +17963,7 @@
     <col width="12" customWidth="1" min="101" max="101"/>
     <col width="12" customWidth="1" min="102" max="102"/>
     <col width="12" customWidth="1" min="103" max="103"/>
+    <col width="12" customWidth="1" min="104" max="104"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18089,6 +18280,9 @@
       <c r="CY1" s="1" t="n">
         <v>20260123</v>
       </c>
+      <c r="CZ1" s="1" t="n">
+        <v>20260126</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18404,6 +18598,9 @@
       <c r="CY2" t="n">
         <v>244.68</v>
       </c>
+      <c r="CZ2" t="n">
+        <v>249.8</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18719,6 +18916,9 @@
       <c r="CY3" t="n">
         <v>234.57</v>
       </c>
+      <c r="CZ3" t="n">
+        <v>237.54</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19034,6 +19234,9 @@
       <c r="CY4" t="n">
         <v>327.45</v>
       </c>
+      <c r="CZ4" t="n">
+        <v>327</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19349,6 +19552,9 @@
       <c r="CY5" t="n">
         <v>450.53</v>
       </c>
+      <c r="CZ5" t="n">
+        <v>462</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19664,6 +19870,9 @@
       <c r="CY6" t="n">
         <v>83.28</v>
       </c>
+      <c r="CZ6" t="n">
+        <v>85.34999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19979,6 +20188,9 @@
       <c r="CY7" t="n">
         <v>186.8233</v>
       </c>
+      <c r="CZ7" t="n">
+        <v>185.99</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20294,6 +20506,9 @@
       <c r="CY8" t="n">
         <v>166.3</v>
       </c>
+      <c r="CZ8" t="n">
+        <v>167.325</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20609,6 +20824,9 @@
       <c r="CY9" t="n">
         <v>95.76000000000001</v>
       </c>
+      <c r="CZ9" t="n">
+        <v>95.79000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20923,6 +21141,9 @@
       </c>
       <c r="CY10" t="n">
         <v>444.04</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>434.28</v>
       </c>
     </row>
   </sheetData>
@@ -20936,7 +21157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CY10"/>
+  <dimension ref="A1:CZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21042,6 +21263,7 @@
     <col width="12" customWidth="1" min="101" max="101"/>
     <col width="12" customWidth="1" min="102" max="102"/>
     <col width="12" customWidth="1" min="103" max="103"/>
+    <col width="12" customWidth="1" min="104" max="104"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21358,6 +21580,9 @@
       <c r="CY1" s="1" t="n">
         <v>20260123</v>
       </c>
+      <c r="CZ1" s="1" t="n">
+        <v>20260126</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21673,6 +21898,9 @@
       <c r="CY2" t="n">
         <v>248.04</v>
       </c>
+      <c r="CZ2" t="n">
+        <v>255.41</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21988,6 +22216,9 @@
       <c r="CY3" t="n">
         <v>239.16</v>
       </c>
+      <c r="CZ3" t="n">
+        <v>238.42</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22303,6 +22534,9 @@
       <c r="CY4" t="n">
         <v>327.93</v>
       </c>
+      <c r="CZ4" t="n">
+        <v>333.26</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -22618,6 +22852,9 @@
       <c r="CY5" t="n">
         <v>465.95</v>
       </c>
+      <c r="CZ5" t="n">
+        <v>470.28</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -22933,6 +23170,9 @@
       <c r="CY6" t="n">
         <v>86.12</v>
       </c>
+      <c r="CZ6" t="n">
+        <v>85.7</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23248,6 +23488,9 @@
       <c r="CY7" t="n">
         <v>187.67</v>
       </c>
+      <c r="CZ7" t="n">
+        <v>186.47</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23563,6 +23806,9 @@
       <c r="CY8" t="n">
         <v>169.6</v>
       </c>
+      <c r="CZ8" t="n">
+        <v>167.47</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23878,6 +24124,9 @@
       <c r="CY9" t="n">
         <v>97.62</v>
       </c>
+      <c r="CZ9" t="n">
+        <v>96.33</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24192,6 +24441,9 @@
       </c>
       <c r="CY10" t="n">
         <v>449.06</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>435.2</v>
       </c>
     </row>
   </sheetData>
@@ -24205,7 +24457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CY10"/>
+  <dimension ref="A1:CZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24311,6 +24563,7 @@
     <col width="12" customWidth="1" min="101" max="101"/>
     <col width="12" customWidth="1" min="102" max="102"/>
     <col width="12" customWidth="1" min="103" max="103"/>
+    <col width="12" customWidth="1" min="104" max="104"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24627,6 +24880,9 @@
       <c r="CY1" s="1" t="n">
         <v>20260123</v>
       </c>
+      <c r="CZ1" s="1" t="n">
+        <v>20260126</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24942,6 +25198,9 @@
       <c r="CY2" t="n">
         <v>41688982</v>
       </c>
+      <c r="CZ2" t="n">
+        <v>55969234</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25257,6 +25516,9 @@
       <c r="CY3" t="n">
         <v>33778478</v>
       </c>
+      <c r="CZ3" t="n">
+        <v>32825530</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -25572,6 +25834,9 @@
       <c r="CY4" t="n">
         <v>27279974</v>
       </c>
+      <c r="CZ4" t="n">
+        <v>26042120</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -25887,6 +26152,9 @@
       <c r="CY5" t="n">
         <v>38000159</v>
       </c>
+      <c r="CZ5" t="n">
+        <v>29291235</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -26202,6 +26470,9 @@
       <c r="CY6" t="n">
         <v>64520383</v>
       </c>
+      <c r="CZ6" t="n">
+        <v>40941875</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -26517,6 +26788,9 @@
       <c r="CY7" t="n">
         <v>142748076</v>
       </c>
+      <c r="CZ7" t="n">
+        <v>124799649</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -26832,6 +27106,9 @@
       <c r="CY8" t="n">
         <v>30285671</v>
       </c>
+      <c r="CZ8" t="n">
+        <v>22777164</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -27147,6 +27424,9 @@
       <c r="CY9" t="n">
         <v>11759837</v>
       </c>
+      <c r="CZ9" t="n">
+        <v>14106671</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27461,6 +27741,9 @@
       </c>
       <c r="CY10" t="n">
         <v>56771364</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>49397415</v>
       </c>
     </row>
   </sheetData>
@@ -27474,7 +27757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CF10"/>
+  <dimension ref="A1:CG10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -27561,6 +27844,7 @@
     <col width="10" customWidth="1" min="82" max="82"/>
     <col width="10" customWidth="1" min="83" max="83"/>
     <col width="10" customWidth="1" min="84" max="84"/>
+    <col width="10" customWidth="1" min="85" max="85"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27820,6 +28104,9 @@
       <c r="CF1" s="1" t="n">
         <v>20260123</v>
       </c>
+      <c r="CG1" s="1" t="n">
+        <v>20260126</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -28078,6 +28365,9 @@
       <c r="CF2" t="n">
         <v>5</v>
       </c>
+      <c r="CG2" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -28336,6 +28626,9 @@
       <c r="CF3" t="n">
         <v>61</v>
       </c>
+      <c r="CG3" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -28594,6 +28887,9 @@
       <c r="CF4" t="n">
         <v>65</v>
       </c>
+      <c r="CG4" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -28852,6 +29148,9 @@
       <c r="CF5" t="n">
         <v>50</v>
       </c>
+      <c r="CG5" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -29110,6 +29409,9 @@
       <c r="CF6" t="n">
         <v>24</v>
       </c>
+      <c r="CG6" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -29368,6 +29670,9 @@
       <c r="CF7" t="n">
         <v>71</v>
       </c>
+      <c r="CG7" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -29626,6 +29931,9 @@
       <c r="CF8" t="n">
         <v>15</v>
       </c>
+      <c r="CG8" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -29884,6 +30192,9 @@
       <c r="CF9" t="n">
         <v>100</v>
       </c>
+      <c r="CG9" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -30141,6 +30452,9 @@
       </c>
       <c r="CF10" t="n">
         <v>45</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -30154,7 +30468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR10"/>
+  <dimension ref="A1:AS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -30201,6 +30515,7 @@
     <col width="10" customWidth="1" min="42" max="42"/>
     <col width="10" customWidth="1" min="43" max="43"/>
     <col width="10" customWidth="1" min="44" max="44"/>
+    <col width="10" customWidth="1" min="45" max="45"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30340,6 +30655,9 @@
       <c r="AR1" s="1" t="n">
         <v>20260123</v>
       </c>
+      <c r="AS1" s="1" t="n">
+        <v>20260126</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -30478,6 +30796,9 @@
       <c r="AR2" t="n">
         <v>3</v>
       </c>
+      <c r="AS2" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -30616,6 +30937,9 @@
       <c r="AR3" t="n">
         <v>60</v>
       </c>
+      <c r="AS3" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -30754,6 +31078,9 @@
       <c r="AR4" t="n">
         <v>88</v>
       </c>
+      <c r="AS4" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -30892,6 +31219,9 @@
       <c r="AR5" t="n">
         <v>22</v>
       </c>
+      <c r="AS5" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -31030,6 +31360,9 @@
       <c r="AR6" t="n">
         <v>0</v>
       </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -31168,6 +31501,9 @@
       <c r="AR7" t="n">
         <v>46</v>
       </c>
+      <c r="AS7" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -31306,6 +31642,9 @@
       <c r="AR8" t="n">
         <v>28</v>
       </c>
+      <c r="AS8" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -31444,6 +31783,9 @@
       <c r="AR9" t="n">
         <v>100</v>
       </c>
+      <c r="AS9" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -31581,6 +31923,9 @@
       </c>
       <c r="AR10" t="n">
         <v>59</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -31594,7 +31939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CF10"/>
+  <dimension ref="A1:CG10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -31681,6 +32026,7 @@
     <col width="10" customWidth="1" min="82" max="82"/>
     <col width="10" customWidth="1" min="83" max="83"/>
     <col width="10" customWidth="1" min="84" max="84"/>
+    <col width="10" customWidth="1" min="85" max="85"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31940,6 +32286,9 @@
       <c r="CF1" s="1" t="n">
         <v>20260123</v>
       </c>
+      <c r="CG1" s="1" t="n">
+        <v>20260126</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -32198,6 +32547,9 @@
       <c r="CF2" t="n">
         <v>-73</v>
       </c>
+      <c r="CG2" t="n">
+        <v>-30</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -32456,6 +32808,9 @@
       <c r="CF3" t="n">
         <v>21</v>
       </c>
+      <c r="CG3" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -32714,6 +33069,9 @@
       <c r="CF4" t="n">
         <v>28</v>
       </c>
+      <c r="CG4" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -32972,6 +33330,9 @@
       <c r="CF5" t="n">
         <v>-22</v>
       </c>
+      <c r="CG5" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -33230,6 +33591,9 @@
       <c r="CF6" t="n">
         <v>-63</v>
       </c>
+      <c r="CG6" t="n">
+        <v>-63</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -33488,6 +33852,9 @@
       <c r="CF7" t="n">
         <v>20</v>
       </c>
+      <c r="CG7" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -33746,6 +34113,9 @@
       <c r="CF8" t="n">
         <v>-49</v>
       </c>
+      <c r="CG8" t="n">
+        <v>-62</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -34004,6 +34374,9 @@
       <c r="CF9" t="n">
         <v>93</v>
       </c>
+      <c r="CG9" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -34261,6 +34634,9 @@
       </c>
       <c r="CF10" t="n">
         <v>11</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>-33</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -602,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS10"/>
+  <dimension ref="A1:AT10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -650,6 +650,7 @@
     <col width="10" customWidth="1" min="43" max="43"/>
     <col width="10" customWidth="1" min="44" max="44"/>
     <col width="10" customWidth="1" min="45" max="45"/>
+    <col width="10" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -792,6 +793,9 @@
       <c r="AS1" s="1" t="n">
         <v>20260126</v>
       </c>
+      <c r="AT1" s="1" t="n">
+        <v>20260127</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -933,6 +937,9 @@
       <c r="AS2" t="n">
         <v>-79</v>
       </c>
+      <c r="AT2" t="n">
+        <v>-61</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1074,6 +1081,9 @@
       <c r="AS3" t="n">
         <v>26</v>
       </c>
+      <c r="AT3" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1215,6 +1225,9 @@
       <c r="AS4" t="n">
         <v>69</v>
       </c>
+      <c r="AT4" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1356,6 +1369,9 @@
       <c r="AS5" t="n">
         <v>-42</v>
       </c>
+      <c r="AT5" t="n">
+        <v>-12</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1497,6 +1513,9 @@
       <c r="AS6" t="n">
         <v>-27</v>
       </c>
+      <c r="AT6" t="n">
+        <v>-26</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1638,6 +1657,9 @@
       <c r="AS7" t="n">
         <v>2</v>
       </c>
+      <c r="AT7" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1779,6 +1801,9 @@
       <c r="AS8" t="n">
         <v>-51</v>
       </c>
+      <c r="AT8" t="n">
+        <v>-58</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1920,6 +1945,9 @@
       <c r="AS9" t="n">
         <v>125</v>
       </c>
+      <c r="AT9" t="n">
+        <v>110</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2060,6 +2088,9 @@
       </c>
       <c r="AS10" t="n">
         <v>-17</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>-26</v>
       </c>
     </row>
   </sheetData>
@@ -2073,7 +2104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG10"/>
+  <dimension ref="A1:CH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2161,6 +2192,7 @@
     <col width="12" customWidth="1" min="83" max="83"/>
     <col width="12" customWidth="1" min="84" max="84"/>
     <col width="12" customWidth="1" min="85" max="85"/>
+    <col width="12" customWidth="1" min="86" max="86"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2589,6 +2621,11 @@
           <t>20260126</t>
         </is>
       </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>20260127</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2850,6 +2887,9 @@
       <c r="CG2" t="n">
         <v>98</v>
       </c>
+      <c r="CH2" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3111,6 +3151,9 @@
       <c r="CG3" t="n">
         <v>101</v>
       </c>
+      <c r="CH3" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3372,6 +3415,9 @@
       <c r="CG4" t="n">
         <v>103</v>
       </c>
+      <c r="CH4" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3633,6 +3679,9 @@
       <c r="CG5" t="n">
         <v>100</v>
       </c>
+      <c r="CH5" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3894,6 +3943,9 @@
       <c r="CG6" t="n">
         <v>96</v>
       </c>
+      <c r="CH6" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4155,6 +4207,9 @@
       <c r="CG7" t="n">
         <v>100</v>
       </c>
+      <c r="CH7" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4416,6 +4471,9 @@
       <c r="CG8" t="n">
         <v>95</v>
       </c>
+      <c r="CH8" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4677,6 +4735,9 @@
       <c r="CG9" t="n">
         <v>107</v>
       </c>
+      <c r="CH9" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4936,6 +4997,9 @@
         <v>101</v>
       </c>
       <c r="CG10" t="n">
+        <v>98</v>
+      </c>
+      <c r="CH10" t="n">
         <v>98</v>
       </c>
     </row>
@@ -7299,7 +7363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS10"/>
+  <dimension ref="A1:AT10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7347,6 +7411,7 @@
     <col width="12" customWidth="1" min="43" max="43"/>
     <col width="12" customWidth="1" min="44" max="44"/>
     <col width="12" customWidth="1" min="45" max="45"/>
+    <col width="12" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7575,6 +7640,11 @@
           <t>20260126</t>
         </is>
       </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>20260127</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7716,6 +7786,9 @@
       <c r="AS2" t="n">
         <v>61</v>
       </c>
+      <c r="AT2" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7857,6 +7930,9 @@
       <c r="AS3" t="n">
         <v>37</v>
       </c>
+      <c r="AT3" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7998,6 +8074,9 @@
       <c r="AS4" t="n">
         <v>36</v>
       </c>
+      <c r="AT4" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8139,6 +8218,9 @@
       <c r="AS5" t="n">
         <v>59</v>
       </c>
+      <c r="AT5" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8280,6 +8362,9 @@
       <c r="AS6" t="n">
         <v>55</v>
       </c>
+      <c r="AT6" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8421,6 +8506,9 @@
       <c r="AS7" t="n">
         <v>34</v>
       </c>
+      <c r="AT7" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8562,6 +8650,9 @@
       <c r="AS8" t="n">
         <v>25</v>
       </c>
+      <c r="AT8" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8703,6 +8794,9 @@
       <c r="AS9" t="n">
         <v>71</v>
       </c>
+      <c r="AT9" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8843,6 +8937,9 @@
       </c>
       <c r="AS10" t="n">
         <v>34</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -8856,7 +8953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW10"/>
+  <dimension ref="A1:BX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8934,6 +9031,7 @@
     <col width="10" customWidth="1" min="73" max="73"/>
     <col width="10" customWidth="1" min="74" max="74"/>
     <col width="10" customWidth="1" min="75" max="75"/>
+    <col width="10" customWidth="1" min="76" max="76"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9166,6 +9264,9 @@
       <c r="BW1" s="1" t="n">
         <v>20260126</v>
       </c>
+      <c r="BX1" s="1" t="n">
+        <v>20260127</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9397,6 +9498,9 @@
       <c r="BW2" t="n">
         <v>-50</v>
       </c>
+      <c r="BX2" t="n">
+        <v>-33</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9628,6 +9732,9 @@
       <c r="BW3" t="n">
         <v>34</v>
       </c>
+      <c r="BX3" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9859,6 +9966,9 @@
       <c r="BW4" t="n">
         <v>67</v>
       </c>
+      <c r="BX4" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10090,6 +10200,9 @@
       <c r="BW5" t="n">
         <v>-18</v>
       </c>
+      <c r="BX5" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10321,6 +10434,9 @@
       <c r="BW6" t="n">
         <v>-81</v>
       </c>
+      <c r="BX6" t="n">
+        <v>-77</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10552,6 +10668,9 @@
       <c r="BW7" t="n">
         <v>22</v>
       </c>
+      <c r="BX7" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10783,6 +10902,9 @@
       <c r="BW8" t="n">
         <v>-71</v>
       </c>
+      <c r="BX8" t="n">
+        <v>-75</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11014,6 +11136,9 @@
       <c r="BW9" t="n">
         <v>90</v>
       </c>
+      <c r="BX9" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11244,6 +11369,9 @@
       </c>
       <c r="BW10" t="n">
         <v>-47</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>-55</v>
       </c>
     </row>
   </sheetData>
@@ -11257,7 +11385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CZ10"/>
+  <dimension ref="A1:DA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11364,6 +11492,7 @@
     <col width="12" customWidth="1" min="102" max="102"/>
     <col width="12" customWidth="1" min="103" max="103"/>
     <col width="12" customWidth="1" min="104" max="104"/>
+    <col width="12" customWidth="1" min="105" max="105"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11683,6 +11812,9 @@
       <c r="CZ1" s="1" t="n">
         <v>20260126</v>
       </c>
+      <c r="DA1" s="1" t="n">
+        <v>20260127</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12001,6 +12133,9 @@
       <c r="CZ2" t="n">
         <v>251.48</v>
       </c>
+      <c r="DA2" t="n">
+        <v>259.17</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12319,6 +12454,9 @@
       <c r="CZ3" t="n">
         <v>239.98</v>
       </c>
+      <c r="DA3" t="n">
+        <v>239.685</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12637,6 +12775,9 @@
       <c r="CZ4" t="n">
         <v>327.805</v>
       </c>
+      <c r="DA4" t="n">
+        <v>335.365</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12955,6 +13096,9 @@
       <c r="CZ5" t="n">
         <v>465.305</v>
       </c>
+      <c r="DA5" t="n">
+        <v>473.7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13273,6 +13417,9 @@
       <c r="CZ6" t="n">
         <v>86.92</v>
       </c>
+      <c r="DA6" t="n">
+        <v>85.27500000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13591,6 +13738,9 @@
       <c r="CZ7" t="n">
         <v>187.16</v>
       </c>
+      <c r="DA7" t="n">
+        <v>187.24</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13909,6 +14059,9 @@
       <c r="CZ8" t="n">
         <v>168.21</v>
       </c>
+      <c r="DA8" t="n">
+        <v>167.48</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14227,6 +14380,9 @@
       <c r="CZ9" t="n">
         <v>97.20999999999999</v>
       </c>
+      <c r="DA9" t="n">
+        <v>95.77</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14544,6 +14700,9 @@
       </c>
       <c r="CZ10" t="n">
         <v>445</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>437.41</v>
       </c>
     </row>
   </sheetData>
@@ -14557,7 +14716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CZ10"/>
+  <dimension ref="A1:DA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14664,6 +14823,7 @@
     <col width="12" customWidth="1" min="102" max="102"/>
     <col width="12" customWidth="1" min="103" max="103"/>
     <col width="12" customWidth="1" min="104" max="104"/>
+    <col width="12" customWidth="1" min="105" max="105"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14983,6 +15143,9 @@
       <c r="CZ1" s="1" t="n">
         <v>20260126</v>
       </c>
+      <c r="DA1" s="1" t="n">
+        <v>20260127</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15301,6 +15464,9 @@
       <c r="CZ2" t="n">
         <v>256.56</v>
       </c>
+      <c r="DA2" t="n">
+        <v>261.95</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15619,6 +15785,9 @@
       <c r="CZ3" t="n">
         <v>240.95</v>
       </c>
+      <c r="DA3" t="n">
+        <v>244.88</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15937,6 +16106,9 @@
       <c r="CZ4" t="n">
         <v>335.84</v>
       </c>
+      <c r="DA4" t="n">
+        <v>337.91</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16255,6 +16427,9 @@
       <c r="CZ5" t="n">
         <v>474.25</v>
       </c>
+      <c r="DA5" t="n">
+        <v>482.87</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16573,6 +16748,9 @@
       <c r="CZ6" t="n">
         <v>86.94</v>
       </c>
+      <c r="DA6" t="n">
+        <v>85.59999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16891,6 +17069,9 @@
       <c r="CZ7" t="n">
         <v>189.12</v>
       </c>
+      <c r="DA7" t="n">
+        <v>190</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17209,6 +17390,9 @@
       <c r="CZ8" t="n">
         <v>170.5897</v>
       </c>
+      <c r="DA8" t="n">
+        <v>169.44</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17527,6 +17711,9 @@
       <c r="CZ9" t="n">
         <v>97.97</v>
       </c>
+      <c r="DA9" t="n">
+        <v>96.645</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17844,6 +18031,9 @@
       </c>
       <c r="CZ10" t="n">
         <v>445.04</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>437.52</v>
       </c>
     </row>
   </sheetData>
@@ -17857,7 +18047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CZ10"/>
+  <dimension ref="A1:DA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17964,6 +18154,7 @@
     <col width="12" customWidth="1" min="102" max="102"/>
     <col width="12" customWidth="1" min="103" max="103"/>
     <col width="12" customWidth="1" min="104" max="104"/>
+    <col width="12" customWidth="1" min="105" max="105"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18283,6 +18474,9 @@
       <c r="CZ1" s="1" t="n">
         <v>20260126</v>
       </c>
+      <c r="DA1" s="1" t="n">
+        <v>20260127</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18601,6 +18795,9 @@
       <c r="CZ2" t="n">
         <v>249.8</v>
       </c>
+      <c r="DA2" t="n">
+        <v>258.21</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18919,6 +19116,9 @@
       <c r="CZ3" t="n">
         <v>237.54</v>
       </c>
+      <c r="DA3" t="n">
+        <v>238.08</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19237,6 +19437,9 @@
       <c r="CZ4" t="n">
         <v>327</v>
       </c>
+      <c r="DA4" t="n">
+        <v>333.48</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19555,6 +19758,9 @@
       <c r="CZ5" t="n">
         <v>462</v>
       </c>
+      <c r="DA5" t="n">
+        <v>473.16</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19873,6 +20079,9 @@
       <c r="CZ6" t="n">
         <v>85.34999999999999</v>
       </c>
+      <c r="DA6" t="n">
+        <v>83.88</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20191,6 +20400,9 @@
       <c r="CZ7" t="n">
         <v>185.99</v>
       </c>
+      <c r="DA7" t="n">
+        <v>185.7</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20509,6 +20721,9 @@
       <c r="CZ8" t="n">
         <v>167.325</v>
       </c>
+      <c r="DA8" t="n">
+        <v>164.69</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20827,6 +21042,9 @@
       <c r="CZ9" t="n">
         <v>95.79000000000001</v>
       </c>
+      <c r="DA9" t="n">
+        <v>95.235</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21144,6 +21362,9 @@
       </c>
       <c r="CZ10" t="n">
         <v>434.28</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>430.69</v>
       </c>
     </row>
   </sheetData>
@@ -21157,7 +21378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CZ10"/>
+  <dimension ref="A1:DA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21264,6 +21485,7 @@
     <col width="12" customWidth="1" min="102" max="102"/>
     <col width="12" customWidth="1" min="103" max="103"/>
     <col width="12" customWidth="1" min="104" max="104"/>
+    <col width="12" customWidth="1" min="105" max="105"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21583,6 +21805,9 @@
       <c r="CZ1" s="1" t="n">
         <v>20260126</v>
       </c>
+      <c r="DA1" s="1" t="n">
+        <v>20260127</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21901,6 +22126,9 @@
       <c r="CZ2" t="n">
         <v>255.41</v>
       </c>
+      <c r="DA2" t="n">
+        <v>258.27</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22219,6 +22447,9 @@
       <c r="CZ3" t="n">
         <v>238.42</v>
       </c>
+      <c r="DA3" t="n">
+        <v>244.68</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22537,6 +22768,9 @@
       <c r="CZ4" t="n">
         <v>333.26</v>
       </c>
+      <c r="DA4" t="n">
+        <v>334.55</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -22855,6 +23089,9 @@
       <c r="CZ5" t="n">
         <v>470.28</v>
       </c>
+      <c r="DA5" t="n">
+        <v>480.58</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23173,6 +23410,9 @@
       <c r="CZ6" t="n">
         <v>85.7</v>
       </c>
+      <c r="DA6" t="n">
+        <v>85.58</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23491,6 +23731,9 @@
       <c r="CZ7" t="n">
         <v>186.47</v>
       </c>
+      <c r="DA7" t="n">
+        <v>188.52</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23809,6 +24052,9 @@
       <c r="CZ8" t="n">
         <v>167.47</v>
       </c>
+      <c r="DA8" t="n">
+        <v>165.7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24127,6 +24373,9 @@
       <c r="CZ9" t="n">
         <v>96.33</v>
       </c>
+      <c r="DA9" t="n">
+        <v>95.72</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24444,6 +24693,9 @@
       </c>
       <c r="CZ10" t="n">
         <v>435.2</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>430.9</v>
       </c>
     </row>
   </sheetData>
@@ -24457,7 +24709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CZ10"/>
+  <dimension ref="A1:DA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24564,6 +24816,7 @@
     <col width="12" customWidth="1" min="102" max="102"/>
     <col width="12" customWidth="1" min="103" max="103"/>
     <col width="12" customWidth="1" min="104" max="104"/>
+    <col width="12" customWidth="1" min="105" max="105"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24883,6 +25136,9 @@
       <c r="CZ1" s="1" t="n">
         <v>20260126</v>
       </c>
+      <c r="DA1" s="1" t="n">
+        <v>20260127</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25201,6 +25457,9 @@
       <c r="CZ2" t="n">
         <v>55969234</v>
       </c>
+      <c r="DA2" t="n">
+        <v>49648271</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25519,6 +25778,9 @@
       <c r="CZ3" t="n">
         <v>32825530</v>
       </c>
+      <c r="DA3" t="n">
+        <v>38029216</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -25837,6 +26099,9 @@
       <c r="CZ4" t="n">
         <v>26042120</v>
       </c>
+      <c r="DA4" t="n">
+        <v>21636164</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -26155,6 +26420,9 @@
       <c r="CZ5" t="n">
         <v>29291235</v>
       </c>
+      <c r="DA5" t="n">
+        <v>29213923</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -26473,6 +26741,9 @@
       <c r="CZ6" t="n">
         <v>40941875</v>
       </c>
+      <c r="DA6" t="n">
+        <v>37790831</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -26791,6 +27062,9 @@
       <c r="CZ7" t="n">
         <v>124799649</v>
       </c>
+      <c r="DA7" t="n">
+        <v>143711557</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -27109,6 +27383,9 @@
       <c r="CZ8" t="n">
         <v>22777164</v>
       </c>
+      <c r="DA8" t="n">
+        <v>26542310</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -27427,6 +27704,9 @@
       <c r="CZ9" t="n">
         <v>14106671</v>
       </c>
+      <c r="DA9" t="n">
+        <v>16403589</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27744,6 +28024,9 @@
       </c>
       <c r="CZ10" t="n">
         <v>49397415</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>37733077</v>
       </c>
     </row>
   </sheetData>
@@ -27757,7 +28040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG10"/>
+  <dimension ref="A1:CH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -27845,6 +28128,7 @@
     <col width="10" customWidth="1" min="83" max="83"/>
     <col width="10" customWidth="1" min="84" max="84"/>
     <col width="10" customWidth="1" min="85" max="85"/>
+    <col width="10" customWidth="1" min="86" max="86"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28107,6 +28391,9 @@
       <c r="CG1" s="1" t="n">
         <v>20260126</v>
       </c>
+      <c r="CH1" s="1" t="n">
+        <v>20260127</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -28368,6 +28655,9 @@
       <c r="CG2" t="n">
         <v>32</v>
       </c>
+      <c r="CH2" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -28629,6 +28919,9 @@
       <c r="CG3" t="n">
         <v>57</v>
       </c>
+      <c r="CH3" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -28890,6 +29183,9 @@
       <c r="CG4" t="n">
         <v>88</v>
       </c>
+      <c r="CH4" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -29151,6 +29447,9 @@
       <c r="CG5" t="n">
         <v>60</v>
       </c>
+      <c r="CH5" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -29412,6 +29711,9 @@
       <c r="CG6" t="n">
         <v>20</v>
       </c>
+      <c r="CH6" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -29673,6 +29975,9 @@
       <c r="CG7" t="n">
         <v>62</v>
       </c>
+      <c r="CH7" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -29934,6 +30239,9 @@
       <c r="CG8" t="n">
         <v>9</v>
       </c>
+      <c r="CH8" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -30195,6 +30503,9 @@
       <c r="CG9" t="n">
         <v>91</v>
       </c>
+      <c r="CH9" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -30454,6 +30765,9 @@
         <v>45</v>
       </c>
       <c r="CG10" t="n">
+        <v>29</v>
+      </c>
+      <c r="CH10" t="n">
         <v>29</v>
       </c>
     </row>
@@ -30468,7 +30782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS10"/>
+  <dimension ref="A1:AT10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -30516,6 +30830,7 @@
     <col width="10" customWidth="1" min="43" max="43"/>
     <col width="10" customWidth="1" min="44" max="44"/>
     <col width="10" customWidth="1" min="45" max="45"/>
+    <col width="10" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30658,6 +30973,9 @@
       <c r="AS1" s="1" t="n">
         <v>20260126</v>
       </c>
+      <c r="AT1" s="1" t="n">
+        <v>20260127</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -30799,6 +31117,9 @@
       <c r="AS2" t="n">
         <v>22</v>
       </c>
+      <c r="AT2" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -30940,6 +31261,9 @@
       <c r="AS3" t="n">
         <v>58</v>
       </c>
+      <c r="AT3" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -31081,6 +31405,9 @@
       <c r="AS4" t="n">
         <v>96</v>
       </c>
+      <c r="AT4" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -31222,6 +31549,9 @@
       <c r="AS5" t="n">
         <v>27</v>
       </c>
+      <c r="AT5" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -31363,6 +31693,9 @@
       <c r="AS6" t="n">
         <v>0</v>
       </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -31504,6 +31837,9 @@
       <c r="AS7" t="n">
         <v>43</v>
       </c>
+      <c r="AT7" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -31645,6 +31981,9 @@
       <c r="AS8" t="n">
         <v>24</v>
       </c>
+      <c r="AT8" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -31786,6 +32125,9 @@
       <c r="AS9" t="n">
         <v>93</v>
       </c>
+      <c r="AT9" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -31926,6 +32268,9 @@
       </c>
       <c r="AS10" t="n">
         <v>45</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -31939,7 +32284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG10"/>
+  <dimension ref="A1:CH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -32027,6 +32372,7 @@
     <col width="10" customWidth="1" min="83" max="83"/>
     <col width="10" customWidth="1" min="84" max="84"/>
     <col width="10" customWidth="1" min="85" max="85"/>
+    <col width="10" customWidth="1" min="86" max="86"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32289,6 +32635,9 @@
       <c r="CG1" s="1" t="n">
         <v>20260126</v>
       </c>
+      <c r="CH1" s="1" t="n">
+        <v>20260127</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -32550,6 +32899,9 @@
       <c r="CG2" t="n">
         <v>-30</v>
       </c>
+      <c r="CH2" t="n">
+        <v>-10</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -32811,6 +33163,9 @@
       <c r="CG3" t="n">
         <v>13</v>
       </c>
+      <c r="CH3" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -33072,6 +33427,9 @@
       <c r="CG4" t="n">
         <v>54</v>
       </c>
+      <c r="CH4" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -33333,6 +33691,9 @@
       <c r="CG5" t="n">
         <v>-3</v>
       </c>
+      <c r="CH5" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -33594,6 +33955,9 @@
       <c r="CG6" t="n">
         <v>-63</v>
       </c>
+      <c r="CH6" t="n">
+        <v>-60</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -33855,6 +34219,9 @@
       <c r="CG7" t="n">
         <v>2</v>
       </c>
+      <c r="CH7" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -34116,6 +34483,9 @@
       <c r="CG8" t="n">
         <v>-62</v>
       </c>
+      <c r="CH8" t="n">
+        <v>-71</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -34377,6 +34747,9 @@
       <c r="CG9" t="n">
         <v>70</v>
       </c>
+      <c r="CH9" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -34637,6 +35010,9 @@
       </c>
       <c r="CG10" t="n">
         <v>-33</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>-52</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -602,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT10"/>
+  <dimension ref="A1:AU10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -651,6 +651,7 @@
     <col width="10" customWidth="1" min="44" max="44"/>
     <col width="10" customWidth="1" min="45" max="45"/>
     <col width="10" customWidth="1" min="46" max="46"/>
+    <col width="10" customWidth="1" min="47" max="47"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -796,6 +797,9 @@
       <c r="AT1" s="1" t="n">
         <v>20260127</v>
       </c>
+      <c r="AU1" s="1" t="n">
+        <v>20260128</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -940,6 +944,9 @@
       <c r="AT2" t="n">
         <v>-61</v>
       </c>
+      <c r="AU2" t="n">
+        <v>-69</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1084,6 +1091,9 @@
       <c r="AT3" t="n">
         <v>60</v>
       </c>
+      <c r="AU3" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1228,6 +1238,9 @@
       <c r="AT4" t="n">
         <v>71</v>
       </c>
+      <c r="AU4" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1372,6 +1385,9 @@
       <c r="AT5" t="n">
         <v>-12</v>
       </c>
+      <c r="AU5" t="n">
+        <v>-7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1516,6 +1532,9 @@
       <c r="AT6" t="n">
         <v>-26</v>
       </c>
+      <c r="AU6" t="n">
+        <v>-25</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1660,6 +1679,9 @@
       <c r="AT7" t="n">
         <v>19</v>
       </c>
+      <c r="AU7" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1804,6 +1826,9 @@
       <c r="AT8" t="n">
         <v>-58</v>
       </c>
+      <c r="AU8" t="n">
+        <v>-92</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1948,6 +1973,9 @@
       <c r="AT9" t="n">
         <v>110</v>
       </c>
+      <c r="AU9" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2091,6 +2119,9 @@
       </c>
       <c r="AT10" t="n">
         <v>-26</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>-24</v>
       </c>
     </row>
   </sheetData>
@@ -2104,7 +2135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CH10"/>
+  <dimension ref="A1:CI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2193,6 +2224,7 @@
     <col width="12" customWidth="1" min="84" max="84"/>
     <col width="12" customWidth="1" min="85" max="85"/>
     <col width="12" customWidth="1" min="86" max="86"/>
+    <col width="12" customWidth="1" min="87" max="87"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2626,6 +2658,11 @@
           <t>20260127</t>
         </is>
       </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>20260128</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2890,6 +2927,9 @@
       <c r="CH2" t="n">
         <v>99</v>
       </c>
+      <c r="CI2" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3154,6 +3194,9 @@
       <c r="CH3" t="n">
         <v>103</v>
       </c>
+      <c r="CI3" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3418,6 +3461,9 @@
       <c r="CH4" t="n">
         <v>103</v>
       </c>
+      <c r="CI4" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3682,6 +3728,9 @@
       <c r="CH5" t="n">
         <v>102</v>
       </c>
+      <c r="CI5" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3946,6 +3995,9 @@
       <c r="CH6" t="n">
         <v>96</v>
       </c>
+      <c r="CI6" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4210,6 +4262,9 @@
       <c r="CH7" t="n">
         <v>101</v>
       </c>
+      <c r="CI7" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4474,6 +4529,9 @@
       <c r="CH8" t="n">
         <v>95</v>
       </c>
+      <c r="CI8" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4738,6 +4796,9 @@
       <c r="CH9" t="n">
         <v>106</v>
       </c>
+      <c r="CI9" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5000,6 +5061,9 @@
         <v>98</v>
       </c>
       <c r="CH10" t="n">
+        <v>98</v>
+      </c>
+      <c r="CI10" t="n">
         <v>98</v>
       </c>
     </row>
@@ -7363,7 +7427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT10"/>
+  <dimension ref="A1:AU10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7412,6 +7476,7 @@
     <col width="12" customWidth="1" min="44" max="44"/>
     <col width="12" customWidth="1" min="45" max="45"/>
     <col width="12" customWidth="1" min="46" max="46"/>
+    <col width="12" customWidth="1" min="47" max="47"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7645,6 +7710,11 @@
           <t>20260127</t>
         </is>
       </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>20260128</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7789,6 +7859,9 @@
       <c r="AT2" t="n">
         <v>54</v>
       </c>
+      <c r="AU2" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7933,6 +8006,9 @@
       <c r="AT3" t="n">
         <v>44</v>
       </c>
+      <c r="AU3" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8077,6 +8153,9 @@
       <c r="AT4" t="n">
         <v>30</v>
       </c>
+      <c r="AU4" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8221,6 +8300,9 @@
       <c r="AT5" t="n">
         <v>59</v>
       </c>
+      <c r="AU5" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8365,6 +8447,9 @@
       <c r="AT6" t="n">
         <v>50</v>
       </c>
+      <c r="AU6" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8509,6 +8594,9 @@
       <c r="AT7" t="n">
         <v>40</v>
       </c>
+      <c r="AU7" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8653,6 +8741,9 @@
       <c r="AT8" t="n">
         <v>30</v>
       </c>
+      <c r="AU8" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8797,6 +8888,9 @@
       <c r="AT9" t="n">
         <v>82</v>
       </c>
+      <c r="AU9" t="n">
+        <v>128</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8940,6 +9034,9 @@
       </c>
       <c r="AT10" t="n">
         <v>26</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -8953,7 +9050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX10"/>
+  <dimension ref="A1:BY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9032,6 +9129,7 @@
     <col width="10" customWidth="1" min="74" max="74"/>
     <col width="10" customWidth="1" min="75" max="75"/>
     <col width="10" customWidth="1" min="76" max="76"/>
+    <col width="10" customWidth="1" min="77" max="77"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9267,6 +9365,9 @@
       <c r="BX1" s="1" t="n">
         <v>20260127</v>
       </c>
+      <c r="BY1" s="1" t="n">
+        <v>20260128</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9501,6 +9602,9 @@
       <c r="BX2" t="n">
         <v>-33</v>
       </c>
+      <c r="BY2" t="n">
+        <v>-40</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9735,6 +9839,9 @@
       <c r="BX3" t="n">
         <v>71</v>
       </c>
+      <c r="BY3" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9969,6 +10076,9 @@
       <c r="BX4" t="n">
         <v>68</v>
       </c>
+      <c r="BY4" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10203,6 +10313,9 @@
       <c r="BX5" t="n">
         <v>25</v>
       </c>
+      <c r="BY5" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10437,6 +10550,9 @@
       <c r="BX6" t="n">
         <v>-77</v>
       </c>
+      <c r="BY6" t="n">
+        <v>-83</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10671,6 +10787,9 @@
       <c r="BX7" t="n">
         <v>39</v>
       </c>
+      <c r="BY7" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10905,6 +11024,9 @@
       <c r="BX8" t="n">
         <v>-75</v>
       </c>
+      <c r="BY8" t="n">
+        <v>-108</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11139,6 +11261,9 @@
       <c r="BX9" t="n">
         <v>76</v>
       </c>
+      <c r="BY9" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11372,6 +11497,9 @@
       </c>
       <c r="BX10" t="n">
         <v>-55</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>-51</v>
       </c>
     </row>
   </sheetData>
@@ -11385,7 +11513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DA10"/>
+  <dimension ref="A1:DB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11493,6 +11621,7 @@
     <col width="12" customWidth="1" min="103" max="103"/>
     <col width="12" customWidth="1" min="104" max="104"/>
     <col width="12" customWidth="1" min="105" max="105"/>
+    <col width="12" customWidth="1" min="106" max="106"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11815,6 +11944,9 @@
       <c r="DA1" s="1" t="n">
         <v>20260127</v>
       </c>
+      <c r="DB1" s="1" t="n">
+        <v>20260128</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12136,6 +12268,9 @@
       <c r="DA2" t="n">
         <v>259.17</v>
       </c>
+      <c r="DB2" t="n">
+        <v>257.65</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12457,6 +12592,9 @@
       <c r="DA3" t="n">
         <v>239.685</v>
       </c>
+      <c r="DB3" t="n">
+        <v>246.365</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12778,6 +12916,9 @@
       <c r="DA4" t="n">
         <v>335.365</v>
       </c>
+      <c r="DB4" t="n">
+        <v>336.06</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13099,6 +13240,9 @@
       <c r="DA5" t="n">
         <v>473.7</v>
       </c>
+      <c r="DB5" t="n">
+        <v>483.21</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13420,6 +13564,9 @@
       <c r="DA6" t="n">
         <v>85.27500000000001</v>
       </c>
+      <c r="DB6" t="n">
+        <v>85.625</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13741,6 +13888,9 @@
       <c r="DA7" t="n">
         <v>187.24</v>
       </c>
+      <c r="DB7" t="n">
+        <v>191.27</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14062,6 +14212,9 @@
       <c r="DA8" t="n">
         <v>167.48</v>
       </c>
+      <c r="DB8" t="n">
+        <v>164.4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14383,6 +14536,9 @@
       <c r="DA9" t="n">
         <v>95.77</v>
       </c>
+      <c r="DB9" t="n">
+        <v>102.3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14703,6 +14859,9 @@
       </c>
       <c r="DA10" t="n">
         <v>437.41</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>431.91</v>
       </c>
     </row>
   </sheetData>
@@ -14716,7 +14875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DA10"/>
+  <dimension ref="A1:DB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14824,6 +14983,7 @@
     <col width="12" customWidth="1" min="103" max="103"/>
     <col width="12" customWidth="1" min="104" max="104"/>
     <col width="12" customWidth="1" min="105" max="105"/>
+    <col width="12" customWidth="1" min="106" max="106"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15146,6 +15306,9 @@
       <c r="DA1" s="1" t="n">
         <v>20260127</v>
       </c>
+      <c r="DB1" s="1" t="n">
+        <v>20260128</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15467,6 +15630,9 @@
       <c r="DA2" t="n">
         <v>261.95</v>
       </c>
+      <c r="DB2" t="n">
+        <v>258.855</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15788,6 +15954,9 @@
       <c r="DA3" t="n">
         <v>244.88</v>
       </c>
+      <c r="DB3" t="n">
+        <v>247.775</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16109,6 +16278,9 @@
       <c r="DA4" t="n">
         <v>337.91</v>
       </c>
+      <c r="DB4" t="n">
+        <v>337.535</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16430,6 +16602,9 @@
       <c r="DA5" t="n">
         <v>482.87</v>
       </c>
+      <c r="DB5" t="n">
+        <v>483.74</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16751,6 +16926,9 @@
       <c r="DA6" t="n">
         <v>85.59999999999999</v>
       </c>
+      <c r="DB6" t="n">
+        <v>86.47</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17072,6 +17250,9 @@
       <c r="DA7" t="n">
         <v>190</v>
       </c>
+      <c r="DB7" t="n">
+        <v>192.35</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17393,6 +17574,9 @@
       <c r="DA8" t="n">
         <v>169.44</v>
       </c>
+      <c r="DB8" t="n">
+        <v>165.045</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17714,6 +17898,9 @@
       <c r="DA9" t="n">
         <v>96.645</v>
       </c>
+      <c r="DB9" t="n">
+        <v>104.82</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18034,6 +18221,9 @@
       </c>
       <c r="DA10" t="n">
         <v>437.52</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>438.26</v>
       </c>
     </row>
   </sheetData>
@@ -18047,7 +18237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DA10"/>
+  <dimension ref="A1:DB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18155,6 +18345,7 @@
     <col width="12" customWidth="1" min="103" max="103"/>
     <col width="12" customWidth="1" min="104" max="104"/>
     <col width="12" customWidth="1" min="105" max="105"/>
+    <col width="12" customWidth="1" min="106" max="106"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18477,6 +18668,9 @@
       <c r="DA1" s="1" t="n">
         <v>20260127</v>
       </c>
+      <c r="DB1" s="1" t="n">
+        <v>20260128</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18798,6 +18992,9 @@
       <c r="DA2" t="n">
         <v>258.21</v>
       </c>
+      <c r="DB2" t="n">
+        <v>254.51</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19119,6 +19316,9 @@
       <c r="DA3" t="n">
         <v>238.08</v>
       </c>
+      <c r="DB3" t="n">
+        <v>241.53</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19440,6 +19640,9 @@
       <c r="DA4" t="n">
         <v>333.48</v>
       </c>
+      <c r="DB4" t="n">
+        <v>331.94</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19761,6 +19964,9 @@
       <c r="DA5" t="n">
         <v>473.16</v>
       </c>
+      <c r="DB5" t="n">
+        <v>478</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20082,6 +20288,9 @@
       <c r="DA6" t="n">
         <v>83.88</v>
       </c>
+      <c r="DB6" t="n">
+        <v>84.295</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20403,6 +20612,9 @@
       <c r="DA7" t="n">
         <v>185.7</v>
       </c>
+      <c r="DB7" t="n">
+        <v>189.84</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20724,6 +20936,9 @@
       <c r="DA8" t="n">
         <v>164.69</v>
       </c>
+      <c r="DB8" t="n">
+        <v>157.24</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21045,6 +21260,9 @@
       <c r="DA9" t="n">
         <v>95.235</v>
       </c>
+      <c r="DB9" t="n">
+        <v>95.09999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21365,6 +21583,9 @@
       </c>
       <c r="DA10" t="n">
         <v>430.69</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>430.1</v>
       </c>
     </row>
   </sheetData>
@@ -21378,7 +21599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DA10"/>
+  <dimension ref="A1:DB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21486,6 +21707,7 @@
     <col width="12" customWidth="1" min="103" max="103"/>
     <col width="12" customWidth="1" min="104" max="104"/>
     <col width="12" customWidth="1" min="105" max="105"/>
+    <col width="12" customWidth="1" min="106" max="106"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21808,6 +22030,9 @@
       <c r="DA1" s="1" t="n">
         <v>20260127</v>
       </c>
+      <c r="DB1" s="1" t="n">
+        <v>20260128</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22129,6 +22354,9 @@
       <c r="DA2" t="n">
         <v>258.27</v>
       </c>
+      <c r="DB2" t="n">
+        <v>256.44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22450,6 +22678,9 @@
       <c r="DA3" t="n">
         <v>244.68</v>
       </c>
+      <c r="DB3" t="n">
+        <v>243.01</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22771,6 +23002,9 @@
       <c r="DA4" t="n">
         <v>334.55</v>
       </c>
+      <c r="DB4" t="n">
+        <v>336.01</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23092,6 +23326,9 @@
       <c r="DA5" t="n">
         <v>480.58</v>
       </c>
+      <c r="DB5" t="n">
+        <v>481.63</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23413,6 +23650,9 @@
       <c r="DA6" t="n">
         <v>85.58</v>
       </c>
+      <c r="DB6" t="n">
+        <v>84.64</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23734,6 +23974,9 @@
       <c r="DA7" t="n">
         <v>188.52</v>
       </c>
+      <c r="DB7" t="n">
+        <v>191.52</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24055,6 +24298,9 @@
       <c r="DA8" t="n">
         <v>165.7</v>
       </c>
+      <c r="DB8" t="n">
+        <v>157.35</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24376,6 +24622,9 @@
       <c r="DA9" t="n">
         <v>95.72</v>
       </c>
+      <c r="DB9" t="n">
+        <v>95.16</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24696,6 +24945,9 @@
       </c>
       <c r="DA10" t="n">
         <v>430.9</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>431.46</v>
       </c>
     </row>
   </sheetData>
@@ -24709,7 +24961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DA10"/>
+  <dimension ref="A1:DB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24817,6 +25069,7 @@
     <col width="12" customWidth="1" min="103" max="103"/>
     <col width="12" customWidth="1" min="104" max="104"/>
     <col width="12" customWidth="1" min="105" max="105"/>
+    <col width="12" customWidth="1" min="106" max="106"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25139,6 +25392,9 @@
       <c r="DA1" s="1" t="n">
         <v>20260127</v>
       </c>
+      <c r="DB1" s="1" t="n">
+        <v>20260128</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25460,6 +25716,9 @@
       <c r="DA2" t="n">
         <v>49648271</v>
       </c>
+      <c r="DB2" t="n">
+        <v>41287971</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25781,6 +26040,9 @@
       <c r="DA3" t="n">
         <v>38029216</v>
       </c>
+      <c r="DB3" t="n">
+        <v>40882657</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -26102,6 +26364,9 @@
       <c r="DA4" t="n">
         <v>21636164</v>
       </c>
+      <c r="DB4" t="n">
+        <v>27434434</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -26423,6 +26688,9 @@
       <c r="DA5" t="n">
         <v>29213923</v>
       </c>
+      <c r="DB5" t="n">
+        <v>36875403</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -26744,6 +27012,9 @@
       <c r="DA6" t="n">
         <v>37790831</v>
       </c>
+      <c r="DB6" t="n">
+        <v>37762612</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -27065,6 +27336,9 @@
       <c r="DA7" t="n">
         <v>143711557</v>
       </c>
+      <c r="DB7" t="n">
+        <v>148552677</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -27386,6 +27660,9 @@
       <c r="DA8" t="n">
         <v>26542310</v>
       </c>
+      <c r="DB8" t="n">
+        <v>44822848</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -27707,6 +27984,9 @@
       <c r="DA9" t="n">
         <v>16403589</v>
       </c>
+      <c r="DB9" t="n">
+        <v>25961583</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28027,6 +28307,9 @@
       </c>
       <c r="DA10" t="n">
         <v>37733077</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>54857403</v>
       </c>
     </row>
   </sheetData>
@@ -28040,7 +28323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CH10"/>
+  <dimension ref="A1:CI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -28129,6 +28412,7 @@
     <col width="10" customWidth="1" min="84" max="84"/>
     <col width="10" customWidth="1" min="85" max="85"/>
     <col width="10" customWidth="1" min="86" max="86"/>
+    <col width="10" customWidth="1" min="87" max="87"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28394,6 +28678,9 @@
       <c r="CH1" s="1" t="n">
         <v>20260127</v>
       </c>
+      <c r="CI1" s="1" t="n">
+        <v>20260128</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -28658,6 +28945,9 @@
       <c r="CH2" t="n">
         <v>43</v>
       </c>
+      <c r="CI2" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -28922,6 +29212,9 @@
       <c r="CH3" t="n">
         <v>87</v>
       </c>
+      <c r="CI3" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -29186,6 +29479,9 @@
       <c r="CH4" t="n">
         <v>94</v>
       </c>
+      <c r="CI4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -29450,6 +29746,9 @@
       <c r="CH5" t="n">
         <v>84</v>
       </c>
+      <c r="CI5" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -29714,6 +30013,9 @@
       <c r="CH6" t="n">
         <v>19</v>
       </c>
+      <c r="CI6" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -29978,6 +30280,9 @@
       <c r="CH7" t="n">
         <v>77</v>
       </c>
+      <c r="CI7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -30242,6 +30547,9 @@
       <c r="CH8" t="n">
         <v>2</v>
       </c>
+      <c r="CI8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -30506,6 +30814,9 @@
       <c r="CH9" t="n">
         <v>86</v>
       </c>
+      <c r="CI9" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -30769,6 +31080,9 @@
       </c>
       <c r="CH10" t="n">
         <v>29</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -30782,7 +31096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT10"/>
+  <dimension ref="A1:AU10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -30831,6 +31145,7 @@
     <col width="10" customWidth="1" min="44" max="44"/>
     <col width="10" customWidth="1" min="45" max="45"/>
     <col width="10" customWidth="1" min="46" max="46"/>
+    <col width="10" customWidth="1" min="47" max="47"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30976,6 +31291,9 @@
       <c r="AT1" s="1" t="n">
         <v>20260127</v>
       </c>
+      <c r="AU1" s="1" t="n">
+        <v>20260128</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -31120,6 +31438,9 @@
       <c r="AT2" t="n">
         <v>29</v>
       </c>
+      <c r="AU2" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -31264,6 +31585,9 @@
       <c r="AT3" t="n">
         <v>75</v>
       </c>
+      <c r="AU3" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -31408,6 +31732,9 @@
       <c r="AT4" t="n">
         <v>98</v>
       </c>
+      <c r="AU4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -31552,6 +31879,9 @@
       <c r="AT5" t="n">
         <v>45</v>
       </c>
+      <c r="AU5" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -31696,6 +32026,9 @@
       <c r="AT6" t="n">
         <v>0</v>
       </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -31840,6 +32173,9 @@
       <c r="AT7" t="n">
         <v>49</v>
       </c>
+      <c r="AU7" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -31984,6 +32320,9 @@
       <c r="AT8" t="n">
         <v>21</v>
       </c>
+      <c r="AU8" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -32128,6 +32467,9 @@
       <c r="AT9" t="n">
         <v>89</v>
       </c>
+      <c r="AU9" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -32271,6 +32613,9 @@
       </c>
       <c r="AT10" t="n">
         <v>40</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -32284,7 +32629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CH10"/>
+  <dimension ref="A1:CI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -32373,6 +32718,7 @@
     <col width="10" customWidth="1" min="84" max="84"/>
     <col width="10" customWidth="1" min="85" max="85"/>
     <col width="10" customWidth="1" min="86" max="86"/>
+    <col width="10" customWidth="1" min="87" max="87"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32638,6 +32984,9 @@
       <c r="CH1" s="1" t="n">
         <v>20260127</v>
       </c>
+      <c r="CI1" s="1" t="n">
+        <v>20260128</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -32902,6 +33251,9 @@
       <c r="CH2" t="n">
         <v>-10</v>
       </c>
+      <c r="CI2" t="n">
+        <v>-17</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -33166,6 +33518,9 @@
       <c r="CH3" t="n">
         <v>57</v>
       </c>
+      <c r="CI3" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -33430,6 +33785,9 @@
       <c r="CH4" t="n">
         <v>56</v>
       </c>
+      <c r="CI4" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -33694,6 +34052,9 @@
       <c r="CH5" t="n">
         <v>39</v>
       </c>
+      <c r="CI5" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -33958,6 +34319,9 @@
       <c r="CH6" t="n">
         <v>-60</v>
       </c>
+      <c r="CI6" t="n">
+        <v>-70</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -34222,6 +34586,9 @@
       <c r="CH7" t="n">
         <v>40</v>
       </c>
+      <c r="CI7" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -34486,6 +34853,9 @@
       <c r="CH8" t="n">
         <v>-71</v>
       </c>
+      <c r="CI8" t="n">
+        <v>-116</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -34750,6 +35120,9 @@
       <c r="CH9" t="n">
         <v>57</v>
       </c>
+      <c r="CI9" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -35013,6 +35386,9 @@
       </c>
       <c r="CH10" t="n">
         <v>-52</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>-46</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -602,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU10"/>
+  <dimension ref="A1:AV10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -652,6 +652,7 @@
     <col width="10" customWidth="1" min="45" max="45"/>
     <col width="10" customWidth="1" min="46" max="46"/>
     <col width="10" customWidth="1" min="47" max="47"/>
+    <col width="10" customWidth="1" min="48" max="48"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -800,6 +801,9 @@
       <c r="AU1" s="1" t="n">
         <v>20260128</v>
       </c>
+      <c r="AV1" s="1" t="n">
+        <v>20260129</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -947,6 +951,9 @@
       <c r="AU2" t="n">
         <v>-69</v>
       </c>
+      <c r="AV2" t="n">
+        <v>-57</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1094,6 +1101,9 @@
       <c r="AU3" t="n">
         <v>49</v>
       </c>
+      <c r="AV3" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1241,6 +1251,9 @@
       <c r="AU4" t="n">
         <v>73</v>
       </c>
+      <c r="AV4" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1388,6 +1401,9 @@
       <c r="AU5" t="n">
         <v>-7</v>
       </c>
+      <c r="AV5" t="n">
+        <v>-148</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1535,6 +1551,9 @@
       <c r="AU6" t="n">
         <v>-25</v>
       </c>
+      <c r="AV6" t="n">
+        <v>-24</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1682,6 +1701,9 @@
       <c r="AU7" t="n">
         <v>44</v>
       </c>
+      <c r="AV7" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1829,6 +1851,9 @@
       <c r="AU8" t="n">
         <v>-92</v>
       </c>
+      <c r="AV8" t="n">
+        <v>-112</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1976,6 +2001,9 @@
       <c r="AU9" t="n">
         <v>98</v>
       </c>
+      <c r="AV9" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2122,6 +2150,9 @@
       </c>
       <c r="AU10" t="n">
         <v>-24</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>-54</v>
       </c>
     </row>
   </sheetData>
@@ -2135,7 +2166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI10"/>
+  <dimension ref="A1:CJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2225,6 +2256,7 @@
     <col width="12" customWidth="1" min="85" max="85"/>
     <col width="12" customWidth="1" min="86" max="86"/>
     <col width="12" customWidth="1" min="87" max="87"/>
+    <col width="12" customWidth="1" min="88" max="88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2663,6 +2695,11 @@
           <t>20260128</t>
         </is>
       </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>20260129</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2930,6 +2967,9 @@
       <c r="CI2" t="n">
         <v>99</v>
       </c>
+      <c r="CJ2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3197,6 +3237,9 @@
       <c r="CI3" t="n">
         <v>102</v>
       </c>
+      <c r="CJ3" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3464,6 +3507,9 @@
       <c r="CI4" t="n">
         <v>103</v>
       </c>
+      <c r="CJ4" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3731,6 +3777,9 @@
       <c r="CI5" t="n">
         <v>102</v>
       </c>
+      <c r="CJ5" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3998,6 +4047,9 @@
       <c r="CI6" t="n">
         <v>95</v>
       </c>
+      <c r="CJ6" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4265,6 +4317,9 @@
       <c r="CI7" t="n">
         <v>103</v>
       </c>
+      <c r="CJ7" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4532,6 +4587,9 @@
       <c r="CI8" t="n">
         <v>91</v>
       </c>
+      <c r="CJ8" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4799,6 +4857,9 @@
       <c r="CI9" t="n">
         <v>105</v>
       </c>
+      <c r="CJ9" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5065,6 +5126,9 @@
       </c>
       <c r="CI10" t="n">
         <v>98</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -7427,7 +7491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU10"/>
+  <dimension ref="A1:AV10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7477,6 +7541,7 @@
     <col width="12" customWidth="1" min="45" max="45"/>
     <col width="12" customWidth="1" min="46" max="46"/>
     <col width="12" customWidth="1" min="47" max="47"/>
+    <col width="12" customWidth="1" min="48" max="48"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7715,6 +7780,11 @@
           <t>20260128</t>
         </is>
       </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>20260129</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7862,6 +7932,9 @@
       <c r="AU2" t="n">
         <v>45</v>
       </c>
+      <c r="AV2" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8009,6 +8082,9 @@
       <c r="AU3" t="n">
         <v>48</v>
       </c>
+      <c r="AV3" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8156,6 +8232,9 @@
       <c r="AU4" t="n">
         <v>39</v>
       </c>
+      <c r="AV4" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8303,6 +8382,9 @@
       <c r="AU5" t="n">
         <v>75</v>
       </c>
+      <c r="AV5" t="n">
+        <v>245</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8450,6 +8532,9 @@
       <c r="AU6" t="n">
         <v>49</v>
       </c>
+      <c r="AV6" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8597,6 +8682,9 @@
       <c r="AU7" t="n">
         <v>42</v>
       </c>
+      <c r="AV7" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8744,6 +8832,9 @@
       <c r="AU8" t="n">
         <v>51</v>
       </c>
+      <c r="AV8" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8891,6 +8982,9 @@
       <c r="AU9" t="n">
         <v>128</v>
       </c>
+      <c r="AV9" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9037,6 +9131,9 @@
       </c>
       <c r="AU10" t="n">
         <v>38</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -9050,7 +9147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY10"/>
+  <dimension ref="A1:BZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9130,6 +9227,7 @@
     <col width="10" customWidth="1" min="75" max="75"/>
     <col width="10" customWidth="1" min="76" max="76"/>
     <col width="10" customWidth="1" min="77" max="77"/>
+    <col width="10" customWidth="1" min="78" max="78"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9368,6 +9466,9 @@
       <c r="BY1" s="1" t="n">
         <v>20260128</v>
       </c>
+      <c r="BZ1" s="1" t="n">
+        <v>20260129</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9605,6 +9706,9 @@
       <c r="BY2" t="n">
         <v>-40</v>
       </c>
+      <c r="BZ2" t="n">
+        <v>-27</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9842,6 +9946,9 @@
       <c r="BY3" t="n">
         <v>56</v>
       </c>
+      <c r="BZ3" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10079,6 +10186,9 @@
       <c r="BY4" t="n">
         <v>69</v>
       </c>
+      <c r="BZ4" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10316,6 +10426,9 @@
       <c r="BY5" t="n">
         <v>29</v>
       </c>
+      <c r="BZ5" t="n">
+        <v>-140</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10553,6 +10666,9 @@
       <c r="BY6" t="n">
         <v>-83</v>
       </c>
+      <c r="BZ6" t="n">
+        <v>-94</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10790,6 +10906,9 @@
       <c r="BY7" t="n">
         <v>65</v>
       </c>
+      <c r="BZ7" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11027,6 +11146,9 @@
       <c r="BY8" t="n">
         <v>-108</v>
       </c>
+      <c r="BZ8" t="n">
+        <v>-118</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11264,6 +11386,9 @@
       <c r="BY9" t="n">
         <v>65</v>
       </c>
+      <c r="BZ9" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11500,6 +11625,9 @@
       </c>
       <c r="BY10" t="n">
         <v>-51</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>-79</v>
       </c>
     </row>
   </sheetData>
@@ -11513,7 +11641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DB10"/>
+  <dimension ref="A1:DC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11622,6 +11750,7 @@
     <col width="12" customWidth="1" min="104" max="104"/>
     <col width="12" customWidth="1" min="105" max="105"/>
     <col width="12" customWidth="1" min="106" max="106"/>
+    <col width="12" customWidth="1" min="107" max="107"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11947,6 +12076,9 @@
       <c r="DB1" s="1" t="n">
         <v>20260128</v>
       </c>
+      <c r="DC1" s="1" t="n">
+        <v>20260129</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12271,6 +12403,9 @@
       <c r="DB2" t="n">
         <v>257.65</v>
       </c>
+      <c r="DC2" t="n">
+        <v>258</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12595,6 +12730,9 @@
       <c r="DB3" t="n">
         <v>246.365</v>
       </c>
+      <c r="DC3" t="n">
+        <v>242.82</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12919,6 +13057,9 @@
       <c r="DB4" t="n">
         <v>336.06</v>
       </c>
+      <c r="DC4" t="n">
+        <v>340.3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13243,6 +13384,9 @@
       <c r="DB5" t="n">
         <v>483.21</v>
       </c>
+      <c r="DC5" t="n">
+        <v>439.99</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13567,6 +13711,9 @@
       <c r="DB6" t="n">
         <v>85.625</v>
       </c>
+      <c r="DC6" t="n">
+        <v>84.31</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13891,6 +14038,9 @@
       <c r="DB7" t="n">
         <v>191.27</v>
       </c>
+      <c r="DC7" t="n">
+        <v>191.34</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14215,6 +14365,9 @@
       <c r="DB8" t="n">
         <v>164.4</v>
       </c>
+      <c r="DC8" t="n">
+        <v>157.63</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14539,6 +14692,9 @@
       <c r="DB9" t="n">
         <v>102.3</v>
       </c>
+      <c r="DC9" t="n">
+        <v>96.76000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14862,6 +15018,9 @@
       </c>
       <c r="DB10" t="n">
         <v>431.91</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>437.8</v>
       </c>
     </row>
   </sheetData>
@@ -14875,7 +15034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DB10"/>
+  <dimension ref="A1:DC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14984,6 +15143,7 @@
     <col width="12" customWidth="1" min="104" max="104"/>
     <col width="12" customWidth="1" min="105" max="105"/>
     <col width="12" customWidth="1" min="106" max="106"/>
+    <col width="12" customWidth="1" min="107" max="107"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15309,6 +15469,9 @@
       <c r="DB1" s="1" t="n">
         <v>20260128</v>
       </c>
+      <c r="DC1" s="1" t="n">
+        <v>20260129</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15633,6 +15796,9 @@
       <c r="DB2" t="n">
         <v>258.855</v>
       </c>
+      <c r="DC2" t="n">
+        <v>259.65</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15957,6 +16123,9 @@
       <c r="DB3" t="n">
         <v>247.775</v>
       </c>
+      <c r="DC3" t="n">
+        <v>243</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16281,6 +16450,9 @@
       <c r="DB4" t="n">
         <v>337.535</v>
       </c>
+      <c r="DC4" t="n">
+        <v>342.29</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16605,6 +16777,9 @@
       <c r="DB5" t="n">
         <v>483.74</v>
       </c>
+      <c r="DC5" t="n">
+        <v>442.5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16929,6 +17104,9 @@
       <c r="DB6" t="n">
         <v>86.47</v>
       </c>
+      <c r="DC6" t="n">
+        <v>84.38</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17253,6 +17431,9 @@
       <c r="DB7" t="n">
         <v>192.35</v>
       </c>
+      <c r="DC7" t="n">
+        <v>193.48</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17577,6 +17758,9 @@
       <c r="DB8" t="n">
         <v>165.045</v>
       </c>
+      <c r="DC8" t="n">
+        <v>157.63</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17901,6 +18085,9 @@
       <c r="DB9" t="n">
         <v>104.82</v>
       </c>
+      <c r="DC9" t="n">
+        <v>96.90000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18224,6 +18411,9 @@
       </c>
       <c r="DB10" t="n">
         <v>438.26</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>440.2299</v>
       </c>
     </row>
   </sheetData>
@@ -18237,7 +18427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DB10"/>
+  <dimension ref="A1:DC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18346,6 +18536,7 @@
     <col width="12" customWidth="1" min="104" max="104"/>
     <col width="12" customWidth="1" min="105" max="105"/>
     <col width="12" customWidth="1" min="106" max="106"/>
+    <col width="12" customWidth="1" min="107" max="107"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18671,6 +18862,9 @@
       <c r="DB1" s="1" t="n">
         <v>20260128</v>
       </c>
+      <c r="DC1" s="1" t="n">
+        <v>20260129</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18995,6 +19189,9 @@
       <c r="DB2" t="n">
         <v>254.51</v>
       </c>
+      <c r="DC2" t="n">
+        <v>254.41</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19319,6 +19516,9 @@
       <c r="DB3" t="n">
         <v>241.53</v>
       </c>
+      <c r="DC3" t="n">
+        <v>236.742</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19643,6 +19843,9 @@
       <c r="DB4" t="n">
         <v>331.94</v>
       </c>
+      <c r="DC4" t="n">
+        <v>326.54</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19967,6 +20170,9 @@
       <c r="DB5" t="n">
         <v>478</v>
       </c>
+      <c r="DC5" t="n">
+        <v>421.02</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20291,6 +20497,9 @@
       <c r="DB6" t="n">
         <v>84.295</v>
       </c>
+      <c r="DC6" t="n">
+        <v>82.3501</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20615,6 +20824,9 @@
       <c r="DB7" t="n">
         <v>189.84</v>
       </c>
+      <c r="DC7" t="n">
+        <v>186.06</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20939,6 +21151,9 @@
       <c r="DB8" t="n">
         <v>157.24</v>
       </c>
+      <c r="DC8" t="n">
+        <v>147.12</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21263,6 +21478,9 @@
       <c r="DB9" t="n">
         <v>95.09999999999999</v>
       </c>
+      <c r="DC9" t="n">
+        <v>92.61</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21586,6 +21804,9 @@
       </c>
       <c r="DB10" t="n">
         <v>430.1</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>414.62</v>
       </c>
     </row>
   </sheetData>
@@ -21599,7 +21820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DB10"/>
+  <dimension ref="A1:DC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21708,6 +21929,7 @@
     <col width="12" customWidth="1" min="104" max="104"/>
     <col width="12" customWidth="1" min="105" max="105"/>
     <col width="12" customWidth="1" min="106" max="106"/>
+    <col width="12" customWidth="1" min="107" max="107"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22033,6 +22255,9 @@
       <c r="DB1" s="1" t="n">
         <v>20260128</v>
       </c>
+      <c r="DC1" s="1" t="n">
+        <v>20260129</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22357,6 +22582,9 @@
       <c r="DB2" t="n">
         <v>256.44</v>
       </c>
+      <c r="DC2" t="n">
+        <v>258.28</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22681,6 +22909,9 @@
       <c r="DB3" t="n">
         <v>243.01</v>
       </c>
+      <c r="DC3" t="n">
+        <v>241.73</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23005,6 +23236,9 @@
       <c r="DB4" t="n">
         <v>336.01</v>
       </c>
+      <c r="DC4" t="n">
+        <v>338.25</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23329,6 +23563,9 @@
       <c r="DB5" t="n">
         <v>481.63</v>
       </c>
+      <c r="DC5" t="n">
+        <v>433.5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23653,6 +23890,9 @@
       <c r="DB6" t="n">
         <v>84.64</v>
       </c>
+      <c r="DC6" t="n">
+        <v>83.16</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23977,6 +24217,9 @@
       <c r="DB7" t="n">
         <v>191.52</v>
       </c>
+      <c r="DC7" t="n">
+        <v>192.51</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24301,6 +24544,9 @@
       <c r="DB8" t="n">
         <v>157.35</v>
       </c>
+      <c r="DC8" t="n">
+        <v>151.86</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24625,6 +24871,9 @@
       <c r="DB9" t="n">
         <v>95.16</v>
       </c>
+      <c r="DC9" t="n">
+        <v>93.88</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24948,6 +25197,9 @@
       </c>
       <c r="DB10" t="n">
         <v>431.46</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>416.56</v>
       </c>
     </row>
   </sheetData>
@@ -24961,7 +25213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DB10"/>
+  <dimension ref="A1:DC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25070,6 +25322,7 @@
     <col width="12" customWidth="1" min="104" max="104"/>
     <col width="12" customWidth="1" min="105" max="105"/>
     <col width="12" customWidth="1" min="106" max="106"/>
+    <col width="12" customWidth="1" min="107" max="107"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25395,6 +25648,9 @@
       <c r="DB1" s="1" t="n">
         <v>20260128</v>
       </c>
+      <c r="DC1" s="1" t="n">
+        <v>20260129</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25719,6 +25975,9 @@
       <c r="DB2" t="n">
         <v>41287971</v>
       </c>
+      <c r="DC2" t="n">
+        <v>67253009</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -26043,6 +26302,9 @@
       <c r="DB3" t="n">
         <v>40882657</v>
       </c>
+      <c r="DC3" t="n">
+        <v>47229643</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -26367,6 +26629,9 @@
       <c r="DB4" t="n">
         <v>27434434</v>
       </c>
+      <c r="DC4" t="n">
+        <v>39785612</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -26691,6 +26956,9 @@
       <c r="DB5" t="n">
         <v>36875403</v>
       </c>
+      <c r="DC5" t="n">
+        <v>128855323</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -27015,6 +27283,9 @@
       <c r="DB6" t="n">
         <v>37762612</v>
       </c>
+      <c r="DC6" t="n">
+        <v>42278102</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -27339,6 +27610,9 @@
       <c r="DB7" t="n">
         <v>148552677</v>
       </c>
+      <c r="DC7" t="n">
+        <v>171764375</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -27663,6 +27937,9 @@
       <c r="DB8" t="n">
         <v>44822848</v>
       </c>
+      <c r="DC8" t="n">
+        <v>59846810</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -27987,6 +28264,9 @@
       <c r="DB9" t="n">
         <v>25961583</v>
       </c>
+      <c r="DC9" t="n">
+        <v>16602870</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28310,6 +28590,9 @@
       </c>
       <c r="DB10" t="n">
         <v>54857403</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>81686127</v>
       </c>
     </row>
   </sheetData>
@@ -28323,7 +28606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI10"/>
+  <dimension ref="A1:CJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -28413,6 +28696,7 @@
     <col width="10" customWidth="1" min="85" max="85"/>
     <col width="10" customWidth="1" min="86" max="86"/>
     <col width="10" customWidth="1" min="87" max="87"/>
+    <col width="10" customWidth="1" min="88" max="88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28681,6 +28965,9 @@
       <c r="CI1" s="1" t="n">
         <v>20260128</v>
       </c>
+      <c r="CJ1" s="1" t="n">
+        <v>20260129</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -28948,6 +29235,9 @@
       <c r="CI2" t="n">
         <v>37</v>
       </c>
+      <c r="CJ2" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -29215,6 +29505,9 @@
       <c r="CI3" t="n">
         <v>79</v>
       </c>
+      <c r="CJ3" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -29482,6 +29775,9 @@
       <c r="CI4" t="n">
         <v>100</v>
       </c>
+      <c r="CJ4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -29749,6 +30045,9 @@
       <c r="CI5" t="n">
         <v>87</v>
       </c>
+      <c r="CJ5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -30016,6 +30315,9 @@
       <c r="CI6" t="n">
         <v>11</v>
       </c>
+      <c r="CJ6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -30283,6 +30585,9 @@
       <c r="CI7" t="n">
         <v>100</v>
       </c>
+      <c r="CJ7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -30550,6 +30855,9 @@
       <c r="CI8" t="n">
         <v>0</v>
       </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -30817,6 +31125,9 @@
       <c r="CI9" t="n">
         <v>82</v>
       </c>
+      <c r="CJ9" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -31083,6 +31394,9 @@
       </c>
       <c r="CI10" t="n">
         <v>35</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -31096,7 +31410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU10"/>
+  <dimension ref="A1:AV10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -31146,6 +31460,7 @@
     <col width="10" customWidth="1" min="45" max="45"/>
     <col width="10" customWidth="1" min="46" max="46"/>
     <col width="10" customWidth="1" min="47" max="47"/>
+    <col width="10" customWidth="1" min="48" max="48"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31294,6 +31609,9 @@
       <c r="AU1" s="1" t="n">
         <v>20260128</v>
       </c>
+      <c r="AV1" s="1" t="n">
+        <v>20260129</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -31441,6 +31759,9 @@
       <c r="AU2" t="n">
         <v>25</v>
       </c>
+      <c r="AV2" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -31588,6 +31909,9 @@
       <c r="AU3" t="n">
         <v>70</v>
       </c>
+      <c r="AV3" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -31735,6 +32059,9 @@
       <c r="AU4" t="n">
         <v>100</v>
       </c>
+      <c r="AV4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -31882,6 +32209,9 @@
       <c r="AU5" t="n">
         <v>51</v>
       </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -32029,6 +32359,9 @@
       <c r="AU6" t="n">
         <v>0</v>
       </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -32176,6 +32509,9 @@
       <c r="AU7" t="n">
         <v>57</v>
       </c>
+      <c r="AV7" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -32323,6 +32659,9 @@
       <c r="AU8" t="n">
         <v>5</v>
       </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -32470,6 +32809,9 @@
       <c r="AU9" t="n">
         <v>86</v>
       </c>
+      <c r="AV9" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -32616,6 +32958,9 @@
       </c>
       <c r="AU10" t="n">
         <v>41</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -32629,7 +32974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI10"/>
+  <dimension ref="A1:CJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -32719,6 +33064,7 @@
     <col width="10" customWidth="1" min="85" max="85"/>
     <col width="10" customWidth="1" min="86" max="86"/>
     <col width="10" customWidth="1" min="87" max="87"/>
+    <col width="10" customWidth="1" min="88" max="88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32987,6 +33333,9 @@
       <c r="CI1" s="1" t="n">
         <v>20260128</v>
       </c>
+      <c r="CJ1" s="1" t="n">
+        <v>20260129</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -33254,6 +33603,9 @@
       <c r="CI2" t="n">
         <v>-17</v>
       </c>
+      <c r="CJ2" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -33521,6 +33873,9 @@
       <c r="CI3" t="n">
         <v>40</v>
       </c>
+      <c r="CJ3" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -33788,6 +34143,9 @@
       <c r="CI4" t="n">
         <v>59</v>
       </c>
+      <c r="CJ4" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -34055,6 +34413,9 @@
       <c r="CI5" t="n">
         <v>45</v>
       </c>
+      <c r="CJ5" t="n">
+        <v>-121</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -34322,6 +34683,9 @@
       <c r="CI6" t="n">
         <v>-70</v>
       </c>
+      <c r="CJ6" t="n">
+        <v>-86</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -34589,6 +34953,9 @@
       <c r="CI7" t="n">
         <v>84</v>
       </c>
+      <c r="CJ7" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -34856,6 +35223,9 @@
       <c r="CI8" t="n">
         <v>-116</v>
       </c>
+      <c r="CJ8" t="n">
+        <v>-124</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -35123,6 +35493,9 @@
       <c r="CI9" t="n">
         <v>46</v>
       </c>
+      <c r="CJ9" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -35389,6 +35762,9 @@
       </c>
       <c r="CI10" t="n">
         <v>-46</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>-111</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -602,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV10"/>
+  <dimension ref="A1:AW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -653,6 +653,7 @@
     <col width="10" customWidth="1" min="46" max="46"/>
     <col width="10" customWidth="1" min="47" max="47"/>
     <col width="10" customWidth="1" min="48" max="48"/>
+    <col width="10" customWidth="1" min="49" max="49"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -804,6 +805,9 @@
       <c r="AV1" s="1" t="n">
         <v>20260129</v>
       </c>
+      <c r="AW1" s="1" t="n">
+        <v>20260130</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -954,6 +958,9 @@
       <c r="AV2" t="n">
         <v>-57</v>
       </c>
+      <c r="AW2" t="n">
+        <v>-49</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1104,6 +1111,9 @@
       <c r="AV3" t="n">
         <v>42</v>
       </c>
+      <c r="AW3" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1254,6 +1264,9 @@
       <c r="AV4" t="n">
         <v>77</v>
       </c>
+      <c r="AW4" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1404,6 +1417,9 @@
       <c r="AV5" t="n">
         <v>-148</v>
       </c>
+      <c r="AW5" t="n">
+        <v>-147</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1554,6 +1570,9 @@
       <c r="AV6" t="n">
         <v>-24</v>
       </c>
+      <c r="AW6" t="n">
+        <v>-22</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1704,6 +1723,9 @@
       <c r="AV7" t="n">
         <v>55</v>
       </c>
+      <c r="AW7" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1854,6 +1876,9 @@
       <c r="AV8" t="n">
         <v>-112</v>
       </c>
+      <c r="AW8" t="n">
+        <v>-131</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2004,6 +2029,9 @@
       <c r="AV9" t="n">
         <v>80</v>
       </c>
+      <c r="AW9" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2153,6 +2181,9 @@
       </c>
       <c r="AV10" t="n">
         <v>-54</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>-23</v>
       </c>
     </row>
   </sheetData>
@@ -2166,7 +2197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ10"/>
+  <dimension ref="A1:CK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2257,6 +2288,7 @@
     <col width="12" customWidth="1" min="86" max="86"/>
     <col width="12" customWidth="1" min="87" max="87"/>
     <col width="12" customWidth="1" min="88" max="88"/>
+    <col width="12" customWidth="1" min="89" max="89"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2700,6 +2732,11 @@
           <t>20260129</t>
         </is>
       </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2970,6 +3007,9 @@
       <c r="CJ2" t="n">
         <v>100</v>
       </c>
+      <c r="CK2" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3240,6 +3280,9 @@
       <c r="CJ3" t="n">
         <v>101</v>
       </c>
+      <c r="CK3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3510,6 +3553,9 @@
       <c r="CJ4" t="n">
         <v>103</v>
       </c>
+      <c r="CK4" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3780,6 +3826,9 @@
       <c r="CJ5" t="n">
         <v>93</v>
       </c>
+      <c r="CK5" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4050,6 +4099,9 @@
       <c r="CJ6" t="n">
         <v>94</v>
       </c>
+      <c r="CK6" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4320,6 +4372,9 @@
       <c r="CJ7" t="n">
         <v>103</v>
       </c>
+      <c r="CK7" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4590,6 +4645,9 @@
       <c r="CJ8" t="n">
         <v>88</v>
       </c>
+      <c r="CK8" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4860,6 +4918,9 @@
       <c r="CJ9" t="n">
         <v>103</v>
       </c>
+      <c r="CK9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5129,6 +5190,9 @@
       </c>
       <c r="CJ10" t="n">
         <v>95</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -5142,7 +5206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ10"/>
+  <dimension ref="A1:BR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5214,6 +5278,7 @@
     <col width="12" customWidth="1" min="67" max="67"/>
     <col width="12" customWidth="1" min="68" max="68"/>
     <col width="12" customWidth="1" min="69" max="69"/>
+    <col width="12" customWidth="1" min="70" max="70"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5562,6 +5627,11 @@
           <t>20251231</t>
         </is>
       </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5775,6 +5845,9 @@
       <c r="BQ2" t="n">
         <v>3.44</v>
       </c>
+      <c r="BR2" t="n">
+        <v>0.43</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5988,6 +6061,9 @@
       <c r="BQ3" t="n">
         <v>3.49</v>
       </c>
+      <c r="BR3" t="n">
+        <v>-4.55</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6201,6 +6277,9 @@
       <c r="BQ4" t="n">
         <v>5.89</v>
       </c>
+      <c r="BR4" t="n">
+        <v>-6.78</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6414,6 +6493,9 @@
       <c r="BQ5" t="n">
         <v>4.93</v>
       </c>
+      <c r="BR5" t="n">
+        <v>67.75</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6627,6 +6709,9 @@
       <c r="BQ6" t="n">
         <v>3.13</v>
       </c>
+      <c r="BR6" t="n">
+        <v>16.7</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6840,6 +6925,9 @@
       <c r="BQ7" t="n">
         <v>5.36</v>
       </c>
+      <c r="BR7" t="n">
+        <v>-23.11</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7053,6 +7141,9 @@
       <c r="BQ8" t="n">
         <v>5.71</v>
       </c>
+      <c r="BR8" t="n">
+        <v>29.09</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7266,6 +7357,9 @@
       <c r="BQ9" t="n">
         <v>1.57</v>
       </c>
+      <c r="BR9" t="n">
+        <v>32.43</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7478,6 +7572,9 @@
       </c>
       <c r="BQ10" t="n">
         <v>16.34</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>-45.71</v>
       </c>
     </row>
   </sheetData>
@@ -7491,7 +7588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV10"/>
+  <dimension ref="A1:AW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7542,6 +7639,7 @@
     <col width="12" customWidth="1" min="46" max="46"/>
     <col width="12" customWidth="1" min="47" max="47"/>
     <col width="12" customWidth="1" min="48" max="48"/>
+    <col width="12" customWidth="1" min="49" max="49"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7785,6 +7883,11 @@
           <t>20260129</t>
         </is>
       </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7935,6 +8038,9 @@
       <c r="AV2" t="n">
         <v>75</v>
       </c>
+      <c r="AW2" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8085,6 +8191,9 @@
       <c r="AV3" t="n">
         <v>58</v>
       </c>
+      <c r="AW3" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8235,6 +8344,9 @@
       <c r="AV4" t="n">
         <v>57</v>
       </c>
+      <c r="AW4" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8385,6 +8497,9 @@
       <c r="AV5" t="n">
         <v>245</v>
       </c>
+      <c r="AW5" t="n">
+        <v>109</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8535,6 +8650,9 @@
       <c r="AV6" t="n">
         <v>54</v>
       </c>
+      <c r="AW6" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8685,6 +8803,9 @@
       <c r="AV7" t="n">
         <v>48</v>
       </c>
+      <c r="AW7" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8835,6 +8956,9 @@
       <c r="AV8" t="n">
         <v>68</v>
       </c>
+      <c r="AW8" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8985,6 +9109,9 @@
       <c r="AV9" t="n">
         <v>81</v>
       </c>
+      <c r="AW9" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9134,6 +9261,9 @@
       </c>
       <c r="AV10" t="n">
         <v>56</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -9147,7 +9277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ10"/>
+  <dimension ref="A1:CA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9228,6 +9358,7 @@
     <col width="10" customWidth="1" min="76" max="76"/>
     <col width="10" customWidth="1" min="77" max="77"/>
     <col width="10" customWidth="1" min="78" max="78"/>
+    <col width="10" customWidth="1" min="79" max="79"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9469,6 +9600,9 @@
       <c r="BZ1" s="1" t="n">
         <v>20260129</v>
       </c>
+      <c r="CA1" s="1" t="n">
+        <v>20260130</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9709,6 +9843,9 @@
       <c r="BZ2" t="n">
         <v>-27</v>
       </c>
+      <c r="CA2" t="n">
+        <v>-18</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9949,6 +10086,9 @@
       <c r="BZ3" t="n">
         <v>45</v>
       </c>
+      <c r="CA3" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10189,6 +10329,9 @@
       <c r="BZ4" t="n">
         <v>73</v>
       </c>
+      <c r="CA4" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10429,6 +10572,9 @@
       <c r="BZ5" t="n">
         <v>-140</v>
       </c>
+      <c r="CA5" t="n">
+        <v>-128</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10669,6 +10815,9 @@
       <c r="BZ6" t="n">
         <v>-94</v>
       </c>
+      <c r="CA6" t="n">
+        <v>-83</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10909,6 +11058,9 @@
       <c r="BZ7" t="n">
         <v>70</v>
       </c>
+      <c r="CA7" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11149,6 +11301,9 @@
       <c r="BZ8" t="n">
         <v>-118</v>
       </c>
+      <c r="CA8" t="n">
+        <v>-123</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11389,6 +11544,9 @@
       <c r="BZ9" t="n">
         <v>48</v>
       </c>
+      <c r="CA9" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11628,6 +11786,9 @@
       </c>
       <c r="BZ10" t="n">
         <v>-79</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>-45</v>
       </c>
     </row>
   </sheetData>
@@ -11641,7 +11802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DC10"/>
+  <dimension ref="A1:DD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11751,6 +11912,7 @@
     <col width="12" customWidth="1" min="105" max="105"/>
     <col width="12" customWidth="1" min="106" max="106"/>
     <col width="12" customWidth="1" min="107" max="107"/>
+    <col width="12" customWidth="1" min="108" max="108"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12079,6 +12241,9 @@
       <c r="DC1" s="1" t="n">
         <v>20260129</v>
       </c>
+      <c r="DD1" s="1" t="n">
+        <v>20260130</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12406,6 +12571,9 @@
       <c r="DC2" t="n">
         <v>258</v>
       </c>
+      <c r="DD2" t="n">
+        <v>255.165</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12733,6 +12901,9 @@
       <c r="DC3" t="n">
         <v>242.82</v>
       </c>
+      <c r="DD3" t="n">
+        <v>239.89</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13060,6 +13231,9 @@
       <c r="DC4" t="n">
         <v>340.3</v>
       </c>
+      <c r="DD4" t="n">
+        <v>340</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13387,6 +13561,9 @@
       <c r="DC5" t="n">
         <v>439.99</v>
       </c>
+      <c r="DD5" t="n">
+        <v>439.17</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13714,6 +13891,9 @@
       <c r="DC6" t="n">
         <v>84.31</v>
       </c>
+      <c r="DD6" t="n">
+        <v>83.09999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14041,6 +14221,9 @@
       <c r="DC7" t="n">
         <v>191.34</v>
       </c>
+      <c r="DD7" t="n">
+        <v>191.21</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14368,6 +14551,9 @@
       <c r="DC8" t="n">
         <v>157.63</v>
       </c>
+      <c r="DD8" t="n">
+        <v>150.05</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14695,6 +14881,9 @@
       <c r="DC9" t="n">
         <v>96.76000000000001</v>
       </c>
+      <c r="DD9" t="n">
+        <v>92.72</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15021,6 +15210,9 @@
       </c>
       <c r="DC10" t="n">
         <v>437.8</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>425.35</v>
       </c>
     </row>
   </sheetData>
@@ -15034,7 +15226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DC10"/>
+  <dimension ref="A1:DD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15144,6 +15336,7 @@
     <col width="12" customWidth="1" min="105" max="105"/>
     <col width="12" customWidth="1" min="106" max="106"/>
     <col width="12" customWidth="1" min="107" max="107"/>
+    <col width="12" customWidth="1" min="108" max="108"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15472,6 +15665,9 @@
       <c r="DC1" s="1" t="n">
         <v>20260129</v>
       </c>
+      <c r="DD1" s="1" t="n">
+        <v>20260130</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15799,6 +15995,9 @@
       <c r="DC2" t="n">
         <v>259.65</v>
       </c>
+      <c r="DD2" t="n">
+        <v>261.8999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16126,6 +16325,9 @@
       <c r="DC3" t="n">
         <v>243</v>
       </c>
+      <c r="DD3" t="n">
+        <v>243.315</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16453,6 +16655,9 @@
       <c r="DC4" t="n">
         <v>342.29</v>
       </c>
+      <c r="DD4" t="n">
+        <v>340</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16780,6 +16985,9 @@
       <c r="DC5" t="n">
         <v>442.5</v>
       </c>
+      <c r="DD5" t="n">
+        <v>439.6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17107,6 +17315,9 @@
       <c r="DC6" t="n">
         <v>84.38</v>
       </c>
+      <c r="DD6" t="n">
+        <v>84.05500000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17434,6 +17645,9 @@
       <c r="DC7" t="n">
         <v>193.48</v>
       </c>
+      <c r="DD7" t="n">
+        <v>194.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17761,6 +17975,9 @@
       <c r="DC8" t="n">
         <v>157.63</v>
       </c>
+      <c r="DD8" t="n">
+        <v>151</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18088,6 +18305,9 @@
       <c r="DC9" t="n">
         <v>96.90000000000001</v>
       </c>
+      <c r="DD9" t="n">
+        <v>93.20999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18414,6 +18634,9 @@
       </c>
       <c r="DC10" t="n">
         <v>440.2299</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>439.88</v>
       </c>
     </row>
   </sheetData>
@@ -18427,7 +18650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DC10"/>
+  <dimension ref="A1:DD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18537,6 +18760,7 @@
     <col width="12" customWidth="1" min="105" max="105"/>
     <col width="12" customWidth="1" min="106" max="106"/>
     <col width="12" customWidth="1" min="107" max="107"/>
+    <col width="12" customWidth="1" min="108" max="108"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18865,6 +19089,9 @@
       <c r="DC1" s="1" t="n">
         <v>20260129</v>
       </c>
+      <c r="DD1" s="1" t="n">
+        <v>20260130</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19192,6 +19419,9 @@
       <c r="DC2" t="n">
         <v>254.41</v>
       </c>
+      <c r="DD2" t="n">
+        <v>252.18</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19519,6 +19749,9 @@
       <c r="DC3" t="n">
         <v>236.742</v>
       </c>
+      <c r="DD3" t="n">
+        <v>237.64</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19846,6 +20079,9 @@
       <c r="DC4" t="n">
         <v>326.54</v>
       </c>
+      <c r="DD4" t="n">
+        <v>332.285</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20173,6 +20409,9 @@
       <c r="DC5" t="n">
         <v>421.02</v>
       </c>
+      <c r="DD5" t="n">
+        <v>426.45</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20500,6 +20739,9 @@
       <c r="DC6" t="n">
         <v>82.3501</v>
       </c>
+      <c r="DD6" t="n">
+        <v>82.78</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20827,6 +21069,9 @@
       <c r="DC7" t="n">
         <v>186.06</v>
       </c>
+      <c r="DD7" t="n">
+        <v>189.47</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21154,6 +21399,9 @@
       <c r="DC8" t="n">
         <v>147.12</v>
       </c>
+      <c r="DD8" t="n">
+        <v>145.139</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21481,6 +21729,9 @@
       <c r="DC9" t="n">
         <v>92.61</v>
       </c>
+      <c r="DD9" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21807,6 +22058,9 @@
       </c>
       <c r="DC10" t="n">
         <v>414.62</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>422.7</v>
       </c>
     </row>
   </sheetData>
@@ -21820,7 +22074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DC10"/>
+  <dimension ref="A1:DD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21930,6 +22184,7 @@
     <col width="12" customWidth="1" min="105" max="105"/>
     <col width="12" customWidth="1" min="106" max="106"/>
     <col width="12" customWidth="1" min="107" max="107"/>
+    <col width="12" customWidth="1" min="108" max="108"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22258,6 +22513,9 @@
       <c r="DC1" s="1" t="n">
         <v>20260129</v>
       </c>
+      <c r="DD1" s="1" t="n">
+        <v>20260130</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22585,6 +22843,9 @@
       <c r="DC2" t="n">
         <v>258.28</v>
       </c>
+      <c r="DD2" t="n">
+        <v>259.48</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22912,6 +23173,9 @@
       <c r="DC3" t="n">
         <v>241.73</v>
       </c>
+      <c r="DD3" t="n">
+        <v>239.3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23239,6 +23503,9 @@
       <c r="DC4" t="n">
         <v>338.25</v>
       </c>
+      <c r="DD4" t="n">
+        <v>338</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23566,6 +23833,9 @@
       <c r="DC5" t="n">
         <v>433.5</v>
       </c>
+      <c r="DD5" t="n">
+        <v>430.29</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23893,6 +24163,9 @@
       <c r="DC6" t="n">
         <v>83.16</v>
       </c>
+      <c r="DD6" t="n">
+        <v>83.48999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24220,6 +24493,9 @@
       <c r="DC7" t="n">
         <v>192.51</v>
       </c>
+      <c r="DD7" t="n">
+        <v>191.13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24547,6 +24823,9 @@
       <c r="DC8" t="n">
         <v>151.86</v>
       </c>
+      <c r="DD8" t="n">
+        <v>146.59</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24874,6 +25153,9 @@
       <c r="DC9" t="n">
         <v>93.88</v>
       </c>
+      <c r="DD9" t="n">
+        <v>91.95</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25200,6 +25482,9 @@
       </c>
       <c r="DC10" t="n">
         <v>416.56</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>430.41</v>
       </c>
     </row>
   </sheetData>
@@ -25213,7 +25498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DC10"/>
+  <dimension ref="A1:DD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25323,6 +25608,7 @@
     <col width="12" customWidth="1" min="105" max="105"/>
     <col width="12" customWidth="1" min="106" max="106"/>
     <col width="12" customWidth="1" min="107" max="107"/>
+    <col width="12" customWidth="1" min="108" max="108"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25651,6 +25937,9 @@
       <c r="DC1" s="1" t="n">
         <v>20260129</v>
       </c>
+      <c r="DD1" s="1" t="n">
+        <v>20260130</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25978,6 +26267,9 @@
       <c r="DC2" t="n">
         <v>67253009</v>
       </c>
+      <c r="DD2" t="n">
+        <v>92443408</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -26305,6 +26597,9 @@
       <c r="DC3" t="n">
         <v>47229643</v>
       </c>
+      <c r="DD3" t="n">
+        <v>46585024</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -26632,6 +26927,9 @@
       <c r="DC4" t="n">
         <v>39785612</v>
       </c>
+      <c r="DD4" t="n">
+        <v>31023954</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -26959,6 +27257,9 @@
       <c r="DC5" t="n">
         <v>128855323</v>
       </c>
+      <c r="DD5" t="n">
+        <v>58566819</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -27286,6 +27587,9 @@
       <c r="DC6" t="n">
         <v>42278102</v>
       </c>
+      <c r="DD6" t="n">
+        <v>45755030</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -27613,6 +27917,9 @@
       <c r="DC7" t="n">
         <v>171764375</v>
       </c>
+      <c r="DD7" t="n">
+        <v>179489463</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -27940,6 +28247,9 @@
       <c r="DC8" t="n">
         <v>59846810</v>
       </c>
+      <c r="DD8" t="n">
+        <v>47271042</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -28267,6 +28577,9 @@
       <c r="DC9" t="n">
         <v>16602870</v>
       </c>
+      <c r="DD9" t="n">
+        <v>10747970</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28593,6 +28906,9 @@
       </c>
       <c r="DC10" t="n">
         <v>81686127</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>82626066</v>
       </c>
     </row>
   </sheetData>
@@ -28606,7 +28922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ10"/>
+  <dimension ref="A1:CK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -28697,6 +29013,7 @@
     <col width="10" customWidth="1" min="86" max="86"/>
     <col width="10" customWidth="1" min="87" max="87"/>
     <col width="10" customWidth="1" min="88" max="88"/>
+    <col width="10" customWidth="1" min="89" max="89"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28968,6 +29285,9 @@
       <c r="CJ1" s="1" t="n">
         <v>20260129</v>
       </c>
+      <c r="CK1" s="1" t="n">
+        <v>20260130</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -29238,6 +29558,9 @@
       <c r="CJ2" t="n">
         <v>46</v>
       </c>
+      <c r="CK2" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -29508,6 +29831,9 @@
       <c r="CJ3" t="n">
         <v>73</v>
       </c>
+      <c r="CK3" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -29778,6 +30104,9 @@
       <c r="CJ4" t="n">
         <v>100</v>
       </c>
+      <c r="CK4" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -30048,6 +30377,9 @@
       <c r="CJ5" t="n">
         <v>0</v>
       </c>
+      <c r="CK5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -30318,6 +30650,9 @@
       <c r="CJ6" t="n">
         <v>0</v>
       </c>
+      <c r="CK6" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -30588,6 +30923,9 @@
       <c r="CJ7" t="n">
         <v>100</v>
       </c>
+      <c r="CK7" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -30858,6 +31196,9 @@
       <c r="CJ8" t="n">
         <v>0</v>
       </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -31128,6 +31469,9 @@
       <c r="CJ9" t="n">
         <v>73</v>
       </c>
+      <c r="CK9" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -31397,6 +31741,9 @@
       </c>
       <c r="CJ10" t="n">
         <v>0</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -31410,7 +31757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV10"/>
+  <dimension ref="A1:AW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -31461,6 +31808,7 @@
     <col width="10" customWidth="1" min="46" max="46"/>
     <col width="10" customWidth="1" min="47" max="47"/>
     <col width="10" customWidth="1" min="48" max="48"/>
+    <col width="10" customWidth="1" min="49" max="49"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31612,6 +31960,9 @@
       <c r="AV1" s="1" t="n">
         <v>20260129</v>
       </c>
+      <c r="AW1" s="1" t="n">
+        <v>20260130</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -31762,6 +32113,9 @@
       <c r="AV2" t="n">
         <v>29</v>
       </c>
+      <c r="AW2" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -31912,6 +32266,9 @@
       <c r="AV3" t="n">
         <v>67</v>
       </c>
+      <c r="AW3" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -32062,6 +32419,9 @@
       <c r="AV4" t="n">
         <v>100</v>
       </c>
+      <c r="AW4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -32212,6 +32572,9 @@
       <c r="AV5" t="n">
         <v>0</v>
       </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -32362,6 +32725,9 @@
       <c r="AV6" t="n">
         <v>0</v>
       </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -32512,6 +32878,9 @@
       <c r="AV7" t="n">
         <v>60</v>
       </c>
+      <c r="AW7" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -32662,6 +33031,9 @@
       <c r="AV8" t="n">
         <v>0</v>
       </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -32812,6 +33184,9 @@
       <c r="AV9" t="n">
         <v>79</v>
       </c>
+      <c r="AW9" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -32961,6 +33336,9 @@
       </c>
       <c r="AV10" t="n">
         <v>26</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -32974,7 +33352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ10"/>
+  <dimension ref="A1:CK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -33065,6 +33443,7 @@
     <col width="10" customWidth="1" min="86" max="86"/>
     <col width="10" customWidth="1" min="87" max="87"/>
     <col width="10" customWidth="1" min="88" max="88"/>
+    <col width="10" customWidth="1" min="89" max="89"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33336,6 +33715,9 @@
       <c r="CJ1" s="1" t="n">
         <v>20260129</v>
       </c>
+      <c r="CK1" s="1" t="n">
+        <v>20260130</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -33606,6 +33988,9 @@
       <c r="CJ2" t="n">
         <v>-1</v>
       </c>
+      <c r="CK2" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -33876,6 +34261,9 @@
       <c r="CJ3" t="n">
         <v>27</v>
       </c>
+      <c r="CK3" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -34146,6 +34534,9 @@
       <c r="CJ4" t="n">
         <v>67</v>
       </c>
+      <c r="CK4" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -34416,6 +34807,9 @@
       <c r="CJ5" t="n">
         <v>-121</v>
       </c>
+      <c r="CK5" t="n">
+        <v>-109</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -34686,6 +35080,9 @@
       <c r="CJ6" t="n">
         <v>-86</v>
       </c>
+      <c r="CK6" t="n">
+        <v>-75</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -34956,6 +35353,9 @@
       <c r="CJ7" t="n">
         <v>88</v>
       </c>
+      <c r="CK7" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -35226,6 +35626,9 @@
       <c r="CJ8" t="n">
         <v>-124</v>
       </c>
+      <c r="CK8" t="n">
+        <v>-122</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -35496,6 +35899,9 @@
       <c r="CJ9" t="n">
         <v>28</v>
       </c>
+      <c r="CK9" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -35765,6 +36171,9 @@
       </c>
       <c r="CJ10" t="n">
         <v>-111</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>-34</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -602,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW10"/>
+  <dimension ref="A1:AX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -654,6 +654,7 @@
     <col width="10" customWidth="1" min="47" max="47"/>
     <col width="10" customWidth="1" min="48" max="48"/>
     <col width="10" customWidth="1" min="49" max="49"/>
+    <col width="10" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -808,6 +809,9 @@
       <c r="AW1" s="1" t="n">
         <v>20260130</v>
       </c>
+      <c r="AX1" s="1" t="n">
+        <v>20260202</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -961,6 +965,9 @@
       <c r="AW2" t="n">
         <v>-49</v>
       </c>
+      <c r="AX2" t="n">
+        <v>-48</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1114,6 +1121,9 @@
       <c r="AW3" t="n">
         <v>31</v>
       </c>
+      <c r="AX3" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1267,6 +1277,9 @@
       <c r="AW4" t="n">
         <v>74</v>
       </c>
+      <c r="AX4" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1420,6 +1433,9 @@
       <c r="AW5" t="n">
         <v>-147</v>
       </c>
+      <c r="AX5" t="n">
+        <v>-137</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1573,6 +1589,9 @@
       <c r="AW6" t="n">
         <v>-22</v>
       </c>
+      <c r="AX6" t="n">
+        <v>-21</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1726,6 +1745,9 @@
       <c r="AW7" t="n">
         <v>51</v>
       </c>
+      <c r="AX7" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1879,6 +1901,9 @@
       <c r="AW8" t="n">
         <v>-131</v>
       </c>
+      <c r="AX8" t="n">
+        <v>-123</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2032,6 +2057,9 @@
       <c r="AW9" t="n">
         <v>56</v>
       </c>
+      <c r="AX9" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2183,6 +2211,9 @@
         <v>-54</v>
       </c>
       <c r="AW10" t="n">
+        <v>-23</v>
+      </c>
+      <c r="AX10" t="n">
         <v>-23</v>
       </c>
     </row>
@@ -2197,7 +2228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CK10"/>
+  <dimension ref="A1:CL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2289,6 +2320,7 @@
     <col width="12" customWidth="1" min="87" max="87"/>
     <col width="12" customWidth="1" min="88" max="88"/>
     <col width="12" customWidth="1" min="89" max="89"/>
+    <col width="12" customWidth="1" min="90" max="90"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2737,6 +2769,11 @@
           <t>20260130</t>
         </is>
       </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>20260202</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3010,6 +3047,9 @@
       <c r="CK2" t="n">
         <v>101</v>
       </c>
+      <c r="CL2" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3283,6 +3323,9 @@
       <c r="CK3" t="n">
         <v>100</v>
       </c>
+      <c r="CL3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3556,6 +3599,9 @@
       <c r="CK4" t="n">
         <v>103</v>
       </c>
+      <c r="CL4" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3829,6 +3875,9 @@
       <c r="CK5" t="n">
         <v>93</v>
       </c>
+      <c r="CL5" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4102,6 +4151,9 @@
       <c r="CK6" t="n">
         <v>95</v>
       </c>
+      <c r="CL6" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4375,6 +4427,9 @@
       <c r="CK7" t="n">
         <v>102</v>
       </c>
+      <c r="CL7" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4648,6 +4703,9 @@
       <c r="CK8" t="n">
         <v>86</v>
       </c>
+      <c r="CL8" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4921,6 +4979,9 @@
       <c r="CK9" t="n">
         <v>100</v>
       </c>
+      <c r="CL9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5192,6 +5253,9 @@
         <v>95</v>
       </c>
       <c r="CK10" t="n">
+        <v>99</v>
+      </c>
+      <c r="CL10" t="n">
         <v>99</v>
       </c>
     </row>
@@ -5206,7 +5270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR10"/>
+  <dimension ref="A1:BS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5279,6 +5343,7 @@
     <col width="12" customWidth="1" min="68" max="68"/>
     <col width="12" customWidth="1" min="69" max="69"/>
     <col width="12" customWidth="1" min="70" max="70"/>
+    <col width="12" customWidth="1" min="71" max="71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5632,6 +5697,11 @@
           <t>20260130</t>
         </is>
       </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>20260202</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5848,6 +5918,9 @@
       <c r="BR2" t="n">
         <v>0.43</v>
       </c>
+      <c r="BS2" t="n">
+        <v>-13.01</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6064,6 +6137,9 @@
       <c r="BR3" t="n">
         <v>-4.55</v>
       </c>
+      <c r="BS3" t="n">
+        <v>-17.29</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6280,6 +6356,9 @@
       <c r="BR4" t="n">
         <v>-6.78</v>
       </c>
+      <c r="BS4" t="n">
+        <v>-13.26</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6496,6 +6575,9 @@
       <c r="BR5" t="n">
         <v>67.75</v>
       </c>
+      <c r="BS5" t="n">
+        <v>74.08</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6712,6 +6794,9 @@
       <c r="BR6" t="n">
         <v>16.7</v>
       </c>
+      <c r="BS6" t="n">
+        <v>17.72</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6928,6 +7013,9 @@
       <c r="BR7" t="n">
         <v>-23.11</v>
       </c>
+      <c r="BS7" t="n">
+        <v>-18.94</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7144,6 +7232,9 @@
       <c r="BR8" t="n">
         <v>29.09</v>
       </c>
+      <c r="BS8" t="n">
+        <v>43.09</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7360,6 +7451,9 @@
       <c r="BR9" t="n">
         <v>32.43</v>
       </c>
+      <c r="BS9" t="n">
+        <v>14.14</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7575,6 +7669,9 @@
       </c>
       <c r="BR10" t="n">
         <v>-45.71</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>-43.8</v>
       </c>
     </row>
   </sheetData>
@@ -7588,7 +7685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW10"/>
+  <dimension ref="A1:AX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7640,6 +7737,7 @@
     <col width="12" customWidth="1" min="47" max="47"/>
     <col width="12" customWidth="1" min="48" max="48"/>
     <col width="12" customWidth="1" min="49" max="49"/>
+    <col width="12" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7888,6 +7986,11 @@
           <t>20260130</t>
         </is>
       </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>20260202</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8041,6 +8144,9 @@
       <c r="AW2" t="n">
         <v>101</v>
       </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8194,6 +8300,9 @@
       <c r="AW3" t="n">
         <v>59</v>
       </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8347,6 +8456,9 @@
       <c r="AW4" t="n">
         <v>44</v>
       </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8500,6 +8612,9 @@
       <c r="AW5" t="n">
         <v>109</v>
       </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8653,6 +8768,9 @@
       <c r="AW6" t="n">
         <v>58</v>
       </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8806,6 +8924,9 @@
       <c r="AW7" t="n">
         <v>50</v>
       </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8959,6 +9080,9 @@
       <c r="AW8" t="n">
         <v>54</v>
       </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9112,6 +9236,9 @@
       <c r="AW9" t="n">
         <v>53</v>
       </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9264,6 +9391,9 @@
       </c>
       <c r="AW10" t="n">
         <v>57</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -9277,7 +9407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA10"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9359,6 +9489,7 @@
     <col width="10" customWidth="1" min="77" max="77"/>
     <col width="10" customWidth="1" min="78" max="78"/>
     <col width="10" customWidth="1" min="79" max="79"/>
+    <col width="10" customWidth="1" min="80" max="80"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9603,6 +9734,9 @@
       <c r="CA1" s="1" t="n">
         <v>20260130</v>
       </c>
+      <c r="CB1" s="1" t="n">
+        <v>20260202</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9846,6 +9980,9 @@
       <c r="CA2" t="n">
         <v>-18</v>
       </c>
+      <c r="CB2" t="n">
+        <v>-16</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10089,6 +10226,9 @@
       <c r="CA3" t="n">
         <v>26</v>
       </c>
+      <c r="CB3" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10332,6 +10472,9 @@
       <c r="CA4" t="n">
         <v>68</v>
       </c>
+      <c r="CB4" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10575,6 +10718,9 @@
       <c r="CA5" t="n">
         <v>-128</v>
       </c>
+      <c r="CB5" t="n">
+        <v>-112</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10818,6 +10964,9 @@
       <c r="CA6" t="n">
         <v>-83</v>
       </c>
+      <c r="CB6" t="n">
+        <v>-77</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11061,6 +11210,9 @@
       <c r="CA7" t="n">
         <v>53</v>
       </c>
+      <c r="CB7" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11304,6 +11456,9 @@
       <c r="CA8" t="n">
         <v>-123</v>
       </c>
+      <c r="CB8" t="n">
+        <v>-108</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11547,6 +11702,9 @@
       <c r="CA9" t="n">
         <v>24</v>
       </c>
+      <c r="CB9" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11789,6 +11947,9 @@
       </c>
       <c r="CA10" t="n">
         <v>-45</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>-42</v>
       </c>
     </row>
   </sheetData>
@@ -11802,7 +11963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DD10"/>
+  <dimension ref="A1:DE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11913,6 +12074,7 @@
     <col width="12" customWidth="1" min="106" max="106"/>
     <col width="12" customWidth="1" min="107" max="107"/>
     <col width="12" customWidth="1" min="108" max="108"/>
+    <col width="12" customWidth="1" min="109" max="109"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12244,6 +12406,9 @@
       <c r="DD1" s="1" t="n">
         <v>20260130</v>
       </c>
+      <c r="DE1" s="1" t="n">
+        <v>20260202</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12574,6 +12739,9 @@
       <c r="DD2" t="n">
         <v>255.165</v>
       </c>
+      <c r="DE2" t="n">
+        <v>259.48</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12904,6 +13072,9 @@
       <c r="DD3" t="n">
         <v>239.89</v>
       </c>
+      <c r="DE3" t="n">
+        <v>239.3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13234,6 +13405,9 @@
       <c r="DD4" t="n">
         <v>340</v>
       </c>
+      <c r="DE4" t="n">
+        <v>338</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13564,6 +13738,9 @@
       <c r="DD5" t="n">
         <v>439.17</v>
       </c>
+      <c r="DE5" t="n">
+        <v>430.29</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13894,6 +14071,9 @@
       <c r="DD6" t="n">
         <v>83.09999999999999</v>
       </c>
+      <c r="DE6" t="n">
+        <v>83.48999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14224,6 +14404,9 @@
       <c r="DD7" t="n">
         <v>191.21</v>
       </c>
+      <c r="DE7" t="n">
+        <v>191.13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14554,6 +14737,9 @@
       <c r="DD8" t="n">
         <v>150.05</v>
       </c>
+      <c r="DE8" t="n">
+        <v>146.59</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14884,6 +15070,9 @@
       <c r="DD9" t="n">
         <v>92.72</v>
       </c>
+      <c r="DE9" t="n">
+        <v>91.95</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15213,6 +15402,9 @@
       </c>
       <c r="DD10" t="n">
         <v>425.35</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>430.41</v>
       </c>
     </row>
   </sheetData>
@@ -15226,7 +15418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DD10"/>
+  <dimension ref="A1:DE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15337,6 +15529,7 @@
     <col width="12" customWidth="1" min="106" max="106"/>
     <col width="12" customWidth="1" min="107" max="107"/>
     <col width="12" customWidth="1" min="108" max="108"/>
+    <col width="12" customWidth="1" min="109" max="109"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15668,6 +15861,9 @@
       <c r="DD1" s="1" t="n">
         <v>20260130</v>
       </c>
+      <c r="DE1" s="1" t="n">
+        <v>20260202</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15998,6 +16194,9 @@
       <c r="DD2" t="n">
         <v>261.8999</v>
       </c>
+      <c r="DE2" t="n">
+        <v>259.48</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16328,6 +16527,9 @@
       <c r="DD3" t="n">
         <v>243.315</v>
       </c>
+      <c r="DE3" t="n">
+        <v>239.3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16658,6 +16860,9 @@
       <c r="DD4" t="n">
         <v>340</v>
       </c>
+      <c r="DE4" t="n">
+        <v>338</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16988,6 +17193,9 @@
       <c r="DD5" t="n">
         <v>439.6</v>
       </c>
+      <c r="DE5" t="n">
+        <v>430.29</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17318,6 +17526,9 @@
       <c r="DD6" t="n">
         <v>84.05500000000001</v>
       </c>
+      <c r="DE6" t="n">
+        <v>83.48999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17648,6 +17859,9 @@
       <c r="DD7" t="n">
         <v>194.49</v>
       </c>
+      <c r="DE7" t="n">
+        <v>191.13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17978,6 +18192,9 @@
       <c r="DD8" t="n">
         <v>151</v>
       </c>
+      <c r="DE8" t="n">
+        <v>146.59</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18308,6 +18525,9 @@
       <c r="DD9" t="n">
         <v>93.20999999999999</v>
       </c>
+      <c r="DE9" t="n">
+        <v>91.95</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18637,6 +18857,9 @@
       </c>
       <c r="DD10" t="n">
         <v>439.88</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>430.41</v>
       </c>
     </row>
   </sheetData>
@@ -18650,7 +18873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DD10"/>
+  <dimension ref="A1:DE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18761,6 +18984,7 @@
     <col width="12" customWidth="1" min="106" max="106"/>
     <col width="12" customWidth="1" min="107" max="107"/>
     <col width="12" customWidth="1" min="108" max="108"/>
+    <col width="12" customWidth="1" min="109" max="109"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19092,6 +19316,9 @@
       <c r="DD1" s="1" t="n">
         <v>20260130</v>
       </c>
+      <c r="DE1" s="1" t="n">
+        <v>20260202</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19422,6 +19649,9 @@
       <c r="DD2" t="n">
         <v>252.18</v>
       </c>
+      <c r="DE2" t="n">
+        <v>259.48</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19752,6 +19982,9 @@
       <c r="DD3" t="n">
         <v>237.64</v>
       </c>
+      <c r="DE3" t="n">
+        <v>239.3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20082,6 +20315,9 @@
       <c r="DD4" t="n">
         <v>332.285</v>
       </c>
+      <c r="DE4" t="n">
+        <v>338</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20412,6 +20648,9 @@
       <c r="DD5" t="n">
         <v>426.45</v>
       </c>
+      <c r="DE5" t="n">
+        <v>430.29</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20742,6 +20981,9 @@
       <c r="DD6" t="n">
         <v>82.78</v>
       </c>
+      <c r="DE6" t="n">
+        <v>83.48999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21072,6 +21314,9 @@
       <c r="DD7" t="n">
         <v>189.47</v>
       </c>
+      <c r="DE7" t="n">
+        <v>191.13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21402,6 +21647,9 @@
       <c r="DD8" t="n">
         <v>145.139</v>
       </c>
+      <c r="DE8" t="n">
+        <v>146.59</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21732,6 +21980,9 @@
       <c r="DD9" t="n">
         <v>91</v>
       </c>
+      <c r="DE9" t="n">
+        <v>91.95</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22061,6 +22312,9 @@
       </c>
       <c r="DD10" t="n">
         <v>422.7</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>430.41</v>
       </c>
     </row>
   </sheetData>
@@ -22074,7 +22328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DD10"/>
+  <dimension ref="A1:DE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22185,6 +22439,7 @@
     <col width="12" customWidth="1" min="106" max="106"/>
     <col width="12" customWidth="1" min="107" max="107"/>
     <col width="12" customWidth="1" min="108" max="108"/>
+    <col width="12" customWidth="1" min="109" max="109"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22516,6 +22771,9 @@
       <c r="DD1" s="1" t="n">
         <v>20260130</v>
       </c>
+      <c r="DE1" s="1" t="n">
+        <v>20260202</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22846,6 +23104,9 @@
       <c r="DD2" t="n">
         <v>259.48</v>
       </c>
+      <c r="DE2" t="n">
+        <v>259.48</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23176,6 +23437,9 @@
       <c r="DD3" t="n">
         <v>239.3</v>
       </c>
+      <c r="DE3" t="n">
+        <v>239.3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23506,6 +23770,9 @@
       <c r="DD4" t="n">
         <v>338</v>
       </c>
+      <c r="DE4" t="n">
+        <v>338</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23836,6 +24103,9 @@
       <c r="DD5" t="n">
         <v>430.29</v>
       </c>
+      <c r="DE5" t="n">
+        <v>430.29</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24166,6 +24436,9 @@
       <c r="DD6" t="n">
         <v>83.48999999999999</v>
       </c>
+      <c r="DE6" t="n">
+        <v>83.48999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24496,6 +24769,9 @@
       <c r="DD7" t="n">
         <v>191.13</v>
       </c>
+      <c r="DE7" t="n">
+        <v>191.13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24826,6 +25102,9 @@
       <c r="DD8" t="n">
         <v>146.59</v>
       </c>
+      <c r="DE8" t="n">
+        <v>146.59</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25156,6 +25435,9 @@
       <c r="DD9" t="n">
         <v>91.95</v>
       </c>
+      <c r="DE9" t="n">
+        <v>91.95</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25484,6 +25766,9 @@
         <v>416.56</v>
       </c>
       <c r="DD10" t="n">
+        <v>430.41</v>
+      </c>
+      <c r="DE10" t="n">
         <v>430.41</v>
       </c>
     </row>
@@ -25498,7 +25783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DD10"/>
+  <dimension ref="A1:DE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25609,6 +25894,7 @@
     <col width="12" customWidth="1" min="106" max="106"/>
     <col width="12" customWidth="1" min="107" max="107"/>
     <col width="12" customWidth="1" min="108" max="108"/>
+    <col width="12" customWidth="1" min="109" max="109"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25940,6 +26226,9 @@
       <c r="DD1" s="1" t="n">
         <v>20260130</v>
       </c>
+      <c r="DE1" s="1" t="n">
+        <v>20260202</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -26270,6 +26559,9 @@
       <c r="DD2" t="n">
         <v>92443408</v>
       </c>
+      <c r="DE2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -26600,6 +26892,9 @@
       <c r="DD3" t="n">
         <v>46585024</v>
       </c>
+      <c r="DE3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -26930,6 +27225,9 @@
       <c r="DD4" t="n">
         <v>31023954</v>
       </c>
+      <c r="DE4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -27260,6 +27558,9 @@
       <c r="DD5" t="n">
         <v>58566819</v>
       </c>
+      <c r="DE5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -27590,6 +27891,9 @@
       <c r="DD6" t="n">
         <v>45755030</v>
       </c>
+      <c r="DE6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -27920,6 +28224,9 @@
       <c r="DD7" t="n">
         <v>179489463</v>
       </c>
+      <c r="DE7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -28250,6 +28557,9 @@
       <c r="DD8" t="n">
         <v>47271042</v>
       </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -28580,6 +28890,9 @@
       <c r="DD9" t="n">
         <v>10747970</v>
       </c>
+      <c r="DE9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28909,6 +29222,9 @@
       </c>
       <c r="DD10" t="n">
         <v>82626066</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -28922,7 +29238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CK10"/>
+  <dimension ref="A1:CL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -29014,6 +29330,7 @@
     <col width="10" customWidth="1" min="87" max="87"/>
     <col width="10" customWidth="1" min="88" max="88"/>
     <col width="10" customWidth="1" min="89" max="89"/>
+    <col width="10" customWidth="1" min="90" max="90"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29288,6 +29605,9 @@
       <c r="CK1" s="1" t="n">
         <v>20260130</v>
       </c>
+      <c r="CL1" s="1" t="n">
+        <v>20260202</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -29561,6 +29881,9 @@
       <c r="CK2" t="n">
         <v>53</v>
       </c>
+      <c r="CL2" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -29834,6 +30157,9 @@
       <c r="CK3" t="n">
         <v>61</v>
       </c>
+      <c r="CL3" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -30107,6 +30433,9 @@
       <c r="CK4" t="n">
         <v>99</v>
       </c>
+      <c r="CL4" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -30380,6 +30709,9 @@
       <c r="CK5" t="n">
         <v>0</v>
       </c>
+      <c r="CL5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -30653,6 +30985,9 @@
       <c r="CK6" t="n">
         <v>4</v>
       </c>
+      <c r="CL6" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -30926,6 +31261,9 @@
       <c r="CK7" t="n">
         <v>90</v>
       </c>
+      <c r="CL7" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -31199,6 +31537,9 @@
       <c r="CK8" t="n">
         <v>0</v>
       </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -31472,6 +31813,9 @@
       <c r="CK9" t="n">
         <v>58</v>
       </c>
+      <c r="CL9" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -31743,6 +32087,9 @@
         <v>0</v>
       </c>
       <c r="CK10" t="n">
+        <v>42</v>
+      </c>
+      <c r="CL10" t="n">
         <v>42</v>
       </c>
     </row>
@@ -31757,7 +32104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW10"/>
+  <dimension ref="A1:AX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -31809,6 +32156,7 @@
     <col width="10" customWidth="1" min="47" max="47"/>
     <col width="10" customWidth="1" min="48" max="48"/>
     <col width="10" customWidth="1" min="49" max="49"/>
+    <col width="10" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31963,6 +32311,9 @@
       <c r="AW1" s="1" t="n">
         <v>20260130</v>
       </c>
+      <c r="AX1" s="1" t="n">
+        <v>20260202</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -32116,6 +32467,9 @@
       <c r="AW2" t="n">
         <v>32</v>
       </c>
+      <c r="AX2" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -32269,6 +32623,9 @@
       <c r="AW3" t="n">
         <v>67</v>
       </c>
+      <c r="AX3" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -32422,6 +32779,9 @@
       <c r="AW4" t="n">
         <v>100</v>
       </c>
+      <c r="AX4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -32575,6 +32935,9 @@
       <c r="AW5" t="n">
         <v>0</v>
       </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -32728,6 +33091,9 @@
       <c r="AW6" t="n">
         <v>0</v>
       </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -32881,6 +33247,9 @@
       <c r="AW7" t="n">
         <v>72</v>
       </c>
+      <c r="AX7" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -33034,6 +33403,9 @@
       <c r="AW8" t="n">
         <v>0</v>
       </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -33187,6 +33559,9 @@
       <c r="AW9" t="n">
         <v>69</v>
       </c>
+      <c r="AX9" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -33338,6 +33713,9 @@
         <v>26</v>
       </c>
       <c r="AW10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX10" t="n">
         <v>40</v>
       </c>
     </row>
@@ -33352,7 +33730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CK10"/>
+  <dimension ref="A1:CL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -33444,6 +33822,7 @@
     <col width="10" customWidth="1" min="87" max="87"/>
     <col width="10" customWidth="1" min="88" max="88"/>
     <col width="10" customWidth="1" min="89" max="89"/>
+    <col width="10" customWidth="1" min="90" max="90"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33718,6 +34097,9 @@
       <c r="CK1" s="1" t="n">
         <v>20260130</v>
       </c>
+      <c r="CL1" s="1" t="n">
+        <v>20260202</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -33991,6 +34373,9 @@
       <c r="CK2" t="n">
         <v>13</v>
       </c>
+      <c r="CL2" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -34264,6 +34649,9 @@
       <c r="CK3" t="n">
         <v>4</v>
       </c>
+      <c r="CL3" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -34537,6 +34925,9 @@
       <c r="CK4" t="n">
         <v>61</v>
       </c>
+      <c r="CL4" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -34810,6 +35201,9 @@
       <c r="CK5" t="n">
         <v>-109</v>
       </c>
+      <c r="CL5" t="n">
+        <v>-93</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -35083,6 +35477,9 @@
       <c r="CK6" t="n">
         <v>-75</v>
       </c>
+      <c r="CL6" t="n">
+        <v>-68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -35356,6 +35753,9 @@
       <c r="CK7" t="n">
         <v>61</v>
       </c>
+      <c r="CL7" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -35629,6 +36029,9 @@
       <c r="CK8" t="n">
         <v>-122</v>
       </c>
+      <c r="CL8" t="n">
+        <v>-102</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -35902,6 +36305,9 @@
       <c r="CK9" t="n">
         <v>2</v>
       </c>
+      <c r="CL9" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -36174,6 +36580,9 @@
       </c>
       <c r="CK10" t="n">
         <v>-34</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>-32</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -602,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX10"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -655,6 +655,7 @@
     <col width="10" customWidth="1" min="48" max="48"/>
     <col width="10" customWidth="1" min="49" max="49"/>
     <col width="10" customWidth="1" min="50" max="50"/>
+    <col width="10" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -812,6 +813,9 @@
       <c r="AX1" s="1" t="n">
         <v>20260202</v>
       </c>
+      <c r="AY1" s="1" t="n">
+        <v>20260203</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -968,6 +972,9 @@
       <c r="AX2" t="n">
         <v>-48</v>
       </c>
+      <c r="AY2" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1124,6 +1131,9 @@
       <c r="AX3" t="n">
         <v>32</v>
       </c>
+      <c r="AY3" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1280,6 +1290,9 @@
       <c r="AX4" t="n">
         <v>72</v>
       </c>
+      <c r="AY4" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1436,6 +1449,9 @@
       <c r="AX5" t="n">
         <v>-137</v>
       </c>
+      <c r="AY5" t="n">
+        <v>-170</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1592,6 +1608,9 @@
       <c r="AX6" t="n">
         <v>-21</v>
       </c>
+      <c r="AY6" t="n">
+        <v>-20</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1748,6 +1767,9 @@
       <c r="AX7" t="n">
         <v>55</v>
       </c>
+      <c r="AY7" t="n">
+        <v>-42</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1904,6 +1926,9 @@
       <c r="AX8" t="n">
         <v>-123</v>
       </c>
+      <c r="AY8" t="n">
+        <v>-72</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2060,6 +2085,9 @@
       <c r="AX9" t="n">
         <v>54</v>
       </c>
+      <c r="AY9" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2215,6 +2243,9 @@
       </c>
       <c r="AX10" t="n">
         <v>-23</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>-40</v>
       </c>
     </row>
   </sheetData>
@@ -2228,7 +2259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CL10"/>
+  <dimension ref="A1:CM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2321,6 +2352,7 @@
     <col width="12" customWidth="1" min="88" max="88"/>
     <col width="12" customWidth="1" min="89" max="89"/>
     <col width="12" customWidth="1" min="90" max="90"/>
+    <col width="12" customWidth="1" min="91" max="91"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2774,6 +2806,11 @@
           <t>20260202</t>
         </is>
       </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>20260203</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3050,6 +3087,9 @@
       <c r="CL2" t="n">
         <v>101</v>
       </c>
+      <c r="CM2" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3326,6 +3366,9 @@
       <c r="CL3" t="n">
         <v>100</v>
       </c>
+      <c r="CM3" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3602,6 +3645,9 @@
       <c r="CL4" t="n">
         <v>102</v>
       </c>
+      <c r="CM4" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3878,6 +3924,9 @@
       <c r="CL5" t="n">
         <v>93</v>
       </c>
+      <c r="CM5" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4154,6 +4203,9 @@
       <c r="CL6" t="n">
         <v>96</v>
       </c>
+      <c r="CM6" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4430,6 +4482,9 @@
       <c r="CL7" t="n">
         <v>102</v>
       </c>
+      <c r="CM7" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4706,6 +4761,9 @@
       <c r="CL8" t="n">
         <v>87</v>
       </c>
+      <c r="CM8" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4982,6 +5040,9 @@
       <c r="CL9" t="n">
         <v>100</v>
       </c>
+      <c r="CM9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5257,6 +5318,9 @@
       </c>
       <c r="CL10" t="n">
         <v>99</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -5270,7 +5334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS10"/>
+  <dimension ref="A1:BT10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5344,6 +5408,7 @@
     <col width="12" customWidth="1" min="69" max="69"/>
     <col width="12" customWidth="1" min="70" max="70"/>
     <col width="12" customWidth="1" min="71" max="71"/>
+    <col width="12" customWidth="1" min="72" max="72"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5702,6 +5767,11 @@
           <t>20260202</t>
         </is>
       </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>20260203</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5921,6 +5991,9 @@
       <c r="BS2" t="n">
         <v>-13.01</v>
       </c>
+      <c r="BT2" t="n">
+        <v>-16.84</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6140,6 +6213,9 @@
       <c r="BS3" t="n">
         <v>-17.29</v>
       </c>
+      <c r="BT3" t="n">
+        <v>-30.35</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6359,6 +6435,9 @@
       <c r="BS4" t="n">
         <v>-13.26</v>
       </c>
+      <c r="BT4" t="n">
+        <v>-19.67</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6578,6 +6657,9 @@
       <c r="BS5" t="n">
         <v>74.08</v>
       </c>
+      <c r="BT5" t="n">
+        <v>91.93000000000001</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6797,6 +6879,9 @@
       <c r="BS6" t="n">
         <v>17.72</v>
       </c>
+      <c r="BT6" t="n">
+        <v>27.14</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7016,6 +7101,9 @@
       <c r="BS7" t="n">
         <v>-18.94</v>
       </c>
+      <c r="BT7" t="n">
+        <v>-13.87</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7235,6 +7323,9 @@
       <c r="BS8" t="n">
         <v>43.09</v>
       </c>
+      <c r="BT8" t="n">
+        <v>41.85</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7454,6 +7545,9 @@
       <c r="BS9" t="n">
         <v>14.14</v>
       </c>
+      <c r="BT9" t="n">
+        <v>-5.58</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7672,6 +7766,9 @@
       </c>
       <c r="BS10" t="n">
         <v>-43.8</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>-40.51</v>
       </c>
     </row>
   </sheetData>
@@ -7685,7 +7782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX10"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7738,6 +7835,7 @@
     <col width="12" customWidth="1" min="48" max="48"/>
     <col width="12" customWidth="1" min="49" max="49"/>
     <col width="12" customWidth="1" min="50" max="50"/>
+    <col width="12" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7991,6 +8089,11 @@
           <t>20260202</t>
         </is>
       </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>20260203</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8147,6 +8250,9 @@
       <c r="AX2" t="n">
         <v>0</v>
       </c>
+      <c r="AY2" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8303,6 +8409,9 @@
       <c r="AX3" t="n">
         <v>0</v>
       </c>
+      <c r="AY3" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8459,6 +8568,9 @@
       <c r="AX4" t="n">
         <v>0</v>
       </c>
+      <c r="AY4" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8615,6 +8727,9 @@
       <c r="AX5" t="n">
         <v>0</v>
       </c>
+      <c r="AY5" t="n">
+        <v>113</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8771,6 +8886,9 @@
       <c r="AX6" t="n">
         <v>0</v>
       </c>
+      <c r="AY6" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8927,6 +9045,9 @@
       <c r="AX7" t="n">
         <v>0</v>
       </c>
+      <c r="AY7" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9083,6 +9204,9 @@
       <c r="AX8" t="n">
         <v>0</v>
       </c>
+      <c r="AY8" t="n">
+        <v>134</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9239,6 +9363,9 @@
       <c r="AX9" t="n">
         <v>0</v>
       </c>
+      <c r="AY9" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9394,6 +9521,9 @@
       </c>
       <c r="AX10" t="n">
         <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -9407,7 +9537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9490,6 +9620,7 @@
     <col width="10" customWidth="1" min="78" max="78"/>
     <col width="10" customWidth="1" min="79" max="79"/>
     <col width="10" customWidth="1" min="80" max="80"/>
+    <col width="10" customWidth="1" min="81" max="81"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9737,6 +9868,9 @@
       <c r="CB1" s="1" t="n">
         <v>20260202</v>
       </c>
+      <c r="CC1" s="1" t="n">
+        <v>20260203</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9983,6 +10117,9 @@
       <c r="CB2" t="n">
         <v>-16</v>
       </c>
+      <c r="CC2" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10229,6 +10366,9 @@
       <c r="CB3" t="n">
         <v>23</v>
       </c>
+      <c r="CC3" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10475,6 +10615,9 @@
       <c r="CB4" t="n">
         <v>66</v>
       </c>
+      <c r="CC4" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10721,6 +10864,9 @@
       <c r="CB5" t="n">
         <v>-112</v>
       </c>
+      <c r="CC5" t="n">
+        <v>-137</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10967,6 +11113,9 @@
       <c r="CB6" t="n">
         <v>-77</v>
       </c>
+      <c r="CC6" t="n">
+        <v>-110</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11213,6 +11362,9 @@
       <c r="CB7" t="n">
         <v>56</v>
       </c>
+      <c r="CC7" t="n">
+        <v>-92</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11459,6 +11611,9 @@
       <c r="CB8" t="n">
         <v>-108</v>
       </c>
+      <c r="CC8" t="n">
+        <v>-60</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11705,6 +11860,9 @@
       <c r="CB9" t="n">
         <v>22</v>
       </c>
+      <c r="CC9" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11950,6 +12108,9 @@
       </c>
       <c r="CB10" t="n">
         <v>-42</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>-59</v>
       </c>
     </row>
   </sheetData>
@@ -11963,7 +12124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DE10"/>
+  <dimension ref="A1:DF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12075,6 +12236,7 @@
     <col width="12" customWidth="1" min="107" max="107"/>
     <col width="12" customWidth="1" min="108" max="108"/>
     <col width="12" customWidth="1" min="109" max="109"/>
+    <col width="12" customWidth="1" min="110" max="110"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12409,6 +12571,9 @@
       <c r="DE1" s="1" t="n">
         <v>20260202</v>
       </c>
+      <c r="DF1" s="1" t="n">
+        <v>20260203</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12742,6 +12907,9 @@
       <c r="DE2" t="n">
         <v>259.48</v>
       </c>
+      <c r="DF2" t="n">
+        <v>269.2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13075,6 +13243,9 @@
       <c r="DE3" t="n">
         <v>239.3</v>
       </c>
+      <c r="DF3" t="n">
+        <v>244.975</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13408,6 +13579,9 @@
       <c r="DE4" t="n">
         <v>338</v>
       </c>
+      <c r="DF4" t="n">
+        <v>347.34</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13741,6 +13915,9 @@
       <c r="DE5" t="n">
         <v>430.29</v>
       </c>
+      <c r="DF5" t="n">
+        <v>422.01</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14074,6 +14251,9 @@
       <c r="DE6" t="n">
         <v>83.48999999999999</v>
       </c>
+      <c r="DF6" t="n">
+        <v>82.23</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14407,6 +14587,9 @@
       <c r="DE7" t="n">
         <v>191.13</v>
       </c>
+      <c r="DF7" t="n">
+        <v>186.24</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14740,6 +14923,9 @@
       <c r="DE8" t="n">
         <v>146.59</v>
       </c>
+      <c r="DF8" t="n">
+        <v>165.05</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15073,6 +15259,9 @@
       <c r="DE9" t="n">
         <v>91.95</v>
       </c>
+      <c r="DF9" t="n">
+        <v>91.62</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15405,6 +15594,9 @@
       </c>
       <c r="DE10" t="n">
         <v>430.41</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>424.27</v>
       </c>
     </row>
   </sheetData>
@@ -15418,7 +15610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DE10"/>
+  <dimension ref="A1:DF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15530,6 +15722,7 @@
     <col width="12" customWidth="1" min="107" max="107"/>
     <col width="12" customWidth="1" min="108" max="108"/>
     <col width="12" customWidth="1" min="109" max="109"/>
+    <col width="12" customWidth="1" min="110" max="110"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15864,6 +16057,9 @@
       <c r="DE1" s="1" t="n">
         <v>20260202</v>
       </c>
+      <c r="DF1" s="1" t="n">
+        <v>20260203</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16197,6 +16393,9 @@
       <c r="DE2" t="n">
         <v>259.48</v>
       </c>
+      <c r="DF2" t="n">
+        <v>271.875</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16530,6 +16729,9 @@
       <c r="DE3" t="n">
         <v>239.3</v>
       </c>
+      <c r="DF3" t="n">
+        <v>246.35</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16863,6 +17065,9 @@
       <c r="DE4" t="n">
         <v>338</v>
       </c>
+      <c r="DF4" t="n">
+        <v>349</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -17196,6 +17401,9 @@
       <c r="DE5" t="n">
         <v>430.29</v>
       </c>
+      <c r="DF5" t="n">
+        <v>422.05</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17529,6 +17737,9 @@
       <c r="DE6" t="n">
         <v>83.48999999999999</v>
       </c>
+      <c r="DF6" t="n">
+        <v>82.45</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17862,6 +18073,9 @@
       <c r="DE7" t="n">
         <v>191.13</v>
       </c>
+      <c r="DF7" t="n">
+        <v>186.27</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18195,6 +18409,9 @@
       <c r="DE8" t="n">
         <v>146.59</v>
       </c>
+      <c r="DF8" t="n">
+        <v>165.078</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18528,6 +18745,9 @@
       <c r="DE9" t="n">
         <v>91.95</v>
       </c>
+      <c r="DF9" t="n">
+        <v>94.40000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18860,6 +19080,9 @@
       </c>
       <c r="DE10" t="n">
         <v>430.41</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>428.56</v>
       </c>
     </row>
   </sheetData>
@@ -18873,7 +19096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DE10"/>
+  <dimension ref="A1:DF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18985,6 +19208,7 @@
     <col width="12" customWidth="1" min="107" max="107"/>
     <col width="12" customWidth="1" min="108" max="108"/>
     <col width="12" customWidth="1" min="109" max="109"/>
+    <col width="12" customWidth="1" min="110" max="110"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19319,6 +19543,9 @@
       <c r="DE1" s="1" t="n">
         <v>20260202</v>
       </c>
+      <c r="DF1" s="1" t="n">
+        <v>20260203</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19652,6 +19879,9 @@
       <c r="DE2" t="n">
         <v>259.48</v>
       </c>
+      <c r="DF2" t="n">
+        <v>267.61</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19985,6 +20215,9 @@
       <c r="DE3" t="n">
         <v>239.3</v>
       </c>
+      <c r="DF3" t="n">
+        <v>235.45</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20318,6 +20551,9 @@
       <c r="DE4" t="n">
         <v>338</v>
       </c>
+      <c r="DF4" t="n">
+        <v>337.4745</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20651,6 +20887,9 @@
       <c r="DE5" t="n">
         <v>430.29</v>
       </c>
+      <c r="DF5" t="n">
+        <v>408.56</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20984,6 +21223,9 @@
       <c r="DE6" t="n">
         <v>83.48999999999999</v>
       </c>
+      <c r="DF6" t="n">
+        <v>79.62</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21317,6 +21559,9 @@
       <c r="DE7" t="n">
         <v>191.13</v>
       </c>
+      <c r="DF7" t="n">
+        <v>176.23</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21650,6 +21895,9 @@
       <c r="DE8" t="n">
         <v>146.59</v>
       </c>
+      <c r="DF8" t="n">
+        <v>153.12</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21983,6 +22231,9 @@
       <c r="DE9" t="n">
         <v>91.95</v>
       </c>
+      <c r="DF9" t="n">
+        <v>91.29000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22315,6 +22566,9 @@
       </c>
       <c r="DE10" t="n">
         <v>430.41</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>413.6901</v>
       </c>
     </row>
   </sheetData>
@@ -22328,7 +22582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DE10"/>
+  <dimension ref="A1:DF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22440,6 +22694,7 @@
     <col width="12" customWidth="1" min="107" max="107"/>
     <col width="12" customWidth="1" min="108" max="108"/>
     <col width="12" customWidth="1" min="109" max="109"/>
+    <col width="12" customWidth="1" min="110" max="110"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22774,6 +23029,9 @@
       <c r="DE1" s="1" t="n">
         <v>20260202</v>
       </c>
+      <c r="DF1" s="1" t="n">
+        <v>20260203</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23107,6 +23365,9 @@
       <c r="DE2" t="n">
         <v>259.48</v>
       </c>
+      <c r="DF2" t="n">
+        <v>269.48</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23440,6 +23701,9 @@
       <c r="DE3" t="n">
         <v>239.3</v>
       </c>
+      <c r="DF3" t="n">
+        <v>238.62</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23773,6 +24037,9 @@
       <c r="DE4" t="n">
         <v>338</v>
       </c>
+      <c r="DF4" t="n">
+        <v>339.71</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24106,6 +24373,9 @@
       <c r="DE5" t="n">
         <v>430.29</v>
       </c>
+      <c r="DF5" t="n">
+        <v>411.21</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24439,6 +24709,9 @@
       <c r="DE6" t="n">
         <v>83.48999999999999</v>
       </c>
+      <c r="DF6" t="n">
+        <v>79.94</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24772,6 +25045,9 @@
       <c r="DE7" t="n">
         <v>191.13</v>
       </c>
+      <c r="DF7" t="n">
+        <v>180.34</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25105,6 +25381,9 @@
       <c r="DE8" t="n">
         <v>146.59</v>
       </c>
+      <c r="DF8" t="n">
+        <v>157.88</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25438,6 +25717,9 @@
       <c r="DE9" t="n">
         <v>91.95</v>
       </c>
+      <c r="DF9" t="n">
+        <v>93.04000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25770,6 +26052,9 @@
       </c>
       <c r="DE10" t="n">
         <v>430.41</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>421.96</v>
       </c>
     </row>
   </sheetData>
@@ -25783,7 +26068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DE10"/>
+  <dimension ref="A1:DF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25895,6 +26180,7 @@
     <col width="12" customWidth="1" min="107" max="107"/>
     <col width="12" customWidth="1" min="108" max="108"/>
     <col width="12" customWidth="1" min="109" max="109"/>
+    <col width="12" customWidth="1" min="110" max="110"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26229,6 +26515,9 @@
       <c r="DE1" s="1" t="n">
         <v>20260202</v>
       </c>
+      <c r="DF1" s="1" t="n">
+        <v>20260203</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -26562,6 +26851,9 @@
       <c r="DE2" t="n">
         <v>0</v>
       </c>
+      <c r="DF2" t="n">
+        <v>64394655</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -26895,6 +27187,9 @@
       <c r="DE3" t="n">
         <v>0</v>
       </c>
+      <c r="DF3" t="n">
+        <v>53831298</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -27228,6 +27523,9 @@
       <c r="DE4" t="n">
         <v>0</v>
       </c>
+      <c r="DF4" t="n">
+        <v>36506709</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -27561,6 +27859,9 @@
       <c r="DE5" t="n">
         <v>0</v>
       </c>
+      <c r="DF5" t="n">
+        <v>61424123</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -27894,6 +28195,9 @@
       <c r="DE6" t="n">
         <v>0</v>
       </c>
+      <c r="DF6" t="n">
+        <v>49789042</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -28227,6 +28531,9 @@
       <c r="DE7" t="n">
         <v>0</v>
       </c>
+      <c r="DF7" t="n">
+        <v>204019589</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -28560,6 +28867,9 @@
       <c r="DE8" t="n">
         <v>0</v>
       </c>
+      <c r="DF8" t="n">
+        <v>113169200</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -28893,6 +29203,9 @@
       <c r="DE9" t="n">
         <v>0</v>
       </c>
+      <c r="DF9" t="n">
+        <v>8361300</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -29225,6 +29538,9 @@
       </c>
       <c r="DE10" t="n">
         <v>0</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>56886549</v>
       </c>
     </row>
   </sheetData>
@@ -29238,7 +29554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CL10"/>
+  <dimension ref="A1:CM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -29331,6 +29647,7 @@
     <col width="10" customWidth="1" min="88" max="88"/>
     <col width="10" customWidth="1" min="89" max="89"/>
     <col width="10" customWidth="1" min="90" max="90"/>
+    <col width="10" customWidth="1" min="91" max="91"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29608,6 +29925,9 @@
       <c r="CL1" s="1" t="n">
         <v>20260202</v>
       </c>
+      <c r="CM1" s="1" t="n">
+        <v>20260203</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -29884,6 +30204,9 @@
       <c r="CL2" t="n">
         <v>53</v>
       </c>
+      <c r="CM2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -30160,6 +30483,9 @@
       <c r="CL3" t="n">
         <v>60</v>
       </c>
+      <c r="CM3" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -30436,6 +30762,9 @@
       <c r="CL4" t="n">
         <v>99</v>
       </c>
+      <c r="CM4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -30712,6 +31041,9 @@
       <c r="CL5" t="n">
         <v>0</v>
       </c>
+      <c r="CM5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -30988,6 +31320,9 @@
       <c r="CL6" t="n">
         <v>4</v>
       </c>
+      <c r="CM6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -31264,6 +31599,9 @@
       <c r="CL7" t="n">
         <v>90</v>
       </c>
+      <c r="CM7" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -31540,6 +31878,9 @@
       <c r="CL8" t="n">
         <v>0</v>
       </c>
+      <c r="CM8" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -31816,6 +32157,9 @@
       <c r="CL9" t="n">
         <v>58</v>
       </c>
+      <c r="CM9" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -32091,6 +32435,9 @@
       </c>
       <c r="CL10" t="n">
         <v>42</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -32104,7 +32451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX10"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -32157,6 +32504,7 @@
     <col width="10" customWidth="1" min="48" max="48"/>
     <col width="10" customWidth="1" min="49" max="49"/>
     <col width="10" customWidth="1" min="50" max="50"/>
+    <col width="10" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32314,6 +32662,9 @@
       <c r="AX1" s="1" t="n">
         <v>20260202</v>
       </c>
+      <c r="AY1" s="1" t="n">
+        <v>20260203</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -32470,6 +32821,9 @@
       <c r="AX2" t="n">
         <v>32</v>
       </c>
+      <c r="AY2" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -32626,6 +32980,9 @@
       <c r="AX3" t="n">
         <v>67</v>
       </c>
+      <c r="AY3" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -32782,6 +33139,9 @@
       <c r="AX4" t="n">
         <v>100</v>
       </c>
+      <c r="AY4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -32938,6 +33298,9 @@
       <c r="AX5" t="n">
         <v>0</v>
       </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -33094,6 +33457,9 @@
       <c r="AX6" t="n">
         <v>0</v>
       </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -33250,6 +33616,9 @@
       <c r="AX7" t="n">
         <v>72</v>
       </c>
+      <c r="AY7" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -33406,6 +33775,9 @@
       <c r="AX8" t="n">
         <v>0</v>
       </c>
+      <c r="AY8" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -33562,6 +33934,9 @@
       <c r="AX9" t="n">
         <v>63</v>
       </c>
+      <c r="AY9" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -33717,6 +34092,9 @@
       </c>
       <c r="AX10" t="n">
         <v>40</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -33730,7 +34108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CL10"/>
+  <dimension ref="A1:CM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -33823,6 +34201,7 @@
     <col width="10" customWidth="1" min="88" max="88"/>
     <col width="10" customWidth="1" min="89" max="89"/>
     <col width="10" customWidth="1" min="90" max="90"/>
+    <col width="10" customWidth="1" min="91" max="91"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -34100,6 +34479,9 @@
       <c r="CL1" s="1" t="n">
         <v>20260202</v>
       </c>
+      <c r="CM1" s="1" t="n">
+        <v>20260203</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -34376,6 +34758,9 @@
       <c r="CL2" t="n">
         <v>19</v>
       </c>
+      <c r="CM2" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -34652,6 +35037,9 @@
       <c r="CL3" t="n">
         <v>-1</v>
       </c>
+      <c r="CM3" t="n">
+        <v>-15</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -34928,6 +35316,9 @@
       <c r="CL4" t="n">
         <v>57</v>
       </c>
+      <c r="CM4" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -35204,6 +35595,9 @@
       <c r="CL5" t="n">
         <v>-93</v>
       </c>
+      <c r="CM5" t="n">
+        <v>-117</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -35480,6 +35874,9 @@
       <c r="CL6" t="n">
         <v>-68</v>
       </c>
+      <c r="CM6" t="n">
+        <v>-110</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -35756,6 +36153,9 @@
       <c r="CL7" t="n">
         <v>58</v>
       </c>
+      <c r="CM7" t="n">
+        <v>-83</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -36032,6 +36432,9 @@
       <c r="CL8" t="n">
         <v>-102</v>
       </c>
+      <c r="CM8" t="n">
+        <v>-46</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -36308,6 +36711,9 @@
       <c r="CL9" t="n">
         <v>-3</v>
       </c>
+      <c r="CM9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -36583,6 +36989,9 @@
       </c>
       <c r="CL10" t="n">
         <v>-32</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>-69</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -602,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:BA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -656,6 +656,8 @@
     <col width="10" customWidth="1" min="49" max="49"/>
     <col width="10" customWidth="1" min="50" max="50"/>
     <col width="10" customWidth="1" min="51" max="51"/>
+    <col width="10" customWidth="1" min="52" max="52"/>
+    <col width="10" customWidth="1" min="53" max="53"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -816,6 +818,12 @@
       <c r="AY1" s="1" t="n">
         <v>20260203</v>
       </c>
+      <c r="AZ1" s="1" t="n">
+        <v>20260204</v>
+      </c>
+      <c r="BA1" s="1" t="n">
+        <v>20260205</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -975,6 +983,12 @@
       <c r="AY2" t="n">
         <v>5</v>
       </c>
+      <c r="AZ2" t="n">
+        <v>41</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1134,6 +1148,12 @@
       <c r="AY3" t="n">
         <v>30</v>
       </c>
+      <c r="AZ3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>-4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1293,6 +1313,12 @@
       <c r="AY4" t="n">
         <v>75</v>
       </c>
+      <c r="AZ4" t="n">
+        <v>54</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1452,6 +1478,12 @@
       <c r="AY5" t="n">
         <v>-170</v>
       </c>
+      <c r="AZ5" t="n">
+        <v>-148</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-136</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1611,6 +1643,12 @@
       <c r="AY6" t="n">
         <v>-20</v>
       </c>
+      <c r="AZ6" t="n">
+        <v>-19</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-17</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1770,6 +1808,12 @@
       <c r="AY7" t="n">
         <v>-42</v>
       </c>
+      <c r="AZ7" t="n">
+        <v>-94</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>-90</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1929,6 +1973,12 @@
       <c r="AY8" t="n">
         <v>-72</v>
       </c>
+      <c r="AZ8" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>-127</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2088,6 +2138,12 @@
       <c r="AY9" t="n">
         <v>65</v>
       </c>
+      <c r="AZ9" t="n">
+        <v>106</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2246,6 +2302,12 @@
       </c>
       <c r="AY10" t="n">
         <v>-40</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>-71</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>-69</v>
       </c>
     </row>
   </sheetData>
@@ -2259,7 +2321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CM10"/>
+  <dimension ref="A1:CO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2353,6 +2415,8 @@
     <col width="12" customWidth="1" min="89" max="89"/>
     <col width="12" customWidth="1" min="90" max="90"/>
     <col width="12" customWidth="1" min="91" max="91"/>
+    <col width="12" customWidth="1" min="92" max="92"/>
+    <col width="12" customWidth="1" min="93" max="93"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2811,6 +2875,16 @@
           <t>20260203</t>
         </is>
       </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>20260204</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>20260205</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3090,6 +3164,12 @@
       <c r="CM2" t="n">
         <v>105</v>
       </c>
+      <c r="CN2" t="n">
+        <v>107</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3369,6 +3449,12 @@
       <c r="CM3" t="n">
         <v>99</v>
       </c>
+      <c r="CN3" t="n">
+        <v>97</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3648,6 +3734,12 @@
       <c r="CM4" t="n">
         <v>103</v>
       </c>
+      <c r="CN4" t="n">
+        <v>100</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3927,6 +4019,12 @@
       <c r="CM5" t="n">
         <v>89</v>
       </c>
+      <c r="CN5" t="n">
+        <v>91</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4206,6 +4304,12 @@
       <c r="CM6" t="n">
         <v>92</v>
       </c>
+      <c r="CN6" t="n">
+        <v>93</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4485,6 +4589,12 @@
       <c r="CM7" t="n">
         <v>97</v>
       </c>
+      <c r="CN7" t="n">
+        <v>94</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4764,6 +4874,12 @@
       <c r="CM8" t="n">
         <v>94</v>
       </c>
+      <c r="CN8" t="n">
+        <v>84</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5043,6 +5159,12 @@
       <c r="CM9" t="n">
         <v>100</v>
       </c>
+      <c r="CN9" t="n">
+        <v>104</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5321,6 +5443,12 @@
       </c>
       <c r="CM10" t="n">
         <v>97</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>94</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -5334,7 +5462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BT10"/>
+  <dimension ref="A1:BV10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5409,6 +5537,8 @@
     <col width="12" customWidth="1" min="70" max="70"/>
     <col width="12" customWidth="1" min="71" max="71"/>
     <col width="12" customWidth="1" min="72" max="72"/>
+    <col width="12" customWidth="1" min="73" max="73"/>
+    <col width="12" customWidth="1" min="74" max="74"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5772,6 +5902,16 @@
           <t>20260203</t>
         </is>
       </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>20260204</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>20260205</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5994,6 +6134,12 @@
       <c r="BT2" t="n">
         <v>-16.84</v>
       </c>
+      <c r="BU2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>14.24</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6216,6 +6362,12 @@
       <c r="BT3" t="n">
         <v>-30.35</v>
       </c>
+      <c r="BU3" t="n">
+        <v>-26.59</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>-23.42</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6438,6 +6590,12 @@
       <c r="BT4" t="n">
         <v>-19.67</v>
       </c>
+      <c r="BU4" t="n">
+        <v>-35.92</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>-42.55</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6660,6 +6818,12 @@
       <c r="BT5" t="n">
         <v>91.93000000000001</v>
       </c>
+      <c r="BU5" t="n">
+        <v>93.95</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>87.59999999999999</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6882,6 +7046,12 @@
       <c r="BT6" t="n">
         <v>27.14</v>
       </c>
+      <c r="BU6" t="n">
+        <v>30.14</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>28.78</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7104,6 +7274,12 @@
       <c r="BT7" t="n">
         <v>-13.87</v>
       </c>
+      <c r="BU7" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>24.69</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7326,6 +7502,12 @@
       <c r="BT8" t="n">
         <v>41.85</v>
       </c>
+      <c r="BU8" t="n">
+        <v>53.72</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>57.24</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7548,6 +7730,12 @@
       <c r="BT9" t="n">
         <v>-5.58</v>
       </c>
+      <c r="BU9" t="n">
+        <v>-5.81</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>-15.07</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7769,6 +7957,12 @@
       </c>
       <c r="BT10" t="n">
         <v>-40.51</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>-26.36</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>-14.7</v>
       </c>
     </row>
   </sheetData>
@@ -7782,7 +7976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:BA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7836,6 +8030,8 @@
     <col width="12" customWidth="1" min="49" max="49"/>
     <col width="12" customWidth="1" min="50" max="50"/>
     <col width="12" customWidth="1" min="51" max="51"/>
+    <col width="12" customWidth="1" min="52" max="52"/>
+    <col width="12" customWidth="1" min="53" max="53"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8094,6 +8290,16 @@
           <t>20260203</t>
         </is>
       </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>20260204</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>20260205</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8253,6 +8459,12 @@
       <c r="AY2" t="n">
         <v>71</v>
       </c>
+      <c r="AZ2" t="n">
+        <v>99</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8412,6 +8624,12 @@
       <c r="AY3" t="n">
         <v>69</v>
       </c>
+      <c r="AZ3" t="n">
+        <v>65</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8571,6 +8789,12 @@
       <c r="AY4" t="n">
         <v>53</v>
       </c>
+      <c r="AZ4" t="n">
+        <v>101</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8730,6 +8954,12 @@
       <c r="AY5" t="n">
         <v>113</v>
       </c>
+      <c r="AZ5" t="n">
+        <v>82</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8889,6 +9119,12 @@
       <c r="AY6" t="n">
         <v>62</v>
       </c>
+      <c r="AZ6" t="n">
+        <v>59</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9048,6 +9284,12 @@
       <c r="AY7" t="n">
         <v>58</v>
       </c>
+      <c r="AZ7" t="n">
+        <v>59</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9207,6 +9449,12 @@
       <c r="AY8" t="n">
         <v>134</v>
       </c>
+      <c r="AZ8" t="n">
+        <v>132</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9366,6 +9614,12 @@
       <c r="AY9" t="n">
         <v>43</v>
       </c>
+      <c r="AZ9" t="n">
+        <v>47</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9524,6 +9778,12 @@
       </c>
       <c r="AY10" t="n">
         <v>40</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>53</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -9537,7 +9797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CC10"/>
+  <dimension ref="A1:CE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9621,6 +9881,8 @@
     <col width="10" customWidth="1" min="79" max="79"/>
     <col width="10" customWidth="1" min="80" max="80"/>
     <col width="10" customWidth="1" min="81" max="81"/>
+    <col width="10" customWidth="1" min="82" max="82"/>
+    <col width="10" customWidth="1" min="83" max="83"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9871,6 +10133,12 @@
       <c r="CC1" s="1" t="n">
         <v>20260203</v>
       </c>
+      <c r="CD1" s="1" t="n">
+        <v>20260204</v>
+      </c>
+      <c r="CE1" s="1" t="n">
+        <v>20260205</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10120,6 +10388,12 @@
       <c r="CC2" t="n">
         <v>42</v>
       </c>
+      <c r="CD2" t="n">
+        <v>80</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10369,6 +10643,12 @@
       <c r="CC3" t="n">
         <v>15</v>
       </c>
+      <c r="CD3" t="n">
+        <v>-33</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>-36</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10618,6 +10898,12 @@
       <c r="CC4" t="n">
         <v>71</v>
       </c>
+      <c r="CD4" t="n">
+        <v>36</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10867,6 +11153,12 @@
       <c r="CC5" t="n">
         <v>-137</v>
       </c>
+      <c r="CD5" t="n">
+        <v>-114</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>-101</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11116,6 +11408,12 @@
       <c r="CC6" t="n">
         <v>-110</v>
       </c>
+      <c r="CD6" t="n">
+        <v>-97</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>-89</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11365,6 +11663,12 @@
       <c r="CC7" t="n">
         <v>-92</v>
       </c>
+      <c r="CD7" t="n">
+        <v>-152</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>-130</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11614,6 +11918,12 @@
       <c r="CC8" t="n">
         <v>-60</v>
       </c>
+      <c r="CD8" t="n">
+        <v>-115</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>-105</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11863,6 +12173,12 @@
       <c r="CC9" t="n">
         <v>33</v>
       </c>
+      <c r="CD9" t="n">
+        <v>71</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12111,6 +12427,12 @@
       </c>
       <c r="CC10" t="n">
         <v>-59</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>-93</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>-89</v>
       </c>
     </row>
   </sheetData>
@@ -12124,7 +12446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DF10"/>
+  <dimension ref="A1:DH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12237,6 +12559,8 @@
     <col width="12" customWidth="1" min="108" max="108"/>
     <col width="12" customWidth="1" min="109" max="109"/>
     <col width="12" customWidth="1" min="110" max="110"/>
+    <col width="12" customWidth="1" min="111" max="111"/>
+    <col width="12" customWidth="1" min="112" max="112"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12574,6 +12898,12 @@
       <c r="DF1" s="1" t="n">
         <v>20260203</v>
       </c>
+      <c r="DG1" s="1" t="n">
+        <v>20260204</v>
+      </c>
+      <c r="DH1" s="1" t="n">
+        <v>20260205</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12910,6 +13240,12 @@
       <c r="DF2" t="n">
         <v>269.2</v>
       </c>
+      <c r="DG2" t="n">
+        <v>272.285</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>276.49</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13246,6 +13582,12 @@
       <c r="DF3" t="n">
         <v>244.975</v>
       </c>
+      <c r="DG3" t="n">
+        <v>238.86</v>
+      </c>
+      <c r="DH3" t="n">
+        <v>232.99</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13582,6 +13924,12 @@
       <c r="DF4" t="n">
         <v>347.34</v>
       </c>
+      <c r="DG4" t="n">
+        <v>342.96</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>333.04</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13918,6 +14266,12 @@
       <c r="DF5" t="n">
         <v>422.01</v>
       </c>
+      <c r="DG5" t="n">
+        <v>411</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>414.19</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14254,6 +14608,12 @@
       <c r="DF6" t="n">
         <v>82.23</v>
       </c>
+      <c r="DG6" t="n">
+        <v>79.98999999999999</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>80.16</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14590,6 +14950,12 @@
       <c r="DF7" t="n">
         <v>186.24</v>
       </c>
+      <c r="DG7" t="n">
+        <v>179.46</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>174.19</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14926,6 +15292,12 @@
       <c r="DF8" t="n">
         <v>165.05</v>
       </c>
+      <c r="DG8" t="n">
+        <v>155.41</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>139.54</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15262,6 +15634,12 @@
       <c r="DF9" t="n">
         <v>91.62</v>
       </c>
+      <c r="DG9" t="n">
+        <v>93.72</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>96.97</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15597,6 +15975,12 @@
       </c>
       <c r="DF10" t="n">
         <v>424.27</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>420.46</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>406.01</v>
       </c>
     </row>
   </sheetData>
@@ -15610,7 +15994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DF10"/>
+  <dimension ref="A1:DH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15723,6 +16107,8 @@
     <col width="12" customWidth="1" min="108" max="108"/>
     <col width="12" customWidth="1" min="109" max="109"/>
     <col width="12" customWidth="1" min="110" max="110"/>
+    <col width="12" customWidth="1" min="111" max="111"/>
+    <col width="12" customWidth="1" min="112" max="112"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16060,6 +16446,12 @@
       <c r="DF1" s="1" t="n">
         <v>20260203</v>
       </c>
+      <c r="DG1" s="1" t="n">
+        <v>20260204</v>
+      </c>
+      <c r="DH1" s="1" t="n">
+        <v>20260205</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16396,6 +16788,12 @@
       <c r="DF2" t="n">
         <v>271.875</v>
       </c>
+      <c r="DG2" t="n">
+        <v>278.95</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>276.49</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16732,6 +17130,12 @@
       <c r="DF3" t="n">
         <v>246.35</v>
       </c>
+      <c r="DG3" t="n">
+        <v>238.86</v>
+      </c>
+      <c r="DH3" t="n">
+        <v>232.99</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17068,6 +17472,12 @@
       <c r="DF4" t="n">
         <v>349</v>
       </c>
+      <c r="DG4" t="n">
+        <v>343.31</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>333.04</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -17404,6 +17814,12 @@
       <c r="DF5" t="n">
         <v>422.05</v>
       </c>
+      <c r="DG5" t="n">
+        <v>419.8</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>414.19</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17740,6 +18156,12 @@
       <c r="DF6" t="n">
         <v>82.45</v>
       </c>
+      <c r="DG6" t="n">
+        <v>81.435</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>80.16</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18076,6 +18498,12 @@
       <c r="DF7" t="n">
         <v>186.27</v>
       </c>
+      <c r="DG7" t="n">
+        <v>179.58</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>174.19</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18412,6 +18840,12 @@
       <c r="DF8" t="n">
         <v>165.078</v>
       </c>
+      <c r="DG8" t="n">
+        <v>155.85</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>139.54</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18748,6 +19182,12 @@
       <c r="DF9" t="n">
         <v>94.40000000000001</v>
       </c>
+      <c r="DG9" t="n">
+        <v>97.11</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>96.97</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -19083,6 +19523,12 @@
       </c>
       <c r="DF10" t="n">
         <v>428.56</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>423.9</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>406.01</v>
       </c>
     </row>
   </sheetData>
@@ -19096,7 +19542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DF10"/>
+  <dimension ref="A1:DH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -19209,6 +19655,8 @@
     <col width="12" customWidth="1" min="108" max="108"/>
     <col width="12" customWidth="1" min="109" max="109"/>
     <col width="12" customWidth="1" min="110" max="110"/>
+    <col width="12" customWidth="1" min="111" max="111"/>
+    <col width="12" customWidth="1" min="112" max="112"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19546,6 +19994,12 @@
       <c r="DF1" s="1" t="n">
         <v>20260203</v>
       </c>
+      <c r="DG1" s="1" t="n">
+        <v>20260204</v>
+      </c>
+      <c r="DH1" s="1" t="n">
+        <v>20260205</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19882,6 +20336,12 @@
       <c r="DF2" t="n">
         <v>267.61</v>
       </c>
+      <c r="DG2" t="n">
+        <v>272.285</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>276.49</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20218,6 +20678,12 @@
       <c r="DF3" t="n">
         <v>235.45</v>
       </c>
+      <c r="DG3" t="n">
+        <v>231.82</v>
+      </c>
+      <c r="DH3" t="n">
+        <v>232.99</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20554,6 +21020,12 @@
       <c r="DF4" t="n">
         <v>337.4745</v>
       </c>
+      <c r="DG4" t="n">
+        <v>328.52</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>333.04</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20890,6 +21362,12 @@
       <c r="DF5" t="n">
         <v>408.56</v>
       </c>
+      <c r="DG5" t="n">
+        <v>409.24</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>414.19</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21226,6 +21704,12 @@
       <c r="DF6" t="n">
         <v>79.62</v>
       </c>
+      <c r="DG6" t="n">
+        <v>79.22499999999999</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>80.16</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21562,6 +22046,12 @@
       <c r="DF7" t="n">
         <v>176.23</v>
       </c>
+      <c r="DG7" t="n">
+        <v>171.91</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>174.19</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21898,6 +22388,12 @@
       <c r="DF8" t="n">
         <v>153.12</v>
       </c>
+      <c r="DG8" t="n">
+        <v>135.68</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>139.54</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22234,6 +22730,12 @@
       <c r="DF9" t="n">
         <v>91.29000000000001</v>
       </c>
+      <c r="DG9" t="n">
+        <v>93.52</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>96.97</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22569,6 +23071,12 @@
       </c>
       <c r="DF10" t="n">
         <v>413.6901</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>399.18</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>406.01</v>
       </c>
     </row>
   </sheetData>
@@ -22582,7 +23090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DF10"/>
+  <dimension ref="A1:DH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22695,6 +23203,8 @@
     <col width="12" customWidth="1" min="108" max="108"/>
     <col width="12" customWidth="1" min="109" max="109"/>
     <col width="12" customWidth="1" min="110" max="110"/>
+    <col width="12" customWidth="1" min="111" max="111"/>
+    <col width="12" customWidth="1" min="112" max="112"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23032,6 +23542,12 @@
       <c r="DF1" s="1" t="n">
         <v>20260203</v>
       </c>
+      <c r="DG1" s="1" t="n">
+        <v>20260204</v>
+      </c>
+      <c r="DH1" s="1" t="n">
+        <v>20260205</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23368,6 +23884,12 @@
       <c r="DF2" t="n">
         <v>269.48</v>
       </c>
+      <c r="DG2" t="n">
+        <v>276.49</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>276.49</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23704,6 +24226,12 @@
       <c r="DF3" t="n">
         <v>238.62</v>
       </c>
+      <c r="DG3" t="n">
+        <v>232.99</v>
+      </c>
+      <c r="DH3" t="n">
+        <v>232.99</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -24040,6 +24568,12 @@
       <c r="DF4" t="n">
         <v>339.71</v>
       </c>
+      <c r="DG4" t="n">
+        <v>333.04</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>333.04</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24376,6 +24910,12 @@
       <c r="DF5" t="n">
         <v>411.21</v>
       </c>
+      <c r="DG5" t="n">
+        <v>414.19</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>414.19</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24712,6 +25252,12 @@
       <c r="DF6" t="n">
         <v>79.94</v>
       </c>
+      <c r="DG6" t="n">
+        <v>80.16</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>80.16</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -25048,6 +25594,12 @@
       <c r="DF7" t="n">
         <v>180.34</v>
       </c>
+      <c r="DG7" t="n">
+        <v>174.19</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>174.19</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25384,6 +25936,12 @@
       <c r="DF8" t="n">
         <v>157.88</v>
       </c>
+      <c r="DG8" t="n">
+        <v>139.54</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>139.54</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25720,6 +26278,12 @@
       <c r="DF9" t="n">
         <v>93.04000000000001</v>
       </c>
+      <c r="DG9" t="n">
+        <v>96.97</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>96.97</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26055,6 +26619,12 @@
       </c>
       <c r="DF10" t="n">
         <v>421.96</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>406.01</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>406.01</v>
       </c>
     </row>
   </sheetData>
@@ -26068,7 +26638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DF10"/>
+  <dimension ref="A1:DH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -26181,6 +26751,8 @@
     <col width="12" customWidth="1" min="108" max="108"/>
     <col width="12" customWidth="1" min="109" max="109"/>
     <col width="12" customWidth="1" min="110" max="110"/>
+    <col width="12" customWidth="1" min="111" max="111"/>
+    <col width="12" customWidth="1" min="112" max="112"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26518,6 +27090,12 @@
       <c r="DF1" s="1" t="n">
         <v>20260203</v>
       </c>
+      <c r="DG1" s="1" t="n">
+        <v>20260204</v>
+      </c>
+      <c r="DH1" s="1" t="n">
+        <v>20260205</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -26854,6 +27432,12 @@
       <c r="DF2" t="n">
         <v>64394655</v>
       </c>
+      <c r="DG2" t="n">
+        <v>90545710</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -27190,6 +27774,12 @@
       <c r="DF3" t="n">
         <v>53831298</v>
       </c>
+      <c r="DG3" t="n">
+        <v>51299947</v>
+      </c>
+      <c r="DH3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -27526,6 +28116,12 @@
       <c r="DF4" t="n">
         <v>36506709</v>
       </c>
+      <c r="DG4" t="n">
+        <v>70618398</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -27862,6 +28458,12 @@
       <c r="DF5" t="n">
         <v>61424123</v>
       </c>
+      <c r="DG5" t="n">
+        <v>45012374</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -28198,6 +28800,12 @@
       <c r="DF6" t="n">
         <v>49789042</v>
       </c>
+      <c r="DG6" t="n">
+        <v>48963242</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -28534,6 +29142,12 @@
       <c r="DF7" t="n">
         <v>204019589</v>
       </c>
+      <c r="DG7" t="n">
+        <v>207014116</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -28870,6 +29484,12 @@
       <c r="DF8" t="n">
         <v>113169200</v>
       </c>
+      <c r="DG8" t="n">
+        <v>113199525</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -29206,6 +29826,12 @@
       <c r="DF9" t="n">
         <v>8361300</v>
       </c>
+      <c r="DG9" t="n">
+        <v>9077080</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -29541,6 +30167,12 @@
       </c>
       <c r="DF10" t="n">
         <v>56886549</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>74606873</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -29554,7 +30186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CM10"/>
+  <dimension ref="A1:CO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -29648,6 +30280,8 @@
     <col width="10" customWidth="1" min="89" max="89"/>
     <col width="10" customWidth="1" min="90" max="90"/>
     <col width="10" customWidth="1" min="91" max="91"/>
+    <col width="10" customWidth="1" min="92" max="92"/>
+    <col width="10" customWidth="1" min="93" max="93"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29928,6 +30562,12 @@
       <c r="CM1" s="1" t="n">
         <v>20260203</v>
       </c>
+      <c r="CN1" s="1" t="n">
+        <v>20260204</v>
+      </c>
+      <c r="CO1" s="1" t="n">
+        <v>20260205</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -30207,6 +30847,12 @@
       <c r="CM2" t="n">
         <v>100</v>
       </c>
+      <c r="CN2" t="n">
+        <v>100</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -30486,6 +31132,12 @@
       <c r="CM3" t="n">
         <v>47</v>
       </c>
+      <c r="CN3" t="n">
+        <v>12</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -30765,6 +31417,12 @@
       <c r="CM4" t="n">
         <v>100</v>
       </c>
+      <c r="CN4" t="n">
+        <v>62</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -31044,6 +31702,12 @@
       <c r="CM5" t="n">
         <v>0</v>
       </c>
+      <c r="CN5" t="n">
+        <v>4</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -31323,6 +31987,12 @@
       <c r="CM6" t="n">
         <v>0</v>
       </c>
+      <c r="CN6" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -31602,6 +32272,12 @@
       <c r="CM7" t="n">
         <v>16</v>
       </c>
+      <c r="CN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -31881,6 +32557,12 @@
       <c r="CM8" t="n">
         <v>32</v>
       </c>
+      <c r="CN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -32160,6 +32842,12 @@
       <c r="CM9" t="n">
         <v>58</v>
       </c>
+      <c r="CN9" t="n">
+        <v>94</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -32438,6 +33126,12 @@
       </c>
       <c r="CM10" t="n">
         <v>16</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -32451,7 +33145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:BA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -32505,6 +33199,8 @@
     <col width="10" customWidth="1" min="49" max="49"/>
     <col width="10" customWidth="1" min="50" max="50"/>
     <col width="10" customWidth="1" min="51" max="51"/>
+    <col width="10" customWidth="1" min="52" max="52"/>
+    <col width="10" customWidth="1" min="53" max="53"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32665,6 +33361,12 @@
       <c r="AY1" s="1" t="n">
         <v>20260203</v>
       </c>
+      <c r="AZ1" s="1" t="n">
+        <v>20260204</v>
+      </c>
+      <c r="BA1" s="1" t="n">
+        <v>20260205</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -32824,6 +33526,12 @@
       <c r="AY2" t="n">
         <v>58</v>
       </c>
+      <c r="AZ2" t="n">
+        <v>75</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -32983,6 +33691,12 @@
       <c r="AY3" t="n">
         <v>67</v>
       </c>
+      <c r="AZ3" t="n">
+        <v>50</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -33142,6 +33856,12 @@
       <c r="AY4" t="n">
         <v>100</v>
       </c>
+      <c r="AZ4" t="n">
+        <v>89</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -33301,6 +34021,12 @@
       <c r="AY5" t="n">
         <v>0</v>
       </c>
+      <c r="AZ5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -33460,6 +34186,12 @@
       <c r="AY6" t="n">
         <v>0</v>
       </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -33619,6 +34351,12 @@
       <c r="AY7" t="n">
         <v>33</v>
       </c>
+      <c r="AZ7" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -33778,6 +34516,12 @@
       <c r="AY8" t="n">
         <v>24</v>
       </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -33937,6 +34681,12 @@
       <c r="AY9" t="n">
         <v>70</v>
       </c>
+      <c r="AZ9" t="n">
+        <v>96</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -34095,6 +34845,12 @@
       </c>
       <c r="AY10" t="n">
         <v>31</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -34108,7 +34864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CM10"/>
+  <dimension ref="A1:CO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -34202,6 +34958,8 @@
     <col width="10" customWidth="1" min="89" max="89"/>
     <col width="10" customWidth="1" min="90" max="90"/>
     <col width="10" customWidth="1" min="91" max="91"/>
+    <col width="10" customWidth="1" min="92" max="92"/>
+    <col width="10" customWidth="1" min="93" max="93"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -34482,6 +35240,12 @@
       <c r="CM1" s="1" t="n">
         <v>20260203</v>
       </c>
+      <c r="CN1" s="1" t="n">
+        <v>20260204</v>
+      </c>
+      <c r="CO1" s="1" t="n">
+        <v>20260205</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -34761,6 +35525,12 @@
       <c r="CM2" t="n">
         <v>108</v>
       </c>
+      <c r="CN2" t="n">
+        <v>132</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>109</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -35040,6 +35810,12 @@
       <c r="CM3" t="n">
         <v>-15</v>
       </c>
+      <c r="CN3" t="n">
+        <v>-69</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>-62</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -35319,6 +36095,12 @@
       <c r="CM4" t="n">
         <v>65</v>
       </c>
+      <c r="CN4" t="n">
+        <v>9</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -35598,6 +36380,12 @@
       <c r="CM5" t="n">
         <v>-117</v>
       </c>
+      <c r="CN5" t="n">
+        <v>-93</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>-82</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -35877,6 +36665,12 @@
       <c r="CM6" t="n">
         <v>-110</v>
       </c>
+      <c r="CN6" t="n">
+        <v>-92</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>-82</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -36156,6 +36950,12 @@
       <c r="CM7" t="n">
         <v>-83</v>
       </c>
+      <c r="CN7" t="n">
+        <v>-127</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>-105</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -36435,6 +37235,12 @@
       <c r="CM8" t="n">
         <v>-46</v>
       </c>
+      <c r="CN8" t="n">
+        <v>-107</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>-92</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -36714,6 +37520,12 @@
       <c r="CM9" t="n">
         <v>7</v>
       </c>
+      <c r="CN9" t="n">
+        <v>64</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -36992,6 +37804,12 @@
       </c>
       <c r="CM10" t="n">
         <v>-69</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>-120</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>-101</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -602,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA10"/>
+  <dimension ref="A1:BB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -658,6 +658,7 @@
     <col width="10" customWidth="1" min="51" max="51"/>
     <col width="10" customWidth="1" min="52" max="52"/>
     <col width="10" customWidth="1" min="53" max="53"/>
+    <col width="10" customWidth="1" min="54" max="54"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -824,6 +825,9 @@
       <c r="BA1" s="1" t="n">
         <v>20260205</v>
       </c>
+      <c r="BB1" s="1" t="n">
+        <v>20260206</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -989,6 +993,9 @@
       <c r="BA2" t="n">
         <v>40</v>
       </c>
+      <c r="BB2" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1154,6 +1161,9 @@
       <c r="BA3" t="n">
         <v>-4</v>
       </c>
+      <c r="BB3" t="n">
+        <v>-70</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1319,6 +1329,9 @@
       <c r="BA4" t="n">
         <v>53</v>
       </c>
+      <c r="BB4" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1484,6 +1497,9 @@
       <c r="BA5" t="n">
         <v>-136</v>
       </c>
+      <c r="BB5" t="n">
+        <v>-163</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1649,6 +1665,9 @@
       <c r="BA6" t="n">
         <v>-17</v>
       </c>
+      <c r="BB6" t="n">
+        <v>-16</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1814,6 +1833,9 @@
       <c r="BA7" t="n">
         <v>-90</v>
       </c>
+      <c r="BB7" t="n">
+        <v>-108</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1979,6 +2001,9 @@
       <c r="BA8" t="n">
         <v>-127</v>
       </c>
+      <c r="BB8" t="n">
+        <v>-149</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2144,6 +2169,9 @@
       <c r="BA9" t="n">
         <v>101</v>
       </c>
+      <c r="BB9" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2308,6 +2336,9 @@
       </c>
       <c r="BA10" t="n">
         <v>-69</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>-84</v>
       </c>
     </row>
   </sheetData>
@@ -2321,7 +2352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CO10"/>
+  <dimension ref="A1:CP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2417,6 +2448,7 @@
     <col width="12" customWidth="1" min="91" max="91"/>
     <col width="12" customWidth="1" min="92" max="92"/>
     <col width="12" customWidth="1" min="93" max="93"/>
+    <col width="12" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2885,6 +2917,11 @@
           <t>20260205</t>
         </is>
       </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>20260206</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3170,6 +3207,9 @@
       <c r="CO2" t="n">
         <v>107</v>
       </c>
+      <c r="CP2" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3455,6 +3495,9 @@
       <c r="CO3" t="n">
         <v>97</v>
       </c>
+      <c r="CP3" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3740,6 +3783,9 @@
       <c r="CO4" t="n">
         <v>100</v>
       </c>
+      <c r="CP4" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4025,6 +4071,9 @@
       <c r="CO5" t="n">
         <v>91</v>
       </c>
+      <c r="CP5" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4310,6 +4359,9 @@
       <c r="CO6" t="n">
         <v>94</v>
       </c>
+      <c r="CP6" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4595,6 +4647,9 @@
       <c r="CO7" t="n">
         <v>94</v>
       </c>
+      <c r="CP7" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4880,6 +4935,9 @@
       <c r="CO8" t="n">
         <v>85</v>
       </c>
+      <c r="CP8" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5165,6 +5223,9 @@
       <c r="CO9" t="n">
         <v>104</v>
       </c>
+      <c r="CP9" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5449,6 +5510,9 @@
       </c>
       <c r="CO10" t="n">
         <v>94</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -5462,7 +5526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV10"/>
+  <dimension ref="A1:BW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5539,6 +5603,7 @@
     <col width="12" customWidth="1" min="72" max="72"/>
     <col width="12" customWidth="1" min="73" max="73"/>
     <col width="12" customWidth="1" min="74" max="74"/>
+    <col width="12" customWidth="1" min="75" max="75"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5912,6 +5977,11 @@
           <t>20260205</t>
         </is>
       </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>20260206</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6140,6 +6210,9 @@
       <c r="BV2" t="n">
         <v>14.24</v>
       </c>
+      <c r="BW2" t="n">
+        <v>23.07</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6368,6 +6441,9 @@
       <c r="BV3" t="n">
         <v>-23.42</v>
       </c>
+      <c r="BW3" t="n">
+        <v>-8.699999999999999</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6596,6 +6672,9 @@
       <c r="BV4" t="n">
         <v>-42.55</v>
       </c>
+      <c r="BW4" t="n">
+        <v>-45.58</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6824,6 +6903,9 @@
       <c r="BV5" t="n">
         <v>87.59999999999999</v>
       </c>
+      <c r="BW5" t="n">
+        <v>92.77</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7052,6 +7134,9 @@
       <c r="BV6" t="n">
         <v>28.78</v>
       </c>
+      <c r="BW6" t="n">
+        <v>22.84</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7280,6 +7365,9 @@
       <c r="BV7" t="n">
         <v>24.69</v>
       </c>
+      <c r="BW7" t="n">
+        <v>43.62</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7508,6 +7596,9 @@
       <c r="BV8" t="n">
         <v>57.24</v>
       </c>
+      <c r="BW8" t="n">
+        <v>69.13</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7736,6 +7827,9 @@
       <c r="BV9" t="n">
         <v>-15.07</v>
       </c>
+      <c r="BW9" t="n">
+        <v>-23.32</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7963,6 +8057,9 @@
       </c>
       <c r="BV10" t="n">
         <v>-14.7</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0.82</v>
       </c>
     </row>
   </sheetData>
@@ -7976,7 +8073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA10"/>
+  <dimension ref="A1:BB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8032,6 +8129,7 @@
     <col width="12" customWidth="1" min="51" max="51"/>
     <col width="12" customWidth="1" min="52" max="52"/>
     <col width="12" customWidth="1" min="53" max="53"/>
+    <col width="12" customWidth="1" min="54" max="54"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8300,6 +8398,11 @@
           <t>20260205</t>
         </is>
       </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>20260206</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8465,6 +8568,9 @@
       <c r="BA2" t="n">
         <v>0</v>
       </c>
+      <c r="BB2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8630,6 +8736,9 @@
       <c r="BA3" t="n">
         <v>0</v>
       </c>
+      <c r="BB3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8795,6 +8904,9 @@
       <c r="BA4" t="n">
         <v>0</v>
       </c>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8960,6 +9072,9 @@
       <c r="BA5" t="n">
         <v>0</v>
       </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9125,6 +9240,9 @@
       <c r="BA6" t="n">
         <v>0</v>
       </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9290,6 +9408,9 @@
       <c r="BA7" t="n">
         <v>0</v>
       </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9455,6 +9576,9 @@
       <c r="BA8" t="n">
         <v>0</v>
       </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9620,6 +9744,9 @@
       <c r="BA9" t="n">
         <v>0</v>
       </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9783,6 +9910,9 @@
         <v>53</v>
       </c>
       <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9797,7 +9927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE10"/>
+  <dimension ref="A1:CF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9883,6 +10013,7 @@
     <col width="10" customWidth="1" min="81" max="81"/>
     <col width="10" customWidth="1" min="82" max="82"/>
     <col width="10" customWidth="1" min="83" max="83"/>
+    <col width="10" customWidth="1" min="84" max="84"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10139,6 +10270,9 @@
       <c r="CE1" s="1" t="n">
         <v>20260205</v>
       </c>
+      <c r="CF1" s="1" t="n">
+        <v>20260206</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10394,6 +10528,9 @@
       <c r="CE2" t="n">
         <v>77</v>
       </c>
+      <c r="CF2" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10649,6 +10786,9 @@
       <c r="CE3" t="n">
         <v>-36</v>
       </c>
+      <c r="CF3" t="n">
+        <v>-113</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10904,6 +11044,9 @@
       <c r="CE4" t="n">
         <v>33</v>
       </c>
+      <c r="CF4" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11159,6 +11302,9 @@
       <c r="CE5" t="n">
         <v>-101</v>
       </c>
+      <c r="CF5" t="n">
+        <v>-124</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11414,6 +11560,9 @@
       <c r="CE6" t="n">
         <v>-89</v>
       </c>
+      <c r="CF6" t="n">
+        <v>-75</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11669,6 +11818,9 @@
       <c r="CE7" t="n">
         <v>-130</v>
       </c>
+      <c r="CF7" t="n">
+        <v>-131</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11924,6 +12076,9 @@
       <c r="CE8" t="n">
         <v>-105</v>
       </c>
+      <c r="CF8" t="n">
+        <v>-121</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12179,6 +12334,9 @@
       <c r="CE9" t="n">
         <v>66</v>
       </c>
+      <c r="CF9" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12433,6 +12591,9 @@
       </c>
       <c r="CE10" t="n">
         <v>-89</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>-107</v>
       </c>
     </row>
   </sheetData>
@@ -12446,7 +12607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DH10"/>
+  <dimension ref="A1:DI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12561,6 +12722,7 @@
     <col width="12" customWidth="1" min="110" max="110"/>
     <col width="12" customWidth="1" min="111" max="111"/>
     <col width="12" customWidth="1" min="112" max="112"/>
+    <col width="12" customWidth="1" min="113" max="113"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12904,6 +13066,9 @@
       <c r="DH1" s="1" t="n">
         <v>20260205</v>
       </c>
+      <c r="DI1" s="1" t="n">
+        <v>20260206</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13246,6 +13411,9 @@
       <c r="DH2" t="n">
         <v>276.49</v>
       </c>
+      <c r="DI2" t="n">
+        <v>275.91</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13588,6 +13756,9 @@
       <c r="DH3" t="n">
         <v>232.99</v>
       </c>
+      <c r="DI3" t="n">
+        <v>222.69</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13930,6 +14101,9 @@
       <c r="DH4" t="n">
         <v>333.04</v>
       </c>
+      <c r="DI4" t="n">
+        <v>331.25</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14272,6 +14446,9 @@
       <c r="DH5" t="n">
         <v>414.19</v>
       </c>
+      <c r="DI5" t="n">
+        <v>393.67</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14614,6 +14791,9 @@
       <c r="DH6" t="n">
         <v>80.16</v>
       </c>
+      <c r="DI6" t="n">
+        <v>80.87</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14956,6 +15136,9 @@
       <c r="DH7" t="n">
         <v>174.19</v>
       </c>
+      <c r="DI7" t="n">
+        <v>171.88</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15298,6 +15481,9 @@
       <c r="DH8" t="n">
         <v>139.54</v>
       </c>
+      <c r="DI8" t="n">
+        <v>130.01</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15640,6 +15826,9 @@
       <c r="DH9" t="n">
         <v>96.97</v>
       </c>
+      <c r="DI9" t="n">
+        <v>96.06999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15981,6 +16170,9 @@
       </c>
       <c r="DH10" t="n">
         <v>406.01</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>397.21</v>
       </c>
     </row>
   </sheetData>
@@ -15994,7 +16186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DH10"/>
+  <dimension ref="A1:DI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -16109,6 +16301,7 @@
     <col width="12" customWidth="1" min="110" max="110"/>
     <col width="12" customWidth="1" min="111" max="111"/>
     <col width="12" customWidth="1" min="112" max="112"/>
+    <col width="12" customWidth="1" min="113" max="113"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16452,6 +16645,9 @@
       <c r="DH1" s="1" t="n">
         <v>20260205</v>
       </c>
+      <c r="DI1" s="1" t="n">
+        <v>20260206</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16794,6 +16990,9 @@
       <c r="DH2" t="n">
         <v>276.49</v>
       </c>
+      <c r="DI2" t="n">
+        <v>275.91</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17136,6 +17335,9 @@
       <c r="DH3" t="n">
         <v>232.99</v>
       </c>
+      <c r="DI3" t="n">
+        <v>222.69</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17478,6 +17680,9 @@
       <c r="DH4" t="n">
         <v>333.04</v>
       </c>
+      <c r="DI4" t="n">
+        <v>331.25</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -17820,6 +18025,9 @@
       <c r="DH5" t="n">
         <v>414.19</v>
       </c>
+      <c r="DI5" t="n">
+        <v>393.67</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18162,6 +18370,9 @@
       <c r="DH6" t="n">
         <v>80.16</v>
       </c>
+      <c r="DI6" t="n">
+        <v>80.87</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18504,6 +18715,9 @@
       <c r="DH7" t="n">
         <v>174.19</v>
       </c>
+      <c r="DI7" t="n">
+        <v>171.88</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18846,6 +19060,9 @@
       <c r="DH8" t="n">
         <v>139.54</v>
       </c>
+      <c r="DI8" t="n">
+        <v>130.01</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19188,6 +19405,9 @@
       <c r="DH9" t="n">
         <v>96.97</v>
       </c>
+      <c r="DI9" t="n">
+        <v>96.06999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -19529,6 +19749,9 @@
       </c>
       <c r="DH10" t="n">
         <v>406.01</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>397.21</v>
       </c>
     </row>
   </sheetData>
@@ -19542,7 +19765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DH10"/>
+  <dimension ref="A1:DI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -19657,6 +19880,7 @@
     <col width="12" customWidth="1" min="110" max="110"/>
     <col width="12" customWidth="1" min="111" max="111"/>
     <col width="12" customWidth="1" min="112" max="112"/>
+    <col width="12" customWidth="1" min="113" max="113"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20000,6 +20224,9 @@
       <c r="DH1" s="1" t="n">
         <v>20260205</v>
       </c>
+      <c r="DI1" s="1" t="n">
+        <v>20260206</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20342,6 +20569,9 @@
       <c r="DH2" t="n">
         <v>276.49</v>
       </c>
+      <c r="DI2" t="n">
+        <v>275.91</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20684,6 +20914,9 @@
       <c r="DH3" t="n">
         <v>232.99</v>
       </c>
+      <c r="DI3" t="n">
+        <v>222.69</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -21026,6 +21259,9 @@
       <c r="DH4" t="n">
         <v>333.04</v>
       </c>
+      <c r="DI4" t="n">
+        <v>331.25</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -21368,6 +21604,9 @@
       <c r="DH5" t="n">
         <v>414.19</v>
       </c>
+      <c r="DI5" t="n">
+        <v>393.67</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21710,6 +21949,9 @@
       <c r="DH6" t="n">
         <v>80.16</v>
       </c>
+      <c r="DI6" t="n">
+        <v>80.87</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -22052,6 +22294,9 @@
       <c r="DH7" t="n">
         <v>174.19</v>
       </c>
+      <c r="DI7" t="n">
+        <v>171.88</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22394,6 +22639,9 @@
       <c r="DH8" t="n">
         <v>139.54</v>
       </c>
+      <c r="DI8" t="n">
+        <v>130.01</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22736,6 +22984,9 @@
       <c r="DH9" t="n">
         <v>96.97</v>
       </c>
+      <c r="DI9" t="n">
+        <v>96.06999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23077,6 +23328,9 @@
       </c>
       <c r="DH10" t="n">
         <v>406.01</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>397.21</v>
       </c>
     </row>
   </sheetData>
@@ -23090,7 +23344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DH10"/>
+  <dimension ref="A1:DI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23205,6 +23459,7 @@
     <col width="12" customWidth="1" min="110" max="110"/>
     <col width="12" customWidth="1" min="111" max="111"/>
     <col width="12" customWidth="1" min="112" max="112"/>
+    <col width="12" customWidth="1" min="113" max="113"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23548,6 +23803,9 @@
       <c r="DH1" s="1" t="n">
         <v>20260205</v>
       </c>
+      <c r="DI1" s="1" t="n">
+        <v>20260206</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23890,6 +24148,9 @@
       <c r="DH2" t="n">
         <v>276.49</v>
       </c>
+      <c r="DI2" t="n">
+        <v>275.91</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -24232,6 +24493,9 @@
       <c r="DH3" t="n">
         <v>232.99</v>
       </c>
+      <c r="DI3" t="n">
+        <v>222.69</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -24574,6 +24838,9 @@
       <c r="DH4" t="n">
         <v>333.04</v>
       </c>
+      <c r="DI4" t="n">
+        <v>331.25</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24916,6 +25183,9 @@
       <c r="DH5" t="n">
         <v>414.19</v>
       </c>
+      <c r="DI5" t="n">
+        <v>393.67</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -25258,6 +25528,9 @@
       <c r="DH6" t="n">
         <v>80.16</v>
       </c>
+      <c r="DI6" t="n">
+        <v>80.87</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -25600,6 +25873,9 @@
       <c r="DH7" t="n">
         <v>174.19</v>
       </c>
+      <c r="DI7" t="n">
+        <v>171.88</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25942,6 +26218,9 @@
       <c r="DH8" t="n">
         <v>139.54</v>
       </c>
+      <c r="DI8" t="n">
+        <v>130.01</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -26284,6 +26563,9 @@
       <c r="DH9" t="n">
         <v>96.97</v>
       </c>
+      <c r="DI9" t="n">
+        <v>96.06999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26625,6 +26907,9 @@
       </c>
       <c r="DH10" t="n">
         <v>406.01</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>397.21</v>
       </c>
     </row>
   </sheetData>
@@ -26638,7 +26923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DH10"/>
+  <dimension ref="A1:DI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -26753,6 +27038,7 @@
     <col width="12" customWidth="1" min="110" max="110"/>
     <col width="12" customWidth="1" min="111" max="111"/>
     <col width="12" customWidth="1" min="112" max="112"/>
+    <col width="12" customWidth="1" min="113" max="113"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27096,6 +27382,9 @@
       <c r="DH1" s="1" t="n">
         <v>20260205</v>
       </c>
+      <c r="DI1" s="1" t="n">
+        <v>20260206</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -27438,6 +27727,9 @@
       <c r="DH2" t="n">
         <v>0</v>
       </c>
+      <c r="DI2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -27780,6 +28072,9 @@
       <c r="DH3" t="n">
         <v>0</v>
       </c>
+      <c r="DI3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -28122,6 +28417,9 @@
       <c r="DH4" t="n">
         <v>0</v>
       </c>
+      <c r="DI4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -28464,6 +28762,9 @@
       <c r="DH5" t="n">
         <v>0</v>
       </c>
+      <c r="DI5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -28806,6 +29107,9 @@
       <c r="DH6" t="n">
         <v>0</v>
       </c>
+      <c r="DI6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -29148,6 +29452,9 @@
       <c r="DH7" t="n">
         <v>0</v>
       </c>
+      <c r="DI7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -29490,6 +29797,9 @@
       <c r="DH8" t="n">
         <v>0</v>
       </c>
+      <c r="DI8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -29832,6 +30142,9 @@
       <c r="DH9" t="n">
         <v>0</v>
       </c>
+      <c r="DI9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -30172,6 +30485,9 @@
         <v>74606873</v>
       </c>
       <c r="DH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -30186,7 +30502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CO10"/>
+  <dimension ref="A1:CP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -30282,6 +30598,7 @@
     <col width="10" customWidth="1" min="91" max="91"/>
     <col width="10" customWidth="1" min="92" max="92"/>
     <col width="10" customWidth="1" min="93" max="93"/>
+    <col width="10" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30568,6 +30885,9 @@
       <c r="CO1" s="1" t="n">
         <v>20260205</v>
       </c>
+      <c r="CP1" s="1" t="n">
+        <v>20260206</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -30853,6 +31173,9 @@
       <c r="CO2" t="n">
         <v>100</v>
       </c>
+      <c r="CP2" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -31138,6 +31461,9 @@
       <c r="CO3" t="n">
         <v>12</v>
       </c>
+      <c r="CP3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -31423,6 +31749,9 @@
       <c r="CO4" t="n">
         <v>62</v>
       </c>
+      <c r="CP4" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -31708,6 +32037,9 @@
       <c r="CO5" t="n">
         <v>4</v>
       </c>
+      <c r="CP5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -31993,6 +32325,9 @@
       <c r="CO6" t="n">
         <v>2</v>
       </c>
+      <c r="CP6" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -32278,6 +32613,9 @@
       <c r="CO7" t="n">
         <v>0</v>
       </c>
+      <c r="CP7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -32563,6 +32901,9 @@
       <c r="CO8" t="n">
         <v>0</v>
       </c>
+      <c r="CP8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -32848,6 +33189,9 @@
       <c r="CO9" t="n">
         <v>93</v>
       </c>
+      <c r="CP9" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -33131,6 +33475,9 @@
         <v>0</v>
       </c>
       <c r="CO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -33145,7 +33492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA10"/>
+  <dimension ref="A1:BB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -33201,6 +33548,7 @@
     <col width="10" customWidth="1" min="51" max="51"/>
     <col width="10" customWidth="1" min="52" max="52"/>
     <col width="10" customWidth="1" min="53" max="53"/>
+    <col width="10" customWidth="1" min="54" max="54"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33367,6 +33715,9 @@
       <c r="BA1" s="1" t="n">
         <v>20260205</v>
       </c>
+      <c r="BB1" s="1" t="n">
+        <v>20260206</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -33532,6 +33883,9 @@
       <c r="BA2" t="n">
         <v>75</v>
       </c>
+      <c r="BB2" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -33697,6 +34051,9 @@
       <c r="BA3" t="n">
         <v>50</v>
       </c>
+      <c r="BB3" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -33862,6 +34219,9 @@
       <c r="BA4" t="n">
         <v>89</v>
       </c>
+      <c r="BB4" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -34027,6 +34387,9 @@
       <c r="BA5" t="n">
         <v>3</v>
       </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -34192,6 +34555,9 @@
       <c r="BA6" t="n">
         <v>0</v>
       </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -34357,6 +34723,9 @@
       <c r="BA7" t="n">
         <v>12</v>
       </c>
+      <c r="BB7" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -34522,6 +34891,9 @@
       <c r="BA8" t="n">
         <v>0</v>
       </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -34687,6 +35059,9 @@
       <c r="BA9" t="n">
         <v>96</v>
       </c>
+      <c r="BB9" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -34851,6 +35226,9 @@
       </c>
       <c r="BA10" t="n">
         <v>15</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -34864,7 +35242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CO10"/>
+  <dimension ref="A1:CP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -34960,6 +35338,7 @@
     <col width="10" customWidth="1" min="91" max="91"/>
     <col width="10" customWidth="1" min="92" max="92"/>
     <col width="10" customWidth="1" min="93" max="93"/>
+    <col width="10" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -35246,6 +35625,9 @@
       <c r="CO1" s="1" t="n">
         <v>20260205</v>
       </c>
+      <c r="CP1" s="1" t="n">
+        <v>20260206</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -35531,6 +35913,9 @@
       <c r="CO2" t="n">
         <v>109</v>
       </c>
+      <c r="CP2" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -35816,6 +36201,9 @@
       <c r="CO3" t="n">
         <v>-62</v>
       </c>
+      <c r="CP3" t="n">
+        <v>-129</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -36101,6 +36489,9 @@
       <c r="CO4" t="n">
         <v>4</v>
       </c>
+      <c r="CP4" t="n">
+        <v>-20</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -36386,6 +36777,9 @@
       <c r="CO5" t="n">
         <v>-82</v>
       </c>
+      <c r="CP5" t="n">
+        <v>-105</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -36671,6 +37065,9 @@
       <c r="CO6" t="n">
         <v>-82</v>
       </c>
+      <c r="CP6" t="n">
+        <v>-65</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -36956,6 +37353,9 @@
       <c r="CO7" t="n">
         <v>-105</v>
       </c>
+      <c r="CP7" t="n">
+        <v>-105</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -37241,6 +37641,9 @@
       <c r="CO8" t="n">
         <v>-92</v>
       </c>
+      <c r="CP8" t="n">
+        <v>-106</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -37526,6 +37929,9 @@
       <c r="CO9" t="n">
         <v>61</v>
       </c>
+      <c r="CP9" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -37810,6 +38216,9 @@
       </c>
       <c r="CO10" t="n">
         <v>-101</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>-109</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -602,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB10"/>
+  <dimension ref="A1:BC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -659,6 +659,7 @@
     <col width="10" customWidth="1" min="52" max="52"/>
     <col width="10" customWidth="1" min="53" max="53"/>
     <col width="10" customWidth="1" min="54" max="54"/>
+    <col width="10" customWidth="1" min="55" max="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -828,6 +829,9 @@
       <c r="BB1" s="1" t="n">
         <v>20260206</v>
       </c>
+      <c r="BC1" s="1" t="n">
+        <v>20260209</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -996,6 +1000,9 @@
       <c r="BB2" t="n">
         <v>36</v>
       </c>
+      <c r="BC2" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1164,6 +1171,9 @@
       <c r="BB3" t="n">
         <v>-70</v>
       </c>
+      <c r="BC3" t="n">
+        <v>-144</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1332,6 +1342,9 @@
       <c r="BB4" t="n">
         <v>46</v>
       </c>
+      <c r="BC4" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1500,6 +1513,9 @@
       <c r="BB5" t="n">
         <v>-163</v>
       </c>
+      <c r="BC5" t="n">
+        <v>-137</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1668,6 +1684,9 @@
       <c r="BB6" t="n">
         <v>-16</v>
       </c>
+      <c r="BC6" t="n">
+        <v>-14</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1836,6 +1855,9 @@
       <c r="BB7" t="n">
         <v>-108</v>
       </c>
+      <c r="BC7" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2004,6 +2026,9 @@
       <c r="BB8" t="n">
         <v>-149</v>
       </c>
+      <c r="BC8" t="n">
+        <v>-121</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2172,6 +2197,9 @@
       <c r="BB9" t="n">
         <v>86</v>
       </c>
+      <c r="BC9" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2339,6 +2367,9 @@
       </c>
       <c r="BB10" t="n">
         <v>-84</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>-54</v>
       </c>
     </row>
   </sheetData>
@@ -2352,7 +2383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CP10"/>
+  <dimension ref="A1:CQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2449,6 +2480,7 @@
     <col width="12" customWidth="1" min="92" max="92"/>
     <col width="12" customWidth="1" min="93" max="93"/>
     <col width="12" customWidth="1" min="94" max="94"/>
+    <col width="12" customWidth="1" min="95" max="95"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2922,6 +2954,11 @@
           <t>20260206</t>
         </is>
       </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>20260209</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3210,6 +3247,9 @@
       <c r="CP2" t="n">
         <v>106</v>
       </c>
+      <c r="CQ2" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3498,6 +3538,9 @@
       <c r="CP3" t="n">
         <v>94</v>
       </c>
+      <c r="CQ3" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3786,6 +3829,9 @@
       <c r="CP4" t="n">
         <v>99</v>
       </c>
+      <c r="CQ4" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4074,6 +4120,9 @@
       <c r="CP5" t="n">
         <v>88</v>
       </c>
+      <c r="CQ5" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4362,6 +4411,9 @@
       <c r="CP6" t="n">
         <v>95</v>
       </c>
+      <c r="CQ6" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4650,6 +4702,9 @@
       <c r="CP7" t="n">
         <v>93</v>
       </c>
+      <c r="CQ7" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4938,6 +4993,9 @@
       <c r="CP8" t="n">
         <v>80</v>
       </c>
+      <c r="CQ8" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5226,6 +5284,9 @@
       <c r="CP9" t="n">
         <v>102</v>
       </c>
+      <c r="CQ9" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5513,6 +5574,9 @@
       </c>
       <c r="CP10" t="n">
         <v>92</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -5526,7 +5590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW10"/>
+  <dimension ref="A1:BX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5604,6 +5668,7 @@
     <col width="12" customWidth="1" min="73" max="73"/>
     <col width="12" customWidth="1" min="74" max="74"/>
     <col width="12" customWidth="1" min="75" max="75"/>
+    <col width="12" customWidth="1" min="76" max="76"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5982,6 +6047,11 @@
           <t>20260206</t>
         </is>
       </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>20260209</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6213,6 +6283,9 @@
       <c r="BW2" t="n">
         <v>23.07</v>
       </c>
+      <c r="BX2" t="n">
+        <v>31.64</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6444,6 +6517,9 @@
       <c r="BW3" t="n">
         <v>-8.699999999999999</v>
       </c>
+      <c r="BX3" t="n">
+        <v>25.67</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6675,6 +6751,9 @@
       <c r="BW4" t="n">
         <v>-45.58</v>
       </c>
+      <c r="BX4" t="n">
+        <v>-38.81</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6906,6 +6985,9 @@
       <c r="BW5" t="n">
         <v>92.77</v>
       </c>
+      <c r="BX5" t="n">
+        <v>85.26000000000001</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7137,6 +7219,9 @@
       <c r="BW6" t="n">
         <v>22.84</v>
       </c>
+      <c r="BX6" t="n">
+        <v>15.96</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7368,6 +7453,9 @@
       <c r="BW7" t="n">
         <v>43.62</v>
       </c>
+      <c r="BX7" t="n">
+        <v>43.97</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7599,6 +7687,9 @@
       <c r="BW8" t="n">
         <v>69.13</v>
       </c>
+      <c r="BX8" t="n">
+        <v>67.83</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7830,6 +7921,9 @@
       <c r="BW9" t="n">
         <v>-23.32</v>
       </c>
+      <c r="BX9" t="n">
+        <v>-24.26</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8060,6 +8154,9 @@
       </c>
       <c r="BW10" t="n">
         <v>0.82</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>3.76</v>
       </c>
     </row>
   </sheetData>
@@ -8073,7 +8170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB10"/>
+  <dimension ref="A1:BC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8130,6 +8227,7 @@
     <col width="12" customWidth="1" min="52" max="52"/>
     <col width="12" customWidth="1" min="53" max="53"/>
     <col width="12" customWidth="1" min="54" max="54"/>
+    <col width="12" customWidth="1" min="55" max="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8403,6 +8501,11 @@
           <t>20260206</t>
         </is>
       </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>20260209</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8571,6 +8674,9 @@
       <c r="BB2" t="n">
         <v>0</v>
       </c>
+      <c r="BC2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8739,6 +8845,9 @@
       <c r="BB3" t="n">
         <v>0</v>
       </c>
+      <c r="BC3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8907,6 +9016,9 @@
       <c r="BB4" t="n">
         <v>0</v>
       </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9075,6 +9187,9 @@
       <c r="BB5" t="n">
         <v>0</v>
       </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9243,6 +9358,9 @@
       <c r="BB6" t="n">
         <v>0</v>
       </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9411,6 +9529,9 @@
       <c r="BB7" t="n">
         <v>0</v>
       </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9579,6 +9700,9 @@
       <c r="BB8" t="n">
         <v>0</v>
       </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9747,6 +9871,9 @@
       <c r="BB9" t="n">
         <v>0</v>
       </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9913,6 +10040,9 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9927,7 +10057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CF10"/>
+  <dimension ref="A1:CG10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10014,6 +10144,7 @@
     <col width="10" customWidth="1" min="82" max="82"/>
     <col width="10" customWidth="1" min="83" max="83"/>
     <col width="10" customWidth="1" min="84" max="84"/>
+    <col width="10" customWidth="1" min="85" max="85"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10273,6 +10404,9 @@
       <c r="CF1" s="1" t="n">
         <v>20260206</v>
       </c>
+      <c r="CG1" s="1" t="n">
+        <v>20260209</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10531,6 +10665,9 @@
       <c r="CF2" t="n">
         <v>72</v>
       </c>
+      <c r="CG2" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10789,6 +10926,9 @@
       <c r="CF3" t="n">
         <v>-113</v>
       </c>
+      <c r="CG3" t="n">
+        <v>-163</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11047,6 +11187,9 @@
       <c r="CF4" t="n">
         <v>21</v>
       </c>
+      <c r="CG4" t="n">
+        <v>-27</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11305,6 +11448,9 @@
       <c r="CF5" t="n">
         <v>-124</v>
       </c>
+      <c r="CG5" t="n">
+        <v>-99</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11563,6 +11709,9 @@
       <c r="CF6" t="n">
         <v>-75</v>
       </c>
+      <c r="CG6" t="n">
+        <v>-56</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11821,6 +11970,9 @@
       <c r="CF7" t="n">
         <v>-131</v>
       </c>
+      <c r="CG7" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12079,6 +12231,9 @@
       <c r="CF8" t="n">
         <v>-121</v>
       </c>
+      <c r="CG8" t="n">
+        <v>-95</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12337,6 +12492,9 @@
       <c r="CF9" t="n">
         <v>53</v>
       </c>
+      <c r="CG9" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12594,6 +12752,9 @@
       </c>
       <c r="CF10" t="n">
         <v>-107</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>-70</v>
       </c>
     </row>
   </sheetData>
@@ -12607,7 +12768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DI10"/>
+  <dimension ref="A1:DJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12723,6 +12884,7 @@
     <col width="12" customWidth="1" min="111" max="111"/>
     <col width="12" customWidth="1" min="112" max="112"/>
     <col width="12" customWidth="1" min="113" max="113"/>
+    <col width="12" customWidth="1" min="114" max="114"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13069,6 +13231,9 @@
       <c r="DI1" s="1" t="n">
         <v>20260206</v>
       </c>
+      <c r="DJ1" s="1" t="n">
+        <v>20260209</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13414,6 +13579,9 @@
       <c r="DI2" t="n">
         <v>275.91</v>
       </c>
+      <c r="DJ2" t="n">
+        <v>278.12</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13759,6 +13927,9 @@
       <c r="DI3" t="n">
         <v>222.69</v>
       </c>
+      <c r="DJ3" t="n">
+        <v>210.32</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14104,6 +14275,9 @@
       <c r="DI4" t="n">
         <v>331.25</v>
       </c>
+      <c r="DJ4" t="n">
+        <v>322.86</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14449,6 +14623,9 @@
       <c r="DI5" t="n">
         <v>393.67</v>
       </c>
+      <c r="DJ5" t="n">
+        <v>401.14</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14794,6 +14971,9 @@
       <c r="DI6" t="n">
         <v>80.87</v>
       </c>
+      <c r="DJ6" t="n">
+        <v>82.2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15139,6 +15319,9 @@
       <c r="DI7" t="n">
         <v>171.88</v>
       </c>
+      <c r="DJ7" t="n">
+        <v>185.41</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15484,6 +15667,9 @@
       <c r="DI8" t="n">
         <v>130.01</v>
       </c>
+      <c r="DJ8" t="n">
+        <v>135.9</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15829,6 +16015,9 @@
       <c r="DI9" t="n">
         <v>96.06999999999999</v>
       </c>
+      <c r="DJ9" t="n">
+        <v>99.45</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16173,6 +16362,9 @@
       </c>
       <c r="DI10" t="n">
         <v>397.21</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>411.11</v>
       </c>
     </row>
   </sheetData>
@@ -16186,7 +16378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DI10"/>
+  <dimension ref="A1:DJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -16302,6 +16494,7 @@
     <col width="12" customWidth="1" min="111" max="111"/>
     <col width="12" customWidth="1" min="112" max="112"/>
     <col width="12" customWidth="1" min="113" max="113"/>
+    <col width="12" customWidth="1" min="114" max="114"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16648,6 +16841,9 @@
       <c r="DI1" s="1" t="n">
         <v>20260206</v>
       </c>
+      <c r="DJ1" s="1" t="n">
+        <v>20260209</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16993,6 +17189,9 @@
       <c r="DI2" t="n">
         <v>275.91</v>
       </c>
+      <c r="DJ2" t="n">
+        <v>278.12</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17338,6 +17537,9 @@
       <c r="DI3" t="n">
         <v>222.69</v>
       </c>
+      <c r="DJ3" t="n">
+        <v>210.32</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17683,6 +17885,9 @@
       <c r="DI4" t="n">
         <v>331.25</v>
       </c>
+      <c r="DJ4" t="n">
+        <v>322.86</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18028,6 +18233,9 @@
       <c r="DI5" t="n">
         <v>393.67</v>
       </c>
+      <c r="DJ5" t="n">
+        <v>401.14</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18373,6 +18581,9 @@
       <c r="DI6" t="n">
         <v>80.87</v>
       </c>
+      <c r="DJ6" t="n">
+        <v>82.2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18718,6 +18929,9 @@
       <c r="DI7" t="n">
         <v>171.88</v>
       </c>
+      <c r="DJ7" t="n">
+        <v>185.41</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19063,6 +19277,9 @@
       <c r="DI8" t="n">
         <v>130.01</v>
       </c>
+      <c r="DJ8" t="n">
+        <v>135.9</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19408,6 +19625,9 @@
       <c r="DI9" t="n">
         <v>96.06999999999999</v>
       </c>
+      <c r="DJ9" t="n">
+        <v>99.45</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -19752,6 +19972,9 @@
       </c>
       <c r="DI10" t="n">
         <v>397.21</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>411.11</v>
       </c>
     </row>
   </sheetData>
@@ -19765,7 +19988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DI10"/>
+  <dimension ref="A1:DJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -19881,6 +20104,7 @@
     <col width="12" customWidth="1" min="111" max="111"/>
     <col width="12" customWidth="1" min="112" max="112"/>
     <col width="12" customWidth="1" min="113" max="113"/>
+    <col width="12" customWidth="1" min="114" max="114"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20227,6 +20451,9 @@
       <c r="DI1" s="1" t="n">
         <v>20260206</v>
       </c>
+      <c r="DJ1" s="1" t="n">
+        <v>20260209</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20572,6 +20799,9 @@
       <c r="DI2" t="n">
         <v>275.91</v>
       </c>
+      <c r="DJ2" t="n">
+        <v>278.12</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20917,6 +21147,9 @@
       <c r="DI3" t="n">
         <v>222.69</v>
       </c>
+      <c r="DJ3" t="n">
+        <v>210.32</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -21262,6 +21495,9 @@
       <c r="DI4" t="n">
         <v>331.25</v>
       </c>
+      <c r="DJ4" t="n">
+        <v>322.86</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -21607,6 +21843,9 @@
       <c r="DI5" t="n">
         <v>393.67</v>
       </c>
+      <c r="DJ5" t="n">
+        <v>401.14</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21952,6 +22191,9 @@
       <c r="DI6" t="n">
         <v>80.87</v>
       </c>
+      <c r="DJ6" t="n">
+        <v>82.2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -22297,6 +22539,9 @@
       <c r="DI7" t="n">
         <v>171.88</v>
       </c>
+      <c r="DJ7" t="n">
+        <v>185.41</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22642,6 +22887,9 @@
       <c r="DI8" t="n">
         <v>130.01</v>
       </c>
+      <c r="DJ8" t="n">
+        <v>135.9</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22987,6 +23235,9 @@
       <c r="DI9" t="n">
         <v>96.06999999999999</v>
       </c>
+      <c r="DJ9" t="n">
+        <v>99.45</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23331,6 +23582,9 @@
       </c>
       <c r="DI10" t="n">
         <v>397.21</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>411.11</v>
       </c>
     </row>
   </sheetData>
@@ -23344,7 +23598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DI10"/>
+  <dimension ref="A1:DJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23460,6 +23714,7 @@
     <col width="12" customWidth="1" min="111" max="111"/>
     <col width="12" customWidth="1" min="112" max="112"/>
     <col width="12" customWidth="1" min="113" max="113"/>
+    <col width="12" customWidth="1" min="114" max="114"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23806,6 +24061,9 @@
       <c r="DI1" s="1" t="n">
         <v>20260206</v>
       </c>
+      <c r="DJ1" s="1" t="n">
+        <v>20260209</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24151,6 +24409,9 @@
       <c r="DI2" t="n">
         <v>275.91</v>
       </c>
+      <c r="DJ2" t="n">
+        <v>278.12</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -24496,6 +24757,9 @@
       <c r="DI3" t="n">
         <v>222.69</v>
       </c>
+      <c r="DJ3" t="n">
+        <v>210.32</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -24841,6 +25105,9 @@
       <c r="DI4" t="n">
         <v>331.25</v>
       </c>
+      <c r="DJ4" t="n">
+        <v>322.86</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -25186,6 +25453,9 @@
       <c r="DI5" t="n">
         <v>393.67</v>
       </c>
+      <c r="DJ5" t="n">
+        <v>401.14</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -25531,6 +25801,9 @@
       <c r="DI6" t="n">
         <v>80.87</v>
       </c>
+      <c r="DJ6" t="n">
+        <v>82.2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -25876,6 +26149,9 @@
       <c r="DI7" t="n">
         <v>171.88</v>
       </c>
+      <c r="DJ7" t="n">
+        <v>185.41</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -26221,6 +26497,9 @@
       <c r="DI8" t="n">
         <v>130.01</v>
       </c>
+      <c r="DJ8" t="n">
+        <v>135.9</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -26566,6 +26845,9 @@
       <c r="DI9" t="n">
         <v>96.06999999999999</v>
       </c>
+      <c r="DJ9" t="n">
+        <v>99.45</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26910,6 +27192,9 @@
       </c>
       <c r="DI10" t="n">
         <v>397.21</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>411.11</v>
       </c>
     </row>
   </sheetData>
@@ -26923,7 +27208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DI10"/>
+  <dimension ref="A1:DJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -27039,6 +27324,7 @@
     <col width="12" customWidth="1" min="111" max="111"/>
     <col width="12" customWidth="1" min="112" max="112"/>
     <col width="12" customWidth="1" min="113" max="113"/>
+    <col width="12" customWidth="1" min="114" max="114"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27385,6 +27671,9 @@
       <c r="DI1" s="1" t="n">
         <v>20260206</v>
       </c>
+      <c r="DJ1" s="1" t="n">
+        <v>20260209</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -27730,6 +28019,9 @@
       <c r="DI2" t="n">
         <v>0</v>
       </c>
+      <c r="DJ2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -28075,6 +28367,9 @@
       <c r="DI3" t="n">
         <v>0</v>
       </c>
+      <c r="DJ3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -28420,6 +28715,9 @@
       <c r="DI4" t="n">
         <v>0</v>
       </c>
+      <c r="DJ4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -28765,6 +29063,9 @@
       <c r="DI5" t="n">
         <v>0</v>
       </c>
+      <c r="DJ5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -29110,6 +29411,9 @@
       <c r="DI6" t="n">
         <v>0</v>
       </c>
+      <c r="DJ6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -29455,6 +29759,9 @@
       <c r="DI7" t="n">
         <v>0</v>
       </c>
+      <c r="DJ7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -29800,6 +30107,9 @@
       <c r="DI8" t="n">
         <v>0</v>
       </c>
+      <c r="DJ8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -30145,6 +30455,9 @@
       <c r="DI9" t="n">
         <v>0</v>
       </c>
+      <c r="DJ9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -30488,6 +30801,9 @@
         <v>0</v>
       </c>
       <c r="DI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -30502,7 +30818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CP10"/>
+  <dimension ref="A1:CQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -30599,6 +30915,7 @@
     <col width="10" customWidth="1" min="92" max="92"/>
     <col width="10" customWidth="1" min="93" max="93"/>
     <col width="10" customWidth="1" min="94" max="94"/>
+    <col width="10" customWidth="1" min="95" max="95"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30888,6 +31205,9 @@
       <c r="CP1" s="1" t="n">
         <v>20260206</v>
       </c>
+      <c r="CQ1" s="1" t="n">
+        <v>20260209</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -31176,6 +31496,9 @@
       <c r="CP2" t="n">
         <v>98</v>
       </c>
+      <c r="CQ2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -31464,6 +31787,9 @@
       <c r="CP3" t="n">
         <v>0</v>
       </c>
+      <c r="CQ3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -31752,6 +32078,9 @@
       <c r="CP4" t="n">
         <v>52</v>
       </c>
+      <c r="CQ4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -32040,6 +32369,9 @@
       <c r="CP5" t="n">
         <v>0</v>
       </c>
+      <c r="CQ5" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -32328,6 +32660,9 @@
       <c r="CP6" t="n">
         <v>9</v>
       </c>
+      <c r="CQ6" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -32616,6 +32951,9 @@
       <c r="CP7" t="n">
         <v>0</v>
       </c>
+      <c r="CQ7" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -32904,6 +33242,9 @@
       <c r="CP8" t="n">
         <v>0</v>
       </c>
+      <c r="CQ8" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -33192,6 +33533,9 @@
       <c r="CP9" t="n">
         <v>82</v>
       </c>
+      <c r="CQ9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -33479,6 +33823,9 @@
       </c>
       <c r="CP10" t="n">
         <v>0</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -33492,7 +33839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB10"/>
+  <dimension ref="A1:BC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -33549,6 +33896,7 @@
     <col width="10" customWidth="1" min="52" max="52"/>
     <col width="10" customWidth="1" min="53" max="53"/>
     <col width="10" customWidth="1" min="54" max="54"/>
+    <col width="10" customWidth="1" min="55" max="55"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33718,6 +34066,9 @@
       <c r="BB1" s="1" t="n">
         <v>20260206</v>
       </c>
+      <c r="BC1" s="1" t="n">
+        <v>20260209</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -33886,6 +34237,9 @@
       <c r="BB2" t="n">
         <v>74</v>
       </c>
+      <c r="BC2" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -34054,6 +34408,9 @@
       <c r="BB3" t="n">
         <v>17</v>
       </c>
+      <c r="BC3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -34222,6 +34579,9 @@
       <c r="BB4" t="n">
         <v>87</v>
       </c>
+      <c r="BC4" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -34390,6 +34750,9 @@
       <c r="BB5" t="n">
         <v>0</v>
       </c>
+      <c r="BC5" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -34558,6 +34921,9 @@
       <c r="BB6" t="n">
         <v>0</v>
       </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -34726,6 +35092,9 @@
       <c r="BB7" t="n">
         <v>4</v>
       </c>
+      <c r="BC7" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -34894,6 +35263,9 @@
       <c r="BB8" t="n">
         <v>0</v>
       </c>
+      <c r="BC8" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -35062,6 +35434,9 @@
       <c r="BB9" t="n">
         <v>90</v>
       </c>
+      <c r="BC9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -35229,6 +35604,9 @@
       </c>
       <c r="BB10" t="n">
         <v>6</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -35242,7 +35620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CP10"/>
+  <dimension ref="A1:CQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -35339,6 +35717,7 @@
     <col width="10" customWidth="1" min="92" max="92"/>
     <col width="10" customWidth="1" min="93" max="93"/>
     <col width="10" customWidth="1" min="94" max="94"/>
+    <col width="10" customWidth="1" min="95" max="95"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -35628,6 +36007,9 @@
       <c r="CP1" s="1" t="n">
         <v>20260206</v>
       </c>
+      <c r="CQ1" s="1" t="n">
+        <v>20260209</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -35916,6 +36298,9 @@
       <c r="CP2" t="n">
         <v>90</v>
       </c>
+      <c r="CQ2" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -36204,6 +36589,9 @@
       <c r="CP3" t="n">
         <v>-129</v>
       </c>
+      <c r="CQ3" t="n">
+        <v>-158</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -36492,6 +36880,9 @@
       <c r="CP4" t="n">
         <v>-20</v>
       </c>
+      <c r="CQ4" t="n">
+        <v>-102</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -36780,6 +37171,9 @@
       <c r="CP5" t="n">
         <v>-105</v>
       </c>
+      <c r="CQ5" t="n">
+        <v>-80</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -37068,6 +37462,9 @@
       <c r="CP6" t="n">
         <v>-65</v>
       </c>
+      <c r="CQ6" t="n">
+        <v>-41</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -37356,6 +37753,9 @@
       <c r="CP7" t="n">
         <v>-105</v>
       </c>
+      <c r="CQ7" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -37644,6 +38044,9 @@
       <c r="CP8" t="n">
         <v>-106</v>
       </c>
+      <c r="CQ8" t="n">
+        <v>-77</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -37932,6 +38335,9 @@
       <c r="CP9" t="n">
         <v>42</v>
       </c>
+      <c r="CQ9" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -38219,6 +38625,9 @@
       </c>
       <c r="CP10" t="n">
         <v>-109</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>-57</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -602,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC10"/>
+  <dimension ref="A1:BD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -660,6 +660,7 @@
     <col width="10" customWidth="1" min="53" max="53"/>
     <col width="10" customWidth="1" min="54" max="54"/>
     <col width="10" customWidth="1" min="55" max="55"/>
+    <col width="10" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,6 +833,9 @@
       <c r="BC1" s="1" t="n">
         <v>20260209</v>
       </c>
+      <c r="BD1" s="1" t="n">
+        <v>20260210</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1003,6 +1007,9 @@
       <c r="BC2" t="n">
         <v>47</v>
       </c>
+      <c r="BD2" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1174,6 +1181,9 @@
       <c r="BC3" t="n">
         <v>-144</v>
       </c>
+      <c r="BD3" t="n">
+        <v>-142</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1345,6 +1355,9 @@
       <c r="BC4" t="n">
         <v>18</v>
       </c>
+      <c r="BD4" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1516,6 +1529,9 @@
       <c r="BC5" t="n">
         <v>-137</v>
       </c>
+      <c r="BD5" t="n">
+        <v>-107</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1687,6 +1703,9 @@
       <c r="BC6" t="n">
         <v>-14</v>
       </c>
+      <c r="BD6" t="n">
+        <v>-12</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1858,6 +1877,9 @@
       <c r="BC7" t="n">
         <v>15</v>
       </c>
+      <c r="BD7" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2029,6 +2051,9 @@
       <c r="BC8" t="n">
         <v>-121</v>
       </c>
+      <c r="BD8" t="n">
+        <v>-92</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2200,6 +2225,9 @@
       <c r="BC9" t="n">
         <v>116</v>
       </c>
+      <c r="BD9" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2370,6 +2398,9 @@
       </c>
       <c r="BC10" t="n">
         <v>-54</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-41</v>
       </c>
     </row>
   </sheetData>
@@ -2383,7 +2414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CQ10"/>
+  <dimension ref="A1:CR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2481,6 +2512,7 @@
     <col width="12" customWidth="1" min="93" max="93"/>
     <col width="12" customWidth="1" min="94" max="94"/>
     <col width="12" customWidth="1" min="95" max="95"/>
+    <col width="12" customWidth="1" min="96" max="96"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2959,6 +2991,11 @@
           <t>20260209</t>
         </is>
       </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>20260210</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3250,6 +3287,9 @@
       <c r="CQ2" t="n">
         <v>107</v>
       </c>
+      <c r="CR2" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3541,6 +3581,9 @@
       <c r="CQ3" t="n">
         <v>89</v>
       </c>
+      <c r="CR3" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3832,6 +3875,9 @@
       <c r="CQ4" t="n">
         <v>97</v>
       </c>
+      <c r="CR4" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4123,6 +4169,9 @@
       <c r="CQ5" t="n">
         <v>90</v>
       </c>
+      <c r="CR5" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4414,6 +4463,9 @@
       <c r="CQ6" t="n">
         <v>97</v>
       </c>
+      <c r="CR6" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4705,6 +4757,9 @@
       <c r="CQ7" t="n">
         <v>101</v>
       </c>
+      <c r="CR7" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4996,6 +5051,9 @@
       <c r="CQ8" t="n">
         <v>85</v>
       </c>
+      <c r="CR8" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5287,6 +5345,9 @@
       <c r="CQ9" t="n">
         <v>105</v>
       </c>
+      <c r="CR9" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5577,6 +5638,9 @@
       </c>
       <c r="CQ10" t="n">
         <v>96</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -5590,7 +5654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX10"/>
+  <dimension ref="A1:BY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5669,6 +5733,7 @@
     <col width="12" customWidth="1" min="74" max="74"/>
     <col width="12" customWidth="1" min="75" max="75"/>
     <col width="12" customWidth="1" min="76" max="76"/>
+    <col width="12" customWidth="1" min="77" max="77"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6052,6 +6117,11 @@
           <t>20260209</t>
         </is>
       </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>20260210</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6286,6 +6356,9 @@
       <c r="BX2" t="n">
         <v>31.64</v>
       </c>
+      <c r="BY2" t="n">
+        <v>34.11</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6520,6 +6593,9 @@
       <c r="BX3" t="n">
         <v>25.67</v>
       </c>
+      <c r="BY3" t="n">
+        <v>49.41</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6754,6 +6830,9 @@
       <c r="BX4" t="n">
         <v>-38.81</v>
       </c>
+      <c r="BY4" t="n">
+        <v>-32.98</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6988,6 +7067,9 @@
       <c r="BX5" t="n">
         <v>85.26000000000001</v>
       </c>
+      <c r="BY5" t="n">
+        <v>70.93000000000001</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7222,6 +7304,9 @@
       <c r="BX6" t="n">
         <v>15.96</v>
       </c>
+      <c r="BY6" t="n">
+        <v>9.539999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7456,6 +7541,9 @@
       <c r="BX7" t="n">
         <v>43.97</v>
       </c>
+      <c r="BY7" t="n">
+        <v>47.11</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7690,6 +7778,9 @@
       <c r="BX8" t="n">
         <v>67.83</v>
       </c>
+      <c r="BY8" t="n">
+        <v>57.76</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7924,6 +8015,9 @@
       <c r="BX9" t="n">
         <v>-24.26</v>
       </c>
+      <c r="BY9" t="n">
+        <v>-25.91</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8157,6 +8251,9 @@
       </c>
       <c r="BX10" t="n">
         <v>3.76</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>1.88</v>
       </c>
     </row>
   </sheetData>
@@ -8170,7 +8267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC10"/>
+  <dimension ref="A1:BD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8228,6 +8325,7 @@
     <col width="12" customWidth="1" min="53" max="53"/>
     <col width="12" customWidth="1" min="54" max="54"/>
     <col width="12" customWidth="1" min="55" max="55"/>
+    <col width="12" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8506,6 +8604,11 @@
           <t>20260209</t>
         </is>
       </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>20260210</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8677,6 +8780,9 @@
       <c r="BC2" t="n">
         <v>0</v>
       </c>
+      <c r="BD2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8848,6 +8954,9 @@
       <c r="BC3" t="n">
         <v>0</v>
       </c>
+      <c r="BD3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9019,6 +9128,9 @@
       <c r="BC4" t="n">
         <v>0</v>
       </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9190,6 +9302,9 @@
       <c r="BC5" t="n">
         <v>0</v>
       </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9361,6 +9476,9 @@
       <c r="BC6" t="n">
         <v>0</v>
       </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9532,6 +9650,9 @@
       <c r="BC7" t="n">
         <v>0</v>
       </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9703,6 +9824,9 @@
       <c r="BC8" t="n">
         <v>0</v>
       </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9874,6 +9998,9 @@
       <c r="BC9" t="n">
         <v>0</v>
       </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10043,6 +10170,9 @@
         <v>0</v>
       </c>
       <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10057,7 +10187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG10"/>
+  <dimension ref="A1:CH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10145,6 +10275,7 @@
     <col width="10" customWidth="1" min="83" max="83"/>
     <col width="10" customWidth="1" min="84" max="84"/>
     <col width="10" customWidth="1" min="85" max="85"/>
+    <col width="10" customWidth="1" min="86" max="86"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10407,6 +10538,9 @@
       <c r="CG1" s="1" t="n">
         <v>20260209</v>
       </c>
+      <c r="CH1" s="1" t="n">
+        <v>20260210</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10668,6 +10802,9 @@
       <c r="CG2" t="n">
         <v>81</v>
       </c>
+      <c r="CH2" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10929,6 +11066,9 @@
       <c r="CG3" t="n">
         <v>-163</v>
       </c>
+      <c r="CH3" t="n">
+        <v>-142</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11190,6 +11330,9 @@
       <c r="CG4" t="n">
         <v>-27</v>
       </c>
+      <c r="CH4" t="n">
+        <v>-22</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11451,6 +11594,9 @@
       <c r="CG5" t="n">
         <v>-99</v>
       </c>
+      <c r="CH5" t="n">
+        <v>-71</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11712,6 +11858,9 @@
       <c r="CG6" t="n">
         <v>-56</v>
       </c>
+      <c r="CH6" t="n">
+        <v>-61</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11973,6 +12122,9 @@
       <c r="CG7" t="n">
         <v>-2</v>
       </c>
+      <c r="CH7" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12234,6 +12386,9 @@
       <c r="CG8" t="n">
         <v>-95</v>
       </c>
+      <c r="CH8" t="n">
+        <v>-68</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12495,6 +12650,9 @@
       <c r="CG9" t="n">
         <v>84</v>
       </c>
+      <c r="CH9" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12755,6 +12913,9 @@
       </c>
       <c r="CG10" t="n">
         <v>-70</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>-50</v>
       </c>
     </row>
   </sheetData>
@@ -12768,7 +12929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DJ10"/>
+  <dimension ref="A1:DK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12885,6 +13046,7 @@
     <col width="12" customWidth="1" min="112" max="112"/>
     <col width="12" customWidth="1" min="113" max="113"/>
     <col width="12" customWidth="1" min="114" max="114"/>
+    <col width="12" customWidth="1" min="115" max="115"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13234,6 +13396,9 @@
       <c r="DJ1" s="1" t="n">
         <v>20260209</v>
       </c>
+      <c r="DK1" s="1" t="n">
+        <v>20260210</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13582,6 +13747,9 @@
       <c r="DJ2" t="n">
         <v>278.12</v>
       </c>
+      <c r="DK2" t="n">
+        <v>274.62</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13930,6 +14098,9 @@
       <c r="DJ3" t="n">
         <v>210.32</v>
       </c>
+      <c r="DK3" t="n">
+        <v>208.72</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14278,6 +14449,9 @@
       <c r="DJ4" t="n">
         <v>322.86</v>
       </c>
+      <c r="DK4" t="n">
+        <v>324.32</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14626,6 +14800,9 @@
       <c r="DJ5" t="n">
         <v>401.14</v>
       </c>
+      <c r="DK5" t="n">
+        <v>413.6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14974,6 +15151,9 @@
       <c r="DJ6" t="n">
         <v>82.2</v>
       </c>
+      <c r="DK6" t="n">
+        <v>81.47</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15322,6 +15502,9 @@
       <c r="DJ7" t="n">
         <v>185.41</v>
       </c>
+      <c r="DK7" t="n">
+        <v>190.04</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15670,6 +15853,9 @@
       <c r="DJ8" t="n">
         <v>135.9</v>
       </c>
+      <c r="DK8" t="n">
+        <v>142.91</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16018,6 +16204,9 @@
       <c r="DJ9" t="n">
         <v>99.45</v>
       </c>
+      <c r="DK9" t="n">
+        <v>98.98</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16365,6 +16554,9 @@
       </c>
       <c r="DJ10" t="n">
         <v>411.11</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>417.32</v>
       </c>
     </row>
   </sheetData>
@@ -16378,7 +16570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DJ10"/>
+  <dimension ref="A1:DK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -16495,6 +16687,7 @@
     <col width="12" customWidth="1" min="112" max="112"/>
     <col width="12" customWidth="1" min="113" max="113"/>
     <col width="12" customWidth="1" min="114" max="114"/>
+    <col width="12" customWidth="1" min="115" max="115"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16844,6 +17037,9 @@
       <c r="DJ1" s="1" t="n">
         <v>20260209</v>
       </c>
+      <c r="DK1" s="1" t="n">
+        <v>20260210</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17192,6 +17388,9 @@
       <c r="DJ2" t="n">
         <v>278.12</v>
       </c>
+      <c r="DK2" t="n">
+        <v>274.62</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17540,6 +17739,9 @@
       <c r="DJ3" t="n">
         <v>210.32</v>
       </c>
+      <c r="DK3" t="n">
+        <v>208.72</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17888,6 +18090,9 @@
       <c r="DJ4" t="n">
         <v>322.86</v>
       </c>
+      <c r="DK4" t="n">
+        <v>324.32</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18236,6 +18441,9 @@
       <c r="DJ5" t="n">
         <v>401.14</v>
       </c>
+      <c r="DK5" t="n">
+        <v>413.6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18584,6 +18792,9 @@
       <c r="DJ6" t="n">
         <v>82.2</v>
       </c>
+      <c r="DK6" t="n">
+        <v>81.47</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18932,6 +19143,9 @@
       <c r="DJ7" t="n">
         <v>185.41</v>
       </c>
+      <c r="DK7" t="n">
+        <v>190.04</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19280,6 +19494,9 @@
       <c r="DJ8" t="n">
         <v>135.9</v>
       </c>
+      <c r="DK8" t="n">
+        <v>142.91</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19628,6 +19845,9 @@
       <c r="DJ9" t="n">
         <v>99.45</v>
       </c>
+      <c r="DK9" t="n">
+        <v>98.98</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -19975,6 +20195,9 @@
       </c>
       <c r="DJ10" t="n">
         <v>411.11</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>417.32</v>
       </c>
     </row>
   </sheetData>
@@ -19988,7 +20211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DJ10"/>
+  <dimension ref="A1:DK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20105,6 +20328,7 @@
     <col width="12" customWidth="1" min="112" max="112"/>
     <col width="12" customWidth="1" min="113" max="113"/>
     <col width="12" customWidth="1" min="114" max="114"/>
+    <col width="12" customWidth="1" min="115" max="115"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20454,6 +20678,9 @@
       <c r="DJ1" s="1" t="n">
         <v>20260209</v>
       </c>
+      <c r="DK1" s="1" t="n">
+        <v>20260210</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20802,6 +21029,9 @@
       <c r="DJ2" t="n">
         <v>278.12</v>
       </c>
+      <c r="DK2" t="n">
+        <v>274.62</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21150,6 +21380,9 @@
       <c r="DJ3" t="n">
         <v>210.32</v>
       </c>
+      <c r="DK3" t="n">
+        <v>208.72</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -21498,6 +21731,9 @@
       <c r="DJ4" t="n">
         <v>322.86</v>
       </c>
+      <c r="DK4" t="n">
+        <v>324.32</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -21846,6 +22082,9 @@
       <c r="DJ5" t="n">
         <v>401.14</v>
       </c>
+      <c r="DK5" t="n">
+        <v>413.6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -22194,6 +22433,9 @@
       <c r="DJ6" t="n">
         <v>82.2</v>
       </c>
+      <c r="DK6" t="n">
+        <v>81.47</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -22542,6 +22784,9 @@
       <c r="DJ7" t="n">
         <v>185.41</v>
       </c>
+      <c r="DK7" t="n">
+        <v>190.04</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22890,6 +23135,9 @@
       <c r="DJ8" t="n">
         <v>135.9</v>
       </c>
+      <c r="DK8" t="n">
+        <v>142.91</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23238,6 +23486,9 @@
       <c r="DJ9" t="n">
         <v>99.45</v>
       </c>
+      <c r="DK9" t="n">
+        <v>98.98</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23585,6 +23836,9 @@
       </c>
       <c r="DJ10" t="n">
         <v>411.11</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>417.32</v>
       </c>
     </row>
   </sheetData>
@@ -23598,7 +23852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DJ10"/>
+  <dimension ref="A1:DK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23715,6 +23969,7 @@
     <col width="12" customWidth="1" min="112" max="112"/>
     <col width="12" customWidth="1" min="113" max="113"/>
     <col width="12" customWidth="1" min="114" max="114"/>
+    <col width="12" customWidth="1" min="115" max="115"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24064,6 +24319,9 @@
       <c r="DJ1" s="1" t="n">
         <v>20260209</v>
       </c>
+      <c r="DK1" s="1" t="n">
+        <v>20260210</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24412,6 +24670,9 @@
       <c r="DJ2" t="n">
         <v>278.12</v>
       </c>
+      <c r="DK2" t="n">
+        <v>274.62</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -24760,6 +25021,9 @@
       <c r="DJ3" t="n">
         <v>210.32</v>
       </c>
+      <c r="DK3" t="n">
+        <v>208.72</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -25108,6 +25372,9 @@
       <c r="DJ4" t="n">
         <v>322.86</v>
       </c>
+      <c r="DK4" t="n">
+        <v>324.32</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -25456,6 +25723,9 @@
       <c r="DJ5" t="n">
         <v>401.14</v>
       </c>
+      <c r="DK5" t="n">
+        <v>413.6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -25804,6 +26074,9 @@
       <c r="DJ6" t="n">
         <v>82.2</v>
       </c>
+      <c r="DK6" t="n">
+        <v>81.47</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -26152,6 +26425,9 @@
       <c r="DJ7" t="n">
         <v>185.41</v>
       </c>
+      <c r="DK7" t="n">
+        <v>190.04</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -26500,6 +26776,9 @@
       <c r="DJ8" t="n">
         <v>135.9</v>
       </c>
+      <c r="DK8" t="n">
+        <v>142.91</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -26848,6 +27127,9 @@
       <c r="DJ9" t="n">
         <v>99.45</v>
       </c>
+      <c r="DK9" t="n">
+        <v>98.98</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27195,6 +27477,9 @@
       </c>
       <c r="DJ10" t="n">
         <v>411.11</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>417.32</v>
       </c>
     </row>
   </sheetData>
@@ -27208,7 +27493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DJ10"/>
+  <dimension ref="A1:DK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -27325,6 +27610,7 @@
     <col width="12" customWidth="1" min="112" max="112"/>
     <col width="12" customWidth="1" min="113" max="113"/>
     <col width="12" customWidth="1" min="114" max="114"/>
+    <col width="12" customWidth="1" min="115" max="115"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27674,6 +27960,9 @@
       <c r="DJ1" s="1" t="n">
         <v>20260209</v>
       </c>
+      <c r="DK1" s="1" t="n">
+        <v>20260210</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -28022,6 +28311,9 @@
       <c r="DJ2" t="n">
         <v>0</v>
       </c>
+      <c r="DK2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -28370,6 +28662,9 @@
       <c r="DJ3" t="n">
         <v>0</v>
       </c>
+      <c r="DK3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -28718,6 +29013,9 @@
       <c r="DJ4" t="n">
         <v>0</v>
       </c>
+      <c r="DK4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -29066,6 +29364,9 @@
       <c r="DJ5" t="n">
         <v>0</v>
       </c>
+      <c r="DK5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -29414,6 +29715,9 @@
       <c r="DJ6" t="n">
         <v>0</v>
       </c>
+      <c r="DK6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -29762,6 +30066,9 @@
       <c r="DJ7" t="n">
         <v>0</v>
       </c>
+      <c r="DK7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -30110,6 +30417,9 @@
       <c r="DJ8" t="n">
         <v>0</v>
       </c>
+      <c r="DK8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -30458,6 +30768,9 @@
       <c r="DJ9" t="n">
         <v>0</v>
       </c>
+      <c r="DK9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -30804,6 +31117,9 @@
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -30818,7 +31134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CQ10"/>
+  <dimension ref="A1:CR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -30916,6 +31232,7 @@
     <col width="10" customWidth="1" min="93" max="93"/>
     <col width="10" customWidth="1" min="94" max="94"/>
     <col width="10" customWidth="1" min="95" max="95"/>
+    <col width="10" customWidth="1" min="96" max="96"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31208,6 +31525,9 @@
       <c r="CQ1" s="1" t="n">
         <v>20260209</v>
       </c>
+      <c r="CR1" s="1" t="n">
+        <v>20260210</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -31499,6 +31819,9 @@
       <c r="CQ2" t="n">
         <v>100</v>
       </c>
+      <c r="CR2" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -31790,6 +32113,9 @@
       <c r="CQ3" t="n">
         <v>0</v>
       </c>
+      <c r="CR3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -32081,6 +32407,9 @@
       <c r="CQ4" t="n">
         <v>5</v>
       </c>
+      <c r="CR4" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -32372,6 +32701,9 @@
       <c r="CQ5" t="n">
         <v>8</v>
       </c>
+      <c r="CR5" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -32663,6 +32995,9 @@
       <c r="CQ6" t="n">
         <v>22</v>
       </c>
+      <c r="CR6" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -32954,6 +33289,9 @@
       <c r="CQ7" t="n">
         <v>66</v>
       </c>
+      <c r="CR7" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -33245,6 +33583,9 @@
       <c r="CQ8" t="n">
         <v>12</v>
       </c>
+      <c r="CR8" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -33536,6 +33877,9 @@
       <c r="CQ9" t="n">
         <v>100</v>
       </c>
+      <c r="CR9" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -33826,6 +34170,9 @@
       </c>
       <c r="CQ10" t="n">
         <v>27</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -33839,7 +34186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC10"/>
+  <dimension ref="A1:BD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -33897,6 +34244,7 @@
     <col width="10" customWidth="1" min="53" max="53"/>
     <col width="10" customWidth="1" min="54" max="54"/>
     <col width="10" customWidth="1" min="55" max="55"/>
+    <col width="10" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -34069,6 +34417,9 @@
       <c r="BC1" s="1" t="n">
         <v>20260209</v>
       </c>
+      <c r="BD1" s="1" t="n">
+        <v>20260210</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -34240,6 +34591,9 @@
       <c r="BC2" t="n">
         <v>80</v>
       </c>
+      <c r="BD2" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -34411,6 +34765,9 @@
       <c r="BC3" t="n">
         <v>0</v>
       </c>
+      <c r="BD3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -34582,6 +34939,9 @@
       <c r="BC4" t="n">
         <v>73</v>
       </c>
+      <c r="BD4" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -34753,6 +35113,9 @@
       <c r="BC5" t="n">
         <v>6</v>
       </c>
+      <c r="BD5" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -34924,6 +35287,9 @@
       <c r="BC6" t="n">
         <v>0</v>
       </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -35095,6 +35461,9 @@
       <c r="BC7" t="n">
         <v>63</v>
       </c>
+      <c r="BD7" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -35266,6 +35635,9 @@
       <c r="BC8" t="n">
         <v>9</v>
       </c>
+      <c r="BD8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -35437,6 +35809,9 @@
       <c r="BC9" t="n">
         <v>100</v>
       </c>
+      <c r="BD9" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -35607,6 +35982,9 @@
       </c>
       <c r="BC10" t="n">
         <v>20</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -35620,7 +35998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CQ10"/>
+  <dimension ref="A1:CR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -35718,6 +36096,7 @@
     <col width="10" customWidth="1" min="93" max="93"/>
     <col width="10" customWidth="1" min="94" max="94"/>
     <col width="10" customWidth="1" min="95" max="95"/>
+    <col width="10" customWidth="1" min="96" max="96"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -36010,6 +36389,9 @@
       <c r="CQ1" s="1" t="n">
         <v>20260209</v>
       </c>
+      <c r="CR1" s="1" t="n">
+        <v>20260210</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -36301,6 +36683,9 @@
       <c r="CQ2" t="n">
         <v>89</v>
       </c>
+      <c r="CR2" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -36592,6 +36977,9 @@
       <c r="CQ3" t="n">
         <v>-158</v>
       </c>
+      <c r="CR3" t="n">
+        <v>-129</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -36883,6 +37271,9 @@
       <c r="CQ4" t="n">
         <v>-102</v>
       </c>
+      <c r="CR4" t="n">
+        <v>-77</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -37174,6 +37565,9 @@
       <c r="CQ5" t="n">
         <v>-80</v>
       </c>
+      <c r="CR5" t="n">
+        <v>-52</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -37465,6 +37859,9 @@
       <c r="CQ6" t="n">
         <v>-41</v>
       </c>
+      <c r="CR6" t="n">
+        <v>-48</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -37756,6 +38153,9 @@
       <c r="CQ7" t="n">
         <v>8</v>
       </c>
+      <c r="CR7" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -38047,6 +38447,9 @@
       <c r="CQ8" t="n">
         <v>-77</v>
       </c>
+      <c r="CR8" t="n">
+        <v>-49</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -38338,6 +38741,9 @@
       <c r="CQ9" t="n">
         <v>97</v>
       </c>
+      <c r="CR9" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -38628,6 +39034,9 @@
       </c>
       <c r="CQ10" t="n">
         <v>-57</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>-33</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -602,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD10"/>
+  <dimension ref="A1:BE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -661,6 +661,7 @@
     <col width="10" customWidth="1" min="54" max="54"/>
     <col width="10" customWidth="1" min="55" max="55"/>
     <col width="10" customWidth="1" min="56" max="56"/>
+    <col width="10" customWidth="1" min="57" max="57"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -836,6 +837,9 @@
       <c r="BD1" s="1" t="n">
         <v>20260210</v>
       </c>
+      <c r="BE1" s="1" t="n">
+        <v>20260211</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1010,6 +1014,9 @@
       <c r="BD2" t="n">
         <v>29</v>
       </c>
+      <c r="BE2" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1184,6 +1191,9 @@
       <c r="BD3" t="n">
         <v>-142</v>
       </c>
+      <c r="BE3" t="n">
+        <v>-140</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1358,6 +1368,9 @@
       <c r="BD4" t="n">
         <v>22</v>
       </c>
+      <c r="BE4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1532,6 +1545,9 @@
       <c r="BD5" t="n">
         <v>-107</v>
       </c>
+      <c r="BE5" t="n">
+        <v>-103</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1706,6 +1722,9 @@
       <c r="BD6" t="n">
         <v>-12</v>
       </c>
+      <c r="BE6" t="n">
+        <v>-11</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1880,6 +1899,9 @@
       <c r="BD7" t="n">
         <v>59</v>
       </c>
+      <c r="BE7" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2054,6 +2076,9 @@
       <c r="BD8" t="n">
         <v>-92</v>
       </c>
+      <c r="BE8" t="n">
+        <v>-98</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2228,6 +2253,9 @@
       <c r="BD9" t="n">
         <v>105</v>
       </c>
+      <c r="BE9" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2401,6 +2429,9 @@
       </c>
       <c r="BD10" t="n">
         <v>-41</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>-27</v>
       </c>
     </row>
   </sheetData>
@@ -2414,7 +2445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR10"/>
+  <dimension ref="A1:CS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2513,6 +2544,7 @@
     <col width="12" customWidth="1" min="94" max="94"/>
     <col width="12" customWidth="1" min="95" max="95"/>
     <col width="12" customWidth="1" min="96" max="96"/>
+    <col width="12" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2996,6 +3028,11 @@
           <t>20260210</t>
         </is>
       </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>20260211</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3290,6 +3327,9 @@
       <c r="CR2" t="n">
         <v>105</v>
       </c>
+      <c r="CS2" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3584,6 +3624,9 @@
       <c r="CR3" t="n">
         <v>89</v>
       </c>
+      <c r="CS3" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3878,6 +3921,9 @@
       <c r="CR4" t="n">
         <v>98</v>
       </c>
+      <c r="CS4" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4172,6 +4218,9 @@
       <c r="CR5" t="n">
         <v>94</v>
       </c>
+      <c r="CS5" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4466,6 +4515,9 @@
       <c r="CR6" t="n">
         <v>97</v>
       </c>
+      <c r="CS6" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4760,6 +4812,9 @@
       <c r="CR7" t="n">
         <v>103</v>
       </c>
+      <c r="CS7" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5054,6 +5109,9 @@
       <c r="CR8" t="n">
         <v>91</v>
       </c>
+      <c r="CS8" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5348,6 +5406,9 @@
       <c r="CR9" t="n">
         <v>104</v>
       </c>
+      <c r="CS9" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5641,6 +5702,9 @@
       </c>
       <c r="CR10" t="n">
         <v>98</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -5654,7 +5718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY10"/>
+  <dimension ref="A1:BZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5734,6 +5798,7 @@
     <col width="12" customWidth="1" min="75" max="75"/>
     <col width="12" customWidth="1" min="76" max="76"/>
     <col width="12" customWidth="1" min="77" max="77"/>
+    <col width="12" customWidth="1" min="78" max="78"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6122,6 +6187,11 @@
           <t>20260210</t>
         </is>
       </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>20260211</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6359,6 +6429,9 @@
       <c r="BY2" t="n">
         <v>34.11</v>
       </c>
+      <c r="BZ2" t="n">
+        <v>34.56</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6596,6 +6669,9 @@
       <c r="BY3" t="n">
         <v>49.41</v>
       </c>
+      <c r="BZ3" t="n">
+        <v>68.5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6833,6 +6909,9 @@
       <c r="BY4" t="n">
         <v>-32.98</v>
       </c>
+      <c r="BZ4" t="n">
+        <v>-21.22</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7070,6 +7149,9 @@
       <c r="BY5" t="n">
         <v>70.93000000000001</v>
       </c>
+      <c r="BZ5" t="n">
+        <v>59.16</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7307,6 +7389,9 @@
       <c r="BY6" t="n">
         <v>9.539999999999999</v>
       </c>
+      <c r="BZ6" t="n">
+        <v>-2.75</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7544,6 +7629,9 @@
       <c r="BY7" t="n">
         <v>47.11</v>
       </c>
+      <c r="BZ7" t="n">
+        <v>47.69</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7781,6 +7869,9 @@
       <c r="BY8" t="n">
         <v>57.76</v>
       </c>
+      <c r="BZ8" t="n">
+        <v>48.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8018,6 +8109,9 @@
       <c r="BY9" t="n">
         <v>-25.91</v>
       </c>
+      <c r="BZ9" t="n">
+        <v>-30.51</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8254,6 +8348,9 @@
       </c>
       <c r="BY10" t="n">
         <v>1.88</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>-1.1</v>
       </c>
     </row>
   </sheetData>
@@ -8267,7 +8364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD10"/>
+  <dimension ref="A1:BE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8326,6 +8423,7 @@
     <col width="12" customWidth="1" min="54" max="54"/>
     <col width="12" customWidth="1" min="55" max="55"/>
     <col width="12" customWidth="1" min="56" max="56"/>
+    <col width="12" customWidth="1" min="57" max="57"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8609,6 +8707,11 @@
           <t>20260210</t>
         </is>
       </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>20260211</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8783,6 +8886,9 @@
       <c r="BD2" t="n">
         <v>0</v>
       </c>
+      <c r="BE2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8957,6 +9063,9 @@
       <c r="BD3" t="n">
         <v>0</v>
       </c>
+      <c r="BE3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9131,6 +9240,9 @@
       <c r="BD4" t="n">
         <v>0</v>
       </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9305,6 +9417,9 @@
       <c r="BD5" t="n">
         <v>0</v>
       </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9479,6 +9594,9 @@
       <c r="BD6" t="n">
         <v>0</v>
       </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9653,6 +9771,9 @@
       <c r="BD7" t="n">
         <v>0</v>
       </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9827,6 +9948,9 @@
       <c r="BD8" t="n">
         <v>0</v>
       </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10001,6 +10125,9 @@
       <c r="BD9" t="n">
         <v>0</v>
       </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10173,6 +10300,9 @@
         <v>0</v>
       </c>
       <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10187,7 +10317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CH10"/>
+  <dimension ref="A1:CI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10276,6 +10406,7 @@
     <col width="10" customWidth="1" min="84" max="84"/>
     <col width="10" customWidth="1" min="85" max="85"/>
     <col width="10" customWidth="1" min="86" max="86"/>
+    <col width="10" customWidth="1" min="87" max="87"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10541,6 +10672,9 @@
       <c r="CH1" s="1" t="n">
         <v>20260210</v>
       </c>
+      <c r="CI1" s="1" t="n">
+        <v>20260211</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10805,6 +10939,9 @@
       <c r="CH2" t="n">
         <v>62</v>
       </c>
+      <c r="CI2" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11069,6 +11206,9 @@
       <c r="CH3" t="n">
         <v>-142</v>
       </c>
+      <c r="CI3" t="n">
+        <v>-129</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11333,6 +11473,9 @@
       <c r="CH4" t="n">
         <v>-22</v>
       </c>
+      <c r="CI4" t="n">
+        <v>-59</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11597,6 +11740,9 @@
       <c r="CH5" t="n">
         <v>-71</v>
       </c>
+      <c r="CI5" t="n">
+        <v>-67</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11861,6 +12007,9 @@
       <c r="CH6" t="n">
         <v>-61</v>
       </c>
+      <c r="CI6" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12125,6 +12274,9 @@
       <c r="CH7" t="n">
         <v>43</v>
       </c>
+      <c r="CI7" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12389,6 +12541,9 @@
       <c r="CH8" t="n">
         <v>-68</v>
       </c>
+      <c r="CI8" t="n">
+        <v>-73</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12653,6 +12808,9 @@
       <c r="CH9" t="n">
         <v>73</v>
       </c>
+      <c r="CI9" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12916,6 +13074,9 @@
       </c>
       <c r="CH10" t="n">
         <v>-50</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>-22</v>
       </c>
     </row>
   </sheetData>
@@ -12929,7 +13090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DK10"/>
+  <dimension ref="A1:DL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13047,6 +13208,7 @@
     <col width="12" customWidth="1" min="113" max="113"/>
     <col width="12" customWidth="1" min="114" max="114"/>
     <col width="12" customWidth="1" min="115" max="115"/>
+    <col width="12" customWidth="1" min="116" max="116"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13399,6 +13561,9 @@
       <c r="DK1" s="1" t="n">
         <v>20260210</v>
       </c>
+      <c r="DL1" s="1" t="n">
+        <v>20260211</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13750,6 +13915,9 @@
       <c r="DK2" t="n">
         <v>274.62</v>
       </c>
+      <c r="DL2" t="n">
+        <v>273.68</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14101,6 +14269,9 @@
       <c r="DK3" t="n">
         <v>208.72</v>
       </c>
+      <c r="DL3" t="n">
+        <v>206.96</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14452,6 +14623,9 @@
       <c r="DK4" t="n">
         <v>324.32</v>
       </c>
+      <c r="DL4" t="n">
+        <v>318.58</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14803,6 +14977,9 @@
       <c r="DK5" t="n">
         <v>413.6</v>
       </c>
+      <c r="DL5" t="n">
+        <v>413.27</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15154,6 +15331,9 @@
       <c r="DK6" t="n">
         <v>81.47</v>
       </c>
+      <c r="DL6" t="n">
+        <v>82.20999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15505,6 +15685,9 @@
       <c r="DK7" t="n">
         <v>190.04</v>
       </c>
+      <c r="DL7" t="n">
+        <v>188.54</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15856,6 +16039,9 @@
       <c r="DK8" t="n">
         <v>142.91</v>
       </c>
+      <c r="DL8" t="n">
+        <v>139.51</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16207,6 +16393,9 @@
       <c r="DK9" t="n">
         <v>98.98</v>
       </c>
+      <c r="DL9" t="n">
+        <v>97.53</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16557,6 +16746,9 @@
       </c>
       <c r="DK10" t="n">
         <v>417.32</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>425.21</v>
       </c>
     </row>
   </sheetData>
@@ -16570,7 +16762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DK10"/>
+  <dimension ref="A1:DL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -16688,6 +16880,7 @@
     <col width="12" customWidth="1" min="113" max="113"/>
     <col width="12" customWidth="1" min="114" max="114"/>
     <col width="12" customWidth="1" min="115" max="115"/>
+    <col width="12" customWidth="1" min="116" max="116"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17040,6 +17233,9 @@
       <c r="DK1" s="1" t="n">
         <v>20260210</v>
       </c>
+      <c r="DL1" s="1" t="n">
+        <v>20260211</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17391,6 +17587,9 @@
       <c r="DK2" t="n">
         <v>274.62</v>
       </c>
+      <c r="DL2" t="n">
+        <v>273.68</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17742,6 +17941,9 @@
       <c r="DK3" t="n">
         <v>208.72</v>
       </c>
+      <c r="DL3" t="n">
+        <v>206.96</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18093,6 +18295,9 @@
       <c r="DK4" t="n">
         <v>324.32</v>
       </c>
+      <c r="DL4" t="n">
+        <v>318.58</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18444,6 +18649,9 @@
       <c r="DK5" t="n">
         <v>413.6</v>
       </c>
+      <c r="DL5" t="n">
+        <v>413.27</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18795,6 +19003,9 @@
       <c r="DK6" t="n">
         <v>81.47</v>
       </c>
+      <c r="DL6" t="n">
+        <v>82.20999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19146,6 +19357,9 @@
       <c r="DK7" t="n">
         <v>190.04</v>
       </c>
+      <c r="DL7" t="n">
+        <v>188.54</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19497,6 +19711,9 @@
       <c r="DK8" t="n">
         <v>142.91</v>
       </c>
+      <c r="DL8" t="n">
+        <v>139.51</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19848,6 +20065,9 @@
       <c r="DK9" t="n">
         <v>98.98</v>
       </c>
+      <c r="DL9" t="n">
+        <v>97.53</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20198,6 +20418,9 @@
       </c>
       <c r="DK10" t="n">
         <v>417.32</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>425.21</v>
       </c>
     </row>
   </sheetData>
@@ -20211,7 +20434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DK10"/>
+  <dimension ref="A1:DL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20329,6 +20552,7 @@
     <col width="12" customWidth="1" min="113" max="113"/>
     <col width="12" customWidth="1" min="114" max="114"/>
     <col width="12" customWidth="1" min="115" max="115"/>
+    <col width="12" customWidth="1" min="116" max="116"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20681,6 +20905,9 @@
       <c r="DK1" s="1" t="n">
         <v>20260210</v>
       </c>
+      <c r="DL1" s="1" t="n">
+        <v>20260211</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21032,6 +21259,9 @@
       <c r="DK2" t="n">
         <v>274.62</v>
       </c>
+      <c r="DL2" t="n">
+        <v>273.68</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21383,6 +21613,9 @@
       <c r="DK3" t="n">
         <v>208.72</v>
       </c>
+      <c r="DL3" t="n">
+        <v>206.96</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -21734,6 +21967,9 @@
       <c r="DK4" t="n">
         <v>324.32</v>
       </c>
+      <c r="DL4" t="n">
+        <v>318.58</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -22085,6 +22321,9 @@
       <c r="DK5" t="n">
         <v>413.6</v>
       </c>
+      <c r="DL5" t="n">
+        <v>413.27</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -22436,6 +22675,9 @@
       <c r="DK6" t="n">
         <v>81.47</v>
       </c>
+      <c r="DL6" t="n">
+        <v>82.20999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -22787,6 +23029,9 @@
       <c r="DK7" t="n">
         <v>190.04</v>
       </c>
+      <c r="DL7" t="n">
+        <v>188.54</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23138,6 +23383,9 @@
       <c r="DK8" t="n">
         <v>142.91</v>
       </c>
+      <c r="DL8" t="n">
+        <v>139.51</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23489,6 +23737,9 @@
       <c r="DK9" t="n">
         <v>98.98</v>
       </c>
+      <c r="DL9" t="n">
+        <v>97.53</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23839,6 +24090,9 @@
       </c>
       <c r="DK10" t="n">
         <v>417.32</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>425.21</v>
       </c>
     </row>
   </sheetData>
@@ -23852,7 +24106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DK10"/>
+  <dimension ref="A1:DL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23970,6 +24224,7 @@
     <col width="12" customWidth="1" min="113" max="113"/>
     <col width="12" customWidth="1" min="114" max="114"/>
     <col width="12" customWidth="1" min="115" max="115"/>
+    <col width="12" customWidth="1" min="116" max="116"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24322,6 +24577,9 @@
       <c r="DK1" s="1" t="n">
         <v>20260210</v>
       </c>
+      <c r="DL1" s="1" t="n">
+        <v>20260211</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24673,6 +24931,9 @@
       <c r="DK2" t="n">
         <v>274.62</v>
       </c>
+      <c r="DL2" t="n">
+        <v>273.68</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25024,6 +25285,9 @@
       <c r="DK3" t="n">
         <v>208.72</v>
       </c>
+      <c r="DL3" t="n">
+        <v>206.96</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -25375,6 +25639,9 @@
       <c r="DK4" t="n">
         <v>324.32</v>
       </c>
+      <c r="DL4" t="n">
+        <v>318.58</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -25726,6 +25993,9 @@
       <c r="DK5" t="n">
         <v>413.6</v>
       </c>
+      <c r="DL5" t="n">
+        <v>413.27</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -26077,6 +26347,9 @@
       <c r="DK6" t="n">
         <v>81.47</v>
       </c>
+      <c r="DL6" t="n">
+        <v>82.20999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -26428,6 +26701,9 @@
       <c r="DK7" t="n">
         <v>190.04</v>
       </c>
+      <c r="DL7" t="n">
+        <v>188.54</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -26779,6 +27055,9 @@
       <c r="DK8" t="n">
         <v>142.91</v>
       </c>
+      <c r="DL8" t="n">
+        <v>139.51</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -27130,6 +27409,9 @@
       <c r="DK9" t="n">
         <v>98.98</v>
       </c>
+      <c r="DL9" t="n">
+        <v>97.53</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27480,6 +27762,9 @@
       </c>
       <c r="DK10" t="n">
         <v>417.32</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>425.21</v>
       </c>
     </row>
   </sheetData>
@@ -27493,7 +27778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DK10"/>
+  <dimension ref="A1:DL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -27611,6 +27896,7 @@
     <col width="12" customWidth="1" min="113" max="113"/>
     <col width="12" customWidth="1" min="114" max="114"/>
     <col width="12" customWidth="1" min="115" max="115"/>
+    <col width="12" customWidth="1" min="116" max="116"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27963,6 +28249,9 @@
       <c r="DK1" s="1" t="n">
         <v>20260210</v>
       </c>
+      <c r="DL1" s="1" t="n">
+        <v>20260211</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -28314,6 +28603,9 @@
       <c r="DK2" t="n">
         <v>0</v>
       </c>
+      <c r="DL2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -28665,6 +28957,9 @@
       <c r="DK3" t="n">
         <v>0</v>
       </c>
+      <c r="DL3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -29016,6 +29311,9 @@
       <c r="DK4" t="n">
         <v>0</v>
       </c>
+      <c r="DL4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -29367,6 +29665,9 @@
       <c r="DK5" t="n">
         <v>0</v>
       </c>
+      <c r="DL5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -29718,6 +30019,9 @@
       <c r="DK6" t="n">
         <v>0</v>
       </c>
+      <c r="DL6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -30069,6 +30373,9 @@
       <c r="DK7" t="n">
         <v>0</v>
       </c>
+      <c r="DL7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -30420,6 +30727,9 @@
       <c r="DK8" t="n">
         <v>0</v>
       </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -30771,6 +31081,9 @@
       <c r="DK9" t="n">
         <v>0</v>
       </c>
+      <c r="DL9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -31120,6 +31433,9 @@
         <v>0</v>
       </c>
       <c r="DK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -31134,7 +31450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR10"/>
+  <dimension ref="A1:CS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -31233,6 +31549,7 @@
     <col width="10" customWidth="1" min="94" max="94"/>
     <col width="10" customWidth="1" min="95" max="95"/>
     <col width="10" customWidth="1" min="96" max="96"/>
+    <col width="10" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31528,6 +31845,9 @@
       <c r="CR1" s="1" t="n">
         <v>20260210</v>
       </c>
+      <c r="CS1" s="1" t="n">
+        <v>20260211</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -31822,6 +32142,9 @@
       <c r="CR2" t="n">
         <v>89</v>
       </c>
+      <c r="CS2" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -32116,6 +32439,9 @@
       <c r="CR3" t="n">
         <v>0</v>
       </c>
+      <c r="CS3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -32410,6 +32736,9 @@
       <c r="CR4" t="n">
         <v>13</v>
       </c>
+      <c r="CS4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -32704,6 +33033,9 @@
       <c r="CR5" t="n">
         <v>23</v>
       </c>
+      <c r="CS5" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -32998,6 +33330,9 @@
       <c r="CR6" t="n">
         <v>15</v>
       </c>
+      <c r="CS6" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -33292,6 +33627,9 @@
       <c r="CR7" t="n">
         <v>88</v>
       </c>
+      <c r="CS7" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -33586,6 +33924,9 @@
       <c r="CR8" t="n">
         <v>26</v>
       </c>
+      <c r="CS8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -33880,6 +34221,9 @@
       <c r="CR9" t="n">
         <v>95</v>
       </c>
+      <c r="CS9" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -34173,6 +34517,9 @@
       </c>
       <c r="CR10" t="n">
         <v>39</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -34186,7 +34533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD10"/>
+  <dimension ref="A1:BE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -34245,6 +34592,7 @@
     <col width="10" customWidth="1" min="54" max="54"/>
     <col width="10" customWidth="1" min="55" max="55"/>
     <col width="10" customWidth="1" min="56" max="56"/>
+    <col width="10" customWidth="1" min="57" max="57"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -34420,6 +34768,9 @@
       <c r="BD1" s="1" t="n">
         <v>20260210</v>
       </c>
+      <c r="BE1" s="1" t="n">
+        <v>20260211</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -34594,6 +34945,9 @@
       <c r="BD2" t="n">
         <v>71</v>
       </c>
+      <c r="BE2" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -34768,6 +35122,9 @@
       <c r="BD3" t="n">
         <v>0</v>
       </c>
+      <c r="BE3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -34942,6 +35299,9 @@
       <c r="BD4" t="n">
         <v>76</v>
       </c>
+      <c r="BE4" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -35116,6 +35476,9 @@
       <c r="BD5" t="n">
         <v>17</v>
       </c>
+      <c r="BE5" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -35290,6 +35653,9 @@
       <c r="BD6" t="n">
         <v>0</v>
       </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -35464,6 +35830,9 @@
       <c r="BD7" t="n">
         <v>89</v>
       </c>
+      <c r="BE7" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -35638,6 +36007,9 @@
       <c r="BD8" t="n">
         <v>20</v>
       </c>
+      <c r="BE8" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -35812,6 +36184,9 @@
       <c r="BD9" t="n">
         <v>97</v>
       </c>
+      <c r="BE9" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -35985,6 +36360,9 @@
       </c>
       <c r="BD10" t="n">
         <v>27</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -35998,7 +36376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR10"/>
+  <dimension ref="A1:CS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -36097,6 +36475,7 @@
     <col width="10" customWidth="1" min="94" max="94"/>
     <col width="10" customWidth="1" min="95" max="95"/>
     <col width="10" customWidth="1" min="96" max="96"/>
+    <col width="10" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -36392,6 +36771,9 @@
       <c r="CR1" s="1" t="n">
         <v>20260210</v>
       </c>
+      <c r="CS1" s="1" t="n">
+        <v>20260211</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -36686,6 +37068,9 @@
       <c r="CR2" t="n">
         <v>64</v>
       </c>
+      <c r="CS2" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -36980,6 +37365,9 @@
       <c r="CR3" t="n">
         <v>-129</v>
       </c>
+      <c r="CS3" t="n">
+        <v>-112</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -37274,6 +37662,9 @@
       <c r="CR4" t="n">
         <v>-77</v>
       </c>
+      <c r="CS4" t="n">
+        <v>-109</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -37568,6 +37959,9 @@
       <c r="CR5" t="n">
         <v>-52</v>
       </c>
+      <c r="CS5" t="n">
+        <v>-48</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -37862,6 +38256,9 @@
       <c r="CR6" t="n">
         <v>-48</v>
       </c>
+      <c r="CS6" t="n">
+        <v>-32</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -38156,6 +38553,9 @@
       <c r="CR7" t="n">
         <v>44</v>
       </c>
+      <c r="CS7" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -38450,6 +38850,9 @@
       <c r="CR8" t="n">
         <v>-49</v>
       </c>
+      <c r="CS8" t="n">
+        <v>-55</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -38744,6 +39147,9 @@
       <c r="CR9" t="n">
         <v>80</v>
       </c>
+      <c r="CS9" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -39037,6 +39443,9 @@
       </c>
       <c r="CR10" t="n">
         <v>-33</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>-4</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -602,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE10"/>
+  <dimension ref="A1:BF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -662,6 +662,7 @@
     <col width="10" customWidth="1" min="55" max="55"/>
     <col width="10" customWidth="1" min="56" max="56"/>
     <col width="10" customWidth="1" min="57" max="57"/>
+    <col width="10" customWidth="1" min="58" max="58"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -840,6 +841,9 @@
       <c r="BE1" s="1" t="n">
         <v>20260211</v>
       </c>
+      <c r="BF1" s="1" t="n">
+        <v>20260212</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1017,6 +1021,9 @@
       <c r="BE2" t="n">
         <v>24</v>
       </c>
+      <c r="BF2" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1194,6 +1201,9 @@
       <c r="BE3" t="n">
         <v>-140</v>
       </c>
+      <c r="BF3" t="n">
+        <v>-143</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1371,6 +1381,9 @@
       <c r="BE4" t="n">
         <v>1</v>
       </c>
+      <c r="BF4" t="n">
+        <v>-30</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1548,6 +1561,9 @@
       <c r="BE5" t="n">
         <v>-103</v>
       </c>
+      <c r="BF5" t="n">
+        <v>-113</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1725,6 +1741,9 @@
       <c r="BE6" t="n">
         <v>-11</v>
       </c>
+      <c r="BF6" t="n">
+        <v>-74</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1902,6 +1921,9 @@
       <c r="BE7" t="n">
         <v>44</v>
       </c>
+      <c r="BF7" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2079,6 +2101,9 @@
       <c r="BE8" t="n">
         <v>-98</v>
       </c>
+      <c r="BF8" t="n">
+        <v>-104</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2256,6 +2281,9 @@
       <c r="BE9" t="n">
         <v>86</v>
       </c>
+      <c r="BF9" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2432,6 +2460,9 @@
       </c>
       <c r="BE10" t="n">
         <v>-27</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>-21</v>
       </c>
     </row>
   </sheetData>
@@ -2445,7 +2476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS10"/>
+  <dimension ref="A1:CT10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2545,6 +2576,7 @@
     <col width="12" customWidth="1" min="95" max="95"/>
     <col width="12" customWidth="1" min="96" max="96"/>
     <col width="12" customWidth="1" min="97" max="97"/>
+    <col width="12" customWidth="1" min="98" max="98"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3033,6 +3065,11 @@
           <t>20260211</t>
         </is>
       </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>20260212</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3330,6 +3367,9 @@
       <c r="CS2" t="n">
         <v>105</v>
       </c>
+      <c r="CT2" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3627,6 +3667,9 @@
       <c r="CS3" t="n">
         <v>89</v>
       </c>
+      <c r="CT3" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3924,6 +3967,9 @@
       <c r="CS4" t="n">
         <v>96</v>
       </c>
+      <c r="CT4" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4221,6 +4267,9 @@
       <c r="CS5" t="n">
         <v>94</v>
       </c>
+      <c r="CT5" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4518,6 +4567,9 @@
       <c r="CS6" t="n">
         <v>98</v>
       </c>
+      <c r="CT6" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4815,6 +4867,9 @@
       <c r="CS7" t="n">
         <v>102</v>
       </c>
+      <c r="CT7" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5112,6 +5167,9 @@
       <c r="CS8" t="n">
         <v>90</v>
       </c>
+      <c r="CT8" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5409,6 +5467,9 @@
       <c r="CS9" t="n">
         <v>102</v>
       </c>
+      <c r="CT9" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5705,6 +5766,9 @@
       </c>
       <c r="CS10" t="n">
         <v>100</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -5718,7 +5782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ10"/>
+  <dimension ref="A1:CA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5799,6 +5863,7 @@
     <col width="12" customWidth="1" min="76" max="76"/>
     <col width="12" customWidth="1" min="77" max="77"/>
     <col width="12" customWidth="1" min="78" max="78"/>
+    <col width="12" customWidth="1" min="79" max="79"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6192,6 +6257,11 @@
           <t>20260211</t>
         </is>
       </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>20260212</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6432,6 +6502,9 @@
       <c r="BZ2" t="n">
         <v>34.56</v>
       </c>
+      <c r="CA2" t="n">
+        <v>35.34</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6672,6 +6745,9 @@
       <c r="BZ3" t="n">
         <v>68.5</v>
       </c>
+      <c r="CA3" t="n">
+        <v>85.23999999999999</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6912,6 +6988,9 @@
       <c r="BZ4" t="n">
         <v>-21.22</v>
       </c>
+      <c r="CA4" t="n">
+        <v>0.33</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7152,6 +7231,9 @@
       <c r="BZ5" t="n">
         <v>59.16</v>
       </c>
+      <c r="CA5" t="n">
+        <v>53.58</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7392,6 +7474,9 @@
       <c r="BZ6" t="n">
         <v>-2.75</v>
       </c>
+      <c r="CA6" t="n">
+        <v>-5.69</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7632,6 +7717,9 @@
       <c r="BZ7" t="n">
         <v>47.69</v>
       </c>
+      <c r="CA7" t="n">
+        <v>48.41</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7872,6 +7960,9 @@
       <c r="BZ8" t="n">
         <v>48.5</v>
       </c>
+      <c r="CA8" t="n">
+        <v>40.04</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8112,6 +8203,9 @@
       <c r="BZ9" t="n">
         <v>-30.51</v>
       </c>
+      <c r="CA9" t="n">
+        <v>-32</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8351,6 +8445,9 @@
       </c>
       <c r="BZ10" t="n">
         <v>-1.1</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>-0.9399999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -8364,7 +8461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE10"/>
+  <dimension ref="A1:BF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8424,6 +8521,7 @@
     <col width="12" customWidth="1" min="55" max="55"/>
     <col width="12" customWidth="1" min="56" max="56"/>
     <col width="12" customWidth="1" min="57" max="57"/>
+    <col width="12" customWidth="1" min="58" max="58"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8712,6 +8810,11 @@
           <t>20260211</t>
         </is>
       </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>20260212</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8889,6 +8992,9 @@
       <c r="BE2" t="n">
         <v>0</v>
       </c>
+      <c r="BF2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9066,6 +9172,9 @@
       <c r="BE3" t="n">
         <v>0</v>
       </c>
+      <c r="BF3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9243,6 +9352,9 @@
       <c r="BE4" t="n">
         <v>0</v>
       </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9420,6 +9532,9 @@
       <c r="BE5" t="n">
         <v>0</v>
       </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9597,6 +9712,9 @@
       <c r="BE6" t="n">
         <v>0</v>
       </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9774,6 +9892,9 @@
       <c r="BE7" t="n">
         <v>0</v>
       </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9951,6 +10072,9 @@
       <c r="BE8" t="n">
         <v>0</v>
       </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10128,6 +10252,9 @@
       <c r="BE9" t="n">
         <v>0</v>
       </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10303,6 +10430,9 @@
         <v>0</v>
       </c>
       <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10317,7 +10447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI10"/>
+  <dimension ref="A1:CJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10407,6 +10537,7 @@
     <col width="10" customWidth="1" min="85" max="85"/>
     <col width="10" customWidth="1" min="86" max="86"/>
     <col width="10" customWidth="1" min="87" max="87"/>
+    <col width="10" customWidth="1" min="88" max="88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10675,6 +10806,9 @@
       <c r="CI1" s="1" t="n">
         <v>20260211</v>
       </c>
+      <c r="CJ1" s="1" t="n">
+        <v>20260212</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10942,6 +11076,9 @@
       <c r="CI2" t="n">
         <v>57</v>
       </c>
+      <c r="CJ2" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11209,6 +11346,9 @@
       <c r="CI3" t="n">
         <v>-129</v>
       </c>
+      <c r="CJ3" t="n">
+        <v>-122</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11476,6 +11616,9 @@
       <c r="CI4" t="n">
         <v>-59</v>
       </c>
+      <c r="CJ4" t="n">
+        <v>-102</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11743,6 +11886,9 @@
       <c r="CI5" t="n">
         <v>-67</v>
       </c>
+      <c r="CJ5" t="n">
+        <v>-76</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12010,6 +12156,9 @@
       <c r="CI6" t="n">
         <v>-50</v>
       </c>
+      <c r="CJ6" t="n">
+        <v>-77</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12277,6 +12426,9 @@
       <c r="CI7" t="n">
         <v>28</v>
       </c>
+      <c r="CJ7" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12544,6 +12696,9 @@
       <c r="CI8" t="n">
         <v>-73</v>
       </c>
+      <c r="CJ8" t="n">
+        <v>-79</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12811,6 +12966,9 @@
       <c r="CI9" t="n">
         <v>54</v>
       </c>
+      <c r="CJ9" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13077,6 +13235,9 @@
       </c>
       <c r="CI10" t="n">
         <v>-22</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>-9</v>
       </c>
     </row>
   </sheetData>
@@ -13090,7 +13251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DL10"/>
+  <dimension ref="A1:DM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13209,6 +13370,7 @@
     <col width="12" customWidth="1" min="114" max="114"/>
     <col width="12" customWidth="1" min="115" max="115"/>
     <col width="12" customWidth="1" min="116" max="116"/>
+    <col width="12" customWidth="1" min="117" max="117"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13564,6 +13726,9 @@
       <c r="DL1" s="1" t="n">
         <v>20260211</v>
       </c>
+      <c r="DM1" s="1" t="n">
+        <v>20260212</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13918,6 +14083,9 @@
       <c r="DL2" t="n">
         <v>273.68</v>
       </c>
+      <c r="DM2" t="n">
+        <v>275.5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14272,6 +14440,9 @@
       <c r="DL3" t="n">
         <v>206.96</v>
       </c>
+      <c r="DM3" t="n">
+        <v>204.08</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14626,6 +14797,9 @@
       <c r="DL4" t="n">
         <v>318.58</v>
       </c>
+      <c r="DM4" t="n">
+        <v>310.96</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14980,6 +15154,9 @@
       <c r="DL5" t="n">
         <v>413.27</v>
       </c>
+      <c r="DM5" t="n">
+        <v>404.37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15334,6 +15511,9 @@
       <c r="DL6" t="n">
         <v>82.20999999999999</v>
       </c>
+      <c r="DM6" t="n">
+        <v>79.62</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15688,6 +15868,9 @@
       <c r="DL7" t="n">
         <v>188.54</v>
       </c>
+      <c r="DM7" t="n">
+        <v>190.05</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16042,6 +16225,9 @@
       <c r="DL8" t="n">
         <v>139.51</v>
       </c>
+      <c r="DM8" t="n">
+        <v>135.68</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16396,6 +16582,9 @@
       <c r="DL9" t="n">
         <v>97.53</v>
       </c>
+      <c r="DM9" t="n">
+        <v>99.12</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16749,6 +16938,9 @@
       </c>
       <c r="DL10" t="n">
         <v>425.21</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>428.27</v>
       </c>
     </row>
   </sheetData>
@@ -16762,7 +16954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DL10"/>
+  <dimension ref="A1:DM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -16881,6 +17073,7 @@
     <col width="12" customWidth="1" min="114" max="114"/>
     <col width="12" customWidth="1" min="115" max="115"/>
     <col width="12" customWidth="1" min="116" max="116"/>
+    <col width="12" customWidth="1" min="117" max="117"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17236,6 +17429,9 @@
       <c r="DL1" s="1" t="n">
         <v>20260211</v>
       </c>
+      <c r="DM1" s="1" t="n">
+        <v>20260212</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17590,6 +17786,9 @@
       <c r="DL2" t="n">
         <v>273.68</v>
       </c>
+      <c r="DM2" t="n">
+        <v>275.5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17944,6 +18143,9 @@
       <c r="DL3" t="n">
         <v>206.96</v>
       </c>
+      <c r="DM3" t="n">
+        <v>204.08</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18298,6 +18500,9 @@
       <c r="DL4" t="n">
         <v>318.58</v>
       </c>
+      <c r="DM4" t="n">
+        <v>310.96</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18652,6 +18857,9 @@
       <c r="DL5" t="n">
         <v>413.27</v>
       </c>
+      <c r="DM5" t="n">
+        <v>404.37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19006,6 +19214,9 @@
       <c r="DL6" t="n">
         <v>82.20999999999999</v>
       </c>
+      <c r="DM6" t="n">
+        <v>79.62</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19360,6 +19571,9 @@
       <c r="DL7" t="n">
         <v>188.54</v>
       </c>
+      <c r="DM7" t="n">
+        <v>190.05</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19714,6 +19928,9 @@
       <c r="DL8" t="n">
         <v>139.51</v>
       </c>
+      <c r="DM8" t="n">
+        <v>135.68</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20068,6 +20285,9 @@
       <c r="DL9" t="n">
         <v>97.53</v>
       </c>
+      <c r="DM9" t="n">
+        <v>99.12</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20421,6 +20641,9 @@
       </c>
       <c r="DL10" t="n">
         <v>425.21</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>428.27</v>
       </c>
     </row>
   </sheetData>
@@ -20434,7 +20657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DL10"/>
+  <dimension ref="A1:DM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20553,6 +20776,7 @@
     <col width="12" customWidth="1" min="114" max="114"/>
     <col width="12" customWidth="1" min="115" max="115"/>
     <col width="12" customWidth="1" min="116" max="116"/>
+    <col width="12" customWidth="1" min="117" max="117"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20908,6 +21132,9 @@
       <c r="DL1" s="1" t="n">
         <v>20260211</v>
       </c>
+      <c r="DM1" s="1" t="n">
+        <v>20260212</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21262,6 +21489,9 @@
       <c r="DL2" t="n">
         <v>273.68</v>
       </c>
+      <c r="DM2" t="n">
+        <v>275.5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21616,6 +21846,9 @@
       <c r="DL3" t="n">
         <v>206.96</v>
       </c>
+      <c r="DM3" t="n">
+        <v>204.08</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -21970,6 +22203,9 @@
       <c r="DL4" t="n">
         <v>318.58</v>
       </c>
+      <c r="DM4" t="n">
+        <v>310.96</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -22324,6 +22560,9 @@
       <c r="DL5" t="n">
         <v>413.27</v>
       </c>
+      <c r="DM5" t="n">
+        <v>404.37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -22678,6 +22917,9 @@
       <c r="DL6" t="n">
         <v>82.20999999999999</v>
       </c>
+      <c r="DM6" t="n">
+        <v>79.62</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23032,6 +23274,9 @@
       <c r="DL7" t="n">
         <v>188.54</v>
       </c>
+      <c r="DM7" t="n">
+        <v>190.05</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23386,6 +23631,9 @@
       <c r="DL8" t="n">
         <v>139.51</v>
       </c>
+      <c r="DM8" t="n">
+        <v>135.68</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23740,6 +23988,9 @@
       <c r="DL9" t="n">
         <v>97.53</v>
       </c>
+      <c r="DM9" t="n">
+        <v>99.12</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24093,6 +24344,9 @@
       </c>
       <c r="DL10" t="n">
         <v>425.21</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>428.27</v>
       </c>
     </row>
   </sheetData>
@@ -24106,7 +24360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DL10"/>
+  <dimension ref="A1:DM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24225,6 +24479,7 @@
     <col width="12" customWidth="1" min="114" max="114"/>
     <col width="12" customWidth="1" min="115" max="115"/>
     <col width="12" customWidth="1" min="116" max="116"/>
+    <col width="12" customWidth="1" min="117" max="117"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24580,6 +24835,9 @@
       <c r="DL1" s="1" t="n">
         <v>20260211</v>
       </c>
+      <c r="DM1" s="1" t="n">
+        <v>20260212</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24934,6 +25192,9 @@
       <c r="DL2" t="n">
         <v>273.68</v>
       </c>
+      <c r="DM2" t="n">
+        <v>275.5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25288,6 +25549,9 @@
       <c r="DL3" t="n">
         <v>206.96</v>
       </c>
+      <c r="DM3" t="n">
+        <v>204.08</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -25642,6 +25906,9 @@
       <c r="DL4" t="n">
         <v>318.58</v>
       </c>
+      <c r="DM4" t="n">
+        <v>310.96</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -25996,6 +26263,9 @@
       <c r="DL5" t="n">
         <v>413.27</v>
       </c>
+      <c r="DM5" t="n">
+        <v>404.37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -26350,6 +26620,9 @@
       <c r="DL6" t="n">
         <v>82.20999999999999</v>
       </c>
+      <c r="DM6" t="n">
+        <v>79.62</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -26704,6 +26977,9 @@
       <c r="DL7" t="n">
         <v>188.54</v>
       </c>
+      <c r="DM7" t="n">
+        <v>190.05</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -27058,6 +27334,9 @@
       <c r="DL8" t="n">
         <v>139.51</v>
       </c>
+      <c r="DM8" t="n">
+        <v>135.68</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -27412,6 +27691,9 @@
       <c r="DL9" t="n">
         <v>97.53</v>
       </c>
+      <c r="DM9" t="n">
+        <v>99.12</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27765,6 +28047,9 @@
       </c>
       <c r="DL10" t="n">
         <v>425.21</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>428.27</v>
       </c>
     </row>
   </sheetData>
@@ -27778,7 +28063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DL10"/>
+  <dimension ref="A1:DM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -27897,6 +28182,7 @@
     <col width="12" customWidth="1" min="114" max="114"/>
     <col width="12" customWidth="1" min="115" max="115"/>
     <col width="12" customWidth="1" min="116" max="116"/>
+    <col width="12" customWidth="1" min="117" max="117"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28252,6 +28538,9 @@
       <c r="DL1" s="1" t="n">
         <v>20260211</v>
       </c>
+      <c r="DM1" s="1" t="n">
+        <v>20260212</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -28606,6 +28895,9 @@
       <c r="DL2" t="n">
         <v>0</v>
       </c>
+      <c r="DM2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -28960,6 +29252,9 @@
       <c r="DL3" t="n">
         <v>0</v>
       </c>
+      <c r="DM3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -29314,6 +29609,9 @@
       <c r="DL4" t="n">
         <v>0</v>
       </c>
+      <c r="DM4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -29668,6 +29966,9 @@
       <c r="DL5" t="n">
         <v>0</v>
       </c>
+      <c r="DM5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -30022,6 +30323,9 @@
       <c r="DL6" t="n">
         <v>0</v>
       </c>
+      <c r="DM6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -30376,6 +30680,9 @@
       <c r="DL7" t="n">
         <v>0</v>
       </c>
+      <c r="DM7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -30730,6 +31037,9 @@
       <c r="DL8" t="n">
         <v>0</v>
       </c>
+      <c r="DM8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -31084,6 +31394,9 @@
       <c r="DL9" t="n">
         <v>0</v>
       </c>
+      <c r="DM9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -31436,6 +31749,9 @@
         <v>0</v>
       </c>
       <c r="DL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -31450,7 +31766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS10"/>
+  <dimension ref="A1:CT10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -31550,6 +31866,7 @@
     <col width="10" customWidth="1" min="95" max="95"/>
     <col width="10" customWidth="1" min="96" max="96"/>
     <col width="10" customWidth="1" min="97" max="97"/>
+    <col width="10" customWidth="1" min="98" max="98"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31848,6 +32165,9 @@
       <c r="CS1" s="1" t="n">
         <v>20260211</v>
       </c>
+      <c r="CT1" s="1" t="n">
+        <v>20260212</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -32145,6 +32465,9 @@
       <c r="CS2" t="n">
         <v>86</v>
       </c>
+      <c r="CT2" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -32442,6 +32765,9 @@
       <c r="CS3" t="n">
         <v>0</v>
       </c>
+      <c r="CT3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -32739,6 +33065,9 @@
       <c r="CS4" t="n">
         <v>0</v>
       </c>
+      <c r="CT4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -33036,6 +33365,9 @@
       <c r="CS5" t="n">
         <v>22</v>
       </c>
+      <c r="CT5" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -33333,6 +33665,9 @@
       <c r="CS6" t="n">
         <v>26</v>
       </c>
+      <c r="CT6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -33630,6 +33965,9 @@
       <c r="CS7" t="n">
         <v>81</v>
       </c>
+      <c r="CT7" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -33927,6 +34265,9 @@
       <c r="CS8" t="n">
         <v>20</v>
       </c>
+      <c r="CT8" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -34224,6 +34565,9 @@
       <c r="CS9" t="n">
         <v>77</v>
       </c>
+      <c r="CT9" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -34520,6 +34864,9 @@
       </c>
       <c r="CS10" t="n">
         <v>54</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -34533,7 +34880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE10"/>
+  <dimension ref="A1:BF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -34593,6 +34940,7 @@
     <col width="10" customWidth="1" min="55" max="55"/>
     <col width="10" customWidth="1" min="56" max="56"/>
     <col width="10" customWidth="1" min="57" max="57"/>
+    <col width="10" customWidth="1" min="58" max="58"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -34771,6 +35119,9 @@
       <c r="BE1" s="1" t="n">
         <v>20260211</v>
       </c>
+      <c r="BF1" s="1" t="n">
+        <v>20260212</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -34948,6 +35299,9 @@
       <c r="BE2" t="n">
         <v>68</v>
       </c>
+      <c r="BF2" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -35125,6 +35479,9 @@
       <c r="BE3" t="n">
         <v>0</v>
       </c>
+      <c r="BF3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -35302,6 +35659,9 @@
       <c r="BE4" t="n">
         <v>67</v>
       </c>
+      <c r="BF4" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -35479,6 +35839,9 @@
       <c r="BE5" t="n">
         <v>17</v>
       </c>
+      <c r="BF5" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -35656,6 +36019,9 @@
       <c r="BE6" t="n">
         <v>0</v>
       </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -35833,6 +36199,9 @@
       <c r="BE7" t="n">
         <v>82</v>
       </c>
+      <c r="BF7" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -36010,6 +36379,9 @@
       <c r="BE8" t="n">
         <v>15</v>
       </c>
+      <c r="BF8" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -36187,6 +36559,9 @@
       <c r="BE9" t="n">
         <v>89</v>
       </c>
+      <c r="BF9" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -36363,6 +36738,9 @@
       </c>
       <c r="BE10" t="n">
         <v>35</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -36376,7 +36754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS10"/>
+  <dimension ref="A1:CT10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -36476,6 +36854,7 @@
     <col width="10" customWidth="1" min="95" max="95"/>
     <col width="10" customWidth="1" min="96" max="96"/>
     <col width="10" customWidth="1" min="97" max="97"/>
+    <col width="10" customWidth="1" min="98" max="98"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -36774,6 +37153,9 @@
       <c r="CS1" s="1" t="n">
         <v>20260211</v>
       </c>
+      <c r="CT1" s="1" t="n">
+        <v>20260212</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -37071,6 +37453,9 @@
       <c r="CS2" t="n">
         <v>55</v>
       </c>
+      <c r="CT2" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -37368,6 +37753,9 @@
       <c r="CS3" t="n">
         <v>-112</v>
       </c>
+      <c r="CT3" t="n">
+        <v>-103</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -37665,6 +38053,9 @@
       <c r="CS4" t="n">
         <v>-109</v>
       </c>
+      <c r="CT4" t="n">
+        <v>-130</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -37962,6 +38353,9 @@
       <c r="CS5" t="n">
         <v>-48</v>
       </c>
+      <c r="CT5" t="n">
+        <v>-58</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -38259,6 +38653,9 @@
       <c r="CS6" t="n">
         <v>-32</v>
       </c>
+      <c r="CT6" t="n">
+        <v>-72</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -38556,6 +38953,9 @@
       <c r="CS7" t="n">
         <v>30</v>
       </c>
+      <c r="CT7" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -38853,6 +39253,9 @@
       <c r="CS8" t="n">
         <v>-55</v>
       </c>
+      <c r="CT8" t="n">
+        <v>-62</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -39150,6 +39553,9 @@
       <c r="CS9" t="n">
         <v>48</v>
       </c>
+      <c r="CT9" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -39446,6 +39852,9 @@
       </c>
       <c r="CS10" t="n">
         <v>-4</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -602,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF10"/>
+  <dimension ref="A1:BG10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -663,6 +663,7 @@
     <col width="10" customWidth="1" min="56" max="56"/>
     <col width="10" customWidth="1" min="57" max="57"/>
     <col width="10" customWidth="1" min="58" max="58"/>
+    <col width="10" customWidth="1" min="59" max="59"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -844,6 +845,9 @@
       <c r="BF1" s="1" t="n">
         <v>20260212</v>
       </c>
+      <c r="BG1" s="1" t="n">
+        <v>20260213</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1024,6 +1028,9 @@
       <c r="BF2" t="n">
         <v>33</v>
       </c>
+      <c r="BG2" t="n">
+        <v>-37</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1204,6 +1211,9 @@
       <c r="BF3" t="n">
         <v>-143</v>
       </c>
+      <c r="BG3" t="n">
+        <v>-150</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1384,6 +1394,9 @@
       <c r="BF4" t="n">
         <v>-30</v>
       </c>
+      <c r="BG4" t="n">
+        <v>-41</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1564,6 +1577,9 @@
       <c r="BF5" t="n">
         <v>-113</v>
       </c>
+      <c r="BG5" t="n">
+        <v>-111</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1744,6 +1760,9 @@
       <c r="BF6" t="n">
         <v>-74</v>
       </c>
+      <c r="BG6" t="n">
+        <v>-91</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1924,6 +1943,9 @@
       <c r="BF7" t="n">
         <v>59</v>
       </c>
+      <c r="BG7" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2104,6 +2126,9 @@
       <c r="BF8" t="n">
         <v>-104</v>
       </c>
+      <c r="BG8" t="n">
+        <v>-117</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2284,6 +2309,9 @@
       <c r="BF9" t="n">
         <v>97</v>
       </c>
+      <c r="BG9" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2463,6 +2491,9 @@
       </c>
       <c r="BF10" t="n">
         <v>-21</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>-45</v>
       </c>
     </row>
   </sheetData>
@@ -2476,7 +2507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CT10"/>
+  <dimension ref="A1:CU10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2577,6 +2608,7 @@
     <col width="12" customWidth="1" min="96" max="96"/>
     <col width="12" customWidth="1" min="97" max="97"/>
     <col width="12" customWidth="1" min="98" max="98"/>
+    <col width="12" customWidth="1" min="99" max="99"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3070,6 +3102,11 @@
           <t>20260212</t>
         </is>
       </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>20260213</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3370,6 +3407,9 @@
       <c r="CT2" t="n">
         <v>105</v>
       </c>
+      <c r="CU2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3670,6 +3710,9 @@
       <c r="CT3" t="n">
         <v>88</v>
       </c>
+      <c r="CU3" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3970,6 +4013,9 @@
       <c r="CT4" t="n">
         <v>94</v>
       </c>
+      <c r="CU4" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4270,6 +4316,9 @@
       <c r="CT5" t="n">
         <v>93</v>
       </c>
+      <c r="CU5" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4570,6 +4619,9 @@
       <c r="CT6" t="n">
         <v>95</v>
       </c>
+      <c r="CU6" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4870,6 +4922,9 @@
       <c r="CT7" t="n">
         <v>103</v>
       </c>
+      <c r="CU7" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5170,6 +5225,9 @@
       <c r="CT8" t="n">
         <v>88</v>
       </c>
+      <c r="CU8" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5470,6 +5528,9 @@
       <c r="CT9" t="n">
         <v>104</v>
       </c>
+      <c r="CU9" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5769,6 +5830,9 @@
       </c>
       <c r="CT10" t="n">
         <v>101</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -5782,7 +5846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CA10"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5864,6 +5928,7 @@
     <col width="12" customWidth="1" min="77" max="77"/>
     <col width="12" customWidth="1" min="78" max="78"/>
     <col width="12" customWidth="1" min="79" max="79"/>
+    <col width="12" customWidth="1" min="80" max="80"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6262,6 +6327,11 @@
           <t>20260212</t>
         </is>
       </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>20260213</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6505,6 +6575,9 @@
       <c r="CA2" t="n">
         <v>35.34</v>
       </c>
+      <c r="CB2" t="n">
+        <v>30.94</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6748,6 +6821,9 @@
       <c r="CA3" t="n">
         <v>85.23999999999999</v>
       </c>
+      <c r="CB3" t="n">
+        <v>98.47</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6991,6 +7067,9 @@
       <c r="CA4" t="n">
         <v>0.33</v>
       </c>
+      <c r="CB4" t="n">
+        <v>20.49</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7234,6 +7313,9 @@
       <c r="CA5" t="n">
         <v>53.58</v>
       </c>
+      <c r="CB5" t="n">
+        <v>48.87</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7477,6 +7559,9 @@
       <c r="CA6" t="n">
         <v>-5.69</v>
       </c>
+      <c r="CB6" t="n">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7720,6 +7805,9 @@
       <c r="CA7" t="n">
         <v>48.41</v>
       </c>
+      <c r="CB7" t="n">
+        <v>46.41</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7963,6 +8051,9 @@
       <c r="CA8" t="n">
         <v>40.04</v>
       </c>
+      <c r="CB8" t="n">
+        <v>34.48</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8206,6 +8297,9 @@
       <c r="CA9" t="n">
         <v>-32</v>
       </c>
+      <c r="CB9" t="n">
+        <v>-33.13</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8448,6 +8542,9 @@
       </c>
       <c r="CA10" t="n">
         <v>-0.9399999999999999</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>-0.28</v>
       </c>
     </row>
   </sheetData>
@@ -8461,7 +8558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF10"/>
+  <dimension ref="A1:BG10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8522,6 +8619,7 @@
     <col width="12" customWidth="1" min="56" max="56"/>
     <col width="12" customWidth="1" min="57" max="57"/>
     <col width="12" customWidth="1" min="58" max="58"/>
+    <col width="12" customWidth="1" min="59" max="59"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8815,6 +8913,11 @@
           <t>20260212</t>
         </is>
       </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>20260213</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8995,6 +9098,9 @@
       <c r="BF2" t="n">
         <v>0</v>
       </c>
+      <c r="BG2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9175,6 +9281,9 @@
       <c r="BF3" t="n">
         <v>0</v>
       </c>
+      <c r="BG3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9355,6 +9464,9 @@
       <c r="BF4" t="n">
         <v>0</v>
       </c>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9535,6 +9647,9 @@
       <c r="BF5" t="n">
         <v>0</v>
       </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9715,6 +9830,9 @@
       <c r="BF6" t="n">
         <v>0</v>
       </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9895,6 +10013,9 @@
       <c r="BF7" t="n">
         <v>0</v>
       </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10075,6 +10196,9 @@
       <c r="BF8" t="n">
         <v>0</v>
       </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10255,6 +10379,9 @@
       <c r="BF9" t="n">
         <v>0</v>
       </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10433,6 +10560,9 @@
         <v>0</v>
       </c>
       <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10447,7 +10577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ10"/>
+  <dimension ref="A1:CK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10538,6 +10668,7 @@
     <col width="10" customWidth="1" min="86" max="86"/>
     <col width="10" customWidth="1" min="87" max="87"/>
     <col width="10" customWidth="1" min="88" max="88"/>
+    <col width="10" customWidth="1" min="89" max="89"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10809,6 +10940,9 @@
       <c r="CJ1" s="1" t="n">
         <v>20260212</v>
       </c>
+      <c r="CK1" s="1" t="n">
+        <v>20260213</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11079,6 +11213,9 @@
       <c r="CJ2" t="n">
         <v>66</v>
       </c>
+      <c r="CK2" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11349,6 +11486,9 @@
       <c r="CJ3" t="n">
         <v>-122</v>
       </c>
+      <c r="CK3" t="n">
+        <v>-122</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11619,6 +11759,9 @@
       <c r="CJ4" t="n">
         <v>-102</v>
       </c>
+      <c r="CK4" t="n">
+        <v>-110</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11889,6 +12032,9 @@
       <c r="CJ5" t="n">
         <v>-76</v>
       </c>
+      <c r="CK5" t="n">
+        <v>-75</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12159,6 +12305,9 @@
       <c r="CJ6" t="n">
         <v>-77</v>
       </c>
+      <c r="CK6" t="n">
+        <v>-112</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12429,6 +12578,9 @@
       <c r="CJ7" t="n">
         <v>41</v>
       </c>
+      <c r="CK7" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12699,6 +12851,9 @@
       <c r="CJ8" t="n">
         <v>-79</v>
       </c>
+      <c r="CK8" t="n">
+        <v>-90</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12969,6 +13124,9 @@
       <c r="CJ9" t="n">
         <v>68</v>
       </c>
+      <c r="CK9" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13238,6 +13396,9 @@
       </c>
       <c r="CJ10" t="n">
         <v>-9</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>-46</v>
       </c>
     </row>
   </sheetData>
@@ -13251,7 +13412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DM10"/>
+  <dimension ref="A1:DN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13371,6 +13532,7 @@
     <col width="12" customWidth="1" min="115" max="115"/>
     <col width="12" customWidth="1" min="116" max="116"/>
     <col width="12" customWidth="1" min="117" max="117"/>
+    <col width="12" customWidth="1" min="118" max="118"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13729,6 +13891,9 @@
       <c r="DM1" s="1" t="n">
         <v>20260212</v>
       </c>
+      <c r="DN1" s="1" t="n">
+        <v>20260213</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14086,6 +14251,9 @@
       <c r="DM2" t="n">
         <v>275.5</v>
       </c>
+      <c r="DN2" t="n">
+        <v>261.73</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14443,6 +14611,9 @@
       <c r="DM3" t="n">
         <v>204.08</v>
       </c>
+      <c r="DN3" t="n">
+        <v>199.6</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14800,6 +14971,9 @@
       <c r="DM4" t="n">
         <v>310.96</v>
       </c>
+      <c r="DN4" t="n">
+        <v>309</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15157,6 +15331,9 @@
       <c r="DM5" t="n">
         <v>404.37</v>
       </c>
+      <c r="DN5" t="n">
+        <v>401.84</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15514,6 +15691,9 @@
       <c r="DM6" t="n">
         <v>79.62</v>
       </c>
+      <c r="DN6" t="n">
+        <v>75.86</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15871,6 +16051,9 @@
       <c r="DM7" t="n">
         <v>190.05</v>
       </c>
+      <c r="DN7" t="n">
+        <v>186.94</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16228,6 +16411,9 @@
       <c r="DM8" t="n">
         <v>135.68</v>
       </c>
+      <c r="DN8" t="n">
+        <v>129.13</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16585,6 +16771,9 @@
       <c r="DM9" t="n">
         <v>99.12</v>
       </c>
+      <c r="DN9" t="n">
+        <v>96.76000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16941,6 +17130,9 @@
       </c>
       <c r="DM10" t="n">
         <v>428.27</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>417.07</v>
       </c>
     </row>
   </sheetData>
@@ -16954,7 +17146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DM10"/>
+  <dimension ref="A1:DN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17074,6 +17266,7 @@
     <col width="12" customWidth="1" min="115" max="115"/>
     <col width="12" customWidth="1" min="116" max="116"/>
     <col width="12" customWidth="1" min="117" max="117"/>
+    <col width="12" customWidth="1" min="118" max="118"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17432,6 +17625,9 @@
       <c r="DM1" s="1" t="n">
         <v>20260212</v>
       </c>
+      <c r="DN1" s="1" t="n">
+        <v>20260213</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17789,6 +17985,9 @@
       <c r="DM2" t="n">
         <v>275.5</v>
       </c>
+      <c r="DN2" t="n">
+        <v>261.73</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18146,6 +18345,9 @@
       <c r="DM3" t="n">
         <v>204.08</v>
       </c>
+      <c r="DN3" t="n">
+        <v>199.6</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18503,6 +18705,9 @@
       <c r="DM4" t="n">
         <v>310.96</v>
       </c>
+      <c r="DN4" t="n">
+        <v>309</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18860,6 +19065,9 @@
       <c r="DM5" t="n">
         <v>404.37</v>
       </c>
+      <c r="DN5" t="n">
+        <v>401.84</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19217,6 +19425,9 @@
       <c r="DM6" t="n">
         <v>79.62</v>
       </c>
+      <c r="DN6" t="n">
+        <v>75.86</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19574,6 +19785,9 @@
       <c r="DM7" t="n">
         <v>190.05</v>
       </c>
+      <c r="DN7" t="n">
+        <v>186.94</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19931,6 +20145,9 @@
       <c r="DM8" t="n">
         <v>135.68</v>
       </c>
+      <c r="DN8" t="n">
+        <v>129.13</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20288,6 +20505,9 @@
       <c r="DM9" t="n">
         <v>99.12</v>
       </c>
+      <c r="DN9" t="n">
+        <v>96.76000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20644,6 +20864,9 @@
       </c>
       <c r="DM10" t="n">
         <v>428.27</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>417.07</v>
       </c>
     </row>
   </sheetData>
@@ -20657,7 +20880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DM10"/>
+  <dimension ref="A1:DN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20777,6 +21000,7 @@
     <col width="12" customWidth="1" min="115" max="115"/>
     <col width="12" customWidth="1" min="116" max="116"/>
     <col width="12" customWidth="1" min="117" max="117"/>
+    <col width="12" customWidth="1" min="118" max="118"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21135,6 +21359,9 @@
       <c r="DM1" s="1" t="n">
         <v>20260212</v>
       </c>
+      <c r="DN1" s="1" t="n">
+        <v>20260213</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21492,6 +21719,9 @@
       <c r="DM2" t="n">
         <v>275.5</v>
       </c>
+      <c r="DN2" t="n">
+        <v>261.73</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21849,6 +22079,9 @@
       <c r="DM3" t="n">
         <v>204.08</v>
       </c>
+      <c r="DN3" t="n">
+        <v>199.6</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22206,6 +22439,9 @@
       <c r="DM4" t="n">
         <v>310.96</v>
       </c>
+      <c r="DN4" t="n">
+        <v>309</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -22563,6 +22799,9 @@
       <c r="DM5" t="n">
         <v>404.37</v>
       </c>
+      <c r="DN5" t="n">
+        <v>401.84</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -22920,6 +23159,9 @@
       <c r="DM6" t="n">
         <v>79.62</v>
       </c>
+      <c r="DN6" t="n">
+        <v>75.86</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23277,6 +23519,9 @@
       <c r="DM7" t="n">
         <v>190.05</v>
       </c>
+      <c r="DN7" t="n">
+        <v>186.94</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23634,6 +23879,9 @@
       <c r="DM8" t="n">
         <v>135.68</v>
       </c>
+      <c r="DN8" t="n">
+        <v>129.13</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23991,6 +24239,9 @@
       <c r="DM9" t="n">
         <v>99.12</v>
       </c>
+      <c r="DN9" t="n">
+        <v>96.76000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24347,6 +24598,9 @@
       </c>
       <c r="DM10" t="n">
         <v>428.27</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>417.07</v>
       </c>
     </row>
   </sheetData>
@@ -24360,7 +24614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DM10"/>
+  <dimension ref="A1:DN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24480,6 +24734,7 @@
     <col width="12" customWidth="1" min="115" max="115"/>
     <col width="12" customWidth="1" min="116" max="116"/>
     <col width="12" customWidth="1" min="117" max="117"/>
+    <col width="12" customWidth="1" min="118" max="118"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24838,6 +25093,9 @@
       <c r="DM1" s="1" t="n">
         <v>20260212</v>
       </c>
+      <c r="DN1" s="1" t="n">
+        <v>20260213</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25195,6 +25453,9 @@
       <c r="DM2" t="n">
         <v>275.5</v>
       </c>
+      <c r="DN2" t="n">
+        <v>261.73</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25552,6 +25813,9 @@
       <c r="DM3" t="n">
         <v>204.08</v>
       </c>
+      <c r="DN3" t="n">
+        <v>199.6</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -25909,6 +26173,9 @@
       <c r="DM4" t="n">
         <v>310.96</v>
       </c>
+      <c r="DN4" t="n">
+        <v>309</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -26266,6 +26533,9 @@
       <c r="DM5" t="n">
         <v>404.37</v>
       </c>
+      <c r="DN5" t="n">
+        <v>401.84</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -26623,6 +26893,9 @@
       <c r="DM6" t="n">
         <v>79.62</v>
       </c>
+      <c r="DN6" t="n">
+        <v>75.86</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -26980,6 +27253,9 @@
       <c r="DM7" t="n">
         <v>190.05</v>
       </c>
+      <c r="DN7" t="n">
+        <v>186.94</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -27337,6 +27613,9 @@
       <c r="DM8" t="n">
         <v>135.68</v>
       </c>
+      <c r="DN8" t="n">
+        <v>129.13</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -27694,6 +27973,9 @@
       <c r="DM9" t="n">
         <v>99.12</v>
       </c>
+      <c r="DN9" t="n">
+        <v>96.76000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28050,6 +28332,9 @@
       </c>
       <c r="DM10" t="n">
         <v>428.27</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>417.07</v>
       </c>
     </row>
   </sheetData>
@@ -28063,7 +28348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DM10"/>
+  <dimension ref="A1:DN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -28183,6 +28468,7 @@
     <col width="12" customWidth="1" min="115" max="115"/>
     <col width="12" customWidth="1" min="116" max="116"/>
     <col width="12" customWidth="1" min="117" max="117"/>
+    <col width="12" customWidth="1" min="118" max="118"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28541,6 +28827,9 @@
       <c r="DM1" s="1" t="n">
         <v>20260212</v>
       </c>
+      <c r="DN1" s="1" t="n">
+        <v>20260213</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -28898,6 +29187,9 @@
       <c r="DM2" t="n">
         <v>0</v>
       </c>
+      <c r="DN2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -29255,6 +29547,9 @@
       <c r="DM3" t="n">
         <v>0</v>
       </c>
+      <c r="DN3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -29612,6 +29907,9 @@
       <c r="DM4" t="n">
         <v>0</v>
       </c>
+      <c r="DN4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -29969,6 +30267,9 @@
       <c r="DM5" t="n">
         <v>0</v>
       </c>
+      <c r="DN5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -30326,6 +30627,9 @@
       <c r="DM6" t="n">
         <v>0</v>
       </c>
+      <c r="DN6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -30683,6 +30987,9 @@
       <c r="DM7" t="n">
         <v>0</v>
       </c>
+      <c r="DN7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -31040,6 +31347,9 @@
       <c r="DM8" t="n">
         <v>0</v>
       </c>
+      <c r="DN8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -31397,6 +31707,9 @@
       <c r="DM9" t="n">
         <v>0</v>
       </c>
+      <c r="DN9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -31752,6 +32065,9 @@
         <v>0</v>
       </c>
       <c r="DM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -31766,7 +32082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CT10"/>
+  <dimension ref="A1:CU10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -31867,6 +32183,7 @@
     <col width="10" customWidth="1" min="96" max="96"/>
     <col width="10" customWidth="1" min="97" max="97"/>
     <col width="10" customWidth="1" min="98" max="98"/>
+    <col width="10" customWidth="1" min="99" max="99"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32168,6 +32485,9 @@
       <c r="CT1" s="1" t="n">
         <v>20260212</v>
       </c>
+      <c r="CU1" s="1" t="n">
+        <v>20260213</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -32468,6 +32788,9 @@
       <c r="CT2" t="n">
         <v>92</v>
       </c>
+      <c r="CU2" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -32768,6 +33091,9 @@
       <c r="CT3" t="n">
         <v>0</v>
       </c>
+      <c r="CU3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -33068,6 +33394,9 @@
       <c r="CT4" t="n">
         <v>0</v>
       </c>
+      <c r="CU4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -33368,6 +33697,9 @@
       <c r="CT5" t="n">
         <v>12</v>
       </c>
+      <c r="CU5" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -33668,6 +34000,9 @@
       <c r="CT6" t="n">
         <v>0</v>
       </c>
+      <c r="CU6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -33968,6 +34303,9 @@
       <c r="CT7" t="n">
         <v>88</v>
       </c>
+      <c r="CU7" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -34268,6 +34606,9 @@
       <c r="CT8" t="n">
         <v>12</v>
       </c>
+      <c r="CU8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -34568,6 +34909,9 @@
       <c r="CT9" t="n">
         <v>96</v>
       </c>
+      <c r="CU9" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -34867,6 +35211,9 @@
       </c>
       <c r="CT10" t="n">
         <v>60</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -34880,7 +35227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF10"/>
+  <dimension ref="A1:BG10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -34941,6 +35288,7 @@
     <col width="10" customWidth="1" min="56" max="56"/>
     <col width="10" customWidth="1" min="57" max="57"/>
     <col width="10" customWidth="1" min="58" max="58"/>
+    <col width="10" customWidth="1" min="59" max="59"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -35122,6 +35470,9 @@
       <c r="BF1" s="1" t="n">
         <v>20260212</v>
       </c>
+      <c r="BG1" s="1" t="n">
+        <v>20260213</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -35302,6 +35653,9 @@
       <c r="BF2" t="n">
         <v>73</v>
       </c>
+      <c r="BG2" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -35482,6 +35836,9 @@
       <c r="BF3" t="n">
         <v>0</v>
       </c>
+      <c r="BG3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -35662,6 +36019,9 @@
       <c r="BF4" t="n">
         <v>48</v>
       </c>
+      <c r="BG4" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -35842,6 +36202,9 @@
       <c r="BF5" t="n">
         <v>9</v>
       </c>
+      <c r="BG5" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -36022,6 +36385,9 @@
       <c r="BF6" t="n">
         <v>0</v>
       </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -36202,6 +36568,9 @@
       <c r="BF7" t="n">
         <v>89</v>
       </c>
+      <c r="BG7" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -36382,6 +36751,9 @@
       <c r="BF8" t="n">
         <v>9</v>
       </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -36562,6 +36934,9 @@
       <c r="BF9" t="n">
         <v>98</v>
       </c>
+      <c r="BG9" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -36741,6 +37116,9 @@
       </c>
       <c r="BF10" t="n">
         <v>38</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -36754,7 +37132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CT10"/>
+  <dimension ref="A1:CU10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -36855,6 +37233,7 @@
     <col width="10" customWidth="1" min="96" max="96"/>
     <col width="10" customWidth="1" min="97" max="97"/>
     <col width="10" customWidth="1" min="98" max="98"/>
+    <col width="10" customWidth="1" min="99" max="99"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37156,6 +37535,9 @@
       <c r="CT1" s="1" t="n">
         <v>20260212</v>
       </c>
+      <c r="CU1" s="1" t="n">
+        <v>20260213</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -37456,6 +37838,9 @@
       <c r="CT2" t="n">
         <v>57</v>
       </c>
+      <c r="CU2" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -37756,6 +38141,9 @@
       <c r="CT3" t="n">
         <v>-103</v>
       </c>
+      <c r="CU3" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -38056,6 +38444,9 @@
       <c r="CT4" t="n">
         <v>-130</v>
       </c>
+      <c r="CU4" t="n">
+        <v>-115</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -38356,6 +38747,9 @@
       <c r="CT5" t="n">
         <v>-58</v>
       </c>
+      <c r="CU5" t="n">
+        <v>-56</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -38656,6 +39050,9 @@
       <c r="CT6" t="n">
         <v>-72</v>
       </c>
+      <c r="CU6" t="n">
+        <v>-118</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -38956,6 +39353,9 @@
       <c r="CT7" t="n">
         <v>39</v>
       </c>
+      <c r="CU7" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -39256,6 +39656,9 @@
       <c r="CT8" t="n">
         <v>-62</v>
       </c>
+      <c r="CU8" t="n">
+        <v>-77</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -39556,6 +39959,9 @@
       <c r="CT9" t="n">
         <v>74</v>
       </c>
+      <c r="CU9" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -39855,6 +40261,9 @@
       </c>
       <c r="CT10" t="n">
         <v>9</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>-28</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -602,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG10"/>
+  <dimension ref="A1:BH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -664,6 +664,7 @@
     <col width="10" customWidth="1" min="57" max="57"/>
     <col width="10" customWidth="1" min="58" max="58"/>
     <col width="10" customWidth="1" min="59" max="59"/>
+    <col width="10" customWidth="1" min="60" max="60"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -848,6 +849,9 @@
       <c r="BG1" s="1" t="n">
         <v>20260213</v>
       </c>
+      <c r="BH1" s="1" t="n">
+        <v>20260217</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1031,6 +1035,9 @@
       <c r="BG2" t="n">
         <v>-37</v>
       </c>
+      <c r="BH2" t="n">
+        <v>-65</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1214,6 +1221,9 @@
       <c r="BG3" t="n">
         <v>-150</v>
       </c>
+      <c r="BH3" t="n">
+        <v>-142</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1397,6 +1407,9 @@
       <c r="BG4" t="n">
         <v>-41</v>
       </c>
+      <c r="BH4" t="n">
+        <v>-59</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1580,6 +1593,9 @@
       <c r="BG5" t="n">
         <v>-111</v>
       </c>
+      <c r="BH5" t="n">
+        <v>-106</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1763,6 +1779,9 @@
       <c r="BG6" t="n">
         <v>-91</v>
       </c>
+      <c r="BH6" t="n">
+        <v>-85</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1946,6 +1965,9 @@
       <c r="BG7" t="n">
         <v>29</v>
       </c>
+      <c r="BH7" t="n">
+        <v>-9</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2129,6 +2151,9 @@
       <c r="BG8" t="n">
         <v>-117</v>
       </c>
+      <c r="BH8" t="n">
+        <v>-104</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2312,6 +2337,9 @@
       <c r="BG9" t="n">
         <v>71</v>
       </c>
+      <c r="BH9" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2493,6 +2521,9 @@
         <v>-21</v>
       </c>
       <c r="BG10" t="n">
+        <v>-45</v>
+      </c>
+      <c r="BH10" t="n">
         <v>-45</v>
       </c>
     </row>
@@ -2507,7 +2538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU10"/>
+  <dimension ref="A1:CV10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2609,6 +2640,7 @@
     <col width="12" customWidth="1" min="97" max="97"/>
     <col width="12" customWidth="1" min="98" max="98"/>
     <col width="12" customWidth="1" min="99" max="99"/>
+    <col width="12" customWidth="1" min="100" max="100"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3107,6 +3139,11 @@
           <t>20260213</t>
         </is>
       </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>20260217</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3410,6 +3447,9 @@
       <c r="CU2" t="n">
         <v>100</v>
       </c>
+      <c r="CV2" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3713,6 +3753,9 @@
       <c r="CU3" t="n">
         <v>87</v>
       </c>
+      <c r="CV3" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4016,6 +4059,9 @@
       <c r="CU4" t="n">
         <v>94</v>
       </c>
+      <c r="CV4" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4319,6 +4365,9 @@
       <c r="CU5" t="n">
         <v>93</v>
       </c>
+      <c r="CV5" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4622,6 +4671,9 @@
       <c r="CU6" t="n">
         <v>91</v>
       </c>
+      <c r="CV6" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4925,6 +4977,9 @@
       <c r="CU7" t="n">
         <v>101</v>
       </c>
+      <c r="CV7" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5228,6 +5283,9 @@
       <c r="CU8" t="n">
         <v>85</v>
       </c>
+      <c r="CV8" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5531,6 +5589,9 @@
       <c r="CU9" t="n">
         <v>101</v>
       </c>
+      <c r="CV9" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5833,6 +5894,9 @@
       </c>
       <c r="CU10" t="n">
         <v>98</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -5846,7 +5910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5929,6 +5993,7 @@
     <col width="12" customWidth="1" min="78" max="78"/>
     <col width="12" customWidth="1" min="79" max="79"/>
     <col width="12" customWidth="1" min="80" max="80"/>
+    <col width="12" customWidth="1" min="81" max="81"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6332,6 +6397,11 @@
           <t>20260213</t>
         </is>
       </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>20260217</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6578,6 +6648,9 @@
       <c r="CB2" t="n">
         <v>30.94</v>
       </c>
+      <c r="CC2" t="n">
+        <v>27.54</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6824,6 +6897,9 @@
       <c r="CB3" t="n">
         <v>98.47</v>
       </c>
+      <c r="CC3" t="n">
+        <v>103.23</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7070,6 +7146,9 @@
       <c r="CB4" t="n">
         <v>20.49</v>
       </c>
+      <c r="CC4" t="n">
+        <v>40.02</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7316,6 +7395,9 @@
       <c r="CB5" t="n">
         <v>48.87</v>
       </c>
+      <c r="CC5" t="n">
+        <v>42.77</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7562,6 +7644,9 @@
       <c r="CB6" t="n">
         <v>2.9</v>
       </c>
+      <c r="CC6" t="n">
+        <v>3.02</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7808,6 +7893,9 @@
       <c r="CB7" t="n">
         <v>46.41</v>
       </c>
+      <c r="CC7" t="n">
+        <v>42.7</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8054,6 +8142,9 @@
       <c r="CB8" t="n">
         <v>34.48</v>
       </c>
+      <c r="CC8" t="n">
+        <v>29.36</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8300,6 +8391,9 @@
       <c r="CB9" t="n">
         <v>-33.13</v>
       </c>
+      <c r="CC9" t="n">
+        <v>-33.68</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8545,6 +8639,9 @@
       </c>
       <c r="CB10" t="n">
         <v>-0.28</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -8558,7 +8655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG10"/>
+  <dimension ref="A1:BH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8620,6 +8717,7 @@
     <col width="12" customWidth="1" min="57" max="57"/>
     <col width="12" customWidth="1" min="58" max="58"/>
     <col width="12" customWidth="1" min="59" max="59"/>
+    <col width="12" customWidth="1" min="60" max="60"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8918,6 +9016,11 @@
           <t>20260213</t>
         </is>
       </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>20260217</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9101,6 +9204,9 @@
       <c r="BG2" t="n">
         <v>0</v>
       </c>
+      <c r="BH2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9284,6 +9390,9 @@
       <c r="BG3" t="n">
         <v>0</v>
       </c>
+      <c r="BH3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9467,6 +9576,9 @@
       <c r="BG4" t="n">
         <v>0</v>
       </c>
+      <c r="BH4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9650,6 +9762,9 @@
       <c r="BG5" t="n">
         <v>0</v>
       </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9833,6 +9948,9 @@
       <c r="BG6" t="n">
         <v>0</v>
       </c>
+      <c r="BH6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10016,6 +10134,9 @@
       <c r="BG7" t="n">
         <v>0</v>
       </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10199,6 +10320,9 @@
       <c r="BG8" t="n">
         <v>0</v>
       </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10382,6 +10506,9 @@
       <c r="BG9" t="n">
         <v>0</v>
       </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10563,6 +10690,9 @@
         <v>0</v>
       </c>
       <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10577,7 +10707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CK10"/>
+  <dimension ref="A1:CL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10669,6 +10799,7 @@
     <col width="10" customWidth="1" min="87" max="87"/>
     <col width="10" customWidth="1" min="88" max="88"/>
     <col width="10" customWidth="1" min="89" max="89"/>
+    <col width="10" customWidth="1" min="90" max="90"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10943,6 +11074,9 @@
       <c r="CK1" s="1" t="n">
         <v>20260213</v>
       </c>
+      <c r="CL1" s="1" t="n">
+        <v>20260217</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11216,6 +11350,9 @@
       <c r="CK2" t="n">
         <v>-5</v>
       </c>
+      <c r="CL2" t="n">
+        <v>-34</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11489,6 +11626,9 @@
       <c r="CK3" t="n">
         <v>-122</v>
       </c>
+      <c r="CL3" t="n">
+        <v>-111</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11762,6 +11902,9 @@
       <c r="CK4" t="n">
         <v>-110</v>
       </c>
+      <c r="CL4" t="n">
+        <v>-118</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12035,6 +12178,9 @@
       <c r="CK5" t="n">
         <v>-75</v>
       </c>
+      <c r="CL5" t="n">
+        <v>-70</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12308,6 +12454,9 @@
       <c r="CK6" t="n">
         <v>-112</v>
       </c>
+      <c r="CL6" t="n">
+        <v>-92</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12581,6 +12730,9 @@
       <c r="CK7" t="n">
         <v>12</v>
       </c>
+      <c r="CL7" t="n">
+        <v>-25</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12854,6 +13006,9 @@
       <c r="CK8" t="n">
         <v>-90</v>
       </c>
+      <c r="CL8" t="n">
+        <v>-76</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13127,6 +13282,9 @@
       <c r="CK9" t="n">
         <v>39</v>
       </c>
+      <c r="CL9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13399,6 +13557,9 @@
       </c>
       <c r="CK10" t="n">
         <v>-46</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>-42</v>
       </c>
     </row>
   </sheetData>
@@ -13412,7 +13573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DN10"/>
+  <dimension ref="A1:DO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13533,6 +13694,7 @@
     <col width="12" customWidth="1" min="116" max="116"/>
     <col width="12" customWidth="1" min="117" max="117"/>
     <col width="12" customWidth="1" min="118" max="118"/>
+    <col width="12" customWidth="1" min="119" max="119"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13894,6 +14056,9 @@
       <c r="DN1" s="1" t="n">
         <v>20260213</v>
       </c>
+      <c r="DO1" s="1" t="n">
+        <v>20260217</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14254,6 +14419,9 @@
       <c r="DN2" t="n">
         <v>261.73</v>
       </c>
+      <c r="DO2" t="n">
+        <v>255.78</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14614,6 +14782,9 @@
       <c r="DN3" t="n">
         <v>199.6</v>
       </c>
+      <c r="DO3" t="n">
+        <v>198.79</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14974,6 +15145,9 @@
       <c r="DN4" t="n">
         <v>309</v>
       </c>
+      <c r="DO4" t="n">
+        <v>305.72</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15334,6 +15508,9 @@
       <c r="DN5" t="n">
         <v>401.84</v>
       </c>
+      <c r="DO5" t="n">
+        <v>401.32</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15694,6 +15871,9 @@
       <c r="DN6" t="n">
         <v>75.86</v>
       </c>
+      <c r="DO6" t="n">
+        <v>76.87</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16054,6 +16234,9 @@
       <c r="DN7" t="n">
         <v>186.94</v>
       </c>
+      <c r="DO7" t="n">
+        <v>182.81</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16414,6 +16597,9 @@
       <c r="DN8" t="n">
         <v>129.13</v>
       </c>
+      <c r="DO8" t="n">
+        <v>131.41</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16774,6 +16960,9 @@
       <c r="DN9" t="n">
         <v>96.76000000000001</v>
       </c>
+      <c r="DO9" t="n">
+        <v>93.79000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17133,6 +17322,9 @@
       </c>
       <c r="DN10" t="n">
         <v>417.07</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>417.44</v>
       </c>
     </row>
   </sheetData>
@@ -17146,7 +17338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DN10"/>
+  <dimension ref="A1:DO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17267,6 +17459,7 @@
     <col width="12" customWidth="1" min="116" max="116"/>
     <col width="12" customWidth="1" min="117" max="117"/>
     <col width="12" customWidth="1" min="118" max="118"/>
+    <col width="12" customWidth="1" min="119" max="119"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17628,6 +17821,9 @@
       <c r="DN1" s="1" t="n">
         <v>20260213</v>
       </c>
+      <c r="DO1" s="1" t="n">
+        <v>20260217</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17988,6 +18184,9 @@
       <c r="DN2" t="n">
         <v>261.73</v>
       </c>
+      <c r="DO2" t="n">
+        <v>255.78</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18348,6 +18547,9 @@
       <c r="DN3" t="n">
         <v>199.6</v>
       </c>
+      <c r="DO3" t="n">
+        <v>198.79</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18708,6 +18910,9 @@
       <c r="DN4" t="n">
         <v>309</v>
       </c>
+      <c r="DO4" t="n">
+        <v>305.72</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19068,6 +19273,9 @@
       <c r="DN5" t="n">
         <v>401.84</v>
       </c>
+      <c r="DO5" t="n">
+        <v>401.32</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19428,6 +19636,9 @@
       <c r="DN6" t="n">
         <v>75.86</v>
       </c>
+      <c r="DO6" t="n">
+        <v>76.87</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19788,6 +19999,9 @@
       <c r="DN7" t="n">
         <v>186.94</v>
       </c>
+      <c r="DO7" t="n">
+        <v>182.81</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20148,6 +20362,9 @@
       <c r="DN8" t="n">
         <v>129.13</v>
       </c>
+      <c r="DO8" t="n">
+        <v>131.41</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20508,6 +20725,9 @@
       <c r="DN9" t="n">
         <v>96.76000000000001</v>
       </c>
+      <c r="DO9" t="n">
+        <v>93.79000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20867,6 +21087,9 @@
       </c>
       <c r="DN10" t="n">
         <v>417.07</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>417.44</v>
       </c>
     </row>
   </sheetData>
@@ -20880,7 +21103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DN10"/>
+  <dimension ref="A1:DO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21001,6 +21224,7 @@
     <col width="12" customWidth="1" min="116" max="116"/>
     <col width="12" customWidth="1" min="117" max="117"/>
     <col width="12" customWidth="1" min="118" max="118"/>
+    <col width="12" customWidth="1" min="119" max="119"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21362,6 +21586,9 @@
       <c r="DN1" s="1" t="n">
         <v>20260213</v>
       </c>
+      <c r="DO1" s="1" t="n">
+        <v>20260217</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21722,6 +21949,9 @@
       <c r="DN2" t="n">
         <v>261.73</v>
       </c>
+      <c r="DO2" t="n">
+        <v>255.78</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22082,6 +22312,9 @@
       <c r="DN3" t="n">
         <v>199.6</v>
       </c>
+      <c r="DO3" t="n">
+        <v>198.79</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22442,6 +22675,9 @@
       <c r="DN4" t="n">
         <v>309</v>
       </c>
+      <c r="DO4" t="n">
+        <v>305.72</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -22802,6 +23038,9 @@
       <c r="DN5" t="n">
         <v>401.84</v>
       </c>
+      <c r="DO5" t="n">
+        <v>401.32</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23162,6 +23401,9 @@
       <c r="DN6" t="n">
         <v>75.86</v>
       </c>
+      <c r="DO6" t="n">
+        <v>76.87</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23522,6 +23764,9 @@
       <c r="DN7" t="n">
         <v>186.94</v>
       </c>
+      <c r="DO7" t="n">
+        <v>182.81</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23882,6 +24127,9 @@
       <c r="DN8" t="n">
         <v>129.13</v>
       </c>
+      <c r="DO8" t="n">
+        <v>131.41</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24242,6 +24490,9 @@
       <c r="DN9" t="n">
         <v>96.76000000000001</v>
       </c>
+      <c r="DO9" t="n">
+        <v>93.79000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24601,6 +24852,9 @@
       </c>
       <c r="DN10" t="n">
         <v>417.07</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>417.44</v>
       </c>
     </row>
   </sheetData>
@@ -24614,7 +24868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DN10"/>
+  <dimension ref="A1:DO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24735,6 +24989,7 @@
     <col width="12" customWidth="1" min="116" max="116"/>
     <col width="12" customWidth="1" min="117" max="117"/>
     <col width="12" customWidth="1" min="118" max="118"/>
+    <col width="12" customWidth="1" min="119" max="119"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25096,6 +25351,9 @@
       <c r="DN1" s="1" t="n">
         <v>20260213</v>
       </c>
+      <c r="DO1" s="1" t="n">
+        <v>20260217</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25456,6 +25714,9 @@
       <c r="DN2" t="n">
         <v>261.73</v>
       </c>
+      <c r="DO2" t="n">
+        <v>255.78</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25816,6 +26077,9 @@
       <c r="DN3" t="n">
         <v>199.6</v>
       </c>
+      <c r="DO3" t="n">
+        <v>198.79</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -26176,6 +26440,9 @@
       <c r="DN4" t="n">
         <v>309</v>
       </c>
+      <c r="DO4" t="n">
+        <v>305.72</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -26536,6 +26803,9 @@
       <c r="DN5" t="n">
         <v>401.84</v>
       </c>
+      <c r="DO5" t="n">
+        <v>401.32</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -26896,6 +27166,9 @@
       <c r="DN6" t="n">
         <v>75.86</v>
       </c>
+      <c r="DO6" t="n">
+        <v>76.87</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -27256,6 +27529,9 @@
       <c r="DN7" t="n">
         <v>186.94</v>
       </c>
+      <c r="DO7" t="n">
+        <v>182.81</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -27616,6 +27892,9 @@
       <c r="DN8" t="n">
         <v>129.13</v>
       </c>
+      <c r="DO8" t="n">
+        <v>131.41</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -27976,6 +28255,9 @@
       <c r="DN9" t="n">
         <v>96.76000000000001</v>
       </c>
+      <c r="DO9" t="n">
+        <v>93.79000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28335,6 +28617,9 @@
       </c>
       <c r="DN10" t="n">
         <v>417.07</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>417.44</v>
       </c>
     </row>
   </sheetData>
@@ -28348,7 +28633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DN10"/>
+  <dimension ref="A1:DO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -28469,6 +28754,7 @@
     <col width="12" customWidth="1" min="116" max="116"/>
     <col width="12" customWidth="1" min="117" max="117"/>
     <col width="12" customWidth="1" min="118" max="118"/>
+    <col width="12" customWidth="1" min="119" max="119"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28830,6 +29116,9 @@
       <c r="DN1" s="1" t="n">
         <v>20260213</v>
       </c>
+      <c r="DO1" s="1" t="n">
+        <v>20260217</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -29190,6 +29479,9 @@
       <c r="DN2" t="n">
         <v>0</v>
       </c>
+      <c r="DO2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -29550,6 +29842,9 @@
       <c r="DN3" t="n">
         <v>0</v>
       </c>
+      <c r="DO3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -29910,6 +30205,9 @@
       <c r="DN4" t="n">
         <v>0</v>
       </c>
+      <c r="DO4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -30270,6 +30568,9 @@
       <c r="DN5" t="n">
         <v>0</v>
       </c>
+      <c r="DO5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -30630,6 +30931,9 @@
       <c r="DN6" t="n">
         <v>0</v>
       </c>
+      <c r="DO6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -30990,6 +31294,9 @@
       <c r="DN7" t="n">
         <v>0</v>
       </c>
+      <c r="DO7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -31350,6 +31657,9 @@
       <c r="DN8" t="n">
         <v>0</v>
       </c>
+      <c r="DO8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -31710,6 +32020,9 @@
       <c r="DN9" t="n">
         <v>0</v>
       </c>
+      <c r="DO9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -32068,6 +32381,9 @@
         <v>0</v>
       </c>
       <c r="DN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -32082,7 +32398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU10"/>
+  <dimension ref="A1:CV10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -32184,6 +32500,7 @@
     <col width="10" customWidth="1" min="97" max="97"/>
     <col width="10" customWidth="1" min="98" max="98"/>
     <col width="10" customWidth="1" min="99" max="99"/>
+    <col width="10" customWidth="1" min="100" max="100"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32488,6 +32805,9 @@
       <c r="CU1" s="1" t="n">
         <v>20260213</v>
       </c>
+      <c r="CV1" s="1" t="n">
+        <v>20260217</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -32791,6 +33111,9 @@
       <c r="CU2" t="n">
         <v>48</v>
       </c>
+      <c r="CV2" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -33094,6 +33417,9 @@
       <c r="CU3" t="n">
         <v>0</v>
       </c>
+      <c r="CV3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -33397,6 +33723,9 @@
       <c r="CU4" t="n">
         <v>0</v>
       </c>
+      <c r="CV4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -33700,6 +34029,9 @@
       <c r="CU5" t="n">
         <v>9</v>
       </c>
+      <c r="CV5" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -34003,6 +34335,9 @@
       <c r="CU6" t="n">
         <v>0</v>
       </c>
+      <c r="CV6" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -34306,6 +34641,9 @@
       <c r="CU7" t="n">
         <v>73</v>
       </c>
+      <c r="CV7" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -34609,6 +34947,9 @@
       <c r="CU8" t="n">
         <v>0</v>
       </c>
+      <c r="CV8" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -34912,6 +35253,9 @@
       <c r="CU9" t="n">
         <v>64</v>
       </c>
+      <c r="CV9" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -35214,6 +35558,9 @@
       </c>
       <c r="CU10" t="n">
         <v>38</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -35227,7 +35574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG10"/>
+  <dimension ref="A1:BH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -35289,6 +35636,7 @@
     <col width="10" customWidth="1" min="57" max="57"/>
     <col width="10" customWidth="1" min="58" max="58"/>
     <col width="10" customWidth="1" min="59" max="59"/>
+    <col width="10" customWidth="1" min="60" max="60"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -35473,6 +35821,9 @@
       <c r="BG1" s="1" t="n">
         <v>20260213</v>
       </c>
+      <c r="BH1" s="1" t="n">
+        <v>20260217</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -35656,6 +36007,9 @@
       <c r="BG2" t="n">
         <v>38</v>
       </c>
+      <c r="BH2" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -35839,6 +36193,9 @@
       <c r="BG3" t="n">
         <v>0</v>
       </c>
+      <c r="BH3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -36022,6 +36379,9 @@
       <c r="BG4" t="n">
         <v>45</v>
       </c>
+      <c r="BH4" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -36205,6 +36565,9 @@
       <c r="BG5" t="n">
         <v>8</v>
       </c>
+      <c r="BH5" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -36388,6 +36751,9 @@
       <c r="BG6" t="n">
         <v>0</v>
       </c>
+      <c r="BH6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -36571,6 +36937,9 @@
       <c r="BG7" t="n">
         <v>74</v>
       </c>
+      <c r="BH7" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -36754,6 +37123,9 @@
       <c r="BG8" t="n">
         <v>0</v>
       </c>
+      <c r="BH8" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -36937,6 +37309,9 @@
       <c r="BG9" t="n">
         <v>84</v>
       </c>
+      <c r="BH9" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -37119,6 +37494,9 @@
       </c>
       <c r="BG10" t="n">
         <v>26</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -37132,7 +37510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU10"/>
+  <dimension ref="A1:CV10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -37234,6 +37612,7 @@
     <col width="10" customWidth="1" min="97" max="97"/>
     <col width="10" customWidth="1" min="98" max="98"/>
     <col width="10" customWidth="1" min="99" max="99"/>
+    <col width="10" customWidth="1" min="100" max="100"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37538,6 +37917,9 @@
       <c r="CU1" s="1" t="n">
         <v>20260213</v>
       </c>
+      <c r="CV1" s="1" t="n">
+        <v>20260217</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -37841,6 +38223,9 @@
       <c r="CU2" t="n">
         <v>-5</v>
       </c>
+      <c r="CV2" t="n">
+        <v>-31</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -38144,6 +38529,9 @@
       <c r="CU3" t="n">
         <v>-100</v>
       </c>
+      <c r="CV3" t="n">
+        <v>-89</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -38447,6 +38835,9 @@
       <c r="CU4" t="n">
         <v>-115</v>
       </c>
+      <c r="CV4" t="n">
+        <v>-109</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -38750,6 +39141,9 @@
       <c r="CU5" t="n">
         <v>-56</v>
       </c>
+      <c r="CV5" t="n">
+        <v>-52</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -39053,6 +39447,9 @@
       <c r="CU6" t="n">
         <v>-118</v>
       </c>
+      <c r="CV6" t="n">
+        <v>-90</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -39356,6 +39753,9 @@
       <c r="CU7" t="n">
         <v>14</v>
       </c>
+      <c r="CV7" t="n">
+        <v>-17</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -39659,6 +40059,9 @@
       <c r="CU8" t="n">
         <v>-77</v>
       </c>
+      <c r="CV8" t="n">
+        <v>-63</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -39962,6 +40365,9 @@
       <c r="CU9" t="n">
         <v>21</v>
       </c>
+      <c r="CV9" t="n">
+        <v>-46</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -40264,6 +40670,9 @@
       </c>
       <c r="CU10" t="n">
         <v>-28</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>-23</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -602,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH10"/>
+  <dimension ref="A1:BI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -665,6 +665,7 @@
     <col width="10" customWidth="1" min="58" max="58"/>
     <col width="10" customWidth="1" min="59" max="59"/>
     <col width="10" customWidth="1" min="60" max="60"/>
+    <col width="10" customWidth="1" min="61" max="61"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -852,6 +853,9 @@
       <c r="BH1" s="1" t="n">
         <v>20260217</v>
       </c>
+      <c r="BI1" s="1" t="n">
+        <v>20260218</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1038,6 +1042,9 @@
       <c r="BH2" t="n">
         <v>-65</v>
       </c>
+      <c r="BI2" t="n">
+        <v>-24</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1224,6 +1231,9 @@
       <c r="BH3" t="n">
         <v>-142</v>
       </c>
+      <c r="BI3" t="n">
+        <v>-123</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1410,6 +1420,9 @@
       <c r="BH4" t="n">
         <v>-59</v>
       </c>
+      <c r="BI4" t="n">
+        <v>-77</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1596,6 +1609,9 @@
       <c r="BH5" t="n">
         <v>-106</v>
       </c>
+      <c r="BI5" t="n">
+        <v>-107</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1782,6 +1798,9 @@
       <c r="BH6" t="n">
         <v>-85</v>
       </c>
+      <c r="BI6" t="n">
+        <v>-82</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1968,6 +1987,9 @@
       <c r="BH7" t="n">
         <v>-9</v>
       </c>
+      <c r="BI7" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2154,6 +2176,9 @@
       <c r="BH8" t="n">
         <v>-104</v>
       </c>
+      <c r="BI8" t="n">
+        <v>-95</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2340,6 +2365,9 @@
       <c r="BH9" t="n">
         <v>42</v>
       </c>
+      <c r="BI9" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2525,6 +2553,9 @@
       </c>
       <c r="BH10" t="n">
         <v>-45</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>-60</v>
       </c>
     </row>
   </sheetData>
@@ -2538,7 +2569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CV10"/>
+  <dimension ref="A1:CW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2641,6 +2672,7 @@
     <col width="12" customWidth="1" min="98" max="98"/>
     <col width="12" customWidth="1" min="99" max="99"/>
     <col width="12" customWidth="1" min="100" max="100"/>
+    <col width="12" customWidth="1" min="101" max="101"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3144,6 +3176,11 @@
           <t>20260217</t>
         </is>
       </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>20260218</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3450,6 +3487,9 @@
       <c r="CV2" t="n">
         <v>97</v>
       </c>
+      <c r="CW2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3756,6 +3796,9 @@
       <c r="CV3" t="n">
         <v>88</v>
       </c>
+      <c r="CW3" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4062,6 +4105,9 @@
       <c r="CV4" t="n">
         <v>93</v>
       </c>
+      <c r="CW4" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4368,6 +4414,9 @@
       <c r="CV5" t="n">
         <v>93</v>
       </c>
+      <c r="CW5" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4674,6 +4723,9 @@
       <c r="CV6" t="n">
         <v>93</v>
       </c>
+      <c r="CW6" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4980,6 +5032,9 @@
       <c r="CV7" t="n">
         <v>99</v>
       </c>
+      <c r="CW7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5286,6 +5341,9 @@
       <c r="CV8" t="n">
         <v>88</v>
       </c>
+      <c r="CW8" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5592,6 +5650,9 @@
       <c r="CV9" t="n">
         <v>98</v>
       </c>
+      <c r="CW9" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5897,6 +5958,9 @@
       </c>
       <c r="CV10" t="n">
         <v>99</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -5910,7 +5974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CC10"/>
+  <dimension ref="A1:CD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5994,6 +6058,7 @@
     <col width="12" customWidth="1" min="79" max="79"/>
     <col width="12" customWidth="1" min="80" max="80"/>
     <col width="12" customWidth="1" min="81" max="81"/>
+    <col width="12" customWidth="1" min="82" max="82"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6402,6 +6467,11 @@
           <t>20260217</t>
         </is>
       </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>20260218</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6651,6 +6721,9 @@
       <c r="CC2" t="n">
         <v>27.54</v>
       </c>
+      <c r="CD2" t="n">
+        <v>18.24</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6900,6 +6973,9 @@
       <c r="CC3" t="n">
         <v>103.23</v>
       </c>
+      <c r="CD3" t="n">
+        <v>102.63</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7149,6 +7225,9 @@
       <c r="CC4" t="n">
         <v>40.02</v>
       </c>
+      <c r="CD4" t="n">
+        <v>57.68</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7398,6 +7477,9 @@
       <c r="CC5" t="n">
         <v>42.77</v>
       </c>
+      <c r="CD5" t="n">
+        <v>38.5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7647,6 +7729,9 @@
       <c r="CC6" t="n">
         <v>3.02</v>
       </c>
+      <c r="CD6" t="n">
+        <v>1.88</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7896,6 +7981,9 @@
       <c r="CC7" t="n">
         <v>42.7</v>
       </c>
+      <c r="CD7" t="n">
+        <v>33.55</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8145,6 +8233,9 @@
       <c r="CC8" t="n">
         <v>29.36</v>
       </c>
+      <c r="CD8" t="n">
+        <v>23.34</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8394,6 +8485,9 @@
       <c r="CC9" t="n">
         <v>-33.68</v>
       </c>
+      <c r="CD9" t="n">
+        <v>-34.25</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8642,6 +8736,9 @@
       </c>
       <c r="CC10" t="n">
         <v>0.3</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>5.14</v>
       </c>
     </row>
   </sheetData>
@@ -8655,7 +8752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH10"/>
+  <dimension ref="A1:BI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8718,6 +8815,7 @@
     <col width="12" customWidth="1" min="58" max="58"/>
     <col width="12" customWidth="1" min="59" max="59"/>
     <col width="12" customWidth="1" min="60" max="60"/>
+    <col width="12" customWidth="1" min="61" max="61"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9021,6 +9119,11 @@
           <t>20260217</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>20260218</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9207,6 +9310,9 @@
       <c r="BH2" t="n">
         <v>0</v>
       </c>
+      <c r="BI2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9393,6 +9499,9 @@
       <c r="BH3" t="n">
         <v>0</v>
       </c>
+      <c r="BI3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9579,6 +9688,9 @@
       <c r="BH4" t="n">
         <v>0</v>
       </c>
+      <c r="BI4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9765,6 +9877,9 @@
       <c r="BH5" t="n">
         <v>0</v>
       </c>
+      <c r="BI5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9951,6 +10066,9 @@
       <c r="BH6" t="n">
         <v>0</v>
       </c>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10137,6 +10255,9 @@
       <c r="BH7" t="n">
         <v>0</v>
       </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10323,6 +10444,9 @@
       <c r="BH8" t="n">
         <v>0</v>
       </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10509,6 +10633,9 @@
       <c r="BH9" t="n">
         <v>0</v>
       </c>
+      <c r="BI9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10693,6 +10820,9 @@
         <v>0</v>
       </c>
       <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10707,7 +10837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CL10"/>
+  <dimension ref="A1:CM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10800,6 +10930,7 @@
     <col width="10" customWidth="1" min="88" max="88"/>
     <col width="10" customWidth="1" min="89" max="89"/>
     <col width="10" customWidth="1" min="90" max="90"/>
+    <col width="10" customWidth="1" min="91" max="91"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11077,6 +11208,9 @@
       <c r="CL1" s="1" t="n">
         <v>20260217</v>
       </c>
+      <c r="CM1" s="1" t="n">
+        <v>20260218</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11353,6 +11487,9 @@
       <c r="CL2" t="n">
         <v>-34</v>
       </c>
+      <c r="CM2" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11629,6 +11766,9 @@
       <c r="CL3" t="n">
         <v>-111</v>
       </c>
+      <c r="CM3" t="n">
+        <v>-93</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11905,6 +12045,9 @@
       <c r="CL4" t="n">
         <v>-118</v>
       </c>
+      <c r="CM4" t="n">
+        <v>-123</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12181,6 +12324,9 @@
       <c r="CL5" t="n">
         <v>-70</v>
       </c>
+      <c r="CM5" t="n">
+        <v>-72</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12457,6 +12603,9 @@
       <c r="CL6" t="n">
         <v>-92</v>
       </c>
+      <c r="CM6" t="n">
+        <v>-84</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12733,6 +12882,9 @@
       <c r="CL7" t="n">
         <v>-25</v>
       </c>
+      <c r="CM7" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13009,6 +13161,9 @@
       <c r="CL8" t="n">
         <v>-76</v>
       </c>
+      <c r="CM8" t="n">
+        <v>-67</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13285,6 +13440,9 @@
       <c r="CL9" t="n">
         <v>1</v>
       </c>
+      <c r="CM9" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13560,6 +13718,9 @@
       </c>
       <c r="CL10" t="n">
         <v>-42</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>-62</v>
       </c>
     </row>
   </sheetData>
@@ -13573,7 +13734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DO10"/>
+  <dimension ref="A1:DP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13695,6 +13856,7 @@
     <col width="12" customWidth="1" min="117" max="117"/>
     <col width="12" customWidth="1" min="118" max="118"/>
     <col width="12" customWidth="1" min="119" max="119"/>
+    <col width="12" customWidth="1" min="120" max="120"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14059,6 +14221,9 @@
       <c r="DO1" s="1" t="n">
         <v>20260217</v>
       </c>
+      <c r="DP1" s="1" t="n">
+        <v>20260218</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14422,6 +14587,9 @@
       <c r="DO2" t="n">
         <v>255.78</v>
       </c>
+      <c r="DP2" t="n">
+        <v>263.88</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14785,6 +14953,9 @@
       <c r="DO3" t="n">
         <v>198.79</v>
       </c>
+      <c r="DP3" t="n">
+        <v>201.15</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15148,6 +15319,9 @@
       <c r="DO4" t="n">
         <v>305.72</v>
       </c>
+      <c r="DP4" t="n">
+        <v>302.02</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15511,6 +15685,9 @@
       <c r="DO5" t="n">
         <v>401.32</v>
       </c>
+      <c r="DP5" t="n">
+        <v>396.86</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15874,6 +16051,9 @@
       <c r="DO6" t="n">
         <v>76.87</v>
       </c>
+      <c r="DP6" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16237,6 +16417,9 @@
       <c r="DO7" t="n">
         <v>182.81</v>
       </c>
+      <c r="DP7" t="n">
+        <v>184.97</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16600,6 +16783,9 @@
       <c r="DO8" t="n">
         <v>131.41</v>
       </c>
+      <c r="DP8" t="n">
+        <v>133.02</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16963,6 +17149,9 @@
       <c r="DO9" t="n">
         <v>93.79000000000001</v>
       </c>
+      <c r="DP9" t="n">
+        <v>95.39</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17325,6 +17514,9 @@
       </c>
       <c r="DO10" t="n">
         <v>417.44</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>410.63</v>
       </c>
     </row>
   </sheetData>
@@ -17338,7 +17530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DO10"/>
+  <dimension ref="A1:DP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17460,6 +17652,7 @@
     <col width="12" customWidth="1" min="117" max="117"/>
     <col width="12" customWidth="1" min="118" max="118"/>
     <col width="12" customWidth="1" min="119" max="119"/>
+    <col width="12" customWidth="1" min="120" max="120"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17824,6 +18017,9 @@
       <c r="DO1" s="1" t="n">
         <v>20260217</v>
       </c>
+      <c r="DP1" s="1" t="n">
+        <v>20260218</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18187,6 +18383,9 @@
       <c r="DO2" t="n">
         <v>255.78</v>
       </c>
+      <c r="DP2" t="n">
+        <v>263.88</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18550,6 +18749,9 @@
       <c r="DO3" t="n">
         <v>198.79</v>
       </c>
+      <c r="DP3" t="n">
+        <v>201.15</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18913,6 +19115,9 @@
       <c r="DO4" t="n">
         <v>305.72</v>
       </c>
+      <c r="DP4" t="n">
+        <v>302.02</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19276,6 +19481,9 @@
       <c r="DO5" t="n">
         <v>401.32</v>
       </c>
+      <c r="DP5" t="n">
+        <v>396.86</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19639,6 +19847,9 @@
       <c r="DO6" t="n">
         <v>76.87</v>
       </c>
+      <c r="DP6" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20002,6 +20213,9 @@
       <c r="DO7" t="n">
         <v>182.81</v>
       </c>
+      <c r="DP7" t="n">
+        <v>184.97</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20365,6 +20579,9 @@
       <c r="DO8" t="n">
         <v>131.41</v>
       </c>
+      <c r="DP8" t="n">
+        <v>133.02</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20728,6 +20945,9 @@
       <c r="DO9" t="n">
         <v>93.79000000000001</v>
       </c>
+      <c r="DP9" t="n">
+        <v>95.39</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21090,6 +21310,9 @@
       </c>
       <c r="DO10" t="n">
         <v>417.44</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>410.63</v>
       </c>
     </row>
   </sheetData>
@@ -21103,7 +21326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DO10"/>
+  <dimension ref="A1:DP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21225,6 +21448,7 @@
     <col width="12" customWidth="1" min="117" max="117"/>
     <col width="12" customWidth="1" min="118" max="118"/>
     <col width="12" customWidth="1" min="119" max="119"/>
+    <col width="12" customWidth="1" min="120" max="120"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21589,6 +21813,9 @@
       <c r="DO1" s="1" t="n">
         <v>20260217</v>
       </c>
+      <c r="DP1" s="1" t="n">
+        <v>20260218</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21952,6 +22179,9 @@
       <c r="DO2" t="n">
         <v>255.78</v>
       </c>
+      <c r="DP2" t="n">
+        <v>263.88</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22315,6 +22545,9 @@
       <c r="DO3" t="n">
         <v>198.79</v>
       </c>
+      <c r="DP3" t="n">
+        <v>201.15</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22678,6 +22911,9 @@
       <c r="DO4" t="n">
         <v>305.72</v>
       </c>
+      <c r="DP4" t="n">
+        <v>302.02</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23041,6 +23277,9 @@
       <c r="DO5" t="n">
         <v>401.32</v>
       </c>
+      <c r="DP5" t="n">
+        <v>396.86</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23404,6 +23643,9 @@
       <c r="DO6" t="n">
         <v>76.87</v>
       </c>
+      <c r="DP6" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23767,6 +24009,9 @@
       <c r="DO7" t="n">
         <v>182.81</v>
       </c>
+      <c r="DP7" t="n">
+        <v>184.97</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24130,6 +24375,9 @@
       <c r="DO8" t="n">
         <v>131.41</v>
       </c>
+      <c r="DP8" t="n">
+        <v>133.02</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24493,6 +24741,9 @@
       <c r="DO9" t="n">
         <v>93.79000000000001</v>
       </c>
+      <c r="DP9" t="n">
+        <v>95.39</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24855,6 +25106,9 @@
       </c>
       <c r="DO10" t="n">
         <v>417.44</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>410.63</v>
       </c>
     </row>
   </sheetData>
@@ -24868,7 +25122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DO10"/>
+  <dimension ref="A1:DP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24990,6 +25244,7 @@
     <col width="12" customWidth="1" min="117" max="117"/>
     <col width="12" customWidth="1" min="118" max="118"/>
     <col width="12" customWidth="1" min="119" max="119"/>
+    <col width="12" customWidth="1" min="120" max="120"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25354,6 +25609,9 @@
       <c r="DO1" s="1" t="n">
         <v>20260217</v>
       </c>
+      <c r="DP1" s="1" t="n">
+        <v>20260218</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25717,6 +25975,9 @@
       <c r="DO2" t="n">
         <v>255.78</v>
       </c>
+      <c r="DP2" t="n">
+        <v>263.88</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -26080,6 +26341,9 @@
       <c r="DO3" t="n">
         <v>198.79</v>
       </c>
+      <c r="DP3" t="n">
+        <v>201.15</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -26443,6 +26707,9 @@
       <c r="DO4" t="n">
         <v>305.72</v>
       </c>
+      <c r="DP4" t="n">
+        <v>302.02</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -26806,6 +27073,9 @@
       <c r="DO5" t="n">
         <v>401.32</v>
       </c>
+      <c r="DP5" t="n">
+        <v>396.86</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -27169,6 +27439,9 @@
       <c r="DO6" t="n">
         <v>76.87</v>
       </c>
+      <c r="DP6" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -27532,6 +27805,9 @@
       <c r="DO7" t="n">
         <v>182.81</v>
       </c>
+      <c r="DP7" t="n">
+        <v>184.97</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -27895,6 +28171,9 @@
       <c r="DO8" t="n">
         <v>131.41</v>
       </c>
+      <c r="DP8" t="n">
+        <v>133.02</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -28258,6 +28537,9 @@
       <c r="DO9" t="n">
         <v>93.79000000000001</v>
       </c>
+      <c r="DP9" t="n">
+        <v>95.39</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28620,6 +28902,9 @@
       </c>
       <c r="DO10" t="n">
         <v>417.44</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>410.63</v>
       </c>
     </row>
   </sheetData>
@@ -28633,7 +28918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DO10"/>
+  <dimension ref="A1:DP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -28755,6 +29040,7 @@
     <col width="12" customWidth="1" min="117" max="117"/>
     <col width="12" customWidth="1" min="118" max="118"/>
     <col width="12" customWidth="1" min="119" max="119"/>
+    <col width="12" customWidth="1" min="120" max="120"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29119,6 +29405,9 @@
       <c r="DO1" s="1" t="n">
         <v>20260217</v>
       </c>
+      <c r="DP1" s="1" t="n">
+        <v>20260218</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -29482,6 +29771,9 @@
       <c r="DO2" t="n">
         <v>0</v>
       </c>
+      <c r="DP2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -29845,6 +30137,9 @@
       <c r="DO3" t="n">
         <v>0</v>
       </c>
+      <c r="DP3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -30208,6 +30503,9 @@
       <c r="DO4" t="n">
         <v>0</v>
       </c>
+      <c r="DP4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -30571,6 +30869,9 @@
       <c r="DO5" t="n">
         <v>0</v>
       </c>
+      <c r="DP5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -30934,6 +31235,9 @@
       <c r="DO6" t="n">
         <v>0</v>
       </c>
+      <c r="DP6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -31297,6 +31601,9 @@
       <c r="DO7" t="n">
         <v>0</v>
       </c>
+      <c r="DP7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -31660,6 +31967,9 @@
       <c r="DO8" t="n">
         <v>0</v>
       </c>
+      <c r="DP8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -32023,6 +32333,9 @@
       <c r="DO9" t="n">
         <v>0</v>
       </c>
+      <c r="DP9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -32384,6 +32697,9 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -32398,7 +32714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CV10"/>
+  <dimension ref="A1:CW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -32501,6 +32817,7 @@
     <col width="10" customWidth="1" min="98" max="98"/>
     <col width="10" customWidth="1" min="99" max="99"/>
     <col width="10" customWidth="1" min="100" max="100"/>
+    <col width="10" customWidth="1" min="101" max="101"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32808,6 +33125,9 @@
       <c r="CV1" s="1" t="n">
         <v>20260217</v>
       </c>
+      <c r="CW1" s="1" t="n">
+        <v>20260218</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -33114,6 +33434,9 @@
       <c r="CV2" t="n">
         <v>29</v>
       </c>
+      <c r="CW2" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -33420,6 +33743,9 @@
       <c r="CV3" t="n">
         <v>0</v>
       </c>
+      <c r="CW3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -33726,6 +34052,9 @@
       <c r="CV4" t="n">
         <v>0</v>
       </c>
+      <c r="CW4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -34032,6 +34361,9 @@
       <c r="CV5" t="n">
         <v>9</v>
       </c>
+      <c r="CW5" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -34338,6 +34670,9 @@
       <c r="CV6" t="n">
         <v>9</v>
       </c>
+      <c r="CW6" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -34644,6 +34979,9 @@
       <c r="CV7" t="n">
         <v>53</v>
       </c>
+      <c r="CW7" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -34950,6 +35288,9 @@
       <c r="CV8" t="n">
         <v>6</v>
       </c>
+      <c r="CW8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -35256,6 +35597,9 @@
       <c r="CV9" t="n">
         <v>25</v>
       </c>
+      <c r="CW9" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -35561,6 +35905,9 @@
       </c>
       <c r="CV10" t="n">
         <v>39</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -35574,7 +35921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH10"/>
+  <dimension ref="A1:BI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -35637,6 +35984,7 @@
     <col width="10" customWidth="1" min="58" max="58"/>
     <col width="10" customWidth="1" min="59" max="59"/>
     <col width="10" customWidth="1" min="60" max="60"/>
+    <col width="10" customWidth="1" min="61" max="61"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -35824,6 +36172,9 @@
       <c r="BH1" s="1" t="n">
         <v>20260217</v>
       </c>
+      <c r="BI1" s="1" t="n">
+        <v>20260218</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -36010,6 +36361,9 @@
       <c r="BH2" t="n">
         <v>23</v>
       </c>
+      <c r="BI2" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -36196,6 +36550,9 @@
       <c r="BH3" t="n">
         <v>0</v>
       </c>
+      <c r="BI3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -36382,6 +36739,9 @@
       <c r="BH4" t="n">
         <v>32</v>
       </c>
+      <c r="BI4" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -36568,6 +36928,9 @@
       <c r="BH5" t="n">
         <v>8</v>
       </c>
+      <c r="BI5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -36754,6 +37117,9 @@
       <c r="BH6" t="n">
         <v>3</v>
       </c>
+      <c r="BI6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -36940,6 +37306,9 @@
       <c r="BH7" t="n">
         <v>55</v>
       </c>
+      <c r="BI7" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -37126,6 +37495,9 @@
       <c r="BH8" t="n">
         <v>4</v>
       </c>
+      <c r="BI8" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -37312,6 +37684,9 @@
       <c r="BH9" t="n">
         <v>67</v>
       </c>
+      <c r="BI9" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -37497,6 +37872,9 @@
       </c>
       <c r="BH10" t="n">
         <v>27</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -37510,7 +37888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CV10"/>
+  <dimension ref="A1:CW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -37613,6 +37991,7 @@
     <col width="10" customWidth="1" min="98" max="98"/>
     <col width="10" customWidth="1" min="99" max="99"/>
     <col width="10" customWidth="1" min="100" max="100"/>
+    <col width="10" customWidth="1" min="101" max="101"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37920,6 +38299,9 @@
       <c r="CV1" s="1" t="n">
         <v>20260217</v>
       </c>
+      <c r="CW1" s="1" t="n">
+        <v>20260218</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -38226,6 +38608,9 @@
       <c r="CV2" t="n">
         <v>-31</v>
       </c>
+      <c r="CW2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -38532,6 +38917,9 @@
       <c r="CV3" t="n">
         <v>-89</v>
       </c>
+      <c r="CW3" t="n">
+        <v>-72</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -38838,6 +39226,9 @@
       <c r="CV4" t="n">
         <v>-109</v>
       </c>
+      <c r="CW4" t="n">
+        <v>-106</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -39144,6 +39535,9 @@
       <c r="CV5" t="n">
         <v>-52</v>
       </c>
+      <c r="CW5" t="n">
+        <v>-54</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -39450,6 +39844,9 @@
       <c r="CV6" t="n">
         <v>-90</v>
       </c>
+      <c r="CW6" t="n">
+        <v>-80</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -39756,6 +40153,9 @@
       <c r="CV7" t="n">
         <v>-17</v>
       </c>
+      <c r="CW7" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -40062,6 +40462,9 @@
       <c r="CV8" t="n">
         <v>-63</v>
       </c>
+      <c r="CW8" t="n">
+        <v>-52</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -40368,6 +40771,9 @@
       <c r="CV9" t="n">
         <v>-46</v>
       </c>
+      <c r="CW9" t="n">
+        <v>-13</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -40673,6 +41079,9 @@
       </c>
       <c r="CV10" t="n">
         <v>-23</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>-46</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -602,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI10"/>
+  <dimension ref="A1:BJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -666,6 +666,7 @@
     <col width="10" customWidth="1" min="59" max="59"/>
     <col width="10" customWidth="1" min="60" max="60"/>
     <col width="10" customWidth="1" min="61" max="61"/>
+    <col width="10" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -856,6 +857,9 @@
       <c r="BI1" s="1" t="n">
         <v>20260218</v>
       </c>
+      <c r="BJ1" s="1" t="n">
+        <v>20260219</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1045,6 +1049,9 @@
       <c r="BI2" t="n">
         <v>-24</v>
       </c>
+      <c r="BJ2" t="n">
+        <v>-22</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1234,6 +1241,9 @@
       <c r="BI3" t="n">
         <v>-123</v>
       </c>
+      <c r="BJ3" t="n">
+        <v>-104</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1423,6 +1433,9 @@
       <c r="BI4" t="n">
         <v>-77</v>
       </c>
+      <c r="BJ4" t="n">
+        <v>-76</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1612,6 +1625,9 @@
       <c r="BI5" t="n">
         <v>-107</v>
       </c>
+      <c r="BJ5" t="n">
+        <v>-98</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1801,6 +1817,9 @@
       <c r="BI6" t="n">
         <v>-82</v>
       </c>
+      <c r="BJ6" t="n">
+        <v>-74</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1990,6 +2009,9 @@
       <c r="BI7" t="n">
         <v>11</v>
       </c>
+      <c r="BJ7" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2179,6 +2201,9 @@
       <c r="BI8" t="n">
         <v>-95</v>
       </c>
+      <c r="BJ8" t="n">
+        <v>-86</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2368,6 +2393,9 @@
       <c r="BI9" t="n">
         <v>55</v>
       </c>
+      <c r="BJ9" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2555,6 +2583,9 @@
         <v>-45</v>
       </c>
       <c r="BI10" t="n">
+        <v>-60</v>
+      </c>
+      <c r="BJ10" t="n">
         <v>-60</v>
       </c>
     </row>
@@ -2569,7 +2600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW10"/>
+  <dimension ref="A1:CX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2673,6 +2704,7 @@
     <col width="12" customWidth="1" min="99" max="99"/>
     <col width="12" customWidth="1" min="100" max="100"/>
     <col width="12" customWidth="1" min="101" max="101"/>
+    <col width="12" customWidth="1" min="102" max="102"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3181,6 +3213,11 @@
           <t>20260218</t>
         </is>
       </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>20260219</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3490,6 +3527,9 @@
       <c r="CW2" t="n">
         <v>100</v>
       </c>
+      <c r="CX2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3799,6 +3839,9 @@
       <c r="CW3" t="n">
         <v>89</v>
       </c>
+      <c r="CX3" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4108,6 +4151,9 @@
       <c r="CW4" t="n">
         <v>92</v>
       </c>
+      <c r="CX4" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4417,6 +4463,9 @@
       <c r="CW5" t="n">
         <v>93</v>
       </c>
+      <c r="CX5" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4726,6 +4775,9 @@
       <c r="CW6" t="n">
         <v>94</v>
       </c>
+      <c r="CX6" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5035,6 +5087,9 @@
       <c r="CW7" t="n">
         <v>100</v>
       </c>
+      <c r="CX7" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5344,6 +5399,9 @@
       <c r="CW8" t="n">
         <v>90</v>
       </c>
+      <c r="CX8" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5653,6 +5711,9 @@
       <c r="CW9" t="n">
         <v>99</v>
       </c>
+      <c r="CX9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5960,6 +6021,9 @@
         <v>99</v>
       </c>
       <c r="CW10" t="n">
+        <v>97</v>
+      </c>
+      <c r="CX10" t="n">
         <v>97</v>
       </c>
     </row>
@@ -5974,7 +6038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CD10"/>
+  <dimension ref="A1:CE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6059,6 +6123,7 @@
     <col width="12" customWidth="1" min="80" max="80"/>
     <col width="12" customWidth="1" min="81" max="81"/>
     <col width="12" customWidth="1" min="82" max="82"/>
+    <col width="12" customWidth="1" min="83" max="83"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6472,6 +6537,11 @@
           <t>20260218</t>
         </is>
       </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>20260219</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6724,6 +6794,9 @@
       <c r="CD2" t="n">
         <v>18.24</v>
       </c>
+      <c r="CE2" t="n">
+        <v>9.640000000000001</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6976,6 +7049,9 @@
       <c r="CD3" t="n">
         <v>102.63</v>
       </c>
+      <c r="CE3" t="n">
+        <v>96.45999999999999</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7228,6 +7304,9 @@
       <c r="CD4" t="n">
         <v>57.68</v>
       </c>
+      <c r="CE4" t="n">
+        <v>68.25</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7480,6 +7559,9 @@
       <c r="CD5" t="n">
         <v>38.5</v>
       </c>
+      <c r="CE5" t="n">
+        <v>35.14</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7732,6 +7814,9 @@
       <c r="CD6" t="n">
         <v>1.88</v>
       </c>
+      <c r="CE6" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7984,6 +8069,9 @@
       <c r="CD7" t="n">
         <v>33.55</v>
       </c>
+      <c r="CE7" t="n">
+        <v>29.47</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8236,6 +8324,9 @@
       <c r="CD8" t="n">
         <v>23.34</v>
       </c>
+      <c r="CE8" t="n">
+        <v>17.06</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8488,6 +8579,9 @@
       <c r="CD9" t="n">
         <v>-34.25</v>
       </c>
+      <c r="CE9" t="n">
+        <v>-32.64</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8739,6 +8833,9 @@
       </c>
       <c r="CD10" t="n">
         <v>5.14</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>8.44</v>
       </c>
     </row>
   </sheetData>
@@ -8752,7 +8849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI10"/>
+  <dimension ref="A1:BJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8816,6 +8913,7 @@
     <col width="12" customWidth="1" min="59" max="59"/>
     <col width="12" customWidth="1" min="60" max="60"/>
     <col width="12" customWidth="1" min="61" max="61"/>
+    <col width="12" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9124,6 +9222,11 @@
           <t>20260218</t>
         </is>
       </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>20260219</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9313,6 +9416,9 @@
       <c r="BI2" t="n">
         <v>0</v>
       </c>
+      <c r="BJ2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9502,6 +9608,9 @@
       <c r="BI3" t="n">
         <v>0</v>
       </c>
+      <c r="BJ3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9691,6 +9800,9 @@
       <c r="BI4" t="n">
         <v>0</v>
       </c>
+      <c r="BJ4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9880,6 +9992,9 @@
       <c r="BI5" t="n">
         <v>0</v>
       </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10069,6 +10184,9 @@
       <c r="BI6" t="n">
         <v>0</v>
       </c>
+      <c r="BJ6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10258,6 +10376,9 @@
       <c r="BI7" t="n">
         <v>0</v>
       </c>
+      <c r="BJ7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10447,6 +10568,9 @@
       <c r="BI8" t="n">
         <v>0</v>
       </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10636,6 +10760,9 @@
       <c r="BI9" t="n">
         <v>0</v>
       </c>
+      <c r="BJ9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10823,6 +10950,9 @@
         <v>0</v>
       </c>
       <c r="BI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10837,7 +10967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CM10"/>
+  <dimension ref="A1:CN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10931,6 +11061,7 @@
     <col width="10" customWidth="1" min="89" max="89"/>
     <col width="10" customWidth="1" min="90" max="90"/>
     <col width="10" customWidth="1" min="91" max="91"/>
+    <col width="10" customWidth="1" min="92" max="92"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11211,6 +11342,9 @@
       <c r="CM1" s="1" t="n">
         <v>20260218</v>
       </c>
+      <c r="CN1" s="1" t="n">
+        <v>20260219</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11490,6 +11624,9 @@
       <c r="CM2" t="n">
         <v>11</v>
       </c>
+      <c r="CN2" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11769,6 +11906,9 @@
       <c r="CM3" t="n">
         <v>-93</v>
       </c>
+      <c r="CN3" t="n">
+        <v>-75</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12048,6 +12188,9 @@
       <c r="CM4" t="n">
         <v>-123</v>
       </c>
+      <c r="CN4" t="n">
+        <v>-108</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12327,6 +12470,9 @@
       <c r="CM5" t="n">
         <v>-72</v>
       </c>
+      <c r="CN5" t="n">
+        <v>-63</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12606,6 +12752,9 @@
       <c r="CM6" t="n">
         <v>-84</v>
       </c>
+      <c r="CN6" t="n">
+        <v>-68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12885,6 +13034,9 @@
       <c r="CM7" t="n">
         <v>-3</v>
       </c>
+      <c r="CN7" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13164,6 +13316,9 @@
       <c r="CM8" t="n">
         <v>-67</v>
       </c>
+      <c r="CN8" t="n">
+        <v>-57</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13443,6 +13598,9 @@
       <c r="CM9" t="n">
         <v>19</v>
       </c>
+      <c r="CN9" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13721,6 +13879,9 @@
       </c>
       <c r="CM10" t="n">
         <v>-62</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>-56</v>
       </c>
     </row>
   </sheetData>
@@ -13734,7 +13895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DP10"/>
+  <dimension ref="A1:DQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13857,6 +14018,7 @@
     <col width="12" customWidth="1" min="118" max="118"/>
     <col width="12" customWidth="1" min="119" max="119"/>
     <col width="12" customWidth="1" min="120" max="120"/>
+    <col width="12" customWidth="1" min="121" max="121"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14224,6 +14386,9 @@
       <c r="DP1" s="1" t="n">
         <v>20260218</v>
       </c>
+      <c r="DQ1" s="1" t="n">
+        <v>20260219</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14590,6 +14755,9 @@
       <c r="DP2" t="n">
         <v>263.88</v>
       </c>
+      <c r="DQ2" t="n">
+        <v>264.35</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14956,6 +15124,9 @@
       <c r="DP3" t="n">
         <v>201.15</v>
       </c>
+      <c r="DQ3" t="n">
+        <v>204.79</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15322,6 +15493,9 @@
       <c r="DP4" t="n">
         <v>302.02</v>
       </c>
+      <c r="DQ4" t="n">
+        <v>303.33</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15688,6 +15862,9 @@
       <c r="DP5" t="n">
         <v>396.86</v>
       </c>
+      <c r="DQ5" t="n">
+        <v>399.6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16054,6 +16231,9 @@
       <c r="DP6" t="n">
         <v>77</v>
       </c>
+      <c r="DQ6" t="n">
+        <v>77.98999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16420,6 +16600,9 @@
       <c r="DP7" t="n">
         <v>184.97</v>
       </c>
+      <c r="DQ7" t="n">
+        <v>187.98</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16786,6 +16969,9 @@
       <c r="DP8" t="n">
         <v>133.02</v>
       </c>
+      <c r="DQ8" t="n">
+        <v>135.38</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17152,6 +17338,9 @@
       <c r="DP9" t="n">
         <v>95.39</v>
       </c>
+      <c r="DQ9" t="n">
+        <v>95.76000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17517,6 +17706,9 @@
       </c>
       <c r="DP10" t="n">
         <v>410.63</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>411.32</v>
       </c>
     </row>
   </sheetData>
@@ -17530,7 +17722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DP10"/>
+  <dimension ref="A1:DQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17653,6 +17845,7 @@
     <col width="12" customWidth="1" min="118" max="118"/>
     <col width="12" customWidth="1" min="119" max="119"/>
     <col width="12" customWidth="1" min="120" max="120"/>
+    <col width="12" customWidth="1" min="121" max="121"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18020,6 +18213,9 @@
       <c r="DP1" s="1" t="n">
         <v>20260218</v>
       </c>
+      <c r="DQ1" s="1" t="n">
+        <v>20260219</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18386,6 +18582,9 @@
       <c r="DP2" t="n">
         <v>263.88</v>
       </c>
+      <c r="DQ2" t="n">
+        <v>264.35</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18752,6 +18951,9 @@
       <c r="DP3" t="n">
         <v>201.15</v>
       </c>
+      <c r="DQ3" t="n">
+        <v>204.79</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19118,6 +19320,9 @@
       <c r="DP4" t="n">
         <v>302.02</v>
       </c>
+      <c r="DQ4" t="n">
+        <v>303.33</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19484,6 +19689,9 @@
       <c r="DP5" t="n">
         <v>396.86</v>
       </c>
+      <c r="DQ5" t="n">
+        <v>399.6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19850,6 +20058,9 @@
       <c r="DP6" t="n">
         <v>77</v>
       </c>
+      <c r="DQ6" t="n">
+        <v>77.98999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20216,6 +20427,9 @@
       <c r="DP7" t="n">
         <v>184.97</v>
       </c>
+      <c r="DQ7" t="n">
+        <v>187.98</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20582,6 +20796,9 @@
       <c r="DP8" t="n">
         <v>133.02</v>
       </c>
+      <c r="DQ8" t="n">
+        <v>135.38</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20948,6 +21165,9 @@
       <c r="DP9" t="n">
         <v>95.39</v>
       </c>
+      <c r="DQ9" t="n">
+        <v>95.76000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21313,6 +21533,9 @@
       </c>
       <c r="DP10" t="n">
         <v>410.63</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>411.32</v>
       </c>
     </row>
   </sheetData>
@@ -21326,7 +21549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DP10"/>
+  <dimension ref="A1:DQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21449,6 +21672,7 @@
     <col width="12" customWidth="1" min="118" max="118"/>
     <col width="12" customWidth="1" min="119" max="119"/>
     <col width="12" customWidth="1" min="120" max="120"/>
+    <col width="12" customWidth="1" min="121" max="121"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21816,6 +22040,9 @@
       <c r="DP1" s="1" t="n">
         <v>20260218</v>
       </c>
+      <c r="DQ1" s="1" t="n">
+        <v>20260219</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22182,6 +22409,9 @@
       <c r="DP2" t="n">
         <v>263.88</v>
       </c>
+      <c r="DQ2" t="n">
+        <v>264.35</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22548,6 +22778,9 @@
       <c r="DP3" t="n">
         <v>201.15</v>
       </c>
+      <c r="DQ3" t="n">
+        <v>204.79</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22914,6 +23147,9 @@
       <c r="DP4" t="n">
         <v>302.02</v>
       </c>
+      <c r="DQ4" t="n">
+        <v>303.33</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23280,6 +23516,9 @@
       <c r="DP5" t="n">
         <v>396.86</v>
       </c>
+      <c r="DQ5" t="n">
+        <v>399.6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23646,6 +23885,9 @@
       <c r="DP6" t="n">
         <v>77</v>
       </c>
+      <c r="DQ6" t="n">
+        <v>77.98999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24012,6 +24254,9 @@
       <c r="DP7" t="n">
         <v>184.97</v>
       </c>
+      <c r="DQ7" t="n">
+        <v>187.98</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24378,6 +24623,9 @@
       <c r="DP8" t="n">
         <v>133.02</v>
       </c>
+      <c r="DQ8" t="n">
+        <v>135.38</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24744,6 +24992,9 @@
       <c r="DP9" t="n">
         <v>95.39</v>
       </c>
+      <c r="DQ9" t="n">
+        <v>95.76000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25109,6 +25360,9 @@
       </c>
       <c r="DP10" t="n">
         <v>410.63</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>411.32</v>
       </c>
     </row>
   </sheetData>
@@ -25122,7 +25376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DP10"/>
+  <dimension ref="A1:DQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25245,6 +25499,7 @@
     <col width="12" customWidth="1" min="118" max="118"/>
     <col width="12" customWidth="1" min="119" max="119"/>
     <col width="12" customWidth="1" min="120" max="120"/>
+    <col width="12" customWidth="1" min="121" max="121"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25612,6 +25867,9 @@
       <c r="DP1" s="1" t="n">
         <v>20260218</v>
       </c>
+      <c r="DQ1" s="1" t="n">
+        <v>20260219</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25978,6 +26236,9 @@
       <c r="DP2" t="n">
         <v>263.88</v>
       </c>
+      <c r="DQ2" t="n">
+        <v>264.35</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -26344,6 +26605,9 @@
       <c r="DP3" t="n">
         <v>201.15</v>
       </c>
+      <c r="DQ3" t="n">
+        <v>204.79</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -26710,6 +26974,9 @@
       <c r="DP4" t="n">
         <v>302.02</v>
       </c>
+      <c r="DQ4" t="n">
+        <v>303.33</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -27076,6 +27343,9 @@
       <c r="DP5" t="n">
         <v>396.86</v>
       </c>
+      <c r="DQ5" t="n">
+        <v>399.6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -27442,6 +27712,9 @@
       <c r="DP6" t="n">
         <v>77</v>
       </c>
+      <c r="DQ6" t="n">
+        <v>77.98999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -27808,6 +28081,9 @@
       <c r="DP7" t="n">
         <v>184.97</v>
       </c>
+      <c r="DQ7" t="n">
+        <v>187.98</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -28174,6 +28450,9 @@
       <c r="DP8" t="n">
         <v>133.02</v>
       </c>
+      <c r="DQ8" t="n">
+        <v>135.38</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -28540,6 +28819,9 @@
       <c r="DP9" t="n">
         <v>95.39</v>
       </c>
+      <c r="DQ9" t="n">
+        <v>95.76000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28905,6 +29187,9 @@
       </c>
       <c r="DP10" t="n">
         <v>410.63</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>411.32</v>
       </c>
     </row>
   </sheetData>
@@ -28918,7 +29203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DP10"/>
+  <dimension ref="A1:DQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -29041,6 +29326,7 @@
     <col width="12" customWidth="1" min="118" max="118"/>
     <col width="12" customWidth="1" min="119" max="119"/>
     <col width="12" customWidth="1" min="120" max="120"/>
+    <col width="12" customWidth="1" min="121" max="121"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29408,6 +29694,9 @@
       <c r="DP1" s="1" t="n">
         <v>20260218</v>
       </c>
+      <c r="DQ1" s="1" t="n">
+        <v>20260219</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -29774,6 +30063,9 @@
       <c r="DP2" t="n">
         <v>0</v>
       </c>
+      <c r="DQ2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -30140,6 +30432,9 @@
       <c r="DP3" t="n">
         <v>0</v>
       </c>
+      <c r="DQ3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -30506,6 +30801,9 @@
       <c r="DP4" t="n">
         <v>0</v>
       </c>
+      <c r="DQ4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -30872,6 +31170,9 @@
       <c r="DP5" t="n">
         <v>0</v>
       </c>
+      <c r="DQ5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -31238,6 +31539,9 @@
       <c r="DP6" t="n">
         <v>0</v>
       </c>
+      <c r="DQ6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -31604,6 +31908,9 @@
       <c r="DP7" t="n">
         <v>0</v>
       </c>
+      <c r="DQ7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -31970,6 +32277,9 @@
       <c r="DP8" t="n">
         <v>0</v>
       </c>
+      <c r="DQ8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -32336,6 +32646,9 @@
       <c r="DP9" t="n">
         <v>0</v>
       </c>
+      <c r="DQ9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -32700,6 +33013,9 @@
         <v>0</v>
       </c>
       <c r="DP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -32714,7 +33030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW10"/>
+  <dimension ref="A1:CX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -32818,6 +33134,7 @@
     <col width="10" customWidth="1" min="99" max="99"/>
     <col width="10" customWidth="1" min="100" max="100"/>
     <col width="10" customWidth="1" min="101" max="101"/>
+    <col width="10" customWidth="1" min="102" max="102"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33128,6 +33445,9 @@
       <c r="CW1" s="1" t="n">
         <v>20260218</v>
       </c>
+      <c r="CX1" s="1" t="n">
+        <v>20260219</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -33437,6 +33757,9 @@
       <c r="CW2" t="n">
         <v>53</v>
       </c>
+      <c r="CX2" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -33746,6 +34069,9 @@
       <c r="CW3" t="n">
         <v>5</v>
       </c>
+      <c r="CX3" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -34055,6 +34381,9 @@
       <c r="CW4" t="n">
         <v>0</v>
       </c>
+      <c r="CX4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -34364,6 +34693,9 @@
       <c r="CW5" t="n">
         <v>4</v>
       </c>
+      <c r="CX5" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -34673,6 +35005,9 @@
       <c r="CW6" t="n">
         <v>11</v>
       </c>
+      <c r="CX6" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -34982,6 +35317,9 @@
       <c r="CW7" t="n">
         <v>63</v>
       </c>
+      <c r="CX7" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -35291,6 +35629,9 @@
       <c r="CW8" t="n">
         <v>10</v>
       </c>
+      <c r="CX8" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -35600,6 +35941,9 @@
       <c r="CW9" t="n">
         <v>46</v>
       </c>
+      <c r="CX9" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -35908,6 +36252,9 @@
       </c>
       <c r="CW10" t="n">
         <v>26</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -35921,7 +36268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI10"/>
+  <dimension ref="A1:BJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -35985,6 +36332,7 @@
     <col width="10" customWidth="1" min="59" max="59"/>
     <col width="10" customWidth="1" min="60" max="60"/>
     <col width="10" customWidth="1" min="61" max="61"/>
+    <col width="10" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -36175,6 +36523,9 @@
       <c r="BI1" s="1" t="n">
         <v>20260218</v>
       </c>
+      <c r="BJ1" s="1" t="n">
+        <v>20260219</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -36364,6 +36715,9 @@
       <c r="BI2" t="n">
         <v>44</v>
       </c>
+      <c r="BJ2" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -36553,6 +36907,9 @@
       <c r="BI3" t="n">
         <v>5</v>
       </c>
+      <c r="BJ3" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -36742,6 +37099,9 @@
       <c r="BI4" t="n">
         <v>25</v>
       </c>
+      <c r="BJ4" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -36931,6 +37291,9 @@
       <c r="BI5" t="n">
         <v>3</v>
       </c>
+      <c r="BJ5" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -37120,6 +37483,9 @@
       <c r="BI6" t="n">
         <v>3</v>
       </c>
+      <c r="BJ6" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -37309,6 +37675,9 @@
       <c r="BI7" t="n">
         <v>65</v>
       </c>
+      <c r="BJ7" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -37498,6 +37867,9 @@
       <c r="BI8" t="n">
         <v>6</v>
       </c>
+      <c r="BJ8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -37687,6 +38059,9 @@
       <c r="BI9" t="n">
         <v>76</v>
       </c>
+      <c r="BJ9" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -37874,6 +38249,9 @@
         <v>27</v>
       </c>
       <c r="BI10" t="n">
+        <v>20</v>
+      </c>
+      <c r="BJ10" t="n">
         <v>20</v>
       </c>
     </row>
@@ -37888,7 +38266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW10"/>
+  <dimension ref="A1:CX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -37992,6 +38370,7 @@
     <col width="10" customWidth="1" min="99" max="99"/>
     <col width="10" customWidth="1" min="100" max="100"/>
     <col width="10" customWidth="1" min="101" max="101"/>
+    <col width="10" customWidth="1" min="102" max="102"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -38302,6 +38681,9 @@
       <c r="CW1" s="1" t="n">
         <v>20260218</v>
       </c>
+      <c r="CX1" s="1" t="n">
+        <v>20260219</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -38611,6 +38993,9 @@
       <c r="CW2" t="n">
         <v>1</v>
       </c>
+      <c r="CX2" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -38920,6 +39305,9 @@
       <c r="CW3" t="n">
         <v>-72</v>
       </c>
+      <c r="CX3" t="n">
+        <v>-56</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -39229,6 +39617,9 @@
       <c r="CW4" t="n">
         <v>-106</v>
       </c>
+      <c r="CX4" t="n">
+        <v>-87</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -39538,6 +39929,9 @@
       <c r="CW5" t="n">
         <v>-54</v>
       </c>
+      <c r="CX5" t="n">
+        <v>-44</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -39847,6 +40241,9 @@
       <c r="CW6" t="n">
         <v>-80</v>
       </c>
+      <c r="CX6" t="n">
+        <v>-58</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -40156,6 +40553,9 @@
       <c r="CW7" t="n">
         <v>-3</v>
       </c>
+      <c r="CX7" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -40465,6 +40865,9 @@
       <c r="CW8" t="n">
         <v>-52</v>
       </c>
+      <c r="CX8" t="n">
+        <v>-39</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -40774,6 +41177,9 @@
       <c r="CW9" t="n">
         <v>-13</v>
       </c>
+      <c r="CX9" t="n">
+        <v>-4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -41082,6 +41488,9 @@
       </c>
       <c r="CW10" t="n">
         <v>-46</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>-39</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -17,6 +17,8 @@
     <sheet name="std" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="quant" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="z30" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="s120" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="z120" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -602,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ10"/>
+  <dimension ref="A1:BK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -667,6 +669,7 @@
     <col width="10" customWidth="1" min="60" max="60"/>
     <col width="10" customWidth="1" min="61" max="61"/>
     <col width="10" customWidth="1" min="62" max="62"/>
+    <col width="10" customWidth="1" min="63" max="63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -860,6 +863,9 @@
       <c r="BJ1" s="1" t="n">
         <v>20260219</v>
       </c>
+      <c r="BK1" s="1" t="n">
+        <v>20260220</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1052,6 +1058,9 @@
       <c r="BJ2" t="n">
         <v>-22</v>
       </c>
+      <c r="BK2" t="n">
+        <v>-22</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1244,6 +1253,9 @@
       <c r="BJ3" t="n">
         <v>-104</v>
       </c>
+      <c r="BK3" t="n">
+        <v>-104</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1436,6 +1448,9 @@
       <c r="BJ4" t="n">
         <v>-76</v>
       </c>
+      <c r="BK4" t="n">
+        <v>-79</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1628,6 +1643,9 @@
       <c r="BJ5" t="n">
         <v>-98</v>
       </c>
+      <c r="BK5" t="n">
+        <v>-94</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1820,6 +1838,9 @@
       <c r="BJ6" t="n">
         <v>-74</v>
       </c>
+      <c r="BK6" t="n">
+        <v>-74</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2012,6 +2033,9 @@
       <c r="BJ7" t="n">
         <v>38</v>
       </c>
+      <c r="BK7" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2204,6 +2228,9 @@
       <c r="BJ8" t="n">
         <v>-86</v>
       </c>
+      <c r="BK8" t="n">
+        <v>-84</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2396,6 +2423,9 @@
       <c r="BJ9" t="n">
         <v>57</v>
       </c>
+      <c r="BK9" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2587,6 +2617,9 @@
       </c>
       <c r="BJ10" t="n">
         <v>-60</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>-62</v>
       </c>
     </row>
   </sheetData>
@@ -2600,7 +2633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CX10"/>
+  <dimension ref="A1:CY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2705,6 +2738,7 @@
     <col width="12" customWidth="1" min="100" max="100"/>
     <col width="12" customWidth="1" min="101" max="101"/>
     <col width="12" customWidth="1" min="102" max="102"/>
+    <col width="12" customWidth="1" min="103" max="103"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3218,6 +3252,11 @@
           <t>20260219</t>
         </is>
       </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>20260220</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4154,6 +4193,9 @@
       <c r="CX4" t="n">
         <v>93</v>
       </c>
+      <c r="CY4" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4466,6 +4508,9 @@
       <c r="CX5" t="n">
         <v>94</v>
       </c>
+      <c r="CY5" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5090,6 +5135,9 @@
       <c r="CX7" t="n">
         <v>101</v>
       </c>
+      <c r="CY7" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5402,6 +5450,9 @@
       <c r="CX8" t="n">
         <v>93</v>
       </c>
+      <c r="CY8" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6025,6 +6076,9 @@
       </c>
       <c r="CX10" t="n">
         <v>97</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -6038,7 +6092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CE10"/>
+  <dimension ref="A1:CF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6124,6 +6178,7 @@
     <col width="12" customWidth="1" min="81" max="81"/>
     <col width="12" customWidth="1" min="82" max="82"/>
     <col width="12" customWidth="1" min="83" max="83"/>
+    <col width="12" customWidth="1" min="84" max="84"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6542,6 +6597,11 @@
           <t>20260219</t>
         </is>
       </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>20260220</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7307,6 +7367,9 @@
       <c r="CE4" t="n">
         <v>68.25</v>
       </c>
+      <c r="CF4" t="n">
+        <v>74.23999999999999</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7562,6 +7625,9 @@
       <c r="CE5" t="n">
         <v>35.14</v>
       </c>
+      <c r="CF5" t="n">
+        <v>30.27</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8072,6 +8138,9 @@
       <c r="CE7" t="n">
         <v>29.47</v>
       </c>
+      <c r="CF7" t="n">
+        <v>25.78</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8327,6 +8396,9 @@
       <c r="CE8" t="n">
         <v>17.06</v>
       </c>
+      <c r="CF8" t="n">
+        <v>9.35</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8836,6 +8908,9 @@
       </c>
       <c r="CE10" t="n">
         <v>8.44</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>-0.67</v>
       </c>
     </row>
   </sheetData>
@@ -8849,7 +8924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ10"/>
+  <dimension ref="A1:BK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8914,6 +8989,7 @@
     <col width="12" customWidth="1" min="60" max="60"/>
     <col width="12" customWidth="1" min="61" max="61"/>
     <col width="12" customWidth="1" min="62" max="62"/>
+    <col width="12" customWidth="1" min="63" max="63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9227,6 +9303,11 @@
           <t>20260219</t>
         </is>
       </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>20260220</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9803,6 +9884,9 @@
       <c r="BJ4" t="n">
         <v>0</v>
       </c>
+      <c r="BK4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9995,6 +10079,9 @@
       <c r="BJ5" t="n">
         <v>0</v>
       </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10379,6 +10466,9 @@
       <c r="BJ7" t="n">
         <v>0</v>
       </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10571,6 +10661,9 @@
       <c r="BJ8" t="n">
         <v>0</v>
       </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10953,6 +11046,9 @@
         <v>0</v>
       </c>
       <c r="BJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10967,7 +11063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CN10"/>
+  <dimension ref="A1:CO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11062,6 +11158,7 @@
     <col width="10" customWidth="1" min="90" max="90"/>
     <col width="10" customWidth="1" min="91" max="91"/>
     <col width="10" customWidth="1" min="92" max="92"/>
+    <col width="10" customWidth="1" min="93" max="93"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11345,6 +11442,9 @@
       <c r="CN1" s="1" t="n">
         <v>20260219</v>
       </c>
+      <c r="CO1" s="1" t="n">
+        <v>20260220</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11627,6 +11727,9 @@
       <c r="CN2" t="n">
         <v>13</v>
       </c>
+      <c r="CO2" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11909,6 +12012,9 @@
       <c r="CN3" t="n">
         <v>-75</v>
       </c>
+      <c r="CO3" t="n">
+        <v>-75</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12191,6 +12297,9 @@
       <c r="CN4" t="n">
         <v>-108</v>
       </c>
+      <c r="CO4" t="n">
+        <v>-100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12473,6 +12582,9 @@
       <c r="CN5" t="n">
         <v>-63</v>
       </c>
+      <c r="CO5" t="n">
+        <v>-61</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12755,6 +12867,9 @@
       <c r="CN6" t="n">
         <v>-68</v>
       </c>
+      <c r="CO6" t="n">
+        <v>-68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13037,6 +13152,9 @@
       <c r="CN7" t="n">
         <v>26</v>
       </c>
+      <c r="CO7" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13319,6 +13437,9 @@
       <c r="CN8" t="n">
         <v>-57</v>
       </c>
+      <c r="CO8" t="n">
+        <v>-54</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13601,6 +13722,9 @@
       <c r="CN9" t="n">
         <v>22</v>
       </c>
+      <c r="CO9" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13882,6 +14006,323 @@
       </c>
       <c r="CN10" t="n">
         <v>-56</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>-51</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>종목코드</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="n">
+        <v>20260220</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>애플</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>아마존닷컴</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>알파벳 A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>마이크로소프트</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>넷플릭스</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>엔비디아</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>팔란티어 테크</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>스타벅스</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SBUX</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>테슬라</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>종목코드</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="n">
+        <v>20260220</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>애플</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>아마존닷컴</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>알파벳 A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>마이크로소프트</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>-122</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>넷플릭스</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>엔비디아</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>팔란티어 테크</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>-111</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>스타벅스</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SBUX</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>테슬라</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>-28</v>
       </c>
     </row>
   </sheetData>
@@ -13895,7 +14336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DQ10"/>
+  <dimension ref="A1:DR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14019,6 +14460,7 @@
     <col width="12" customWidth="1" min="119" max="119"/>
     <col width="12" customWidth="1" min="120" max="120"/>
     <col width="12" customWidth="1" min="121" max="121"/>
+    <col width="12" customWidth="1" min="122" max="122"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14389,6 +14831,9 @@
       <c r="DQ1" s="1" t="n">
         <v>20260219</v>
       </c>
+      <c r="DR1" s="1" t="n">
+        <v>20260220</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15496,6 +15941,9 @@
       <c r="DQ4" t="n">
         <v>303.33</v>
       </c>
+      <c r="DR4" t="n">
+        <v>302.85</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15865,6 +16313,9 @@
       <c r="DQ5" t="n">
         <v>399.6</v>
       </c>
+      <c r="DR5" t="n">
+        <v>398.46</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16603,6 +17054,9 @@
       <c r="DQ7" t="n">
         <v>187.98</v>
       </c>
+      <c r="DR7" t="n">
+        <v>187.9</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16972,6 +17426,9 @@
       <c r="DQ8" t="n">
         <v>135.38</v>
       </c>
+      <c r="DR8" t="n">
+        <v>134.89</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17709,6 +18166,9 @@
       </c>
       <c r="DQ10" t="n">
         <v>411.32</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>411.71</v>
       </c>
     </row>
   </sheetData>
@@ -17722,7 +18182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DQ10"/>
+  <dimension ref="A1:DR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17846,6 +18306,7 @@
     <col width="12" customWidth="1" min="119" max="119"/>
     <col width="12" customWidth="1" min="120" max="120"/>
     <col width="12" customWidth="1" min="121" max="121"/>
+    <col width="12" customWidth="1" min="122" max="122"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18216,6 +18677,9 @@
       <c r="DQ1" s="1" t="n">
         <v>20260219</v>
       </c>
+      <c r="DR1" s="1" t="n">
+        <v>20260220</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19323,6 +19787,9 @@
       <c r="DQ4" t="n">
         <v>303.33</v>
       </c>
+      <c r="DR4" t="n">
+        <v>302.85</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19692,6 +20159,9 @@
       <c r="DQ5" t="n">
         <v>399.6</v>
       </c>
+      <c r="DR5" t="n">
+        <v>398.46</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20430,6 +20900,9 @@
       <c r="DQ7" t="n">
         <v>187.98</v>
       </c>
+      <c r="DR7" t="n">
+        <v>187.9</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20799,6 +21272,9 @@
       <c r="DQ8" t="n">
         <v>135.38</v>
       </c>
+      <c r="DR8" t="n">
+        <v>134.89</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21536,6 +22012,9 @@
       </c>
       <c r="DQ10" t="n">
         <v>411.32</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>411.71</v>
       </c>
     </row>
   </sheetData>
@@ -21549,7 +22028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DQ10"/>
+  <dimension ref="A1:DR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21673,6 +22152,7 @@
     <col width="12" customWidth="1" min="119" max="119"/>
     <col width="12" customWidth="1" min="120" max="120"/>
     <col width="12" customWidth="1" min="121" max="121"/>
+    <col width="12" customWidth="1" min="122" max="122"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22043,6 +22523,9 @@
       <c r="DQ1" s="1" t="n">
         <v>20260219</v>
       </c>
+      <c r="DR1" s="1" t="n">
+        <v>20260220</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23150,6 +23633,9 @@
       <c r="DQ4" t="n">
         <v>303.33</v>
       </c>
+      <c r="DR4" t="n">
+        <v>302.85</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23519,6 +24005,9 @@
       <c r="DQ5" t="n">
         <v>399.6</v>
       </c>
+      <c r="DR5" t="n">
+        <v>398.46</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24257,6 +24746,9 @@
       <c r="DQ7" t="n">
         <v>187.98</v>
       </c>
+      <c r="DR7" t="n">
+        <v>187.9</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24626,6 +25118,9 @@
       <c r="DQ8" t="n">
         <v>135.38</v>
       </c>
+      <c r="DR8" t="n">
+        <v>134.89</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25363,6 +25858,9 @@
       </c>
       <c r="DQ10" t="n">
         <v>411.32</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>411.71</v>
       </c>
     </row>
   </sheetData>
@@ -25376,7 +25874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DQ10"/>
+  <dimension ref="A1:DR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25500,6 +25998,7 @@
     <col width="12" customWidth="1" min="119" max="119"/>
     <col width="12" customWidth="1" min="120" max="120"/>
     <col width="12" customWidth="1" min="121" max="121"/>
+    <col width="12" customWidth="1" min="122" max="122"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25870,6 +26369,9 @@
       <c r="DQ1" s="1" t="n">
         <v>20260219</v>
       </c>
+      <c r="DR1" s="1" t="n">
+        <v>20260220</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -26977,6 +27479,9 @@
       <c r="DQ4" t="n">
         <v>303.33</v>
       </c>
+      <c r="DR4" t="n">
+        <v>302.85</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -27346,6 +27851,9 @@
       <c r="DQ5" t="n">
         <v>399.6</v>
       </c>
+      <c r="DR5" t="n">
+        <v>398.46</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -28084,6 +28592,9 @@
       <c r="DQ7" t="n">
         <v>187.98</v>
       </c>
+      <c r="DR7" t="n">
+        <v>187.9</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -28453,6 +28964,9 @@
       <c r="DQ8" t="n">
         <v>135.38</v>
       </c>
+      <c r="DR8" t="n">
+        <v>134.89</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -29190,6 +29704,9 @@
       </c>
       <c r="DQ10" t="n">
         <v>411.32</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>411.71</v>
       </c>
     </row>
   </sheetData>
@@ -29203,7 +29720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DQ10"/>
+  <dimension ref="A1:DR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -29327,6 +29844,7 @@
     <col width="12" customWidth="1" min="119" max="119"/>
     <col width="12" customWidth="1" min="120" max="120"/>
     <col width="12" customWidth="1" min="121" max="121"/>
+    <col width="12" customWidth="1" min="122" max="122"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29697,6 +30215,9 @@
       <c r="DQ1" s="1" t="n">
         <v>20260219</v>
       </c>
+      <c r="DR1" s="1" t="n">
+        <v>20260220</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -30804,6 +31325,9 @@
       <c r="DQ4" t="n">
         <v>0</v>
       </c>
+      <c r="DR4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -31173,6 +31697,9 @@
       <c r="DQ5" t="n">
         <v>0</v>
       </c>
+      <c r="DR5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -31911,6 +32438,9 @@
       <c r="DQ7" t="n">
         <v>0</v>
       </c>
+      <c r="DR7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -32280,6 +32810,9 @@
       <c r="DQ8" t="n">
         <v>0</v>
       </c>
+      <c r="DR8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -33016,6 +33549,9 @@
         <v>0</v>
       </c>
       <c r="DQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -33030,7 +33566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CX10"/>
+  <dimension ref="A1:CY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -33135,6 +33671,7 @@
     <col width="10" customWidth="1" min="100" max="100"/>
     <col width="10" customWidth="1" min="101" max="101"/>
     <col width="10" customWidth="1" min="102" max="102"/>
+    <col width="10" customWidth="1" min="103" max="103"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33448,6 +33985,9 @@
       <c r="CX1" s="1" t="n">
         <v>20260219</v>
       </c>
+      <c r="CY1" s="1" t="n">
+        <v>20260220</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -33760,6 +34300,9 @@
       <c r="CX2" t="n">
         <v>54</v>
       </c>
+      <c r="CY2" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -34072,6 +34615,9 @@
       <c r="CX3" t="n">
         <v>13</v>
       </c>
+      <c r="CY3" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -34384,6 +34930,9 @@
       <c r="CX4" t="n">
         <v>3</v>
       </c>
+      <c r="CY4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -34696,6 +35245,9 @@
       <c r="CX5" t="n">
         <v>7</v>
       </c>
+      <c r="CY5" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -35008,6 +35560,9 @@
       <c r="CX6" t="n">
         <v>21</v>
       </c>
+      <c r="CY6" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -35320,6 +35875,9 @@
       <c r="CX7" t="n">
         <v>78</v>
       </c>
+      <c r="CY7" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -35632,6 +36190,9 @@
       <c r="CX8" t="n">
         <v>15</v>
       </c>
+      <c r="CY8" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -35944,6 +36505,9 @@
       <c r="CX9" t="n">
         <v>51</v>
       </c>
+      <c r="CY9" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -36255,6 +36819,9 @@
       </c>
       <c r="CX10" t="n">
         <v>27</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -36268,7 +36835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ10"/>
+  <dimension ref="A1:BK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -36333,6 +36900,7 @@
     <col width="10" customWidth="1" min="60" max="60"/>
     <col width="10" customWidth="1" min="61" max="61"/>
     <col width="10" customWidth="1" min="62" max="62"/>
+    <col width="10" customWidth="1" min="63" max="63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -36526,6 +37094,9 @@
       <c r="BJ1" s="1" t="n">
         <v>20260219</v>
       </c>
+      <c r="BK1" s="1" t="n">
+        <v>20260220</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -36718,6 +37289,9 @@
       <c r="BJ2" t="n">
         <v>45</v>
       </c>
+      <c r="BK2" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -36910,6 +37484,9 @@
       <c r="BJ3" t="n">
         <v>12</v>
       </c>
+      <c r="BK3" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -37102,6 +37679,9 @@
       <c r="BJ4" t="n">
         <v>15</v>
       </c>
+      <c r="BK4" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -37294,6 +37874,9 @@
       <c r="BJ5" t="n">
         <v>6</v>
       </c>
+      <c r="BK5" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -37486,6 +38069,9 @@
       <c r="BJ6" t="n">
         <v>6</v>
       </c>
+      <c r="BK6" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -37678,6 +38264,9 @@
       <c r="BJ7" t="n">
         <v>79</v>
       </c>
+      <c r="BK7" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -37870,6 +38459,9 @@
       <c r="BJ8" t="n">
         <v>10</v>
       </c>
+      <c r="BK8" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -38062,6 +38654,9 @@
       <c r="BJ9" t="n">
         <v>79</v>
       </c>
+      <c r="BK9" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -38253,6 +38848,9 @@
       </c>
       <c r="BJ10" t="n">
         <v>20</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -38266,7 +38864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CX10"/>
+  <dimension ref="A1:CY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -38371,6 +38969,7 @@
     <col width="10" customWidth="1" min="100" max="100"/>
     <col width="10" customWidth="1" min="101" max="101"/>
     <col width="10" customWidth="1" min="102" max="102"/>
+    <col width="10" customWidth="1" min="103" max="103"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -38684,6 +39283,9 @@
       <c r="CX1" s="1" t="n">
         <v>20260219</v>
       </c>
+      <c r="CY1" s="1" t="n">
+        <v>20260220</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -38996,6 +39598,9 @@
       <c r="CX2" t="n">
         <v>-1</v>
       </c>
+      <c r="CY2" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -39308,6 +39913,9 @@
       <c r="CX3" t="n">
         <v>-56</v>
       </c>
+      <c r="CY3" t="n">
+        <v>-56</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -39620,6 +40228,9 @@
       <c r="CX4" t="n">
         <v>-87</v>
       </c>
+      <c r="CY4" t="n">
+        <v>-78</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -39932,6 +40543,9 @@
       <c r="CX5" t="n">
         <v>-44</v>
       </c>
+      <c r="CY5" t="n">
+        <v>-42</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -40244,6 +40858,9 @@
       <c r="CX6" t="n">
         <v>-58</v>
       </c>
+      <c r="CY6" t="n">
+        <v>-58</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -40556,6 +41173,9 @@
       <c r="CX7" t="n">
         <v>20</v>
       </c>
+      <c r="CY7" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -40868,6 +41488,9 @@
       <c r="CX8" t="n">
         <v>-39</v>
       </c>
+      <c r="CY8" t="n">
+        <v>-37</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -41180,6 +41803,9 @@
       <c r="CX9" t="n">
         <v>-4</v>
       </c>
+      <c r="CY9" t="n">
+        <v>-4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -41491,6 +42117,9 @@
       </c>
       <c r="CX10" t="n">
         <v>-39</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>-35</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK10"/>
+  <dimension ref="A1:BL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -670,6 +670,7 @@
     <col width="10" customWidth="1" min="61" max="61"/>
     <col width="10" customWidth="1" min="62" max="62"/>
     <col width="10" customWidth="1" min="63" max="63"/>
+    <col width="10" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -866,6 +867,9 @@
       <c r="BK1" s="1" t="n">
         <v>20260220</v>
       </c>
+      <c r="BL1" s="1" t="n">
+        <v>20260223</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1061,6 +1065,9 @@
       <c r="BK2" t="n">
         <v>-22</v>
       </c>
+      <c r="BL2" t="n">
+        <v>-20</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1256,6 +1263,9 @@
       <c r="BK3" t="n">
         <v>-104</v>
       </c>
+      <c r="BL3" t="n">
+        <v>-79</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1451,6 +1461,9 @@
       <c r="BK4" t="n">
         <v>-79</v>
       </c>
+      <c r="BL4" t="n">
+        <v>-23</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1646,6 +1659,9 @@
       <c r="BK5" t="n">
         <v>-94</v>
       </c>
+      <c r="BL5" t="n">
+        <v>-92</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1841,6 +1857,9 @@
       <c r="BK6" t="n">
         <v>-74</v>
       </c>
+      <c r="BL6" t="n">
+        <v>-68</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2036,6 +2055,9 @@
       <c r="BK7" t="n">
         <v>36</v>
       </c>
+      <c r="BL7" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2231,6 +2253,9 @@
       <c r="BK8" t="n">
         <v>-84</v>
       </c>
+      <c r="BL8" t="n">
+        <v>-80</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2426,6 +2451,9 @@
       <c r="BK9" t="n">
         <v>57</v>
       </c>
+      <c r="BL9" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2620,6 +2648,9 @@
       </c>
       <c r="BK10" t="n">
         <v>-62</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>-61</v>
       </c>
     </row>
   </sheetData>
@@ -2633,7 +2664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CY10"/>
+  <dimension ref="A1:CZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2739,6 +2770,7 @@
     <col width="12" customWidth="1" min="101" max="101"/>
     <col width="12" customWidth="1" min="102" max="102"/>
     <col width="12" customWidth="1" min="103" max="103"/>
+    <col width="12" customWidth="1" min="104" max="104"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3257,6 +3289,11 @@
           <t>20260220</t>
         </is>
       </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>20260223</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4196,6 +4233,9 @@
       <c r="CY4" t="n">
         <v>93</v>
       </c>
+      <c r="CZ4" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4511,6 +4551,9 @@
       <c r="CY5" t="n">
         <v>94</v>
       </c>
+      <c r="CZ5" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5138,6 +5181,9 @@
       <c r="CY7" t="n">
         <v>101</v>
       </c>
+      <c r="CZ7" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5453,6 +5499,9 @@
       <c r="CY8" t="n">
         <v>93</v>
       </c>
+      <c r="CZ8" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6078,6 +6127,9 @@
         <v>97</v>
       </c>
       <c r="CY10" t="n">
+        <v>98</v>
+      </c>
+      <c r="CZ10" t="n">
         <v>98</v>
       </c>
     </row>
@@ -6092,7 +6144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CF10"/>
+  <dimension ref="A1:CG10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6179,6 +6231,7 @@
     <col width="12" customWidth="1" min="82" max="82"/>
     <col width="12" customWidth="1" min="83" max="83"/>
     <col width="12" customWidth="1" min="84" max="84"/>
+    <col width="12" customWidth="1" min="85" max="85"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6602,6 +6655,11 @@
           <t>20260220</t>
         </is>
       </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>20260223</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7370,6 +7428,9 @@
       <c r="CF4" t="n">
         <v>74.23999999999999</v>
       </c>
+      <c r="CG4" t="n">
+        <v>69.89</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7628,6 +7689,9 @@
       <c r="CF5" t="n">
         <v>30.27</v>
       </c>
+      <c r="CG5" t="n">
+        <v>20.44</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8141,6 +8205,9 @@
       <c r="CF7" t="n">
         <v>25.78</v>
       </c>
+      <c r="CG7" t="n">
+        <v>22.9</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8399,6 +8466,9 @@
       <c r="CF8" t="n">
         <v>9.35</v>
       </c>
+      <c r="CG8" t="n">
+        <v>-3.32</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8911,6 +8981,9 @@
       </c>
       <c r="CF10" t="n">
         <v>-0.67</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>-14.43</v>
       </c>
     </row>
   </sheetData>
@@ -8924,7 +8997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK10"/>
+  <dimension ref="A1:BL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8990,6 +9063,7 @@
     <col width="12" customWidth="1" min="61" max="61"/>
     <col width="12" customWidth="1" min="62" max="62"/>
     <col width="12" customWidth="1" min="63" max="63"/>
+    <col width="12" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9308,6 +9382,11 @@
           <t>20260220</t>
         </is>
       </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>20260223</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9887,6 +9966,9 @@
       <c r="BK4" t="n">
         <v>0</v>
       </c>
+      <c r="BL4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10082,6 +10164,9 @@
       <c r="BK5" t="n">
         <v>0</v>
       </c>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10469,6 +10554,9 @@
       <c r="BK7" t="n">
         <v>0</v>
       </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10664,6 +10752,9 @@
       <c r="BK8" t="n">
         <v>0</v>
       </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11049,6 +11140,9 @@
         <v>0</v>
       </c>
       <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11063,7 +11157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CO10"/>
+  <dimension ref="A1:CP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11159,6 +11253,7 @@
     <col width="10" customWidth="1" min="91" max="91"/>
     <col width="10" customWidth="1" min="92" max="92"/>
     <col width="10" customWidth="1" min="93" max="93"/>
+    <col width="10" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11445,6 +11540,9 @@
       <c r="CO1" s="1" t="n">
         <v>20260220</v>
       </c>
+      <c r="CP1" s="1" t="n">
+        <v>20260223</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11730,6 +11828,9 @@
       <c r="CO2" t="n">
         <v>13</v>
       </c>
+      <c r="CP2" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12015,6 +12116,9 @@
       <c r="CO3" t="n">
         <v>-75</v>
       </c>
+      <c r="CP3" t="n">
+        <v>-55</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12300,6 +12404,9 @@
       <c r="CO4" t="n">
         <v>-100</v>
       </c>
+      <c r="CP4" t="n">
+        <v>-46</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12585,6 +12692,9 @@
       <c r="CO5" t="n">
         <v>-61</v>
       </c>
+      <c r="CP5" t="n">
+        <v>-59</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12870,6 +12980,9 @@
       <c r="CO6" t="n">
         <v>-68</v>
       </c>
+      <c r="CP6" t="n">
+        <v>-57</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13155,6 +13268,9 @@
       <c r="CO7" t="n">
         <v>26</v>
       </c>
+      <c r="CP7" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13440,6 +13556,9 @@
       <c r="CO8" t="n">
         <v>-54</v>
       </c>
+      <c r="CP8" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13725,6 +13844,9 @@
       <c r="CO9" t="n">
         <v>22</v>
       </c>
+      <c r="CP9" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14009,6 +14131,9 @@
       </c>
       <c r="CO10" t="n">
         <v>-51</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>-48</v>
       </c>
     </row>
   </sheetData>
@@ -14022,12 +14147,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14044,6 +14170,9 @@
       <c r="C1" s="1" t="n">
         <v>20260220</v>
       </c>
+      <c r="D1" s="1" t="n">
+        <v>20260223</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14056,6 +14185,9 @@
           <t>AAPL</t>
         </is>
       </c>
+      <c r="D2" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14068,6 +14200,9 @@
           <t>AMZN</t>
         </is>
       </c>
+      <c r="D3" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14083,6 +14218,9 @@
       <c r="C4" t="n">
         <v>71</v>
       </c>
+      <c r="D4" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14098,6 +14236,9 @@
       <c r="C5" t="n">
         <v>3</v>
       </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14110,6 +14251,9 @@
           <t>NFLX</t>
         </is>
       </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14125,6 +14269,9 @@
       <c r="C7" t="n">
         <v>52</v>
       </c>
+      <c r="D7" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14140,6 +14287,9 @@
       <c r="C8" t="n">
         <v>7</v>
       </c>
+      <c r="D8" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14152,6 +14302,9 @@
           <t>SBUX</t>
         </is>
       </c>
+      <c r="D9" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14165,6 +14318,9 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>51</v>
+      </c>
+      <c r="D10" t="n">
         <v>51</v>
       </c>
     </row>
@@ -14179,12 +14335,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14201,6 +14358,9 @@
       <c r="C1" s="1" t="n">
         <v>20260220</v>
       </c>
+      <c r="D1" s="1" t="n">
+        <v>20260223</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14213,6 +14373,9 @@
           <t>AAPL</t>
         </is>
       </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14225,6 +14388,9 @@
           <t>AMZN</t>
         </is>
       </c>
+      <c r="D3" t="n">
+        <v>-84</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14240,6 +14406,9 @@
       <c r="C4" t="n">
         <v>20</v>
       </c>
+      <c r="D4" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14255,6 +14424,9 @@
       <c r="C5" t="n">
         <v>-122</v>
       </c>
+      <c r="D5" t="n">
+        <v>-120</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14267,6 +14439,9 @@
           <t>NFLX</t>
         </is>
       </c>
+      <c r="D6" t="n">
+        <v>-47</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14282,6 +14457,9 @@
       <c r="C7" t="n">
         <v>25</v>
       </c>
+      <c r="D7" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14297,6 +14475,9 @@
       <c r="C8" t="n">
         <v>-111</v>
       </c>
+      <c r="D8" t="n">
+        <v>-108</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14309,6 +14490,9 @@
           <t>SBUX</t>
         </is>
       </c>
+      <c r="D9" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14323,6 +14507,9 @@
       </c>
       <c r="C10" t="n">
         <v>-28</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-30</v>
       </c>
     </row>
   </sheetData>
@@ -14336,7 +14523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DR10"/>
+  <dimension ref="A1:DS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14461,6 +14648,7 @@
     <col width="12" customWidth="1" min="120" max="120"/>
     <col width="12" customWidth="1" min="121" max="121"/>
     <col width="12" customWidth="1" min="122" max="122"/>
+    <col width="12" customWidth="1" min="123" max="123"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14834,6 +15022,9 @@
       <c r="DR1" s="1" t="n">
         <v>20260220</v>
       </c>
+      <c r="DS1" s="1" t="n">
+        <v>20260223</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15203,6 +15394,9 @@
       <c r="DQ2" t="n">
         <v>264.35</v>
       </c>
+      <c r="DS2" t="n">
+        <v>264.58</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15572,6 +15766,9 @@
       <c r="DQ3" t="n">
         <v>204.79</v>
       </c>
+      <c r="DS3" t="n">
+        <v>210.11</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15944,6 +16141,9 @@
       <c r="DR4" t="n">
         <v>302.85</v>
       </c>
+      <c r="DS4" t="n">
+        <v>314.98</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16316,6 +16516,9 @@
       <c r="DR5" t="n">
         <v>398.46</v>
       </c>
+      <c r="DS5" t="n">
+        <v>397.23</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16685,6 +16888,9 @@
       <c r="DQ6" t="n">
         <v>77.98999999999999</v>
       </c>
+      <c r="DS6" t="n">
+        <v>78.67</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17057,6 +17263,9 @@
       <c r="DR7" t="n">
         <v>187.9</v>
       </c>
+      <c r="DS7" t="n">
+        <v>189.82</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17429,6 +17638,9 @@
       <c r="DR8" t="n">
         <v>134.89</v>
       </c>
+      <c r="DS8" t="n">
+        <v>135.24</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17798,6 +18010,9 @@
       <c r="DQ9" t="n">
         <v>95.76000000000001</v>
       </c>
+      <c r="DS9" t="n">
+        <v>97.48999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18169,6 +18384,9 @@
       </c>
       <c r="DR10" t="n">
         <v>411.71</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>411.82</v>
       </c>
     </row>
   </sheetData>
@@ -18182,7 +18400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DR10"/>
+  <dimension ref="A1:DS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18307,6 +18525,7 @@
     <col width="12" customWidth="1" min="120" max="120"/>
     <col width="12" customWidth="1" min="121" max="121"/>
     <col width="12" customWidth="1" min="122" max="122"/>
+    <col width="12" customWidth="1" min="123" max="123"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18680,6 +18899,9 @@
       <c r="DR1" s="1" t="n">
         <v>20260220</v>
       </c>
+      <c r="DS1" s="1" t="n">
+        <v>20260223</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19049,6 +19271,9 @@
       <c r="DQ2" t="n">
         <v>264.35</v>
       </c>
+      <c r="DS2" t="n">
+        <v>264.58</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19418,6 +19643,9 @@
       <c r="DQ3" t="n">
         <v>204.79</v>
       </c>
+      <c r="DS3" t="n">
+        <v>210.11</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19790,6 +20018,9 @@
       <c r="DR4" t="n">
         <v>302.85</v>
       </c>
+      <c r="DS4" t="n">
+        <v>314.98</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20162,6 +20393,9 @@
       <c r="DR5" t="n">
         <v>398.46</v>
       </c>
+      <c r="DS5" t="n">
+        <v>397.23</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20531,6 +20765,9 @@
       <c r="DQ6" t="n">
         <v>77.98999999999999</v>
       </c>
+      <c r="DS6" t="n">
+        <v>78.67</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20903,6 +21140,9 @@
       <c r="DR7" t="n">
         <v>187.9</v>
       </c>
+      <c r="DS7" t="n">
+        <v>189.82</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21275,6 +21515,9 @@
       <c r="DR8" t="n">
         <v>134.89</v>
       </c>
+      <c r="DS8" t="n">
+        <v>135.24</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21644,6 +21887,9 @@
       <c r="DQ9" t="n">
         <v>95.76000000000001</v>
       </c>
+      <c r="DS9" t="n">
+        <v>97.48999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22015,6 +22261,9 @@
       </c>
       <c r="DR10" t="n">
         <v>411.71</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>411.82</v>
       </c>
     </row>
   </sheetData>
@@ -22028,7 +22277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DR10"/>
+  <dimension ref="A1:DS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22153,6 +22402,7 @@
     <col width="12" customWidth="1" min="120" max="120"/>
     <col width="12" customWidth="1" min="121" max="121"/>
     <col width="12" customWidth="1" min="122" max="122"/>
+    <col width="12" customWidth="1" min="123" max="123"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22526,6 +22776,9 @@
       <c r="DR1" s="1" t="n">
         <v>20260220</v>
       </c>
+      <c r="DS1" s="1" t="n">
+        <v>20260223</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22895,6 +23148,9 @@
       <c r="DQ2" t="n">
         <v>264.35</v>
       </c>
+      <c r="DS2" t="n">
+        <v>264.58</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23264,6 +23520,9 @@
       <c r="DQ3" t="n">
         <v>204.79</v>
       </c>
+      <c r="DS3" t="n">
+        <v>210.11</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23636,6 +23895,9 @@
       <c r="DR4" t="n">
         <v>302.85</v>
       </c>
+      <c r="DS4" t="n">
+        <v>314.98</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24008,6 +24270,9 @@
       <c r="DR5" t="n">
         <v>398.46</v>
       </c>
+      <c r="DS5" t="n">
+        <v>397.23</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24377,6 +24642,9 @@
       <c r="DQ6" t="n">
         <v>77.98999999999999</v>
       </c>
+      <c r="DS6" t="n">
+        <v>78.67</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24749,6 +25017,9 @@
       <c r="DR7" t="n">
         <v>187.9</v>
       </c>
+      <c r="DS7" t="n">
+        <v>189.82</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25121,6 +25392,9 @@
       <c r="DR8" t="n">
         <v>134.89</v>
       </c>
+      <c r="DS8" t="n">
+        <v>135.24</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25490,6 +25764,9 @@
       <c r="DQ9" t="n">
         <v>95.76000000000001</v>
       </c>
+      <c r="DS9" t="n">
+        <v>97.48999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25861,6 +26138,9 @@
       </c>
       <c r="DR10" t="n">
         <v>411.71</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>411.82</v>
       </c>
     </row>
   </sheetData>
@@ -25874,7 +26154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DR10"/>
+  <dimension ref="A1:DS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25999,6 +26279,7 @@
     <col width="12" customWidth="1" min="120" max="120"/>
     <col width="12" customWidth="1" min="121" max="121"/>
     <col width="12" customWidth="1" min="122" max="122"/>
+    <col width="12" customWidth="1" min="123" max="123"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26372,6 +26653,9 @@
       <c r="DR1" s="1" t="n">
         <v>20260220</v>
       </c>
+      <c r="DS1" s="1" t="n">
+        <v>20260223</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -26741,6 +27025,9 @@
       <c r="DQ2" t="n">
         <v>264.35</v>
       </c>
+      <c r="DS2" t="n">
+        <v>264.58</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -27110,6 +27397,9 @@
       <c r="DQ3" t="n">
         <v>204.79</v>
       </c>
+      <c r="DS3" t="n">
+        <v>210.11</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -27482,6 +27772,9 @@
       <c r="DR4" t="n">
         <v>302.85</v>
       </c>
+      <c r="DS4" t="n">
+        <v>314.98</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -27854,6 +28147,9 @@
       <c r="DR5" t="n">
         <v>398.46</v>
       </c>
+      <c r="DS5" t="n">
+        <v>397.23</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -28223,6 +28519,9 @@
       <c r="DQ6" t="n">
         <v>77.98999999999999</v>
       </c>
+      <c r="DS6" t="n">
+        <v>78.67</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -28595,6 +28894,9 @@
       <c r="DR7" t="n">
         <v>187.9</v>
       </c>
+      <c r="DS7" t="n">
+        <v>189.82</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -28967,6 +29269,9 @@
       <c r="DR8" t="n">
         <v>134.89</v>
       </c>
+      <c r="DS8" t="n">
+        <v>135.24</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -29336,6 +29641,9 @@
       <c r="DQ9" t="n">
         <v>95.76000000000001</v>
       </c>
+      <c r="DS9" t="n">
+        <v>97.48999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -29707,6 +30015,9 @@
       </c>
       <c r="DR10" t="n">
         <v>411.71</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>411.82</v>
       </c>
     </row>
   </sheetData>
@@ -29720,7 +30031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DR10"/>
+  <dimension ref="A1:DS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -29845,6 +30156,7 @@
     <col width="12" customWidth="1" min="120" max="120"/>
     <col width="12" customWidth="1" min="121" max="121"/>
     <col width="12" customWidth="1" min="122" max="122"/>
+    <col width="12" customWidth="1" min="123" max="123"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30218,6 +30530,9 @@
       <c r="DR1" s="1" t="n">
         <v>20260220</v>
       </c>
+      <c r="DS1" s="1" t="n">
+        <v>20260223</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -30587,6 +30902,9 @@
       <c r="DQ2" t="n">
         <v>0</v>
       </c>
+      <c r="DS2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -30956,6 +31274,9 @@
       <c r="DQ3" t="n">
         <v>0</v>
       </c>
+      <c r="DS3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -31328,6 +31649,9 @@
       <c r="DR4" t="n">
         <v>0</v>
       </c>
+      <c r="DS4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -31700,6 +32024,9 @@
       <c r="DR5" t="n">
         <v>0</v>
       </c>
+      <c r="DS5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -32069,6 +32396,9 @@
       <c r="DQ6" t="n">
         <v>0</v>
       </c>
+      <c r="DS6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -32441,6 +32771,9 @@
       <c r="DR7" t="n">
         <v>0</v>
       </c>
+      <c r="DS7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -32813,6 +33146,9 @@
       <c r="DR8" t="n">
         <v>0</v>
       </c>
+      <c r="DS8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -33182,6 +33518,9 @@
       <c r="DQ9" t="n">
         <v>0</v>
       </c>
+      <c r="DS9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -33552,6 +33891,9 @@
         <v>0</v>
       </c>
       <c r="DR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -33566,7 +33908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CY10"/>
+  <dimension ref="A1:CZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -33672,6 +34014,7 @@
     <col width="10" customWidth="1" min="101" max="101"/>
     <col width="10" customWidth="1" min="102" max="102"/>
     <col width="10" customWidth="1" min="103" max="103"/>
+    <col width="10" customWidth="1" min="104" max="104"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33988,6 +34331,9 @@
       <c r="CY1" s="1" t="n">
         <v>20260220</v>
       </c>
+      <c r="CZ1" s="1" t="n">
+        <v>20260223</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -34303,6 +34649,9 @@
       <c r="CY2" t="n">
         <v>54</v>
       </c>
+      <c r="CZ2" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -34618,6 +34967,9 @@
       <c r="CY3" t="n">
         <v>13</v>
       </c>
+      <c r="CZ3" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -34933,6 +35285,9 @@
       <c r="CY4" t="n">
         <v>2</v>
       </c>
+      <c r="CZ4" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -35248,6 +35603,9 @@
       <c r="CY5" t="n">
         <v>5</v>
       </c>
+      <c r="CZ5" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -35563,6 +35921,9 @@
       <c r="CY6" t="n">
         <v>21</v>
       </c>
+      <c r="CZ6" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -35878,6 +36239,9 @@
       <c r="CY7" t="n">
         <v>78</v>
       </c>
+      <c r="CZ7" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -36193,6 +36557,9 @@
       <c r="CY8" t="n">
         <v>14</v>
       </c>
+      <c r="CZ8" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -36508,6 +36875,9 @@
       <c r="CY9" t="n">
         <v>51</v>
       </c>
+      <c r="CZ9" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -36822,6 +37192,9 @@
       </c>
       <c r="CY10" t="n">
         <v>28</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -36835,7 +37208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK10"/>
+  <dimension ref="A1:BL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -36901,6 +37274,7 @@
     <col width="10" customWidth="1" min="61" max="61"/>
     <col width="10" customWidth="1" min="62" max="62"/>
     <col width="10" customWidth="1" min="63" max="63"/>
+    <col width="10" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37097,6 +37471,9 @@
       <c r="BK1" s="1" t="n">
         <v>20260220</v>
       </c>
+      <c r="BL1" s="1" t="n">
+        <v>20260223</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -37292,6 +37669,9 @@
       <c r="BK2" t="n">
         <v>45</v>
       </c>
+      <c r="BL2" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -37487,6 +37867,9 @@
       <c r="BK3" t="n">
         <v>12</v>
       </c>
+      <c r="BL3" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -37682,6 +38065,9 @@
       <c r="BK4" t="n">
         <v>14</v>
       </c>
+      <c r="BL4" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -37877,6 +38263,9 @@
       <c r="BK5" t="n">
         <v>5</v>
       </c>
+      <c r="BL5" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -38072,6 +38461,9 @@
       <c r="BK6" t="n">
         <v>6</v>
       </c>
+      <c r="BL6" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -38267,6 +38659,9 @@
       <c r="BK7" t="n">
         <v>79</v>
       </c>
+      <c r="BL7" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -38462,6 +38857,9 @@
       <c r="BK8" t="n">
         <v>9</v>
       </c>
+      <c r="BL8" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -38657,6 +39055,9 @@
       <c r="BK9" t="n">
         <v>79</v>
       </c>
+      <c r="BL9" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -38850,6 +39251,9 @@
         <v>20</v>
       </c>
       <c r="BK10" t="n">
+        <v>16</v>
+      </c>
+      <c r="BL10" t="n">
         <v>16</v>
       </c>
     </row>
@@ -38864,7 +39268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CY10"/>
+  <dimension ref="A1:CZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -38970,6 +39374,7 @@
     <col width="10" customWidth="1" min="101" max="101"/>
     <col width="10" customWidth="1" min="102" max="102"/>
     <col width="10" customWidth="1" min="103" max="103"/>
+    <col width="10" customWidth="1" min="104" max="104"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -39286,6 +39691,9 @@
       <c r="CY1" s="1" t="n">
         <v>20260220</v>
       </c>
+      <c r="CZ1" s="1" t="n">
+        <v>20260223</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -39601,6 +40009,9 @@
       <c r="CY2" t="n">
         <v>-1</v>
       </c>
+      <c r="CZ2" t="n">
+        <v>-4</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -39916,6 +40327,9 @@
       <c r="CY3" t="n">
         <v>-56</v>
       </c>
+      <c r="CZ3" t="n">
+        <v>-37</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -40231,6 +40645,9 @@
       <c r="CY4" t="n">
         <v>-78</v>
       </c>
+      <c r="CZ4" t="n">
+        <v>-31</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -40546,6 +40963,9 @@
       <c r="CY5" t="n">
         <v>-42</v>
       </c>
+      <c r="CZ5" t="n">
+        <v>-40</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -40861,6 +41281,9 @@
       <c r="CY6" t="n">
         <v>-58</v>
       </c>
+      <c r="CZ6" t="n">
+        <v>-42</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -41176,6 +41599,9 @@
       <c r="CY7" t="n">
         <v>18</v>
       </c>
+      <c r="CZ7" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -41491,6 +41917,9 @@
       <c r="CY8" t="n">
         <v>-37</v>
       </c>
+      <c r="CZ8" t="n">
+        <v>-32</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -41806,6 +42235,9 @@
       <c r="CY9" t="n">
         <v>-4</v>
       </c>
+      <c r="CZ9" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -42120,6 +42552,9 @@
       </c>
       <c r="CY10" t="n">
         <v>-35</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>-32</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL10"/>
+  <dimension ref="A1:BM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -671,6 +671,7 @@
     <col width="10" customWidth="1" min="62" max="62"/>
     <col width="10" customWidth="1" min="63" max="63"/>
     <col width="10" customWidth="1" min="64" max="64"/>
+    <col width="10" customWidth="1" min="65" max="65"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -870,6 +871,9 @@
       <c r="BL1" s="1" t="n">
         <v>20260223</v>
       </c>
+      <c r="BM1" s="1" t="n">
+        <v>20260224</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1068,6 +1072,9 @@
       <c r="BL2" t="n">
         <v>-20</v>
       </c>
+      <c r="BM2" t="n">
+        <v>-11</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1266,6 +1273,9 @@
       <c r="BL3" t="n">
         <v>-79</v>
       </c>
+      <c r="BM3" t="n">
+        <v>-95</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1464,6 +1474,9 @@
       <c r="BL4" t="n">
         <v>-23</v>
       </c>
+      <c r="BM4" t="n">
+        <v>-38</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1662,6 +1675,9 @@
       <c r="BL5" t="n">
         <v>-92</v>
       </c>
+      <c r="BM5" t="n">
+        <v>-105</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1860,6 +1876,9 @@
       <c r="BL6" t="n">
         <v>-68</v>
       </c>
+      <c r="BM6" t="n">
+        <v>-81</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2058,6 +2077,9 @@
       <c r="BL7" t="n">
         <v>52</v>
       </c>
+      <c r="BM7" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2256,6 +2278,9 @@
       <c r="BL8" t="n">
         <v>-80</v>
       </c>
+      <c r="BM8" t="n">
+        <v>-88</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2454,6 +2479,9 @@
       <c r="BL9" t="n">
         <v>71</v>
       </c>
+      <c r="BM9" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2651,6 +2679,9 @@
       </c>
       <c r="BL10" t="n">
         <v>-61</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>-85</v>
       </c>
     </row>
   </sheetData>
@@ -2664,7 +2695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CZ10"/>
+  <dimension ref="A1:DA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2771,6 +2802,7 @@
     <col width="12" customWidth="1" min="102" max="102"/>
     <col width="12" customWidth="1" min="103" max="103"/>
     <col width="12" customWidth="1" min="104" max="104"/>
+    <col width="12" customWidth="1" min="105" max="105"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3294,6 +3326,11 @@
           <t>20260223</t>
         </is>
       </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4236,6 +4273,9 @@
       <c r="CZ4" t="n">
         <v>97</v>
       </c>
+      <c r="DA4" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4554,6 +4594,9 @@
       <c r="CZ5" t="n">
         <v>95</v>
       </c>
+      <c r="DA5" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5184,6 +5227,9 @@
       <c r="CZ7" t="n">
         <v>102</v>
       </c>
+      <c r="DA7" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5502,6 +5548,9 @@
       <c r="CZ8" t="n">
         <v>95</v>
       </c>
+      <c r="DA8" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6131,6 +6180,9 @@
       </c>
       <c r="CZ10" t="n">
         <v>98</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -6144,7 +6196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG10"/>
+  <dimension ref="A1:CH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6232,6 +6284,7 @@
     <col width="12" customWidth="1" min="83" max="83"/>
     <col width="12" customWidth="1" min="84" max="84"/>
     <col width="12" customWidth="1" min="85" max="85"/>
+    <col width="12" customWidth="1" min="86" max="86"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6660,6 +6713,11 @@
           <t>20260223</t>
         </is>
       </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7431,6 +7489,9 @@
       <c r="CG4" t="n">
         <v>69.89</v>
       </c>
+      <c r="CH4" t="n">
+        <v>64.94</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7692,6 +7753,9 @@
       <c r="CG5" t="n">
         <v>20.44</v>
       </c>
+      <c r="CH5" t="n">
+        <v>9.9</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8208,6 +8272,9 @@
       <c r="CG7" t="n">
         <v>22.9</v>
       </c>
+      <c r="CH7" t="n">
+        <v>21.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8469,6 +8536,9 @@
       <c r="CG8" t="n">
         <v>-3.32</v>
       </c>
+      <c r="CH8" t="n">
+        <v>-15.22</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8984,6 +9054,9 @@
       </c>
       <c r="CG10" t="n">
         <v>-14.43</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>-13.85</v>
       </c>
     </row>
   </sheetData>
@@ -8997,7 +9070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL10"/>
+  <dimension ref="A1:BM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9064,6 +9137,7 @@
     <col width="12" customWidth="1" min="62" max="62"/>
     <col width="12" customWidth="1" min="63" max="63"/>
     <col width="12" customWidth="1" min="64" max="64"/>
+    <col width="12" customWidth="1" min="65" max="65"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9387,6 +9461,11 @@
           <t>20260223</t>
         </is>
       </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9969,6 +10048,9 @@
       <c r="BL4" t="n">
         <v>0</v>
       </c>
+      <c r="BM4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10167,6 +10249,9 @@
       <c r="BL5" t="n">
         <v>0</v>
       </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10557,6 +10642,9 @@
       <c r="BL7" t="n">
         <v>0</v>
       </c>
+      <c r="BM7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10755,6 +10843,9 @@
       <c r="BL8" t="n">
         <v>0</v>
       </c>
+      <c r="BM8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11143,6 +11234,9 @@
         <v>0</v>
       </c>
       <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11157,7 +11251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CP10"/>
+  <dimension ref="A1:CQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11254,6 +11348,7 @@
     <col width="10" customWidth="1" min="92" max="92"/>
     <col width="10" customWidth="1" min="93" max="93"/>
     <col width="10" customWidth="1" min="94" max="94"/>
+    <col width="10" customWidth="1" min="95" max="95"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11543,6 +11638,9 @@
       <c r="CP1" s="1" t="n">
         <v>20260223</v>
       </c>
+      <c r="CQ1" s="1" t="n">
+        <v>20260224</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11831,6 +11929,9 @@
       <c r="CP2" t="n">
         <v>14</v>
       </c>
+      <c r="CQ2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12119,6 +12220,9 @@
       <c r="CP3" t="n">
         <v>-55</v>
       </c>
+      <c r="CQ3" t="n">
+        <v>-65</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12407,6 +12511,9 @@
       <c r="CP4" t="n">
         <v>-46</v>
       </c>
+      <c r="CQ4" t="n">
+        <v>-57</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12695,6 +12802,9 @@
       <c r="CP5" t="n">
         <v>-59</v>
       </c>
+      <c r="CQ5" t="n">
+        <v>-74</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12983,6 +13093,9 @@
       <c r="CP6" t="n">
         <v>-57</v>
       </c>
+      <c r="CQ6" t="n">
+        <v>-82</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13271,6 +13384,9 @@
       <c r="CP7" t="n">
         <v>42</v>
       </c>
+      <c r="CQ7" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13559,6 +13675,9 @@
       <c r="CP8" t="n">
         <v>-50</v>
       </c>
+      <c r="CQ8" t="n">
+        <v>-59</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13847,6 +13966,9 @@
       <c r="CP9" t="n">
         <v>46</v>
       </c>
+      <c r="CQ9" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14134,6 +14256,9 @@
       </c>
       <c r="CP10" t="n">
         <v>-48</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>-82</v>
       </c>
     </row>
   </sheetData>
@@ -14147,13 +14272,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14173,6 +14299,9 @@
       <c r="D1" s="1" t="n">
         <v>20260223</v>
       </c>
+      <c r="E1" s="1" t="n">
+        <v>20260224</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14188,6 +14317,9 @@
       <c r="D2" t="n">
         <v>64</v>
       </c>
+      <c r="E2" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14203,6 +14335,9 @@
       <c r="D3" t="n">
         <v>21</v>
       </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14221,6 +14356,9 @@
       <c r="D4" t="n">
         <v>81</v>
       </c>
+      <c r="E4" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14239,6 +14377,9 @@
       <c r="D5" t="n">
         <v>2</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14254,6 +14395,9 @@
       <c r="D6" t="n">
         <v>0</v>
       </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14272,6 +14416,9 @@
       <c r="D7" t="n">
         <v>57</v>
       </c>
+      <c r="E7" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14290,6 +14437,9 @@
       <c r="D8" t="n">
         <v>8</v>
       </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14305,6 +14455,9 @@
       <c r="D9" t="n">
         <v>91</v>
       </c>
+      <c r="E9" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14322,6 +14475,9 @@
       </c>
       <c r="D10" t="n">
         <v>51</v>
+      </c>
+      <c r="E10" t="n">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -14335,13 +14491,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14361,6 +14518,9 @@
       <c r="D1" s="1" t="n">
         <v>20260223</v>
       </c>
+      <c r="E1" s="1" t="n">
+        <v>20260224</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14376,6 +14536,9 @@
       <c r="D2" t="n">
         <v>10</v>
       </c>
+      <c r="E2" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14391,6 +14554,9 @@
       <c r="D3" t="n">
         <v>-84</v>
       </c>
+      <c r="E3" t="n">
+        <v>-103</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14409,6 +14575,9 @@
       <c r="D4" t="n">
         <v>36</v>
       </c>
+      <c r="E4" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14427,6 +14596,9 @@
       <c r="D5" t="n">
         <v>-120</v>
       </c>
+      <c r="E5" t="n">
+        <v>-132</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14442,6 +14614,9 @@
       <c r="D6" t="n">
         <v>-47</v>
       </c>
+      <c r="E6" t="n">
+        <v>-46</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14460,6 +14635,9 @@
       <c r="D7" t="n">
         <v>37</v>
       </c>
+      <c r="E7" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14478,6 +14656,9 @@
       <c r="D8" t="n">
         <v>-108</v>
       </c>
+      <c r="E8" t="n">
+        <v>-119</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14493,6 +14674,9 @@
       <c r="D9" t="n">
         <v>104</v>
       </c>
+      <c r="E9" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14510,6 +14694,9 @@
       </c>
       <c r="D10" t="n">
         <v>-30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-53</v>
       </c>
     </row>
   </sheetData>
@@ -14523,7 +14710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DS10"/>
+  <dimension ref="A1:DT10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14649,6 +14836,7 @@
     <col width="12" customWidth="1" min="121" max="121"/>
     <col width="12" customWidth="1" min="122" max="122"/>
     <col width="12" customWidth="1" min="123" max="123"/>
+    <col width="12" customWidth="1" min="124" max="124"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15025,6 +15213,9 @@
       <c r="DS1" s="1" t="n">
         <v>20260223</v>
       </c>
+      <c r="DT1" s="1" t="n">
+        <v>20260224</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15397,6 +15588,9 @@
       <c r="DS2" t="n">
         <v>264.58</v>
       </c>
+      <c r="DT2" t="n">
+        <v>266.18</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15769,6 +15963,9 @@
       <c r="DS3" t="n">
         <v>210.11</v>
       </c>
+      <c r="DT3" t="n">
+        <v>205.27</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16144,6 +16341,9 @@
       <c r="DS4" t="n">
         <v>314.98</v>
       </c>
+      <c r="DT4" t="n">
+        <v>311.49</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16519,6 +16719,9 @@
       <c r="DS5" t="n">
         <v>397.23</v>
       </c>
+      <c r="DT5" t="n">
+        <v>384.47</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16891,6 +17094,9 @@
       <c r="DS6" t="n">
         <v>78.67</v>
       </c>
+      <c r="DT6" t="n">
+        <v>76.02</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17266,6 +17472,9 @@
       <c r="DS7" t="n">
         <v>189.82</v>
       </c>
+      <c r="DT7" t="n">
+        <v>191.55</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17641,6 +17850,9 @@
       <c r="DS8" t="n">
         <v>135.24</v>
       </c>
+      <c r="DT8" t="n">
+        <v>130.6</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18013,6 +18225,9 @@
       <c r="DS9" t="n">
         <v>97.48999999999999</v>
       </c>
+      <c r="DT9" t="n">
+        <v>94.78</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18387,6 +18602,9 @@
       </c>
       <c r="DS10" t="n">
         <v>411.82</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>399.83</v>
       </c>
     </row>
   </sheetData>
@@ -18400,7 +18618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DS10"/>
+  <dimension ref="A1:DT10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18526,6 +18744,7 @@
     <col width="12" customWidth="1" min="121" max="121"/>
     <col width="12" customWidth="1" min="122" max="122"/>
     <col width="12" customWidth="1" min="123" max="123"/>
+    <col width="12" customWidth="1" min="124" max="124"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18902,6 +19121,9 @@
       <c r="DS1" s="1" t="n">
         <v>20260223</v>
       </c>
+      <c r="DT1" s="1" t="n">
+        <v>20260224</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19274,6 +19496,9 @@
       <c r="DS2" t="n">
         <v>264.58</v>
       </c>
+      <c r="DT2" t="n">
+        <v>266.18</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19646,6 +19871,9 @@
       <c r="DS3" t="n">
         <v>210.11</v>
       </c>
+      <c r="DT3" t="n">
+        <v>205.27</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20021,6 +20249,9 @@
       <c r="DS4" t="n">
         <v>314.98</v>
       </c>
+      <c r="DT4" t="n">
+        <v>311.49</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20396,6 +20627,9 @@
       <c r="DS5" t="n">
         <v>397.23</v>
       </c>
+      <c r="DT5" t="n">
+        <v>384.47</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20768,6 +21002,9 @@
       <c r="DS6" t="n">
         <v>78.67</v>
       </c>
+      <c r="DT6" t="n">
+        <v>76.02</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21143,6 +21380,9 @@
       <c r="DS7" t="n">
         <v>189.82</v>
       </c>
+      <c r="DT7" t="n">
+        <v>191.55</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21518,6 +21758,9 @@
       <c r="DS8" t="n">
         <v>135.24</v>
       </c>
+      <c r="DT8" t="n">
+        <v>130.6</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21890,6 +22133,9 @@
       <c r="DS9" t="n">
         <v>97.48999999999999</v>
       </c>
+      <c r="DT9" t="n">
+        <v>94.78</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22264,6 +22510,9 @@
       </c>
       <c r="DS10" t="n">
         <v>411.82</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>399.83</v>
       </c>
     </row>
   </sheetData>
@@ -22277,7 +22526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DS10"/>
+  <dimension ref="A1:DT10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22403,6 +22652,7 @@
     <col width="12" customWidth="1" min="121" max="121"/>
     <col width="12" customWidth="1" min="122" max="122"/>
     <col width="12" customWidth="1" min="123" max="123"/>
+    <col width="12" customWidth="1" min="124" max="124"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22779,6 +23029,9 @@
       <c r="DS1" s="1" t="n">
         <v>20260223</v>
       </c>
+      <c r="DT1" s="1" t="n">
+        <v>20260224</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23151,6 +23404,9 @@
       <c r="DS2" t="n">
         <v>264.58</v>
       </c>
+      <c r="DT2" t="n">
+        <v>266.18</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23523,6 +23779,9 @@
       <c r="DS3" t="n">
         <v>210.11</v>
       </c>
+      <c r="DT3" t="n">
+        <v>205.27</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23898,6 +24157,9 @@
       <c r="DS4" t="n">
         <v>314.98</v>
       </c>
+      <c r="DT4" t="n">
+        <v>311.49</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24273,6 +24535,9 @@
       <c r="DS5" t="n">
         <v>397.23</v>
       </c>
+      <c r="DT5" t="n">
+        <v>384.47</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24645,6 +24910,9 @@
       <c r="DS6" t="n">
         <v>78.67</v>
       </c>
+      <c r="DT6" t="n">
+        <v>76.02</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -25020,6 +25288,9 @@
       <c r="DS7" t="n">
         <v>189.82</v>
       </c>
+      <c r="DT7" t="n">
+        <v>191.55</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25395,6 +25666,9 @@
       <c r="DS8" t="n">
         <v>135.24</v>
       </c>
+      <c r="DT8" t="n">
+        <v>130.6</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25767,6 +26041,9 @@
       <c r="DS9" t="n">
         <v>97.48999999999999</v>
       </c>
+      <c r="DT9" t="n">
+        <v>94.78</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26141,6 +26418,9 @@
       </c>
       <c r="DS10" t="n">
         <v>411.82</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>399.83</v>
       </c>
     </row>
   </sheetData>
@@ -26154,7 +26434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DS10"/>
+  <dimension ref="A1:DT10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -26280,6 +26560,7 @@
     <col width="12" customWidth="1" min="121" max="121"/>
     <col width="12" customWidth="1" min="122" max="122"/>
     <col width="12" customWidth="1" min="123" max="123"/>
+    <col width="12" customWidth="1" min="124" max="124"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26656,6 +26937,9 @@
       <c r="DS1" s="1" t="n">
         <v>20260223</v>
       </c>
+      <c r="DT1" s="1" t="n">
+        <v>20260224</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -27028,6 +27312,9 @@
       <c r="DS2" t="n">
         <v>264.58</v>
       </c>
+      <c r="DT2" t="n">
+        <v>266.18</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -27400,6 +27687,9 @@
       <c r="DS3" t="n">
         <v>210.11</v>
       </c>
+      <c r="DT3" t="n">
+        <v>205.27</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -27775,6 +28065,9 @@
       <c r="DS4" t="n">
         <v>314.98</v>
       </c>
+      <c r="DT4" t="n">
+        <v>311.49</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -28150,6 +28443,9 @@
       <c r="DS5" t="n">
         <v>397.23</v>
       </c>
+      <c r="DT5" t="n">
+        <v>384.47</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -28522,6 +28818,9 @@
       <c r="DS6" t="n">
         <v>78.67</v>
       </c>
+      <c r="DT6" t="n">
+        <v>76.02</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -28897,6 +29196,9 @@
       <c r="DS7" t="n">
         <v>189.82</v>
       </c>
+      <c r="DT7" t="n">
+        <v>191.55</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -29272,6 +29574,9 @@
       <c r="DS8" t="n">
         <v>135.24</v>
       </c>
+      <c r="DT8" t="n">
+        <v>130.6</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -29644,6 +29949,9 @@
       <c r="DS9" t="n">
         <v>97.48999999999999</v>
       </c>
+      <c r="DT9" t="n">
+        <v>94.78</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -30018,6 +30326,9 @@
       </c>
       <c r="DS10" t="n">
         <v>411.82</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>399.83</v>
       </c>
     </row>
   </sheetData>
@@ -30031,7 +30342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DS10"/>
+  <dimension ref="A1:DT10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -30157,6 +30468,7 @@
     <col width="12" customWidth="1" min="121" max="121"/>
     <col width="12" customWidth="1" min="122" max="122"/>
     <col width="12" customWidth="1" min="123" max="123"/>
+    <col width="12" customWidth="1" min="124" max="124"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30533,6 +30845,9 @@
       <c r="DS1" s="1" t="n">
         <v>20260223</v>
       </c>
+      <c r="DT1" s="1" t="n">
+        <v>20260224</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -30905,6 +31220,9 @@
       <c r="DS2" t="n">
         <v>0</v>
       </c>
+      <c r="DT2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -31277,6 +31595,9 @@
       <c r="DS3" t="n">
         <v>0</v>
       </c>
+      <c r="DT3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -31652,6 +31973,9 @@
       <c r="DS4" t="n">
         <v>0</v>
       </c>
+      <c r="DT4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -32027,6 +32351,9 @@
       <c r="DS5" t="n">
         <v>0</v>
       </c>
+      <c r="DT5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -32399,6 +32726,9 @@
       <c r="DS6" t="n">
         <v>0</v>
       </c>
+      <c r="DT6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -32774,6 +33104,9 @@
       <c r="DS7" t="n">
         <v>0</v>
       </c>
+      <c r="DT7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -33149,6 +33482,9 @@
       <c r="DS8" t="n">
         <v>0</v>
       </c>
+      <c r="DT8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -33521,6 +33857,9 @@
       <c r="DS9" t="n">
         <v>0</v>
       </c>
+      <c r="DT9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -33894,6 +34233,9 @@
         <v>0</v>
       </c>
       <c r="DS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -33908,7 +34250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CZ10"/>
+  <dimension ref="A1:DA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -34015,6 +34357,7 @@
     <col width="10" customWidth="1" min="102" max="102"/>
     <col width="10" customWidth="1" min="103" max="103"/>
     <col width="10" customWidth="1" min="104" max="104"/>
+    <col width="10" customWidth="1" min="105" max="105"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -34334,6 +34677,9 @@
       <c r="CZ1" s="1" t="n">
         <v>20260223</v>
       </c>
+      <c r="DA1" s="1" t="n">
+        <v>20260224</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -34652,6 +34998,9 @@
       <c r="CZ2" t="n">
         <v>55</v>
       </c>
+      <c r="DA2" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -34970,6 +35319,9 @@
       <c r="CZ3" t="n">
         <v>25</v>
       </c>
+      <c r="DA3" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -35288,6 +35640,9 @@
       <c r="CZ4" t="n">
         <v>34</v>
       </c>
+      <c r="DA4" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -35606,6 +35961,9 @@
       <c r="CZ5" t="n">
         <v>4</v>
       </c>
+      <c r="DA5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -35924,6 +36282,9 @@
       <c r="CZ6" t="n">
         <v>27</v>
       </c>
+      <c r="DA6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -36242,6 +36603,9 @@
       <c r="CZ7" t="n">
         <v>87</v>
       </c>
+      <c r="DA7" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -36560,6 +36924,9 @@
       <c r="CZ8" t="n">
         <v>16</v>
       </c>
+      <c r="DA8" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -36878,6 +37245,9 @@
       <c r="CZ9" t="n">
         <v>74</v>
       </c>
+      <c r="DA9" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -37195,6 +37565,9 @@
       </c>
       <c r="CZ10" t="n">
         <v>38</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -37208,7 +37581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL10"/>
+  <dimension ref="A1:BM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -37275,6 +37648,7 @@
     <col width="10" customWidth="1" min="62" max="62"/>
     <col width="10" customWidth="1" min="63" max="63"/>
     <col width="10" customWidth="1" min="64" max="64"/>
+    <col width="10" customWidth="1" min="65" max="65"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37474,6 +37848,9 @@
       <c r="BL1" s="1" t="n">
         <v>20260223</v>
       </c>
+      <c r="BM1" s="1" t="n">
+        <v>20260224</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -37672,6 +38049,9 @@
       <c r="BL2" t="n">
         <v>45</v>
       </c>
+      <c r="BM2" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -37870,6 +38250,9 @@
       <c r="BL3" t="n">
         <v>23</v>
       </c>
+      <c r="BM3" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -38068,6 +38451,9 @@
       <c r="BL4" t="n">
         <v>42</v>
       </c>
+      <c r="BM4" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -38266,6 +38652,9 @@
       <c r="BL5" t="n">
         <v>4</v>
       </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -38464,6 +38853,9 @@
       <c r="BL6" t="n">
         <v>8</v>
       </c>
+      <c r="BM6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -38662,6 +39054,9 @@
       <c r="BL7" t="n">
         <v>88</v>
       </c>
+      <c r="BM7" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -38860,6 +39255,9 @@
       <c r="BL8" t="n">
         <v>9</v>
       </c>
+      <c r="BM8" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -39058,6 +39456,9 @@
       <c r="BL9" t="n">
         <v>89</v>
       </c>
+      <c r="BM9" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -39255,6 +39656,9 @@
       </c>
       <c r="BL10" t="n">
         <v>16</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -39268,7 +39672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CZ10"/>
+  <dimension ref="A1:DA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -39375,6 +39779,7 @@
     <col width="10" customWidth="1" min="102" max="102"/>
     <col width="10" customWidth="1" min="103" max="103"/>
     <col width="10" customWidth="1" min="104" max="104"/>
+    <col width="10" customWidth="1" min="105" max="105"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -39694,6 +40099,9 @@
       <c r="CZ1" s="1" t="n">
         <v>20260223</v>
       </c>
+      <c r="DA1" s="1" t="n">
+        <v>20260224</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -40012,6 +40420,9 @@
       <c r="CZ2" t="n">
         <v>-4</v>
       </c>
+      <c r="DA2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -40330,6 +40741,9 @@
       <c r="CZ3" t="n">
         <v>-37</v>
       </c>
+      <c r="DA3" t="n">
+        <v>-46</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -40648,6 +41062,9 @@
       <c r="CZ4" t="n">
         <v>-31</v>
       </c>
+      <c r="DA4" t="n">
+        <v>-40</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -40966,6 +41383,9 @@
       <c r="CZ5" t="n">
         <v>-40</v>
       </c>
+      <c r="DA5" t="n">
+        <v>-59</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -41284,6 +41704,9 @@
       <c r="CZ6" t="n">
         <v>-42</v>
       </c>
+      <c r="DA6" t="n">
+        <v>-77</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -41602,6 +42025,9 @@
       <c r="CZ7" t="n">
         <v>33</v>
       </c>
+      <c r="DA7" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -41920,6 +42346,9 @@
       <c r="CZ8" t="n">
         <v>-32</v>
       </c>
+      <c r="DA8" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -42238,6 +42667,9 @@
       <c r="CZ9" t="n">
         <v>34</v>
       </c>
+      <c r="DA9" t="n">
+        <v>-25</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -42555,6 +42987,9 @@
       </c>
       <c r="CZ10" t="n">
         <v>-32</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>-81</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM10"/>
+  <dimension ref="A1:BN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -672,6 +672,7 @@
     <col width="10" customWidth="1" min="63" max="63"/>
     <col width="10" customWidth="1" min="64" max="64"/>
     <col width="10" customWidth="1" min="65" max="65"/>
+    <col width="10" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -874,6 +875,9 @@
       <c r="BM1" s="1" t="n">
         <v>20260224</v>
       </c>
+      <c r="BN1" s="1" t="n">
+        <v>20260225</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1075,6 +1079,9 @@
       <c r="BM2" t="n">
         <v>-11</v>
       </c>
+      <c r="BN2" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1276,6 +1283,9 @@
       <c r="BM3" t="n">
         <v>-95</v>
       </c>
+      <c r="BN3" t="n">
+        <v>-78</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1477,6 +1487,9 @@
       <c r="BM4" t="n">
         <v>-38</v>
       </c>
+      <c r="BN4" t="n">
+        <v>-40</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1678,6 +1691,9 @@
       <c r="BM5" t="n">
         <v>-105</v>
       </c>
+      <c r="BN5" t="n">
+        <v>-93</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1879,6 +1895,9 @@
       <c r="BM6" t="n">
         <v>-81</v>
       </c>
+      <c r="BN6" t="n">
+        <v>-67</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2080,6 +2099,9 @@
       <c r="BM7" t="n">
         <v>66</v>
       </c>
+      <c r="BN7" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2281,6 +2303,9 @@
       <c r="BM8" t="n">
         <v>-88</v>
       </c>
+      <c r="BN8" t="n">
+        <v>-89</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2482,6 +2507,9 @@
       <c r="BM9" t="n">
         <v>43</v>
       </c>
+      <c r="BN9" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2682,6 +2710,9 @@
       </c>
       <c r="BM10" t="n">
         <v>-85</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>-63</v>
       </c>
     </row>
   </sheetData>
@@ -2695,7 +2726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DA10"/>
+  <dimension ref="A1:DB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2803,6 +2834,7 @@
     <col width="12" customWidth="1" min="103" max="103"/>
     <col width="12" customWidth="1" min="104" max="104"/>
     <col width="12" customWidth="1" min="105" max="105"/>
+    <col width="12" customWidth="1" min="106" max="106"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3331,6 +3363,11 @@
           <t>20260224</t>
         </is>
       </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>20260225</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4276,6 +4313,9 @@
       <c r="DA4" t="n">
         <v>97</v>
       </c>
+      <c r="DB4" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4597,6 +4637,9 @@
       <c r="DA5" t="n">
         <v>93</v>
       </c>
+      <c r="DB5" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5230,6 +5273,9 @@
       <c r="DA7" t="n">
         <v>103</v>
       </c>
+      <c r="DB7" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5551,6 +5597,9 @@
       <c r="DA8" t="n">
         <v>93</v>
       </c>
+      <c r="DB8" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6183,6 +6232,9 @@
       </c>
       <c r="DA10" t="n">
         <v>96</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -6196,7 +6248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CH10"/>
+  <dimension ref="A1:CI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6285,6 +6337,7 @@
     <col width="12" customWidth="1" min="84" max="84"/>
     <col width="12" customWidth="1" min="85" max="85"/>
     <col width="12" customWidth="1" min="86" max="86"/>
+    <col width="12" customWidth="1" min="87" max="87"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6718,6 +6771,11 @@
           <t>20260224</t>
         </is>
       </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>20260225</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7492,6 +7550,9 @@
       <c r="CH4" t="n">
         <v>64.94</v>
       </c>
+      <c r="CI4" t="n">
+        <v>58.78</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7756,6 +7817,9 @@
       <c r="CH5" t="n">
         <v>9.9</v>
       </c>
+      <c r="CI5" t="n">
+        <v>-10.73</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8275,6 +8339,9 @@
       <c r="CH7" t="n">
         <v>21.49</v>
       </c>
+      <c r="CI7" t="n">
+        <v>20.4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8539,6 +8606,9 @@
       <c r="CH8" t="n">
         <v>-15.22</v>
       </c>
+      <c r="CI8" t="n">
+        <v>-28.04</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9057,6 +9127,9 @@
       </c>
       <c r="CH10" t="n">
         <v>-13.85</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>-17.66</v>
       </c>
     </row>
   </sheetData>
@@ -9070,7 +9143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM10"/>
+  <dimension ref="A1:BN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9138,6 +9211,7 @@
     <col width="12" customWidth="1" min="63" max="63"/>
     <col width="12" customWidth="1" min="64" max="64"/>
     <col width="12" customWidth="1" min="65" max="65"/>
+    <col width="12" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9466,6 +9540,11 @@
           <t>20260224</t>
         </is>
       </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>20260225</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10051,6 +10130,9 @@
       <c r="BM4" t="n">
         <v>0</v>
       </c>
+      <c r="BN4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10252,6 +10334,9 @@
       <c r="BM5" t="n">
         <v>0</v>
       </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10645,6 +10730,9 @@
       <c r="BM7" t="n">
         <v>0</v>
       </c>
+      <c r="BN7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10846,6 +10934,9 @@
       <c r="BM8" t="n">
         <v>0</v>
       </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11237,6 +11328,9 @@
         <v>0</v>
       </c>
       <c r="BM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11251,7 +11345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CQ10"/>
+  <dimension ref="A1:CR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11349,6 +11443,7 @@
     <col width="10" customWidth="1" min="93" max="93"/>
     <col width="10" customWidth="1" min="94" max="94"/>
     <col width="10" customWidth="1" min="95" max="95"/>
+    <col width="10" customWidth="1" min="96" max="96"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11641,6 +11736,9 @@
       <c r="CQ1" s="1" t="n">
         <v>20260224</v>
       </c>
+      <c r="CR1" s="1" t="n">
+        <v>20260225</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11932,6 +12030,9 @@
       <c r="CQ2" t="n">
         <v>21</v>
       </c>
+      <c r="CR2" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12223,6 +12324,9 @@
       <c r="CQ3" t="n">
         <v>-65</v>
       </c>
+      <c r="CR3" t="n">
+        <v>-52</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12514,6 +12618,9 @@
       <c r="CQ4" t="n">
         <v>-57</v>
       </c>
+      <c r="CR4" t="n">
+        <v>-55</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12805,6 +12912,9 @@
       <c r="CQ5" t="n">
         <v>-74</v>
       </c>
+      <c r="CR5" t="n">
+        <v>-63</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13096,6 +13206,9 @@
       <c r="CQ6" t="n">
         <v>-82</v>
       </c>
+      <c r="CR6" t="n">
+        <v>-55</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13387,6 +13500,9 @@
       <c r="CQ7" t="n">
         <v>55</v>
       </c>
+      <c r="CR7" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13678,6 +13794,9 @@
       <c r="CQ8" t="n">
         <v>-59</v>
       </c>
+      <c r="CR8" t="n">
+        <v>-61</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13969,6 +14088,9 @@
       <c r="CQ9" t="n">
         <v>-2</v>
       </c>
+      <c r="CR9" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14259,6 +14381,9 @@
       </c>
       <c r="CQ10" t="n">
         <v>-82</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>-47</v>
       </c>
     </row>
   </sheetData>
@@ -14272,7 +14397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14280,6 +14405,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14302,6 +14428,9 @@
       <c r="E1" s="1" t="n">
         <v>20260224</v>
       </c>
+      <c r="F1" s="1" t="n">
+        <v>20260225</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14320,6 +14449,9 @@
       <c r="E2" t="n">
         <v>66</v>
       </c>
+      <c r="F2" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14338,6 +14470,9 @@
       <c r="E3" t="n">
         <v>12</v>
       </c>
+      <c r="F3" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14359,6 +14494,9 @@
       <c r="E4" t="n">
         <v>74</v>
       </c>
+      <c r="F4" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14380,6 +14518,9 @@
       <c r="E5" t="n">
         <v>0</v>
       </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14398,6 +14539,9 @@
       <c r="E6" t="n">
         <v>0</v>
       </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14419,6 +14563,9 @@
       <c r="E7" t="n">
         <v>61</v>
       </c>
+      <c r="F7" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14440,6 +14587,9 @@
       <c r="E8" t="n">
         <v>2</v>
       </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14458,6 +14608,9 @@
       <c r="E9" t="n">
         <v>78</v>
       </c>
+      <c r="F9" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14478,6 +14631,9 @@
       </c>
       <c r="E10" t="n">
         <v>42</v>
+      </c>
+      <c r="F10" t="n">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -14491,7 +14647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14499,6 +14655,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14521,6 +14678,9 @@
       <c r="E1" s="1" t="n">
         <v>20260224</v>
       </c>
+      <c r="F1" s="1" t="n">
+        <v>20260225</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14539,6 +14699,9 @@
       <c r="E2" t="n">
         <v>15</v>
       </c>
+      <c r="F2" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14557,6 +14720,9 @@
       <c r="E3" t="n">
         <v>-103</v>
       </c>
+      <c r="F3" t="n">
+        <v>-86</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14578,6 +14744,9 @@
       <c r="E4" t="n">
         <v>31</v>
       </c>
+      <c r="F4" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14599,6 +14768,9 @@
       <c r="E5" t="n">
         <v>-132</v>
       </c>
+      <c r="F5" t="n">
+        <v>-122</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14617,6 +14789,9 @@
       <c r="E6" t="n">
         <v>-46</v>
       </c>
+      <c r="F6" t="n">
+        <v>-45</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14638,6 +14813,9 @@
       <c r="E7" t="n">
         <v>47</v>
       </c>
+      <c r="F7" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14659,6 +14837,9 @@
       <c r="E8" t="n">
         <v>-119</v>
       </c>
+      <c r="F8" t="n">
+        <v>-120</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14677,6 +14858,9 @@
       <c r="E9" t="n">
         <v>75</v>
       </c>
+      <c r="F9" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14697,6 +14881,9 @@
       </c>
       <c r="E10" t="n">
         <v>-53</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-39</v>
       </c>
     </row>
   </sheetData>
@@ -14710,7 +14897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DT10"/>
+  <dimension ref="A1:DU10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14837,6 +15024,7 @@
     <col width="12" customWidth="1" min="122" max="122"/>
     <col width="12" customWidth="1" min="123" max="123"/>
     <col width="12" customWidth="1" min="124" max="124"/>
+    <col width="12" customWidth="1" min="125" max="125"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15216,6 +15404,9 @@
       <c r="DT1" s="1" t="n">
         <v>20260224</v>
       </c>
+      <c r="DU1" s="1" t="n">
+        <v>20260225</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15591,6 +15782,9 @@
       <c r="DT2" t="n">
         <v>266.18</v>
       </c>
+      <c r="DU2" t="n">
+        <v>272.14</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15966,6 +16160,9 @@
       <c r="DT3" t="n">
         <v>205.27</v>
       </c>
+      <c r="DU3" t="n">
+        <v>208.56</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16344,6 +16541,9 @@
       <c r="DT4" t="n">
         <v>311.49</v>
       </c>
+      <c r="DU4" t="n">
+        <v>310.9</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16722,6 +16922,9 @@
       <c r="DT5" t="n">
         <v>384.47</v>
       </c>
+      <c r="DU5" t="n">
+        <v>389</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17097,6 +17300,9 @@
       <c r="DT6" t="n">
         <v>76.02</v>
       </c>
+      <c r="DU6" t="n">
+        <v>78.04000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17475,6 +17681,9 @@
       <c r="DT7" t="n">
         <v>191.55</v>
       </c>
+      <c r="DU7" t="n">
+        <v>192.85</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17853,6 +18062,9 @@
       <c r="DT8" t="n">
         <v>130.6</v>
       </c>
+      <c r="DU8" t="n">
+        <v>128.84</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18228,6 +18440,9 @@
       <c r="DT9" t="n">
         <v>94.78</v>
       </c>
+      <c r="DU9" t="n">
+        <v>96.51000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18605,6 +18820,9 @@
       </c>
       <c r="DT10" t="n">
         <v>399.83</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>409.38</v>
       </c>
     </row>
   </sheetData>
@@ -18618,7 +18836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DT10"/>
+  <dimension ref="A1:DU10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18745,6 +18963,7 @@
     <col width="12" customWidth="1" min="122" max="122"/>
     <col width="12" customWidth="1" min="123" max="123"/>
     <col width="12" customWidth="1" min="124" max="124"/>
+    <col width="12" customWidth="1" min="125" max="125"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19124,6 +19343,9 @@
       <c r="DT1" s="1" t="n">
         <v>20260224</v>
       </c>
+      <c r="DU1" s="1" t="n">
+        <v>20260225</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19499,6 +19721,9 @@
       <c r="DT2" t="n">
         <v>266.18</v>
       </c>
+      <c r="DU2" t="n">
+        <v>272.14</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19874,6 +20099,9 @@
       <c r="DT3" t="n">
         <v>205.27</v>
       </c>
+      <c r="DU3" t="n">
+        <v>208.56</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20252,6 +20480,9 @@
       <c r="DT4" t="n">
         <v>311.49</v>
       </c>
+      <c r="DU4" t="n">
+        <v>310.9</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20630,6 +20861,9 @@
       <c r="DT5" t="n">
         <v>384.47</v>
       </c>
+      <c r="DU5" t="n">
+        <v>389</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21005,6 +21239,9 @@
       <c r="DT6" t="n">
         <v>76.02</v>
       </c>
+      <c r="DU6" t="n">
+        <v>78.04000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21383,6 +21620,9 @@
       <c r="DT7" t="n">
         <v>191.55</v>
       </c>
+      <c r="DU7" t="n">
+        <v>192.85</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21761,6 +22001,9 @@
       <c r="DT8" t="n">
         <v>130.6</v>
       </c>
+      <c r="DU8" t="n">
+        <v>128.84</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22136,6 +22379,9 @@
       <c r="DT9" t="n">
         <v>94.78</v>
       </c>
+      <c r="DU9" t="n">
+        <v>96.51000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22513,6 +22759,9 @@
       </c>
       <c r="DT10" t="n">
         <v>399.83</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>409.38</v>
       </c>
     </row>
   </sheetData>
@@ -22526,7 +22775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DT10"/>
+  <dimension ref="A1:DU10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22653,6 +22902,7 @@
     <col width="12" customWidth="1" min="122" max="122"/>
     <col width="12" customWidth="1" min="123" max="123"/>
     <col width="12" customWidth="1" min="124" max="124"/>
+    <col width="12" customWidth="1" min="125" max="125"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23032,6 +23282,9 @@
       <c r="DT1" s="1" t="n">
         <v>20260224</v>
       </c>
+      <c r="DU1" s="1" t="n">
+        <v>20260225</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23407,6 +23660,9 @@
       <c r="DT2" t="n">
         <v>266.18</v>
       </c>
+      <c r="DU2" t="n">
+        <v>272.14</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23782,6 +24038,9 @@
       <c r="DT3" t="n">
         <v>205.27</v>
       </c>
+      <c r="DU3" t="n">
+        <v>208.56</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -24160,6 +24419,9 @@
       <c r="DT4" t="n">
         <v>311.49</v>
       </c>
+      <c r="DU4" t="n">
+        <v>310.9</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24538,6 +24800,9 @@
       <c r="DT5" t="n">
         <v>384.47</v>
       </c>
+      <c r="DU5" t="n">
+        <v>389</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24913,6 +25178,9 @@
       <c r="DT6" t="n">
         <v>76.02</v>
       </c>
+      <c r="DU6" t="n">
+        <v>78.04000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -25291,6 +25559,9 @@
       <c r="DT7" t="n">
         <v>191.55</v>
       </c>
+      <c r="DU7" t="n">
+        <v>192.85</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25669,6 +25940,9 @@
       <c r="DT8" t="n">
         <v>130.6</v>
       </c>
+      <c r="DU8" t="n">
+        <v>128.84</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -26044,6 +26318,9 @@
       <c r="DT9" t="n">
         <v>94.78</v>
       </c>
+      <c r="DU9" t="n">
+        <v>96.51000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26421,6 +26698,9 @@
       </c>
       <c r="DT10" t="n">
         <v>399.83</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>409.38</v>
       </c>
     </row>
   </sheetData>
@@ -26434,7 +26714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DT10"/>
+  <dimension ref="A1:DU10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -26561,6 +26841,7 @@
     <col width="12" customWidth="1" min="122" max="122"/>
     <col width="12" customWidth="1" min="123" max="123"/>
     <col width="12" customWidth="1" min="124" max="124"/>
+    <col width="12" customWidth="1" min="125" max="125"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26940,6 +27221,9 @@
       <c r="DT1" s="1" t="n">
         <v>20260224</v>
       </c>
+      <c r="DU1" s="1" t="n">
+        <v>20260225</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -27315,6 +27599,9 @@
       <c r="DT2" t="n">
         <v>266.18</v>
       </c>
+      <c r="DU2" t="n">
+        <v>272.14</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -27690,6 +27977,9 @@
       <c r="DT3" t="n">
         <v>205.27</v>
       </c>
+      <c r="DU3" t="n">
+        <v>208.56</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -28068,6 +28358,9 @@
       <c r="DT4" t="n">
         <v>311.49</v>
       </c>
+      <c r="DU4" t="n">
+        <v>310.9</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -28446,6 +28739,9 @@
       <c r="DT5" t="n">
         <v>384.47</v>
       </c>
+      <c r="DU5" t="n">
+        <v>389</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -28821,6 +29117,9 @@
       <c r="DT6" t="n">
         <v>76.02</v>
       </c>
+      <c r="DU6" t="n">
+        <v>78.04000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -29199,6 +29498,9 @@
       <c r="DT7" t="n">
         <v>191.55</v>
       </c>
+      <c r="DU7" t="n">
+        <v>192.85</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -29577,6 +29879,9 @@
       <c r="DT8" t="n">
         <v>130.6</v>
       </c>
+      <c r="DU8" t="n">
+        <v>128.84</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -29952,6 +30257,9 @@
       <c r="DT9" t="n">
         <v>94.78</v>
       </c>
+      <c r="DU9" t="n">
+        <v>96.51000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -30329,6 +30637,9 @@
       </c>
       <c r="DT10" t="n">
         <v>399.83</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>409.38</v>
       </c>
     </row>
   </sheetData>
@@ -30342,7 +30653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DT10"/>
+  <dimension ref="A1:DU10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -30469,6 +30780,7 @@
     <col width="12" customWidth="1" min="122" max="122"/>
     <col width="12" customWidth="1" min="123" max="123"/>
     <col width="12" customWidth="1" min="124" max="124"/>
+    <col width="12" customWidth="1" min="125" max="125"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30848,6 +31160,9 @@
       <c r="DT1" s="1" t="n">
         <v>20260224</v>
       </c>
+      <c r="DU1" s="1" t="n">
+        <v>20260225</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -31223,6 +31538,9 @@
       <c r="DT2" t="n">
         <v>0</v>
       </c>
+      <c r="DU2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -31598,6 +31916,9 @@
       <c r="DT3" t="n">
         <v>0</v>
       </c>
+      <c r="DU3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -31976,6 +32297,9 @@
       <c r="DT4" t="n">
         <v>0</v>
       </c>
+      <c r="DU4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -32354,6 +32678,9 @@
       <c r="DT5" t="n">
         <v>0</v>
       </c>
+      <c r="DU5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -32729,6 +33056,9 @@
       <c r="DT6" t="n">
         <v>0</v>
       </c>
+      <c r="DU6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -33107,6 +33437,9 @@
       <c r="DT7" t="n">
         <v>0</v>
       </c>
+      <c r="DU7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -33485,6 +33818,9 @@
       <c r="DT8" t="n">
         <v>0</v>
       </c>
+      <c r="DU8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -33860,6 +34196,9 @@
       <c r="DT9" t="n">
         <v>0</v>
       </c>
+      <c r="DU9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -34236,6 +34575,9 @@
         <v>0</v>
       </c>
       <c r="DT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -34250,7 +34592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DA10"/>
+  <dimension ref="A1:DB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -34358,6 +34700,7 @@
     <col width="10" customWidth="1" min="103" max="103"/>
     <col width="10" customWidth="1" min="104" max="104"/>
     <col width="10" customWidth="1" min="105" max="105"/>
+    <col width="10" customWidth="1" min="106" max="106"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -34680,6 +35023,9 @@
       <c r="DA1" s="1" t="n">
         <v>20260224</v>
       </c>
+      <c r="DB1" s="1" t="n">
+        <v>20260225</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -35001,6 +35347,9 @@
       <c r="DA2" t="n">
         <v>47</v>
       </c>
+      <c r="DB2" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -35322,6 +35671,9 @@
       <c r="DA3" t="n">
         <v>14</v>
       </c>
+      <c r="DB3" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -35643,6 +35995,9 @@
       <c r="DA4" t="n">
         <v>25</v>
       </c>
+      <c r="DB4" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -35964,6 +36319,9 @@
       <c r="DA5" t="n">
         <v>0</v>
       </c>
+      <c r="DB5" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -36285,6 +36643,9 @@
       <c r="DA6" t="n">
         <v>2</v>
       </c>
+      <c r="DB6" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -36606,6 +36967,9 @@
       <c r="DA7" t="n">
         <v>95</v>
       </c>
+      <c r="DB7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -36927,6 +37291,9 @@
       <c r="DA8" t="n">
         <v>4</v>
       </c>
+      <c r="DB8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -37248,6 +37615,9 @@
       <c r="DA9" t="n">
         <v>38</v>
       </c>
+      <c r="DB9" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -37568,6 +37938,9 @@
       </c>
       <c r="DA10" t="n">
         <v>8</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -37581,7 +37954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM10"/>
+  <dimension ref="A1:BN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -37649,6 +38022,7 @@
     <col width="10" customWidth="1" min="63" max="63"/>
     <col width="10" customWidth="1" min="64" max="64"/>
     <col width="10" customWidth="1" min="65" max="65"/>
+    <col width="10" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37851,6 +38225,9 @@
       <c r="BM1" s="1" t="n">
         <v>20260224</v>
       </c>
+      <c r="BN1" s="1" t="n">
+        <v>20260225</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -38052,6 +38429,9 @@
       <c r="BM2" t="n">
         <v>49</v>
       </c>
+      <c r="BN2" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -38253,6 +38633,9 @@
       <c r="BM3" t="n">
         <v>13</v>
       </c>
+      <c r="BN3" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -38454,6 +38837,9 @@
       <c r="BM4" t="n">
         <v>34</v>
       </c>
+      <c r="BN4" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -38655,6 +39041,9 @@
       <c r="BM5" t="n">
         <v>0</v>
       </c>
+      <c r="BN5" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -38856,6 +39245,9 @@
       <c r="BM6" t="n">
         <v>0</v>
       </c>
+      <c r="BN6" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -39057,6 +39449,9 @@
       <c r="BM7" t="n">
         <v>96</v>
       </c>
+      <c r="BN7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -39258,6 +39653,9 @@
       <c r="BM8" t="n">
         <v>2</v>
       </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -39459,6 +39857,9 @@
       <c r="BM9" t="n">
         <v>73</v>
       </c>
+      <c r="BN9" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -39659,6 +40060,9 @@
       </c>
       <c r="BM10" t="n">
         <v>3</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -39672,7 +40076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DA10"/>
+  <dimension ref="A1:DB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -39780,6 +40184,7 @@
     <col width="10" customWidth="1" min="103" max="103"/>
     <col width="10" customWidth="1" min="104" max="104"/>
     <col width="10" customWidth="1" min="105" max="105"/>
+    <col width="10" customWidth="1" min="106" max="106"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -40102,6 +40507,9 @@
       <c r="DA1" s="1" t="n">
         <v>20260224</v>
       </c>
+      <c r="DB1" s="1" t="n">
+        <v>20260225</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -40423,6 +40831,9 @@
       <c r="DA2" t="n">
         <v>0</v>
       </c>
+      <c r="DB2" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -40744,6 +41155,9 @@
       <c r="DA3" t="n">
         <v>-46</v>
       </c>
+      <c r="DB3" t="n">
+        <v>-32</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -41065,6 +41479,9 @@
       <c r="DA4" t="n">
         <v>-40</v>
       </c>
+      <c r="DB4" t="n">
+        <v>-38</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -41386,6 +41803,9 @@
       <c r="DA5" t="n">
         <v>-59</v>
       </c>
+      <c r="DB5" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -41707,6 +42127,9 @@
       <c r="DA6" t="n">
         <v>-77</v>
       </c>
+      <c r="DB6" t="n">
+        <v>-40</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -42028,6 +42451,9 @@
       <c r="DA7" t="n">
         <v>44</v>
       </c>
+      <c r="DB7" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -42349,6 +42775,9 @@
       <c r="DA8" t="n">
         <v>-50</v>
       </c>
+      <c r="DB8" t="n">
+        <v>-58</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -42670,6 +43099,9 @@
       <c r="DA9" t="n">
         <v>-25</v>
       </c>
+      <c r="DB9" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -42990,6 +43422,9 @@
       </c>
       <c r="DA10" t="n">
         <v>-81</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>-31</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -19,6 +19,7 @@
     <sheet name="z30" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="s120" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="z120" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="gap60" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -14891,6 +14892,2208 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BN10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="12" customWidth="1" min="36" max="36"/>
+    <col width="12" customWidth="1" min="37" max="37"/>
+    <col width="12" customWidth="1" min="38" max="38"/>
+    <col width="12" customWidth="1" min="39" max="39"/>
+    <col width="12" customWidth="1" min="40" max="40"/>
+    <col width="12" customWidth="1" min="41" max="41"/>
+    <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="12" customWidth="1" min="43" max="43"/>
+    <col width="12" customWidth="1" min="44" max="44"/>
+    <col width="12" customWidth="1" min="45" max="45"/>
+    <col width="12" customWidth="1" min="46" max="46"/>
+    <col width="12" customWidth="1" min="47" max="47"/>
+    <col width="12" customWidth="1" min="48" max="48"/>
+    <col width="12" customWidth="1" min="49" max="49"/>
+    <col width="12" customWidth="1" min="50" max="50"/>
+    <col width="12" customWidth="1" min="51" max="51"/>
+    <col width="12" customWidth="1" min="52" max="52"/>
+    <col width="12" customWidth="1" min="53" max="53"/>
+    <col width="12" customWidth="1" min="54" max="54"/>
+    <col width="12" customWidth="1" min="55" max="55"/>
+    <col width="12" customWidth="1" min="56" max="56"/>
+    <col width="12" customWidth="1" min="57" max="57"/>
+    <col width="12" customWidth="1" min="58" max="58"/>
+    <col width="12" customWidth="1" min="59" max="59"/>
+    <col width="12" customWidth="1" min="60" max="60"/>
+    <col width="12" customWidth="1" min="61" max="61"/>
+    <col width="12" customWidth="1" min="62" max="62"/>
+    <col width="12" customWidth="1" min="63" max="63"/>
+    <col width="12" customWidth="1" min="64" max="64"/>
+    <col width="12" customWidth="1" min="65" max="65"/>
+    <col width="12" customWidth="1" min="66" max="66"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>종목코드</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>20251121</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>20251124</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>20251125</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>20251126</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>20251128</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>20251201</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>20251202</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>20251203</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>20251204</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>20251205</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>20251208</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>20251209</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>20251210</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>20251211</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>20251212</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>20251215</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>20251216</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>20251217</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>20251218</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>20251219</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>20251222</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>20251223</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>20251224</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>20251226</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>20251229</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>20251230</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>20251231</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>20260102</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>20260105</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>20260106</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>20260107</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>20260108</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>20260109</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>20260112</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>20260113</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>20260114</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>20260115</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>20260116</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>20260120</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>20260121</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>20260122</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>20260123</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>20260126</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>20260127</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>20260128</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>20260129</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>20260130</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>20260202</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>20260203</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>20260204</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>20260205</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>20260206</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>20260209</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>20260210</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>20260211</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>20260212</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>20260213</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>20260217</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>20260218</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>20260219</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>20260220</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>20260223</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>20260225</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>애플</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>106</v>
+      </c>
+      <c r="D2" t="n">
+        <v>108</v>
+      </c>
+      <c r="E2" t="n">
+        <v>108</v>
+      </c>
+      <c r="F2" t="n">
+        <v>108</v>
+      </c>
+      <c r="G2" t="n">
+        <v>108</v>
+      </c>
+      <c r="H2" t="n">
+        <v>109</v>
+      </c>
+      <c r="I2" t="n">
+        <v>110</v>
+      </c>
+      <c r="J2" t="n">
+        <v>109</v>
+      </c>
+      <c r="K2" t="n">
+        <v>107</v>
+      </c>
+      <c r="L2" t="n">
+        <v>106</v>
+      </c>
+      <c r="M2" t="n">
+        <v>106</v>
+      </c>
+      <c r="N2" t="n">
+        <v>105</v>
+      </c>
+      <c r="O2" t="n">
+        <v>105</v>
+      </c>
+      <c r="P2" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>105</v>
+      </c>
+      <c r="R2" t="n">
+        <v>103</v>
+      </c>
+      <c r="S2" t="n">
+        <v>103</v>
+      </c>
+      <c r="T2" t="n">
+        <v>102</v>
+      </c>
+      <c r="U2" t="n">
+        <v>102</v>
+      </c>
+      <c r="V2" t="n">
+        <v>102</v>
+      </c>
+      <c r="W2" t="n">
+        <v>101</v>
+      </c>
+      <c r="X2" t="n">
+        <v>102</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>102</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>102</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>102</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>102</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>101</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>101</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>97</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>96</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>96</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>96</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>96</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>96</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>96</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>94</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>91</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>92</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>92</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>92</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>95</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>96</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>95</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>96</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>97</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>97</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>103</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>103</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>103</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>103</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>102</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>102</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>102</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>97</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>95</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>98</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>아마존닷컴</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>97</v>
+      </c>
+      <c r="D3" t="n">
+        <v>99</v>
+      </c>
+      <c r="E3" t="n">
+        <v>101</v>
+      </c>
+      <c r="F3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G3" t="n">
+        <v>102</v>
+      </c>
+      <c r="H3" t="n">
+        <v>102</v>
+      </c>
+      <c r="I3" t="n">
+        <v>103</v>
+      </c>
+      <c r="J3" t="n">
+        <v>102</v>
+      </c>
+      <c r="K3" t="n">
+        <v>100</v>
+      </c>
+      <c r="L3" t="n">
+        <v>101</v>
+      </c>
+      <c r="M3" t="n">
+        <v>99</v>
+      </c>
+      <c r="N3" t="n">
+        <v>100</v>
+      </c>
+      <c r="O3" t="n">
+        <v>102</v>
+      </c>
+      <c r="P3" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>99</v>
+      </c>
+      <c r="R3" t="n">
+        <v>98</v>
+      </c>
+      <c r="S3" t="n">
+        <v>98</v>
+      </c>
+      <c r="T3" t="n">
+        <v>97</v>
+      </c>
+      <c r="U3" t="n">
+        <v>100</v>
+      </c>
+      <c r="V3" t="n">
+        <v>100</v>
+      </c>
+      <c r="W3" t="n">
+        <v>100</v>
+      </c>
+      <c r="X3" t="n">
+        <v>102</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>102</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>102</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>101</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>101</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>101</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>99</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>99</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>105</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>105</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>107</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>107</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>106</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>105</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>102</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>102</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>103</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>99</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>99</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>102</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>102</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>104</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>104</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>103</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>102</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>102</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>102</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>100</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>100</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>96</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>90</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>90</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>89</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>88</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>87</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>86</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>88</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>알파벳 A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>116</v>
+      </c>
+      <c r="D4" t="n">
+        <v>123</v>
+      </c>
+      <c r="E4" t="n">
+        <v>124</v>
+      </c>
+      <c r="F4" t="n">
+        <v>122</v>
+      </c>
+      <c r="G4" t="n">
+        <v>121</v>
+      </c>
+      <c r="H4" t="n">
+        <v>119</v>
+      </c>
+      <c r="I4" t="n">
+        <v>118</v>
+      </c>
+      <c r="J4" t="n">
+        <v>119</v>
+      </c>
+      <c r="K4" t="n">
+        <v>118</v>
+      </c>
+      <c r="L4" t="n">
+        <v>119</v>
+      </c>
+      <c r="M4" t="n">
+        <v>115</v>
+      </c>
+      <c r="N4" t="n">
+        <v>116</v>
+      </c>
+      <c r="O4" t="n">
+        <v>117</v>
+      </c>
+      <c r="P4" t="n">
+        <v>114</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>112</v>
+      </c>
+      <c r="R4" t="n">
+        <v>111</v>
+      </c>
+      <c r="S4" t="n">
+        <v>110</v>
+      </c>
+      <c r="T4" t="n">
+        <v>107</v>
+      </c>
+      <c r="U4" t="n">
+        <v>108</v>
+      </c>
+      <c r="V4" t="n">
+        <v>110</v>
+      </c>
+      <c r="W4" t="n">
+        <v>110</v>
+      </c>
+      <c r="X4" t="n">
+        <v>111</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>111</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>109</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>109</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>109</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>109</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>108</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>111</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>112</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>112</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>112</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>109</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>106</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>108</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>108</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>107</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>108</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>108</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>108</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>109</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>108</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>108</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>108</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>106</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>105</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>105</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>102</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>102</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>100</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>97</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>97</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>96</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>94</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>95</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>95</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>98</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>97</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>마이크로소프트</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>92</v>
+      </c>
+      <c r="D5" t="n">
+        <v>93</v>
+      </c>
+      <c r="E5" t="n">
+        <v>93</v>
+      </c>
+      <c r="F5" t="n">
+        <v>95</v>
+      </c>
+      <c r="G5" t="n">
+        <v>97</v>
+      </c>
+      <c r="H5" t="n">
+        <v>96</v>
+      </c>
+      <c r="I5" t="n">
+        <v>96</v>
+      </c>
+      <c r="J5" t="n">
+        <v>94</v>
+      </c>
+      <c r="K5" t="n">
+        <v>95</v>
+      </c>
+      <c r="L5" t="n">
+        <v>95</v>
+      </c>
+      <c r="M5" t="n">
+        <v>97</v>
+      </c>
+      <c r="N5" t="n">
+        <v>97</v>
+      </c>
+      <c r="O5" t="n">
+        <v>94</v>
+      </c>
+      <c r="P5" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>95</v>
+      </c>
+      <c r="R5" t="n">
+        <v>94</v>
+      </c>
+      <c r="S5" t="n">
+        <v>94</v>
+      </c>
+      <c r="T5" t="n">
+        <v>94</v>
+      </c>
+      <c r="U5" t="n">
+        <v>96</v>
+      </c>
+      <c r="V5" t="n">
+        <v>97</v>
+      </c>
+      <c r="W5" t="n">
+        <v>96</v>
+      </c>
+      <c r="X5" t="n">
+        <v>97</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>97</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>97</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>97</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>97</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>97</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>95</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>96</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>97</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>96</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>97</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>96</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>95</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>93</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>93</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>94</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>93</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>91</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>92</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>96</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>97</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>99</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>89</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>86</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>87</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>87</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>83</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>85</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>88</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>88</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>87</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>86</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>87</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>86</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>87</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>87</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>87</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>84</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>넷플릭스</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H6" t="n">
+        <v>11</v>
+      </c>
+      <c r="I6" t="n">
+        <v>11</v>
+      </c>
+      <c r="J6" t="n">
+        <v>11</v>
+      </c>
+      <c r="K6" t="n">
+        <v>11</v>
+      </c>
+      <c r="L6" t="n">
+        <v>11</v>
+      </c>
+      <c r="M6" t="n">
+        <v>11</v>
+      </c>
+      <c r="N6" t="n">
+        <v>11</v>
+      </c>
+      <c r="O6" t="n">
+        <v>11</v>
+      </c>
+      <c r="P6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>11</v>
+      </c>
+      <c r="R6" t="n">
+        <v>12</v>
+      </c>
+      <c r="S6" t="n">
+        <v>12</v>
+      </c>
+      <c r="T6" t="n">
+        <v>12</v>
+      </c>
+      <c r="U6" t="n">
+        <v>12</v>
+      </c>
+      <c r="V6" t="n">
+        <v>13</v>
+      </c>
+      <c r="W6" t="n">
+        <v>13</v>
+      </c>
+      <c r="X6" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>31</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>37</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>40</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>49</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>56</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>64</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>75</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>86</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>82</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>84</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>84</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>엔비디아</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>97</v>
+      </c>
+      <c r="D7" t="n">
+        <v>99</v>
+      </c>
+      <c r="E7" t="n">
+        <v>96</v>
+      </c>
+      <c r="F7" t="n">
+        <v>98</v>
+      </c>
+      <c r="G7" t="n">
+        <v>96</v>
+      </c>
+      <c r="H7" t="n">
+        <v>97</v>
+      </c>
+      <c r="I7" t="n">
+        <v>98</v>
+      </c>
+      <c r="J7" t="n">
+        <v>97</v>
+      </c>
+      <c r="K7" t="n">
+        <v>99</v>
+      </c>
+      <c r="L7" t="n">
+        <v>98</v>
+      </c>
+      <c r="M7" t="n">
+        <v>100</v>
+      </c>
+      <c r="N7" t="n">
+        <v>100</v>
+      </c>
+      <c r="O7" t="n">
+        <v>99</v>
+      </c>
+      <c r="P7" t="n">
+        <v>97</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>94</v>
+      </c>
+      <c r="R7" t="n">
+        <v>95</v>
+      </c>
+      <c r="S7" t="n">
+        <v>96</v>
+      </c>
+      <c r="T7" t="n">
+        <v>92</v>
+      </c>
+      <c r="U7" t="n">
+        <v>94</v>
+      </c>
+      <c r="V7" t="n">
+        <v>97</v>
+      </c>
+      <c r="W7" t="n">
+        <v>99</v>
+      </c>
+      <c r="X7" t="n">
+        <v>102</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>101</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>102</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>101</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>101</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>101</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>103</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>101</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>102</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>99</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>99</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>99</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>98</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>98</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>99</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>101</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>101</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>103</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>104</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>103</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>103</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>98</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>94</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>94</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>93</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>101</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>103</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>103</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>103</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>102</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>99</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>101</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>102</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>102</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>103</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>104</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>팔란티어 테크</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>88</v>
+      </c>
+      <c r="D8" t="n">
+        <v>92</v>
+      </c>
+      <c r="E8" t="n">
+        <v>92</v>
+      </c>
+      <c r="F8" t="n">
+        <v>93</v>
+      </c>
+      <c r="G8" t="n">
+        <v>95</v>
+      </c>
+      <c r="H8" t="n">
+        <v>94</v>
+      </c>
+      <c r="I8" t="n">
+        <v>96</v>
+      </c>
+      <c r="J8" t="n">
+        <v>99</v>
+      </c>
+      <c r="K8" t="n">
+        <v>100</v>
+      </c>
+      <c r="L8" t="n">
+        <v>102</v>
+      </c>
+      <c r="M8" t="n">
+        <v>101</v>
+      </c>
+      <c r="N8" t="n">
+        <v>102</v>
+      </c>
+      <c r="O8" t="n">
+        <v>105</v>
+      </c>
+      <c r="P8" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>102</v>
+      </c>
+      <c r="R8" t="n">
+        <v>102</v>
+      </c>
+      <c r="S8" t="n">
+        <v>104</v>
+      </c>
+      <c r="T8" t="n">
+        <v>99</v>
+      </c>
+      <c r="U8" t="n">
+        <v>103</v>
+      </c>
+      <c r="V8" t="n">
+        <v>107</v>
+      </c>
+      <c r="W8" t="n">
+        <v>107</v>
+      </c>
+      <c r="X8" t="n">
+        <v>107</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>107</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>104</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>102</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>98</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>93</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>96</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>101</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>98</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>98</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>99</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>99</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>99</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>98</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>94</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>92</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>92</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>95</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>94</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>93</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>88</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>86</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>83</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>84</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>90</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>80</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>80</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>75</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>79</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>84</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>82</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>80</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>76</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>78</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>79</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>81</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>81</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>81</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>79</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>스타벅스</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SBUX</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>102</v>
+      </c>
+      <c r="D9" t="n">
+        <v>99</v>
+      </c>
+      <c r="E9" t="n">
+        <v>102</v>
+      </c>
+      <c r="F9" t="n">
+        <v>103</v>
+      </c>
+      <c r="G9" t="n">
+        <v>104</v>
+      </c>
+      <c r="H9" t="n">
+        <v>101</v>
+      </c>
+      <c r="I9" t="n">
+        <v>102</v>
+      </c>
+      <c r="J9" t="n">
+        <v>104</v>
+      </c>
+      <c r="K9" t="n">
+        <v>101</v>
+      </c>
+      <c r="L9" t="n">
+        <v>101</v>
+      </c>
+      <c r="M9" t="n">
+        <v>99</v>
+      </c>
+      <c r="N9" t="n">
+        <v>98</v>
+      </c>
+      <c r="O9" t="n">
+        <v>100</v>
+      </c>
+      <c r="P9" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>101</v>
+      </c>
+      <c r="R9" t="n">
+        <v>101</v>
+      </c>
+      <c r="S9" t="n">
+        <v>101</v>
+      </c>
+      <c r="T9" t="n">
+        <v>101</v>
+      </c>
+      <c r="U9" t="n">
+        <v>106</v>
+      </c>
+      <c r="V9" t="n">
+        <v>105</v>
+      </c>
+      <c r="W9" t="n">
+        <v>102</v>
+      </c>
+      <c r="X9" t="n">
+        <v>99</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>101</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>102</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>101</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>106</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>102</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>104</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>105</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>106</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>106</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>107</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>109</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>109</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>109</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>112</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>111</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>113</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>111</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>111</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>108</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>105</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>105</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>106</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>110</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>110</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>109</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>112</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>112</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>110</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>111</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>108</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>105</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>106</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>테슬라</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>93</v>
+      </c>
+      <c r="D10" t="n">
+        <v>99</v>
+      </c>
+      <c r="E10" t="n">
+        <v>99</v>
+      </c>
+      <c r="F10" t="n">
+        <v>101</v>
+      </c>
+      <c r="G10" t="n">
+        <v>101</v>
+      </c>
+      <c r="H10" t="n">
+        <v>101</v>
+      </c>
+      <c r="I10" t="n">
+        <v>100</v>
+      </c>
+      <c r="J10" t="n">
+        <v>104</v>
+      </c>
+      <c r="K10" t="n">
+        <v>105</v>
+      </c>
+      <c r="L10" t="n">
+        <v>105</v>
+      </c>
+      <c r="M10" t="n">
+        <v>101</v>
+      </c>
+      <c r="N10" t="n">
+        <v>102</v>
+      </c>
+      <c r="O10" t="n">
+        <v>104</v>
+      </c>
+      <c r="P10" t="n">
+        <v>103</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>105</v>
+      </c>
+      <c r="R10" t="n">
+        <v>109</v>
+      </c>
+      <c r="S10" t="n">
+        <v>112</v>
+      </c>
+      <c r="T10" t="n">
+        <v>107</v>
+      </c>
+      <c r="U10" t="n">
+        <v>110</v>
+      </c>
+      <c r="V10" t="n">
+        <v>109</v>
+      </c>
+      <c r="W10" t="n">
+        <v>111</v>
+      </c>
+      <c r="X10" t="n">
+        <v>110</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>110</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>107</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>104</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>103</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>101</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>99</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>98</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>97</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>98</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>101</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>101</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>99</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>99</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>98</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>94</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>97</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>101</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>101</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>98</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>97</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>97</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>94</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>98</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>98</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>96</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>92</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>92</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>91</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>94</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>95</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>97</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>98</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>95</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>95</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>93</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>94</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>94</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>94</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>91</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>93</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -605,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN10"/>
+  <dimension ref="A1:BO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -674,6 +674,7 @@
     <col width="10" customWidth="1" min="64" max="64"/>
     <col width="10" customWidth="1" min="65" max="65"/>
     <col width="10" customWidth="1" min="66" max="66"/>
+    <col width="10" customWidth="1" min="67" max="67"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -879,6 +880,9 @@
       <c r="BN1" s="1" t="n">
         <v>20260225</v>
       </c>
+      <c r="BO1" s="1" t="n">
+        <v>20260226</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1083,6 +1087,9 @@
       <c r="BN2" t="n">
         <v>19</v>
       </c>
+      <c r="BO2" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1287,6 +1294,9 @@
       <c r="BN3" t="n">
         <v>-78</v>
       </c>
+      <c r="BO3" t="n">
+        <v>-68</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1491,6 +1501,9 @@
       <c r="BN4" t="n">
         <v>-40</v>
       </c>
+      <c r="BO4" t="n">
+        <v>-30</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1695,6 +1708,9 @@
       <c r="BN5" t="n">
         <v>-93</v>
       </c>
+      <c r="BO5" t="n">
+        <v>-74</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1899,6 +1915,9 @@
       <c r="BN6" t="n">
         <v>-67</v>
       </c>
+      <c r="BO6" t="n">
+        <v>-39</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2103,6 +2122,9 @@
       <c r="BN7" t="n">
         <v>75</v>
       </c>
+      <c r="BO7" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2307,6 +2329,9 @@
       <c r="BN8" t="n">
         <v>-89</v>
       </c>
+      <c r="BO8" t="n">
+        <v>-73</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2511,6 +2536,9 @@
       <c r="BN9" t="n">
         <v>58</v>
       </c>
+      <c r="BO9" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2714,6 +2742,9 @@
       </c>
       <c r="BN10" t="n">
         <v>-63</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>-45</v>
       </c>
     </row>
   </sheetData>
@@ -2727,7 +2758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DB10"/>
+  <dimension ref="A1:DC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2836,6 +2867,7 @@
     <col width="12" customWidth="1" min="104" max="104"/>
     <col width="12" customWidth="1" min="105" max="105"/>
     <col width="12" customWidth="1" min="106" max="106"/>
+    <col width="12" customWidth="1" min="107" max="107"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3369,6 +3401,11 @@
           <t>20260225</t>
         </is>
       </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>20260226</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4317,6 +4354,9 @@
       <c r="DB4" t="n">
         <v>97</v>
       </c>
+      <c r="DC4" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4641,6 +4681,9 @@
       <c r="DB5" t="n">
         <v>95</v>
       </c>
+      <c r="DC5" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5277,6 +5320,9 @@
       <c r="DB7" t="n">
         <v>104</v>
       </c>
+      <c r="DC7" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5601,6 +5647,9 @@
       <c r="DB8" t="n">
         <v>93</v>
       </c>
+      <c r="DC8" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6236,6 +6285,9 @@
       </c>
       <c r="DB10" t="n">
         <v>99</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -6249,7 +6301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI10"/>
+  <dimension ref="A1:CJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6339,6 +6391,7 @@
     <col width="12" customWidth="1" min="85" max="85"/>
     <col width="12" customWidth="1" min="86" max="86"/>
     <col width="12" customWidth="1" min="87" max="87"/>
+    <col width="12" customWidth="1" min="88" max="88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6777,6 +6830,11 @@
           <t>20260225</t>
         </is>
       </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>20260226</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7554,6 +7612,9 @@
       <c r="CI4" t="n">
         <v>58.78</v>
       </c>
+      <c r="CJ4" t="n">
+        <v>50.24</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7821,6 +7882,9 @@
       <c r="CI5" t="n">
         <v>-10.73</v>
       </c>
+      <c r="CJ5" t="n">
+        <v>-43.99</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8343,6 +8407,9 @@
       <c r="CI7" t="n">
         <v>20.4</v>
       </c>
+      <c r="CJ7" t="n">
+        <v>20.64</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8610,6 +8677,9 @@
       <c r="CI8" t="n">
         <v>-28.04</v>
       </c>
+      <c r="CJ8" t="n">
+        <v>-36.89</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9131,6 +9201,9 @@
       </c>
       <c r="CI10" t="n">
         <v>-17.66</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>-23.64</v>
       </c>
     </row>
   </sheetData>
@@ -9144,7 +9217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN10"/>
+  <dimension ref="A1:BO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9213,6 +9286,7 @@
     <col width="12" customWidth="1" min="64" max="64"/>
     <col width="12" customWidth="1" min="65" max="65"/>
     <col width="12" customWidth="1" min="66" max="66"/>
+    <col width="12" customWidth="1" min="67" max="67"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9546,6 +9620,11 @@
           <t>20260225</t>
         </is>
       </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>20260226</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10134,6 +10213,9 @@
       <c r="BN4" t="n">
         <v>0</v>
       </c>
+      <c r="BO4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10338,6 +10420,9 @@
       <c r="BN5" t="n">
         <v>0</v>
       </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10734,6 +10819,9 @@
       <c r="BN7" t="n">
         <v>0</v>
       </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10938,6 +11026,9 @@
       <c r="BN8" t="n">
         <v>0</v>
       </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11332,6 +11423,9 @@
         <v>0</v>
       </c>
       <c r="BN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11346,7 +11440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR10"/>
+  <dimension ref="A1:CS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11445,6 +11539,7 @@
     <col width="10" customWidth="1" min="94" max="94"/>
     <col width="10" customWidth="1" min="95" max="95"/>
     <col width="10" customWidth="1" min="96" max="96"/>
+    <col width="10" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11740,6 +11835,9 @@
       <c r="CR1" s="1" t="n">
         <v>20260225</v>
       </c>
+      <c r="CS1" s="1" t="n">
+        <v>20260226</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12034,6 +12132,9 @@
       <c r="CR2" t="n">
         <v>50</v>
       </c>
+      <c r="CS2" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12328,6 +12429,9 @@
       <c r="CR3" t="n">
         <v>-52</v>
       </c>
+      <c r="CS3" t="n">
+        <v>-42</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12622,6 +12726,9 @@
       <c r="CR4" t="n">
         <v>-55</v>
       </c>
+      <c r="CS4" t="n">
+        <v>-44</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12916,6 +13023,9 @@
       <c r="CR5" t="n">
         <v>-63</v>
       </c>
+      <c r="CS5" t="n">
+        <v>-41</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13210,6 +13320,9 @@
       <c r="CR6" t="n">
         <v>-55</v>
       </c>
+      <c r="CS6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13504,6 +13617,9 @@
       <c r="CR7" t="n">
         <v>63</v>
       </c>
+      <c r="CS7" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13798,6 +13914,9 @@
       <c r="CR8" t="n">
         <v>-61</v>
       </c>
+      <c r="CS8" t="n">
+        <v>-43</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14092,6 +14211,9 @@
       <c r="CR9" t="n">
         <v>27</v>
       </c>
+      <c r="CS9" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14385,6 +14507,9 @@
       </c>
       <c r="CR10" t="n">
         <v>-47</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>-17</v>
       </c>
     </row>
   </sheetData>
@@ -14398,7 +14523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14407,6 +14532,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14432,6 +14558,9 @@
       <c r="F1" s="1" t="n">
         <v>20260225</v>
       </c>
+      <c r="G1" s="1" t="n">
+        <v>20260226</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14453,6 +14582,9 @@
       <c r="F2" t="n">
         <v>76</v>
       </c>
+      <c r="G2" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14474,6 +14606,9 @@
       <c r="F3" t="n">
         <v>18</v>
       </c>
+      <c r="G3" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14498,6 +14633,9 @@
       <c r="F4" t="n">
         <v>73</v>
       </c>
+      <c r="G4" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14522,6 +14660,9 @@
       <c r="F5" t="n">
         <v>3</v>
       </c>
+      <c r="G5" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14543,6 +14684,9 @@
       <c r="F6" t="n">
         <v>0</v>
       </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14567,6 +14711,9 @@
       <c r="F7" t="n">
         <v>65</v>
       </c>
+      <c r="G7" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14591,6 +14738,9 @@
       <c r="F8" t="n">
         <v>0</v>
       </c>
+      <c r="G8" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14612,6 +14762,9 @@
       <c r="F9" t="n">
         <v>86</v>
       </c>
+      <c r="G9" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14635,6 +14788,9 @@
       </c>
       <c r="F10" t="n">
         <v>47</v>
+      </c>
+      <c r="G10" t="n">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -14648,7 +14804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14657,6 +14813,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14682,6 +14839,9 @@
       <c r="F1" s="1" t="n">
         <v>20260225</v>
       </c>
+      <c r="G1" s="1" t="n">
+        <v>20260226</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14703,6 +14863,9 @@
       <c r="F2" t="n">
         <v>37</v>
       </c>
+      <c r="G2" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14724,6 +14887,9 @@
       <c r="F3" t="n">
         <v>-86</v>
       </c>
+      <c r="G3" t="n">
+        <v>-76</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14748,6 +14914,9 @@
       <c r="F4" t="n">
         <v>29</v>
       </c>
+      <c r="G4" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14772,6 +14941,9 @@
       <c r="F5" t="n">
         <v>-122</v>
       </c>
+      <c r="G5" t="n">
+        <v>-104</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14793,6 +14965,9 @@
       <c r="F6" t="n">
         <v>-45</v>
       </c>
+      <c r="G6" t="n">
+        <v>-44</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14817,6 +14992,9 @@
       <c r="F7" t="n">
         <v>55</v>
       </c>
+      <c r="G7" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14841,6 +15019,9 @@
       <c r="F8" t="n">
         <v>-120</v>
       </c>
+      <c r="G8" t="n">
+        <v>-103</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14862,6 +15043,9 @@
       <c r="F9" t="n">
         <v>91</v>
       </c>
+      <c r="G9" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14885,6 +15069,9 @@
       </c>
       <c r="F10" t="n">
         <v>-39</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-27</v>
       </c>
     </row>
   </sheetData>
@@ -14898,7 +15085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN10"/>
+  <dimension ref="A1:BO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -14967,6 +15154,7 @@
     <col width="12" customWidth="1" min="64" max="64"/>
     <col width="12" customWidth="1" min="65" max="65"/>
     <col width="12" customWidth="1" min="66" max="66"/>
+    <col width="12" customWidth="1" min="67" max="67"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15300,6 +15488,11 @@
           <t>20260225</t>
         </is>
       </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>20260226</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15888,6 +16081,9 @@
       <c r="BN4" t="n">
         <v>97</v>
       </c>
+      <c r="BO4" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16092,6 +16288,9 @@
       <c r="BN5" t="n">
         <v>85</v>
       </c>
+      <c r="BO5" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16488,6 +16687,9 @@
       <c r="BN7" t="n">
         <v>104</v>
       </c>
+      <c r="BO7" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16692,6 +16894,9 @@
       <c r="BN8" t="n">
         <v>78</v>
       </c>
+      <c r="BO8" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17087,6 +17292,9 @@
       </c>
       <c r="BN10" t="n">
         <v>93</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -17100,7 +17308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DU10"/>
+  <dimension ref="A1:DV10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17228,6 +17436,7 @@
     <col width="12" customWidth="1" min="123" max="123"/>
     <col width="12" customWidth="1" min="124" max="124"/>
     <col width="12" customWidth="1" min="125" max="125"/>
+    <col width="12" customWidth="1" min="126" max="126"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17610,6 +17819,9 @@
       <c r="DU1" s="1" t="n">
         <v>20260225</v>
       </c>
+      <c r="DV1" s="1" t="n">
+        <v>20260226</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17988,6 +18200,9 @@
       <c r="DU2" t="n">
         <v>272.14</v>
       </c>
+      <c r="DV2" t="n">
+        <v>274.23</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18366,6 +18581,9 @@
       <c r="DU3" t="n">
         <v>208.56</v>
       </c>
+      <c r="DV3" t="n">
+        <v>210.64</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18747,6 +18965,9 @@
       <c r="DU4" t="n">
         <v>310.9</v>
       </c>
+      <c r="DV4" t="n">
+        <v>312.9</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19128,6 +19349,9 @@
       <c r="DU5" t="n">
         <v>389</v>
       </c>
+      <c r="DV5" t="n">
+        <v>400.6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19506,6 +19730,9 @@
       <c r="DU6" t="n">
         <v>78.04000000000001</v>
       </c>
+      <c r="DV6" t="n">
+        <v>82.7</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19887,6 +20114,9 @@
       <c r="DU7" t="n">
         <v>192.85</v>
       </c>
+      <c r="DV7" t="n">
+        <v>195.56</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20268,6 +20498,9 @@
       <c r="DU8" t="n">
         <v>128.84</v>
       </c>
+      <c r="DV8" t="n">
+        <v>134.19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20646,6 +20879,9 @@
       <c r="DU9" t="n">
         <v>96.51000000000001</v>
       </c>
+      <c r="DV9" t="n">
+        <v>97.93000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21026,6 +21262,9 @@
       </c>
       <c r="DU10" t="n">
         <v>409.38</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>417.4</v>
       </c>
     </row>
   </sheetData>
@@ -21039,7 +21278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DU10"/>
+  <dimension ref="A1:DV10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21167,6 +21406,7 @@
     <col width="12" customWidth="1" min="123" max="123"/>
     <col width="12" customWidth="1" min="124" max="124"/>
     <col width="12" customWidth="1" min="125" max="125"/>
+    <col width="12" customWidth="1" min="126" max="126"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21549,6 +21789,9 @@
       <c r="DU1" s="1" t="n">
         <v>20260225</v>
       </c>
+      <c r="DV1" s="1" t="n">
+        <v>20260226</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21927,6 +22170,9 @@
       <c r="DU2" t="n">
         <v>272.14</v>
       </c>
+      <c r="DV2" t="n">
+        <v>274.23</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22305,6 +22551,9 @@
       <c r="DU3" t="n">
         <v>208.56</v>
       </c>
+      <c r="DV3" t="n">
+        <v>210.64</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22686,6 +22935,9 @@
       <c r="DU4" t="n">
         <v>310.9</v>
       </c>
+      <c r="DV4" t="n">
+        <v>312.9</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23067,6 +23319,9 @@
       <c r="DU5" t="n">
         <v>389</v>
       </c>
+      <c r="DV5" t="n">
+        <v>400.6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23445,6 +23700,9 @@
       <c r="DU6" t="n">
         <v>78.04000000000001</v>
       </c>
+      <c r="DV6" t="n">
+        <v>82.7</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23826,6 +24084,9 @@
       <c r="DU7" t="n">
         <v>192.85</v>
       </c>
+      <c r="DV7" t="n">
+        <v>195.56</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24207,6 +24468,9 @@
       <c r="DU8" t="n">
         <v>128.84</v>
       </c>
+      <c r="DV8" t="n">
+        <v>134.19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24585,6 +24849,9 @@
       <c r="DU9" t="n">
         <v>96.51000000000001</v>
       </c>
+      <c r="DV9" t="n">
+        <v>97.93000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24965,6 +25232,9 @@
       </c>
       <c r="DU10" t="n">
         <v>409.38</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>417.4</v>
       </c>
     </row>
   </sheetData>
@@ -24978,7 +25248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DU10"/>
+  <dimension ref="A1:DV10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25106,6 +25376,7 @@
     <col width="12" customWidth="1" min="123" max="123"/>
     <col width="12" customWidth="1" min="124" max="124"/>
     <col width="12" customWidth="1" min="125" max="125"/>
+    <col width="12" customWidth="1" min="126" max="126"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25488,6 +25759,9 @@
       <c r="DU1" s="1" t="n">
         <v>20260225</v>
       </c>
+      <c r="DV1" s="1" t="n">
+        <v>20260226</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25866,6 +26140,9 @@
       <c r="DU2" t="n">
         <v>272.14</v>
       </c>
+      <c r="DV2" t="n">
+        <v>274.23</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -26244,6 +26521,9 @@
       <c r="DU3" t="n">
         <v>208.56</v>
       </c>
+      <c r="DV3" t="n">
+        <v>210.64</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -26625,6 +26905,9 @@
       <c r="DU4" t="n">
         <v>310.9</v>
       </c>
+      <c r="DV4" t="n">
+        <v>312.9</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -27006,6 +27289,9 @@
       <c r="DU5" t="n">
         <v>389</v>
       </c>
+      <c r="DV5" t="n">
+        <v>400.6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -27384,6 +27670,9 @@
       <c r="DU6" t="n">
         <v>78.04000000000001</v>
       </c>
+      <c r="DV6" t="n">
+        <v>82.7</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -27765,6 +28054,9 @@
       <c r="DU7" t="n">
         <v>192.85</v>
       </c>
+      <c r="DV7" t="n">
+        <v>195.56</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -28146,6 +28438,9 @@
       <c r="DU8" t="n">
         <v>128.84</v>
       </c>
+      <c r="DV8" t="n">
+        <v>134.19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -28524,6 +28819,9 @@
       <c r="DU9" t="n">
         <v>96.51000000000001</v>
       </c>
+      <c r="DV9" t="n">
+        <v>97.93000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -28904,6 +29202,9 @@
       </c>
       <c r="DU10" t="n">
         <v>409.38</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>417.4</v>
       </c>
     </row>
   </sheetData>
@@ -28917,7 +29218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DU10"/>
+  <dimension ref="A1:DV10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -29045,6 +29346,7 @@
     <col width="12" customWidth="1" min="123" max="123"/>
     <col width="12" customWidth="1" min="124" max="124"/>
     <col width="12" customWidth="1" min="125" max="125"/>
+    <col width="12" customWidth="1" min="126" max="126"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29427,6 +29729,9 @@
       <c r="DU1" s="1" t="n">
         <v>20260225</v>
       </c>
+      <c r="DV1" s="1" t="n">
+        <v>20260226</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -29805,6 +30110,9 @@
       <c r="DU2" t="n">
         <v>272.14</v>
       </c>
+      <c r="DV2" t="n">
+        <v>274.23</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -30183,6 +30491,9 @@
       <c r="DU3" t="n">
         <v>208.56</v>
       </c>
+      <c r="DV3" t="n">
+        <v>210.64</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -30564,6 +30875,9 @@
       <c r="DU4" t="n">
         <v>310.9</v>
       </c>
+      <c r="DV4" t="n">
+        <v>312.9</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -30945,6 +31259,9 @@
       <c r="DU5" t="n">
         <v>389</v>
       </c>
+      <c r="DV5" t="n">
+        <v>400.6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -31323,6 +31640,9 @@
       <c r="DU6" t="n">
         <v>78.04000000000001</v>
       </c>
+      <c r="DV6" t="n">
+        <v>82.7</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -31704,6 +32024,9 @@
       <c r="DU7" t="n">
         <v>192.85</v>
       </c>
+      <c r="DV7" t="n">
+        <v>195.56</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -32085,6 +32408,9 @@
       <c r="DU8" t="n">
         <v>128.84</v>
       </c>
+      <c r="DV8" t="n">
+        <v>134.19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -32463,6 +32789,9 @@
       <c r="DU9" t="n">
         <v>96.51000000000001</v>
       </c>
+      <c r="DV9" t="n">
+        <v>97.93000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -32843,6 +33172,9 @@
       </c>
       <c r="DU10" t="n">
         <v>409.38</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>417.4</v>
       </c>
     </row>
   </sheetData>
@@ -32856,7 +33188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DU10"/>
+  <dimension ref="A1:DV10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -32984,6 +33316,7 @@
     <col width="12" customWidth="1" min="123" max="123"/>
     <col width="12" customWidth="1" min="124" max="124"/>
     <col width="12" customWidth="1" min="125" max="125"/>
+    <col width="12" customWidth="1" min="126" max="126"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33366,6 +33699,9 @@
       <c r="DU1" s="1" t="n">
         <v>20260225</v>
       </c>
+      <c r="DV1" s="1" t="n">
+        <v>20260226</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -33744,6 +34080,9 @@
       <c r="DU2" t="n">
         <v>0</v>
       </c>
+      <c r="DV2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -34122,6 +34461,9 @@
       <c r="DU3" t="n">
         <v>0</v>
       </c>
+      <c r="DV3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -34503,6 +34845,9 @@
       <c r="DU4" t="n">
         <v>0</v>
       </c>
+      <c r="DV4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -34884,6 +35229,9 @@
       <c r="DU5" t="n">
         <v>0</v>
       </c>
+      <c r="DV5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -35262,6 +35610,9 @@
       <c r="DU6" t="n">
         <v>0</v>
       </c>
+      <c r="DV6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -35643,6 +35994,9 @@
       <c r="DU7" t="n">
         <v>0</v>
       </c>
+      <c r="DV7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -36024,6 +36378,9 @@
       <c r="DU8" t="n">
         <v>0</v>
       </c>
+      <c r="DV8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -36402,6 +36759,9 @@
       <c r="DU9" t="n">
         <v>0</v>
       </c>
+      <c r="DV9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -36781,6 +37141,9 @@
         <v>0</v>
       </c>
       <c r="DU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -36795,7 +37158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DB10"/>
+  <dimension ref="A1:DC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -36904,6 +37267,7 @@
     <col width="10" customWidth="1" min="104" max="104"/>
     <col width="10" customWidth="1" min="105" max="105"/>
     <col width="10" customWidth="1" min="106" max="106"/>
+    <col width="10" customWidth="1" min="107" max="107"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37229,6 +37593,9 @@
       <c r="DB1" s="1" t="n">
         <v>20260225</v>
       </c>
+      <c r="DC1" s="1" t="n">
+        <v>20260226</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -37553,6 +37920,9 @@
       <c r="DB2" t="n">
         <v>73</v>
       </c>
+      <c r="DC2" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -37877,6 +38247,9 @@
       <c r="DB3" t="n">
         <v>21</v>
       </c>
+      <c r="DC3" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -38201,6 +38574,9 @@
       <c r="DB4" t="n">
         <v>24</v>
       </c>
+      <c r="DC4" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -38525,6 +38901,9 @@
       <c r="DB5" t="n">
         <v>5</v>
       </c>
+      <c r="DC5" t="n">
+        <v>33</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -38849,6 +39228,9 @@
       <c r="DB6" t="n">
         <v>22</v>
       </c>
+      <c r="DC6" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -39173,6 +39555,9 @@
       <c r="DB7" t="n">
         <v>100</v>
       </c>
+      <c r="DC7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -39497,6 +39882,9 @@
       <c r="DB8" t="n">
         <v>0</v>
       </c>
+      <c r="DC8" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -39821,6 +40209,9 @@
       <c r="DB9" t="n">
         <v>61</v>
       </c>
+      <c r="DC9" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -40144,6 +40535,9 @@
       </c>
       <c r="DB10" t="n">
         <v>36</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -40157,7 +40551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN10"/>
+  <dimension ref="A1:BO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -40226,6 +40620,7 @@
     <col width="10" customWidth="1" min="64" max="64"/>
     <col width="10" customWidth="1" min="65" max="65"/>
     <col width="10" customWidth="1" min="66" max="66"/>
+    <col width="10" customWidth="1" min="67" max="67"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -40431,6 +40826,9 @@
       <c r="BN1" s="1" t="n">
         <v>20260225</v>
       </c>
+      <c r="BO1" s="1" t="n">
+        <v>20260226</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -40635,6 +41033,9 @@
       <c r="BN2" t="n">
         <v>64</v>
       </c>
+      <c r="BO2" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -40839,6 +41240,9 @@
       <c r="BN3" t="n">
         <v>20</v>
       </c>
+      <c r="BO3" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -41043,6 +41447,9 @@
       <c r="BN4" t="n">
         <v>33</v>
       </c>
+      <c r="BO4" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -41247,6 +41654,9 @@
       <c r="BN5" t="n">
         <v>4</v>
       </c>
+      <c r="BO5" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -41451,6 +41861,9 @@
       <c r="BN6" t="n">
         <v>7</v>
       </c>
+      <c r="BO6" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -41655,6 +42068,9 @@
       <c r="BN7" t="n">
         <v>100</v>
       </c>
+      <c r="BO7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -41859,6 +42275,9 @@
       <c r="BN8" t="n">
         <v>0</v>
       </c>
+      <c r="BO8" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -42063,6 +42482,9 @@
       <c r="BN9" t="n">
         <v>83</v>
       </c>
+      <c r="BO9" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -42266,6 +42688,9 @@
       </c>
       <c r="BN10" t="n">
         <v>13</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -42279,7 +42704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DB10"/>
+  <dimension ref="A1:DC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -42388,6 +42813,7 @@
     <col width="10" customWidth="1" min="104" max="104"/>
     <col width="10" customWidth="1" min="105" max="105"/>
     <col width="10" customWidth="1" min="106" max="106"/>
+    <col width="10" customWidth="1" min="107" max="107"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -42713,6 +43139,9 @@
       <c r="DB1" s="1" t="n">
         <v>20260225</v>
       </c>
+      <c r="DC1" s="1" t="n">
+        <v>20260226</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -43037,6 +43466,9 @@
       <c r="DB2" t="n">
         <v>33</v>
       </c>
+      <c r="DC2" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -43361,6 +43793,9 @@
       <c r="DB3" t="n">
         <v>-32</v>
       </c>
+      <c r="DC3" t="n">
+        <v>-23</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -43685,6 +44120,9 @@
       <c r="DB4" t="n">
         <v>-38</v>
       </c>
+      <c r="DC4" t="n">
+        <v>-27</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -44009,6 +44447,9 @@
       <c r="DB5" t="n">
         <v>-50</v>
       </c>
+      <c r="DC5" t="n">
+        <v>-22</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -44333,6 +44774,9 @@
       <c r="DB6" t="n">
         <v>-40</v>
       </c>
+      <c r="DC6" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -44657,6 +45101,9 @@
       <c r="DB7" t="n">
         <v>51</v>
       </c>
+      <c r="DC7" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -44981,6 +45428,9 @@
       <c r="DB8" t="n">
         <v>-58</v>
       </c>
+      <c r="DC8" t="n">
+        <v>-24</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -45305,6 +45755,9 @@
       <c r="DB9" t="n">
         <v>15</v>
       </c>
+      <c r="DC9" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -45628,6 +46081,9 @@
       </c>
       <c r="DB10" t="n">
         <v>-31</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -605,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO10"/>
+  <dimension ref="A1:BP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -675,6 +675,7 @@
     <col width="10" customWidth="1" min="65" max="65"/>
     <col width="10" customWidth="1" min="66" max="66"/>
     <col width="10" customWidth="1" min="67" max="67"/>
+    <col width="10" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -883,6 +884,9 @@
       <c r="BO1" s="1" t="n">
         <v>20260226</v>
       </c>
+      <c r="BP1" s="1" t="n">
+        <v>20260227</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1090,6 +1094,9 @@
       <c r="BO2" t="n">
         <v>30</v>
       </c>
+      <c r="BP2" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1297,6 +1304,9 @@
       <c r="BO3" t="n">
         <v>-68</v>
       </c>
+      <c r="BP3" t="n">
+        <v>-75</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1504,6 +1514,9 @@
       <c r="BO4" t="n">
         <v>-30</v>
       </c>
+      <c r="BP4" t="n">
+        <v>-30</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1711,6 +1724,9 @@
       <c r="BO5" t="n">
         <v>-74</v>
       </c>
+      <c r="BP5" t="n">
+        <v>-70</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1918,6 +1934,9 @@
       <c r="BO6" t="n">
         <v>-39</v>
       </c>
+      <c r="BP6" t="n">
+        <v>-26</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2125,6 +2144,9 @@
       <c r="BO7" t="n">
         <v>95</v>
       </c>
+      <c r="BP7" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2332,6 +2354,9 @@
       <c r="BO8" t="n">
         <v>-73</v>
       </c>
+      <c r="BP8" t="n">
+        <v>-67</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2539,6 +2564,9 @@
       <c r="BO9" t="n">
         <v>69</v>
       </c>
+      <c r="BP9" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2744,6 +2772,9 @@
         <v>-63</v>
       </c>
       <c r="BO10" t="n">
+        <v>-45</v>
+      </c>
+      <c r="BP10" t="n">
         <v>-45</v>
       </c>
     </row>
@@ -2758,7 +2789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DC10"/>
+  <dimension ref="A1:DD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2868,6 +2899,7 @@
     <col width="12" customWidth="1" min="105" max="105"/>
     <col width="12" customWidth="1" min="106" max="106"/>
     <col width="12" customWidth="1" min="107" max="107"/>
+    <col width="12" customWidth="1" min="108" max="108"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3406,6 +3438,11 @@
           <t>20260226</t>
         </is>
       </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>20260227</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4684,6 +4721,9 @@
       <c r="DC5" t="n">
         <v>99</v>
       </c>
+      <c r="DD5" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5323,6 +5363,9 @@
       <c r="DC7" t="n">
         <v>105</v>
       </c>
+      <c r="DD7" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5649,6 +5692,9 @@
       </c>
       <c r="DC8" t="n">
         <v>97</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>99</v>
       </c>
     </row>
     <row r="9">
@@ -6301,7 +6347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ10"/>
+  <dimension ref="A1:CK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6392,6 +6438,7 @@
     <col width="12" customWidth="1" min="86" max="86"/>
     <col width="12" customWidth="1" min="87" max="87"/>
     <col width="12" customWidth="1" min="88" max="88"/>
+    <col width="12" customWidth="1" min="89" max="89"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6835,6 +6882,11 @@
           <t>20260226</t>
         </is>
       </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>20260227</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7885,6 +7937,9 @@
       <c r="CJ5" t="n">
         <v>-43.99</v>
       </c>
+      <c r="CK5" t="n">
+        <v>-50.28</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8410,6 +8465,9 @@
       <c r="CJ7" t="n">
         <v>20.64</v>
       </c>
+      <c r="CK7" t="n">
+        <v>14.67</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8679,6 +8737,9 @@
       </c>
       <c r="CJ8" t="n">
         <v>-36.89</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>-42.44</v>
       </c>
     </row>
     <row r="9">
@@ -9217,7 +9278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO10"/>
+  <dimension ref="A1:BP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9287,6 +9348,7 @@
     <col width="12" customWidth="1" min="65" max="65"/>
     <col width="12" customWidth="1" min="66" max="66"/>
     <col width="12" customWidth="1" min="67" max="67"/>
+    <col width="12" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9625,6 +9687,11 @@
           <t>20260226</t>
         </is>
       </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>20260227</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10423,6 +10490,9 @@
       <c r="BO5" t="n">
         <v>0</v>
       </c>
+      <c r="BP5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10822,6 +10892,9 @@
       <c r="BO7" t="n">
         <v>0</v>
       </c>
+      <c r="BP7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11027,6 +11100,9 @@
         <v>0</v>
       </c>
       <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11440,7 +11516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS10"/>
+  <dimension ref="A1:CT10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11540,6 +11616,7 @@
     <col width="10" customWidth="1" min="95" max="95"/>
     <col width="10" customWidth="1" min="96" max="96"/>
     <col width="10" customWidth="1" min="97" max="97"/>
+    <col width="10" customWidth="1" min="98" max="98"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11838,6 +11915,9 @@
       <c r="CS1" s="1" t="n">
         <v>20260226</v>
       </c>
+      <c r="CT1" s="1" t="n">
+        <v>20260227</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12135,6 +12215,9 @@
       <c r="CS2" t="n">
         <v>57</v>
       </c>
+      <c r="CT2" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12432,6 +12515,9 @@
       <c r="CS3" t="n">
         <v>-42</v>
       </c>
+      <c r="CT3" t="n">
+        <v>-48</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12729,6 +12815,9 @@
       <c r="CS4" t="n">
         <v>-44</v>
       </c>
+      <c r="CT4" t="n">
+        <v>-44</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13026,6 +13115,9 @@
       <c r="CS5" t="n">
         <v>-41</v>
       </c>
+      <c r="CT5" t="n">
+        <v>-37</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13323,6 +13415,9 @@
       <c r="CS6" t="n">
         <v>3</v>
       </c>
+      <c r="CT6" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13620,6 +13715,9 @@
       <c r="CS7" t="n">
         <v>81</v>
       </c>
+      <c r="CT7" t="n">
+        <v>-12</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13917,6 +14015,9 @@
       <c r="CS8" t="n">
         <v>-43</v>
       </c>
+      <c r="CT8" t="n">
+        <v>-35</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14214,6 +14315,9 @@
       <c r="CS9" t="n">
         <v>53</v>
       </c>
+      <c r="CT9" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14509,6 +14613,9 @@
         <v>-47</v>
       </c>
       <c r="CS10" t="n">
+        <v>-17</v>
+      </c>
+      <c r="CT10" t="n">
         <v>-17</v>
       </c>
     </row>
@@ -14523,7 +14630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14533,6 +14640,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14561,6 +14669,9 @@
       <c r="G1" s="1" t="n">
         <v>20260226</v>
       </c>
+      <c r="H1" s="1" t="n">
+        <v>20260227</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14585,6 +14696,9 @@
       <c r="G2" t="n">
         <v>80</v>
       </c>
+      <c r="H2" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14609,6 +14723,9 @@
       <c r="G3" t="n">
         <v>21</v>
       </c>
+      <c r="H3" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14636,6 +14753,9 @@
       <c r="G4" t="n">
         <v>75</v>
       </c>
+      <c r="H4" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14663,6 +14783,9 @@
       <c r="G5" t="n">
         <v>10</v>
       </c>
+      <c r="H5" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14687,6 +14810,9 @@
       <c r="G6" t="n">
         <v>1</v>
       </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14714,6 +14840,9 @@
       <c r="G7" t="n">
         <v>71</v>
       </c>
+      <c r="H7" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14741,6 +14870,9 @@
       <c r="G8" t="n">
         <v>7</v>
       </c>
+      <c r="H8" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14765,6 +14897,9 @@
       <c r="G9" t="n">
         <v>93</v>
       </c>
+      <c r="H9" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14790,6 +14925,9 @@
         <v>47</v>
       </c>
       <c r="G10" t="n">
+        <v>49</v>
+      </c>
+      <c r="H10" t="n">
         <v>49</v>
       </c>
     </row>
@@ -14804,7 +14942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14814,6 +14952,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14842,6 +14981,9 @@
       <c r="G1" s="1" t="n">
         <v>20260226</v>
       </c>
+      <c r="H1" s="1" t="n">
+        <v>20260227</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14866,6 +15008,9 @@
       <c r="G2" t="n">
         <v>44</v>
       </c>
+      <c r="H2" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14890,6 +15035,9 @@
       <c r="G3" t="n">
         <v>-76</v>
       </c>
+      <c r="H3" t="n">
+        <v>-86</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14917,6 +15065,9 @@
       <c r="G4" t="n">
         <v>32</v>
       </c>
+      <c r="H4" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14944,6 +15095,9 @@
       <c r="G5" t="n">
         <v>-104</v>
       </c>
+      <c r="H5" t="n">
+        <v>-99</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14968,6 +15122,9 @@
       <c r="G6" t="n">
         <v>-44</v>
       </c>
+      <c r="H6" t="n">
+        <v>-43</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14995,6 +15152,9 @@
       <c r="G7" t="n">
         <v>73</v>
       </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15022,6 +15182,9 @@
       <c r="G8" t="n">
         <v>-103</v>
       </c>
+      <c r="H8" t="n">
+        <v>-97</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15046,6 +15209,9 @@
       <c r="G9" t="n">
         <v>102</v>
       </c>
+      <c r="H9" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15071,6 +15237,9 @@
         <v>-39</v>
       </c>
       <c r="G10" t="n">
+        <v>-27</v>
+      </c>
+      <c r="H10" t="n">
         <v>-27</v>
       </c>
     </row>
@@ -15085,7 +15254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO10"/>
+  <dimension ref="A1:BP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -15155,6 +15324,7 @@
     <col width="12" customWidth="1" min="65" max="65"/>
     <col width="12" customWidth="1" min="66" max="66"/>
     <col width="12" customWidth="1" min="67" max="67"/>
+    <col width="12" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15493,6 +15663,11 @@
           <t>20260226</t>
         </is>
       </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>20260227</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16291,6 +16466,9 @@
       <c r="BO5" t="n">
         <v>88</v>
       </c>
+      <c r="BP5" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16690,6 +16868,9 @@
       <c r="BO7" t="n">
         <v>106</v>
       </c>
+      <c r="BP7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16896,6 +17077,9 @@
       </c>
       <c r="BO8" t="n">
         <v>81</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>83</v>
       </c>
     </row>
     <row r="9">
@@ -17308,7 +17492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DV10"/>
+  <dimension ref="A1:DW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17437,6 +17621,7 @@
     <col width="12" customWidth="1" min="124" max="124"/>
     <col width="12" customWidth="1" min="125" max="125"/>
     <col width="12" customWidth="1" min="126" max="126"/>
+    <col width="12" customWidth="1" min="127" max="127"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17822,6 +18007,9 @@
       <c r="DV1" s="1" t="n">
         <v>20260226</v>
       </c>
+      <c r="DW1" s="1" t="n">
+        <v>20260227</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18203,6 +18391,9 @@
       <c r="DV2" t="n">
         <v>274.23</v>
       </c>
+      <c r="DW2" t="n">
+        <v>272.95</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18584,6 +18775,9 @@
       <c r="DV3" t="n">
         <v>210.64</v>
       </c>
+      <c r="DW3" t="n">
+        <v>207.92</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19352,6 +19546,9 @@
       <c r="DV5" t="n">
         <v>400.6</v>
       </c>
+      <c r="DW5" t="n">
+        <v>401.72</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19733,6 +19930,9 @@
       <c r="DV6" t="n">
         <v>82.7</v>
       </c>
+      <c r="DW6" t="n">
+        <v>84.59</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20117,6 +20317,9 @@
       <c r="DV7" t="n">
         <v>195.56</v>
       </c>
+      <c r="DW7" t="n">
+        <v>184.89</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20501,6 +20704,9 @@
       <c r="DV8" t="n">
         <v>134.19</v>
       </c>
+      <c r="DW8" t="n">
+        <v>135.94</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20881,6 +21087,9 @@
       </c>
       <c r="DV9" t="n">
         <v>97.93000000000001</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>98.08</v>
       </c>
     </row>
     <row r="10">
@@ -21278,7 +21487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DV10"/>
+  <dimension ref="A1:DW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21407,6 +21616,7 @@
     <col width="12" customWidth="1" min="124" max="124"/>
     <col width="12" customWidth="1" min="125" max="125"/>
     <col width="12" customWidth="1" min="126" max="126"/>
+    <col width="12" customWidth="1" min="127" max="127"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21792,6 +22002,9 @@
       <c r="DV1" s="1" t="n">
         <v>20260226</v>
       </c>
+      <c r="DW1" s="1" t="n">
+        <v>20260227</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22173,6 +22386,9 @@
       <c r="DV2" t="n">
         <v>274.23</v>
       </c>
+      <c r="DW2" t="n">
+        <v>272.95</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22554,6 +22770,9 @@
       <c r="DV3" t="n">
         <v>210.64</v>
       </c>
+      <c r="DW3" t="n">
+        <v>207.92</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23322,6 +23541,9 @@
       <c r="DV5" t="n">
         <v>400.6</v>
       </c>
+      <c r="DW5" t="n">
+        <v>401.72</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23703,6 +23925,9 @@
       <c r="DV6" t="n">
         <v>82.7</v>
       </c>
+      <c r="DW6" t="n">
+        <v>84.59</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24087,6 +24312,9 @@
       <c r="DV7" t="n">
         <v>195.56</v>
       </c>
+      <c r="DW7" t="n">
+        <v>184.89</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24471,6 +24699,9 @@
       <c r="DV8" t="n">
         <v>134.19</v>
       </c>
+      <c r="DW8" t="n">
+        <v>135.94</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24851,6 +25082,9 @@
       </c>
       <c r="DV9" t="n">
         <v>97.93000000000001</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>98.08</v>
       </c>
     </row>
     <row r="10">
@@ -25248,7 +25482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DV10"/>
+  <dimension ref="A1:DW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25377,6 +25611,7 @@
     <col width="12" customWidth="1" min="124" max="124"/>
     <col width="12" customWidth="1" min="125" max="125"/>
     <col width="12" customWidth="1" min="126" max="126"/>
+    <col width="12" customWidth="1" min="127" max="127"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25762,6 +25997,9 @@
       <c r="DV1" s="1" t="n">
         <v>20260226</v>
       </c>
+      <c r="DW1" s="1" t="n">
+        <v>20260227</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -26143,6 +26381,9 @@
       <c r="DV2" t="n">
         <v>274.23</v>
       </c>
+      <c r="DW2" t="n">
+        <v>272.95</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -26524,6 +26765,9 @@
       <c r="DV3" t="n">
         <v>210.64</v>
       </c>
+      <c r="DW3" t="n">
+        <v>207.92</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -27292,6 +27536,9 @@
       <c r="DV5" t="n">
         <v>400.6</v>
       </c>
+      <c r="DW5" t="n">
+        <v>401.72</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -27673,6 +27920,9 @@
       <c r="DV6" t="n">
         <v>82.7</v>
       </c>
+      <c r="DW6" t="n">
+        <v>84.59</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -28057,6 +28307,9 @@
       <c r="DV7" t="n">
         <v>195.56</v>
       </c>
+      <c r="DW7" t="n">
+        <v>184.89</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -28441,6 +28694,9 @@
       <c r="DV8" t="n">
         <v>134.19</v>
       </c>
+      <c r="DW8" t="n">
+        <v>135.94</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -28821,6 +29077,9 @@
       </c>
       <c r="DV9" t="n">
         <v>97.93000000000001</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>98.08</v>
       </c>
     </row>
     <row r="10">
@@ -29218,7 +29477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DV10"/>
+  <dimension ref="A1:DW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -29347,6 +29606,7 @@
     <col width="12" customWidth="1" min="124" max="124"/>
     <col width="12" customWidth="1" min="125" max="125"/>
     <col width="12" customWidth="1" min="126" max="126"/>
+    <col width="12" customWidth="1" min="127" max="127"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29732,6 +29992,9 @@
       <c r="DV1" s="1" t="n">
         <v>20260226</v>
       </c>
+      <c r="DW1" s="1" t="n">
+        <v>20260227</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -30113,6 +30376,9 @@
       <c r="DV2" t="n">
         <v>274.23</v>
       </c>
+      <c r="DW2" t="n">
+        <v>272.95</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -30494,6 +30760,9 @@
       <c r="DV3" t="n">
         <v>210.64</v>
       </c>
+      <c r="DW3" t="n">
+        <v>207.92</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -31262,6 +31531,9 @@
       <c r="DV5" t="n">
         <v>400.6</v>
       </c>
+      <c r="DW5" t="n">
+        <v>401.72</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -31643,6 +31915,9 @@
       <c r="DV6" t="n">
         <v>82.7</v>
       </c>
+      <c r="DW6" t="n">
+        <v>84.59</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -32027,6 +32302,9 @@
       <c r="DV7" t="n">
         <v>195.56</v>
       </c>
+      <c r="DW7" t="n">
+        <v>184.89</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -32411,6 +32689,9 @@
       <c r="DV8" t="n">
         <v>134.19</v>
       </c>
+      <c r="DW8" t="n">
+        <v>135.94</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -32791,6 +33072,9 @@
       </c>
       <c r="DV9" t="n">
         <v>97.93000000000001</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>98.08</v>
       </c>
     </row>
     <row r="10">
@@ -33188,7 +33472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DV10"/>
+  <dimension ref="A1:DW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -33317,6 +33601,7 @@
     <col width="12" customWidth="1" min="124" max="124"/>
     <col width="12" customWidth="1" min="125" max="125"/>
     <col width="12" customWidth="1" min="126" max="126"/>
+    <col width="12" customWidth="1" min="127" max="127"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33702,6 +33987,9 @@
       <c r="DV1" s="1" t="n">
         <v>20260226</v>
       </c>
+      <c r="DW1" s="1" t="n">
+        <v>20260227</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -34083,6 +34371,9 @@
       <c r="DV2" t="n">
         <v>0</v>
       </c>
+      <c r="DW2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -34464,6 +34755,9 @@
       <c r="DV3" t="n">
         <v>0</v>
       </c>
+      <c r="DW3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -35232,6 +35526,9 @@
       <c r="DV5" t="n">
         <v>0</v>
       </c>
+      <c r="DW5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -35613,6 +35910,9 @@
       <c r="DV6" t="n">
         <v>0</v>
       </c>
+      <c r="DW6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -35997,6 +36297,9 @@
       <c r="DV7" t="n">
         <v>0</v>
       </c>
+      <c r="DW7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -36381,6 +36684,9 @@
       <c r="DV8" t="n">
         <v>0</v>
       </c>
+      <c r="DW8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -36760,6 +37066,9 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -37158,7 +37467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DC10"/>
+  <dimension ref="A1:DD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -37268,6 +37577,7 @@
     <col width="10" customWidth="1" min="105" max="105"/>
     <col width="10" customWidth="1" min="106" max="106"/>
     <col width="10" customWidth="1" min="107" max="107"/>
+    <col width="10" customWidth="1" min="108" max="108"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37596,6 +37906,9 @@
       <c r="DC1" s="1" t="n">
         <v>20260226</v>
       </c>
+      <c r="DD1" s="1" t="n">
+        <v>20260227</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -37923,6 +38236,9 @@
       <c r="DC2" t="n">
         <v>83</v>
       </c>
+      <c r="DD2" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -38250,6 +38566,9 @@
       <c r="DC3" t="n">
         <v>27</v>
       </c>
+      <c r="DD3" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -38577,6 +38896,9 @@
       <c r="DC4" t="n">
         <v>29</v>
       </c>
+      <c r="DD4" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -38904,6 +39226,9 @@
       <c r="DC5" t="n">
         <v>33</v>
       </c>
+      <c r="DD5" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -39231,6 +39556,9 @@
       <c r="DC6" t="n">
         <v>78</v>
       </c>
+      <c r="DD6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -39558,6 +39886,9 @@
       <c r="DC7" t="n">
         <v>100</v>
       </c>
+      <c r="DD7" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -39885,6 +40216,9 @@
       <c r="DC8" t="n">
         <v>18</v>
       </c>
+      <c r="DD8" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -40212,6 +40546,9 @@
       <c r="DC9" t="n">
         <v>80</v>
       </c>
+      <c r="DD9" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -40537,6 +40874,9 @@
         <v>36</v>
       </c>
       <c r="DC10" t="n">
+        <v>61</v>
+      </c>
+      <c r="DD10" t="n">
         <v>61</v>
       </c>
     </row>
@@ -40551,7 +40891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO10"/>
+  <dimension ref="A1:BP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -40621,6 +40961,7 @@
     <col width="10" customWidth="1" min="65" max="65"/>
     <col width="10" customWidth="1" min="66" max="66"/>
     <col width="10" customWidth="1" min="67" max="67"/>
+    <col width="10" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -40829,6 +41170,9 @@
       <c r="BO1" s="1" t="n">
         <v>20260226</v>
       </c>
+      <c r="BP1" s="1" t="n">
+        <v>20260227</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -41036,6 +41380,9 @@
       <c r="BO2" t="n">
         <v>70</v>
       </c>
+      <c r="BP2" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -41243,6 +41590,9 @@
       <c r="BO3" t="n">
         <v>24</v>
       </c>
+      <c r="BP3" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -41450,6 +41800,9 @@
       <c r="BO4" t="n">
         <v>38</v>
       </c>
+      <c r="BP4" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -41657,6 +42010,9 @@
       <c r="BO5" t="n">
         <v>15</v>
       </c>
+      <c r="BP5" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -41864,6 +42220,9 @@
       <c r="BO6" t="n">
         <v>20</v>
       </c>
+      <c r="BP6" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -42071,6 +42430,9 @@
       <c r="BO7" t="n">
         <v>100</v>
       </c>
+      <c r="BP7" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -42278,6 +42640,9 @@
       <c r="BO8" t="n">
         <v>8</v>
       </c>
+      <c r="BP8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -42485,6 +42850,9 @@
       <c r="BO9" t="n">
         <v>91</v>
       </c>
+      <c r="BP9" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -42690,6 +43058,9 @@
         <v>13</v>
       </c>
       <c r="BO10" t="n">
+        <v>22</v>
+      </c>
+      <c r="BP10" t="n">
         <v>22</v>
       </c>
     </row>
@@ -42704,7 +43075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DC10"/>
+  <dimension ref="A1:DD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -42814,6 +43185,7 @@
     <col width="10" customWidth="1" min="105" max="105"/>
     <col width="10" customWidth="1" min="106" max="106"/>
     <col width="10" customWidth="1" min="107" max="107"/>
+    <col width="10" customWidth="1" min="108" max="108"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -43142,6 +43514,9 @@
       <c r="DC1" s="1" t="n">
         <v>20260226</v>
       </c>
+      <c r="DD1" s="1" t="n">
+        <v>20260227</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -43469,6 +43844,9 @@
       <c r="DC2" t="n">
         <v>42</v>
       </c>
+      <c r="DD2" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -43796,6 +44174,9 @@
       <c r="DC3" t="n">
         <v>-23</v>
       </c>
+      <c r="DD3" t="n">
+        <v>-27</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -44123,6 +44504,9 @@
       <c r="DC4" t="n">
         <v>-27</v>
       </c>
+      <c r="DD4" t="n">
+        <v>-27</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -44450,6 +44834,9 @@
       <c r="DC5" t="n">
         <v>-22</v>
       </c>
+      <c r="DD5" t="n">
+        <v>-13</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -44777,6 +45164,9 @@
       <c r="DC6" t="n">
         <v>46</v>
       </c>
+      <c r="DD6" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -45104,6 +45494,9 @@
       <c r="DC7" t="n">
         <v>68</v>
       </c>
+      <c r="DD7" t="n">
+        <v>-9</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -45431,6 +45824,9 @@
       <c r="DC8" t="n">
         <v>-24</v>
       </c>
+      <c r="DD8" t="n">
+        <v>-8</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -45758,6 +46154,9 @@
       <c r="DC9" t="n">
         <v>44</v>
       </c>
+      <c r="DD9" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -46083,6 +46482,9 @@
         <v>-31</v>
       </c>
       <c r="DC10" t="n">
+        <v>14</v>
+      </c>
+      <c r="DD10" t="n">
         <v>14</v>
       </c>
     </row>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -605,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP10"/>
+  <dimension ref="A1:BQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -676,6 +676,7 @@
     <col width="10" customWidth="1" min="66" max="66"/>
     <col width="10" customWidth="1" min="67" max="67"/>
     <col width="10" customWidth="1" min="68" max="68"/>
+    <col width="10" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -887,6 +888,9 @@
       <c r="BP1" s="1" t="n">
         <v>20260227</v>
       </c>
+      <c r="BQ1" s="1" t="n">
+        <v>20260302</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1097,6 +1101,9 @@
       <c r="BP2" t="n">
         <v>24</v>
       </c>
+      <c r="BQ2" t="n">
+        <v>-19</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1307,6 +1314,9 @@
       <c r="BP3" t="n">
         <v>-75</v>
       </c>
+      <c r="BQ3" t="n">
+        <v>-65</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1517,6 +1527,9 @@
       <c r="BP4" t="n">
         <v>-30</v>
       </c>
+      <c r="BQ4" t="n">
+        <v>-35</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1727,6 +1740,9 @@
       <c r="BP5" t="n">
         <v>-70</v>
       </c>
+      <c r="BQ5" t="n">
+        <v>-79</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1937,6 +1953,9 @@
       <c r="BP6" t="n">
         <v>-26</v>
       </c>
+      <c r="BQ6" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2147,6 +2166,9 @@
       <c r="BP7" t="n">
         <v>-1</v>
       </c>
+      <c r="BQ7" t="n">
+        <v>-69</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2357,6 +2379,9 @@
       <c r="BP8" t="n">
         <v>-67</v>
       </c>
+      <c r="BQ8" t="n">
+        <v>-62</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2567,6 +2592,9 @@
       <c r="BP9" t="n">
         <v>68</v>
       </c>
+      <c r="BQ9" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2776,6 +2804,9 @@
       </c>
       <c r="BP10" t="n">
         <v>-45</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>-74</v>
       </c>
     </row>
   </sheetData>
@@ -2789,7 +2820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DD10"/>
+  <dimension ref="A1:DE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2900,6 +2931,7 @@
     <col width="12" customWidth="1" min="106" max="106"/>
     <col width="12" customWidth="1" min="107" max="107"/>
     <col width="12" customWidth="1" min="108" max="108"/>
+    <col width="12" customWidth="1" min="109" max="109"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3443,6 +3475,11 @@
           <t>20260227</t>
         </is>
       </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4724,6 +4761,9 @@
       <c r="DD5" t="n">
         <v>99</v>
       </c>
+      <c r="DE5" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5366,6 +5406,9 @@
       <c r="DD7" t="n">
         <v>99</v>
       </c>
+      <c r="DE7" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5695,6 +5738,9 @@
       </c>
       <c r="DD8" t="n">
         <v>99</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -6347,7 +6393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CK10"/>
+  <dimension ref="A1:CL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6439,6 +6485,7 @@
     <col width="12" customWidth="1" min="87" max="87"/>
     <col width="12" customWidth="1" min="88" max="88"/>
     <col width="12" customWidth="1" min="89" max="89"/>
+    <col width="12" customWidth="1" min="90" max="90"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6887,6 +6934,11 @@
           <t>20260227</t>
         </is>
       </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7940,6 +7992,9 @@
       <c r="CK5" t="n">
         <v>-50.28</v>
       </c>
+      <c r="CL5" t="n">
+        <v>-55.34</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8468,6 +8523,9 @@
       <c r="CK7" t="n">
         <v>14.67</v>
       </c>
+      <c r="CL7" t="n">
+        <v>14.53</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8740,6 +8798,9 @@
       </c>
       <c r="CK8" t="n">
         <v>-42.44</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>-44.69</v>
       </c>
     </row>
     <row r="9">
@@ -9278,7 +9339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP10"/>
+  <dimension ref="A1:BQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9349,6 +9410,7 @@
     <col width="12" customWidth="1" min="66" max="66"/>
     <col width="12" customWidth="1" min="67" max="67"/>
     <col width="12" customWidth="1" min="68" max="68"/>
+    <col width="12" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9692,6 +9754,11 @@
           <t>20260227</t>
         </is>
       </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10493,6 +10560,9 @@
       <c r="BP5" t="n">
         <v>0</v>
       </c>
+      <c r="BQ5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10895,6 +10965,9 @@
       <c r="BP7" t="n">
         <v>0</v>
       </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11103,6 +11176,9 @@
         <v>0</v>
       </c>
       <c r="BP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11516,7 +11592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CT10"/>
+  <dimension ref="A1:CU10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11617,6 +11693,7 @@
     <col width="10" customWidth="1" min="96" max="96"/>
     <col width="10" customWidth="1" min="97" max="97"/>
     <col width="10" customWidth="1" min="98" max="98"/>
+    <col width="10" customWidth="1" min="99" max="99"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11918,6 +11995,9 @@
       <c r="CT1" s="1" t="n">
         <v>20260227</v>
       </c>
+      <c r="CU1" s="1" t="n">
+        <v>20260302</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12218,6 +12298,9 @@
       <c r="CT2" t="n">
         <v>48</v>
       </c>
+      <c r="CU2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12518,6 +12601,9 @@
       <c r="CT3" t="n">
         <v>-48</v>
       </c>
+      <c r="CU3" t="n">
+        <v>-38</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12818,6 +12904,9 @@
       <c r="CT4" t="n">
         <v>-44</v>
       </c>
+      <c r="CU4" t="n">
+        <v>-46</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13118,6 +13207,9 @@
       <c r="CT5" t="n">
         <v>-37</v>
       </c>
+      <c r="CU5" t="n">
+        <v>-49</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13418,6 +13510,9 @@
       <c r="CT6" t="n">
         <v>31</v>
       </c>
+      <c r="CU6" t="n">
+        <v>157</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13718,6 +13813,9 @@
       <c r="CT7" t="n">
         <v>-12</v>
       </c>
+      <c r="CU7" t="n">
+        <v>-73</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14018,6 +14116,9 @@
       <c r="CT8" t="n">
         <v>-35</v>
       </c>
+      <c r="CU8" t="n">
+        <v>-28</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14318,6 +14419,9 @@
       <c r="CT9" t="n">
         <v>54</v>
       </c>
+      <c r="CU9" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14617,6 +14721,9 @@
       </c>
       <c r="CT10" t="n">
         <v>-17</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>-67</v>
       </c>
     </row>
   </sheetData>
@@ -14630,7 +14737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14641,6 +14748,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14672,6 +14780,9 @@
       <c r="H1" s="1" t="n">
         <v>20260227</v>
       </c>
+      <c r="I1" s="1" t="n">
+        <v>20260302</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14699,6 +14810,9 @@
       <c r="H2" t="n">
         <v>78</v>
       </c>
+      <c r="I2" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14726,6 +14840,9 @@
       <c r="H3" t="n">
         <v>17</v>
       </c>
+      <c r="I3" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14756,6 +14873,9 @@
       <c r="H4" t="n">
         <v>75</v>
       </c>
+      <c r="I4" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14786,6 +14906,9 @@
       <c r="H5" t="n">
         <v>11</v>
       </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14813,6 +14936,9 @@
       <c r="H6" t="n">
         <v>1</v>
       </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14843,6 +14969,9 @@
       <c r="H7" t="n">
         <v>43</v>
       </c>
+      <c r="I7" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14873,6 +15002,9 @@
       <c r="H8" t="n">
         <v>9</v>
       </c>
+      <c r="I8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14900,6 +15032,9 @@
       <c r="H9" t="n">
         <v>93</v>
       </c>
+      <c r="I9" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14929,6 +15064,9 @@
       </c>
       <c r="H10" t="n">
         <v>49</v>
+      </c>
+      <c r="I10" t="n">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -14942,7 +15080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14953,6 +15091,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14984,6 +15123,9 @@
       <c r="H1" s="1" t="n">
         <v>20260227</v>
       </c>
+      <c r="I1" s="1" t="n">
+        <v>20260302</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15011,6 +15153,9 @@
       <c r="H2" t="n">
         <v>38</v>
       </c>
+      <c r="I2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15038,6 +15183,9 @@
       <c r="H3" t="n">
         <v>-86</v>
       </c>
+      <c r="I3" t="n">
+        <v>-76</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15068,6 +15216,9 @@
       <c r="H4" t="n">
         <v>32</v>
       </c>
+      <c r="I4" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15098,6 +15249,9 @@
       <c r="H5" t="n">
         <v>-99</v>
       </c>
+      <c r="I5" t="n">
+        <v>-108</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15125,6 +15279,9 @@
       <c r="H6" t="n">
         <v>-43</v>
       </c>
+      <c r="I6" t="n">
+        <v>-42</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15155,6 +15312,9 @@
       <c r="H7" t="n">
         <v>0</v>
       </c>
+      <c r="I7" t="n">
+        <v>-55</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15185,6 +15345,9 @@
       <c r="H8" t="n">
         <v>-97</v>
       </c>
+      <c r="I8" t="n">
+        <v>-92</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15212,6 +15375,9 @@
       <c r="H9" t="n">
         <v>101</v>
       </c>
+      <c r="I9" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15241,6 +15407,9 @@
       </c>
       <c r="H10" t="n">
         <v>-27</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-58</v>
       </c>
     </row>
   </sheetData>
@@ -15254,7 +15423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP10"/>
+  <dimension ref="A1:BQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -15325,6 +15494,7 @@
     <col width="12" customWidth="1" min="66" max="66"/>
     <col width="12" customWidth="1" min="67" max="67"/>
     <col width="12" customWidth="1" min="68" max="68"/>
+    <col width="12" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15668,6 +15838,11 @@
           <t>20260227</t>
         </is>
       </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16469,6 +16644,9 @@
       <c r="BP5" t="n">
         <v>89</v>
       </c>
+      <c r="BQ5" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16871,6 +17049,9 @@
       <c r="BP7" t="n">
         <v>100</v>
       </c>
+      <c r="BQ7" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17080,6 +17261,9 @@
       </c>
       <c r="BP8" t="n">
         <v>83</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="9">
@@ -17492,7 +17676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DW10"/>
+  <dimension ref="A1:DX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17622,6 +17806,7 @@
     <col width="12" customWidth="1" min="125" max="125"/>
     <col width="12" customWidth="1" min="126" max="126"/>
     <col width="12" customWidth="1" min="127" max="127"/>
+    <col width="12" customWidth="1" min="128" max="128"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18010,6 +18195,9 @@
       <c r="DW1" s="1" t="n">
         <v>20260227</v>
       </c>
+      <c r="DX1" s="1" t="n">
+        <v>20260302</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18394,6 +18582,9 @@
       <c r="DW2" t="n">
         <v>272.95</v>
       </c>
+      <c r="DX2" t="n">
+        <v>264.18</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18778,6 +18969,9 @@
       <c r="DW3" t="n">
         <v>207.92</v>
       </c>
+      <c r="DX3" t="n">
+        <v>210</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19162,6 +19356,9 @@
       <c r="DV4" t="n">
         <v>312.9</v>
       </c>
+      <c r="DX4" t="n">
+        <v>311.76</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19549,6 +19746,9 @@
       <c r="DW5" t="n">
         <v>401.72</v>
       </c>
+      <c r="DX5" t="n">
+        <v>392.74</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19933,6 +20133,9 @@
       <c r="DW6" t="n">
         <v>84.59</v>
       </c>
+      <c r="DX6" t="n">
+        <v>96.23999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20320,6 +20523,9 @@
       <c r="DW7" t="n">
         <v>184.89</v>
       </c>
+      <c r="DX7" t="n">
+        <v>177.19</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20707,6 +20913,9 @@
       <c r="DW8" t="n">
         <v>135.94</v>
       </c>
+      <c r="DX8" t="n">
+        <v>137.19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21091,6 +21300,9 @@
       <c r="DW9" t="n">
         <v>98.08</v>
       </c>
+      <c r="DX9" t="n">
+        <v>98.02</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21474,6 +21686,9 @@
       </c>
       <c r="DV10" t="n">
         <v>417.4</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>402.51</v>
       </c>
     </row>
   </sheetData>
@@ -21487,7 +21702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DW10"/>
+  <dimension ref="A1:DX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21617,6 +21832,7 @@
     <col width="12" customWidth="1" min="125" max="125"/>
     <col width="12" customWidth="1" min="126" max="126"/>
     <col width="12" customWidth="1" min="127" max="127"/>
+    <col width="12" customWidth="1" min="128" max="128"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22005,6 +22221,9 @@
       <c r="DW1" s="1" t="n">
         <v>20260227</v>
       </c>
+      <c r="DX1" s="1" t="n">
+        <v>20260302</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22389,6 +22608,9 @@
       <c r="DW2" t="n">
         <v>272.95</v>
       </c>
+      <c r="DX2" t="n">
+        <v>264.18</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22773,6 +22995,9 @@
       <c r="DW3" t="n">
         <v>207.92</v>
       </c>
+      <c r="DX3" t="n">
+        <v>210</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23157,6 +23382,9 @@
       <c r="DV4" t="n">
         <v>312.9</v>
       </c>
+      <c r="DX4" t="n">
+        <v>311.76</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23544,6 +23772,9 @@
       <c r="DW5" t="n">
         <v>401.72</v>
       </c>
+      <c r="DX5" t="n">
+        <v>392.74</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23928,6 +24159,9 @@
       <c r="DW6" t="n">
         <v>84.59</v>
       </c>
+      <c r="DX6" t="n">
+        <v>96.23999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24315,6 +24549,9 @@
       <c r="DW7" t="n">
         <v>184.89</v>
       </c>
+      <c r="DX7" t="n">
+        <v>177.19</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24702,6 +24939,9 @@
       <c r="DW8" t="n">
         <v>135.94</v>
       </c>
+      <c r="DX8" t="n">
+        <v>137.19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25086,6 +25326,9 @@
       <c r="DW9" t="n">
         <v>98.08</v>
       </c>
+      <c r="DX9" t="n">
+        <v>98.02</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25469,6 +25712,9 @@
       </c>
       <c r="DV10" t="n">
         <v>417.4</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>402.51</v>
       </c>
     </row>
   </sheetData>
@@ -25482,7 +25728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DW10"/>
+  <dimension ref="A1:DX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25612,6 +25858,7 @@
     <col width="12" customWidth="1" min="125" max="125"/>
     <col width="12" customWidth="1" min="126" max="126"/>
     <col width="12" customWidth="1" min="127" max="127"/>
+    <col width="12" customWidth="1" min="128" max="128"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26000,6 +26247,9 @@
       <c r="DW1" s="1" t="n">
         <v>20260227</v>
       </c>
+      <c r="DX1" s="1" t="n">
+        <v>20260302</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -26384,6 +26634,9 @@
       <c r="DW2" t="n">
         <v>272.95</v>
       </c>
+      <c r="DX2" t="n">
+        <v>264.18</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -26768,6 +27021,9 @@
       <c r="DW3" t="n">
         <v>207.92</v>
       </c>
+      <c r="DX3" t="n">
+        <v>210</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -27152,6 +27408,9 @@
       <c r="DV4" t="n">
         <v>312.9</v>
       </c>
+      <c r="DX4" t="n">
+        <v>311.76</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -27539,6 +27798,9 @@
       <c r="DW5" t="n">
         <v>401.72</v>
       </c>
+      <c r="DX5" t="n">
+        <v>392.74</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -27923,6 +28185,9 @@
       <c r="DW6" t="n">
         <v>84.59</v>
       </c>
+      <c r="DX6" t="n">
+        <v>96.23999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -28310,6 +28575,9 @@
       <c r="DW7" t="n">
         <v>184.89</v>
       </c>
+      <c r="DX7" t="n">
+        <v>177.19</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -28697,6 +28965,9 @@
       <c r="DW8" t="n">
         <v>135.94</v>
       </c>
+      <c r="DX8" t="n">
+        <v>137.19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -29081,6 +29352,9 @@
       <c r="DW9" t="n">
         <v>98.08</v>
       </c>
+      <c r="DX9" t="n">
+        <v>98.02</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -29464,6 +29738,9 @@
       </c>
       <c r="DV10" t="n">
         <v>417.4</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>402.51</v>
       </c>
     </row>
   </sheetData>
@@ -29477,7 +29754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DW10"/>
+  <dimension ref="A1:DX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -29607,6 +29884,7 @@
     <col width="12" customWidth="1" min="125" max="125"/>
     <col width="12" customWidth="1" min="126" max="126"/>
     <col width="12" customWidth="1" min="127" max="127"/>
+    <col width="12" customWidth="1" min="128" max="128"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29995,6 +30273,9 @@
       <c r="DW1" s="1" t="n">
         <v>20260227</v>
       </c>
+      <c r="DX1" s="1" t="n">
+        <v>20260302</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -30379,6 +30660,9 @@
       <c r="DW2" t="n">
         <v>272.95</v>
       </c>
+      <c r="DX2" t="n">
+        <v>264.18</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -30763,6 +31047,9 @@
       <c r="DW3" t="n">
         <v>207.92</v>
       </c>
+      <c r="DX3" t="n">
+        <v>210</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -31147,6 +31434,9 @@
       <c r="DV4" t="n">
         <v>312.9</v>
       </c>
+      <c r="DX4" t="n">
+        <v>311.76</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -31534,6 +31824,9 @@
       <c r="DW5" t="n">
         <v>401.72</v>
       </c>
+      <c r="DX5" t="n">
+        <v>392.74</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -31918,6 +32211,9 @@
       <c r="DW6" t="n">
         <v>84.59</v>
       </c>
+      <c r="DX6" t="n">
+        <v>96.23999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -32305,6 +32601,9 @@
       <c r="DW7" t="n">
         <v>184.89</v>
       </c>
+      <c r="DX7" t="n">
+        <v>177.19</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -32692,6 +32991,9 @@
       <c r="DW8" t="n">
         <v>135.94</v>
       </c>
+      <c r="DX8" t="n">
+        <v>137.19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -33076,6 +33378,9 @@
       <c r="DW9" t="n">
         <v>98.08</v>
       </c>
+      <c r="DX9" t="n">
+        <v>98.02</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -33459,6 +33764,9 @@
       </c>
       <c r="DV10" t="n">
         <v>417.4</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>402.51</v>
       </c>
     </row>
   </sheetData>
@@ -33472,7 +33780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DW10"/>
+  <dimension ref="A1:DX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -33602,6 +33910,7 @@
     <col width="12" customWidth="1" min="125" max="125"/>
     <col width="12" customWidth="1" min="126" max="126"/>
     <col width="12" customWidth="1" min="127" max="127"/>
+    <col width="12" customWidth="1" min="128" max="128"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33990,6 +34299,9 @@
       <c r="DW1" s="1" t="n">
         <v>20260227</v>
       </c>
+      <c r="DX1" s="1" t="n">
+        <v>20260302</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -34374,6 +34686,9 @@
       <c r="DW2" t="n">
         <v>0</v>
       </c>
+      <c r="DX2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -34758,6 +35073,9 @@
       <c r="DW3" t="n">
         <v>0</v>
       </c>
+      <c r="DX3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -35142,6 +35460,9 @@
       <c r="DV4" t="n">
         <v>0</v>
       </c>
+      <c r="DX4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -35529,6 +35850,9 @@
       <c r="DW5" t="n">
         <v>0</v>
       </c>
+      <c r="DX5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -35913,6 +36237,9 @@
       <c r="DW6" t="n">
         <v>0</v>
       </c>
+      <c r="DX6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -36300,6 +36627,9 @@
       <c r="DW7" t="n">
         <v>0</v>
       </c>
+      <c r="DX7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -36687,6 +37017,9 @@
       <c r="DW8" t="n">
         <v>0</v>
       </c>
+      <c r="DX8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -37071,6 +37404,9 @@
       <c r="DW9" t="n">
         <v>0</v>
       </c>
+      <c r="DX9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -37453,6 +37789,9 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -37467,7 +37806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DD10"/>
+  <dimension ref="A1:DE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -37578,6 +37917,7 @@
     <col width="10" customWidth="1" min="106" max="106"/>
     <col width="10" customWidth="1" min="107" max="107"/>
     <col width="10" customWidth="1" min="108" max="108"/>
+    <col width="10" customWidth="1" min="109" max="109"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37909,6 +38249,9 @@
       <c r="DD1" s="1" t="n">
         <v>20260227</v>
       </c>
+      <c r="DE1" s="1" t="n">
+        <v>20260302</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -38239,6 +38582,9 @@
       <c r="DD2" t="n">
         <v>77</v>
       </c>
+      <c r="DE2" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -38569,6 +38915,9 @@
       <c r="DD3" t="n">
         <v>21</v>
       </c>
+      <c r="DE3" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -38899,6 +39248,9 @@
       <c r="DD4" t="n">
         <v>29</v>
       </c>
+      <c r="DE4" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -39229,6 +39581,9 @@
       <c r="DD5" t="n">
         <v>38</v>
       </c>
+      <c r="DE5" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -39559,6 +39914,9 @@
       <c r="DD6" t="n">
         <v>100</v>
       </c>
+      <c r="DE6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -39889,6 +40247,9 @@
       <c r="DD7" t="n">
         <v>55</v>
       </c>
+      <c r="DE7" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -40219,6 +40580,9 @@
       <c r="DD8" t="n">
         <v>24</v>
       </c>
+      <c r="DE8" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -40549,6 +40913,9 @@
       <c r="DD9" t="n">
         <v>82</v>
       </c>
+      <c r="DE9" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -40878,6 +41245,9 @@
       </c>
       <c r="DD10" t="n">
         <v>61</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -40891,7 +41261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP10"/>
+  <dimension ref="A1:BQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -40962,6 +41332,7 @@
     <col width="10" customWidth="1" min="66" max="66"/>
     <col width="10" customWidth="1" min="67" max="67"/>
     <col width="10" customWidth="1" min="68" max="68"/>
+    <col width="10" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -41173,6 +41544,9 @@
       <c r="BP1" s="1" t="n">
         <v>20260227</v>
       </c>
+      <c r="BQ1" s="1" t="n">
+        <v>20260302</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -41383,6 +41757,9 @@
       <c r="BP2" t="n">
         <v>66</v>
       </c>
+      <c r="BQ2" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -41593,6 +41970,9 @@
       <c r="BP3" t="n">
         <v>19</v>
       </c>
+      <c r="BQ3" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -41803,6 +42183,9 @@
       <c r="BP4" t="n">
         <v>38</v>
       </c>
+      <c r="BQ4" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -42013,6 +42396,9 @@
       <c r="BP5" t="n">
         <v>16</v>
       </c>
+      <c r="BQ5" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -42223,6 +42609,9 @@
       <c r="BP6" t="n">
         <v>26</v>
       </c>
+      <c r="BQ6" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -42433,6 +42822,9 @@
       <c r="BP7" t="n">
         <v>57</v>
       </c>
+      <c r="BQ7" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -42643,6 +43035,9 @@
       <c r="BP8" t="n">
         <v>11</v>
       </c>
+      <c r="BQ8" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -42853,6 +43248,9 @@
       <c r="BP9" t="n">
         <v>92</v>
       </c>
+      <c r="BQ9" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -43062,6 +43460,9 @@
       </c>
       <c r="BP10" t="n">
         <v>22</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -43075,7 +43476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DD10"/>
+  <dimension ref="A1:DE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -43186,6 +43587,7 @@
     <col width="10" customWidth="1" min="106" max="106"/>
     <col width="10" customWidth="1" min="107" max="107"/>
     <col width="10" customWidth="1" min="108" max="108"/>
+    <col width="10" customWidth="1" min="109" max="109"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -43517,6 +43919,9 @@
       <c r="DD1" s="1" t="n">
         <v>20260227</v>
       </c>
+      <c r="DE1" s="1" t="n">
+        <v>20260302</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -43847,6 +44252,9 @@
       <c r="DD2" t="n">
         <v>30</v>
       </c>
+      <c r="DE2" t="n">
+        <v>-35</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -44177,6 +44585,9 @@
       <c r="DD3" t="n">
         <v>-27</v>
       </c>
+      <c r="DE3" t="n">
+        <v>-17</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -44507,6 +44918,9 @@
       <c r="DD4" t="n">
         <v>-27</v>
       </c>
+      <c r="DE4" t="n">
+        <v>-27</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -44837,6 +45251,9 @@
       <c r="DD5" t="n">
         <v>-13</v>
       </c>
+      <c r="DE5" t="n">
+        <v>-48</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -45167,6 +45584,9 @@
       <c r="DD6" t="n">
         <v>82</v>
       </c>
+      <c r="DE6" t="n">
+        <v>173</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -45497,6 +45917,9 @@
       <c r="DD7" t="n">
         <v>-9</v>
       </c>
+      <c r="DE7" t="n">
+        <v>-61</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -45827,6 +46250,9 @@
       <c r="DD8" t="n">
         <v>-8</v>
       </c>
+      <c r="DE8" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -46157,6 +46583,9 @@
       <c r="DD9" t="n">
         <v>43</v>
       </c>
+      <c r="DE9" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -46486,6 +46915,9 @@
       </c>
       <c r="DD10" t="n">
         <v>14</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>-60</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -605,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ10"/>
+  <dimension ref="A1:BR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -677,6 +677,7 @@
     <col width="10" customWidth="1" min="67" max="67"/>
     <col width="10" customWidth="1" min="68" max="68"/>
     <col width="10" customWidth="1" min="69" max="69"/>
+    <col width="10" customWidth="1" min="70" max="70"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -891,6 +892,9 @@
       <c r="BQ1" s="1" t="n">
         <v>20260302</v>
       </c>
+      <c r="BR1" s="1" t="n">
+        <v>20260303</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1104,6 +1108,9 @@
       <c r="BQ2" t="n">
         <v>-19</v>
       </c>
+      <c r="BR2" t="n">
+        <v>-20</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1317,6 +1324,9 @@
       <c r="BQ3" t="n">
         <v>-65</v>
       </c>
+      <c r="BR3" t="n">
+        <v>-67</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1530,6 +1540,9 @@
       <c r="BQ4" t="n">
         <v>-35</v>
       </c>
+      <c r="BR4" t="n">
+        <v>-70</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1743,6 +1756,9 @@
       <c r="BQ5" t="n">
         <v>-79</v>
       </c>
+      <c r="BR5" t="n">
+        <v>-62</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1956,6 +1972,9 @@
       <c r="BQ6" t="n">
         <v>52</v>
       </c>
+      <c r="BR6" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2169,6 +2188,9 @@
       <c r="BQ7" t="n">
         <v>-69</v>
       </c>
+      <c r="BR7" t="n">
+        <v>-44</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2382,6 +2404,9 @@
       <c r="BQ8" t="n">
         <v>-62</v>
       </c>
+      <c r="BR8" t="n">
+        <v>-37</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2595,6 +2620,9 @@
       <c r="BQ9" t="n">
         <v>65</v>
       </c>
+      <c r="BR9" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2807,6 +2835,9 @@
       </c>
       <c r="BQ10" t="n">
         <v>-74</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>-91</v>
       </c>
     </row>
   </sheetData>
@@ -2820,7 +2851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DE10"/>
+  <dimension ref="A1:DF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2932,6 +2963,7 @@
     <col width="12" customWidth="1" min="107" max="107"/>
     <col width="12" customWidth="1" min="108" max="108"/>
     <col width="12" customWidth="1" min="109" max="109"/>
+    <col width="12" customWidth="1" min="110" max="110"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3480,6 +3512,11 @@
           <t>20260302</t>
         </is>
       </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>20260303</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4764,6 +4801,9 @@
       <c r="DE5" t="n">
         <v>97</v>
       </c>
+      <c r="DF5" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5409,6 +5449,9 @@
       <c r="DE7" t="n">
         <v>96</v>
       </c>
+      <c r="DF7" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5741,6 +5784,9 @@
       </c>
       <c r="DE8" t="n">
         <v>100</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>108</v>
       </c>
     </row>
     <row r="9">
@@ -6393,7 +6439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CL10"/>
+  <dimension ref="A1:CM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6486,6 +6532,7 @@
     <col width="12" customWidth="1" min="88" max="88"/>
     <col width="12" customWidth="1" min="89" max="89"/>
     <col width="12" customWidth="1" min="90" max="90"/>
+    <col width="12" customWidth="1" min="91" max="91"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6939,6 +6986,11 @@
           <t>20260302</t>
         </is>
       </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>20260303</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7995,6 +8047,9 @@
       <c r="CL5" t="n">
         <v>-55.34</v>
       </c>
+      <c r="CM5" t="n">
+        <v>-63.72</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8526,6 +8581,9 @@
       <c r="CL7" t="n">
         <v>14.53</v>
       </c>
+      <c r="CM7" t="n">
+        <v>10.92</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8801,6 +8859,9 @@
       </c>
       <c r="CL8" t="n">
         <v>-44.69</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>-43.32</v>
       </c>
     </row>
     <row r="9">
@@ -9339,7 +9400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ10"/>
+  <dimension ref="A1:BR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9411,6 +9472,7 @@
     <col width="12" customWidth="1" min="67" max="67"/>
     <col width="12" customWidth="1" min="68" max="68"/>
     <col width="12" customWidth="1" min="69" max="69"/>
+    <col width="12" customWidth="1" min="70" max="70"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9759,6 +9821,11 @@
           <t>20260302</t>
         </is>
       </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>20260303</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10563,6 +10630,9 @@
       <c r="BQ5" t="n">
         <v>0</v>
       </c>
+      <c r="BR5" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10968,6 +11038,9 @@
       <c r="BQ7" t="n">
         <v>0</v>
       </c>
+      <c r="BR7" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11180,6 +11253,9 @@
       </c>
       <c r="BQ8" t="n">
         <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>118</v>
       </c>
     </row>
     <row r="9">
@@ -11592,7 +11668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CU10"/>
+  <dimension ref="A1:CV10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11694,6 +11770,7 @@
     <col width="10" customWidth="1" min="97" max="97"/>
     <col width="10" customWidth="1" min="98" max="98"/>
     <col width="10" customWidth="1" min="99" max="99"/>
+    <col width="10" customWidth="1" min="100" max="100"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11998,6 +12075,9 @@
       <c r="CU1" s="1" t="n">
         <v>20260302</v>
       </c>
+      <c r="CV1" s="1" t="n">
+        <v>20260303</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12301,6 +12381,9 @@
       <c r="CU2" t="n">
         <v>2</v>
       </c>
+      <c r="CV2" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12604,6 +12687,9 @@
       <c r="CU3" t="n">
         <v>-38</v>
       </c>
+      <c r="CV3" t="n">
+        <v>-40</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12907,6 +12993,9 @@
       <c r="CU4" t="n">
         <v>-46</v>
       </c>
+      <c r="CV4" t="n">
+        <v>-73</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13210,6 +13299,9 @@
       <c r="CU5" t="n">
         <v>-49</v>
       </c>
+      <c r="CV5" t="n">
+        <v>-27</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13513,6 +13605,9 @@
       <c r="CU6" t="n">
         <v>157</v>
       </c>
+      <c r="CV6" t="n">
+        <v>146</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13816,6 +13911,9 @@
       <c r="CU7" t="n">
         <v>-73</v>
       </c>
+      <c r="CV7" t="n">
+        <v>-47</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14119,6 +14217,9 @@
       <c r="CU8" t="n">
         <v>-28</v>
       </c>
+      <c r="CV8" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14422,6 +14523,9 @@
       <c r="CU9" t="n">
         <v>50</v>
       </c>
+      <c r="CV9" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14724,6 +14828,9 @@
       </c>
       <c r="CU10" t="n">
         <v>-67</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>-94</v>
       </c>
     </row>
   </sheetData>
@@ -14737,7 +14844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14749,6 +14856,7 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14783,6 +14891,9 @@
       <c r="I1" s="1" t="n">
         <v>20260302</v>
       </c>
+      <c r="J1" s="1" t="n">
+        <v>20260303</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14813,6 +14924,9 @@
       <c r="I2" t="n">
         <v>63</v>
       </c>
+      <c r="J2" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14843,6 +14957,9 @@
       <c r="I3" t="n">
         <v>20</v>
       </c>
+      <c r="J3" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14876,6 +14993,9 @@
       <c r="I4" t="n">
         <v>74</v>
       </c>
+      <c r="J4" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14909,6 +15029,9 @@
       <c r="I5" t="n">
         <v>5</v>
       </c>
+      <c r="J5" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14939,6 +15062,9 @@
       <c r="I6" t="n">
         <v>2</v>
       </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14972,6 +15098,9 @@
       <c r="I7" t="n">
         <v>19</v>
       </c>
+      <c r="J7" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15005,6 +15134,9 @@
       <c r="I8" t="n">
         <v>11</v>
       </c>
+      <c r="J8" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15035,6 +15167,9 @@
       <c r="I9" t="n">
         <v>93</v>
       </c>
+      <c r="J9" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15067,6 +15202,9 @@
       </c>
       <c r="I10" t="n">
         <v>39</v>
+      </c>
+      <c r="J10" t="n">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -15080,7 +15218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15092,6 +15230,7 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15126,6 +15265,9 @@
       <c r="I1" s="1" t="n">
         <v>20260302</v>
       </c>
+      <c r="J1" s="1" t="n">
+        <v>20260303</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15156,6 +15298,9 @@
       <c r="I2" t="n">
         <v>3</v>
       </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15186,6 +15331,9 @@
       <c r="I3" t="n">
         <v>-76</v>
       </c>
+      <c r="J3" t="n">
+        <v>-79</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15219,6 +15367,9 @@
       <c r="I4" t="n">
         <v>29</v>
       </c>
+      <c r="J4" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15252,6 +15403,9 @@
       <c r="I5" t="n">
         <v>-108</v>
       </c>
+      <c r="J5" t="n">
+        <v>-92</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15282,6 +15436,9 @@
       <c r="I6" t="n">
         <v>-42</v>
       </c>
+      <c r="J6" t="n">
+        <v>-41</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15315,6 +15472,9 @@
       <c r="I7" t="n">
         <v>-55</v>
       </c>
+      <c r="J7" t="n">
+        <v>-36</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15348,6 +15508,9 @@
       <c r="I8" t="n">
         <v>-92</v>
       </c>
+      <c r="J8" t="n">
+        <v>-64</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15378,6 +15541,9 @@
       <c r="I9" t="n">
         <v>97</v>
       </c>
+      <c r="J9" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15410,6 +15576,9 @@
       </c>
       <c r="I10" t="n">
         <v>-58</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-81</v>
       </c>
     </row>
   </sheetData>
@@ -15423,7 +15592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ10"/>
+  <dimension ref="A1:BR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -15495,6 +15664,7 @@
     <col width="12" customWidth="1" min="67" max="67"/>
     <col width="12" customWidth="1" min="68" max="68"/>
     <col width="12" customWidth="1" min="69" max="69"/>
+    <col width="12" customWidth="1" min="70" max="70"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15843,6 +16013,11 @@
           <t>20260302</t>
         </is>
       </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>20260303</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16647,6 +16822,9 @@
       <c r="BQ5" t="n">
         <v>87</v>
       </c>
+      <c r="BR5" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17052,6 +17230,9 @@
       <c r="BQ7" t="n">
         <v>96</v>
       </c>
+      <c r="BR7" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17264,6 +17445,9 @@
       </c>
       <c r="BQ8" t="n">
         <v>84</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="9">
@@ -17676,7 +17860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DX10"/>
+  <dimension ref="A1:DY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17807,6 +17991,7 @@
     <col width="12" customWidth="1" min="126" max="126"/>
     <col width="12" customWidth="1" min="127" max="127"/>
     <col width="12" customWidth="1" min="128" max="128"/>
+    <col width="12" customWidth="1" min="129" max="129"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18198,6 +18383,9 @@
       <c r="DX1" s="1" t="n">
         <v>20260302</v>
       </c>
+      <c r="DY1" s="1" t="n">
+        <v>20260303</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18585,6 +18773,9 @@
       <c r="DX2" t="n">
         <v>264.18</v>
       </c>
+      <c r="DY2" t="n">
+        <v>263.48</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18972,6 +19163,9 @@
       <c r="DX3" t="n">
         <v>210</v>
       </c>
+      <c r="DY3" t="n">
+        <v>203.1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19359,6 +19553,9 @@
       <c r="DX4" t="n">
         <v>311.76</v>
       </c>
+      <c r="DY4" t="n">
+        <v>298.59</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19749,6 +19946,9 @@
       <c r="DX5" t="n">
         <v>392.74</v>
       </c>
+      <c r="DY5" t="n">
+        <v>393.14</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20136,6 +20336,9 @@
       <c r="DX6" t="n">
         <v>96.23999999999999</v>
       </c>
+      <c r="DY6" t="n">
+        <v>96.01000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20526,6 +20729,9 @@
       <c r="DX7" t="n">
         <v>177.19</v>
       </c>
+      <c r="DY7" t="n">
+        <v>178.49</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20916,6 +21122,9 @@
       <c r="DX8" t="n">
         <v>137.19</v>
       </c>
+      <c r="DY8" t="n">
+        <v>142.1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21303,6 +21512,9 @@
       <c r="DX9" t="n">
         <v>98.02</v>
       </c>
+      <c r="DY9" t="n">
+        <v>94.92</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21689,6 +21901,9 @@
       </c>
       <c r="DX10" t="n">
         <v>402.51</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>395.09</v>
       </c>
     </row>
   </sheetData>
@@ -21702,7 +21917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DX10"/>
+  <dimension ref="A1:DY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21833,6 +22048,7 @@
     <col width="12" customWidth="1" min="126" max="126"/>
     <col width="12" customWidth="1" min="127" max="127"/>
     <col width="12" customWidth="1" min="128" max="128"/>
+    <col width="12" customWidth="1" min="129" max="129"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22224,6 +22440,9 @@
       <c r="DX1" s="1" t="n">
         <v>20260302</v>
       </c>
+      <c r="DY1" s="1" t="n">
+        <v>20260303</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22611,6 +22830,9 @@
       <c r="DX2" t="n">
         <v>264.18</v>
       </c>
+      <c r="DY2" t="n">
+        <v>265.56</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22998,6 +23220,9 @@
       <c r="DX3" t="n">
         <v>210</v>
       </c>
+      <c r="DY3" t="n">
+        <v>209.178</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23385,6 +23610,9 @@
       <c r="DX4" t="n">
         <v>311.76</v>
       </c>
+      <c r="DY4" t="n">
+        <v>303.94</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23775,6 +24003,9 @@
       <c r="DX5" t="n">
         <v>392.74</v>
       </c>
+      <c r="DY5" t="n">
+        <v>406.7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24162,6 +24393,9 @@
       <c r="DX6" t="n">
         <v>96.23999999999999</v>
       </c>
+      <c r="DY6" t="n">
+        <v>98.45999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24552,6 +24786,9 @@
       <c r="DX7" t="n">
         <v>177.19</v>
       </c>
+      <c r="DY7" t="n">
+        <v>180.9</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24942,6 +25179,9 @@
       <c r="DX8" t="n">
         <v>137.19</v>
       </c>
+      <c r="DY8" t="n">
+        <v>147.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25329,6 +25569,9 @@
       <c r="DX9" t="n">
         <v>98.02</v>
       </c>
+      <c r="DY9" t="n">
+        <v>97.09</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25715,6 +25958,9 @@
       </c>
       <c r="DX10" t="n">
         <v>402.51</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>396.34</v>
       </c>
     </row>
   </sheetData>
@@ -25728,7 +25974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DX10"/>
+  <dimension ref="A1:DY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25859,6 +26105,7 @@
     <col width="12" customWidth="1" min="126" max="126"/>
     <col width="12" customWidth="1" min="127" max="127"/>
     <col width="12" customWidth="1" min="128" max="128"/>
+    <col width="12" customWidth="1" min="129" max="129"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26250,6 +26497,9 @@
       <c r="DX1" s="1" t="n">
         <v>20260302</v>
       </c>
+      <c r="DY1" s="1" t="n">
+        <v>20260303</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -26637,6 +26887,9 @@
       <c r="DX2" t="n">
         <v>264.18</v>
       </c>
+      <c r="DY2" t="n">
+        <v>260.13</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -27024,6 +27277,9 @@
       <c r="DX3" t="n">
         <v>210</v>
       </c>
+      <c r="DY3" t="n">
+        <v>202.48</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -27411,6 +27667,9 @@
       <c r="DX4" t="n">
         <v>311.76</v>
       </c>
+      <c r="DY4" t="n">
+        <v>296.71</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -27801,6 +28060,9 @@
       <c r="DX5" t="n">
         <v>392.74</v>
       </c>
+      <c r="DY5" t="n">
+        <v>392.67</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -28188,6 +28450,9 @@
       <c r="DX6" t="n">
         <v>96.23999999999999</v>
       </c>
+      <c r="DY6" t="n">
+        <v>95.33</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -28578,6 +28843,9 @@
       <c r="DX7" t="n">
         <v>177.19</v>
       </c>
+      <c r="DY7" t="n">
+        <v>176.92</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -28968,6 +29236,9 @@
       <c r="DX8" t="n">
         <v>137.19</v>
       </c>
+      <c r="DY8" t="n">
+        <v>138.2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -29355,6 +29626,9 @@
       <c r="DX9" t="n">
         <v>98.02</v>
       </c>
+      <c r="DY9" t="n">
+        <v>94.40000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -29741,6 +30015,9 @@
       </c>
       <c r="DX10" t="n">
         <v>402.51</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>385.39</v>
       </c>
     </row>
   </sheetData>
@@ -29754,7 +30031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DX10"/>
+  <dimension ref="A1:DY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -29885,6 +30162,7 @@
     <col width="12" customWidth="1" min="126" max="126"/>
     <col width="12" customWidth="1" min="127" max="127"/>
     <col width="12" customWidth="1" min="128" max="128"/>
+    <col width="12" customWidth="1" min="129" max="129"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30276,6 +30554,9 @@
       <c r="DX1" s="1" t="n">
         <v>20260302</v>
       </c>
+      <c r="DY1" s="1" t="n">
+        <v>20260303</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -30663,6 +30944,9 @@
       <c r="DX2" t="n">
         <v>264.18</v>
       </c>
+      <c r="DY2" t="n">
+        <v>263.75</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -31050,6 +31334,9 @@
       <c r="DX3" t="n">
         <v>210</v>
       </c>
+      <c r="DY3" t="n">
+        <v>208.73</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -31437,6 +31724,9 @@
       <c r="DX4" t="n">
         <v>311.76</v>
       </c>
+      <c r="DY4" t="n">
+        <v>303.58</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -31827,6 +32117,9 @@
       <c r="DX5" t="n">
         <v>392.74</v>
       </c>
+      <c r="DY5" t="n">
+        <v>403.93</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -32214,6 +32507,9 @@
       <c r="DX6" t="n">
         <v>96.23999999999999</v>
       </c>
+      <c r="DY6" t="n">
+        <v>97.7</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -32604,6 +32900,9 @@
       <c r="DX7" t="n">
         <v>177.19</v>
       </c>
+      <c r="DY7" t="n">
+        <v>180.05</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -32994,6 +33293,9 @@
       <c r="DX8" t="n">
         <v>137.19</v>
       </c>
+      <c r="DY8" t="n">
+        <v>147.22</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -33381,6 +33683,9 @@
       <c r="DX9" t="n">
         <v>98.02</v>
       </c>
+      <c r="DY9" t="n">
+        <v>96.68000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -33767,6 +34072,9 @@
       </c>
       <c r="DX10" t="n">
         <v>402.51</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>392.43</v>
       </c>
     </row>
   </sheetData>
@@ -33780,7 +34088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DX10"/>
+  <dimension ref="A1:DY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -33911,6 +34219,7 @@
     <col width="12" customWidth="1" min="126" max="126"/>
     <col width="12" customWidth="1" min="127" max="127"/>
     <col width="12" customWidth="1" min="128" max="128"/>
+    <col width="12" customWidth="1" min="129" max="129"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -34302,6 +34611,9 @@
       <c r="DX1" s="1" t="n">
         <v>20260302</v>
       </c>
+      <c r="DY1" s="1" t="n">
+        <v>20260303</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -34689,6 +35001,9 @@
       <c r="DX2" t="n">
         <v>0</v>
       </c>
+      <c r="DY2" t="n">
+        <v>38568921</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -35076,6 +35391,9 @@
       <c r="DX3" t="n">
         <v>0</v>
       </c>
+      <c r="DY3" t="n">
+        <v>43184918</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -35463,6 +35781,9 @@
       <c r="DX4" t="n">
         <v>0</v>
       </c>
+      <c r="DY4" t="n">
+        <v>35496961</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -35853,6 +36174,9 @@
       <c r="DX5" t="n">
         <v>0</v>
       </c>
+      <c r="DY5" t="n">
+        <v>38199209</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -36240,6 +36564,9 @@
       <c r="DX6" t="n">
         <v>0</v>
       </c>
+      <c r="DY6" t="n">
+        <v>59149000</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -36630,6 +36957,9 @@
       <c r="DX7" t="n">
         <v>0</v>
       </c>
+      <c r="DY7" t="n">
+        <v>178099430</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -37020,6 +37350,9 @@
       <c r="DX8" t="n">
         <v>0</v>
       </c>
+      <c r="DY8" t="n">
+        <v>67460192</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -37407,6 +37740,9 @@
       <c r="DX9" t="n">
         <v>0</v>
       </c>
+      <c r="DY9" t="n">
+        <v>7197169</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -37793,6 +38129,9 @@
       </c>
       <c r="DX10" t="n">
         <v>0</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>62617298</v>
       </c>
     </row>
   </sheetData>
@@ -37806,7 +38145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DE10"/>
+  <dimension ref="A1:DF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -37918,6 +38257,7 @@
     <col width="10" customWidth="1" min="107" max="107"/>
     <col width="10" customWidth="1" min="108" max="108"/>
     <col width="10" customWidth="1" min="109" max="109"/>
+    <col width="10" customWidth="1" min="110" max="110"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -38252,6 +38592,9 @@
       <c r="DE1" s="1" t="n">
         <v>20260302</v>
       </c>
+      <c r="DF1" s="1" t="n">
+        <v>20260303</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -38585,6 +38928,9 @@
       <c r="DE2" t="n">
         <v>38</v>
       </c>
+      <c r="DF2" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -38918,6 +39264,9 @@
       <c r="DE3" t="n">
         <v>28</v>
       </c>
+      <c r="DF3" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -39251,6 +39600,9 @@
       <c r="DE4" t="n">
         <v>26</v>
       </c>
+      <c r="DF4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -39584,6 +39936,9 @@
       <c r="DE5" t="n">
         <v>18</v>
       </c>
+      <c r="DF5" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -39917,6 +40272,9 @@
       <c r="DE6" t="n">
         <v>100</v>
       </c>
+      <c r="DF6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -40250,6 +40608,9 @@
       <c r="DE7" t="n">
         <v>22</v>
       </c>
+      <c r="DF7" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -40583,6 +40944,9 @@
       <c r="DE8" t="n">
         <v>29</v>
       </c>
+      <c r="DF8" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -40916,6 +41280,9 @@
       <c r="DE9" t="n">
         <v>81</v>
       </c>
+      <c r="DF9" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -41248,6 +41615,9 @@
       </c>
       <c r="DE10" t="n">
         <v>16</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -41261,7 +41631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ10"/>
+  <dimension ref="A1:BR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -41333,6 +41703,7 @@
     <col width="10" customWidth="1" min="67" max="67"/>
     <col width="10" customWidth="1" min="68" max="68"/>
     <col width="10" customWidth="1" min="69" max="69"/>
+    <col width="10" customWidth="1" min="70" max="70"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -41547,6 +41918,9 @@
       <c r="BQ1" s="1" t="n">
         <v>20260302</v>
       </c>
+      <c r="BR1" s="1" t="n">
+        <v>20260303</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -41760,6 +42134,9 @@
       <c r="BQ2" t="n">
         <v>44</v>
       </c>
+      <c r="BR2" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -41973,6 +42350,9 @@
       <c r="BQ3" t="n">
         <v>23</v>
       </c>
+      <c r="BR3" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -42186,6 +42566,9 @@
       <c r="BQ4" t="n">
         <v>35</v>
       </c>
+      <c r="BR4" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -42399,6 +42782,9 @@
       <c r="BQ5" t="n">
         <v>8</v>
       </c>
+      <c r="BR5" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -42612,6 +42998,9 @@
       <c r="BQ6" t="n">
         <v>61</v>
       </c>
+      <c r="BR6" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -42825,6 +43214,9 @@
       <c r="BQ7" t="n">
         <v>25</v>
       </c>
+      <c r="BR7" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -43038,6 +43430,9 @@
       <c r="BQ8" t="n">
         <v>13</v>
       </c>
+      <c r="BR8" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -43251,6 +43646,9 @@
       <c r="BQ9" t="n">
         <v>92</v>
       </c>
+      <c r="BR9" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -43463,6 +43861,9 @@
       </c>
       <c r="BQ10" t="n">
         <v>6</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -43476,7 +43877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DE10"/>
+  <dimension ref="A1:DF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -43588,6 +43989,7 @@
     <col width="10" customWidth="1" min="107" max="107"/>
     <col width="10" customWidth="1" min="108" max="108"/>
     <col width="10" customWidth="1" min="109" max="109"/>
+    <col width="10" customWidth="1" min="110" max="110"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -43922,6 +44324,9 @@
       <c r="DE1" s="1" t="n">
         <v>20260302</v>
       </c>
+      <c r="DF1" s="1" t="n">
+        <v>20260303</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -44255,6 +44660,9 @@
       <c r="DE2" t="n">
         <v>-35</v>
       </c>
+      <c r="DF2" t="n">
+        <v>-41</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -44588,6 +44996,9 @@
       <c r="DE3" t="n">
         <v>-17</v>
       </c>
+      <c r="DF3" t="n">
+        <v>-17</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -44921,6 +45332,9 @@
       <c r="DE4" t="n">
         <v>-27</v>
       </c>
+      <c r="DF4" t="n">
+        <v>-54</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -45254,6 +45668,9 @@
       <c r="DE5" t="n">
         <v>-48</v>
       </c>
+      <c r="DF5" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -45587,6 +46004,9 @@
       <c r="DE6" t="n">
         <v>173</v>
       </c>
+      <c r="DF6" t="n">
+        <v>139</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -45920,6 +46340,9 @@
       <c r="DE7" t="n">
         <v>-61</v>
       </c>
+      <c r="DF7" t="n">
+        <v>-36</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -46253,6 +46676,9 @@
       <c r="DE8" t="n">
         <v>4</v>
       </c>
+      <c r="DF8" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -46586,6 +47012,9 @@
       <c r="DE9" t="n">
         <v>38</v>
       </c>
+      <c r="DF9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -46918,6 +47347,9 @@
       </c>
       <c r="DE10" t="n">
         <v>-60</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>-99</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -605,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR10"/>
+  <dimension ref="A1:BS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -678,6 +678,7 @@
     <col width="10" customWidth="1" min="68" max="68"/>
     <col width="10" customWidth="1" min="69" max="69"/>
     <col width="10" customWidth="1" min="70" max="70"/>
+    <col width="10" customWidth="1" min="71" max="71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -895,6 +896,9 @@
       <c r="BR1" s="1" t="n">
         <v>20260303</v>
       </c>
+      <c r="BS1" s="1" t="n">
+        <v>20260304</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1111,6 +1115,9 @@
       <c r="BR2" t="n">
         <v>-20</v>
       </c>
+      <c r="BS2" t="n">
+        <v>-21</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1327,6 +1334,9 @@
       <c r="BR3" t="n">
         <v>-67</v>
       </c>
+      <c r="BS3" t="n">
+        <v>-65</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1543,6 +1553,9 @@
       <c r="BR4" t="n">
         <v>-70</v>
       </c>
+      <c r="BS4" t="n">
+        <v>-67</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1759,6 +1772,9 @@
       <c r="BR5" t="n">
         <v>-62</v>
       </c>
+      <c r="BS5" t="n">
+        <v>-58</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1975,6 +1991,9 @@
       <c r="BR6" t="n">
         <v>67</v>
       </c>
+      <c r="BS6" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2191,6 +2210,9 @@
       <c r="BR7" t="n">
         <v>-44</v>
       </c>
+      <c r="BS7" t="n">
+        <v>-15</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2407,6 +2429,9 @@
       <c r="BR8" t="n">
         <v>-37</v>
       </c>
+      <c r="BS8" t="n">
+        <v>-33</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2623,6 +2648,9 @@
       <c r="BR9" t="n">
         <v>51</v>
       </c>
+      <c r="BS9" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2838,6 +2866,9 @@
       </c>
       <c r="BR10" t="n">
         <v>-91</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>-78</v>
       </c>
     </row>
   </sheetData>
@@ -2851,7 +2882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DF10"/>
+  <dimension ref="A1:DG10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2964,6 +2995,7 @@
     <col width="12" customWidth="1" min="108" max="108"/>
     <col width="12" customWidth="1" min="109" max="109"/>
     <col width="12" customWidth="1" min="110" max="110"/>
+    <col width="12" customWidth="1" min="111" max="111"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3517,6 +3549,11 @@
           <t>20260303</t>
         </is>
       </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>20260304</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4804,6 +4841,9 @@
       <c r="DF5" t="n">
         <v>101</v>
       </c>
+      <c r="DG5" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5452,6 +5492,9 @@
       <c r="DF7" t="n">
         <v>97</v>
       </c>
+      <c r="DG7" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5787,6 +5830,9 @@
       </c>
       <c r="DF8" t="n">
         <v>108</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>109</v>
       </c>
     </row>
     <row r="9">
@@ -6439,7 +6485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CM10"/>
+  <dimension ref="A1:CN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6533,6 +6579,7 @@
     <col width="12" customWidth="1" min="89" max="89"/>
     <col width="12" customWidth="1" min="90" max="90"/>
     <col width="12" customWidth="1" min="91" max="91"/>
+    <col width="12" customWidth="1" min="92" max="92"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6991,6 +7038,11 @@
           <t>20260303</t>
         </is>
       </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>20260304</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8050,6 +8102,9 @@
       <c r="CM5" t="n">
         <v>-63.72</v>
       </c>
+      <c r="CN5" t="n">
+        <v>-63.86</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8584,6 +8639,9 @@
       <c r="CM7" t="n">
         <v>10.92</v>
       </c>
+      <c r="CN7" t="n">
+        <v>7.13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8862,6 +8920,9 @@
       </c>
       <c r="CM8" t="n">
         <v>-43.32</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>-53.22</v>
       </c>
     </row>
     <row r="9">
@@ -9400,7 +9461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR10"/>
+  <dimension ref="A1:BS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9473,6 +9534,7 @@
     <col width="12" customWidth="1" min="68" max="68"/>
     <col width="12" customWidth="1" min="69" max="69"/>
     <col width="12" customWidth="1" min="70" max="70"/>
+    <col width="12" customWidth="1" min="71" max="71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9826,6 +9888,11 @@
           <t>20260303</t>
         </is>
       </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>20260304</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10633,6 +10700,9 @@
       <c r="BR5" t="n">
         <v>94</v>
       </c>
+      <c r="BS5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11041,6 +11111,9 @@
       <c r="BR7" t="n">
         <v>79</v>
       </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11256,6 +11329,9 @@
       </c>
       <c r="BR8" t="n">
         <v>118</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -11668,7 +11744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CV10"/>
+  <dimension ref="A1:CW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11771,6 +11847,7 @@
     <col width="10" customWidth="1" min="98" max="98"/>
     <col width="10" customWidth="1" min="99" max="99"/>
     <col width="10" customWidth="1" min="100" max="100"/>
+    <col width="10" customWidth="1" min="101" max="101"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12078,6 +12155,9 @@
       <c r="CV1" s="1" t="n">
         <v>20260303</v>
       </c>
+      <c r="CW1" s="1" t="n">
+        <v>20260304</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12384,6 +12464,9 @@
       <c r="CV2" t="n">
         <v>-1</v>
       </c>
+      <c r="CW2" t="n">
+        <v>-4</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12690,6 +12773,9 @@
       <c r="CV3" t="n">
         <v>-40</v>
       </c>
+      <c r="CW3" t="n">
+        <v>-37</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12996,6 +13082,9 @@
       <c r="CV4" t="n">
         <v>-73</v>
       </c>
+      <c r="CW4" t="n">
+        <v>-68</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13302,6 +13391,9 @@
       <c r="CV5" t="n">
         <v>-27</v>
       </c>
+      <c r="CW5" t="n">
+        <v>-23</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13608,6 +13700,9 @@
       <c r="CV6" t="n">
         <v>146</v>
       </c>
+      <c r="CW6" t="n">
+        <v>123</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13914,6 +14009,9 @@
       <c r="CV7" t="n">
         <v>-47</v>
       </c>
+      <c r="CW7" t="n">
+        <v>-23</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14220,6 +14318,9 @@
       <c r="CV8" t="n">
         <v>9</v>
       </c>
+      <c r="CW8" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14526,6 +14627,9 @@
       <c r="CV9" t="n">
         <v>16</v>
       </c>
+      <c r="CW9" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14831,6 +14935,9 @@
       </c>
       <c r="CV10" t="n">
         <v>-94</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>-71</v>
       </c>
     </row>
   </sheetData>
@@ -14844,7 +14951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14857,6 +14964,7 @@
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14894,6 +15002,9 @@
       <c r="J1" s="1" t="n">
         <v>20260303</v>
       </c>
+      <c r="K1" s="1" t="n">
+        <v>20260304</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14927,6 +15038,9 @@
       <c r="J2" t="n">
         <v>62</v>
       </c>
+      <c r="K2" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14960,6 +15074,9 @@
       <c r="J3" t="n">
         <v>18</v>
       </c>
+      <c r="K3" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14996,6 +15113,9 @@
       <c r="J4" t="n">
         <v>65</v>
       </c>
+      <c r="K4" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15032,6 +15152,9 @@
       <c r="J5" t="n">
         <v>12</v>
       </c>
+      <c r="K5" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15065,6 +15188,9 @@
       <c r="J6" t="n">
         <v>2</v>
       </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15101,6 +15227,9 @@
       <c r="J7" t="n">
         <v>27</v>
       </c>
+      <c r="K7" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15137,6 +15266,9 @@
       <c r="J8" t="n">
         <v>23</v>
       </c>
+      <c r="K8" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15170,6 +15302,9 @@
       <c r="J9" t="n">
         <v>87</v>
       </c>
+      <c r="K9" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15205,6 +15340,9 @@
       </c>
       <c r="J10" t="n">
         <v>32</v>
+      </c>
+      <c r="K10" t="n">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -15218,7 +15356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15231,6 +15369,7 @@
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15268,6 +15407,9 @@
       <c r="J1" s="1" t="n">
         <v>20260303</v>
       </c>
+      <c r="K1" s="1" t="n">
+        <v>20260304</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15301,6 +15443,9 @@
       <c r="J2" t="n">
         <v>1</v>
       </c>
+      <c r="K2" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15334,6 +15479,9 @@
       <c r="J3" t="n">
         <v>-79</v>
       </c>
+      <c r="K3" t="n">
+        <v>-78</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15370,6 +15518,9 @@
       <c r="J4" t="n">
         <v>16</v>
       </c>
+      <c r="K4" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15406,6 +15557,9 @@
       <c r="J5" t="n">
         <v>-92</v>
       </c>
+      <c r="K5" t="n">
+        <v>-88</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15439,6 +15593,9 @@
       <c r="J6" t="n">
         <v>-41</v>
       </c>
+      <c r="K6" t="n">
+        <v>-40</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15475,6 +15632,9 @@
       <c r="J7" t="n">
         <v>-36</v>
       </c>
+      <c r="K7" t="n">
+        <v>-14</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15511,6 +15671,9 @@
       <c r="J8" t="n">
         <v>-64</v>
       </c>
+      <c r="K8" t="n">
+        <v>-59</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15544,6 +15707,9 @@
       <c r="J9" t="n">
         <v>83</v>
       </c>
+      <c r="K9" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15579,6 +15745,9 @@
       </c>
       <c r="J10" t="n">
         <v>-81</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-75</v>
       </c>
     </row>
   </sheetData>
@@ -15592,7 +15761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR10"/>
+  <dimension ref="A1:BS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -15665,6 +15834,7 @@
     <col width="12" customWidth="1" min="68" max="68"/>
     <col width="12" customWidth="1" min="69" max="69"/>
     <col width="12" customWidth="1" min="70" max="70"/>
+    <col width="12" customWidth="1" min="71" max="71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16018,6 +16188,11 @@
           <t>20260303</t>
         </is>
       </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>20260304</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16825,6 +17000,9 @@
       <c r="BR5" t="n">
         <v>90</v>
       </c>
+      <c r="BS5" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17233,6 +17411,9 @@
       <c r="BR7" t="n">
         <v>97</v>
       </c>
+      <c r="BS7" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17448,6 +17629,9 @@
       </c>
       <c r="BR8" t="n">
         <v>90</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>91</v>
       </c>
     </row>
     <row r="9">
@@ -17860,7 +18044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DY10"/>
+  <dimension ref="A1:DZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17992,6 +18176,7 @@
     <col width="12" customWidth="1" min="127" max="127"/>
     <col width="12" customWidth="1" min="128" max="128"/>
     <col width="12" customWidth="1" min="129" max="129"/>
+    <col width="12" customWidth="1" min="130" max="130"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18386,6 +18571,9 @@
       <c r="DY1" s="1" t="n">
         <v>20260303</v>
       </c>
+      <c r="DZ1" s="1" t="n">
+        <v>20260304</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18776,6 +18964,9 @@
       <c r="DY2" t="n">
         <v>263.48</v>
       </c>
+      <c r="DZ2" t="n">
+        <v>262.94</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19166,6 +19357,9 @@
       <c r="DY3" t="n">
         <v>203.1</v>
       </c>
+      <c r="DZ3" t="n">
+        <v>207.29</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19556,6 +19750,9 @@
       <c r="DY4" t="n">
         <v>298.59</v>
       </c>
+      <c r="DZ4" t="n">
+        <v>301.45</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19949,6 +20146,9 @@
       <c r="DY5" t="n">
         <v>393.14</v>
       </c>
+      <c r="DZ5" t="n">
+        <v>402.44</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20339,6 +20539,9 @@
       <c r="DY6" t="n">
         <v>96.01000000000001</v>
       </c>
+      <c r="DZ6" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20732,6 +20935,9 @@
       <c r="DY7" t="n">
         <v>178.49</v>
       </c>
+      <c r="DZ7" t="n">
+        <v>179.64</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21125,6 +21331,9 @@
       <c r="DY8" t="n">
         <v>142.1</v>
       </c>
+      <c r="DZ8" t="n">
+        <v>146.02</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21515,6 +21724,9 @@
       <c r="DY9" t="n">
         <v>94.92</v>
       </c>
+      <c r="DZ9" t="n">
+        <v>95.89</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21904,6 +22116,9 @@
       </c>
       <c r="DY10" t="n">
         <v>395.09</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>390.79</v>
       </c>
     </row>
   </sheetData>
@@ -21917,7 +22132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DY10"/>
+  <dimension ref="A1:DZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22049,6 +22264,7 @@
     <col width="12" customWidth="1" min="127" max="127"/>
     <col width="12" customWidth="1" min="128" max="128"/>
     <col width="12" customWidth="1" min="129" max="129"/>
+    <col width="12" customWidth="1" min="130" max="130"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22443,6 +22659,9 @@
       <c r="DY1" s="1" t="n">
         <v>20260303</v>
       </c>
+      <c r="DZ1" s="1" t="n">
+        <v>20260304</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22833,6 +23052,9 @@
       <c r="DY2" t="n">
         <v>265.56</v>
       </c>
+      <c r="DZ2" t="n">
+        <v>263.94</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23223,6 +23445,9 @@
       <c r="DY3" t="n">
         <v>209.178</v>
       </c>
+      <c r="DZ3" t="n">
+        <v>209.14</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23613,6 +23838,9 @@
       <c r="DY4" t="n">
         <v>303.94</v>
       </c>
+      <c r="DZ4" t="n">
+        <v>304.36</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24006,6 +24234,9 @@
       <c r="DY5" t="n">
         <v>406.7</v>
       </c>
+      <c r="DZ5" t="n">
+        <v>405.5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24396,6 +24627,9 @@
       <c r="DY6" t="n">
         <v>98.45999999999999</v>
       </c>
+      <c r="DZ6" t="n">
+        <v>97.61</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24789,6 +25023,9 @@
       <c r="DY7" t="n">
         <v>180.9</v>
       </c>
+      <c r="DZ7" t="n">
+        <v>183.24</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25182,6 +25419,9 @@
       <c r="DY8" t="n">
         <v>147.5</v>
       </c>
+      <c r="DZ8" t="n">
+        <v>148.71</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25572,6 +25812,9 @@
       <c r="DY9" t="n">
         <v>97.09</v>
       </c>
+      <c r="DZ9" t="n">
+        <v>96.42</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25961,6 +26204,9 @@
       </c>
       <c r="DY10" t="n">
         <v>396.34</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>398.4</v>
       </c>
     </row>
   </sheetData>
@@ -25974,7 +26220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DY10"/>
+  <dimension ref="A1:DZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -26106,6 +26352,7 @@
     <col width="12" customWidth="1" min="127" max="127"/>
     <col width="12" customWidth="1" min="128" max="128"/>
     <col width="12" customWidth="1" min="129" max="129"/>
+    <col width="12" customWidth="1" min="130" max="130"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26500,6 +26747,9 @@
       <c r="DY1" s="1" t="n">
         <v>20260303</v>
       </c>
+      <c r="DZ1" s="1" t="n">
+        <v>20260304</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -26890,6 +27140,9 @@
       <c r="DY2" t="n">
         <v>260.13</v>
       </c>
+      <c r="DZ2" t="n">
+        <v>262.61</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -27280,6 +27533,9 @@
       <c r="DY3" t="n">
         <v>202.48</v>
       </c>
+      <c r="DZ3" t="n">
+        <v>206.6</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -27670,6 +27926,9 @@
       <c r="DY4" t="n">
         <v>296.71</v>
       </c>
+      <c r="DZ4" t="n">
+        <v>300.33</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -28063,6 +28322,9 @@
       <c r="DY5" t="n">
         <v>392.67</v>
       </c>
+      <c r="DZ5" t="n">
+        <v>401.61</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -28453,6 +28715,9 @@
       <c r="DY6" t="n">
         <v>95.33</v>
       </c>
+      <c r="DZ6" t="n">
+        <v>96.98</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -28846,6 +29111,9 @@
       <c r="DY7" t="n">
         <v>176.92</v>
       </c>
+      <c r="DZ7" t="n">
+        <v>179.14</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -29239,6 +29507,9 @@
       <c r="DY8" t="n">
         <v>138.2</v>
       </c>
+      <c r="DZ8" t="n">
+        <v>145.9</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -29629,6 +29900,9 @@
       <c r="DY9" t="n">
         <v>94.40000000000001</v>
       </c>
+      <c r="DZ9" t="n">
+        <v>95.77</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -30018,6 +30292,9 @@
       </c>
       <c r="DY10" t="n">
         <v>385.39</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>389.54</v>
       </c>
     </row>
   </sheetData>
@@ -30031,7 +30308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DY10"/>
+  <dimension ref="A1:DZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -30163,6 +30440,7 @@
     <col width="12" customWidth="1" min="127" max="127"/>
     <col width="12" customWidth="1" min="128" max="128"/>
     <col width="12" customWidth="1" min="129" max="129"/>
+    <col width="12" customWidth="1" min="130" max="130"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30557,6 +30835,9 @@
       <c r="DY1" s="1" t="n">
         <v>20260303</v>
       </c>
+      <c r="DZ1" s="1" t="n">
+        <v>20260304</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -30947,6 +31228,9 @@
       <c r="DY2" t="n">
         <v>263.75</v>
       </c>
+      <c r="DZ2" t="n">
+        <v>263.39</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -31337,6 +31621,9 @@
       <c r="DY3" t="n">
         <v>208.73</v>
       </c>
+      <c r="DZ3" t="n">
+        <v>208.59</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -31727,6 +32014,9 @@
       <c r="DY4" t="n">
         <v>303.58</v>
       </c>
+      <c r="DZ4" t="n">
+        <v>303.58</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -32120,6 +32410,9 @@
       <c r="DY5" t="n">
         <v>403.93</v>
       </c>
+      <c r="DZ5" t="n">
+        <v>404.9</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -32510,6 +32803,9 @@
       <c r="DY6" t="n">
         <v>97.7</v>
       </c>
+      <c r="DZ6" t="n">
+        <v>97.06999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -32903,6 +33199,9 @@
       <c r="DY7" t="n">
         <v>180.05</v>
       </c>
+      <c r="DZ7" t="n">
+        <v>183.22</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -33296,6 +33595,9 @@
       <c r="DY8" t="n">
         <v>147.22</v>
       </c>
+      <c r="DZ8" t="n">
+        <v>148.71</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -33686,6 +33988,9 @@
       <c r="DY9" t="n">
         <v>96.68000000000001</v>
       </c>
+      <c r="DZ9" t="n">
+        <v>96.2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -34075,6 +34380,9 @@
       </c>
       <c r="DY10" t="n">
         <v>392.43</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>397.46</v>
       </c>
     </row>
   </sheetData>
@@ -34088,7 +34396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DY10"/>
+  <dimension ref="A1:DZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -34220,6 +34528,7 @@
     <col width="12" customWidth="1" min="127" max="127"/>
     <col width="12" customWidth="1" min="128" max="128"/>
     <col width="12" customWidth="1" min="129" max="129"/>
+    <col width="12" customWidth="1" min="130" max="130"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -34614,6 +34923,9 @@
       <c r="DY1" s="1" t="n">
         <v>20260303</v>
       </c>
+      <c r="DZ1" s="1" t="n">
+        <v>20260304</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -35004,6 +35316,9 @@
       <c r="DY2" t="n">
         <v>38568921</v>
       </c>
+      <c r="DZ2" t="n">
+        <v>14765</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -35394,6 +35709,9 @@
       <c r="DY3" t="n">
         <v>43184918</v>
       </c>
+      <c r="DZ3" t="n">
+        <v>34200</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -35784,6 +36102,9 @@
       <c r="DY4" t="n">
         <v>35496961</v>
       </c>
+      <c r="DZ4" t="n">
+        <v>33851</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -36177,6 +36498,9 @@
       <c r="DY5" t="n">
         <v>38199209</v>
       </c>
+      <c r="DZ5" t="n">
+        <v>34498</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -36567,6 +36891,9 @@
       <c r="DY6" t="n">
         <v>59149000</v>
       </c>
+      <c r="DZ6" t="n">
+        <v>23319</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -36960,6 +37287,9 @@
       <c r="DY7" t="n">
         <v>178099430</v>
       </c>
+      <c r="DZ7" t="n">
+        <v>304086</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -37353,6 +37683,9 @@
       <c r="DY8" t="n">
         <v>67460192</v>
       </c>
+      <c r="DZ8" t="n">
+        <v>51082</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -37743,6 +38076,9 @@
       <c r="DY9" t="n">
         <v>7197169</v>
       </c>
+      <c r="DZ9" t="n">
+        <v>773</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -38132,6 +38468,9 @@
       </c>
       <c r="DY10" t="n">
         <v>62617298</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>118307</v>
       </c>
     </row>
   </sheetData>
@@ -38145,7 +38484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DF10"/>
+  <dimension ref="A1:DG10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -38258,6 +38597,7 @@
     <col width="10" customWidth="1" min="108" max="108"/>
     <col width="10" customWidth="1" min="109" max="109"/>
     <col width="10" customWidth="1" min="110" max="110"/>
+    <col width="10" customWidth="1" min="111" max="111"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -38595,6 +38935,9 @@
       <c r="DF1" s="1" t="n">
         <v>20260303</v>
       </c>
+      <c r="DG1" s="1" t="n">
+        <v>20260304</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -38931,6 +39274,9 @@
       <c r="DF2" t="n">
         <v>36</v>
       </c>
+      <c r="DG2" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -39267,6 +39613,9 @@
       <c r="DF3" t="n">
         <v>25</v>
       </c>
+      <c r="DG3" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -39603,6 +39952,9 @@
       <c r="DF4" t="n">
         <v>4</v>
       </c>
+      <c r="DG4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -39939,6 +40291,9 @@
       <c r="DF5" t="n">
         <v>65</v>
       </c>
+      <c r="DG5" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -40275,6 +40630,9 @@
       <c r="DF6" t="n">
         <v>100</v>
       </c>
+      <c r="DG6" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -40611,6 +40969,9 @@
       <c r="DF7" t="n">
         <v>35</v>
       </c>
+      <c r="DG7" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -40947,6 +41308,9 @@
       <c r="DF8" t="n">
         <v>63</v>
       </c>
+      <c r="DG8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -41283,6 +41647,9 @@
       <c r="DF9" t="n">
         <v>63</v>
       </c>
+      <c r="DG9" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -41618,6 +41985,9 @@
       </c>
       <c r="DF10" t="n">
         <v>0</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -41631,7 +42001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR10"/>
+  <dimension ref="A1:BS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -41704,6 +42074,7 @@
     <col width="10" customWidth="1" min="68" max="68"/>
     <col width="10" customWidth="1" min="69" max="69"/>
     <col width="10" customWidth="1" min="70" max="70"/>
+    <col width="10" customWidth="1" min="71" max="71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -41921,6 +42292,9 @@
       <c r="BR1" s="1" t="n">
         <v>20260303</v>
       </c>
+      <c r="BS1" s="1" t="n">
+        <v>20260304</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -42137,6 +42511,9 @@
       <c r="BR2" t="n">
         <v>46</v>
       </c>
+      <c r="BS2" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -42353,6 +42730,9 @@
       <c r="BR3" t="n">
         <v>20</v>
       </c>
+      <c r="BS3" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -42569,6 +42949,9 @@
       <c r="BR4" t="n">
         <v>16</v>
       </c>
+      <c r="BS4" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -42785,6 +43168,9 @@
       <c r="BR5" t="n">
         <v>18</v>
       </c>
+      <c r="BS5" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -43001,6 +43387,9 @@
       <c r="BR6" t="n">
         <v>78</v>
       </c>
+      <c r="BS6" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -43217,6 +43606,9 @@
       <c r="BR7" t="n">
         <v>37</v>
       </c>
+      <c r="BS7" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -43433,6 +43825,9 @@
       <c r="BR8" t="n">
         <v>28</v>
       </c>
+      <c r="BS8" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -43649,6 +44044,9 @@
       <c r="BR9" t="n">
         <v>84</v>
       </c>
+      <c r="BS9" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -43864,6 +44262,9 @@
       </c>
       <c r="BR10" t="n">
         <v>0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -43877,7 +44278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DF10"/>
+  <dimension ref="A1:DG10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -43990,6 +44391,7 @@
     <col width="10" customWidth="1" min="108" max="108"/>
     <col width="10" customWidth="1" min="109" max="109"/>
     <col width="10" customWidth="1" min="110" max="110"/>
+    <col width="10" customWidth="1" min="111" max="111"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -44327,6 +44729,9 @@
       <c r="DF1" s="1" t="n">
         <v>20260303</v>
       </c>
+      <c r="DG1" s="1" t="n">
+        <v>20260304</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -44663,6 +45068,9 @@
       <c r="DF2" t="n">
         <v>-41</v>
       </c>
+      <c r="DG2" t="n">
+        <v>-47</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -44999,6 +45407,9 @@
       <c r="DF3" t="n">
         <v>-17</v>
       </c>
+      <c r="DG3" t="n">
+        <v>-13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -45335,6 +45746,9 @@
       <c r="DF4" t="n">
         <v>-54</v>
       </c>
+      <c r="DG4" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -45671,6 +46085,9 @@
       <c r="DF5" t="n">
         <v>13</v>
       </c>
+      <c r="DG5" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -46007,6 +46424,9 @@
       <c r="DF6" t="n">
         <v>139</v>
       </c>
+      <c r="DG6" t="n">
+        <v>109</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -46343,6 +46763,9 @@
       <c r="DF7" t="n">
         <v>-36</v>
       </c>
+      <c r="DG7" t="n">
+        <v>-14</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -46679,6 +47102,9 @@
       <c r="DF8" t="n">
         <v>77</v>
       </c>
+      <c r="DG8" t="n">
+        <v>114</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -47015,6 +47441,9 @@
       <c r="DF9" t="n">
         <v>3</v>
       </c>
+      <c r="DG9" t="n">
+        <v>-17</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -47350,6 +47779,9 @@
       </c>
       <c r="DF10" t="n">
         <v>-99</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>-69</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -605,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS10"/>
+  <dimension ref="A1:BT10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -679,6 +679,7 @@
     <col width="10" customWidth="1" min="69" max="69"/>
     <col width="10" customWidth="1" min="70" max="70"/>
     <col width="10" customWidth="1" min="71" max="71"/>
+    <col width="10" customWidth="1" min="72" max="72"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -899,6 +900,9 @@
       <c r="BS1" s="1" t="n">
         <v>20260304</v>
       </c>
+      <c r="BT1" s="1" t="n">
+        <v>20260305</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1118,6 +1122,9 @@
       <c r="BS2" t="n">
         <v>-21</v>
       </c>
+      <c r="BT2" t="n">
+        <v>-22</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1337,6 +1344,9 @@
       <c r="BS3" t="n">
         <v>-65</v>
       </c>
+      <c r="BT3" t="n">
+        <v>-35</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1556,6 +1566,9 @@
       <c r="BS4" t="n">
         <v>-67</v>
       </c>
+      <c r="BT4" t="n">
+        <v>-66</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1775,6 +1788,9 @@
       <c r="BS5" t="n">
         <v>-58</v>
       </c>
+      <c r="BT5" t="n">
+        <v>-55</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1994,6 +2010,9 @@
       <c r="BS6" t="n">
         <v>65</v>
       </c>
+      <c r="BT6" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2213,6 +2232,9 @@
       <c r="BS7" t="n">
         <v>-15</v>
       </c>
+      <c r="BT7" t="n">
+        <v>-16</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2432,6 +2454,9 @@
       <c r="BS8" t="n">
         <v>-33</v>
       </c>
+      <c r="BT8" t="n">
+        <v>-20</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2651,6 +2676,9 @@
       <c r="BS9" t="n">
         <v>45</v>
       </c>
+      <c r="BT9" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2869,6 +2897,9 @@
       </c>
       <c r="BS10" t="n">
         <v>-78</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>-58</v>
       </c>
     </row>
   </sheetData>
@@ -2882,7 +2913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DG10"/>
+  <dimension ref="A1:DH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2996,6 +3027,7 @@
     <col width="12" customWidth="1" min="109" max="109"/>
     <col width="12" customWidth="1" min="110" max="110"/>
     <col width="12" customWidth="1" min="111" max="111"/>
+    <col width="12" customWidth="1" min="112" max="112"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3554,6 +3586,11 @@
           <t>20260304</t>
         </is>
       </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>20260305</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4844,6 +4881,9 @@
       <c r="DG5" t="n">
         <v>101</v>
       </c>
+      <c r="DH5" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5495,6 +5535,9 @@
       <c r="DG7" t="n">
         <v>99</v>
       </c>
+      <c r="DH7" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5833,6 +5876,9 @@
       </c>
       <c r="DG8" t="n">
         <v>109</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>112</v>
       </c>
     </row>
     <row r="9">
@@ -6485,7 +6531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CN10"/>
+  <dimension ref="A1:CO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6580,6 +6626,7 @@
     <col width="12" customWidth="1" min="90" max="90"/>
     <col width="12" customWidth="1" min="91" max="91"/>
     <col width="12" customWidth="1" min="92" max="92"/>
+    <col width="12" customWidth="1" min="93" max="93"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7043,6 +7090,11 @@
           <t>20260304</t>
         </is>
       </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>20260305</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8105,6 +8157,9 @@
       <c r="CN5" t="n">
         <v>-63.86</v>
       </c>
+      <c r="CO5" t="n">
+        <v>-64.86</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8642,6 +8697,9 @@
       <c r="CN7" t="n">
         <v>7.13</v>
       </c>
+      <c r="CO7" t="n">
+        <v>-2.03</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8923,6 +8981,9 @@
       </c>
       <c r="CN8" t="n">
         <v>-53.22</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>-41.02</v>
       </c>
     </row>
     <row r="9">
@@ -9461,7 +9522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS10"/>
+  <dimension ref="A1:BT10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9535,6 +9596,7 @@
     <col width="12" customWidth="1" min="69" max="69"/>
     <col width="12" customWidth="1" min="70" max="70"/>
     <col width="12" customWidth="1" min="71" max="71"/>
+    <col width="12" customWidth="1" min="72" max="72"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9893,6 +9955,11 @@
           <t>20260304</t>
         </is>
       </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>20260305</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10703,6 +10770,9 @@
       <c r="BS5" t="n">
         <v>0</v>
       </c>
+      <c r="BT5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11114,6 +11184,9 @@
       <c r="BS7" t="n">
         <v>0</v>
       </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11331,6 +11404,9 @@
         <v>118</v>
       </c>
       <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11744,7 +11820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW10"/>
+  <dimension ref="A1:CX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11848,6 +11924,7 @@
     <col width="10" customWidth="1" min="99" max="99"/>
     <col width="10" customWidth="1" min="100" max="100"/>
     <col width="10" customWidth="1" min="101" max="101"/>
+    <col width="10" customWidth="1" min="102" max="102"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12158,6 +12235,9 @@
       <c r="CW1" s="1" t="n">
         <v>20260304</v>
       </c>
+      <c r="CX1" s="1" t="n">
+        <v>20260305</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12467,6 +12547,9 @@
       <c r="CW2" t="n">
         <v>-4</v>
       </c>
+      <c r="CX2" t="n">
+        <v>-10</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12776,6 +12859,9 @@
       <c r="CW3" t="n">
         <v>-37</v>
       </c>
+      <c r="CX3" t="n">
+        <v>-11</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13085,6 +13171,9 @@
       <c r="CW4" t="n">
         <v>-68</v>
       </c>
+      <c r="CX4" t="n">
+        <v>-64</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13394,6 +13483,9 @@
       <c r="CW5" t="n">
         <v>-23</v>
       </c>
+      <c r="CX5" t="n">
+        <v>-19</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13703,6 +13795,9 @@
       <c r="CW6" t="n">
         <v>123</v>
       </c>
+      <c r="CX6" t="n">
+        <v>119</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14012,6 +14107,9 @@
       <c r="CW7" t="n">
         <v>-23</v>
       </c>
+      <c r="CX7" t="n">
+        <v>-23</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14321,6 +14419,9 @@
       <c r="CW8" t="n">
         <v>18</v>
       </c>
+      <c r="CX8" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14630,6 +14731,9 @@
       <c r="CW9" t="n">
         <v>2</v>
       </c>
+      <c r="CX9" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14938,6 +15042,9 @@
       </c>
       <c r="CW10" t="n">
         <v>-71</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>-38</v>
       </c>
     </row>
   </sheetData>
@@ -14951,7 +15058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14965,6 +15072,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15005,6 +15113,9 @@
       <c r="K1" s="1" t="n">
         <v>20260304</v>
       </c>
+      <c r="L1" s="1" t="n">
+        <v>20260305</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15041,6 +15152,9 @@
       <c r="K2" t="n">
         <v>62</v>
       </c>
+      <c r="L2" t="n">
+        <v>59</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15077,6 +15191,9 @@
       <c r="K3" t="n">
         <v>18</v>
       </c>
+      <c r="L3" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15116,6 +15233,9 @@
       <c r="K4" t="n">
         <v>65</v>
       </c>
+      <c r="L4" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15155,6 +15275,9 @@
       <c r="K5" t="n">
         <v>13</v>
       </c>
+      <c r="L5" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15191,6 +15314,9 @@
       <c r="K6" t="n">
         <v>2</v>
       </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15230,6 +15356,9 @@
       <c r="K7" t="n">
         <v>35</v>
       </c>
+      <c r="L7" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15269,6 +15398,9 @@
       <c r="K8" t="n">
         <v>25</v>
       </c>
+      <c r="L8" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15305,6 +15437,9 @@
       <c r="K9" t="n">
         <v>85</v>
       </c>
+      <c r="L9" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15343,6 +15478,9 @@
       </c>
       <c r="K10" t="n">
         <v>35</v>
+      </c>
+      <c r="L10" t="n">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -15356,7 +15494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15370,6 +15508,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15410,6 +15549,9 @@
       <c r="K1" s="1" t="n">
         <v>20260304</v>
       </c>
+      <c r="L1" s="1" t="n">
+        <v>20260305</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15446,6 +15588,9 @@
       <c r="K2" t="n">
         <v>-2</v>
       </c>
+      <c r="L2" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15482,6 +15627,9 @@
       <c r="K3" t="n">
         <v>-78</v>
       </c>
+      <c r="L3" t="n">
+        <v>-44</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15521,6 +15669,9 @@
       <c r="K4" t="n">
         <v>16</v>
       </c>
+      <c r="L4" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15560,6 +15711,9 @@
       <c r="K5" t="n">
         <v>-88</v>
       </c>
+      <c r="L5" t="n">
+        <v>-85</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15596,6 +15750,9 @@
       <c r="K6" t="n">
         <v>-40</v>
       </c>
+      <c r="L6" t="n">
+        <v>-39</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15635,6 +15792,9 @@
       <c r="K7" t="n">
         <v>-14</v>
       </c>
+      <c r="L7" t="n">
+        <v>-14</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15674,6 +15834,9 @@
       <c r="K8" t="n">
         <v>-59</v>
       </c>
+      <c r="L8" t="n">
+        <v>-45</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15710,6 +15873,9 @@
       <c r="K9" t="n">
         <v>77</v>
       </c>
+      <c r="L9" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15748,6 +15914,9 @@
       </c>
       <c r="K10" t="n">
         <v>-75</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-60</v>
       </c>
     </row>
   </sheetData>
@@ -15761,7 +15930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS10"/>
+  <dimension ref="A1:BT10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -15835,6 +16004,7 @@
     <col width="12" customWidth="1" min="69" max="69"/>
     <col width="12" customWidth="1" min="70" max="70"/>
     <col width="12" customWidth="1" min="71" max="71"/>
+    <col width="12" customWidth="1" min="72" max="72"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16193,6 +16363,11 @@
           <t>20260304</t>
         </is>
       </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>20260305</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17003,6 +17178,9 @@
       <c r="BS5" t="n">
         <v>90</v>
       </c>
+      <c r="BT5" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17414,6 +17592,9 @@
       <c r="BS7" t="n">
         <v>99</v>
       </c>
+      <c r="BT7" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17632,6 +17813,9 @@
       </c>
       <c r="BS8" t="n">
         <v>91</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>95</v>
       </c>
     </row>
     <row r="9">
@@ -18044,7 +18228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DZ10"/>
+  <dimension ref="A1:EA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18177,6 +18361,7 @@
     <col width="12" customWidth="1" min="128" max="128"/>
     <col width="12" customWidth="1" min="129" max="129"/>
     <col width="12" customWidth="1" min="130" max="130"/>
+    <col width="12" customWidth="1" min="131" max="131"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18574,6 +18759,9 @@
       <c r="DZ1" s="1" t="n">
         <v>20260304</v>
       </c>
+      <c r="EA1" s="1" t="n">
+        <v>20260305</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18967,6 +19155,9 @@
       <c r="DZ2" t="n">
         <v>262.94</v>
       </c>
+      <c r="EA2" t="n">
+        <v>262.28</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19360,6 +19551,9 @@
       <c r="DZ3" t="n">
         <v>207.29</v>
       </c>
+      <c r="EA3" t="n">
+        <v>215.85</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19753,6 +19947,9 @@
       <c r="DZ4" t="n">
         <v>301.45</v>
       </c>
+      <c r="EA4" t="n">
+        <v>302.29</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20149,6 +20346,9 @@
       <c r="DZ5" t="n">
         <v>402.44</v>
       </c>
+      <c r="EA5" t="n">
+        <v>404.93</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20542,6 +20742,9 @@
       <c r="DZ6" t="n">
         <v>97</v>
       </c>
+      <c r="EA6" t="n">
+        <v>98.06999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20938,6 +21141,9 @@
       <c r="DZ7" t="n">
         <v>179.64</v>
       </c>
+      <c r="EA7" t="n">
+        <v>182.2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21334,6 +21540,9 @@
       <c r="DZ8" t="n">
         <v>146.02</v>
       </c>
+      <c r="EA8" t="n">
+        <v>152.29</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21727,6 +21936,9 @@
       <c r="DZ9" t="n">
         <v>95.89</v>
       </c>
+      <c r="EA9" t="n">
+        <v>96.63</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22119,6 +22331,9 @@
       </c>
       <c r="DZ10" t="n">
         <v>390.79</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>405.03</v>
       </c>
     </row>
   </sheetData>
@@ -22132,7 +22347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DZ10"/>
+  <dimension ref="A1:EA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22265,6 +22480,7 @@
     <col width="12" customWidth="1" min="128" max="128"/>
     <col width="12" customWidth="1" min="129" max="129"/>
     <col width="12" customWidth="1" min="130" max="130"/>
+    <col width="12" customWidth="1" min="131" max="131"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22662,6 +22878,9 @@
       <c r="DZ1" s="1" t="n">
         <v>20260304</v>
       </c>
+      <c r="EA1" s="1" t="n">
+        <v>20260305</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23055,6 +23274,9 @@
       <c r="DZ2" t="n">
         <v>263.94</v>
       </c>
+      <c r="EA2" t="n">
+        <v>262.95</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23448,6 +23670,9 @@
       <c r="DZ3" t="n">
         <v>209.14</v>
       </c>
+      <c r="EA3" t="n">
+        <v>217.24</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23841,6 +24066,9 @@
       <c r="DZ4" t="n">
         <v>304.36</v>
       </c>
+      <c r="EA4" t="n">
+        <v>303.9</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24237,6 +24465,9 @@
       <c r="DZ5" t="n">
         <v>405.5</v>
       </c>
+      <c r="EA5" t="n">
+        <v>406.96</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24630,6 +24861,9 @@
       <c r="DZ6" t="n">
         <v>97.61</v>
       </c>
+      <c r="EA6" t="n">
+        <v>98.59999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -25026,6 +25260,9 @@
       <c r="DZ7" t="n">
         <v>183.24</v>
       </c>
+      <c r="EA7" t="n">
+        <v>183.41</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25422,6 +25659,9 @@
       <c r="DZ8" t="n">
         <v>148.71</v>
       </c>
+      <c r="EA8" t="n">
+        <v>154.44</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25815,6 +26055,9 @@
       <c r="DZ9" t="n">
         <v>96.42</v>
       </c>
+      <c r="EA9" t="n">
+        <v>96.81999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26207,6 +26450,9 @@
       </c>
       <c r="DZ10" t="n">
         <v>398.4</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>407</v>
       </c>
     </row>
   </sheetData>
@@ -26220,7 +26466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DZ10"/>
+  <dimension ref="A1:EA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -26353,6 +26599,7 @@
     <col width="12" customWidth="1" min="128" max="128"/>
     <col width="12" customWidth="1" min="129" max="129"/>
     <col width="12" customWidth="1" min="130" max="130"/>
+    <col width="12" customWidth="1" min="131" max="131"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26750,6 +26997,9 @@
       <c r="DZ1" s="1" t="n">
         <v>20260304</v>
       </c>
+      <c r="EA1" s="1" t="n">
+        <v>20260305</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -27143,6 +27393,9 @@
       <c r="DZ2" t="n">
         <v>262.61</v>
       </c>
+      <c r="EA2" t="n">
+        <v>261.8</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -27536,6 +27789,9 @@
       <c r="DZ3" t="n">
         <v>206.6</v>
       </c>
+      <c r="EA3" t="n">
+        <v>215.37</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -27929,6 +28185,9 @@
       <c r="DZ4" t="n">
         <v>300.33</v>
       </c>
+      <c r="EA4" t="n">
+        <v>301.87</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -28325,6 +28584,9 @@
       <c r="DZ5" t="n">
         <v>401.61</v>
       </c>
+      <c r="EA5" t="n">
+        <v>404.35</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -28718,6 +28980,9 @@
       <c r="DZ6" t="n">
         <v>96.98</v>
       </c>
+      <c r="EA6" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -29114,6 +29379,9 @@
       <c r="DZ7" t="n">
         <v>179.14</v>
       </c>
+      <c r="EA7" t="n">
+        <v>182.16</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -29510,6 +29778,9 @@
       <c r="DZ8" t="n">
         <v>145.9</v>
       </c>
+      <c r="EA8" t="n">
+        <v>152.23</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -29903,6 +30174,9 @@
       <c r="DZ9" t="n">
         <v>95.77</v>
       </c>
+      <c r="EA9" t="n">
+        <v>96.63</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -30295,6 +30569,9 @@
       </c>
       <c r="DZ10" t="n">
         <v>389.54</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>404.6</v>
       </c>
     </row>
   </sheetData>
@@ -30308,7 +30585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DZ10"/>
+  <dimension ref="A1:EA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -30441,6 +30718,7 @@
     <col width="12" customWidth="1" min="128" max="128"/>
     <col width="12" customWidth="1" min="129" max="129"/>
     <col width="12" customWidth="1" min="130" max="130"/>
+    <col width="12" customWidth="1" min="131" max="131"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30838,6 +31116,9 @@
       <c r="DZ1" s="1" t="n">
         <v>20260304</v>
       </c>
+      <c r="EA1" s="1" t="n">
+        <v>20260305</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -31231,6 +31512,9 @@
       <c r="DZ2" t="n">
         <v>263.39</v>
       </c>
+      <c r="EA2" t="n">
+        <v>262.95</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -31624,6 +31908,9 @@
       <c r="DZ3" t="n">
         <v>208.59</v>
       </c>
+      <c r="EA3" t="n">
+        <v>216.56</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -32017,6 +32304,9 @@
       <c r="DZ4" t="n">
         <v>303.58</v>
       </c>
+      <c r="EA4" t="n">
+        <v>303.51</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -32413,6 +32703,9 @@
       <c r="DZ5" t="n">
         <v>404.9</v>
       </c>
+      <c r="EA5" t="n">
+        <v>405.88</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -32806,6 +33099,9 @@
       <c r="DZ6" t="n">
         <v>97.06999999999999</v>
       </c>
+      <c r="EA6" t="n">
+        <v>98.44</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -33202,6 +33498,9 @@
       <c r="DZ7" t="n">
         <v>183.22</v>
       </c>
+      <c r="EA7" t="n">
+        <v>183.2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -33598,6 +33897,9 @@
       <c r="DZ8" t="n">
         <v>148.71</v>
       </c>
+      <c r="EA8" t="n">
+        <v>153.98</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -33991,6 +34293,9 @@
       <c r="DZ9" t="n">
         <v>96.2</v>
       </c>
+      <c r="EA9" t="n">
+        <v>96.81</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -34383,6 +34688,9 @@
       </c>
       <c r="DZ10" t="n">
         <v>397.46</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>406.5</v>
       </c>
     </row>
   </sheetData>
@@ -34396,7 +34704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DZ10"/>
+  <dimension ref="A1:EA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -34529,6 +34837,7 @@
     <col width="12" customWidth="1" min="128" max="128"/>
     <col width="12" customWidth="1" min="129" max="129"/>
     <col width="12" customWidth="1" min="130" max="130"/>
+    <col width="12" customWidth="1" min="131" max="131"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -34926,6 +35235,9 @@
       <c r="DZ1" s="1" t="n">
         <v>20260304</v>
       </c>
+      <c r="EA1" s="1" t="n">
+        <v>20260305</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -35319,6 +35631,9 @@
       <c r="DZ2" t="n">
         <v>14765</v>
       </c>
+      <c r="EA2" t="n">
+        <v>9051</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -35712,6 +36027,9 @@
       <c r="DZ3" t="n">
         <v>34200</v>
       </c>
+      <c r="EA3" t="n">
+        <v>18507</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -36105,6 +36423,9 @@
       <c r="DZ4" t="n">
         <v>33851</v>
       </c>
+      <c r="EA4" t="n">
+        <v>7325</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -36501,6 +36822,9 @@
       <c r="DZ5" t="n">
         <v>34498</v>
       </c>
+      <c r="EA5" t="n">
+        <v>8179</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -36894,6 +37218,9 @@
       <c r="DZ6" t="n">
         <v>23319</v>
       </c>
+      <c r="EA6" t="n">
+        <v>1749</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -37290,6 +37617,9 @@
       <c r="DZ7" t="n">
         <v>304086</v>
       </c>
+      <c r="EA7" t="n">
+        <v>68912</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -37686,6 +38016,9 @@
       <c r="DZ8" t="n">
         <v>51082</v>
       </c>
+      <c r="EA8" t="n">
+        <v>17312</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -38079,6 +38412,9 @@
       <c r="DZ9" t="n">
         <v>773</v>
       </c>
+      <c r="EA9" t="n">
+        <v>170</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -38471,6 +38807,9 @@
       </c>
       <c r="DZ10" t="n">
         <v>118307</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>27213</v>
       </c>
     </row>
   </sheetData>
@@ -38484,7 +38823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DG10"/>
+  <dimension ref="A1:DH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -38598,6 +38937,7 @@
     <col width="10" customWidth="1" min="109" max="109"/>
     <col width="10" customWidth="1" min="110" max="110"/>
     <col width="10" customWidth="1" min="111" max="111"/>
+    <col width="10" customWidth="1" min="112" max="112"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -38938,6 +39278,9 @@
       <c r="DG1" s="1" t="n">
         <v>20260304</v>
       </c>
+      <c r="DH1" s="1" t="n">
+        <v>20260305</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -39277,6 +39620,9 @@
       <c r="DG2" t="n">
         <v>34</v>
       </c>
+      <c r="DH2" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -39616,6 +39962,9 @@
       <c r="DG3" t="n">
         <v>25</v>
       </c>
+      <c r="DH3" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -39955,6 +40304,9 @@
       <c r="DG4" t="n">
         <v>4</v>
       </c>
+      <c r="DH4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -40294,6 +40646,9 @@
       <c r="DG5" t="n">
         <v>69</v>
       </c>
+      <c r="DH5" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -40633,6 +40988,9 @@
       <c r="DG6" t="n">
         <v>97</v>
       </c>
+      <c r="DH6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -40972,6 +41330,9 @@
       <c r="DG7" t="n">
         <v>48</v>
       </c>
+      <c r="DH7" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -41311,6 +41672,9 @@
       <c r="DG8" t="n">
         <v>100</v>
       </c>
+      <c r="DH8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -41650,6 +42014,9 @@
       <c r="DG9" t="n">
         <v>49</v>
       </c>
+      <c r="DH9" t="n">
+        <v>53</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -41988,6 +42355,9 @@
       </c>
       <c r="DG10" t="n">
         <v>14</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -42001,7 +42371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS10"/>
+  <dimension ref="A1:BT10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -42075,6 +42445,7 @@
     <col width="10" customWidth="1" min="69" max="69"/>
     <col width="10" customWidth="1" min="70" max="70"/>
     <col width="10" customWidth="1" min="71" max="71"/>
+    <col width="10" customWidth="1" min="72" max="72"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -42295,6 +42666,9 @@
       <c r="BS1" s="1" t="n">
         <v>20260304</v>
       </c>
+      <c r="BT1" s="1" t="n">
+        <v>20260305</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -42514,6 +42888,9 @@
       <c r="BS2" t="n">
         <v>49</v>
       </c>
+      <c r="BT2" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -42733,6 +43110,9 @@
       <c r="BS3" t="n">
         <v>20</v>
       </c>
+      <c r="BT3" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -42952,6 +43332,9 @@
       <c r="BS4" t="n">
         <v>16</v>
       </c>
+      <c r="BT4" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -43171,6 +43554,9 @@
       <c r="BS5" t="n">
         <v>19</v>
       </c>
+      <c r="BT5" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -43390,6 +43776,9 @@
       <c r="BS6" t="n">
         <v>78</v>
       </c>
+      <c r="BT6" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -43609,6 +43998,9 @@
       <c r="BS7" t="n">
         <v>50</v>
       </c>
+      <c r="BT7" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -43828,6 +44220,9 @@
       <c r="BS8" t="n">
         <v>30</v>
       </c>
+      <c r="BT8" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -44047,6 +44442,9 @@
       <c r="BS9" t="n">
         <v>81</v>
       </c>
+      <c r="BT9" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -44265,6 +44663,9 @@
       </c>
       <c r="BS10" t="n">
         <v>5</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -44278,7 +44679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DG10"/>
+  <dimension ref="A1:DH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -44392,6 +44793,7 @@
     <col width="10" customWidth="1" min="109" max="109"/>
     <col width="10" customWidth="1" min="110" max="110"/>
     <col width="10" customWidth="1" min="111" max="111"/>
+    <col width="10" customWidth="1" min="112" max="112"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -44732,6 +45134,9 @@
       <c r="DG1" s="1" t="n">
         <v>20260304</v>
       </c>
+      <c r="DH1" s="1" t="n">
+        <v>20260305</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -45071,6 +45476,9 @@
       <c r="DG2" t="n">
         <v>-47</v>
       </c>
+      <c r="DH2" t="n">
+        <v>-47</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -45410,6 +45818,9 @@
       <c r="DG3" t="n">
         <v>-13</v>
       </c>
+      <c r="DH3" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -45749,6 +46160,9 @@
       <c r="DG4" t="n">
         <v>-50</v>
       </c>
+      <c r="DH4" t="n">
+        <v>-48</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -46088,6 +46502,9 @@
       <c r="DG5" t="n">
         <v>22</v>
       </c>
+      <c r="DH5" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -46427,6 +46844,9 @@
       <c r="DG6" t="n">
         <v>109</v>
       </c>
+      <c r="DH6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -46766,6 +47186,9 @@
       <c r="DG7" t="n">
         <v>-14</v>
       </c>
+      <c r="DH7" t="n">
+        <v>-18</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -47105,6 +47528,9 @@
       <c r="DG8" t="n">
         <v>114</v>
       </c>
+      <c r="DH8" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -47444,6 +47870,9 @@
       <c r="DG9" t="n">
         <v>-17</v>
       </c>
+      <c r="DH9" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -47782,6 +48211,9 @@
       </c>
       <c r="DG10" t="n">
         <v>-69</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>-18</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -605,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BT10"/>
+  <dimension ref="A1:BU10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -680,6 +680,7 @@
     <col width="10" customWidth="1" min="70" max="70"/>
     <col width="10" customWidth="1" min="71" max="71"/>
     <col width="10" customWidth="1" min="72" max="72"/>
+    <col width="10" customWidth="1" min="73" max="73"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -903,6 +904,9 @@
       <c r="BT1" s="1" t="n">
         <v>20260305</v>
       </c>
+      <c r="BU1" s="1" t="n">
+        <v>20260306</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1125,6 +1129,9 @@
       <c r="BT2" t="n">
         <v>-22</v>
       </c>
+      <c r="BU2" t="n">
+        <v>-51</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1347,6 +1354,9 @@
       <c r="BT3" t="n">
         <v>-35</v>
       </c>
+      <c r="BU3" t="n">
+        <v>-46</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1569,6 +1579,9 @@
       <c r="BT4" t="n">
         <v>-66</v>
       </c>
+      <c r="BU4" t="n">
+        <v>-83</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1791,6 +1804,9 @@
       <c r="BT5" t="n">
         <v>-55</v>
       </c>
+      <c r="BU5" t="n">
+        <v>-49</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2013,6 +2029,9 @@
       <c r="BT6" t="n">
         <v>77</v>
       </c>
+      <c r="BU6" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2235,6 +2254,9 @@
       <c r="BT7" t="n">
         <v>-16</v>
       </c>
+      <c r="BU7" t="n">
+        <v>-62</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2457,6 +2479,9 @@
       <c r="BT8" t="n">
         <v>-20</v>
       </c>
+      <c r="BU8" t="n">
+        <v>-11</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2679,6 +2704,9 @@
       <c r="BT9" t="n">
         <v>49</v>
       </c>
+      <c r="BU9" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2900,6 +2928,9 @@
       </c>
       <c r="BT10" t="n">
         <v>-58</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>-74</v>
       </c>
     </row>
   </sheetData>
@@ -2913,7 +2944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DH10"/>
+  <dimension ref="A1:DI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3028,6 +3059,7 @@
     <col width="12" customWidth="1" min="110" max="110"/>
     <col width="12" customWidth="1" min="111" max="111"/>
     <col width="12" customWidth="1" min="112" max="112"/>
+    <col width="12" customWidth="1" min="113" max="113"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3591,6 +3623,11 @@
           <t>20260305</t>
         </is>
       </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>20260306</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4884,6 +4921,9 @@
       <c r="DH5" t="n">
         <v>101</v>
       </c>
+      <c r="DI5" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5538,6 +5578,9 @@
       <c r="DH7" t="n">
         <v>99</v>
       </c>
+      <c r="DI7" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5879,6 +5922,9 @@
       </c>
       <c r="DH8" t="n">
         <v>112</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>114</v>
       </c>
     </row>
     <row r="9">
@@ -6531,7 +6577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CO10"/>
+  <dimension ref="A1:CP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6627,6 +6673,7 @@
     <col width="12" customWidth="1" min="91" max="91"/>
     <col width="12" customWidth="1" min="92" max="92"/>
     <col width="12" customWidth="1" min="93" max="93"/>
+    <col width="12" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7095,6 +7142,11 @@
           <t>20260305</t>
         </is>
       </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>20260306</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8160,6 +8212,9 @@
       <c r="CO5" t="n">
         <v>-64.86</v>
       </c>
+      <c r="CP5" t="n">
+        <v>-65.38</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8700,6 +8755,9 @@
       <c r="CO7" t="n">
         <v>-2.03</v>
       </c>
+      <c r="CP7" t="n">
+        <v>-7.41</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8984,6 +9042,9 @@
       </c>
       <c r="CO8" t="n">
         <v>-41.02</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>-27.45</v>
       </c>
     </row>
     <row r="9">
@@ -9522,7 +9583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BT10"/>
+  <dimension ref="A1:BU10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9597,6 +9658,7 @@
     <col width="12" customWidth="1" min="70" max="70"/>
     <col width="12" customWidth="1" min="71" max="71"/>
     <col width="12" customWidth="1" min="72" max="72"/>
+    <col width="12" customWidth="1" min="73" max="73"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9960,6 +10022,11 @@
           <t>20260305</t>
         </is>
       </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>20260306</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10773,6 +10840,9 @@
       <c r="BT5" t="n">
         <v>0</v>
       </c>
+      <c r="BU5" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11187,6 +11257,9 @@
       <c r="BT7" t="n">
         <v>0</v>
       </c>
+      <c r="BU7" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11408,6 +11481,9 @@
       </c>
       <c r="BT8" t="n">
         <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>133</v>
       </c>
     </row>
     <row r="9">
@@ -11820,7 +11896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CX10"/>
+  <dimension ref="A1:CY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11925,6 +12001,7 @@
     <col width="10" customWidth="1" min="100" max="100"/>
     <col width="10" customWidth="1" min="101" max="101"/>
     <col width="10" customWidth="1" min="102" max="102"/>
+    <col width="10" customWidth="1" min="103" max="103"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12238,6 +12315,9 @@
       <c r="CX1" s="1" t="n">
         <v>20260305</v>
       </c>
+      <c r="CY1" s="1" t="n">
+        <v>20260306</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12550,6 +12630,9 @@
       <c r="CX2" t="n">
         <v>-10</v>
       </c>
+      <c r="CY2" t="n">
+        <v>-45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12862,6 +12945,9 @@
       <c r="CX3" t="n">
         <v>-11</v>
       </c>
+      <c r="CY3" t="n">
+        <v>-20</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13174,6 +13260,9 @@
       <c r="CX4" t="n">
         <v>-64</v>
       </c>
+      <c r="CY4" t="n">
+        <v>-76</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13486,6 +13575,9 @@
       <c r="CX5" t="n">
         <v>-19</v>
       </c>
+      <c r="CY5" t="n">
+        <v>-11</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13798,6 +13890,9 @@
       <c r="CX6" t="n">
         <v>119</v>
       </c>
+      <c r="CY6" t="n">
+        <v>109</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14110,6 +14205,9 @@
       <c r="CX7" t="n">
         <v>-23</v>
       </c>
+      <c r="CY7" t="n">
+        <v>-64</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14422,6 +14520,9 @@
       <c r="CX8" t="n">
         <v>42</v>
       </c>
+      <c r="CY8" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14734,6 +14835,9 @@
       <c r="CX9" t="n">
         <v>15</v>
       </c>
+      <c r="CY9" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15045,6 +15149,9 @@
       </c>
       <c r="CX10" t="n">
         <v>-38</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>-67</v>
       </c>
     </row>
   </sheetData>
@@ -15058,7 +15165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15073,6 +15180,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15116,6 +15224,9 @@
       <c r="L1" s="1" t="n">
         <v>20260305</v>
       </c>
+      <c r="M1" s="1" t="n">
+        <v>20260306</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15155,6 +15266,9 @@
       <c r="L2" t="n">
         <v>59</v>
       </c>
+      <c r="M2" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15194,6 +15308,9 @@
       <c r="L3" t="n">
         <v>32</v>
       </c>
+      <c r="M3" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15236,6 +15353,9 @@
       <c r="L4" t="n">
         <v>65</v>
       </c>
+      <c r="M4" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15278,6 +15398,9 @@
       <c r="L5" t="n">
         <v>14</v>
       </c>
+      <c r="M5" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15317,6 +15440,9 @@
       <c r="L6" t="n">
         <v>2</v>
       </c>
+      <c r="M6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15359,6 +15485,9 @@
       <c r="L7" t="n">
         <v>35</v>
       </c>
+      <c r="M7" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15401,6 +15530,9 @@
       <c r="L8" t="n">
         <v>32</v>
       </c>
+      <c r="M8" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15440,6 +15572,9 @@
       <c r="L9" t="n">
         <v>87</v>
       </c>
+      <c r="M9" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15481,6 +15616,9 @@
       </c>
       <c r="L10" t="n">
         <v>31</v>
+      </c>
+      <c r="M10" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -15494,7 +15632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15509,6 +15647,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15552,6 +15691,9 @@
       <c r="L1" s="1" t="n">
         <v>20260305</v>
       </c>
+      <c r="M1" s="1" t="n">
+        <v>20260306</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15591,6 +15733,9 @@
       <c r="L2" t="n">
         <v>-5</v>
       </c>
+      <c r="M2" t="n">
+        <v>-31</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15630,6 +15775,9 @@
       <c r="L3" t="n">
         <v>-44</v>
       </c>
+      <c r="M3" t="n">
+        <v>-57</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15672,6 +15820,9 @@
       <c r="L4" t="n">
         <v>15</v>
       </c>
+      <c r="M4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15714,6 +15865,9 @@
       <c r="L5" t="n">
         <v>-85</v>
       </c>
+      <c r="M5" t="n">
+        <v>-80</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15753,6 +15907,9 @@
       <c r="L6" t="n">
         <v>-39</v>
       </c>
+      <c r="M6" t="n">
+        <v>-38</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15795,6 +15952,9 @@
       <c r="L7" t="n">
         <v>-14</v>
       </c>
+      <c r="M7" t="n">
+        <v>-53</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15837,6 +15997,9 @@
       <c r="L8" t="n">
         <v>-45</v>
       </c>
+      <c r="M8" t="n">
+        <v>-36</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15876,6 +16039,9 @@
       <c r="L9" t="n">
         <v>81</v>
       </c>
+      <c r="M9" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15917,6 +16083,9 @@
       </c>
       <c r="L10" t="n">
         <v>-60</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-84</v>
       </c>
     </row>
   </sheetData>
@@ -15930,7 +16099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BT10"/>
+  <dimension ref="A1:BU10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -16005,6 +16174,7 @@
     <col width="12" customWidth="1" min="70" max="70"/>
     <col width="12" customWidth="1" min="71" max="71"/>
     <col width="12" customWidth="1" min="72" max="72"/>
+    <col width="12" customWidth="1" min="73" max="73"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16368,6 +16538,11 @@
           <t>20260305</t>
         </is>
       </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>20260306</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17181,6 +17356,9 @@
       <c r="BT5" t="n">
         <v>91</v>
       </c>
+      <c r="BU5" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17595,6 +17773,9 @@
       <c r="BT7" t="n">
         <v>99</v>
       </c>
+      <c r="BU7" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17816,6 +17997,9 @@
       </c>
       <c r="BT8" t="n">
         <v>95</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>97</v>
       </c>
     </row>
     <row r="9">
@@ -18228,7 +18412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EA10"/>
+  <dimension ref="A1:EB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18362,6 +18546,7 @@
     <col width="12" customWidth="1" min="129" max="129"/>
     <col width="12" customWidth="1" min="130" max="130"/>
     <col width="12" customWidth="1" min="131" max="131"/>
+    <col width="12" customWidth="1" min="132" max="132"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18762,6 +18947,9 @@
       <c r="EA1" s="1" t="n">
         <v>20260305</v>
       </c>
+      <c r="EB1" s="1" t="n">
+        <v>20260306</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19158,6 +19346,9 @@
       <c r="EA2" t="n">
         <v>262.28</v>
       </c>
+      <c r="EB2" t="n">
+        <v>258.63</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19554,6 +19745,9 @@
       <c r="EA3" t="n">
         <v>215.85</v>
       </c>
+      <c r="EB3" t="n">
+        <v>214.99</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19950,6 +20144,9 @@
       <c r="EA4" t="n">
         <v>302.29</v>
       </c>
+      <c r="EB4" t="n">
+        <v>296.09</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20349,6 +20546,9 @@
       <c r="EA5" t="n">
         <v>404.93</v>
       </c>
+      <c r="EB5" t="n">
+        <v>409.2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20745,6 +20945,9 @@
       <c r="EA6" t="n">
         <v>98.06999999999999</v>
       </c>
+      <c r="EB6" t="n">
+        <v>99.33</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21144,6 +21347,9 @@
       <c r="EA7" t="n">
         <v>182.2</v>
       </c>
+      <c r="EB7" t="n">
+        <v>179.84</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21543,6 +21749,9 @@
       <c r="EA8" t="n">
         <v>152.29</v>
       </c>
+      <c r="EB8" t="n">
+        <v>150.44</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21939,6 +22148,9 @@
       <c r="EA9" t="n">
         <v>96.63</v>
       </c>
+      <c r="EB9" t="n">
+        <v>97.06999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22334,6 +22546,9 @@
       </c>
       <c r="EA10" t="n">
         <v>405.03</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>398.09</v>
       </c>
     </row>
   </sheetData>
@@ -22347,7 +22562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EA10"/>
+  <dimension ref="A1:EB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22481,6 +22696,7 @@
     <col width="12" customWidth="1" min="129" max="129"/>
     <col width="12" customWidth="1" min="130" max="130"/>
     <col width="12" customWidth="1" min="131" max="131"/>
+    <col width="12" customWidth="1" min="132" max="132"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22881,6 +23097,9 @@
       <c r="EA1" s="1" t="n">
         <v>20260305</v>
       </c>
+      <c r="EB1" s="1" t="n">
+        <v>20260306</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23277,6 +23496,9 @@
       <c r="EA2" t="n">
         <v>262.95</v>
       </c>
+      <c r="EB2" t="n">
+        <v>258.77</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23673,6 +23895,9 @@
       <c r="EA3" t="n">
         <v>217.24</v>
       </c>
+      <c r="EB3" t="n">
+        <v>217.32</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -24069,6 +24294,9 @@
       <c r="EA4" t="n">
         <v>303.9</v>
       </c>
+      <c r="EB4" t="n">
+        <v>300.53</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24468,6 +24696,9 @@
       <c r="EA5" t="n">
         <v>406.96</v>
       </c>
+      <c r="EB5" t="n">
+        <v>413.05</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24864,6 +25095,9 @@
       <c r="EA6" t="n">
         <v>98.59999999999999</v>
       </c>
+      <c r="EB6" t="n">
+        <v>99.88</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -25263,6 +25497,9 @@
       <c r="EA7" t="n">
         <v>183.41</v>
       </c>
+      <c r="EB7" t="n">
+        <v>182.7561</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25662,6 +25899,9 @@
       <c r="EA8" t="n">
         <v>154.44</v>
       </c>
+      <c r="EB8" t="n">
+        <v>161.45</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -26058,6 +26298,9 @@
       <c r="EA9" t="n">
         <v>96.81999999999999</v>
       </c>
+      <c r="EB9" t="n">
+        <v>99.22</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26453,6 +26696,9 @@
       </c>
       <c r="EA10" t="n">
         <v>407</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>402.35</v>
       </c>
     </row>
   </sheetData>
@@ -26466,7 +26712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EA10"/>
+  <dimension ref="A1:EB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -26600,6 +26846,7 @@
     <col width="12" customWidth="1" min="129" max="129"/>
     <col width="12" customWidth="1" min="130" max="130"/>
     <col width="12" customWidth="1" min="131" max="131"/>
+    <col width="12" customWidth="1" min="132" max="132"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27000,6 +27247,9 @@
       <c r="EA1" s="1" t="n">
         <v>20260305</v>
       </c>
+      <c r="EB1" s="1" t="n">
+        <v>20260306</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -27396,6 +27646,9 @@
       <c r="EA2" t="n">
         <v>261.8</v>
       </c>
+      <c r="EB2" t="n">
+        <v>254.37</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -27792,6 +28045,9 @@
       <c r="EA3" t="n">
         <v>215.37</v>
       </c>
+      <c r="EB3" t="n">
+        <v>212.53</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -28188,6 +28444,9 @@
       <c r="EA4" t="n">
         <v>301.87</v>
       </c>
+      <c r="EB4" t="n">
+        <v>295.18</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -28587,6 +28846,9 @@
       <c r="EA5" t="n">
         <v>404.35</v>
       </c>
+      <c r="EB5" t="n">
+        <v>408.5101</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -28983,6 +29245,9 @@
       <c r="EA6" t="n">
         <v>98</v>
       </c>
+      <c r="EB6" t="n">
+        <v>97.40000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -29382,6 +29647,9 @@
       <c r="EA7" t="n">
         <v>182.16</v>
       </c>
+      <c r="EB7" t="n">
+        <v>176.8201</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -29781,6 +30049,9 @@
       <c r="EA8" t="n">
         <v>152.23</v>
       </c>
+      <c r="EB8" t="n">
+        <v>150.29</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -30177,6 +30448,9 @@
       <c r="EA9" t="n">
         <v>96.63</v>
       </c>
+      <c r="EB9" t="n">
+        <v>95.56</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -30572,6 +30846,9 @@
       </c>
       <c r="EA10" t="n">
         <v>404.6</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>394.21</v>
       </c>
     </row>
   </sheetData>
@@ -30585,7 +30862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EA10"/>
+  <dimension ref="A1:EB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -30719,6 +30996,7 @@
     <col width="12" customWidth="1" min="129" max="129"/>
     <col width="12" customWidth="1" min="130" max="130"/>
     <col width="12" customWidth="1" min="131" max="131"/>
+    <col width="12" customWidth="1" min="132" max="132"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31119,6 +31397,9 @@
       <c r="EA1" s="1" t="n">
         <v>20260305</v>
       </c>
+      <c r="EB1" s="1" t="n">
+        <v>20260306</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -31515,6 +31796,9 @@
       <c r="EA2" t="n">
         <v>262.95</v>
       </c>
+      <c r="EB2" t="n">
+        <v>257.46</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -31911,6 +32195,9 @@
       <c r="EA3" t="n">
         <v>216.56</v>
       </c>
+      <c r="EB3" t="n">
+        <v>213.21</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -32307,6 +32594,9 @@
       <c r="EA4" t="n">
         <v>303.51</v>
       </c>
+      <c r="EB4" t="n">
+        <v>298.52</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -32706,6 +32996,9 @@
       <c r="EA5" t="n">
         <v>405.88</v>
       </c>
+      <c r="EB5" t="n">
+        <v>408.96</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -33102,6 +33395,9 @@
       <c r="EA6" t="n">
         <v>98.44</v>
       </c>
+      <c r="EB6" t="n">
+        <v>99.02</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -33501,6 +33797,9 @@
       <c r="EA7" t="n">
         <v>183.2</v>
       </c>
+      <c r="EB7" t="n">
+        <v>177.82</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -33900,6 +34199,9 @@
       <c r="EA8" t="n">
         <v>153.98</v>
       </c>
+      <c r="EB8" t="n">
+        <v>157.16</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -34296,6 +34598,9 @@
       <c r="EA9" t="n">
         <v>96.81</v>
       </c>
+      <c r="EB9" t="n">
+        <v>98.98999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -34691,6 +34996,9 @@
       </c>
       <c r="EA10" t="n">
         <v>406.5</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>396.73</v>
       </c>
     </row>
   </sheetData>
@@ -34704,7 +35012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EA10"/>
+  <dimension ref="A1:EB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -34838,6 +35146,7 @@
     <col width="12" customWidth="1" min="129" max="129"/>
     <col width="12" customWidth="1" min="130" max="130"/>
     <col width="12" customWidth="1" min="131" max="131"/>
+    <col width="12" customWidth="1" min="132" max="132"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -35238,6 +35547,9 @@
       <c r="EA1" s="1" t="n">
         <v>20260305</v>
       </c>
+      <c r="EB1" s="1" t="n">
+        <v>20260306</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -35634,6 +35946,9 @@
       <c r="EA2" t="n">
         <v>9051</v>
       </c>
+      <c r="EB2" t="n">
+        <v>41120042</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -36030,6 +36345,9 @@
       <c r="EA3" t="n">
         <v>18507</v>
       </c>
+      <c r="EB3" t="n">
+        <v>51152716</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -36426,6 +36744,9 @@
       <c r="EA4" t="n">
         <v>7325</v>
       </c>
+      <c r="EB4" t="n">
+        <v>25576916</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -36825,6 +37146,9 @@
       <c r="EA5" t="n">
         <v>8179</v>
       </c>
+      <c r="EB5" t="n">
+        <v>31123859</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -37221,6 +37545,9 @@
       <c r="EA6" t="n">
         <v>1749</v>
       </c>
+      <c r="EB6" t="n">
+        <v>41196294</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -37620,6 +37947,9 @@
       <c r="EA7" t="n">
         <v>68912</v>
       </c>
+      <c r="EB7" t="n">
+        <v>189021949</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -38019,6 +38349,9 @@
       <c r="EA8" t="n">
         <v>17312</v>
       </c>
+      <c r="EB8" t="n">
+        <v>74980855</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -38415,6 +38748,9 @@
       <c r="EA9" t="n">
         <v>170</v>
       </c>
+      <c r="EB9" t="n">
+        <v>10826676</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -38810,6 +39146,9 @@
       </c>
       <c r="EA10" t="n">
         <v>27213</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>64054561</v>
       </c>
     </row>
   </sheetData>
@@ -38823,7 +39162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DH10"/>
+  <dimension ref="A1:DI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -38938,6 +39277,7 @@
     <col width="10" customWidth="1" min="110" max="110"/>
     <col width="10" customWidth="1" min="111" max="111"/>
     <col width="10" customWidth="1" min="112" max="112"/>
+    <col width="10" customWidth="1" min="113" max="113"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -39281,6 +39621,9 @@
       <c r="DH1" s="1" t="n">
         <v>20260305</v>
       </c>
+      <c r="DI1" s="1" t="n">
+        <v>20260306</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -39623,6 +39966,9 @@
       <c r="DH2" t="n">
         <v>32</v>
       </c>
+      <c r="DI2" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -39965,6 +40311,9 @@
       <c r="DH3" t="n">
         <v>52</v>
       </c>
+      <c r="DI3" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -40307,6 +40656,9 @@
       <c r="DH4" t="n">
         <v>5</v>
       </c>
+      <c r="DI4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -40649,6 +41001,9 @@
       <c r="DH5" t="n">
         <v>72</v>
       </c>
+      <c r="DI5" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -40991,6 +41346,9 @@
       <c r="DH6" t="n">
         <v>100</v>
       </c>
+      <c r="DI6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -41333,6 +41691,9 @@
       <c r="DH7" t="n">
         <v>48</v>
       </c>
+      <c r="DI7" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -41675,6 +42036,9 @@
       <c r="DH8" t="n">
         <v>100</v>
       </c>
+      <c r="DI8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -42017,6 +42381,9 @@
       <c r="DH9" t="n">
         <v>53</v>
       </c>
+      <c r="DI9" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -42358,6 +42725,9 @@
       </c>
       <c r="DH10" t="n">
         <v>39</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -42371,7 +42741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BT10"/>
+  <dimension ref="A1:BU10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -42446,6 +42816,7 @@
     <col width="10" customWidth="1" min="70" max="70"/>
     <col width="10" customWidth="1" min="71" max="71"/>
     <col width="10" customWidth="1" min="72" max="72"/>
+    <col width="10" customWidth="1" min="73" max="73"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -42669,6 +43040,9 @@
       <c r="BT1" s="1" t="n">
         <v>20260305</v>
       </c>
+      <c r="BU1" s="1" t="n">
+        <v>20260306</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -42891,6 +43265,9 @@
       <c r="BT2" t="n">
         <v>51</v>
       </c>
+      <c r="BU2" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -43113,6 +43490,9 @@
       <c r="BT3" t="n">
         <v>37</v>
       </c>
+      <c r="BU3" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -43335,6 +43715,9 @@
       <c r="BT4" t="n">
         <v>16</v>
       </c>
+      <c r="BU4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -43557,6 +43940,9 @@
       <c r="BT5" t="n">
         <v>20</v>
       </c>
+      <c r="BU5" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -43779,6 +44165,9 @@
       <c r="BT6" t="n">
         <v>93</v>
       </c>
+      <c r="BU6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -44001,6 +44390,9 @@
       <c r="BT7" t="n">
         <v>50</v>
       </c>
+      <c r="BU7" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -44223,6 +44615,9 @@
       <c r="BT8" t="n">
         <v>38</v>
       </c>
+      <c r="BU8" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -44445,6 +44840,9 @@
       <c r="BT9" t="n">
         <v>85</v>
       </c>
+      <c r="BU9" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -44666,6 +45064,9 @@
       </c>
       <c r="BT10" t="n">
         <v>14</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -44679,7 +45080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DH10"/>
+  <dimension ref="A1:DI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -44794,6 +45195,7 @@
     <col width="10" customWidth="1" min="110" max="110"/>
     <col width="10" customWidth="1" min="111" max="111"/>
     <col width="10" customWidth="1" min="112" max="112"/>
+    <col width="10" customWidth="1" min="113" max="113"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -45137,6 +45539,9 @@
       <c r="DH1" s="1" t="n">
         <v>20260305</v>
       </c>
+      <c r="DI1" s="1" t="n">
+        <v>20260306</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -45479,6 +45884,9 @@
       <c r="DH2" t="n">
         <v>-47</v>
       </c>
+      <c r="DI2" t="n">
+        <v>-78</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -45821,6 +46229,9 @@
       <c r="DH3" t="n">
         <v>32</v>
       </c>
+      <c r="DI3" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -46163,6 +46574,9 @@
       <c r="DH4" t="n">
         <v>-48</v>
       </c>
+      <c r="DI4" t="n">
+        <v>-67</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -46505,6 +46919,9 @@
       <c r="DH5" t="n">
         <v>32</v>
       </c>
+      <c r="DI5" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -46847,6 +47264,9 @@
       <c r="DH6" t="n">
         <v>100</v>
       </c>
+      <c r="DI6" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -47189,6 +47609,9 @@
       <c r="DH7" t="n">
         <v>-18</v>
       </c>
+      <c r="DI7" t="n">
+        <v>-68</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -47531,6 +47954,9 @@
       <c r="DH8" t="n">
         <v>126</v>
       </c>
+      <c r="DI8" t="n">
+        <v>119</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -47873,6 +48299,9 @@
       <c r="DH9" t="n">
         <v>-5</v>
       </c>
+      <c r="DI9" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -48214,6 +48643,9 @@
       </c>
       <c r="DH10" t="n">
         <v>-18</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>-65</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -605,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU10"/>
+  <dimension ref="A1:BV10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -681,6 +681,7 @@
     <col width="10" customWidth="1" min="71" max="71"/>
     <col width="10" customWidth="1" min="72" max="72"/>
     <col width="10" customWidth="1" min="73" max="73"/>
+    <col width="10" customWidth="1" min="74" max="74"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -907,6 +908,9 @@
       <c r="BU1" s="1" t="n">
         <v>20260306</v>
       </c>
+      <c r="BV1" s="1" t="n">
+        <v>20260309</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1132,6 +1136,9 @@
       <c r="BU2" t="n">
         <v>-51</v>
       </c>
+      <c r="BV2" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1357,6 +1364,9 @@
       <c r="BU3" t="n">
         <v>-46</v>
       </c>
+      <c r="BV3" t="n">
+        <v>-45</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1582,6 +1592,9 @@
       <c r="BU4" t="n">
         <v>-83</v>
       </c>
+      <c r="BV4" t="n">
+        <v>-81</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1807,6 +1820,9 @@
       <c r="BU5" t="n">
         <v>-49</v>
       </c>
+      <c r="BV5" t="n">
+        <v>-48</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2032,6 +2048,9 @@
       <c r="BU6" t="n">
         <v>82</v>
       </c>
+      <c r="BV6" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2257,6 +2276,9 @@
       <c r="BU7" t="n">
         <v>-62</v>
       </c>
+      <c r="BV7" t="n">
+        <v>-60</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2482,6 +2504,9 @@
       <c r="BU8" t="n">
         <v>-11</v>
       </c>
+      <c r="BV8" t="n">
+        <v>-11</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2707,6 +2732,9 @@
       <c r="BU9" t="n">
         <v>67</v>
       </c>
+      <c r="BV9" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2931,6 +2959,9 @@
       </c>
       <c r="BU10" t="n">
         <v>-74</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>-72</v>
       </c>
     </row>
   </sheetData>
@@ -2944,7 +2975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DI10"/>
+  <dimension ref="A1:DJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3060,6 +3091,7 @@
     <col width="12" customWidth="1" min="111" max="111"/>
     <col width="12" customWidth="1" min="112" max="112"/>
     <col width="12" customWidth="1" min="113" max="113"/>
+    <col width="12" customWidth="1" min="114" max="114"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3628,6 +3660,11 @@
           <t>20260306</t>
         </is>
       </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>20260309</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4924,6 +4961,9 @@
       <c r="DI5" t="n">
         <v>102</v>
       </c>
+      <c r="DJ5" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5581,6 +5621,9 @@
       <c r="DI7" t="n">
         <v>96</v>
       </c>
+      <c r="DJ7" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5925,6 +5968,9 @@
       </c>
       <c r="DI8" t="n">
         <v>114</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>113</v>
       </c>
     </row>
     <row r="9">
@@ -6577,7 +6623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CP10"/>
+  <dimension ref="A1:CQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6674,6 +6720,7 @@
     <col width="12" customWidth="1" min="92" max="92"/>
     <col width="12" customWidth="1" min="93" max="93"/>
     <col width="12" customWidth="1" min="94" max="94"/>
+    <col width="12" customWidth="1" min="95" max="95"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7147,6 +7194,11 @@
           <t>20260306</t>
         </is>
       </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>20260309</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8215,6 +8267,9 @@
       <c r="CP5" t="n">
         <v>-65.38</v>
       </c>
+      <c r="CQ5" t="n">
+        <v>-63.6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8758,6 +8813,9 @@
       <c r="CP7" t="n">
         <v>-7.41</v>
       </c>
+      <c r="CQ7" t="n">
+        <v>-16.86</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9045,6 +9103,9 @@
       </c>
       <c r="CP8" t="n">
         <v>-27.45</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>-17.68</v>
       </c>
     </row>
     <row r="9">
@@ -9583,7 +9644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU10"/>
+  <dimension ref="A1:BV10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9659,6 +9720,7 @@
     <col width="12" customWidth="1" min="71" max="71"/>
     <col width="12" customWidth="1" min="72" max="72"/>
     <col width="12" customWidth="1" min="73" max="73"/>
+    <col width="12" customWidth="1" min="74" max="74"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10027,6 +10089,11 @@
           <t>20260306</t>
         </is>
       </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>20260309</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10843,6 +10910,9 @@
       <c r="BU5" t="n">
         <v>79</v>
       </c>
+      <c r="BV5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11260,6 +11330,9 @@
       <c r="BU7" t="n">
         <v>88</v>
       </c>
+      <c r="BV7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11484,6 +11557,9 @@
       </c>
       <c r="BU8" t="n">
         <v>133</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -11896,7 +11972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CY10"/>
+  <dimension ref="A1:CZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12002,6 +12078,7 @@
     <col width="10" customWidth="1" min="101" max="101"/>
     <col width="10" customWidth="1" min="102" max="102"/>
     <col width="10" customWidth="1" min="103" max="103"/>
+    <col width="10" customWidth="1" min="104" max="104"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12318,6 +12395,9 @@
       <c r="CY1" s="1" t="n">
         <v>20260306</v>
       </c>
+      <c r="CZ1" s="1" t="n">
+        <v>20260309</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12633,6 +12713,9 @@
       <c r="CY2" t="n">
         <v>-45</v>
       </c>
+      <c r="CZ2" t="n">
+        <v>-49</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12948,6 +13031,9 @@
       <c r="CY3" t="n">
         <v>-20</v>
       </c>
+      <c r="CZ3" t="n">
+        <v>-18</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13263,6 +13349,9 @@
       <c r="CY4" t="n">
         <v>-76</v>
       </c>
+      <c r="CZ4" t="n">
+        <v>-71</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13578,6 +13667,9 @@
       <c r="CY5" t="n">
         <v>-11</v>
       </c>
+      <c r="CZ5" t="n">
+        <v>-8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13893,6 +13985,9 @@
       <c r="CY6" t="n">
         <v>109</v>
       </c>
+      <c r="CZ6" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14208,6 +14303,9 @@
       <c r="CY7" t="n">
         <v>-64</v>
       </c>
+      <c r="CZ7" t="n">
+        <v>-60</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14523,6 +14621,9 @@
       <c r="CY8" t="n">
         <v>58</v>
       </c>
+      <c r="CZ8" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14838,6 +14939,9 @@
       <c r="CY9" t="n">
         <v>67</v>
       </c>
+      <c r="CZ9" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15152,6 +15256,9 @@
       </c>
       <c r="CY10" t="n">
         <v>-67</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>-65</v>
       </c>
     </row>
   </sheetData>
@@ -15165,7 +15272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15181,6 +15288,7 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15227,6 +15335,9 @@
       <c r="M1" s="1" t="n">
         <v>20260306</v>
       </c>
+      <c r="N1" s="1" t="n">
+        <v>20260309</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15269,6 +15380,9 @@
       <c r="M2" t="n">
         <v>45</v>
       </c>
+      <c r="N2" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15311,6 +15425,9 @@
       <c r="M3" t="n">
         <v>26</v>
       </c>
+      <c r="N3" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15356,6 +15473,9 @@
       <c r="M4" t="n">
         <v>60</v>
       </c>
+      <c r="N4" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15401,6 +15521,9 @@
       <c r="M5" t="n">
         <v>16</v>
       </c>
+      <c r="N5" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15443,6 +15566,9 @@
       <c r="M6" t="n">
         <v>2</v>
       </c>
+      <c r="N6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15488,6 +15614,9 @@
       <c r="M7" t="n">
         <v>20</v>
       </c>
+      <c r="N7" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15533,6 +15662,9 @@
       <c r="M8" t="n">
         <v>36</v>
       </c>
+      <c r="N8" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15575,6 +15707,9 @@
       <c r="M9" t="n">
         <v>98</v>
       </c>
+      <c r="N9" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15618,6 +15753,9 @@
         <v>31</v>
       </c>
       <c r="M10" t="n">
+        <v>6</v>
+      </c>
+      <c r="N10" t="n">
         <v>6</v>
       </c>
     </row>
@@ -15632,7 +15770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15648,6 +15786,7 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15694,6 +15833,9 @@
       <c r="M1" s="1" t="n">
         <v>20260306</v>
       </c>
+      <c r="N1" s="1" t="n">
+        <v>20260309</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15736,6 +15878,9 @@
       <c r="M2" t="n">
         <v>-31</v>
       </c>
+      <c r="N2" t="n">
+        <v>-33</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15778,6 +15923,9 @@
       <c r="M3" t="n">
         <v>-57</v>
       </c>
+      <c r="N3" t="n">
+        <v>-57</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15823,6 +15971,9 @@
       <c r="M4" t="n">
         <v>6</v>
       </c>
+      <c r="N4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15868,6 +16019,9 @@
       <c r="M5" t="n">
         <v>-80</v>
       </c>
+      <c r="N5" t="n">
+        <v>-78</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15910,6 +16064,9 @@
       <c r="M6" t="n">
         <v>-38</v>
       </c>
+      <c r="N6" t="n">
+        <v>-38</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15955,6 +16112,9 @@
       <c r="M7" t="n">
         <v>-53</v>
       </c>
+      <c r="N7" t="n">
+        <v>-53</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16000,6 +16160,9 @@
       <c r="M8" t="n">
         <v>-36</v>
       </c>
+      <c r="N8" t="n">
+        <v>-35</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16042,6 +16205,9 @@
       <c r="M9" t="n">
         <v>98</v>
       </c>
+      <c r="N9" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16085,6 +16251,9 @@
         <v>-60</v>
       </c>
       <c r="M10" t="n">
+        <v>-84</v>
+      </c>
+      <c r="N10" t="n">
         <v>-84</v>
       </c>
     </row>
@@ -16099,7 +16268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU10"/>
+  <dimension ref="A1:BV10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -16175,6 +16344,7 @@
     <col width="12" customWidth="1" min="71" max="71"/>
     <col width="12" customWidth="1" min="72" max="72"/>
     <col width="12" customWidth="1" min="73" max="73"/>
+    <col width="12" customWidth="1" min="74" max="74"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16543,6 +16713,11 @@
           <t>20260306</t>
         </is>
       </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>20260309</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17359,6 +17534,9 @@
       <c r="BU5" t="n">
         <v>92</v>
       </c>
+      <c r="BV5" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17776,6 +17954,9 @@
       <c r="BU7" t="n">
         <v>96</v>
       </c>
+      <c r="BV7" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17999,6 +18180,9 @@
         <v>95</v>
       </c>
       <c r="BU8" t="n">
+        <v>97</v>
+      </c>
+      <c r="BV8" t="n">
         <v>97</v>
       </c>
     </row>
@@ -18412,7 +18596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EB10"/>
+  <dimension ref="A1:EC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18547,6 +18731,7 @@
     <col width="12" customWidth="1" min="130" max="130"/>
     <col width="12" customWidth="1" min="131" max="131"/>
     <col width="12" customWidth="1" min="132" max="132"/>
+    <col width="12" customWidth="1" min="133" max="133"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18950,6 +19135,9 @@
       <c r="EB1" s="1" t="n">
         <v>20260306</v>
       </c>
+      <c r="EC1" s="1" t="n">
+        <v>20260309</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19349,6 +19537,9 @@
       <c r="EB2" t="n">
         <v>258.63</v>
       </c>
+      <c r="EC2" t="n">
+        <v>257.46</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19748,6 +19939,9 @@
       <c r="EB3" t="n">
         <v>214.99</v>
       </c>
+      <c r="EC3" t="n">
+        <v>213.21</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20147,6 +20341,9 @@
       <c r="EB4" t="n">
         <v>296.09</v>
       </c>
+      <c r="EC4" t="n">
+        <v>298.31</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20549,6 +20746,9 @@
       <c r="EB5" t="n">
         <v>409.2</v>
       </c>
+      <c r="EC5" t="n">
+        <v>408.96</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20948,6 +21148,9 @@
       <c r="EB6" t="n">
         <v>99.33</v>
       </c>
+      <c r="EC6" t="n">
+        <v>99.02</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21350,6 +21553,9 @@
       <c r="EB7" t="n">
         <v>179.84</v>
       </c>
+      <c r="EC7" t="n">
+        <v>177.82</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21752,6 +21958,9 @@
       <c r="EB8" t="n">
         <v>150.44</v>
       </c>
+      <c r="EC8" t="n">
+        <v>157.16</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22151,6 +22360,9 @@
       <c r="EB9" t="n">
         <v>97.06999999999999</v>
       </c>
+      <c r="EC9" t="n">
+        <v>98.98999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22549,6 +22761,9 @@
       </c>
       <c r="EB10" t="n">
         <v>398.09</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>396.73</v>
       </c>
     </row>
   </sheetData>
@@ -22562,7 +22777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EB10"/>
+  <dimension ref="A1:EC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22697,6 +22912,7 @@
     <col width="12" customWidth="1" min="130" max="130"/>
     <col width="12" customWidth="1" min="131" max="131"/>
     <col width="12" customWidth="1" min="132" max="132"/>
+    <col width="12" customWidth="1" min="133" max="133"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23100,6 +23316,9 @@
       <c r="EB1" s="1" t="n">
         <v>20260306</v>
       </c>
+      <c r="EC1" s="1" t="n">
+        <v>20260309</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23499,6 +23718,9 @@
       <c r="EB2" t="n">
         <v>258.77</v>
       </c>
+      <c r="EC2" t="n">
+        <v>257.46</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23898,6 +24120,9 @@
       <c r="EB3" t="n">
         <v>217.32</v>
       </c>
+      <c r="EC3" t="n">
+        <v>213.21</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -24297,6 +24522,9 @@
       <c r="EB4" t="n">
         <v>300.53</v>
       </c>
+      <c r="EC4" t="n">
+        <v>298.31</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24699,6 +24927,9 @@
       <c r="EB5" t="n">
         <v>413.05</v>
       </c>
+      <c r="EC5" t="n">
+        <v>408.96</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -25098,6 +25329,9 @@
       <c r="EB6" t="n">
         <v>99.88</v>
       </c>
+      <c r="EC6" t="n">
+        <v>99.02</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -25500,6 +25734,9 @@
       <c r="EB7" t="n">
         <v>182.7561</v>
       </c>
+      <c r="EC7" t="n">
+        <v>177.82</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25902,6 +26139,9 @@
       <c r="EB8" t="n">
         <v>161.45</v>
       </c>
+      <c r="EC8" t="n">
+        <v>157.16</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -26301,6 +26541,9 @@
       <c r="EB9" t="n">
         <v>99.22</v>
       </c>
+      <c r="EC9" t="n">
+        <v>98.98999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26699,6 +26942,9 @@
       </c>
       <c r="EB10" t="n">
         <v>402.35</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>396.73</v>
       </c>
     </row>
   </sheetData>
@@ -26712,7 +26958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EB10"/>
+  <dimension ref="A1:EC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -26847,6 +27093,7 @@
     <col width="12" customWidth="1" min="130" max="130"/>
     <col width="12" customWidth="1" min="131" max="131"/>
     <col width="12" customWidth="1" min="132" max="132"/>
+    <col width="12" customWidth="1" min="133" max="133"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27250,6 +27497,9 @@
       <c r="EB1" s="1" t="n">
         <v>20260306</v>
       </c>
+      <c r="EC1" s="1" t="n">
+        <v>20260309</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -27649,6 +27899,9 @@
       <c r="EB2" t="n">
         <v>254.37</v>
       </c>
+      <c r="EC2" t="n">
+        <v>257.46</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -28048,6 +28301,9 @@
       <c r="EB3" t="n">
         <v>212.53</v>
       </c>
+      <c r="EC3" t="n">
+        <v>213.21</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -28447,6 +28703,9 @@
       <c r="EB4" t="n">
         <v>295.18</v>
       </c>
+      <c r="EC4" t="n">
+        <v>298.31</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -28849,6 +29108,9 @@
       <c r="EB5" t="n">
         <v>408.5101</v>
       </c>
+      <c r="EC5" t="n">
+        <v>408.96</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -29248,6 +29510,9 @@
       <c r="EB6" t="n">
         <v>97.40000000000001</v>
       </c>
+      <c r="EC6" t="n">
+        <v>99.02</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -29650,6 +29915,9 @@
       <c r="EB7" t="n">
         <v>176.8201</v>
       </c>
+      <c r="EC7" t="n">
+        <v>177.82</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -30052,6 +30320,9 @@
       <c r="EB8" t="n">
         <v>150.29</v>
       </c>
+      <c r="EC8" t="n">
+        <v>157.16</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -30451,6 +30722,9 @@
       <c r="EB9" t="n">
         <v>95.56</v>
       </c>
+      <c r="EC9" t="n">
+        <v>98.98999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -30849,6 +31123,9 @@
       </c>
       <c r="EB10" t="n">
         <v>394.21</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>396.73</v>
       </c>
     </row>
   </sheetData>
@@ -30862,7 +31139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EB10"/>
+  <dimension ref="A1:EC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -30997,6 +31274,7 @@
     <col width="12" customWidth="1" min="130" max="130"/>
     <col width="12" customWidth="1" min="131" max="131"/>
     <col width="12" customWidth="1" min="132" max="132"/>
+    <col width="12" customWidth="1" min="133" max="133"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31400,6 +31678,9 @@
       <c r="EB1" s="1" t="n">
         <v>20260306</v>
       </c>
+      <c r="EC1" s="1" t="n">
+        <v>20260309</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -31799,6 +32080,9 @@
       <c r="EB2" t="n">
         <v>257.46</v>
       </c>
+      <c r="EC2" t="n">
+        <v>257.46</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -32198,6 +32482,9 @@
       <c r="EB3" t="n">
         <v>213.21</v>
       </c>
+      <c r="EC3" t="n">
+        <v>213.21</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -32597,6 +32884,9 @@
       <c r="EB4" t="n">
         <v>298.52</v>
       </c>
+      <c r="EC4" t="n">
+        <v>298.31</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -32999,6 +33289,9 @@
       <c r="EB5" t="n">
         <v>408.96</v>
       </c>
+      <c r="EC5" t="n">
+        <v>408.96</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -33398,6 +33691,9 @@
       <c r="EB6" t="n">
         <v>99.02</v>
       </c>
+      <c r="EC6" t="n">
+        <v>99.02</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -33800,6 +34096,9 @@
       <c r="EB7" t="n">
         <v>177.82</v>
       </c>
+      <c r="EC7" t="n">
+        <v>177.82</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -34202,6 +34501,9 @@
       <c r="EB8" t="n">
         <v>157.16</v>
       </c>
+      <c r="EC8" t="n">
+        <v>157.16</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -34601,6 +34903,9 @@
       <c r="EB9" t="n">
         <v>98.98999999999999</v>
       </c>
+      <c r="EC9" t="n">
+        <v>98.98999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -34998,6 +35303,9 @@
         <v>406.5</v>
       </c>
       <c r="EB10" t="n">
+        <v>396.73</v>
+      </c>
+      <c r="EC10" t="n">
         <v>396.73</v>
       </c>
     </row>
@@ -35012,7 +35320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EB10"/>
+  <dimension ref="A1:EC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -35147,6 +35455,7 @@
     <col width="12" customWidth="1" min="130" max="130"/>
     <col width="12" customWidth="1" min="131" max="131"/>
     <col width="12" customWidth="1" min="132" max="132"/>
+    <col width="12" customWidth="1" min="133" max="133"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -35550,6 +35859,9 @@
       <c r="EB1" s="1" t="n">
         <v>20260306</v>
       </c>
+      <c r="EC1" s="1" t="n">
+        <v>20260309</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -35949,6 +36261,9 @@
       <c r="EB2" t="n">
         <v>41120042</v>
       </c>
+      <c r="EC2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -36348,6 +36663,9 @@
       <c r="EB3" t="n">
         <v>51152716</v>
       </c>
+      <c r="EC3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -36747,6 +37065,9 @@
       <c r="EB4" t="n">
         <v>25576916</v>
       </c>
+      <c r="EC4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -37149,6 +37470,9 @@
       <c r="EB5" t="n">
         <v>31123859</v>
       </c>
+      <c r="EC5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -37548,6 +37872,9 @@
       <c r="EB6" t="n">
         <v>41196294</v>
       </c>
+      <c r="EC6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -37950,6 +38277,9 @@
       <c r="EB7" t="n">
         <v>189021949</v>
       </c>
+      <c r="EC7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -38352,6 +38682,9 @@
       <c r="EB8" t="n">
         <v>74980855</v>
       </c>
+      <c r="EC8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -38751,6 +39084,9 @@
       <c r="EB9" t="n">
         <v>10826676</v>
       </c>
+      <c r="EC9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -39149,6 +39485,9 @@
       </c>
       <c r="EB10" t="n">
         <v>64054561</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -39162,7 +39501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DI10"/>
+  <dimension ref="A1:DJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -39278,6 +39617,7 @@
     <col width="10" customWidth="1" min="111" max="111"/>
     <col width="10" customWidth="1" min="112" max="112"/>
     <col width="10" customWidth="1" min="113" max="113"/>
+    <col width="10" customWidth="1" min="114" max="114"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -39624,6 +39964,9 @@
       <c r="DI1" s="1" t="n">
         <v>20260306</v>
       </c>
+      <c r="DJ1" s="1" t="n">
+        <v>20260309</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -39969,6 +40312,9 @@
       <c r="DI2" t="n">
         <v>8</v>
       </c>
+      <c r="DJ2" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -40314,6 +40660,9 @@
       <c r="DI3" t="n">
         <v>42</v>
       </c>
+      <c r="DJ3" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -40659,6 +41008,9 @@
       <c r="DI4" t="n">
         <v>0</v>
       </c>
+      <c r="DJ4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -41004,6 +41356,9 @@
       <c r="DI5" t="n">
         <v>84</v>
       </c>
+      <c r="DJ5" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -41349,6 +41704,9 @@
       <c r="DI6" t="n">
         <v>100</v>
       </c>
+      <c r="DJ6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -41694,6 +42052,9 @@
       <c r="DI7" t="n">
         <v>25</v>
       </c>
+      <c r="DJ7" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -42039,6 +42400,9 @@
       <c r="DI8" t="n">
         <v>100</v>
       </c>
+      <c r="DJ8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -42384,6 +42748,9 @@
       <c r="DI9" t="n">
         <v>92</v>
       </c>
+      <c r="DJ9" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -42727,6 +43094,9 @@
         <v>39</v>
       </c>
       <c r="DI10" t="n">
+        <v>12</v>
+      </c>
+      <c r="DJ10" t="n">
         <v>12</v>
       </c>
     </row>
@@ -42741,7 +43111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU10"/>
+  <dimension ref="A1:BV10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -42817,6 +43187,7 @@
     <col width="10" customWidth="1" min="71" max="71"/>
     <col width="10" customWidth="1" min="72" max="72"/>
     <col width="10" customWidth="1" min="73" max="73"/>
+    <col width="10" customWidth="1" min="74" max="74"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -43043,6 +43414,9 @@
       <c r="BU1" s="1" t="n">
         <v>20260306</v>
       </c>
+      <c r="BV1" s="1" t="n">
+        <v>20260309</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -43268,6 +43642,9 @@
       <c r="BU2" t="n">
         <v>34</v>
       </c>
+      <c r="BV2" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -43493,6 +43870,9 @@
       <c r="BU3" t="n">
         <v>30</v>
       </c>
+      <c r="BV3" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -43718,6 +44098,9 @@
       <c r="BU4" t="n">
         <v>4</v>
       </c>
+      <c r="BV4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -43943,6 +44326,9 @@
       <c r="BU5" t="n">
         <v>23</v>
       </c>
+      <c r="BV5" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -44168,6 +44554,9 @@
       <c r="BU6" t="n">
         <v>100</v>
       </c>
+      <c r="BV6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -44393,6 +44782,9 @@
       <c r="BU7" t="n">
         <v>28</v>
       </c>
+      <c r="BV7" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -44618,6 +45010,9 @@
       <c r="BU8" t="n">
         <v>43</v>
       </c>
+      <c r="BV8" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -44843,6 +45238,9 @@
       <c r="BU9" t="n">
         <v>97</v>
       </c>
+      <c r="BV9" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -45066,6 +45464,9 @@
         <v>14</v>
       </c>
       <c r="BU10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BV10" t="n">
         <v>4</v>
       </c>
     </row>
@@ -45080,7 +45481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DI10"/>
+  <dimension ref="A1:DJ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -45196,6 +45597,7 @@
     <col width="10" customWidth="1" min="111" max="111"/>
     <col width="10" customWidth="1" min="112" max="112"/>
     <col width="10" customWidth="1" min="113" max="113"/>
+    <col width="10" customWidth="1" min="114" max="114"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -45542,6 +45944,9 @@
       <c r="DI1" s="1" t="n">
         <v>20260306</v>
       </c>
+      <c r="DJ1" s="1" t="n">
+        <v>20260309</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -45887,6 +46292,9 @@
       <c r="DI2" t="n">
         <v>-78</v>
       </c>
+      <c r="DJ2" t="n">
+        <v>-70</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -46232,6 +46640,9 @@
       <c r="DI3" t="n">
         <v>24</v>
       </c>
+      <c r="DJ3" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -46577,6 +46988,9 @@
       <c r="DI4" t="n">
         <v>-67</v>
       </c>
+      <c r="DJ4" t="n">
+        <v>-66</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -46922,6 +47336,9 @@
       <c r="DI5" t="n">
         <v>57</v>
       </c>
+      <c r="DJ5" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -47267,6 +47684,9 @@
       <c r="DI6" t="n">
         <v>89</v>
       </c>
+      <c r="DJ6" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -47612,6 +48032,9 @@
       <c r="DI7" t="n">
         <v>-68</v>
       </c>
+      <c r="DJ7" t="n">
+        <v>-79</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -47957,6 +48380,9 @@
       <c r="DI8" t="n">
         <v>119</v>
       </c>
+      <c r="DJ8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -48302,6 +48728,9 @@
       <c r="DI9" t="n">
         <v>64</v>
       </c>
+      <c r="DJ9" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -48646,6 +49075,9 @@
       </c>
       <c r="DI10" t="n">
         <v>-65</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>-61</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -605,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV10"/>
+  <dimension ref="A1:BW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -682,6 +682,7 @@
     <col width="10" customWidth="1" min="72" max="72"/>
     <col width="10" customWidth="1" min="73" max="73"/>
     <col width="10" customWidth="1" min="74" max="74"/>
+    <col width="10" customWidth="1" min="75" max="75"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -911,6 +912,9 @@
       <c r="BV1" s="1" t="n">
         <v>20260309</v>
       </c>
+      <c r="BW1" s="1" t="n">
+        <v>20260310</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1139,6 +1143,9 @@
       <c r="BV2" t="n">
         <v>-50</v>
       </c>
+      <c r="BW2" t="n">
+        <v>-34</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1367,6 +1374,9 @@
       <c r="BV3" t="n">
         <v>-45</v>
       </c>
+      <c r="BW3" t="n">
+        <v>-43</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1595,6 +1605,9 @@
       <c r="BV4" t="n">
         <v>-81</v>
       </c>
+      <c r="BW4" t="n">
+        <v>-47</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1823,6 +1836,9 @@
       <c r="BV5" t="n">
         <v>-48</v>
       </c>
+      <c r="BW5" t="n">
+        <v>-46</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2051,6 +2067,9 @@
       <c r="BV6" t="n">
         <v>81</v>
       </c>
+      <c r="BW6" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2279,6 +2298,9 @@
       <c r="BV7" t="n">
         <v>-60</v>
       </c>
+      <c r="BW7" t="n">
+        <v>-18</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2507,6 +2529,9 @@
       <c r="BV8" t="n">
         <v>-11</v>
       </c>
+      <c r="BW8" t="n">
+        <v>-11</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2735,6 +2760,9 @@
       <c r="BV9" t="n">
         <v>65</v>
       </c>
+      <c r="BW9" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2962,6 +2990,9 @@
       </c>
       <c r="BV10" t="n">
         <v>-72</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>-66</v>
       </c>
     </row>
   </sheetData>
@@ -2975,7 +3006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DJ10"/>
+  <dimension ref="A1:DK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3092,6 +3123,7 @@
     <col width="12" customWidth="1" min="112" max="112"/>
     <col width="12" customWidth="1" min="113" max="113"/>
     <col width="12" customWidth="1" min="114" max="114"/>
+    <col width="12" customWidth="1" min="115" max="115"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3665,6 +3697,11 @@
           <t>20260309</t>
         </is>
       </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>20260310</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4964,6 +5001,9 @@
       <c r="DJ5" t="n">
         <v>102</v>
       </c>
+      <c r="DK5" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5624,6 +5664,9 @@
       <c r="DJ7" t="n">
         <v>96</v>
       </c>
+      <c r="DK7" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5971,6 +6014,9 @@
       </c>
       <c r="DJ8" t="n">
         <v>113</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>112</v>
       </c>
     </row>
     <row r="9">
@@ -6623,7 +6669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CQ10"/>
+  <dimension ref="A1:CR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6721,6 +6767,7 @@
     <col width="12" customWidth="1" min="93" max="93"/>
     <col width="12" customWidth="1" min="94" max="94"/>
     <col width="12" customWidth="1" min="95" max="95"/>
+    <col width="12" customWidth="1" min="96" max="96"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7199,6 +7246,11 @@
           <t>20260309</t>
         </is>
       </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>20260310</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8270,6 +8322,9 @@
       <c r="CQ5" t="n">
         <v>-63.6</v>
       </c>
+      <c r="CR5" t="n">
+        <v>-60.6</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8816,6 +8871,9 @@
       <c r="CQ7" t="n">
         <v>-16.86</v>
       </c>
+      <c r="CR7" t="n">
+        <v>-15.52</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9106,6 +9164,9 @@
       </c>
       <c r="CQ8" t="n">
         <v>-17.68</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>-8.390000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -9644,7 +9705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV10"/>
+  <dimension ref="A1:BW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9721,6 +9782,7 @@
     <col width="12" customWidth="1" min="72" max="72"/>
     <col width="12" customWidth="1" min="73" max="73"/>
     <col width="12" customWidth="1" min="74" max="74"/>
+    <col width="12" customWidth="1" min="75" max="75"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10094,6 +10156,11 @@
           <t>20260309</t>
         </is>
       </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>20260310</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10913,6 +10980,9 @@
       <c r="BV5" t="n">
         <v>0</v>
       </c>
+      <c r="BW5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11333,6 +11403,9 @@
       <c r="BV7" t="n">
         <v>0</v>
       </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11559,6 +11632,9 @@
         <v>133</v>
       </c>
       <c r="BV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11972,7 +12048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CZ10"/>
+  <dimension ref="A1:DA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12079,6 +12155,7 @@
     <col width="10" customWidth="1" min="102" max="102"/>
     <col width="10" customWidth="1" min="103" max="103"/>
     <col width="10" customWidth="1" min="104" max="104"/>
+    <col width="10" customWidth="1" min="105" max="105"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12398,6 +12475,9 @@
       <c r="CZ1" s="1" t="n">
         <v>20260309</v>
       </c>
+      <c r="DA1" s="1" t="n">
+        <v>20260310</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12716,6 +12796,9 @@
       <c r="CZ2" t="n">
         <v>-49</v>
       </c>
+      <c r="DA2" t="n">
+        <v>-40</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13034,6 +13117,9 @@
       <c r="CZ3" t="n">
         <v>-18</v>
       </c>
+      <c r="DA3" t="n">
+        <v>-14</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13352,6 +13438,9 @@
       <c r="CZ4" t="n">
         <v>-71</v>
       </c>
+      <c r="DA4" t="n">
+        <v>-40</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13670,6 +13759,9 @@
       <c r="CZ5" t="n">
         <v>-8</v>
       </c>
+      <c r="DA5" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13988,6 +14080,9 @@
       <c r="CZ6" t="n">
         <v>98</v>
       </c>
+      <c r="DA6" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14306,6 +14401,9 @@
       <c r="CZ7" t="n">
         <v>-60</v>
       </c>
+      <c r="DA7" t="n">
+        <v>-20</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14624,6 +14722,9 @@
       <c r="CZ8" t="n">
         <v>64</v>
       </c>
+      <c r="DA8" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14942,6 +15043,9 @@
       <c r="CZ9" t="n">
         <v>63</v>
       </c>
+      <c r="DA9" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15259,6 +15363,9 @@
       </c>
       <c r="CZ10" t="n">
         <v>-65</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>-57</v>
       </c>
     </row>
   </sheetData>
@@ -15272,7 +15379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15289,6 +15396,7 @@
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15338,6 +15446,9 @@
       <c r="N1" s="1" t="n">
         <v>20260309</v>
       </c>
+      <c r="O1" s="1" t="n">
+        <v>20260310</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15383,6 +15494,9 @@
       <c r="N2" t="n">
         <v>42</v>
       </c>
+      <c r="O2" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15428,6 +15542,9 @@
       <c r="N3" t="n">
         <v>26</v>
       </c>
+      <c r="O3" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15476,6 +15593,9 @@
       <c r="N4" t="n">
         <v>60</v>
       </c>
+      <c r="O4" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15524,6 +15644,9 @@
       <c r="N5" t="n">
         <v>16</v>
       </c>
+      <c r="O5" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15569,6 +15692,9 @@
       <c r="N6" t="n">
         <v>2</v>
       </c>
+      <c r="O6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15617,6 +15743,9 @@
       <c r="N7" t="n">
         <v>20</v>
       </c>
+      <c r="O7" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15665,6 +15794,9 @@
       <c r="N8" t="n">
         <v>36</v>
       </c>
+      <c r="O8" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15710,6 +15842,9 @@
       <c r="N9" t="n">
         <v>98</v>
       </c>
+      <c r="O9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15757,6 +15892,9 @@
       </c>
       <c r="N10" t="n">
         <v>6</v>
+      </c>
+      <c r="O10" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -15770,7 +15908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15787,6 +15925,7 @@
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15836,6 +15975,9 @@
       <c r="N1" s="1" t="n">
         <v>20260309</v>
       </c>
+      <c r="O1" s="1" t="n">
+        <v>20260310</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15881,6 +16023,9 @@
       <c r="N2" t="n">
         <v>-33</v>
       </c>
+      <c r="O2" t="n">
+        <v>-23</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15926,6 +16071,9 @@
       <c r="N3" t="n">
         <v>-57</v>
       </c>
+      <c r="O3" t="n">
+        <v>-55</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15974,6 +16122,9 @@
       <c r="N4" t="n">
         <v>5</v>
       </c>
+      <c r="O4" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16022,6 +16173,9 @@
       <c r="N5" t="n">
         <v>-78</v>
       </c>
+      <c r="O5" t="n">
+        <v>-76</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16067,6 +16221,9 @@
       <c r="N6" t="n">
         <v>-38</v>
       </c>
+      <c r="O6" t="n">
+        <v>-37</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16115,6 +16272,9 @@
       <c r="N7" t="n">
         <v>-53</v>
       </c>
+      <c r="O7" t="n">
+        <v>-19</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16163,6 +16323,9 @@
       <c r="N8" t="n">
         <v>-35</v>
       </c>
+      <c r="O8" t="n">
+        <v>-37</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16208,6 +16371,9 @@
       <c r="N9" t="n">
         <v>96</v>
       </c>
+      <c r="O9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16255,6 +16421,9 @@
       </c>
       <c r="N10" t="n">
         <v>-84</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-79</v>
       </c>
     </row>
   </sheetData>
@@ -16268,7 +16437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV10"/>
+  <dimension ref="A1:BW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -16345,6 +16514,7 @@
     <col width="12" customWidth="1" min="72" max="72"/>
     <col width="12" customWidth="1" min="73" max="73"/>
     <col width="12" customWidth="1" min="74" max="74"/>
+    <col width="12" customWidth="1" min="75" max="75"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16718,6 +16888,11 @@
           <t>20260309</t>
         </is>
       </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>20260310</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17537,6 +17712,9 @@
       <c r="BV5" t="n">
         <v>92</v>
       </c>
+      <c r="BW5" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17957,6 +18135,9 @@
       <c r="BV7" t="n">
         <v>96</v>
       </c>
+      <c r="BW7" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18183,6 +18364,9 @@
         <v>97</v>
       </c>
       <c r="BV8" t="n">
+        <v>97</v>
+      </c>
+      <c r="BW8" t="n">
         <v>97</v>
       </c>
     </row>
@@ -18596,7 +18780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EC10"/>
+  <dimension ref="A1:ED10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18732,6 +18916,7 @@
     <col width="12" customWidth="1" min="131" max="131"/>
     <col width="12" customWidth="1" min="132" max="132"/>
     <col width="12" customWidth="1" min="133" max="133"/>
+    <col width="12" customWidth="1" min="134" max="134"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19138,6 +19323,9 @@
       <c r="EC1" s="1" t="n">
         <v>20260309</v>
       </c>
+      <c r="ED1" s="1" t="n">
+        <v>20260310</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19540,6 +19728,9 @@
       <c r="EC2" t="n">
         <v>257.46</v>
       </c>
+      <c r="ED2" t="n">
+        <v>259.88</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19942,6 +20133,9 @@
       <c r="EC3" t="n">
         <v>213.21</v>
       </c>
+      <c r="ED3" t="n">
+        <v>213.49</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20344,6 +20538,9 @@
       <c r="EC4" t="n">
         <v>298.31</v>
       </c>
+      <c r="ED4" t="n">
+        <v>306.36</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20749,6 +20946,9 @@
       <c r="EC5" t="n">
         <v>408.96</v>
       </c>
+      <c r="ED5" t="n">
+        <v>409.41</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21151,6 +21351,9 @@
       <c r="EC6" t="n">
         <v>99.02</v>
       </c>
+      <c r="ED6" t="n">
+        <v>98.31999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21556,6 +21759,9 @@
       <c r="EC7" t="n">
         <v>177.82</v>
       </c>
+      <c r="ED7" t="n">
+        <v>182.65</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21961,6 +22167,9 @@
       <c r="EC8" t="n">
         <v>157.16</v>
       </c>
+      <c r="ED8" t="n">
+        <v>156.43</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22363,6 +22572,9 @@
       <c r="EC9" t="n">
         <v>98.98999999999999</v>
       </c>
+      <c r="ED9" t="n">
+        <v>99.77</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22764,6 +22976,9 @@
       </c>
       <c r="EC10" t="n">
         <v>396.73</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>398.68</v>
       </c>
     </row>
   </sheetData>
@@ -22777,7 +22992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EC10"/>
+  <dimension ref="A1:ED10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22913,6 +23128,7 @@
     <col width="12" customWidth="1" min="131" max="131"/>
     <col width="12" customWidth="1" min="132" max="132"/>
     <col width="12" customWidth="1" min="133" max="133"/>
+    <col width="12" customWidth="1" min="134" max="134"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23319,6 +23535,9 @@
       <c r="EC1" s="1" t="n">
         <v>20260309</v>
       </c>
+      <c r="ED1" s="1" t="n">
+        <v>20260310</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23721,6 +23940,9 @@
       <c r="EC2" t="n">
         <v>257.46</v>
       </c>
+      <c r="ED2" t="n">
+        <v>259.88</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -24123,6 +24345,9 @@
       <c r="EC3" t="n">
         <v>213.21</v>
       </c>
+      <c r="ED3" t="n">
+        <v>213.49</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -24525,6 +24750,9 @@
       <c r="EC4" t="n">
         <v>298.31</v>
       </c>
+      <c r="ED4" t="n">
+        <v>306.36</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24930,6 +25158,9 @@
       <c r="EC5" t="n">
         <v>408.96</v>
       </c>
+      <c r="ED5" t="n">
+        <v>409.41</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -25332,6 +25563,9 @@
       <c r="EC6" t="n">
         <v>99.02</v>
       </c>
+      <c r="ED6" t="n">
+        <v>98.31999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -25737,6 +25971,9 @@
       <c r="EC7" t="n">
         <v>177.82</v>
       </c>
+      <c r="ED7" t="n">
+        <v>182.65</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -26142,6 +26379,9 @@
       <c r="EC8" t="n">
         <v>157.16</v>
       </c>
+      <c r="ED8" t="n">
+        <v>156.43</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -26544,6 +26784,9 @@
       <c r="EC9" t="n">
         <v>98.98999999999999</v>
       </c>
+      <c r="ED9" t="n">
+        <v>99.77</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -26945,6 +27188,9 @@
       </c>
       <c r="EC10" t="n">
         <v>396.73</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>398.68</v>
       </c>
     </row>
   </sheetData>
@@ -26958,7 +27204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EC10"/>
+  <dimension ref="A1:ED10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -27094,6 +27340,7 @@
     <col width="12" customWidth="1" min="131" max="131"/>
     <col width="12" customWidth="1" min="132" max="132"/>
     <col width="12" customWidth="1" min="133" max="133"/>
+    <col width="12" customWidth="1" min="134" max="134"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27500,6 +27747,9 @@
       <c r="EC1" s="1" t="n">
         <v>20260309</v>
       </c>
+      <c r="ED1" s="1" t="n">
+        <v>20260310</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -27902,6 +28152,9 @@
       <c r="EC2" t="n">
         <v>257.46</v>
       </c>
+      <c r="ED2" t="n">
+        <v>259.88</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -28304,6 +28557,9 @@
       <c r="EC3" t="n">
         <v>213.21</v>
       </c>
+      <c r="ED3" t="n">
+        <v>213.49</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -28706,6 +28962,9 @@
       <c r="EC4" t="n">
         <v>298.31</v>
       </c>
+      <c r="ED4" t="n">
+        <v>306.36</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -29111,6 +29370,9 @@
       <c r="EC5" t="n">
         <v>408.96</v>
       </c>
+      <c r="ED5" t="n">
+        <v>409.41</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -29513,6 +29775,9 @@
       <c r="EC6" t="n">
         <v>99.02</v>
       </c>
+      <c r="ED6" t="n">
+        <v>98.31999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -29918,6 +30183,9 @@
       <c r="EC7" t="n">
         <v>177.82</v>
       </c>
+      <c r="ED7" t="n">
+        <v>182.65</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -30323,6 +30591,9 @@
       <c r="EC8" t="n">
         <v>157.16</v>
       </c>
+      <c r="ED8" t="n">
+        <v>156.43</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -30725,6 +30996,9 @@
       <c r="EC9" t="n">
         <v>98.98999999999999</v>
       </c>
+      <c r="ED9" t="n">
+        <v>99.77</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -31126,6 +31400,9 @@
       </c>
       <c r="EC10" t="n">
         <v>396.73</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>398.68</v>
       </c>
     </row>
   </sheetData>
@@ -31139,7 +31416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EC10"/>
+  <dimension ref="A1:ED10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -31275,6 +31552,7 @@
     <col width="12" customWidth="1" min="131" max="131"/>
     <col width="12" customWidth="1" min="132" max="132"/>
     <col width="12" customWidth="1" min="133" max="133"/>
+    <col width="12" customWidth="1" min="134" max="134"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31681,6 +31959,9 @@
       <c r="EC1" s="1" t="n">
         <v>20260309</v>
       </c>
+      <c r="ED1" s="1" t="n">
+        <v>20260310</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -32083,6 +32364,9 @@
       <c r="EC2" t="n">
         <v>257.46</v>
       </c>
+      <c r="ED2" t="n">
+        <v>259.88</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -32485,6 +32769,9 @@
       <c r="EC3" t="n">
         <v>213.21</v>
       </c>
+      <c r="ED3" t="n">
+        <v>213.49</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -32887,6 +33174,9 @@
       <c r="EC4" t="n">
         <v>298.31</v>
       </c>
+      <c r="ED4" t="n">
+        <v>306.36</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -33292,6 +33582,9 @@
       <c r="EC5" t="n">
         <v>408.96</v>
       </c>
+      <c r="ED5" t="n">
+        <v>409.41</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -33694,6 +33987,9 @@
       <c r="EC6" t="n">
         <v>99.02</v>
       </c>
+      <c r="ED6" t="n">
+        <v>98.31999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -34099,6 +34395,9 @@
       <c r="EC7" t="n">
         <v>177.82</v>
       </c>
+      <c r="ED7" t="n">
+        <v>182.65</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -34504,6 +34803,9 @@
       <c r="EC8" t="n">
         <v>157.16</v>
       </c>
+      <c r="ED8" t="n">
+        <v>156.43</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -34906,6 +35208,9 @@
       <c r="EC9" t="n">
         <v>98.98999999999999</v>
       </c>
+      <c r="ED9" t="n">
+        <v>99.77</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -35307,6 +35612,9 @@
       </c>
       <c r="EC10" t="n">
         <v>396.73</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>398.68</v>
       </c>
     </row>
   </sheetData>
@@ -35320,7 +35628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EC10"/>
+  <dimension ref="A1:ED10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -35456,6 +35764,7 @@
     <col width="12" customWidth="1" min="131" max="131"/>
     <col width="12" customWidth="1" min="132" max="132"/>
     <col width="12" customWidth="1" min="133" max="133"/>
+    <col width="12" customWidth="1" min="134" max="134"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -35862,6 +36171,9 @@
       <c r="EC1" s="1" t="n">
         <v>20260309</v>
       </c>
+      <c r="ED1" s="1" t="n">
+        <v>20260310</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -36264,6 +36576,9 @@
       <c r="EC2" t="n">
         <v>0</v>
       </c>
+      <c r="ED2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -36666,6 +36981,9 @@
       <c r="EC3" t="n">
         <v>0</v>
       </c>
+      <c r="ED3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -37068,6 +37386,9 @@
       <c r="EC4" t="n">
         <v>0</v>
       </c>
+      <c r="ED4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -37473,6 +37794,9 @@
       <c r="EC5" t="n">
         <v>0</v>
       </c>
+      <c r="ED5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -37875,6 +38199,9 @@
       <c r="EC6" t="n">
         <v>0</v>
       </c>
+      <c r="ED6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -38280,6 +38607,9 @@
       <c r="EC7" t="n">
         <v>0</v>
       </c>
+      <c r="ED7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -38685,6 +39015,9 @@
       <c r="EC8" t="n">
         <v>0</v>
       </c>
+      <c r="ED8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -39087,6 +39420,9 @@
       <c r="EC9" t="n">
         <v>0</v>
       </c>
+      <c r="ED9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -39487,6 +39823,9 @@
         <v>64054561</v>
       </c>
       <c r="EC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -39501,7 +39840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DJ10"/>
+  <dimension ref="A1:DK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -39618,6 +39957,7 @@
     <col width="10" customWidth="1" min="112" max="112"/>
     <col width="10" customWidth="1" min="113" max="113"/>
     <col width="10" customWidth="1" min="114" max="114"/>
+    <col width="10" customWidth="1" min="115" max="115"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -39967,6 +40307,9 @@
       <c r="DJ1" s="1" t="n">
         <v>20260309</v>
       </c>
+      <c r="DK1" s="1" t="n">
+        <v>20260310</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -40315,6 +40658,9 @@
       <c r="DJ2" t="n">
         <v>8</v>
       </c>
+      <c r="DK2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -40663,6 +41009,9 @@
       <c r="DJ3" t="n">
         <v>60</v>
       </c>
+      <c r="DK3" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -41011,6 +41360,9 @@
       <c r="DJ4" t="n">
         <v>0</v>
       </c>
+      <c r="DK4" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -41359,6 +41711,9 @@
       <c r="DJ5" t="n">
         <v>84</v>
       </c>
+      <c r="DK5" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -41707,6 +42062,9 @@
       <c r="DJ6" t="n">
         <v>100</v>
       </c>
+      <c r="DK6" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -42055,6 +42413,9 @@
       <c r="DJ7" t="n">
         <v>3</v>
       </c>
+      <c r="DK7" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -42403,6 +42764,9 @@
       <c r="DJ8" t="n">
         <v>100</v>
       </c>
+      <c r="DK8" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -42751,6 +43115,9 @@
       <c r="DJ9" t="n">
         <v>92</v>
       </c>
+      <c r="DK9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -43098,6 +43465,9 @@
       </c>
       <c r="DJ10" t="n">
         <v>12</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -43111,7 +43481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV10"/>
+  <dimension ref="A1:BW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -43188,6 +43558,7 @@
     <col width="10" customWidth="1" min="72" max="72"/>
     <col width="10" customWidth="1" min="73" max="73"/>
     <col width="10" customWidth="1" min="74" max="74"/>
+    <col width="10" customWidth="1" min="75" max="75"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -43417,6 +43788,9 @@
       <c r="BV1" s="1" t="n">
         <v>20260309</v>
       </c>
+      <c r="BW1" s="1" t="n">
+        <v>20260310</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -43645,6 +44019,9 @@
       <c r="BV2" t="n">
         <v>34</v>
       </c>
+      <c r="BW2" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -43873,6 +44250,9 @@
       <c r="BV3" t="n">
         <v>30</v>
       </c>
+      <c r="BW3" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -44101,6 +44481,9 @@
       <c r="BV4" t="n">
         <v>4</v>
       </c>
+      <c r="BW4" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -44329,6 +44712,9 @@
       <c r="BV5" t="n">
         <v>24</v>
       </c>
+      <c r="BW5" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -44557,6 +44943,9 @@
       <c r="BV6" t="n">
         <v>100</v>
       </c>
+      <c r="BW6" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -44785,6 +45174,9 @@
       <c r="BV7" t="n">
         <v>28</v>
       </c>
+      <c r="BW7" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -45013,6 +45405,9 @@
       <c r="BV8" t="n">
         <v>43</v>
       </c>
+      <c r="BW8" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -45241,6 +45636,9 @@
       <c r="BV9" t="n">
         <v>97</v>
       </c>
+      <c r="BW9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -45468,6 +45866,9 @@
       </c>
       <c r="BV10" t="n">
         <v>4</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -45481,7 +45882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DJ10"/>
+  <dimension ref="A1:DK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -45598,6 +45999,7 @@
     <col width="10" customWidth="1" min="112" max="112"/>
     <col width="10" customWidth="1" min="113" max="113"/>
     <col width="10" customWidth="1" min="114" max="114"/>
+    <col width="10" customWidth="1" min="115" max="115"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -45947,6 +46349,9 @@
       <c r="DJ1" s="1" t="n">
         <v>20260309</v>
       </c>
+      <c r="DK1" s="1" t="n">
+        <v>20260310</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -46295,6 +46700,9 @@
       <c r="DJ2" t="n">
         <v>-70</v>
       </c>
+      <c r="DK2" t="n">
+        <v>-48</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -46643,6 +47051,9 @@
       <c r="DJ3" t="n">
         <v>42</v>
       </c>
+      <c r="DK3" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -46991,6 +47402,9 @@
       <c r="DJ4" t="n">
         <v>-66</v>
       </c>
+      <c r="DK4" t="n">
+        <v>-16</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -47339,6 +47753,9 @@
       <c r="DJ5" t="n">
         <v>51</v>
       </c>
+      <c r="DK5" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -47687,6 +48104,9 @@
       <c r="DJ6" t="n">
         <v>78</v>
       </c>
+      <c r="DK6" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -48035,6 +48455,9 @@
       <c r="DJ7" t="n">
         <v>-79</v>
       </c>
+      <c r="DK7" t="n">
+        <v>-30</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -48383,6 +48806,9 @@
       <c r="DJ8" t="n">
         <v>100</v>
       </c>
+      <c r="DK8" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -48731,6 +49157,9 @@
       <c r="DJ9" t="n">
         <v>58</v>
       </c>
+      <c r="DK9" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -49078,6 +49507,9 @@
       </c>
       <c r="DJ10" t="n">
         <v>-61</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>-52</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_Individual.xlsx
+++ b/US_Stocks_Individual.xlsx
@@ -605,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW10"/>
+  <dimension ref="A1:BX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -683,6 +683,7 @@
     <col width="10" customWidth="1" min="73" max="73"/>
     <col width="10" customWidth="1" min="74" max="74"/>
     <col width="10" customWidth="1" min="75" max="75"/>
+    <col width="10" customWidth="1" min="76" max="76"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -915,6 +916,9 @@
       <c r="BW1" s="1" t="n">
         <v>20260310</v>
       </c>
+      <c r="BX1" s="1" t="n">
+        <v>20260311</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1146,6 +1150,9 @@
       <c r="BW2" t="n">
         <v>-34</v>
       </c>
+      <c r="BX2" t="n">
+        <v>-28</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1377,6 +1384,9 @@
       <c r="BW3" t="n">
         <v>-43</v>
       </c>
+      <c r="BX3" t="n">
+        <v>-39</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1608,6 +1618,9 @@
       <c r="BW4" t="n">
         <v>-47</v>
       </c>
+      <c r="BX4" t="n">
+        <v>-43</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1839,6 +1852,9 @@
       <c r="BW5" t="n">
         <v>-46</v>
       </c>
+      <c r="BX5" t="n">
+        <v>-49</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2070,6 +2086,9 @@
       <c r="BW6" t="n">
         <v>76</v>
       </c>
+      <c r="BX6" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2301,6 +2320,9 @@
       <c r="BW7" t="n">
         <v>-18</v>
       </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2532,6 +2554,9 @@
       <c r="BW8" t="n">
         <v>-11</v>
       </c>
+      <c r="BX8" t="n">
+        <v>-23</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2763,6 +2788,9 @@
       <c r="BW9" t="n">
         <v>70</v>
       </c>
+      <c r="BX9" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2993,6 +3021,9 @@
       </c>
       <c r="BW10" t="n">
         <v>-66</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>-62</v>
       </c>
     </row>
   </sheetData>
@@ -3006,7 +3037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DK10"/>
+  <dimension ref="A1:DL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3124,6 +3155,7 @@
     <col width="12" customWidth="1" min="113" max="113"/>
     <col width="12" customWidth="1" min="114" max="114"/>
     <col width="12" customWidth="1" min="115" max="115"/>
+    <col width="12" customWidth="1" min="116" max="116"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3702,6 +3734,11 @@
           <t>20260310</t>
         </is>
       </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>20260311</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5004,6 +5041,9 @@
       <c r="DK5" t="n">
         <v>102</v>
       </c>
+      <c r="DL5" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5667,6 +5707,9 @@
       <c r="DK7" t="n">
         <v>98</v>
       </c>
+      <c r="DL7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6017,6 +6060,9 @@
       </c>
       <c r="DK8" t="n">
         <v>112</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>107</v>
       </c>
     </row>
     <row r="9">
@@ -6669,7 +6715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR10"/>
+  <dimension ref="A1:CS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6768,6 +6814,7 @@
     <col width="12" customWidth="1" min="94" max="94"/>
     <col width="12" customWidth="1" min="95" max="95"/>
     <col width="12" customWidth="1" min="96" max="96"/>
+    <col width="12" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7251,6 +7298,11 @@
           <t>20260310</t>
         </is>
       </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>20260311</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8325,6 +8377,9 @@
       <c r="CR5" t="n">
         <v>-60.6</v>
       </c>
+      <c r="CS5" t="n">
+        <v>-60.92</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8874,6 +8929,9 @@
       <c r="CR7" t="n">
         <v>-15.52</v>
       </c>
+      <c r="CS7" t="n">
+        <v>-16.37</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9167,6 +9225,9 @@
       </c>
       <c r="CR8" t="n">
         <v>-8.390000000000001</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>-3.3</v>
       </c>
     </row>
     <row r="9">
@@ -9705,7 +9766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW10"/>
+  <dimension ref="A1:BX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9783,6 +9844,7 @@
     <col width="12" customWidth="1" min="73" max="73"/>
     <col width="12" customWidth="1" min="74" max="74"/>
     <col width="12" customWidth="1" min="75" max="75"/>
+    <col width="12" customWidth="1" min="76" max="76"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10161,6 +10223,11 @@
           <t>20260310</t>
         </is>
       </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>20260311</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10983,6 +11050,9 @@
       <c r="BW5" t="n">
         <v>0</v>
       </c>
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11406,6 +11476,9 @@
       <c r="BW7" t="n">
         <v>0</v>
       </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11635,6 +11708,9 @@
         <v>0</v>
       </c>
       <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12048,7 +12124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DA10"/>
+  <dimension ref="A1:DB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12156,6 +12232,7 @@
     <col width="10" customWidth="1" min="103" max="103"/>
     <col width="10" customWidth="1" min="104" max="104"/>
     <col width="10" customWidth="1" min="105" max="105"/>
+    <col width="10" customWidth="1" min="106" max="106"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12478,6 +12555,9 @@
       <c r="DA1" s="1" t="n">
         <v>20260310</v>
       </c>
+      <c r="DB1" s="1" t="n">
+        <v>20260311</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12799,6 +12879,9 @@
       <c r="DA2" t="n">
         <v>-40</v>
       </c>
+      <c r="DB2" t="n">
+        <v>-35</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13120,6 +13203,9 @@
       <c r="DA3" t="n">
         <v>-14</v>
       </c>
+      <c r="DB3" t="n">
+        <v>-9</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13441,6 +13527,9 @@
       <c r="DA4" t="n">
         <v>-40</v>
       </c>
+      <c r="DB4" t="n">
+        <v>-35</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13762,6 +13851,9 @@
       <c r="DA5" t="n">
         <v>-3</v>
       </c>
+      <c r="DB5" t="n">
+        <v>-7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14083,6 +14175,9 @@
       <c r="DA6" t="n">
         <v>86</v>
       </c>
+      <c r="DB6" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14404,6 +14499,9 @@
       <c r="DA7" t="n">
         <v>-20</v>
       </c>
+      <c r="DB7" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14725,6 +14823,9 @@
       <c r="DA8" t="n">
         <v>66</v>
       </c>
+      <c r="DB8" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15046,6 +15147,9 @@
       <c r="DA9" t="n">
         <v>77</v>
       </c>
+      <c r="DB9" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15366,6 +15470,9 @@
       </c>
       <c r="DA10" t="n">
         <v>-57</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>-53</v>
       </c>
     </row>
   </sheetData>
@@ -15379,7 +15486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15397,6 +15504,7 @@
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15449,6 +15557,9 @@
       <c r="O1" s="1" t="n">
         <v>20260310</v>
       </c>
+      <c r="P1" s="1" t="n">
+        <v>20260311</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15497,6 +15608,9 @@
       <c r="O2" t="n">
         <v>46</v>
       </c>
+      <c r="P2" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15545,6 +15659,9 @@
       <c r="O3" t="n">
         <v>27</v>
       </c>
+      <c r="P3" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15596,6 +15713,9 @@
       <c r="O4" t="n">
         <v>68</v>
       </c>
+      <c r="P4" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15647,6 +15767,9 @@
       <c r="O5" t="n">
         <v>16</v>
       </c>
+      <c r="P5" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15695,6 +15818,9 @@
       <c r="O6" t="n">
         <v>2</v>
       </c>
+      <c r="P6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15746,6 +15872,9 @@
       <c r="O7" t="n">
         <v>34</v>
       </c>
+      <c r="P7" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15797,6 +15926,9 @@
       <c r="O8" t="n">
         <v>35</v>
       </c>
+      <c r="P8" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15845,6 +15977,9 @@
       <c r="O9" t="n">
         <v>100</v>
       </c>
+      <c r="P9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15894,6 +16029,9 @@
         <v>6</v>
       </c>
       <c r="O10" t="n">
+        <v>8</v>
+      </c>
+      <c r="P10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -15908,7 +16046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15926,6 +16064,7 @@
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15978,6 +16117,9 @@
       <c r="O1" s="1" t="n">
         <v>20260310</v>
       </c>
+      <c r="P1" s="1" t="n">
+        <v>20260311</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16026,6 +16168,9 @@
       <c r="O2" t="n">
         <v>-23</v>
       </c>
+      <c r="P2" t="n">
+        <v>-20</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16074,6 +16219,9 @@
       <c r="O3" t="n">
         <v>-55</v>
       </c>
+      <c r="P3" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16125,6 +16273,9 @@
       <c r="O4" t="n">
         <v>18</v>
       </c>
+      <c r="P4" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16176,6 +16327,9 @@
       <c r="O5" t="n">
         <v>-76</v>
       </c>
+      <c r="P5" t="n">
+        <v>-79</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16224,6 +16378,9 @@
       <c r="O6" t="n">
         <v>-37</v>
       </c>
+      <c r="P6" t="n">
+        <v>-37</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16275,6 +16432,9 @@
       <c r="O7" t="n">
         <v>-19</v>
       </c>
+      <c r="P7" t="n">
+        <v>-4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16326,6 +16486,9 @@
       <c r="O8" t="n">
         <v>-37</v>
       </c>
+      <c r="P8" t="n">
+        <v>-50</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16374,6 +16537,9 @@
       <c r="O9" t="n">
         <v>100</v>
       </c>
+      <c r="P9" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16424,6 +16590,9 @@
       </c>
       <c r="O10" t="n">
         <v>-79</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-77</v>
       </c>
     </row>
   </sheetData>
@@ -16437,7 +16606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW10"/>
+  <dimension ref="A1:BX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -16515,6 +16684,7 @@
     <col width="12" customWidth="1" min="73" max="73"/>
     <col width="12" customWidth="1" min="74" max="74"/>
     <col width="12" customWidth="1" min="75" max="75"/>
+    <col width="12" customWidth="1" min="76" max="76"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16893,6 +17063,11 @@
           <t>20260310</t>
         </is>
       </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>20260311</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17715,6 +17890,9 @@
       <c r="BW5" t="n">
         <v>92</v>
       </c>
+      <c r="BX5" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18138,6 +18316,9 @@
       <c r="BW7" t="n">
         <v>99</v>
       </c>
+      <c r="BX7" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18368,6 +18549,9 @@
       </c>
       <c r="BW8" t="n">
         <v>97</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>94</v>
       </c>
     </row>
     <row r="9">
@@ -18780,7 +18964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:ED10"/>
+  <dimension ref="A1:EE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -18917,6 +19101,7 @@
     <col width="12" customWidth="1" min="132" max="132"/>
     <col width="12" customWidth="1" min="133" max="133"/>
     <col width="12" customWidth="1" min="134" max="134"/>
+    <col width="12" customWidth="1" min="135" max="135"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19326,6 +19511,9 @@
       <c r="ED1" s="1" t="n">
         <v>20260310</v>
       </c>
+      <c r="EE1" s="1" t="n">
+        <v>20260311</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19731,6 +19919,9 @@
       <c r="ED2" t="n">
         <v>259.88</v>
       </c>
+      <c r="EE2" t="n">
+        <v>260.83</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20136,6 +20327,9 @@
       <c r="ED3" t="n">
         <v>213.49</v>
       </c>
+      <c r="EE3" t="n">
+        <v>214.33</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20541,6 +20735,9 @@
       <c r="ED4" t="n">
         <v>306.36</v>
       </c>
+      <c r="EE4" t="n">
+        <v>307.04</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20949,6 +21146,9 @@
       <c r="ED5" t="n">
         <v>409.41</v>
       </c>
+      <c r="EE5" t="n">
+        <v>405.76</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21354,6 +21554,9 @@
       <c r="ED6" t="n">
         <v>98.31999999999999</v>
       </c>
+      <c r="EE6" t="n">
+        <v>96.94</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21762,6 +21965,9 @@
       <c r="ED7" t="n">
         <v>182.65</v>
       </c>
+      <c r="EE7" t="n">
+        <v>184.77</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22170,6 +22376,9 @@
       <c r="ED8" t="n">
         <v>156.43</v>
       </c>
+      <c r="EE8" t="n">
+        <v>151.14</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22575,6 +22784,9 @@
       <c r="ED9" t="n">
         <v>99.77</v>
       </c>
+      <c r="EE9" t="n">
+        <v>100.77</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22979,6 +23191,9 @@
       </c>
       <c r="ED10" t="n">
         <v>398.68</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>399.235</v>
       </c>
     </row>
   </sheetData>
@@ -22992,7 +23207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:ED10"/>
+  <dimension ref="A1:EE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23129,6 +23344,7 @@
     <col width="12" customWidth="1" min="132" max="132"/>
     <col width="12" customWidth="1" min="133" max="133"/>
     <col width="12" customWidth="1" min="134" max="134"/>
+    <col width="12" customWidth="1" min="135" max="135"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23538,6 +23754,9 @@
       <c r="ED1" s="1" t="n">
         <v>20260310</v>
       </c>
+      <c r="EE1" s="1" t="n">
+        <v>20260311</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23943,6 +24162,9 @@
       <c r="ED2" t="n">
         <v>259.88</v>
       </c>
+      <c r="EE2" t="n">
+        <v>260.83</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -24348,6 +24570,9 @@
       <c r="ED3" t="n">
         <v>213.49</v>
       </c>
+      <c r="EE3" t="n">
+        <v>214.33</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -24753,6 +24978,9 @@
       <c r="ED4" t="n">
         <v>306.36</v>
       </c>
+      <c r="EE4" t="n">
+        <v>307.04</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -25161,6 +25389,9 @@
       <c r="ED5" t="n">
         <v>409.41</v>
       </c>
+      <c r="EE5" t="n">
+        <v>405.76</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -25566,6 +25797,9 @@
       <c r="ED6" t="n">
         <v>98.31999999999999</v>
       </c>
+      <c r="EE6" t="n">
+        <v>96.94</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -25974,6 +26208,9 @@
       <c r="ED7" t="n">
         <v>182.65</v>
       </c>
+      <c r="EE7" t="n">
+        <v>184.77</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -26382,6 +26619,9 @@
       <c r="ED8" t="n">
         <v>156.43</v>
       </c>
+      <c r="EE8" t="n">
+        <v>151.14</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -26787,6 +27027,9 @@
       <c r="ED9" t="n">
         <v>99.77</v>
       </c>
+      <c r="EE9" t="n">
+        <v>100.77</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -27191,6 +27434,9 @@
       </c>
       <c r="ED10" t="n">
         <v>398.68</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>399.235</v>
       </c>
     </row>
   </sheetData>
@@ -27204,7 +27450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:ED10"/>
+  <dimension ref="A1:EE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -27341,6 +27587,7 @@
     <col width="12" customWidth="1" min="132" max="132"/>
     <col width="12" customWidth="1" min="133" max="133"/>
     <col width="12" customWidth="1" min="134" max="134"/>
+    <col width="12" customWidth="1" min="135" max="135"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27750,6 +27997,9 @@
       <c r="ED1" s="1" t="n">
         <v>20260310</v>
       </c>
+      <c r="EE1" s="1" t="n">
+        <v>20260311</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -28155,6 +28405,9 @@
       <c r="ED2" t="n">
         <v>259.88</v>
       </c>
+      <c r="EE2" t="n">
+        <v>260.83</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -28560,6 +28813,9 @@
       <c r="ED3" t="n">
         <v>213.49</v>
       </c>
+      <c r="EE3" t="n">
+        <v>214.33</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -28965,6 +29221,9 @@
       <c r="ED4" t="n">
         <v>306.36</v>
       </c>
+      <c r="EE4" t="n">
+        <v>307.04</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -29373,6 +29632,9 @@
       <c r="ED5" t="n">
         <v>409.41</v>
       </c>
+      <c r="EE5" t="n">
+        <v>405.76</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -29778,6 +30040,9 @@
       <c r="ED6" t="n">
         <v>98.31999999999999</v>
       </c>
+      <c r="EE6" t="n">
+        <v>96.94</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -30186,6 +30451,9 @@
       <c r="ED7" t="n">
         <v>182.65</v>
       </c>
+      <c r="EE7" t="n">
+        <v>184.77</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -30594,6 +30862,9 @@
       <c r="ED8" t="n">
         <v>156.43</v>
       </c>
+      <c r="EE8" t="n">
+        <v>151.14</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -30999,6 +31270,9 @@
       <c r="ED9" t="n">
         <v>99.77</v>
       </c>
+      <c r="EE9" t="n">
+        <v>100.77</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -31403,6 +31677,9 @@
       </c>
       <c r="ED10" t="n">
         <v>398.68</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>399.235</v>
       </c>
     </row>
   </sheetData>
@@ -31416,7 +31693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:ED10"/>
+  <dimension ref="A1:EE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -31553,6 +31830,7 @@
     <col width="12" customWidth="1" min="132" max="132"/>
     <col width="12" customWidth="1" min="133" max="133"/>
     <col width="12" customWidth="1" min="134" max="134"/>
+    <col width="12" customWidth="1" min="135" max="135"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31962,6 +32240,9 @@
       <c r="ED1" s="1" t="n">
         <v>20260310</v>
       </c>
+      <c r="EE1" s="1" t="n">
+        <v>20260311</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -32367,6 +32648,9 @@
       <c r="ED2" t="n">
         <v>259.88</v>
       </c>
+      <c r="EE2" t="n">
+        <v>260.83</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -32772,6 +33056,9 @@
       <c r="ED3" t="n">
         <v>213.49</v>
       </c>
+      <c r="EE3" t="n">
+        <v>214.33</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -33177,6 +33464,9 @@
       <c r="ED4" t="n">
         <v>306.36</v>
       </c>
+      <c r="EE4" t="n">
+        <v>307.04</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -33585,6 +33875,9 @@
       <c r="ED5" t="n">
         <v>409.41</v>
       </c>
+      <c r="EE5" t="n">
+        <v>405.76</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -33990,6 +34283,9 @@
       <c r="ED6" t="n">
         <v>98.31999999999999</v>
       </c>
+      <c r="EE6" t="n">
+        <v>96.94</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -34398,6 +34694,9 @@
       <c r="ED7" t="n">
         <v>182.65</v>
       </c>
+      <c r="EE7" t="n">
+        <v>184.77</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -34806,6 +35105,9 @@
       <c r="ED8" t="n">
         <v>156.43</v>
       </c>
+      <c r="EE8" t="n">
+        <v>151.14</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -35211,6 +35513,9 @@
       <c r="ED9" t="n">
         <v>99.77</v>
       </c>
+      <c r="EE9" t="n">
+        <v>100.77</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -35615,6 +35920,9 @@
       </c>
       <c r="ED10" t="n">
         <v>398.68</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>399.235</v>
       </c>
     </row>
   </sheetData>
@@ -35628,7 +35936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:ED10"/>
+  <dimension ref="A1:EE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -35765,6 +36073,7 @@
     <col width="12" customWidth="1" min="132" max="132"/>
     <col width="12" customWidth="1" min="133" max="133"/>
     <col width="12" customWidth="1" min="134" max="134"/>
+    <col width="12" customWidth="1" min="135" max="135"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -36174,6 +36483,9 @@
       <c r="ED1" s="1" t="n">
         <v>20260310</v>
       </c>
+      <c r="EE1" s="1" t="n">
+        <v>20260311</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -36579,6 +36891,9 @@
       <c r="ED2" t="n">
         <v>0</v>
       </c>
+      <c r="EE2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -36984,6 +37299,9 @@
       <c r="ED3" t="n">
         <v>0</v>
       </c>
+      <c r="EE3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -37389,6 +37707,9 @@
       <c r="ED4" t="n">
         <v>0</v>
       </c>
+      <c r="EE4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -37797,6 +38118,9 @@
       <c r="ED5" t="n">
         <v>0</v>
       </c>
+      <c r="EE5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -38202,6 +38526,9 @@
       <c r="ED6" t="n">
         <v>0</v>
       </c>
+      <c r="EE6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -38610,6 +38937,9 @@
       <c r="ED7" t="n">
         <v>0</v>
       </c>
+      <c r="EE7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -39018,6 +39348,9 @@
       <c r="ED8" t="n">
         <v>0</v>
       </c>
+      <c r="EE8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -39423,6 +39756,9 @@
       <c r="ED9" t="n">
         <v>0</v>
       </c>
+      <c r="EE9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -39826,6 +40162,9 @@
         <v>0</v>
       </c>
       <c r="ED10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -39840,7 +40179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DK10"/>
+  <dimension ref="A1:DL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -39958,6 +40297,7 @@
     <col width="10" customWidth="1" min="113" max="113"/>
     <col width="10" customWidth="1" min="114" max="114"/>
     <col width="10" customWidth="1" min="115" max="115"/>
+    <col width="10" customWidth="1" min="116" max="116"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -40310,6 +40650,9 @@
       <c r="DK1" s="1" t="n">
         <v>20260310</v>
       </c>
+      <c r="DL1" s="1" t="n">
+        <v>20260311</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -40661,6 +41004,9 @@
       <c r="DK2" t="n">
         <v>18</v>
       </c>
+      <c r="DL2" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -41012,6 +41358,9 @@
       <c r="DK3" t="n">
         <v>83</v>
       </c>
+      <c r="DL3" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -41363,6 +41712,9 @@
       <c r="DK4" t="n">
         <v>31</v>
       </c>
+      <c r="DL4" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -41714,6 +42066,9 @@
       <c r="DK5" t="n">
         <v>86</v>
       </c>
+      <c r="DL5" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -42065,6 +42420,9 @@
       <c r="DK6" t="n">
         <v>97</v>
       </c>
+      <c r="DL6" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -42416,6 +42774,9 @@
       <c r="DK7" t="n">
         <v>30</v>
       </c>
+      <c r="DL7" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -42767,6 +43128,9 @@
       <c r="DK8" t="n">
         <v>97</v>
       </c>
+      <c r="DL8" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -43118,6 +43482,9 @@
       <c r="DK9" t="n">
         <v>100</v>
       </c>
+      <c r="DL9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -43468,6 +43835,9 @@
       </c>
       <c r="DK10" t="n">
         <v>17</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -43481,7 +43851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW10"/>
+  <dimension ref="A1:BX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -43559,6 +43929,7 @@
     <col width="10" customWidth="1" min="73" max="73"/>
     <col width="10" customWidth="1" min="74" max="74"/>
     <col width="10" customWidth="1" min="75" max="75"/>
+    <col width="10" customWidth="1" min="76" max="76"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -43791,6 +44162,9 @@
       <c r="BW1" s="1" t="n">
         <v>20260310</v>
       </c>
+      <c r="BX1" s="1" t="n">
+        <v>20260311</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -44022,6 +44396,9 @@
       <c r="BW2" t="n">
         <v>41</v>
       </c>
+      <c r="BX2" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -44253,6 +44630,9 @@
       <c r="BW3" t="n">
         <v>30</v>
       </c>
+      <c r="BX3" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -44484,6 +44864,9 @@
       <c r="BW4" t="n">
         <v>22</v>
       </c>
+      <c r="BX4" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -44715,6 +45098,9 @@
       <c r="BW5" t="n">
         <v>24</v>
       </c>
+      <c r="BX5" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -44946,6 +45332,9 @@
       <c r="BW6" t="n">
         <v>97</v>
       </c>
+      <c r="BX6" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -45177,6 +45566,9 @@
       <c r="BW7" t="n">
         <v>48</v>
       </c>
+      <c r="BX7" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -45408,6 +45800,9 @@
       <c r="BW8" t="n">
         <v>42</v>
       </c>
+      <c r="BX8" t="n">
+        <v>34</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -45639,6 +46034,9 @@
       <c r="BW9" t="n">
         <v>100</v>
       </c>
+      <c r="BX9" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -45869,6 +46267,9 @@
       </c>
       <c r="BW10" t="n">
         <v>6</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -45882,7 +46283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DK10"/>
+  <dimension ref="A1:DL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -46000,6 +46401,7 @@
     <col width="10" customWidth="1" min="113" max="113"/>
     <col width="10" customWidth="1" min="114" max="114"/>
     <col width="10" customWidth="1" min="115" max="115"/>
+    <col width="10" customWidth="1" min="116" max="116"/>
   </cols>
   <sheetData>
     <ro